--- a/ArmCoreV1_QSPI/SSCProject/lan9252_app.xlsx
+++ b/ArmCoreV1_QSPI/SSCProject/lan9252_app.xlsx
@@ -5,14 +5,14 @@
   <workbookPr/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="22192" windowHeight="10455"/>
   </bookViews>
   <sheets>
     <sheet name="Profile" sheetId="11" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Profile!$B$10:$P$61</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Profile!$B$1:$P$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Profile!$B$10:$P$75</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Profile!$B$1:$P$76</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="84">
   <si>
     <t>Device Profile:</t>
   </si>
@@ -305,46 +305,70 @@
     <t>InputData</t>
   </si>
   <si>
-    <t>USINT</t>
-  </si>
-  <si>
-    <t>InU8_Test1</t>
-  </si>
-  <si>
-    <t>BOOL</t>
-  </si>
-  <si>
-    <t>InB1_Test2</t>
-  </si>
-  <si>
-    <t>BIT7</t>
-  </si>
-  <si>
-    <t>InB7_Test3</t>
-  </si>
-  <si>
     <t>UINT</t>
   </si>
   <si>
-    <t>InU16_Test4</t>
-  </si>
-  <si>
-    <t>REAL</t>
-  </si>
-  <si>
-    <t>InF_Test5</t>
-  </si>
-  <si>
-    <t>UDINT</t>
-  </si>
-  <si>
-    <t>InU32_Test6</t>
-  </si>
-  <si>
-    <t>LREAL</t>
-  </si>
-  <si>
-    <t>InD_Test7</t>
+    <t>InU16_CrtFsmState</t>
+  </si>
+  <si>
+    <t>InU16_BeamIndexFB</t>
+  </si>
+  <si>
+    <t>InU16_BankIndexFB</t>
+  </si>
+  <si>
+    <t>InU16_RidiationIndexFB</t>
+  </si>
+  <si>
+    <t>InU16_LeafCrtControlMode</t>
+  </si>
+  <si>
+    <t>InU16_CarCrtControlMode</t>
+  </si>
+  <si>
+    <t>InU16_JawYCrtControlMode</t>
+  </si>
+  <si>
+    <t>InU16_JawXCrtControlMode</t>
+  </si>
+  <si>
+    <t>InU16_PlanCmdFB</t>
+  </si>
+  <si>
+    <t>InU16_FaultInfo1</t>
+  </si>
+  <si>
+    <t>InU16_FaultInfo2</t>
+  </si>
+  <si>
+    <t>InU16_FaultCode</t>
+  </si>
+  <si>
+    <t>ARRAY [0..3] OF UINT</t>
+  </si>
+  <si>
+    <t>InAU16_Reserve1</t>
+  </si>
+  <si>
+    <t>ARRAY [0..81] OF UINT</t>
+  </si>
+  <si>
+    <t>InAU16_LeafCrtPos</t>
+  </si>
+  <si>
+    <t>InU16_CarCrtPos</t>
+  </si>
+  <si>
+    <t>ARRAY [0..1] OF UINT</t>
+  </si>
+  <si>
+    <t>InAU16_JawCrtPos</t>
+  </si>
+  <si>
+    <t>InU16_JawInfo</t>
+  </si>
+  <si>
+    <t>InAU16_Reserve2</t>
   </si>
   <si>
     <t>//0x7nnx</t>
@@ -359,25 +383,34 @@
     <t>OutputData</t>
   </si>
   <si>
-    <t>OutU8_Test1</t>
-  </si>
-  <si>
-    <t>OutB1_Test2</t>
-  </si>
-  <si>
-    <t>OutB7_Test3</t>
-  </si>
-  <si>
-    <t>OutU16_Test4</t>
-  </si>
-  <si>
-    <t>OutF_Test5</t>
-  </si>
-  <si>
-    <t>OutU32_Test6</t>
-  </si>
-  <si>
-    <t>OutD_Test7</t>
+    <t>OutU16_FsmStateSetting</t>
+  </si>
+  <si>
+    <t>OutU16_BeamIndex</t>
+  </si>
+  <si>
+    <t>OutU16_BankIndex</t>
+  </si>
+  <si>
+    <t>OutU16_RidiationIndex</t>
+  </si>
+  <si>
+    <t>OutU16_LeafControlModeSetting</t>
+  </si>
+  <si>
+    <t>OutU16_CarControlModeSetting</t>
+  </si>
+  <si>
+    <t>OutU16_JawYControlModeSetting</t>
+  </si>
+  <si>
+    <t>OutU16_JawXControlModeSetting</t>
+  </si>
+  <si>
+    <t>OutU16_PlanCmd</t>
+  </si>
+  <si>
+    <t>OutU16_Reserve</t>
   </si>
   <si>
     <t>//0x8nnx</t>
@@ -1092,14 +1125,14 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1450,13 +1483,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T912"/>
+  <dimension ref="A1:T926"/>
   <sheetFormatPr defaultColWidth="10.7079646017699" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="3.85840707964602" style="2" customWidth="1"/>
     <col min="2" max="2" width="20.283185840708" style="2" customWidth="1"/>
     <col min="3" max="4" width="14.7079646017699" style="2" customWidth="1"/>
-    <col min="5" max="5" width="22.1858407079646" style="2" customWidth="1"/>
+    <col min="5" max="5" width="24.0973451327434" style="2" customWidth="1"/>
     <col min="6" max="6" width="40.7079646017699" style="2" customWidth="1"/>
     <col min="7" max="7" width="11.7079646017699" style="2" customWidth="1"/>
     <col min="8" max="9" width="7.70796460176991" style="2" customWidth="1"/>
@@ -1495,10 +1528,10 @@
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="21"/>
-      <c r="S1" s="21"/>
-      <c r="T1" s="21"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
     </row>
     <row r="2" spans="1:20">
       <c r="A2" s="3"/>
@@ -1521,10 +1554,10 @@
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="21"/>
-      <c r="S2" s="21"/>
-      <c r="T2" s="21"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="3"/>
@@ -1543,10 +1576,10 @@
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
-      <c r="Q3" s="21"/>
-      <c r="R3" s="21"/>
-      <c r="S3" s="21"/>
-      <c r="T3" s="21"/>
+      <c r="Q3" s="20"/>
+      <c r="R3" s="20"/>
+      <c r="S3" s="20"/>
+      <c r="T3" s="20"/>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="3"/>
@@ -1565,10 +1598,10 @@
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
-      <c r="Q4" s="21"/>
-      <c r="R4" s="21"/>
-      <c r="S4" s="21"/>
-      <c r="T4" s="21"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="20"/>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="3"/>
@@ -1587,10 +1620,10 @@
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="21"/>
-      <c r="S5" s="21"/>
-      <c r="T5" s="21"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="20"/>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="3"/>
@@ -1609,10 +1642,10 @@
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
-      <c r="Q6" s="21"/>
-      <c r="R6" s="21"/>
-      <c r="S6" s="21"/>
-      <c r="T6" s="21"/>
+      <c r="Q6" s="20"/>
+      <c r="R6" s="20"/>
+      <c r="S6" s="20"/>
+      <c r="T6" s="20"/>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="3"/>
@@ -1631,10 +1664,10 @@
       <c r="N7" s="9"/>
       <c r="O7" s="9"/>
       <c r="P7" s="9"/>
-      <c r="Q7" s="21"/>
-      <c r="R7" s="21"/>
-      <c r="S7" s="21"/>
-      <c r="T7" s="21"/>
+      <c r="Q7" s="20"/>
+      <c r="R7" s="20"/>
+      <c r="S7" s="20"/>
+      <c r="T7" s="20"/>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="3"/>
@@ -1712,10 +1745,10 @@
       <c r="M10" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="N10" s="20" t="s">
+      <c r="N10" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="O10" s="20" t="s">
+      <c r="O10" s="19" t="s">
         <v>19</v>
       </c>
       <c r="P10" s="11" t="s">
@@ -2264,10 +2297,10 @@
         <v>2</v>
       </c>
       <c r="E38" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F38" s="12" t="s">
         <v>44</v>
-      </c>
-      <c r="F38" s="12" t="s">
-        <v>45</v>
       </c>
       <c r="G38" s="12"/>
       <c r="H38" s="12"/>
@@ -2288,10 +2321,10 @@
         <v>3</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G39" s="12"/>
       <c r="H39" s="12"/>
@@ -2314,10 +2347,10 @@
         <v>4</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G40" s="12"/>
       <c r="H40" s="12"/>
@@ -2338,10 +2371,10 @@
         <v>5</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G41" s="12"/>
       <c r="H41" s="12"/>
@@ -2362,10 +2395,10 @@
         <v>6</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G42" s="12"/>
       <c r="H42" s="12"/>
@@ -2386,10 +2419,10 @@
         <v>7</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G43" s="12"/>
       <c r="H43" s="12"/>
@@ -2402,40 +2435,42 @@
       <c r="O43" s="3"/>
       <c r="P43" s="12"/>
     </row>
-    <row r="44" s="1" customFormat="1" spans="1:16">
-      <c r="A44" s="12"/>
-      <c r="B44" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="C44" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="D44" s="18"/>
-      <c r="E44" s="18"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="18"/>
-      <c r="H44" s="18"/>
-      <c r="I44" s="18"/>
-      <c r="J44" s="18"/>
-      <c r="K44" s="18"/>
-      <c r="L44" s="18"/>
-      <c r="M44" s="18"/>
-      <c r="N44" s="18"/>
-      <c r="O44" s="18"/>
-      <c r="P44" s="18"/>
-    </row>
-    <row r="45" spans="1:16">
+    <row r="44" customFormat="1" spans="1:16">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="17">
+        <v>8</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F44" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G44" s="12"/>
+      <c r="H44" s="12"/>
+      <c r="I44" s="12"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3"/>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3"/>
+      <c r="O44" s="3"/>
+      <c r="P44" s="12"/>
+    </row>
+    <row r="45" customFormat="1" spans="1:16">
       <c r="A45" s="3"/>
-      <c r="B45" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D45" s="17"/>
-      <c r="E45" s="12"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="17">
+        <v>9</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>42</v>
+      </c>
       <c r="F45" s="12" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="G45" s="12"/>
       <c r="H45" s="12"/>
@@ -2453,13 +2488,13 @@
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
       <c r="D46" s="17">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E46" s="12" t="s">
         <v>42</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G46" s="12"/>
       <c r="H46" s="12"/>
@@ -2477,13 +2512,13 @@
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
       <c r="D47" s="17">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="G47" s="12"/>
       <c r="H47" s="12"/>
@@ -2501,13 +2536,13 @@
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
       <c r="D48" s="17">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="G48" s="12"/>
       <c r="H48" s="12"/>
@@ -2525,13 +2560,13 @@
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
       <c r="D49" s="17">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="G49" s="12"/>
       <c r="H49" s="12"/>
@@ -2549,13 +2584,13 @@
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
       <c r="D50" s="17">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G50" s="12"/>
       <c r="H50" s="12"/>
@@ -2573,13 +2608,13 @@
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
       <c r="D51" s="17">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G51" s="12"/>
       <c r="H51" s="12"/>
@@ -2597,13 +2632,13 @@
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
       <c r="D52" s="17">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G52" s="12"/>
       <c r="H52" s="12"/>
@@ -2616,35 +2651,43 @@
       <c r="O52" s="3"/>
       <c r="P52" s="12"/>
     </row>
-    <row r="53" s="1" customFormat="1" spans="1:16">
-      <c r="A53" s="12"/>
-      <c r="B53" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="C53" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="D53" s="18"/>
-      <c r="E53" s="18"/>
-      <c r="F53" s="19"/>
-      <c r="G53" s="18"/>
-      <c r="H53" s="18"/>
-      <c r="I53" s="18"/>
-      <c r="J53" s="18"/>
-      <c r="K53" s="18"/>
-      <c r="L53" s="18"/>
-      <c r="M53" s="18"/>
-      <c r="N53" s="18"/>
-      <c r="O53" s="18"/>
-      <c r="P53" s="18"/>
-    </row>
-    <row r="54" spans="1:16">
+    <row r="53" customFormat="1" spans="1:16">
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="17">
+        <v>17</v>
+      </c>
+      <c r="E53" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F53" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G53" s="12"/>
+      <c r="H53" s="12"/>
+      <c r="I53" s="12"/>
+      <c r="J53" s="3"/>
+      <c r="K53" s="3"/>
+      <c r="L53" s="3"/>
+      <c r="M53" s="3"/>
+      <c r="N53" s="3"/>
+      <c r="O53" s="3"/>
+      <c r="P53" s="12"/>
+    </row>
+    <row r="54" customFormat="1" spans="1:16">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
-      <c r="D54" s="17"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
+      <c r="D54" s="17">
+        <v>18</v>
+      </c>
+      <c r="E54" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F54" s="12" t="s">
+        <v>63</v>
+      </c>
       <c r="G54" s="12"/>
       <c r="H54" s="12"/>
       <c r="I54" s="12"/>
@@ -2656,53 +2699,65 @@
       <c r="O54" s="3"/>
       <c r="P54" s="12"/>
     </row>
-    <row r="55" spans="1:16">
-      <c r="A55" s="3"/>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="17"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="3"/>
-      <c r="K55" s="3"/>
-      <c r="L55" s="3"/>
-      <c r="M55" s="3"/>
-      <c r="N55" s="3"/>
-      <c r="O55" s="3"/>
-      <c r="P55" s="12"/>
-    </row>
-    <row r="56" s="1" customFormat="1" spans="1:16">
-      <c r="A56" s="12"/>
-      <c r="B56" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="C56" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="D56" s="18"/>
-      <c r="E56" s="18"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="18"/>
-      <c r="H56" s="18"/>
-      <c r="I56" s="18"/>
-      <c r="J56" s="18"/>
-      <c r="K56" s="18"/>
-      <c r="L56" s="18"/>
-      <c r="M56" s="18"/>
-      <c r="N56" s="18"/>
-      <c r="O56" s="18"/>
-      <c r="P56" s="18"/>
-    </row>
-    <row r="57" spans="1:16">
+    <row r="55" s="1" customFormat="1" spans="1:16">
+      <c r="A55" s="12"/>
+      <c r="B55" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="C55" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="18"/>
+      <c r="H55" s="18"/>
+      <c r="I55" s="18"/>
+      <c r="J55" s="18"/>
+      <c r="K55" s="18"/>
+      <c r="L55" s="18"/>
+      <c r="M55" s="18"/>
+      <c r="N55" s="18"/>
+      <c r="O55" s="18"/>
+      <c r="P55" s="18"/>
+    </row>
+    <row r="56" spans="1:16">
+      <c r="A56" s="3"/>
+      <c r="B56" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D56" s="17"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="G56" s="12"/>
+      <c r="H56" s="12"/>
+      <c r="I56" s="12"/>
+      <c r="J56" s="3"/>
+      <c r="K56" s="3"/>
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+      <c r="P56" s="12"/>
+    </row>
+    <row r="57" customFormat="1" spans="1:16">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
-      <c r="D57" s="17"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
+      <c r="D57" s="17">
+        <v>1</v>
+      </c>
+      <c r="E57" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F57" s="12" t="s">
+        <v>68</v>
+      </c>
       <c r="G57" s="12"/>
       <c r="H57" s="12"/>
       <c r="I57" s="12"/>
@@ -2714,13 +2769,19 @@
       <c r="O57" s="3"/>
       <c r="P57" s="12"/>
     </row>
-    <row r="58" spans="1:16">
+    <row r="58" customFormat="1" spans="1:16">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
-      <c r="D58" s="17"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
+      <c r="D58" s="17">
+        <v>2</v>
+      </c>
+      <c r="E58" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F58" s="12" t="s">
+        <v>69</v>
+      </c>
       <c r="G58" s="12"/>
       <c r="H58" s="12"/>
       <c r="I58" s="12"/>
@@ -2732,35 +2793,43 @@
       <c r="O58" s="3"/>
       <c r="P58" s="12"/>
     </row>
-    <row r="59" s="1" customFormat="1" spans="1:16">
-      <c r="A59" s="12"/>
-      <c r="B59" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="C59" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="D59" s="18"/>
-      <c r="E59" s="18"/>
-      <c r="F59" s="18"/>
-      <c r="G59" s="18"/>
-      <c r="H59" s="18"/>
-      <c r="I59" s="18"/>
-      <c r="J59" s="18"/>
-      <c r="K59" s="18"/>
-      <c r="L59" s="18"/>
-      <c r="M59" s="18"/>
-      <c r="N59" s="18"/>
-      <c r="O59" s="18"/>
-      <c r="P59" s="18"/>
-    </row>
-    <row r="60" spans="1:16">
+    <row r="59" customFormat="1" spans="1:16">
+      <c r="A59" s="3"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="17">
+        <v>3</v>
+      </c>
+      <c r="E59" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F59" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G59" s="12"/>
+      <c r="H59" s="12"/>
+      <c r="I59" s="12"/>
+      <c r="J59" s="3"/>
+      <c r="K59" s="3"/>
+      <c r="L59" s="3"/>
+      <c r="M59" s="3"/>
+      <c r="N59" s="3"/>
+      <c r="O59" s="3"/>
+      <c r="P59" s="12"/>
+    </row>
+    <row r="60" customFormat="1" spans="1:16">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
-      <c r="D60" s="17"/>
-      <c r="E60" s="12"/>
-      <c r="F60" s="12"/>
+      <c r="D60" s="17">
+        <v>4</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F60" s="12" t="s">
+        <v>71</v>
+      </c>
       <c r="G60" s="12"/>
       <c r="H60" s="12"/>
       <c r="I60" s="12"/>
@@ -2772,13 +2841,19 @@
       <c r="O60" s="3"/>
       <c r="P60" s="12"/>
     </row>
-    <row r="61" spans="1:16">
+    <row r="61" customFormat="1" spans="1:16">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
-      <c r="D61" s="17"/>
-      <c r="E61" s="12"/>
-      <c r="F61" s="12"/>
+      <c r="D61" s="17">
+        <v>5</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F61" s="12" t="s">
+        <v>72</v>
+      </c>
       <c r="G61" s="12"/>
       <c r="H61" s="12"/>
       <c r="I61" s="12"/>
@@ -2790,269 +2865,521 @@
       <c r="O61" s="3"/>
       <c r="P61" s="12"/>
     </row>
-    <row r="62" spans="1:16">
+    <row r="62" customFormat="1" spans="1:16">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
-      <c r="F62" s="18"/>
-      <c r="G62" s="3"/>
-      <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
+      <c r="D62" s="17">
+        <v>6</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F62" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="G62" s="12"/>
+      <c r="H62" s="12"/>
+      <c r="I62" s="12"/>
       <c r="J62" s="3"/>
       <c r="K62" s="3"/>
       <c r="L62" s="3"/>
       <c r="M62" s="3"/>
       <c r="N62" s="3"/>
       <c r="O62" s="3"/>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="1:16">
+      <c r="P62" s="12"/>
+    </row>
+    <row r="63" customFormat="1" spans="1:16">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
-      <c r="D63" s="3"/>
-      <c r="E63" s="3"/>
-      <c r="F63" s="12"/>
-      <c r="G63" s="3"/>
-      <c r="H63" s="3"/>
-      <c r="I63" s="3"/>
+      <c r="D63" s="17">
+        <v>7</v>
+      </c>
+      <c r="E63" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F63" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="G63" s="12"/>
+      <c r="H63" s="12"/>
+      <c r="I63" s="12"/>
       <c r="J63" s="3"/>
       <c r="K63" s="3"/>
       <c r="L63" s="3"/>
       <c r="M63" s="3"/>
       <c r="N63" s="3"/>
       <c r="O63" s="3"/>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="1:16">
+      <c r="P63" s="12"/>
+    </row>
+    <row r="64" customFormat="1" spans="1:16">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
-      <c r="E64" s="3"/>
-      <c r="F64" s="12"/>
-      <c r="G64" s="3"/>
-      <c r="H64" s="3"/>
-      <c r="I64" s="3"/>
+      <c r="D64" s="17">
+        <v>8</v>
+      </c>
+      <c r="E64" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F64" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="G64" s="12"/>
+      <c r="H64" s="12"/>
+      <c r="I64" s="12"/>
       <c r="J64" s="3"/>
       <c r="K64" s="3"/>
       <c r="L64" s="3"/>
       <c r="M64" s="3"/>
       <c r="N64" s="3"/>
       <c r="O64" s="3"/>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="1:16">
+      <c r="P64" s="12"/>
+    </row>
+    <row r="65" customFormat="1" spans="1:16">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="18"/>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
+      <c r="D65" s="17">
+        <v>9</v>
+      </c>
+      <c r="E65" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F65" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="G65" s="12"/>
+      <c r="H65" s="12"/>
+      <c r="I65" s="12"/>
       <c r="J65" s="3"/>
       <c r="K65" s="3"/>
       <c r="L65" s="3"/>
       <c r="M65" s="3"/>
       <c r="N65" s="3"/>
       <c r="O65" s="3"/>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="1:16">
+      <c r="P65" s="12"/>
+    </row>
+    <row r="66" customFormat="1" spans="1:16">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
-      <c r="D66" s="3"/>
-      <c r="E66" s="3"/>
-      <c r="F66" s="12"/>
-      <c r="G66" s="3"/>
-      <c r="H66" s="3"/>
-      <c r="I66" s="3"/>
+      <c r="D66" s="17">
+        <v>10</v>
+      </c>
+      <c r="E66" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F66" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="G66" s="12"/>
+      <c r="H66" s="12"/>
+      <c r="I66" s="12"/>
       <c r="J66" s="3"/>
       <c r="K66" s="3"/>
       <c r="L66" s="3"/>
       <c r="M66" s="3"/>
       <c r="N66" s="3"/>
       <c r="O66" s="3"/>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="1:16">
-      <c r="A67" s="3"/>
-      <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
-      <c r="F67" s="12"/>
-      <c r="G67" s="3"/>
-      <c r="H67" s="3"/>
-      <c r="I67" s="3"/>
-      <c r="J67" s="3"/>
-      <c r="K67" s="3"/>
-      <c r="L67" s="3"/>
-      <c r="M67" s="3"/>
-      <c r="N67" s="3"/>
-      <c r="O67" s="3"/>
-      <c r="P67" s="3"/>
+      <c r="P66" s="12"/>
+    </row>
+    <row r="67" s="1" customFormat="1" spans="1:16">
+      <c r="A67" s="12"/>
+      <c r="B67" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C67" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="D67" s="18"/>
+      <c r="E67" s="18"/>
+      <c r="F67" s="21"/>
+      <c r="G67" s="18"/>
+      <c r="H67" s="18"/>
+      <c r="I67" s="18"/>
+      <c r="J67" s="18"/>
+      <c r="K67" s="18"/>
+      <c r="L67" s="18"/>
+      <c r="M67" s="18"/>
+      <c r="N67" s="18"/>
+      <c r="O67" s="18"/>
+      <c r="P67" s="18"/>
     </row>
     <row r="68" spans="1:16">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
-      <c r="I68" s="3"/>
+      <c r="D68" s="17"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12"/>
+      <c r="H68" s="12"/>
+      <c r="I68" s="12"/>
       <c r="J68" s="3"/>
       <c r="K68" s="3"/>
       <c r="L68" s="3"/>
       <c r="M68" s="3"/>
       <c r="N68" s="3"/>
       <c r="O68" s="3"/>
-      <c r="P68" s="3"/>
+      <c r="P68" s="12"/>
     </row>
     <row r="69" spans="1:16">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
-      <c r="I69" s="3"/>
+      <c r="D69" s="17"/>
+      <c r="E69" s="12"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="12"/>
+      <c r="H69" s="12"/>
+      <c r="I69" s="12"/>
       <c r="J69" s="3"/>
       <c r="K69" s="3"/>
       <c r="L69" s="3"/>
       <c r="M69" s="3"/>
       <c r="N69" s="3"/>
       <c r="O69" s="3"/>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="1:16">
-      <c r="A70" s="3"/>
-      <c r="B70" s="3"/>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3"/>
-      <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
-      <c r="G70" s="3"/>
-      <c r="H70" s="3"/>
-      <c r="I70" s="3"/>
-      <c r="J70" s="3"/>
-      <c r="K70" s="3"/>
-      <c r="L70" s="3"/>
-      <c r="M70" s="3"/>
-      <c r="N70" s="3"/>
-      <c r="O70" s="3"/>
-      <c r="P70" s="3"/>
+      <c r="P69" s="12"/>
+    </row>
+    <row r="70" s="1" customFormat="1" spans="1:16">
+      <c r="A70" s="12"/>
+      <c r="B70" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C70" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D70" s="18"/>
+      <c r="E70" s="18"/>
+      <c r="F70" s="12"/>
+      <c r="G70" s="18"/>
+      <c r="H70" s="18"/>
+      <c r="I70" s="18"/>
+      <c r="J70" s="18"/>
+      <c r="K70" s="18"/>
+      <c r="L70" s="18"/>
+      <c r="M70" s="18"/>
+      <c r="N70" s="18"/>
+      <c r="O70" s="18"/>
+      <c r="P70" s="18"/>
     </row>
     <row r="71" spans="1:16">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
-      <c r="D71" s="3"/>
-      <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
-      <c r="G71" s="3"/>
-      <c r="H71" s="3"/>
-      <c r="I71" s="3"/>
+      <c r="D71" s="17"/>
+      <c r="E71" s="12"/>
+      <c r="F71" s="12"/>
+      <c r="G71" s="12"/>
+      <c r="H71" s="12"/>
+      <c r="I71" s="12"/>
       <c r="J71" s="3"/>
       <c r="K71" s="3"/>
       <c r="L71" s="3"/>
       <c r="M71" s="3"/>
       <c r="N71" s="3"/>
       <c r="O71" s="3"/>
-      <c r="P71" s="3"/>
+      <c r="P71" s="12"/>
     </row>
     <row r="72" spans="1:16">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
-      <c r="D72" s="3"/>
-      <c r="E72" s="3"/>
-      <c r="F72" s="3"/>
-      <c r="G72" s="3"/>
-      <c r="H72" s="3"/>
-      <c r="I72" s="3"/>
+      <c r="D72" s="17"/>
+      <c r="E72" s="12"/>
+      <c r="F72" s="12"/>
+      <c r="G72" s="12"/>
+      <c r="H72" s="12"/>
+      <c r="I72" s="12"/>
       <c r="J72" s="3"/>
       <c r="K72" s="3"/>
       <c r="L72" s="3"/>
       <c r="M72" s="3"/>
       <c r="N72" s="3"/>
       <c r="O72" s="3"/>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="3:6">
-      <c r="C73" s="3"/>
-      <c r="F73" s="3"/>
-    </row>
-    <row r="74" spans="3:6">
+      <c r="P72" s="12"/>
+    </row>
+    <row r="73" s="1" customFormat="1" spans="1:16">
+      <c r="A73" s="12"/>
+      <c r="B73" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="C73" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D73" s="18"/>
+      <c r="E73" s="18"/>
+      <c r="F73" s="18"/>
+      <c r="G73" s="18"/>
+      <c r="H73" s="18"/>
+      <c r="I73" s="18"/>
+      <c r="J73" s="18"/>
+      <c r="K73" s="18"/>
+      <c r="L73" s="18"/>
+      <c r="M73" s="18"/>
+      <c r="N73" s="18"/>
+      <c r="O73" s="18"/>
+      <c r="P73" s="18"/>
+    </row>
+    <row r="74" spans="1:16">
+      <c r="A74" s="3"/>
+      <c r="B74" s="3"/>
       <c r="C74" s="3"/>
-      <c r="F74" s="3"/>
-    </row>
-    <row r="75" spans="3:6">
+      <c r="D74" s="17"/>
+      <c r="E74" s="12"/>
+      <c r="F74" s="12"/>
+      <c r="G74" s="12"/>
+      <c r="H74" s="12"/>
+      <c r="I74" s="12"/>
+      <c r="J74" s="3"/>
+      <c r="K74" s="3"/>
+      <c r="L74" s="3"/>
+      <c r="M74" s="3"/>
+      <c r="N74" s="3"/>
+      <c r="O74" s="3"/>
+      <c r="P74" s="12"/>
+    </row>
+    <row r="75" spans="1:16">
+      <c r="A75" s="3"/>
+      <c r="B75" s="3"/>
       <c r="C75" s="3"/>
-      <c r="F75" s="3"/>
-    </row>
-    <row r="76" spans="3:6">
+      <c r="D75" s="17"/>
+      <c r="E75" s="12"/>
+      <c r="F75" s="12"/>
+      <c r="G75" s="12"/>
+      <c r="H75" s="12"/>
+      <c r="I75" s="12"/>
+      <c r="J75" s="3"/>
+      <c r="K75" s="3"/>
+      <c r="L75" s="3"/>
+      <c r="M75" s="3"/>
+      <c r="N75" s="3"/>
+      <c r="O75" s="3"/>
+      <c r="P75" s="12"/>
+    </row>
+    <row r="76" spans="1:16">
+      <c r="A76" s="3"/>
+      <c r="B76" s="3"/>
       <c r="C76" s="3"/>
-      <c r="F76" s="3"/>
-    </row>
-    <row r="77" spans="3:6">
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="18"/>
+      <c r="G76" s="3"/>
+      <c r="H76" s="3"/>
+      <c r="I76" s="3"/>
+      <c r="J76" s="3"/>
+      <c r="K76" s="3"/>
+      <c r="L76" s="3"/>
+      <c r="M76" s="3"/>
+      <c r="N76" s="3"/>
+      <c r="O76" s="3"/>
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="1:16">
+      <c r="A77" s="3"/>
+      <c r="B77" s="3"/>
       <c r="C77" s="3"/>
-      <c r="F77" s="3"/>
-    </row>
-    <row r="78" spans="3:6">
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="12"/>
+      <c r="G77" s="3"/>
+      <c r="H77" s="3"/>
+      <c r="I77" s="3"/>
+      <c r="J77" s="3"/>
+      <c r="K77" s="3"/>
+      <c r="L77" s="3"/>
+      <c r="M77" s="3"/>
+      <c r="N77" s="3"/>
+      <c r="O77" s="3"/>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="78" spans="1:16">
+      <c r="A78" s="3"/>
+      <c r="B78" s="3"/>
       <c r="C78" s="3"/>
-      <c r="F78" s="3"/>
-    </row>
-    <row r="79" spans="3:3">
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="12"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3"/>
+      <c r="I78" s="3"/>
+      <c r="J78" s="3"/>
+      <c r="K78" s="3"/>
+      <c r="L78" s="3"/>
+      <c r="M78" s="3"/>
+      <c r="N78" s="3"/>
+      <c r="O78" s="3"/>
+      <c r="P78" s="3"/>
+    </row>
+    <row r="79" spans="1:16">
+      <c r="A79" s="3"/>
+      <c r="B79" s="3"/>
       <c r="C79" s="3"/>
-    </row>
-    <row r="80" spans="3:3">
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="18"/>
+      <c r="G79" s="3"/>
+      <c r="H79" s="3"/>
+      <c r="I79" s="3"/>
+      <c r="J79" s="3"/>
+      <c r="K79" s="3"/>
+      <c r="L79" s="3"/>
+      <c r="M79" s="3"/>
+      <c r="N79" s="3"/>
+      <c r="O79" s="3"/>
+      <c r="P79" s="3"/>
+    </row>
+    <row r="80" spans="1:16">
+      <c r="A80" s="3"/>
+      <c r="B80" s="3"/>
       <c r="C80" s="3"/>
-    </row>
-    <row r="81" spans="3:3">
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="12"/>
+      <c r="G80" s="3"/>
+      <c r="H80" s="3"/>
+      <c r="I80" s="3"/>
+      <c r="J80" s="3"/>
+      <c r="K80" s="3"/>
+      <c r="L80" s="3"/>
+      <c r="M80" s="3"/>
+      <c r="N80" s="3"/>
+      <c r="O80" s="3"/>
+      <c r="P80" s="3"/>
+    </row>
+    <row r="81" spans="1:16">
+      <c r="A81" s="3"/>
+      <c r="B81" s="3"/>
       <c r="C81" s="3"/>
-    </row>
-    <row r="82" spans="3:3">
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="12"/>
+      <c r="G81" s="3"/>
+      <c r="H81" s="3"/>
+      <c r="I81" s="3"/>
+      <c r="J81" s="3"/>
+      <c r="K81" s="3"/>
+      <c r="L81" s="3"/>
+      <c r="M81" s="3"/>
+      <c r="N81" s="3"/>
+      <c r="O81" s="3"/>
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="1:16">
+      <c r="A82" s="3"/>
+      <c r="B82" s="3"/>
       <c r="C82" s="3"/>
-    </row>
-    <row r="83" spans="3:3">
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3"/>
+      <c r="H82" s="3"/>
+      <c r="I82" s="3"/>
+      <c r="J82" s="3"/>
+      <c r="K82" s="3"/>
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="1:16">
+      <c r="A83" s="3"/>
+      <c r="B83" s="3"/>
       <c r="C83" s="3"/>
-    </row>
-    <row r="84" spans="3:3">
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3"/>
+      <c r="H83" s="3"/>
+      <c r="I83" s="3"/>
+      <c r="J83" s="3"/>
+      <c r="K83" s="3"/>
+      <c r="L83" s="3"/>
+      <c r="M83" s="3"/>
+      <c r="N83" s="3"/>
+      <c r="O83" s="3"/>
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="1:16">
+      <c r="A84" s="3"/>
+      <c r="B84" s="3"/>
       <c r="C84" s="3"/>
-    </row>
-    <row r="85" spans="3:3">
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
+      <c r="H84" s="3"/>
+      <c r="I84" s="3"/>
+      <c r="J84" s="3"/>
+      <c r="K84" s="3"/>
+      <c r="L84" s="3"/>
+      <c r="M84" s="3"/>
+      <c r="N84" s="3"/>
+      <c r="O84" s="3"/>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="1:16">
+      <c r="A85" s="3"/>
+      <c r="B85" s="3"/>
       <c r="C85" s="3"/>
-    </row>
-    <row r="86" spans="3:3">
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3"/>
+      <c r="H85" s="3"/>
+      <c r="I85" s="3"/>
+      <c r="J85" s="3"/>
+      <c r="K85" s="3"/>
+      <c r="L85" s="3"/>
+      <c r="M85" s="3"/>
+      <c r="N85" s="3"/>
+      <c r="O85" s="3"/>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="1:16">
+      <c r="A86" s="3"/>
+      <c r="B86" s="3"/>
       <c r="C86" s="3"/>
-    </row>
-    <row r="87" spans="3:3">
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
+      <c r="H86" s="3"/>
+      <c r="I86" s="3"/>
+      <c r="J86" s="3"/>
+      <c r="K86" s="3"/>
+      <c r="L86" s="3"/>
+      <c r="M86" s="3"/>
+      <c r="N86" s="3"/>
+      <c r="O86" s="3"/>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:6">
       <c r="C87" s="3"/>
-    </row>
-    <row r="88" spans="3:3">
+      <c r="F87" s="3"/>
+    </row>
+    <row r="88" spans="3:6">
       <c r="C88" s="3"/>
-    </row>
-    <row r="89" spans="3:3">
+      <c r="F88" s="3"/>
+    </row>
+    <row r="89" spans="3:6">
       <c r="C89" s="3"/>
-    </row>
-    <row r="90" spans="3:3">
+      <c r="F89" s="3"/>
+    </row>
+    <row r="90" spans="3:6">
       <c r="C90" s="3"/>
-    </row>
-    <row r="91" spans="3:3">
+      <c r="F90" s="3"/>
+    </row>
+    <row r="91" spans="3:6">
       <c r="C91" s="3"/>
-    </row>
-    <row r="92" spans="3:3">
+      <c r="F91" s="3"/>
+    </row>
+    <row r="92" spans="3:6">
       <c r="C92" s="3"/>
+      <c r="F92" s="3"/>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" s="3"/>
@@ -5514,30 +5841,72 @@
     <row r="912" spans="3:3">
       <c r="C912" s="3"/>
     </row>
+    <row r="913" spans="3:3">
+      <c r="C913" s="3"/>
+    </row>
+    <row r="914" spans="3:3">
+      <c r="C914" s="3"/>
+    </row>
+    <row r="915" spans="3:3">
+      <c r="C915" s="3"/>
+    </row>
+    <row r="916" spans="3:3">
+      <c r="C916" s="3"/>
+    </row>
+    <row r="917" spans="3:3">
+      <c r="C917" s="3"/>
+    </row>
+    <row r="918" spans="3:3">
+      <c r="C918" s="3"/>
+    </row>
+    <row r="919" spans="3:3">
+      <c r="C919" s="3"/>
+    </row>
+    <row r="920" spans="3:3">
+      <c r="C920" s="3"/>
+    </row>
+    <row r="921" spans="3:3">
+      <c r="C921" s="3"/>
+    </row>
+    <row r="922" spans="3:3">
+      <c r="C922" s="3"/>
+    </row>
+    <row r="923" spans="3:3">
+      <c r="C923" s="3"/>
+    </row>
+    <row r="924" spans="3:3">
+      <c r="C924" s="3"/>
+    </row>
+    <row r="925" spans="3:3">
+      <c r="C925" s="3"/>
+    </row>
+    <row r="926" spans="3:3">
+      <c r="C926" s="3"/>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatRows="0" insertRows="0" insertHyperlinks="0" deleteRows="0" sort="0" autoFilter="0"/>
-  <autoFilter ref="B10:P61">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B10:P75" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="F1:P6"/>
   </mergeCells>
   <dataValidations count="6">
-    <dataValidation allowBlank="1" showInputMessage="1" sqref="C11 C14 C17 C20 C23 C26 C29 C32 C35 C44 C53 C56 C59"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Object Code value" error="The Object code value shall be:&#10;VARIABLE&#10;RECORD&#10;ARRAY" sqref="C36 C37 C38 C39 C42 C43 C45 C46 C52 C12:C13 C15:C16 C18:C19 C21:C22 C24:C25 C27:C28 C30:C31 C33:C34 C40:C41 C47:C48 C49:C51 C54:C55 C57:C58 C60:C72">
+    <dataValidation allowBlank="1" showInputMessage="1" sqref="C11 C14 C17 C20 C23 C26 C29 C32 C35 C55 C67 C70 C73"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Object Code value" error="The Object code value shall be:&#10;VARIABLE&#10;RECORD&#10;ARRAY" sqref="C12:C13 C15:C16 C18:C19 C21:C22 C24:C25 C27:C28 C30:C31 C33:C34 C36:C54 C56:C66 C68:C69 C71:C72 C74:C86">
       <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Category" error="The value for the entry category shall be &#10;M : (mandatory)&#10;O : (optional) &#10;C : (conditional)" sqref="J36 J37 J38 J39 J42 J43 J45 J46 J52 J12:J13 J15:J16 J18:J19 J21:J22 J24:J25 J27:J28 J30:J31 J33:J34 J40:J41 J47:J48 J49:J51 J54:J55 J57:J58 J60:J72">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C87:C926">
+      <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Category" error="The value for the entry category shall be &#10;M : (mandatory)&#10;O : (optional) &#10;C : (conditional)" sqref="J12:J13 J15:J16 J18:J19 J21:J22 J24:J25 J27:J28 J30:J31 J33:J34 J36:J54 J56:J66 J68:J69 J71:J72 J74:J86">
       <formula1>"M,O,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Backup/Setting Flag" error="The entry flag shall be&#10;B : (Backup)&#10;S : (Setting)" sqref="K36 K37 K38 K39 K42 K43 K45 K46 K52 K12:K13 K15:K16 K18:K19 K21:K22 K24:K25 K27:K28 K30:K31 K33:K34 K40:K41 K47:K48 K49:K51 K54:K55 K57:K58 K60:K72">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Backup/Setting Flag" error="The entry flag shall be&#10;B : (Backup)&#10;S : (Setting)" sqref="K12:K13 K15:K16 K18:K19 K21:K22 K24:K25 K27:K28 K30:K31 K33:K34 K36:K54 K56:K66 K68:K69 K71:K72 K74:K86">
       <formula1>"B,S"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M36:O36 M37:O37 M38:O38 M39:O39 M42:O42 M43:O43 M45:O45 M46:O46 M52:O52 M12:O13 M18:O19 M24:O25 M30:O31 M40:O41 M54:O55 M60:O61 M15:O16 M21:O22 M27:O28 M33:O34 M47:O48 M57:O58 M49:O51">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M12:O13 M18:O19 M24:O25 M30:O31 M68:O69 M74:O75 M15:O16 M21:O22 M27:O28 M33:O34 M71:O72 M36:O54 M56:O66">
       <formula1>"rx,tx"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C73:C912">
-      <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.236220472440945" right="0.236220472440945" top="0.748031496062992" bottom="0.748031496062992" header="0.31496062992126" footer="0.31496062992126"/>

--- a/ArmCoreV1_QSPI/SSCProject/lan9252_app.xlsx
+++ b/ArmCoreV1_QSPI/SSCProject/lan9252_app.xlsx
@@ -1,20 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WORK\arm_core_develop\bgm_arm_io_develop\FW-ArmCore\ArmCoreV1_QSPI\SSCProject\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <workbookProtection lockStructure="1"/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="17660"/>
   </bookViews>
   <sheets>
     <sheet name="Profile" sheetId="11" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Profile!$B$10:$P$61</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Profile!$B$1:$P$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Profile!$B$10:$P$76</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Profile!$B$1:$P$77</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="96">
   <si>
     <t>Device Profile:</t>
   </si>
@@ -308,107 +313,508 @@
     <t>USINT</t>
   </si>
   <si>
-    <t>InU8_Test1</t>
-  </si>
-  <si>
-    <t>BOOL</t>
-  </si>
-  <si>
-    <t>InB1_Test2</t>
-  </si>
-  <si>
-    <t>BIT7</t>
-  </si>
-  <si>
-    <t>InB7_Test3</t>
-  </si>
-  <si>
     <t>UINT</t>
   </si>
   <si>
-    <t>InU16_Test4</t>
+    <t>//0x7nnx</t>
+  </si>
+  <si>
+    <t>Output Data of the Module (0x7000 - 0x7FFF)</t>
+  </si>
+  <si>
+    <t>0x7010</t>
+  </si>
+  <si>
+    <t>OutputData</t>
+  </si>
+  <si>
+    <t>//0x8nnx</t>
+  </si>
+  <si>
+    <t>Configuration Data of the Module (0x8000 - 0x8FFF)</t>
+  </si>
+  <si>
+    <t>//0x9nnx</t>
+  </si>
+  <si>
+    <t>Information Data of the Module (0x9000 - 0x9FFF)</t>
+  </si>
+  <si>
+    <t>//0xAnnx</t>
+  </si>
+  <si>
+    <t>Diagnosis Data of the Module (0xA000 - 0xAFFF)</t>
+  </si>
+  <si>
+    <r>
+      <t>InU16_Ra</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>diationIndex</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>U</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SINT</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InU8_FsmState</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>U</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nU16_NotReadyEvent</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>U</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DINT</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>In</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>U32_WaringInterlock</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nU32_MinorInterlock</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InU32_SeriousInterlock</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EAL</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nF_PrimaryDoseTotalActual</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nF_SecondaryDoseTotalActual</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nF_PrimaryDoseRateActual</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nF_SecondaryDoseRateActual</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RM IO FSM State</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RM IO Interlock</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InU32_DoseAInterlock</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>InU32_Dose</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Interlock</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>DOSEA</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>DOSEB</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>DOSEB</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>REAL</t>
-  </si>
-  <si>
-    <t>InF_Test5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InU8_DoseAFsmState</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InU8_DoseBFsmState</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>U</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DINT</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EAL</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InF_AfcPositionCurrent</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>OutU8_RequireState</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>O</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>utU8_BeamId</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>InU8_BeamI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>d</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>O</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>utU16_RadiationIndex</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EAL</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>O</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>utF_GantryPosition</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>UDINT</t>
-  </si>
-  <si>
-    <t>InU32_Test6</t>
-  </si>
-  <si>
-    <t>LREAL</t>
-  </si>
-  <si>
-    <t>InD_Test7</t>
-  </si>
-  <si>
-    <t>//0x7nnx</t>
-  </si>
-  <si>
-    <t>Output Data of the Module (0x7000 - 0x7FFF)</t>
-  </si>
-  <si>
-    <t>0x7010</t>
-  </si>
-  <si>
-    <t>OutputData</t>
-  </si>
-  <si>
-    <t>OutU8_Test1</t>
-  </si>
-  <si>
-    <t>OutB1_Test2</t>
-  </si>
-  <si>
-    <t>OutB7_Test3</t>
-  </si>
-  <si>
-    <t>OutU16_Test4</t>
-  </si>
-  <si>
-    <t>OutF_Test5</t>
-  </si>
-  <si>
-    <t>OutU32_Test6</t>
-  </si>
-  <si>
-    <t>OutD_Test7</t>
-  </si>
-  <si>
-    <t>//0x8nnx</t>
-  </si>
-  <si>
-    <t>Configuration Data of the Module (0x8000 - 0x8FFF)</t>
-  </si>
-  <si>
-    <t>//0x9nnx</t>
-  </si>
-  <si>
-    <t>Information Data of the Module (0x9000 - 0x9FFF)</t>
-  </si>
-  <si>
-    <t>//0xAnnx</t>
-  </si>
-  <si>
-    <t>Diagnosis Data of the Module (0xA000 - 0xAFFF)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>UDINT</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>OutU32_InterlockOverride</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>OutU32_UnreadyOveride</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>REAL</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InF_BeamOnTime</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ARM IO First Trigger Out start count </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>UDINT</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InU32_AfcState</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -439,151 +845,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -592,210 +868,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.349986266670736"/>
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.149998474074526"/>
+        <fgColor theme="0" tint="-0.14996795556505021"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.15"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -803,253 +893,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
       <protection locked="0"/>
@@ -1063,9 +911,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -1102,62 +947,24 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1444,33 +1251,33 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:T912"/>
-  <sheetFormatPr defaultColWidth="10.7079646017699" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:T927"/>
+  <sheetFormatPr defaultColWidth="10.7265625" defaultRowHeight="14" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="3.85840707964602" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.283185840708" style="2" customWidth="1"/>
-    <col min="3" max="4" width="14.7079646017699" style="2" customWidth="1"/>
-    <col min="5" max="5" width="22.1858407079646" style="2" customWidth="1"/>
-    <col min="6" max="6" width="40.7079646017699" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11.7079646017699" style="2" customWidth="1"/>
-    <col min="8" max="9" width="7.70796460176991" style="2" customWidth="1"/>
-    <col min="10" max="10" width="10.283185840708" style="2" customWidth="1"/>
-    <col min="11" max="11" width="7.70796460176991" style="2" customWidth="1"/>
-    <col min="12" max="12" width="11.7079646017699" style="2" customWidth="1"/>
-    <col min="13" max="13" width="7.70796460176991" style="2" customWidth="1"/>
-    <col min="14" max="14" width="11.7079646017699" style="2" customWidth="1"/>
-    <col min="15" max="15" width="11.858407079646" style="2" customWidth="1"/>
-    <col min="16" max="16" width="35.7079646017699" style="2" customWidth="1"/>
-    <col min="17" max="16384" width="10.7079646017699" style="2"/>
+    <col min="1" max="1" width="3.81640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.26953125" style="2" customWidth="1"/>
+    <col min="3" max="4" width="14.7265625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="22.1796875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="40.7265625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11.7265625" style="2" customWidth="1"/>
+    <col min="8" max="9" width="7.7265625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="10.26953125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="7.7265625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11.7265625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="7.7265625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11.7265625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="11.81640625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="43.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="10.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1" spans="1:20">
+    <row r="1" spans="1:20" ht="18.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -1482,93 +1289,93 @@
         <v>1</v>
       </c>
       <c r="E1" s="4"/>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="21"/>
-      <c r="S1" s="21"/>
-      <c r="T1" s="21"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
     </row>
     <row r="2" spans="1:20">
       <c r="A2" s="3"/>
       <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="21"/>
-      <c r="S2" s="21"/>
-      <c r="T2" s="21"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="3"/>
-      <c r="B3" s="8"/>
+      <c r="B3" s="7"/>
       <c r="C3" s="5"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="21"/>
-      <c r="R3" s="21"/>
-      <c r="S3" s="21"/>
-      <c r="T3" s="21"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="22"/>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="20"/>
+      <c r="R3" s="20"/>
+      <c r="S3" s="20"/>
+      <c r="T3" s="20"/>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="3"/>
-      <c r="B4" s="8"/>
+      <c r="B4" s="7"/>
       <c r="C4" s="5"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="21"/>
-      <c r="R4" s="21"/>
-      <c r="S4" s="21"/>
-      <c r="T4" s="21"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="20"/>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="3"/>
@@ -1576,21 +1383,21 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="21"/>
-      <c r="S5" s="21"/>
-      <c r="T5" s="21"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="20"/>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="3"/>
@@ -1598,21 +1405,21 @@
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="21"/>
-      <c r="R6" s="21"/>
-      <c r="S6" s="21"/>
-      <c r="T6" s="21"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="20"/>
+      <c r="R6" s="20"/>
+      <c r="S6" s="20"/>
+      <c r="T6" s="20"/>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="3"/>
@@ -1620,25 +1427,25 @@
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="21"/>
-      <c r="R7" s="21"/>
-      <c r="S7" s="21"/>
-      <c r="T7" s="21"/>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="20"/>
+      <c r="R7" s="20"/>
+      <c r="S7" s="20"/>
+      <c r="T7" s="20"/>
+    </row>
+    <row r="8" spans="1:20">
       <c r="A8" s="3"/>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="9" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="4"/>
@@ -1656,7 +1463,7 @@
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:20">
       <c r="A9" s="3"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -1674,539 +1481,539 @@
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:20">
       <c r="A10" s="3"/>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="J10" s="11" t="s">
+      <c r="J10" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="K10" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="L10" s="11" t="s">
+      <c r="L10" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="M10" s="11" t="s">
+      <c r="M10" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="N10" s="20" t="s">
+      <c r="N10" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="O10" s="20" t="s">
+      <c r="O10" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="P10" s="11" t="s">
+      <c r="P10" s="10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" spans="1:16">
-      <c r="A11" s="12"/>
-      <c r="B11" s="13" t="s">
+    <row r="11" spans="1:20" s="1" customFormat="1">
+      <c r="A11" s="11"/>
+      <c r="B11" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="13"/>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="12"/>
+    </row>
+    <row r="12" spans="1:20">
       <c r="A12" s="3"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="16"/>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13"/>
+      <c r="P12" s="15"/>
+    </row>
+    <row r="13" spans="1:20">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
-      <c r="P13" s="12"/>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:16">
-      <c r="A14" s="12"/>
-      <c r="B14" s="18" t="s">
+      <c r="P13" s="11"/>
+    </row>
+    <row r="14" spans="1:20" s="1" customFormat="1">
+      <c r="A14" s="11"/>
+      <c r="B14" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
-      <c r="L14" s="18"/>
-      <c r="M14" s="18"/>
-      <c r="N14" s="18"/>
-      <c r="O14" s="18"/>
-      <c r="P14" s="18"/>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+    </row>
+    <row r="15" spans="1:20">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
-      <c r="P15" s="12"/>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="P15" s="11"/>
+    </row>
+    <row r="16" spans="1:20">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-      <c r="P16" s="12"/>
-    </row>
-    <row r="17" s="1" customFormat="1" hidden="1" outlineLevel="1" spans="1:16">
-      <c r="A17" s="12"/>
-      <c r="B17" s="18" t="s">
+      <c r="P16" s="11"/>
+    </row>
+    <row r="17" spans="1:16" s="1" customFormat="1" hidden="1" outlineLevel="1">
+      <c r="A17" s="11"/>
+      <c r="B17" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="18"/>
-      <c r="L17" s="18"/>
-      <c r="M17" s="18"/>
-      <c r="N17" s="18"/>
-      <c r="O17" s="18"/>
-      <c r="P17" s="18"/>
-    </row>
-    <row r="18" hidden="1" outlineLevel="1" spans="1:16">
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+    </row>
+    <row r="18" spans="1:16" hidden="1" outlineLevel="1">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
-      <c r="P18" s="12"/>
-    </row>
-    <row r="19" hidden="1" outlineLevel="1" spans="1:16">
+      <c r="P18" s="11"/>
+    </row>
+    <row r="19" spans="1:16" hidden="1" outlineLevel="1">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-      <c r="P19" s="12"/>
-    </row>
-    <row r="20" s="1" customFormat="1" hidden="1" outlineLevel="1" spans="1:16">
-      <c r="A20" s="12"/>
-      <c r="B20" s="18" t="s">
+      <c r="P19" s="11"/>
+    </row>
+    <row r="20" spans="1:16" s="1" customFormat="1" hidden="1" outlineLevel="1">
+      <c r="A20" s="11"/>
+      <c r="B20" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="18"/>
-      <c r="K20" s="18"/>
-      <c r="L20" s="18"/>
-      <c r="M20" s="18"/>
-      <c r="N20" s="18"/>
-      <c r="O20" s="18"/>
-      <c r="P20" s="18"/>
-    </row>
-    <row r="21" hidden="1" outlineLevel="1" spans="1:16">
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+    </row>
+    <row r="21" spans="1:16" hidden="1" outlineLevel="1">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
-      <c r="P21" s="12"/>
-    </row>
-    <row r="22" hidden="1" outlineLevel="1" spans="1:16">
+      <c r="P21" s="11"/>
+    </row>
+    <row r="22" spans="1:16" hidden="1" outlineLevel="1">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
-      <c r="P22" s="12"/>
-    </row>
-    <row r="23" s="1" customFormat="1" hidden="1" outlineLevel="1" spans="1:16">
-      <c r="A23" s="12"/>
-      <c r="B23" s="18" t="s">
+      <c r="P22" s="11"/>
+    </row>
+    <row r="23" spans="1:16" s="1" customFormat="1" hidden="1" outlineLevel="1">
+      <c r="A23" s="11"/>
+      <c r="B23" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="18"/>
-      <c r="K23" s="18"/>
-      <c r="L23" s="18"/>
-      <c r="M23" s="18"/>
-      <c r="N23" s="18"/>
-      <c r="O23" s="18"/>
-      <c r="P23" s="18"/>
-    </row>
-    <row r="24" hidden="1" outlineLevel="1" spans="1:16">
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="17"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="17"/>
+    </row>
+    <row r="24" spans="1:16" hidden="1" outlineLevel="1">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
-      <c r="P24" s="12"/>
-    </row>
-    <row r="25" hidden="1" outlineLevel="1" spans="1:16">
+      <c r="P24" s="11"/>
+    </row>
+    <row r="25" spans="1:16" hidden="1" outlineLevel="1">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
-      <c r="P25" s="12"/>
-    </row>
-    <row r="26" s="1" customFormat="1" hidden="1" outlineLevel="1" spans="1:16">
-      <c r="A26" s="12"/>
-      <c r="B26" s="18" t="s">
+      <c r="P25" s="11"/>
+    </row>
+    <row r="26" spans="1:16" s="1" customFormat="1" hidden="1" outlineLevel="1">
+      <c r="A26" s="11"/>
+      <c r="B26" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="18"/>
-      <c r="K26" s="18"/>
-      <c r="L26" s="18"/>
-      <c r="M26" s="18"/>
-      <c r="N26" s="18"/>
-      <c r="O26" s="18"/>
-      <c r="P26" s="18"/>
-    </row>
-    <row r="27" hidden="1" outlineLevel="1" spans="1:16">
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17"/>
+      <c r="M26" s="17"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="17"/>
+      <c r="P26" s="17"/>
+    </row>
+    <row r="27" spans="1:16" hidden="1" outlineLevel="1">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
-      <c r="P27" s="12"/>
-    </row>
-    <row r="28" hidden="1" outlineLevel="1" spans="1:16">
+      <c r="P27" s="11"/>
+    </row>
+    <row r="28" spans="1:16" hidden="1" outlineLevel="1">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
-      <c r="P28" s="12"/>
-    </row>
-    <row r="29" s="1" customFormat="1" hidden="1" outlineLevel="1" spans="1:16">
-      <c r="A29" s="12"/>
-      <c r="B29" s="18" t="s">
+      <c r="P28" s="11"/>
+    </row>
+    <row r="29" spans="1:16" s="1" customFormat="1" hidden="1" outlineLevel="1">
+      <c r="A29" s="11"/>
+      <c r="B29" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="C29" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="18"/>
-      <c r="J29" s="18"/>
-      <c r="K29" s="18"/>
-      <c r="L29" s="18"/>
-      <c r="M29" s="18"/>
-      <c r="N29" s="18"/>
-      <c r="O29" s="18"/>
-      <c r="P29" s="18"/>
-    </row>
-    <row r="30" hidden="1" outlineLevel="1" spans="1:16">
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
+      <c r="P29" s="17"/>
+    </row>
+    <row r="30" spans="1:16" hidden="1" outlineLevel="1">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
-      <c r="P30" s="12"/>
-    </row>
-    <row r="31" hidden="1" outlineLevel="1" spans="1:16">
+      <c r="P30" s="11"/>
+    </row>
+    <row r="31" spans="1:16" hidden="1" outlineLevel="1">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
-      <c r="P31" s="12"/>
-    </row>
-    <row r="32" s="1" customFormat="1" hidden="1" outlineLevel="1" spans="1:16">
-      <c r="A32" s="12"/>
-      <c r="B32" s="18" t="s">
+      <c r="P31" s="11"/>
+    </row>
+    <row r="32" spans="1:16" s="1" customFormat="1" hidden="1" outlineLevel="1">
+      <c r="A32" s="11"/>
+      <c r="B32" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="18"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="18"/>
-      <c r="M32" s="18"/>
-      <c r="N32" s="18"/>
-      <c r="O32" s="18"/>
-      <c r="P32" s="18"/>
-    </row>
-    <row r="33" hidden="1" outlineLevel="1" spans="1:16">
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="17"/>
+      <c r="M32" s="17"/>
+      <c r="N32" s="17"/>
+      <c r="O32" s="17"/>
+      <c r="P32" s="17"/>
+    </row>
+    <row r="33" spans="1:16" hidden="1" outlineLevel="1">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
-      <c r="P33" s="12"/>
-    </row>
-    <row r="34" hidden="1" outlineLevel="1" spans="1:16">
+      <c r="P33" s="11"/>
+    </row>
+    <row r="34" spans="1:16" hidden="1" outlineLevel="1">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
-      <c r="P34" s="12"/>
-    </row>
-    <row r="35" s="1" customFormat="1" collapsed="1" spans="1:16">
-      <c r="A35" s="12"/>
-      <c r="B35" s="18" t="s">
+      <c r="P34" s="11"/>
+    </row>
+    <row r="35" spans="1:16" s="1" customFormat="1" collapsed="1">
+      <c r="A35" s="11"/>
+      <c r="B35" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C35" s="18" t="s">
+      <c r="C35" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="18"/>
-      <c r="K35" s="18"/>
-      <c r="L35" s="18"/>
-      <c r="M35" s="18"/>
-      <c r="N35" s="18"/>
-      <c r="O35" s="18"/>
-      <c r="P35" s="18"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="17"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="17"/>
+      <c r="L35" s="17"/>
+      <c r="M35" s="17"/>
+      <c r="N35" s="17"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="17"/>
     </row>
     <row r="36" spans="1:16">
       <c r="A36" s="3"/>
@@ -2216,854 +2023,1151 @@
       <c r="C36" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D36" s="17"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12" t="s">
+      <c r="D36" s="16"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="12"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
       <c r="J36" s="3"/>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
       <c r="N36" s="3"/>
       <c r="O36" s="3"/>
-      <c r="P36" s="12"/>
-    </row>
-    <row r="37" customFormat="1" spans="1:16">
+      <c r="P36" s="11"/>
+    </row>
+    <row r="37" spans="1:16" customFormat="1">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
-      <c r="D37" s="17">
+      <c r="D37" s="16">
         <v>1</v>
       </c>
-      <c r="E37" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F37" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="G37" s="12"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="12"/>
+      <c r="E37" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="F37" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
       <c r="N37" s="3"/>
       <c r="O37" s="3"/>
-      <c r="P37" s="12"/>
-    </row>
-    <row r="38" customFormat="1" spans="1:16">
+      <c r="P37" s="21" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" customFormat="1">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
-      <c r="D38" s="17">
+      <c r="D38" s="16">
         <v>2</v>
       </c>
-      <c r="E38" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="F38" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="G38" s="12"/>
-      <c r="H38" s="12"/>
-      <c r="I38" s="12"/>
+      <c r="E38" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F38" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
-      <c r="P38" s="12"/>
-    </row>
-    <row r="39" customFormat="1" spans="1:16">
+      <c r="P38" s="11"/>
+    </row>
+    <row r="39" spans="1:16" customFormat="1">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
-      <c r="D39" s="17">
+      <c r="D39" s="16">
         <v>3</v>
       </c>
-      <c r="E39" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="F39" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="G39" s="12"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="12"/>
+      <c r="E39" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F39" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-      <c r="P39" s="12"/>
-    </row>
-    <row r="40" customFormat="1" spans="1:16">
-      <c r="A40" s="3">
-        <v>4</v>
-      </c>
+      <c r="P39" s="11"/>
+    </row>
+    <row r="40" spans="1:16" customFormat="1">
+      <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
-      <c r="D40" s="17">
+      <c r="D40" s="16">
         <v>4</v>
       </c>
-      <c r="E40" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F40" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G40" s="12"/>
-      <c r="H40" s="12"/>
-      <c r="I40" s="12"/>
+      <c r="E40" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="F40" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-      <c r="P40" s="12"/>
-    </row>
-    <row r="41" customFormat="1" spans="1:16">
+      <c r="P40" s="11"/>
+    </row>
+    <row r="41" spans="1:16" customFormat="1">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
-      <c r="D41" s="17">
+      <c r="D41" s="16">
         <v>5</v>
       </c>
-      <c r="E41" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="F41" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="G41" s="12"/>
-      <c r="H41" s="12"/>
-      <c r="I41" s="12"/>
+      <c r="E41" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="F41" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
       <c r="J41" s="3"/>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
       <c r="N41" s="3"/>
       <c r="O41" s="3"/>
-      <c r="P41" s="12"/>
-    </row>
-    <row r="42" customFormat="1" spans="1:16">
+      <c r="P41" s="11"/>
+    </row>
+    <row r="42" spans="1:16" customFormat="1">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
-      <c r="D42" s="17">
+      <c r="D42" s="16">
         <v>6</v>
       </c>
-      <c r="E42" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="F42" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="G42" s="12"/>
-      <c r="H42" s="12"/>
-      <c r="I42" s="12"/>
+      <c r="E42" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="F42" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="G42" s="11"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11"/>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
       <c r="N42" s="3"/>
       <c r="O42" s="3"/>
-      <c r="P42" s="12"/>
-    </row>
-    <row r="43" customFormat="1" spans="1:16">
+      <c r="P42" s="11"/>
+    </row>
+    <row r="43" spans="1:16" customFormat="1">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
-      <c r="D43" s="17">
+      <c r="D43" s="16">
         <v>7</v>
       </c>
-      <c r="E43" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="F43" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G43" s="12"/>
-      <c r="H43" s="12"/>
-      <c r="I43" s="12"/>
+      <c r="E43" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="F43" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
       <c r="J43" s="3"/>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
       <c r="N43" s="3"/>
       <c r="O43" s="3"/>
-      <c r="P43" s="12"/>
-    </row>
-    <row r="44" s="1" customFormat="1" spans="1:16">
-      <c r="A44" s="12"/>
-      <c r="B44" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="C44" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="D44" s="18"/>
-      <c r="E44" s="18"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="18"/>
-      <c r="H44" s="18"/>
-      <c r="I44" s="18"/>
-      <c r="J44" s="18"/>
-      <c r="K44" s="18"/>
-      <c r="L44" s="18"/>
-      <c r="M44" s="18"/>
-      <c r="N44" s="18"/>
-      <c r="O44" s="18"/>
-      <c r="P44" s="18"/>
-    </row>
-    <row r="45" spans="1:16">
+      <c r="P43" s="21" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" customFormat="1">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="16">
+        <v>8</v>
+      </c>
+      <c r="E44" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="F44" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3"/>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3"/>
+      <c r="O44" s="3"/>
+      <c r="P44" s="21" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" customFormat="1">
       <c r="A45" s="3"/>
-      <c r="B45" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D45" s="17"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="G45" s="12"/>
-      <c r="H45" s="12"/>
-      <c r="I45" s="12"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="16">
+        <v>9</v>
+      </c>
+      <c r="E45" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="F45" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="11"/>
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
-      <c r="P45" s="12"/>
-    </row>
-    <row r="46" customFormat="1" spans="1:16">
+      <c r="P45" s="21" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" customFormat="1">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
-      <c r="D46" s="17">
-        <v>1</v>
-      </c>
-      <c r="E46" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F46" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="G46" s="12"/>
-      <c r="H46" s="12"/>
-      <c r="I46" s="12"/>
+      <c r="D46" s="16">
+        <v>10</v>
+      </c>
+      <c r="E46" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="F46" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="11"/>
       <c r="J46" s="3"/>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
-      <c r="P46" s="12"/>
-    </row>
-    <row r="47" customFormat="1" spans="1:16">
+      <c r="P46" s="21" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" customFormat="1">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
-      <c r="D47" s="17">
-        <v>2</v>
-      </c>
-      <c r="E47" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="F47" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="G47" s="12"/>
-      <c r="H47" s="12"/>
-      <c r="I47" s="12"/>
+      <c r="D47" s="16">
+        <v>11</v>
+      </c>
+      <c r="E47" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="F47" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="11"/>
       <c r="J47" s="3"/>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
-      <c r="P47" s="12"/>
-    </row>
-    <row r="48" customFormat="1" spans="1:16">
+      <c r="P47" s="21" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" customFormat="1">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
-      <c r="D48" s="17">
-        <v>3</v>
-      </c>
-      <c r="E48" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="F48" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G48" s="12"/>
-      <c r="H48" s="12"/>
-      <c r="I48" s="12"/>
+      <c r="D48" s="16">
+        <v>12</v>
+      </c>
+      <c r="E48" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="F48" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="11"/>
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
-      <c r="P48" s="12"/>
-    </row>
-    <row r="49" customFormat="1" spans="1:16">
+      <c r="P48" s="21" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" customFormat="1">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
-      <c r="D49" s="17">
-        <v>4</v>
-      </c>
-      <c r="E49" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F49" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="G49" s="12"/>
-      <c r="H49" s="12"/>
-      <c r="I49" s="12"/>
+      <c r="D49" s="16">
+        <v>13</v>
+      </c>
+      <c r="E49" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="F49" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="11"/>
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
       <c r="N49" s="3"/>
       <c r="O49" s="3"/>
-      <c r="P49" s="12"/>
-    </row>
-    <row r="50" customFormat="1" spans="1:16">
+      <c r="P49" s="21"/>
+    </row>
+    <row r="50" spans="1:16" customFormat="1">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
-      <c r="D50" s="17">
-        <v>5</v>
-      </c>
-      <c r="E50" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="F50" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="G50" s="12"/>
-      <c r="H50" s="12"/>
-      <c r="I50" s="12"/>
+      <c r="D50" s="16">
+        <v>14</v>
+      </c>
+      <c r="E50" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="F50" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="11"/>
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
       <c r="O50" s="3"/>
-      <c r="P50" s="12"/>
-    </row>
-    <row r="51" customFormat="1" spans="1:16">
+      <c r="P50" s="21"/>
+    </row>
+    <row r="51" spans="1:16" customFormat="1">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
-      <c r="D51" s="17">
-        <v>6</v>
-      </c>
-      <c r="E51" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="F51" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="G51" s="12"/>
-      <c r="H51" s="12"/>
-      <c r="I51" s="12"/>
+      <c r="D51" s="16">
+        <v>15</v>
+      </c>
+      <c r="E51" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="F51" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11"/>
       <c r="J51" s="3"/>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
       <c r="N51" s="3"/>
       <c r="O51" s="3"/>
-      <c r="P51" s="12"/>
-    </row>
-    <row r="52" customFormat="1" spans="1:16">
+      <c r="P51" s="11"/>
+    </row>
+    <row r="52" spans="1:16" customFormat="1">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
-      <c r="D52" s="17">
-        <v>7</v>
-      </c>
-      <c r="E52" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="F52" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G52" s="12"/>
-      <c r="H52" s="12"/>
-      <c r="I52" s="12"/>
+      <c r="D52" s="16">
+        <v>16</v>
+      </c>
+      <c r="E52" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="F52" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="G52" s="11"/>
+      <c r="H52" s="11"/>
+      <c r="I52" s="11"/>
       <c r="J52" s="3"/>
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
       <c r="M52" s="3"/>
       <c r="N52" s="3"/>
       <c r="O52" s="3"/>
-      <c r="P52" s="12"/>
-    </row>
-    <row r="53" s="1" customFormat="1" spans="1:16">
-      <c r="A53" s="12"/>
-      <c r="B53" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="C53" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="D53" s="18"/>
-      <c r="E53" s="18"/>
-      <c r="F53" s="19"/>
-      <c r="G53" s="18"/>
-      <c r="H53" s="18"/>
-      <c r="I53" s="18"/>
-      <c r="J53" s="18"/>
-      <c r="K53" s="18"/>
-      <c r="L53" s="18"/>
-      <c r="M53" s="18"/>
-      <c r="N53" s="18"/>
-      <c r="O53" s="18"/>
-      <c r="P53" s="18"/>
-    </row>
-    <row r="54" spans="1:16">
+      <c r="P52" s="11"/>
+    </row>
+    <row r="53" spans="1:16" customFormat="1">
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="16">
+        <v>17</v>
+      </c>
+      <c r="E53" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F53" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="G53" s="11"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="3"/>
+      <c r="K53" s="3"/>
+      <c r="L53" s="3"/>
+      <c r="M53" s="3"/>
+      <c r="N53" s="3"/>
+      <c r="O53" s="3"/>
+      <c r="P53" s="11"/>
+    </row>
+    <row r="54" spans="1:16" customFormat="1">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
-      <c r="D54" s="17"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
+      <c r="D54" s="16">
+        <v>18</v>
+      </c>
+      <c r="E54" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="F54" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="G54" s="11"/>
+      <c r="H54" s="11"/>
+      <c r="I54" s="11"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
-      <c r="P54" s="12"/>
-    </row>
-    <row r="55" spans="1:16">
+      <c r="P54" s="11"/>
+    </row>
+    <row r="55" spans="1:16" customFormat="1">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
-      <c r="D55" s="17"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
+      <c r="D55" s="16"/>
+      <c r="E55" s="11"/>
+      <c r="F55" s="11"/>
+      <c r="G55" s="11"/>
+      <c r="H55" s="11"/>
+      <c r="I55" s="11"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-      <c r="P55" s="12"/>
-    </row>
-    <row r="56" s="1" customFormat="1" spans="1:16">
-      <c r="A56" s="12"/>
-      <c r="B56" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="C56" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="D56" s="18"/>
-      <c r="E56" s="18"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="18"/>
-      <c r="H56" s="18"/>
-      <c r="I56" s="18"/>
-      <c r="J56" s="18"/>
-      <c r="K56" s="18"/>
-      <c r="L56" s="18"/>
-      <c r="M56" s="18"/>
-      <c r="N56" s="18"/>
-      <c r="O56" s="18"/>
-      <c r="P56" s="18"/>
-    </row>
-    <row r="57" spans="1:16">
-      <c r="A57" s="3"/>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
+      <c r="P55" s="11"/>
+    </row>
+    <row r="56" spans="1:16" customFormat="1">
+      <c r="A56" s="3"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="16"/>
+      <c r="E56" s="11"/>
+      <c r="F56" s="11"/>
+      <c r="G56" s="11"/>
+      <c r="H56" s="11"/>
+      <c r="I56" s="11"/>
+      <c r="J56" s="3"/>
+      <c r="K56" s="3"/>
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+      <c r="P56" s="11"/>
+    </row>
+    <row r="57" spans="1:16" s="1" customFormat="1">
+      <c r="A57" s="11"/>
+      <c r="B57" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C57" s="17" t="s">
+        <v>45</v>
+      </c>
       <c r="D57" s="17"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="3"/>
-      <c r="K57" s="3"/>
-      <c r="L57" s="3"/>
-      <c r="M57" s="3"/>
-      <c r="N57" s="3"/>
-      <c r="O57" s="3"/>
-      <c r="P57" s="12"/>
+      <c r="E57" s="17"/>
+      <c r="F57" s="17"/>
+      <c r="G57" s="17"/>
+      <c r="H57" s="17"/>
+      <c r="I57" s="17"/>
+      <c r="J57" s="17"/>
+      <c r="K57" s="17"/>
+      <c r="L57" s="17"/>
+      <c r="M57" s="17"/>
+      <c r="N57" s="17"/>
+      <c r="O57" s="17"/>
+      <c r="P57" s="17"/>
     </row>
     <row r="58" spans="1:16">
       <c r="A58" s="3"/>
-      <c r="B58" s="3"/>
-      <c r="C58" s="3"/>
-      <c r="D58" s="17"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
+      <c r="B58" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D58" s="16"/>
+      <c r="E58" s="11"/>
+      <c r="F58" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G58" s="11"/>
+      <c r="H58" s="11"/>
+      <c r="I58" s="11"/>
       <c r="J58" s="3"/>
       <c r="K58" s="3"/>
       <c r="L58" s="3"/>
       <c r="M58" s="3"/>
       <c r="N58" s="3"/>
       <c r="O58" s="3"/>
-      <c r="P58" s="12"/>
-    </row>
-    <row r="59" s="1" customFormat="1" spans="1:16">
-      <c r="A59" s="12"/>
-      <c r="B59" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="C59" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="D59" s="18"/>
-      <c r="E59" s="18"/>
-      <c r="F59" s="18"/>
-      <c r="G59" s="18"/>
-      <c r="H59" s="18"/>
-      <c r="I59" s="18"/>
-      <c r="J59" s="18"/>
-      <c r="K59" s="18"/>
-      <c r="L59" s="18"/>
-      <c r="M59" s="18"/>
-      <c r="N59" s="18"/>
-      <c r="O59" s="18"/>
-      <c r="P59" s="18"/>
-    </row>
-    <row r="60" spans="1:16">
+      <c r="P58" s="11"/>
+    </row>
+    <row r="59" spans="1:16" customFormat="1">
+      <c r="A59" s="3"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="16">
+        <v>1</v>
+      </c>
+      <c r="E59" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F59" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="G59" s="11"/>
+      <c r="H59" s="11"/>
+      <c r="I59" s="11"/>
+      <c r="J59" s="3"/>
+      <c r="K59" s="3"/>
+      <c r="L59" s="3"/>
+      <c r="M59" s="3"/>
+      <c r="N59" s="3"/>
+      <c r="O59" s="3"/>
+      <c r="P59" s="11"/>
+    </row>
+    <row r="60" spans="1:16" customFormat="1">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
-      <c r="D60" s="17"/>
-      <c r="E60" s="12"/>
-      <c r="F60" s="12"/>
-      <c r="G60" s="12"/>
-      <c r="H60" s="12"/>
-      <c r="I60" s="12"/>
+      <c r="D60" s="16">
+        <v>2</v>
+      </c>
+      <c r="E60" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F60" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="G60" s="11"/>
+      <c r="H60" s="11"/>
+      <c r="I60" s="11"/>
       <c r="J60" s="3"/>
       <c r="K60" s="3"/>
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
       <c r="N60" s="3"/>
       <c r="O60" s="3"/>
-      <c r="P60" s="12"/>
-    </row>
-    <row r="61" spans="1:16">
+      <c r="P60" s="11"/>
+    </row>
+    <row r="61" spans="1:16" customFormat="1">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
-      <c r="D61" s="17"/>
-      <c r="E61" s="12"/>
-      <c r="F61" s="12"/>
-      <c r="G61" s="12"/>
-      <c r="H61" s="12"/>
-      <c r="I61" s="12"/>
+      <c r="D61" s="16">
+        <v>3</v>
+      </c>
+      <c r="E61" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F61" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="G61" s="11"/>
+      <c r="H61" s="11"/>
+      <c r="I61" s="11"/>
       <c r="J61" s="3"/>
       <c r="K61" s="3"/>
       <c r="L61" s="3"/>
       <c r="M61" s="3"/>
       <c r="N61" s="3"/>
       <c r="O61" s="3"/>
-      <c r="P61" s="12"/>
-    </row>
-    <row r="62" spans="1:16">
+      <c r="P61" s="11"/>
+    </row>
+    <row r="62" spans="1:16" customFormat="1">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
-      <c r="F62" s="18"/>
-      <c r="G62" s="3"/>
-      <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
+      <c r="D62" s="16">
+        <v>4</v>
+      </c>
+      <c r="E62" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="F62" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="G62" s="11"/>
+      <c r="H62" s="11"/>
+      <c r="I62" s="11"/>
       <c r="J62" s="3"/>
       <c r="K62" s="3"/>
       <c r="L62" s="3"/>
       <c r="M62" s="3"/>
       <c r="N62" s="3"/>
       <c r="O62" s="3"/>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="1:16">
+      <c r="P62" s="11"/>
+    </row>
+    <row r="63" spans="1:16" customFormat="1">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
-      <c r="D63" s="3"/>
-      <c r="E63" s="3"/>
-      <c r="F63" s="12"/>
-      <c r="G63" s="3"/>
-      <c r="H63" s="3"/>
-      <c r="I63" s="3"/>
+      <c r="D63" s="16">
+        <v>5</v>
+      </c>
+      <c r="E63" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="F63" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="G63" s="11"/>
+      <c r="H63" s="11"/>
+      <c r="I63" s="11"/>
       <c r="J63" s="3"/>
       <c r="K63" s="3"/>
       <c r="L63" s="3"/>
       <c r="M63" s="3"/>
       <c r="N63" s="3"/>
       <c r="O63" s="3"/>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="1:16">
+      <c r="P63" s="11"/>
+    </row>
+    <row r="64" spans="1:16" customFormat="1">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
-      <c r="E64" s="3"/>
-      <c r="F64" s="12"/>
-      <c r="G64" s="3"/>
-      <c r="H64" s="3"/>
-      <c r="I64" s="3"/>
+      <c r="D64" s="16">
+        <v>6</v>
+      </c>
+      <c r="E64" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="F64" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="G64" s="11"/>
+      <c r="H64" s="11"/>
+      <c r="I64" s="11"/>
       <c r="J64" s="3"/>
       <c r="K64" s="3"/>
       <c r="L64" s="3"/>
       <c r="M64" s="3"/>
       <c r="N64" s="3"/>
       <c r="O64" s="3"/>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="1:16">
+      <c r="P64" s="11"/>
+    </row>
+    <row r="65" spans="1:16" customFormat="1">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="18"/>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
+      <c r="D65" s="16"/>
+      <c r="E65" s="11"/>
+      <c r="F65" s="11"/>
+      <c r="G65" s="11"/>
+      <c r="H65" s="11"/>
+      <c r="I65" s="11"/>
       <c r="J65" s="3"/>
       <c r="K65" s="3"/>
       <c r="L65" s="3"/>
       <c r="M65" s="3"/>
       <c r="N65" s="3"/>
       <c r="O65" s="3"/>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="1:16">
+      <c r="P65" s="11"/>
+    </row>
+    <row r="66" spans="1:16" customFormat="1">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
-      <c r="D66" s="3"/>
-      <c r="E66" s="3"/>
-      <c r="F66" s="12"/>
-      <c r="G66" s="3"/>
-      <c r="H66" s="3"/>
-      <c r="I66" s="3"/>
+      <c r="D66" s="16"/>
+      <c r="E66" s="11"/>
+      <c r="F66" s="11"/>
+      <c r="G66" s="11"/>
+      <c r="H66" s="11"/>
+      <c r="I66" s="11"/>
       <c r="J66" s="3"/>
       <c r="K66" s="3"/>
       <c r="L66" s="3"/>
       <c r="M66" s="3"/>
       <c r="N66" s="3"/>
       <c r="O66" s="3"/>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="1:16">
+      <c r="P66" s="11"/>
+    </row>
+    <row r="67" spans="1:16" customFormat="1">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
-      <c r="F67" s="12"/>
-      <c r="G67" s="3"/>
-      <c r="H67" s="3"/>
-      <c r="I67" s="3"/>
+      <c r="D67" s="16"/>
+      <c r="E67" s="11"/>
+      <c r="F67" s="11"/>
+      <c r="G67" s="11"/>
+      <c r="H67" s="11"/>
+      <c r="I67" s="11"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-      <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="1:16">
-      <c r="A68" s="3"/>
-      <c r="B68" s="3"/>
-      <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
-      <c r="I68" s="3"/>
-      <c r="J68" s="3"/>
-      <c r="K68" s="3"/>
-      <c r="L68" s="3"/>
-      <c r="M68" s="3"/>
-      <c r="N68" s="3"/>
-      <c r="O68" s="3"/>
-      <c r="P68" s="3"/>
+      <c r="P67" s="11"/>
+    </row>
+    <row r="68" spans="1:16" s="1" customFormat="1">
+      <c r="A68" s="11"/>
+      <c r="B68" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C68" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D68" s="17"/>
+      <c r="E68" s="17"/>
+      <c r="F68" s="18"/>
+      <c r="G68" s="17"/>
+      <c r="H68" s="17"/>
+      <c r="I68" s="17"/>
+      <c r="J68" s="17"/>
+      <c r="K68" s="17"/>
+      <c r="L68" s="17"/>
+      <c r="M68" s="17"/>
+      <c r="N68" s="17"/>
+      <c r="O68" s="17"/>
+      <c r="P68" s="17"/>
     </row>
     <row r="69" spans="1:16">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
-      <c r="I69" s="3"/>
+      <c r="D69" s="16"/>
+      <c r="E69" s="11"/>
+      <c r="F69" s="11"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="11"/>
+      <c r="I69" s="11"/>
       <c r="J69" s="3"/>
       <c r="K69" s="3"/>
       <c r="L69" s="3"/>
       <c r="M69" s="3"/>
       <c r="N69" s="3"/>
       <c r="O69" s="3"/>
-      <c r="P69" s="3"/>
+      <c r="P69" s="11"/>
     </row>
     <row r="70" spans="1:16">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
-      <c r="D70" s="3"/>
-      <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
-      <c r="G70" s="3"/>
-      <c r="H70" s="3"/>
-      <c r="I70" s="3"/>
+      <c r="D70" s="16"/>
+      <c r="E70" s="11"/>
+      <c r="F70" s="11"/>
+      <c r="G70" s="11"/>
+      <c r="H70" s="11"/>
+      <c r="I70" s="11"/>
       <c r="J70" s="3"/>
       <c r="K70" s="3"/>
       <c r="L70" s="3"/>
       <c r="M70" s="3"/>
       <c r="N70" s="3"/>
       <c r="O70" s="3"/>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="1:16">
-      <c r="A71" s="3"/>
-      <c r="B71" s="3"/>
-      <c r="C71" s="3"/>
-      <c r="D71" s="3"/>
-      <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
-      <c r="G71" s="3"/>
-      <c r="H71" s="3"/>
-      <c r="I71" s="3"/>
-      <c r="J71" s="3"/>
-      <c r="K71" s="3"/>
-      <c r="L71" s="3"/>
-      <c r="M71" s="3"/>
-      <c r="N71" s="3"/>
-      <c r="O71" s="3"/>
-      <c r="P71" s="3"/>
+      <c r="P70" s="11"/>
+    </row>
+    <row r="71" spans="1:16" s="1" customFormat="1">
+      <c r="A71" s="11"/>
+      <c r="B71" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C71" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D71" s="17"/>
+      <c r="E71" s="17"/>
+      <c r="F71" s="11"/>
+      <c r="G71" s="17"/>
+      <c r="H71" s="17"/>
+      <c r="I71" s="17"/>
+      <c r="J71" s="17"/>
+      <c r="K71" s="17"/>
+      <c r="L71" s="17"/>
+      <c r="M71" s="17"/>
+      <c r="N71" s="17"/>
+      <c r="O71" s="17"/>
+      <c r="P71" s="17"/>
     </row>
     <row r="72" spans="1:16">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
-      <c r="D72" s="3"/>
-      <c r="E72" s="3"/>
-      <c r="F72" s="3"/>
-      <c r="G72" s="3"/>
-      <c r="H72" s="3"/>
-      <c r="I72" s="3"/>
+      <c r="D72" s="16"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="11"/>
+      <c r="G72" s="11"/>
+      <c r="H72" s="11"/>
+      <c r="I72" s="11"/>
       <c r="J72" s="3"/>
       <c r="K72" s="3"/>
       <c r="L72" s="3"/>
       <c r="M72" s="3"/>
       <c r="N72" s="3"/>
       <c r="O72" s="3"/>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="3:6">
+      <c r="P72" s="11"/>
+    </row>
+    <row r="73" spans="1:16">
+      <c r="A73" s="3"/>
+      <c r="B73" s="3"/>
       <c r="C73" s="3"/>
-      <c r="F73" s="3"/>
-    </row>
-    <row r="74" spans="3:6">
-      <c r="C74" s="3"/>
-      <c r="F74" s="3"/>
-    </row>
-    <row r="75" spans="3:6">
+      <c r="D73" s="16"/>
+      <c r="E73" s="11"/>
+      <c r="F73" s="11"/>
+      <c r="G73" s="11"/>
+      <c r="H73" s="11"/>
+      <c r="I73" s="11"/>
+      <c r="J73" s="3"/>
+      <c r="K73" s="3"/>
+      <c r="L73" s="3"/>
+      <c r="M73" s="3"/>
+      <c r="N73" s="3"/>
+      <c r="O73" s="3"/>
+      <c r="P73" s="11"/>
+    </row>
+    <row r="74" spans="1:16" s="1" customFormat="1">
+      <c r="A74" s="11"/>
+      <c r="B74" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C74" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D74" s="17"/>
+      <c r="E74" s="17"/>
+      <c r="F74" s="17"/>
+      <c r="G74" s="17"/>
+      <c r="H74" s="17"/>
+      <c r="I74" s="17"/>
+      <c r="J74" s="17"/>
+      <c r="K74" s="17"/>
+      <c r="L74" s="17"/>
+      <c r="M74" s="17"/>
+      <c r="N74" s="17"/>
+      <c r="O74" s="17"/>
+      <c r="P74" s="17"/>
+    </row>
+    <row r="75" spans="1:16">
+      <c r="A75" s="3"/>
+      <c r="B75" s="3"/>
       <c r="C75" s="3"/>
-      <c r="F75" s="3"/>
-    </row>
-    <row r="76" spans="3:6">
+      <c r="D75" s="16"/>
+      <c r="E75" s="11"/>
+      <c r="F75" s="11"/>
+      <c r="G75" s="11"/>
+      <c r="H75" s="11"/>
+      <c r="I75" s="11"/>
+      <c r="J75" s="3"/>
+      <c r="K75" s="3"/>
+      <c r="L75" s="3"/>
+      <c r="M75" s="3"/>
+      <c r="N75" s="3"/>
+      <c r="O75" s="3"/>
+      <c r="P75" s="11"/>
+    </row>
+    <row r="76" spans="1:16">
+      <c r="A76" s="3"/>
+      <c r="B76" s="3"/>
       <c r="C76" s="3"/>
-      <c r="F76" s="3"/>
-    </row>
-    <row r="77" spans="3:6">
+      <c r="D76" s="16"/>
+      <c r="E76" s="11"/>
+      <c r="F76" s="11"/>
+      <c r="G76" s="11"/>
+      <c r="H76" s="11"/>
+      <c r="I76" s="11"/>
+      <c r="J76" s="3"/>
+      <c r="K76" s="3"/>
+      <c r="L76" s="3"/>
+      <c r="M76" s="3"/>
+      <c r="N76" s="3"/>
+      <c r="O76" s="3"/>
+      <c r="P76" s="11"/>
+    </row>
+    <row r="77" spans="1:16">
+      <c r="A77" s="3"/>
+      <c r="B77" s="3"/>
       <c r="C77" s="3"/>
-      <c r="F77" s="3"/>
-    </row>
-    <row r="78" spans="3:6">
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="17"/>
+      <c r="G77" s="3"/>
+      <c r="H77" s="3"/>
+      <c r="I77" s="3"/>
+      <c r="J77" s="3"/>
+      <c r="K77" s="3"/>
+      <c r="L77" s="3"/>
+      <c r="M77" s="3"/>
+      <c r="N77" s="3"/>
+      <c r="O77" s="3"/>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="78" spans="1:16">
+      <c r="A78" s="3"/>
+      <c r="B78" s="3"/>
       <c r="C78" s="3"/>
-      <c r="F78" s="3"/>
-    </row>
-    <row r="79" spans="3:3">
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="11"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3"/>
+      <c r="I78" s="3"/>
+      <c r="J78" s="3"/>
+      <c r="K78" s="3"/>
+      <c r="L78" s="3"/>
+      <c r="M78" s="3"/>
+      <c r="N78" s="3"/>
+      <c r="O78" s="3"/>
+      <c r="P78" s="3"/>
+    </row>
+    <row r="79" spans="1:16">
+      <c r="A79" s="3"/>
+      <c r="B79" s="3"/>
       <c r="C79" s="3"/>
-    </row>
-    <row r="80" spans="3:3">
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="11"/>
+      <c r="G79" s="3"/>
+      <c r="H79" s="3"/>
+      <c r="I79" s="3"/>
+      <c r="J79" s="3"/>
+      <c r="K79" s="3"/>
+      <c r="L79" s="3"/>
+      <c r="M79" s="3"/>
+      <c r="N79" s="3"/>
+      <c r="O79" s="3"/>
+      <c r="P79" s="3"/>
+    </row>
+    <row r="80" spans="1:16">
+      <c r="A80" s="3"/>
+      <c r="B80" s="3"/>
       <c r="C80" s="3"/>
-    </row>
-    <row r="81" spans="3:3">
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="17"/>
+      <c r="G80" s="3"/>
+      <c r="H80" s="3"/>
+      <c r="I80" s="3"/>
+      <c r="J80" s="3"/>
+      <c r="K80" s="3"/>
+      <c r="L80" s="3"/>
+      <c r="M80" s="3"/>
+      <c r="N80" s="3"/>
+      <c r="O80" s="3"/>
+      <c r="P80" s="3"/>
+    </row>
+    <row r="81" spans="1:16">
+      <c r="A81" s="3"/>
+      <c r="B81" s="3"/>
       <c r="C81" s="3"/>
-    </row>
-    <row r="82" spans="3:3">
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="11"/>
+      <c r="G81" s="3"/>
+      <c r="H81" s="3"/>
+      <c r="I81" s="3"/>
+      <c r="J81" s="3"/>
+      <c r="K81" s="3"/>
+      <c r="L81" s="3"/>
+      <c r="M81" s="3"/>
+      <c r="N81" s="3"/>
+      <c r="O81" s="3"/>
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="1:16">
+      <c r="A82" s="3"/>
+      <c r="B82" s="3"/>
       <c r="C82" s="3"/>
-    </row>
-    <row r="83" spans="3:3">
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="11"/>
+      <c r="G82" s="3"/>
+      <c r="H82" s="3"/>
+      <c r="I82" s="3"/>
+      <c r="J82" s="3"/>
+      <c r="K82" s="3"/>
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="1:16">
+      <c r="A83" s="3"/>
+      <c r="B83" s="3"/>
       <c r="C83" s="3"/>
-    </row>
-    <row r="84" spans="3:3">
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3"/>
+      <c r="H83" s="3"/>
+      <c r="I83" s="3"/>
+      <c r="J83" s="3"/>
+      <c r="K83" s="3"/>
+      <c r="L83" s="3"/>
+      <c r="M83" s="3"/>
+      <c r="N83" s="3"/>
+      <c r="O83" s="3"/>
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="1:16">
+      <c r="A84" s="3"/>
+      <c r="B84" s="3"/>
       <c r="C84" s="3"/>
-    </row>
-    <row r="85" spans="3:3">
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
+      <c r="H84" s="3"/>
+      <c r="I84" s="3"/>
+      <c r="J84" s="3"/>
+      <c r="K84" s="3"/>
+      <c r="L84" s="3"/>
+      <c r="M84" s="3"/>
+      <c r="N84" s="3"/>
+      <c r="O84" s="3"/>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="1:16">
+      <c r="A85" s="3"/>
+      <c r="B85" s="3"/>
       <c r="C85" s="3"/>
-    </row>
-    <row r="86" spans="3:3">
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3"/>
+      <c r="H85" s="3"/>
+      <c r="I85" s="3"/>
+      <c r="J85" s="3"/>
+      <c r="K85" s="3"/>
+      <c r="L85" s="3"/>
+      <c r="M85" s="3"/>
+      <c r="N85" s="3"/>
+      <c r="O85" s="3"/>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="1:16">
+      <c r="A86" s="3"/>
+      <c r="B86" s="3"/>
       <c r="C86" s="3"/>
-    </row>
-    <row r="87" spans="3:3">
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
+      <c r="H86" s="3"/>
+      <c r="I86" s="3"/>
+      <c r="J86" s="3"/>
+      <c r="K86" s="3"/>
+      <c r="L86" s="3"/>
+      <c r="M86" s="3"/>
+      <c r="N86" s="3"/>
+      <c r="O86" s="3"/>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="1:16">
+      <c r="A87" s="3"/>
+      <c r="B87" s="3"/>
       <c r="C87" s="3"/>
-    </row>
-    <row r="88" spans="3:3">
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
+      <c r="H87" s="3"/>
+      <c r="I87" s="3"/>
+      <c r="J87" s="3"/>
+      <c r="K87" s="3"/>
+      <c r="L87" s="3"/>
+      <c r="M87" s="3"/>
+      <c r="N87" s="3"/>
+      <c r="O87" s="3"/>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="1:16">
       <c r="C88" s="3"/>
-    </row>
-    <row r="89" spans="3:3">
+      <c r="F88" s="3"/>
+    </row>
+    <row r="89" spans="1:16">
       <c r="C89" s="3"/>
-    </row>
-    <row r="90" spans="3:3">
+      <c r="F89" s="3"/>
+    </row>
+    <row r="90" spans="1:16">
       <c r="C90" s="3"/>
-    </row>
-    <row r="91" spans="3:3">
+      <c r="F90" s="3"/>
+    </row>
+    <row r="91" spans="1:16">
       <c r="C91" s="3"/>
-    </row>
-    <row r="92" spans="3:3">
+      <c r="F91" s="3"/>
+    </row>
+    <row r="92" spans="1:16">
       <c r="C92" s="3"/>
-    </row>
-    <row r="93" spans="3:3">
+      <c r="F92" s="3"/>
+    </row>
+    <row r="93" spans="1:16">
       <c r="C93" s="3"/>
-    </row>
-    <row r="94" spans="3:3">
+      <c r="F93" s="3"/>
+    </row>
+    <row r="94" spans="1:16">
       <c r="C94" s="3"/>
     </row>
-    <row r="95" spans="3:3">
+    <row r="95" spans="1:16">
       <c r="C95" s="3"/>
     </row>
-    <row r="96" spans="3:3">
+    <row r="96" spans="1:16">
       <c r="C96" s="3"/>
     </row>
     <row r="97" spans="3:3">
@@ -5514,34 +5618,78 @@
     <row r="912" spans="3:3">
       <c r="C912" s="3"/>
     </row>
+    <row r="913" spans="3:3">
+      <c r="C913" s="3"/>
+    </row>
+    <row r="914" spans="3:3">
+      <c r="C914" s="3"/>
+    </row>
+    <row r="915" spans="3:3">
+      <c r="C915" s="3"/>
+    </row>
+    <row r="916" spans="3:3">
+      <c r="C916" s="3"/>
+    </row>
+    <row r="917" spans="3:3">
+      <c r="C917" s="3"/>
+    </row>
+    <row r="918" spans="3:3">
+      <c r="C918" s="3"/>
+    </row>
+    <row r="919" spans="3:3">
+      <c r="C919" s="3"/>
+    </row>
+    <row r="920" spans="3:3">
+      <c r="C920" s="3"/>
+    </row>
+    <row r="921" spans="3:3">
+      <c r="C921" s="3"/>
+    </row>
+    <row r="922" spans="3:3">
+      <c r="C922" s="3"/>
+    </row>
+    <row r="923" spans="3:3">
+      <c r="C923" s="3"/>
+    </row>
+    <row r="924" spans="3:3">
+      <c r="C924" s="3"/>
+    </row>
+    <row r="925" spans="3:3">
+      <c r="C925" s="3"/>
+    </row>
+    <row r="926" spans="3:3">
+      <c r="C926" s="3"/>
+    </row>
+    <row r="927" spans="3:3">
+      <c r="C927" s="3"/>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatRows="0" insertRows="0" insertHyperlinks="0" deleteRows="0" sort="0" autoFilter="0"/>
-  <autoFilter ref="B10:P61">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="B10:P76"/>
   <mergeCells count="1">
     <mergeCell ref="F1:P6"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="6">
-    <dataValidation allowBlank="1" showInputMessage="1" sqref="C11 C14 C17 C20 C23 C26 C29 C32 C35 C44 C53 C56 C59"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Object Code value" error="The Object code value shall be:&#10;VARIABLE&#10;RECORD&#10;ARRAY" sqref="C36 C37 C38 C39 C42 C43 C45 C46 C52 C12:C13 C15:C16 C18:C19 C21:C22 C24:C25 C27:C28 C30:C31 C33:C34 C40:C41 C47:C48 C49:C51 C54:C55 C57:C58 C60:C72">
+    <dataValidation allowBlank="1" showInputMessage="1" sqref="C11 C14 C17 C20 C23 C26 C29 C32 C35 C57 C68 C71 C74"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Object Code value" error="The Object code value shall be:_x000a_VARIABLE_x000a_RECORD_x000a_ARRAY" sqref="C12:C13 C15:C16 C18:C19 C21:C22 C24:C25 C27:C28 C30:C31 C33:C34 C58:C67 C69:C70 C72:C73 C75:C87 C36:C56">
       <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Category" error="The value for the entry category shall be &#10;M : (mandatory)&#10;O : (optional) &#10;C : (conditional)" sqref="J36 J37 J38 J39 J42 J43 J45 J46 J52 J12:J13 J15:J16 J18:J19 J21:J22 J24:J25 J27:J28 J30:J31 J33:J34 J40:J41 J47:J48 J49:J51 J54:J55 J57:J58 J60:J72">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Category" error="The value for the entry category shall be _x000a_M : (mandatory)_x000a_O : (optional) _x000a_C : (conditional)" sqref="J12:J13 J15:J16 J18:J19 J21:J22 J24:J25 J27:J28 J30:J31 J33:J34 J58:J67 J69:J70 J72:J73 J75:J87 J36:J56">
       <formula1>"M,O,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Backup/Setting Flag" error="The entry flag shall be&#10;B : (Backup)&#10;S : (Setting)" sqref="K36 K37 K38 K39 K42 K43 K45 K46 K52 K12:K13 K15:K16 K18:K19 K21:K22 K24:K25 K27:K28 K30:K31 K33:K34 K40:K41 K47:K48 K49:K51 K54:K55 K57:K58 K60:K72">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Backup/Setting Flag" error="The entry flag shall be_x000a_B : (Backup)_x000a_S : (Setting)" sqref="K12:K13 K15:K16 K18:K19 K21:K22 K24:K25 K27:K28 K30:K31 K33:K34 K58:K67 K69:K70 K72:K73 K75:K87 K36:K56">
       <formula1>"B,S"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M36:O36 M37:O37 M38:O38 M39:O39 M42:O42 M43:O43 M45:O45 M46:O46 M52:O52 M12:O13 M18:O19 M24:O25 M30:O31 M40:O41 M54:O55 M60:O61 M15:O16 M21:O22 M27:O28 M33:O34 M47:O48 M57:O58 M49:O51">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M12:O13 M18:O19 M24:O25 M30:O31 M69:O70 M75:O76 M15:O16 M21:O22 M27:O28 M33:O34 M72:O73 M58:O67 M36:O56">
       <formula1>"rx,tx"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C73:C912">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C88:C927">
       <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.236220472440945" right="0.236220472440945" top="0.748031496062992" bottom="0.748031496062992" header="0.31496062992126" footer="0.31496062992126"/>
-  <pageSetup paperSize="9" scale="61" fitToWidth="0" fitToHeight="0" orientation="landscape"/>
+  <pageMargins left="0.23622047244094499" right="0.23622047244094499" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
+  <pageSetup paperSize="9" scale="61" fitToWidth="0" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;F&amp;CPage &amp;P of &amp;N</oddFooter>
   </headerFooter>

--- a/ArmCoreV1_QSPI/SSCProject/lan9252_app.xlsx
+++ b/ArmCoreV1_QSPI/SSCProject/lan9252_app.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SI\project\RTM_ON_NEW\FW-ArmCore\ArmCoreV1_QSPI\SSCProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E71522-6154-41A7-B508-5A17479C0666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A209D8DA-B5D9-4902-9B15-B19E1D529420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-7730" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-36960" yWindow="-6180" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Profile" sheetId="11" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Profile!$B$10:$P$197</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Profile!$B$1:$P$198</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Profile!$B$10:$P$198</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Profile!$B$1:$P$199</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="214">
   <si>
     <t>Device Profile:</t>
   </si>
@@ -989,6 +989,13 @@
   <si>
     <t>OutU8_reserved2</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>OutF_gantry_velocity_prepare</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>REAL</t>
   </si>
 </sst>
 </file>
@@ -1162,9 +1169,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1175,6 +1179,9 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1481,7 +1488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T1048"/>
+  <dimension ref="A1:T1049"/>
   <sheetFormatPr defaultColWidth="10.7265625" defaultRowHeight="14" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.81640625" style="2" customWidth="1"/>
@@ -1513,19 +1520,19 @@
         <v>1</v>
       </c>
       <c r="E1" s="4"/>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
       <c r="Q1" s="20"/>
       <c r="R1" s="20"/>
       <c r="S1" s="20"/>
@@ -1541,17 +1548,17 @@
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="21"/>
-      <c r="O2" s="21"/>
-      <c r="P2" s="21"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
       <c r="Q2" s="20"/>
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
@@ -1563,17 +1570,17 @@
       <c r="C3" s="5"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
-      <c r="L3" s="21"/>
-      <c r="M3" s="21"/>
-      <c r="N3" s="21"/>
-      <c r="O3" s="21"/>
-      <c r="P3" s="21"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
       <c r="Q3" s="20"/>
       <c r="R3" s="20"/>
       <c r="S3" s="20"/>
@@ -1585,17 +1592,17 @@
       <c r="C4" s="5"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
-      <c r="N4" s="21"/>
-      <c r="O4" s="21"/>
-      <c r="P4" s="21"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
       <c r="Q4" s="20"/>
       <c r="R4" s="20"/>
       <c r="S4" s="20"/>
@@ -1607,17 +1614,17 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="21"/>
-      <c r="N5" s="21"/>
-      <c r="O5" s="21"/>
-      <c r="P5" s="21"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="26"/>
+      <c r="N5" s="26"/>
+      <c r="O5" s="26"/>
+      <c r="P5" s="26"/>
       <c r="Q5" s="20"/>
       <c r="R5" s="20"/>
       <c r="S5" s="20"/>
@@ -1629,17 +1636,17 @@
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="21"/>
-      <c r="L6" s="21"/>
-      <c r="M6" s="21"/>
-      <c r="N6" s="21"/>
-      <c r="O6" s="21"/>
-      <c r="P6" s="21"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="26"/>
+      <c r="M6" s="26"/>
+      <c r="N6" s="26"/>
+      <c r="O6" s="26"/>
+      <c r="P6" s="26"/>
       <c r="Q6" s="20"/>
       <c r="R6" s="20"/>
       <c r="S6" s="20"/>
@@ -2267,25 +2274,25 @@
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
-      <c r="D37" s="25">
+      <c r="D37" s="24">
         <v>1</v>
       </c>
-      <c r="E37" s="25" t="s">
+      <c r="E37" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F37" s="25" t="s">
+      <c r="F37" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="G37" s="23"/>
-      <c r="H37" s="23"/>
-      <c r="I37" s="23"/>
-      <c r="J37" s="24"/>
-      <c r="K37" s="24"/>
-      <c r="L37" s="24"/>
-      <c r="M37" s="24"/>
-      <c r="N37" s="24"/>
-      <c r="O37" s="24"/>
-      <c r="P37" s="22" t="s">
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="23"/>
+      <c r="K37" s="23"/>
+      <c r="L37" s="23"/>
+      <c r="M37" s="23"/>
+      <c r="N37" s="23"/>
+      <c r="O37" s="23"/>
+      <c r="P37" s="21" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2293,49 +2300,49 @@
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
-      <c r="D38" s="25">
+      <c r="D38" s="24">
         <v>2</v>
       </c>
-      <c r="E38" s="25" t="s">
+      <c r="E38" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F38" s="25" t="s">
+      <c r="F38" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="G38" s="23"/>
-      <c r="H38" s="23"/>
-      <c r="I38" s="23"/>
-      <c r="J38" s="24"/>
-      <c r="K38" s="24"/>
-      <c r="L38" s="24"/>
-      <c r="M38" s="24"/>
-      <c r="N38" s="24"/>
-      <c r="O38" s="24"/>
-      <c r="P38" s="22"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="23"/>
+      <c r="K38" s="23"/>
+      <c r="L38" s="23"/>
+      <c r="M38" s="23"/>
+      <c r="N38" s="23"/>
+      <c r="O38" s="23"/>
+      <c r="P38" s="21"/>
     </row>
     <row r="39" spans="1:16" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
-      <c r="D39" s="25">
+      <c r="D39" s="24">
         <v>3</v>
       </c>
-      <c r="E39" s="25" t="s">
+      <c r="E39" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F39" s="25" t="s">
+      <c r="F39" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="G39" s="23"/>
-      <c r="H39" s="23"/>
-      <c r="I39" s="23"/>
-      <c r="J39" s="24"/>
-      <c r="K39" s="24"/>
-      <c r="L39" s="24"/>
-      <c r="M39" s="24"/>
-      <c r="N39" s="24"/>
-      <c r="O39" s="24"/>
-      <c r="P39" s="22" t="s">
+      <c r="G39" s="22"/>
+      <c r="H39" s="22"/>
+      <c r="I39" s="22"/>
+      <c r="J39" s="23"/>
+      <c r="K39" s="23"/>
+      <c r="L39" s="23"/>
+      <c r="M39" s="23"/>
+      <c r="N39" s="23"/>
+      <c r="O39" s="23"/>
+      <c r="P39" s="21" t="s">
         <v>56</v>
       </c>
     </row>
@@ -2343,13 +2350,13 @@
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
-      <c r="D40" s="25">
+      <c r="D40" s="24">
         <v>4</v>
       </c>
-      <c r="E40" s="25" t="s">
+      <c r="E40" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F40" s="25" t="s">
+      <c r="F40" s="24" t="s">
         <v>63</v>
       </c>
       <c r="G40" s="11"/>
@@ -2369,13 +2376,13 @@
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
-      <c r="D41" s="25">
+      <c r="D41" s="24">
         <v>5</v>
       </c>
-      <c r="E41" s="25" t="s">
+      <c r="E41" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F41" s="25" t="s">
+      <c r="F41" s="24" t="s">
         <v>192</v>
       </c>
       <c r="G41" s="11"/>
@@ -2393,13 +2400,13 @@
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
-      <c r="D42" s="25">
+      <c r="D42" s="24">
         <v>6</v>
       </c>
-      <c r="E42" s="25" t="s">
+      <c r="E42" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="F42" s="25" t="s">
+      <c r="F42" s="24" t="s">
         <v>64</v>
       </c>
       <c r="G42" s="11"/>
@@ -2417,13 +2424,13 @@
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
-      <c r="D43" s="25">
+      <c r="D43" s="24">
         <v>7</v>
       </c>
-      <c r="E43" s="25" t="s">
+      <c r="E43" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F43" s="25" t="s">
+      <c r="F43" s="24" t="s">
         <v>65</v>
       </c>
       <c r="G43" s="11"/>
@@ -2441,13 +2448,13 @@
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
-      <c r="D44" s="25">
+      <c r="D44" s="24">
         <v>8</v>
       </c>
-      <c r="E44" s="25" t="s">
+      <c r="E44" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F44" s="25" t="s">
+      <c r="F44" s="24" t="s">
         <v>66</v>
       </c>
       <c r="G44" s="11"/>
@@ -2465,13 +2472,13 @@
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
-      <c r="D45" s="25">
+      <c r="D45" s="24">
         <v>9</v>
       </c>
-      <c r="E45" s="25" t="s">
+      <c r="E45" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="F45" s="25" t="s">
+      <c r="F45" s="24" t="s">
         <v>193</v>
       </c>
       <c r="G45" s="11"/>
@@ -2489,13 +2496,13 @@
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
-      <c r="D46" s="25">
+      <c r="D46" s="24">
         <v>10</v>
       </c>
-      <c r="E46" s="25" t="s">
+      <c r="E46" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F46" s="25" t="s">
+      <c r="F46" s="24" t="s">
         <v>67</v>
       </c>
       <c r="G46" s="11"/>
@@ -2513,13 +2520,13 @@
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
-      <c r="D47" s="25">
+      <c r="D47" s="24">
         <v>11</v>
       </c>
-      <c r="E47" s="25" t="s">
+      <c r="E47" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F47" s="25" t="s">
+      <c r="F47" s="24" t="s">
         <v>194</v>
       </c>
       <c r="G47" s="11"/>
@@ -2537,13 +2544,13 @@
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
-      <c r="D48" s="25">
+      <c r="D48" s="24">
         <v>12</v>
       </c>
-      <c r="E48" s="25" t="s">
+      <c r="E48" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="F48" s="25" t="s">
+      <c r="F48" s="24" t="s">
         <v>68</v>
       </c>
       <c r="G48" s="11"/>
@@ -2561,13 +2568,13 @@
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
-      <c r="D49" s="25">
+      <c r="D49" s="24">
         <v>13</v>
       </c>
-      <c r="E49" s="25" t="s">
+      <c r="E49" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F49" s="25" t="s">
+      <c r="F49" s="24" t="s">
         <v>69</v>
       </c>
       <c r="G49" s="11"/>
@@ -2585,13 +2592,13 @@
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
-      <c r="D50" s="25">
+      <c r="D50" s="24">
         <v>14</v>
       </c>
-      <c r="E50" s="25" t="s">
+      <c r="E50" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F50" s="25" t="s">
+      <c r="F50" s="24" t="s">
         <v>70</v>
       </c>
       <c r="G50" s="11"/>
@@ -2609,13 +2616,13 @@
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
-      <c r="D51" s="25">
+      <c r="D51" s="24">
         <v>15</v>
       </c>
-      <c r="E51" s="25" t="s">
+      <c r="E51" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F51" s="25" t="s">
+      <c r="F51" s="24" t="s">
         <v>71</v>
       </c>
       <c r="G51" s="11"/>
@@ -2633,13 +2640,13 @@
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
-      <c r="D52" s="25">
+      <c r="D52" s="24">
         <v>16</v>
       </c>
-      <c r="E52" s="25" t="s">
+      <c r="E52" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F52" s="25" t="s">
+      <c r="F52" s="24" t="s">
         <v>72</v>
       </c>
       <c r="G52" s="11"/>
@@ -2657,13 +2664,13 @@
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
-      <c r="D53" s="25">
+      <c r="D53" s="24">
         <v>17</v>
       </c>
-      <c r="E53" s="25" t="s">
+      <c r="E53" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F53" s="25" t="s">
+      <c r="F53" s="24" t="s">
         <v>73</v>
       </c>
       <c r="G53" s="11"/>
@@ -2681,13 +2688,13 @@
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
-      <c r="D54" s="25">
+      <c r="D54" s="24">
         <v>18</v>
       </c>
-      <c r="E54" s="25" t="s">
+      <c r="E54" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F54" s="25" t="s">
+      <c r="F54" s="24" t="s">
         <v>74</v>
       </c>
       <c r="G54" s="11"/>
@@ -2705,13 +2712,13 @@
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
-      <c r="D55" s="25">
+      <c r="D55" s="24">
         <v>19</v>
       </c>
-      <c r="E55" s="25" t="s">
+      <c r="E55" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="F55" s="25" t="s">
+      <c r="F55" s="24" t="s">
         <v>195</v>
       </c>
       <c r="G55" s="11"/>
@@ -2729,13 +2736,13 @@
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
-      <c r="D56" s="25">
+      <c r="D56" s="24">
         <v>20</v>
       </c>
-      <c r="E56" s="25" t="s">
+      <c r="E56" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F56" s="25" t="s">
+      <c r="F56" s="24" t="s">
         <v>75</v>
       </c>
       <c r="G56" s="11"/>
@@ -2753,13 +2760,13 @@
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
-      <c r="D57" s="25">
+      <c r="D57" s="24">
         <v>21</v>
       </c>
-      <c r="E57" s="25" t="s">
+      <c r="E57" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F57" s="25" t="s">
+      <c r="F57" s="24" t="s">
         <v>196</v>
       </c>
       <c r="G57" s="11"/>
@@ -2777,13 +2784,13 @@
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
-      <c r="D58" s="25">
+      <c r="D58" s="24">
         <v>22</v>
       </c>
-      <c r="E58" s="25" t="s">
+      <c r="E58" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="F58" s="25" t="s">
+      <c r="F58" s="24" t="s">
         <v>76</v>
       </c>
       <c r="G58" s="11"/>
@@ -2801,13 +2808,13 @@
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
-      <c r="D59" s="25">
+      <c r="D59" s="24">
         <v>23</v>
       </c>
-      <c r="E59" s="25" t="s">
+      <c r="E59" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F59" s="25" t="s">
+      <c r="F59" s="24" t="s">
         <v>77</v>
       </c>
       <c r="G59" s="11"/>
@@ -2825,13 +2832,13 @@
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
-      <c r="D60" s="25">
+      <c r="D60" s="24">
         <v>24</v>
       </c>
-      <c r="E60" s="25" t="s">
+      <c r="E60" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F60" s="25" t="s">
+      <c r="F60" s="24" t="s">
         <v>78</v>
       </c>
       <c r="G60" s="11"/>
@@ -2849,13 +2856,13 @@
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
-      <c r="D61" s="25">
+      <c r="D61" s="24">
         <v>25</v>
       </c>
-      <c r="E61" s="25" t="s">
+      <c r="E61" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F61" s="25" t="s">
+      <c r="F61" s="24" t="s">
         <v>79</v>
       </c>
       <c r="G61" s="11"/>
@@ -2873,13 +2880,13 @@
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
-      <c r="D62" s="25">
+      <c r="D62" s="24">
         <v>26</v>
       </c>
-      <c r="E62" s="25" t="s">
+      <c r="E62" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F62" s="25" t="s">
+      <c r="F62" s="24" t="s">
         <v>80</v>
       </c>
       <c r="G62" s="11"/>
@@ -2897,13 +2904,13 @@
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
-      <c r="D63" s="25">
+      <c r="D63" s="24">
         <v>27</v>
       </c>
-      <c r="E63" s="26" t="s">
+      <c r="E63" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="F63" s="26" t="s">
+      <c r="F63" s="25" t="s">
         <v>81</v>
       </c>
       <c r="G63" s="11"/>
@@ -2921,13 +2928,13 @@
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
-      <c r="D64" s="25">
+      <c r="D64" s="24">
         <v>28</v>
       </c>
-      <c r="E64" s="26" t="s">
+      <c r="E64" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="F64" s="26" t="s">
+      <c r="F64" s="25" t="s">
         <v>82</v>
       </c>
       <c r="G64" s="11"/>
@@ -2945,13 +2952,13 @@
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
-      <c r="D65" s="25">
+      <c r="D65" s="24">
         <v>29</v>
       </c>
-      <c r="E65" s="25" t="s">
+      <c r="E65" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="F65" s="25" t="s">
+      <c r="F65" s="24" t="s">
         <v>197</v>
       </c>
       <c r="G65" s="11"/>
@@ -2969,13 +2976,13 @@
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
-      <c r="D66" s="25">
+      <c r="D66" s="24">
         <v>30</v>
       </c>
-      <c r="E66" s="26" t="s">
+      <c r="E66" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="F66" s="26" t="s">
+      <c r="F66" s="25" t="s">
         <v>83</v>
       </c>
       <c r="G66" s="11"/>
@@ -2993,13 +3000,13 @@
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
-      <c r="D67" s="25">
+      <c r="D67" s="24">
         <v>31</v>
       </c>
-      <c r="E67" s="26" t="s">
+      <c r="E67" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="F67" s="26" t="s">
+      <c r="F67" s="25" t="s">
         <v>198</v>
       </c>
       <c r="G67" s="11"/>
@@ -3017,13 +3024,13 @@
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
-      <c r="D68" s="25">
+      <c r="D68" s="24">
         <v>32</v>
       </c>
-      <c r="E68" s="26" t="s">
+      <c r="E68" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="F68" s="26" t="s">
+      <c r="F68" s="25" t="s">
         <v>84</v>
       </c>
       <c r="G68" s="11"/>
@@ -3041,13 +3048,13 @@
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
-      <c r="D69" s="25">
+      <c r="D69" s="24">
         <v>33</v>
       </c>
-      <c r="E69" s="26" t="s">
+      <c r="E69" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="F69" s="26" t="s">
+      <c r="F69" s="25" t="s">
         <v>85</v>
       </c>
       <c r="G69" s="11"/>
@@ -3065,13 +3072,13 @@
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
-      <c r="D70" s="25">
+      <c r="D70" s="24">
         <v>34</v>
       </c>
-      <c r="E70" s="26" t="s">
+      <c r="E70" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="F70" s="26" t="s">
+      <c r="F70" s="25" t="s">
         <v>86</v>
       </c>
       <c r="G70" s="11"/>
@@ -3089,13 +3096,13 @@
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
-      <c r="D71" s="25">
+      <c r="D71" s="24">
         <v>35</v>
       </c>
-      <c r="E71" s="26" t="s">
+      <c r="E71" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="F71" s="26" t="s">
+      <c r="F71" s="25" t="s">
         <v>87</v>
       </c>
       <c r="G71" s="11"/>
@@ -3113,13 +3120,13 @@
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
-      <c r="D72" s="25">
+      <c r="D72" s="24">
         <v>36</v>
       </c>
-      <c r="E72" s="26" t="s">
+      <c r="E72" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="F72" s="26" t="s">
+      <c r="F72" s="25" t="s">
         <v>88</v>
       </c>
       <c r="G72" s="11"/>
@@ -3137,13 +3144,13 @@
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
-      <c r="D73" s="25">
+      <c r="D73" s="24">
         <v>37</v>
       </c>
-      <c r="E73" s="25" t="s">
+      <c r="E73" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="F73" s="26" t="s">
+      <c r="F73" s="25" t="s">
         <v>90</v>
       </c>
       <c r="G73" s="11"/>
@@ -3161,13 +3168,13 @@
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
-      <c r="D74" s="25">
+      <c r="D74" s="24">
         <v>38</v>
       </c>
-      <c r="E74" s="25" t="s">
+      <c r="E74" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="F74" s="26" t="s">
+      <c r="F74" s="25" t="s">
         <v>91</v>
       </c>
       <c r="G74" s="11"/>
@@ -3185,13 +3192,13 @@
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
-      <c r="D75" s="25">
+      <c r="D75" s="24">
         <v>39</v>
       </c>
-      <c r="E75" s="25" t="s">
+      <c r="E75" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="F75" s="26" t="s">
+      <c r="F75" s="25" t="s">
         <v>92</v>
       </c>
       <c r="G75" s="11"/>
@@ -3209,13 +3216,13 @@
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
-      <c r="D76" s="25">
+      <c r="D76" s="24">
         <v>40</v>
       </c>
-      <c r="E76" s="25" t="s">
+      <c r="E76" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F76" s="26" t="s">
+      <c r="F76" s="25" t="s">
         <v>93</v>
       </c>
       <c r="G76" s="11"/>
@@ -3233,13 +3240,13 @@
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
-      <c r="D77" s="25">
+      <c r="D77" s="24">
         <v>41</v>
       </c>
-      <c r="E77" s="25" t="s">
+      <c r="E77" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F77" s="26" t="s">
+      <c r="F77" s="25" t="s">
         <v>199</v>
       </c>
       <c r="G77" s="11"/>
@@ -3257,13 +3264,13 @@
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
-      <c r="D78" s="25">
+      <c r="D78" s="24">
         <v>42</v>
       </c>
-      <c r="E78" s="25" t="s">
+      <c r="E78" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F78" s="26" t="s">
+      <c r="F78" s="25" t="s">
         <v>94</v>
       </c>
       <c r="G78" s="11"/>
@@ -3281,13 +3288,13 @@
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
-      <c r="D79" s="25">
+      <c r="D79" s="24">
         <v>43</v>
       </c>
-      <c r="E79" s="25" t="s">
+      <c r="E79" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="F79" s="26" t="s">
+      <c r="F79" s="25" t="s">
         <v>95</v>
       </c>
       <c r="G79" s="11"/>
@@ -3305,13 +3312,13 @@
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
-      <c r="D80" s="25">
+      <c r="D80" s="24">
         <v>44</v>
       </c>
-      <c r="E80" s="25" t="s">
+      <c r="E80" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="F80" s="26" t="s">
+      <c r="F80" s="25" t="s">
         <v>96</v>
       </c>
       <c r="G80" s="11"/>
@@ -3329,13 +3336,13 @@
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
-      <c r="D81" s="25">
+      <c r="D81" s="24">
         <v>45</v>
       </c>
-      <c r="E81" s="25" t="s">
+      <c r="E81" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F81" s="26" t="s">
+      <c r="F81" s="25" t="s">
         <v>97</v>
       </c>
       <c r="G81" s="11"/>
@@ -3353,13 +3360,13 @@
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
-      <c r="D82" s="25">
+      <c r="D82" s="24">
         <v>46</v>
       </c>
-      <c r="E82" s="25" t="s">
+      <c r="E82" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F82" s="26" t="s">
+      <c r="F82" s="25" t="s">
         <v>200</v>
       </c>
       <c r="G82" s="11"/>
@@ -3377,13 +3384,13 @@
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
-      <c r="D83" s="25">
+      <c r="D83" s="24">
         <v>47</v>
       </c>
-      <c r="E83" s="25" t="s">
+      <c r="E83" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F83" s="26" t="s">
+      <c r="F83" s="25" t="s">
         <v>98</v>
       </c>
       <c r="G83" s="11"/>
@@ -3401,13 +3408,13 @@
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
-      <c r="D84" s="25">
+      <c r="D84" s="24">
         <v>48</v>
       </c>
-      <c r="E84" s="25" t="s">
+      <c r="E84" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F84" s="26" t="s">
+      <c r="F84" s="25" t="s">
         <v>99</v>
       </c>
       <c r="G84" s="11"/>
@@ -3425,13 +3432,13 @@
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
-      <c r="D85" s="25">
+      <c r="D85" s="24">
         <v>49</v>
       </c>
-      <c r="E85" s="25" t="s">
+      <c r="E85" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="F85" s="26" t="s">
+      <c r="F85" s="25" t="s">
         <v>100</v>
       </c>
       <c r="G85" s="11"/>
@@ -3449,13 +3456,13 @@
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
-      <c r="D86" s="25">
+      <c r="D86" s="24">
         <v>50</v>
       </c>
-      <c r="E86" s="25" t="s">
+      <c r="E86" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F86" s="25" t="s">
+      <c r="F86" s="24" t="s">
         <v>101</v>
       </c>
       <c r="G86" s="11"/>
@@ -3473,13 +3480,13 @@
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
-      <c r="D87" s="25">
+      <c r="D87" s="24">
         <v>51</v>
       </c>
-      <c r="E87" s="25" t="s">
+      <c r="E87" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F87" s="25" t="s">
+      <c r="F87" s="24" t="s">
         <v>102</v>
       </c>
       <c r="G87" s="11"/>
@@ -3497,13 +3504,13 @@
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
-      <c r="D88" s="25">
+      <c r="D88" s="24">
         <v>52</v>
       </c>
-      <c r="E88" s="25" t="s">
+      <c r="E88" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="F88" s="25" t="s">
+      <c r="F88" s="24" t="s">
         <v>201</v>
       </c>
       <c r="G88" s="11"/>
@@ -3521,13 +3528,13 @@
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
-      <c r="D89" s="25">
+      <c r="D89" s="24">
         <v>53</v>
       </c>
-      <c r="E89" s="25" t="s">
+      <c r="E89" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F89" s="25" t="s">
+      <c r="F89" s="24" t="s">
         <v>103</v>
       </c>
       <c r="G89" s="11"/>
@@ -3545,13 +3552,13 @@
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
-      <c r="D90" s="25">
+      <c r="D90" s="24">
         <v>54</v>
       </c>
-      <c r="E90" s="25" t="s">
+      <c r="E90" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F90" s="25" t="s">
+      <c r="F90" s="24" t="s">
         <v>202</v>
       </c>
       <c r="G90" s="11"/>
@@ -3569,13 +3576,13 @@
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
-      <c r="D91" s="25">
+      <c r="D91" s="24">
         <v>55</v>
       </c>
-      <c r="E91" s="25" t="s">
+      <c r="E91" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="F91" s="25" t="s">
+      <c r="F91" s="24" t="s">
         <v>104</v>
       </c>
       <c r="G91" s="11"/>
@@ -3593,13 +3600,13 @@
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
-      <c r="D92" s="25">
+      <c r="D92" s="24">
         <v>56</v>
       </c>
-      <c r="E92" s="25" t="s">
+      <c r="E92" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F92" s="25" t="s">
+      <c r="F92" s="24" t="s">
         <v>105</v>
       </c>
       <c r="G92" s="11"/>
@@ -3617,13 +3624,13 @@
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
-      <c r="D93" s="25">
+      <c r="D93" s="24">
         <v>57</v>
       </c>
-      <c r="E93" s="25" t="s">
+      <c r="E93" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F93" s="25" t="s">
+      <c r="F93" s="24" t="s">
         <v>106</v>
       </c>
       <c r="G93" s="11"/>
@@ -3641,13 +3648,13 @@
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
-      <c r="D94" s="25">
+      <c r="D94" s="24">
         <v>58</v>
       </c>
-      <c r="E94" s="25" t="s">
+      <c r="E94" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F94" s="25" t="s">
+      <c r="F94" s="24" t="s">
         <v>107</v>
       </c>
       <c r="G94" s="11"/>
@@ -3665,13 +3672,13 @@
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
-      <c r="D95" s="25">
+      <c r="D95" s="24">
         <v>59</v>
       </c>
-      <c r="E95" s="25" t="s">
+      <c r="E95" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F95" s="25" t="s">
+      <c r="F95" s="24" t="s">
         <v>108</v>
       </c>
       <c r="G95" s="11"/>
@@ -3689,13 +3696,13 @@
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
-      <c r="D96" s="25">
+      <c r="D96" s="24">
         <v>60</v>
       </c>
-      <c r="E96" s="25" t="s">
+      <c r="E96" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F96" s="25" t="s">
+      <c r="F96" s="24" t="s">
         <v>109</v>
       </c>
       <c r="G96" s="11"/>
@@ -3713,13 +3720,13 @@
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
-      <c r="D97" s="25">
+      <c r="D97" s="24">
         <v>61</v>
       </c>
-      <c r="E97" s="25" t="s">
+      <c r="E97" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F97" s="25" t="s">
+      <c r="F97" s="24" t="s">
         <v>110</v>
       </c>
       <c r="G97" s="11"/>
@@ -3737,13 +3744,13 @@
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
-      <c r="D98" s="25">
+      <c r="D98" s="24">
         <v>62</v>
       </c>
-      <c r="E98" s="25" t="s">
+      <c r="E98" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="F98" s="25" t="s">
+      <c r="F98" s="24" t="s">
         <v>203</v>
       </c>
       <c r="G98" s="11"/>
@@ -3761,13 +3768,13 @@
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
-      <c r="D99" s="25">
+      <c r="D99" s="24">
         <v>63</v>
       </c>
-      <c r="E99" s="25" t="s">
+      <c r="E99" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F99" s="25" t="s">
+      <c r="F99" s="24" t="s">
         <v>111</v>
       </c>
       <c r="G99" s="11"/>
@@ -3785,13 +3792,13 @@
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
-      <c r="D100" s="25">
+      <c r="D100" s="24">
         <v>64</v>
       </c>
-      <c r="E100" s="25" t="s">
+      <c r="E100" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F100" s="25" t="s">
+      <c r="F100" s="24" t="s">
         <v>204</v>
       </c>
       <c r="G100" s="11"/>
@@ -3809,13 +3816,13 @@
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
-      <c r="D101" s="25">
+      <c r="D101" s="24">
         <v>65</v>
       </c>
-      <c r="E101" s="25" t="s">
+      <c r="E101" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="F101" s="25" t="s">
+      <c r="F101" s="24" t="s">
         <v>112</v>
       </c>
       <c r="G101" s="11"/>
@@ -3833,13 +3840,13 @@
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
-      <c r="D102" s="25">
+      <c r="D102" s="24">
         <v>66</v>
       </c>
-      <c r="E102" s="25" t="s">
+      <c r="E102" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F102" s="25" t="s">
+      <c r="F102" s="24" t="s">
         <v>113</v>
       </c>
       <c r="G102" s="11"/>
@@ -3857,13 +3864,13 @@
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
-      <c r="D103" s="25">
+      <c r="D103" s="24">
         <v>67</v>
       </c>
-      <c r="E103" s="25" t="s">
+      <c r="E103" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F103" s="25" t="s">
+      <c r="F103" s="24" t="s">
         <v>114</v>
       </c>
       <c r="G103" s="11"/>
@@ -3881,13 +3888,13 @@
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
-      <c r="D104" s="25">
+      <c r="D104" s="24">
         <v>68</v>
       </c>
-      <c r="E104" s="25" t="s">
+      <c r="E104" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F104" s="25" t="s">
+      <c r="F104" s="24" t="s">
         <v>115</v>
       </c>
       <c r="G104" s="11"/>
@@ -3905,13 +3912,13 @@
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
-      <c r="D105" s="25">
+      <c r="D105" s="24">
         <v>69</v>
       </c>
-      <c r="E105" s="25" t="s">
+      <c r="E105" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F105" s="25" t="s">
+      <c r="F105" s="24" t="s">
         <v>116</v>
       </c>
       <c r="G105" s="11"/>
@@ -3929,13 +3936,13 @@
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
-      <c r="D106" s="25">
+      <c r="D106" s="24">
         <v>70</v>
       </c>
-      <c r="E106" s="25" t="s">
+      <c r="E106" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F106" s="25" t="s">
+      <c r="F106" s="24" t="s">
         <v>117</v>
       </c>
       <c r="G106" s="11"/>
@@ -3953,13 +3960,13 @@
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
-      <c r="D107" s="25">
+      <c r="D107" s="24">
         <v>71</v>
       </c>
-      <c r="E107" s="25" t="s">
+      <c r="E107" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F107" s="25" t="s">
+      <c r="F107" s="24" t="s">
         <v>118</v>
       </c>
       <c r="G107" s="11"/>
@@ -3977,13 +3984,13 @@
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
-      <c r="D108" s="25">
+      <c r="D108" s="24">
         <v>72</v>
       </c>
-      <c r="E108" s="25" t="s">
+      <c r="E108" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="F108" s="25" t="s">
+      <c r="F108" s="24" t="s">
         <v>205</v>
       </c>
       <c r="G108" s="11"/>
@@ -4001,13 +4008,13 @@
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
-      <c r="D109" s="25">
+      <c r="D109" s="24">
         <v>73</v>
       </c>
-      <c r="E109" s="25" t="s">
+      <c r="E109" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F109" s="25" t="s">
+      <c r="F109" s="24" t="s">
         <v>119</v>
       </c>
       <c r="G109" s="11"/>
@@ -4025,13 +4032,13 @@
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
-      <c r="D110" s="25">
+      <c r="D110" s="24">
         <v>74</v>
       </c>
-      <c r="E110" s="25" t="s">
+      <c r="E110" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F110" s="25" t="s">
+      <c r="F110" s="24" t="s">
         <v>206</v>
       </c>
       <c r="G110" s="11"/>
@@ -4049,13 +4056,13 @@
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
-      <c r="D111" s="25">
+      <c r="D111" s="24">
         <v>75</v>
       </c>
-      <c r="E111" s="25" t="s">
+      <c r="E111" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="F111" s="25" t="s">
+      <c r="F111" s="24" t="s">
         <v>120</v>
       </c>
       <c r="G111" s="11"/>
@@ -4073,13 +4080,13 @@
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
-      <c r="D112" s="25">
+      <c r="D112" s="24">
         <v>76</v>
       </c>
-      <c r="E112" s="25" t="s">
+      <c r="E112" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F112" s="25" t="s">
+      <c r="F112" s="24" t="s">
         <v>121</v>
       </c>
       <c r="G112" s="11"/>
@@ -4097,13 +4104,13 @@
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
-      <c r="D113" s="25">
+      <c r="D113" s="24">
         <v>77</v>
       </c>
-      <c r="E113" s="25" t="s">
+      <c r="E113" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F113" s="25" t="s">
+      <c r="F113" s="24" t="s">
         <v>122</v>
       </c>
       <c r="G113" s="11"/>
@@ -4121,13 +4128,13 @@
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
-      <c r="D114" s="25">
+      <c r="D114" s="24">
         <v>78</v>
       </c>
-      <c r="E114" s="25" t="s">
+      <c r="E114" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F114" s="25" t="s">
+      <c r="F114" s="24" t="s">
         <v>123</v>
       </c>
       <c r="G114" s="11"/>
@@ -4145,13 +4152,13 @@
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
-      <c r="D115" s="25">
+      <c r="D115" s="24">
         <v>79</v>
       </c>
-      <c r="E115" s="25" t="s">
+      <c r="E115" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F115" s="25" t="s">
+      <c r="F115" s="24" t="s">
         <v>124</v>
       </c>
       <c r="G115" s="11"/>
@@ -4169,13 +4176,13 @@
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
-      <c r="D116" s="25">
+      <c r="D116" s="24">
         <v>80</v>
       </c>
-      <c r="E116" s="25" t="s">
+      <c r="E116" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F116" s="25" t="s">
+      <c r="F116" s="24" t="s">
         <v>125</v>
       </c>
       <c r="G116" s="11"/>
@@ -4193,13 +4200,13 @@
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
-      <c r="D117" s="25">
+      <c r="D117" s="24">
         <v>81</v>
       </c>
-      <c r="E117" s="25" t="s">
+      <c r="E117" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="F117" s="25" t="s">
+      <c r="F117" s="24" t="s">
         <v>126</v>
       </c>
       <c r="G117" s="11"/>
@@ -4217,13 +4224,13 @@
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
-      <c r="D118" s="25">
+      <c r="D118" s="24">
         <v>82</v>
       </c>
-      <c r="E118" s="25" t="s">
+      <c r="E118" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="F118" s="25" t="s">
+      <c r="F118" s="24" t="s">
         <v>127</v>
       </c>
       <c r="G118" s="11"/>
@@ -4241,13 +4248,13 @@
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
-      <c r="D119" s="25">
+      <c r="D119" s="24">
         <v>83</v>
       </c>
-      <c r="E119" s="25" t="s">
+      <c r="E119" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F119" s="25" t="s">
+      <c r="F119" s="24" t="s">
         <v>128</v>
       </c>
       <c r="G119" s="11"/>
@@ -4265,13 +4272,13 @@
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
-      <c r="D120" s="25">
+      <c r="D120" s="24">
         <v>84</v>
       </c>
-      <c r="E120" s="25" t="s">
+      <c r="E120" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F120" s="25" t="s">
+      <c r="F120" s="24" t="s">
         <v>129</v>
       </c>
       <c r="G120" s="11"/>
@@ -4289,13 +4296,13 @@
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
-      <c r="D121" s="25">
+      <c r="D121" s="24">
         <v>85</v>
       </c>
-      <c r="E121" s="25" t="s">
+      <c r="E121" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="F121" s="25" t="s">
+      <c r="F121" s="24" t="s">
         <v>207</v>
       </c>
       <c r="G121" s="11"/>
@@ -4313,13 +4320,13 @@
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
-      <c r="D122" s="25">
+      <c r="D122" s="24">
         <v>86</v>
       </c>
-      <c r="E122" s="25" t="s">
+      <c r="E122" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F122" s="25" t="s">
+      <c r="F122" s="24" t="s">
         <v>130</v>
       </c>
       <c r="G122" s="11"/>
@@ -4337,13 +4344,13 @@
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
-      <c r="D123" s="25">
+      <c r="D123" s="24">
         <v>87</v>
       </c>
-      <c r="E123" s="25" t="s">
+      <c r="E123" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F123" s="25" t="s">
+      <c r="F123" s="24" t="s">
         <v>208</v>
       </c>
       <c r="G123" s="11"/>
@@ -4361,13 +4368,13 @@
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
-      <c r="D124" s="25">
+      <c r="D124" s="24">
         <v>88</v>
       </c>
-      <c r="E124" s="25" t="s">
+      <c r="E124" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="F124" s="25" t="s">
+      <c r="F124" s="24" t="s">
         <v>131</v>
       </c>
       <c r="G124" s="11"/>
@@ -4385,13 +4392,13 @@
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
-      <c r="D125" s="25">
+      <c r="D125" s="24">
         <v>89</v>
       </c>
-      <c r="E125" s="25" t="s">
+      <c r="E125" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F125" s="25" t="s">
+      <c r="F125" s="24" t="s">
         <v>132</v>
       </c>
       <c r="G125" s="11"/>
@@ -4409,13 +4416,13 @@
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
-      <c r="D126" s="25">
+      <c r="D126" s="24">
         <v>90</v>
       </c>
-      <c r="E126" s="25" t="s">
+      <c r="E126" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F126" s="25" t="s">
+      <c r="F126" s="24" t="s">
         <v>133</v>
       </c>
       <c r="G126" s="11"/>
@@ -4433,13 +4440,13 @@
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
-      <c r="D127" s="25">
+      <c r="D127" s="24">
         <v>91</v>
       </c>
-      <c r="E127" s="25" t="s">
+      <c r="E127" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F127" s="25" t="s">
+      <c r="F127" s="24" t="s">
         <v>134</v>
       </c>
       <c r="G127" s="11"/>
@@ -4457,13 +4464,13 @@
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
-      <c r="D128" s="25">
+      <c r="D128" s="24">
         <v>92</v>
       </c>
-      <c r="E128" s="25" t="s">
+      <c r="E128" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F128" s="25" t="s">
+      <c r="F128" s="24" t="s">
         <v>135</v>
       </c>
       <c r="G128" s="11"/>
@@ -4481,13 +4488,13 @@
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
-      <c r="D129" s="25">
+      <c r="D129" s="24">
         <v>93</v>
       </c>
-      <c r="E129" s="25" t="s">
+      <c r="E129" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F129" s="25" t="s">
+      <c r="F129" s="24" t="s">
         <v>136</v>
       </c>
       <c r="G129" s="11"/>
@@ -4505,13 +4512,13 @@
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
-      <c r="D130" s="25">
+      <c r="D130" s="24">
         <v>94</v>
       </c>
-      <c r="E130" s="25" t="s">
+      <c r="E130" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="F130" s="25" t="s">
+      <c r="F130" s="24" t="s">
         <v>137</v>
       </c>
       <c r="G130" s="11"/>
@@ -4529,13 +4536,13 @@
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
-      <c r="D131" s="25">
+      <c r="D131" s="24">
         <v>95</v>
       </c>
-      <c r="E131" s="25" t="s">
+      <c r="E131" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="F131" s="25" t="s">
+      <c r="F131" s="24" t="s">
         <v>138</v>
       </c>
       <c r="G131" s="11"/>
@@ -4553,13 +4560,13 @@
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
-      <c r="D132" s="25">
+      <c r="D132" s="24">
         <v>96</v>
       </c>
-      <c r="E132" s="25" t="s">
+      <c r="E132" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="F132" s="25" t="s">
+      <c r="F132" s="24" t="s">
         <v>139</v>
       </c>
       <c r="G132" s="11"/>
@@ -4577,13 +4584,13 @@
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
-      <c r="D133" s="25">
+      <c r="D133" s="24">
         <v>97</v>
       </c>
-      <c r="E133" s="25" t="s">
+      <c r="E133" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="F133" s="25" t="s">
+      <c r="F133" s="24" t="s">
         <v>140</v>
       </c>
       <c r="G133" s="11"/>
@@ -4601,13 +4608,13 @@
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
-      <c r="D134" s="25">
+      <c r="D134" s="24">
         <v>98</v>
       </c>
-      <c r="E134" s="25" t="s">
+      <c r="E134" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="F134" s="25" t="s">
+      <c r="F134" s="24" t="s">
         <v>141</v>
       </c>
       <c r="G134" s="11"/>
@@ -4625,13 +4632,13 @@
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
-      <c r="D135" s="25">
+      <c r="D135" s="24">
         <v>99</v>
       </c>
-      <c r="E135" s="25" t="s">
+      <c r="E135" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="F135" s="25" t="s">
+      <c r="F135" s="24" t="s">
         <v>142</v>
       </c>
       <c r="G135" s="11"/>
@@ -4649,13 +4656,13 @@
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
-      <c r="D136" s="25">
+      <c r="D136" s="24">
         <v>100</v>
       </c>
-      <c r="E136" s="25" t="s">
+      <c r="E136" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="F136" s="25" t="s">
+      <c r="F136" s="24" t="s">
         <v>143</v>
       </c>
       <c r="G136" s="11"/>
@@ -4673,13 +4680,13 @@
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
-      <c r="D137" s="25">
+      <c r="D137" s="24">
         <v>101</v>
       </c>
-      <c r="E137" s="25" t="s">
+      <c r="E137" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="F137" s="25" t="s">
+      <c r="F137" s="24" t="s">
         <v>144</v>
       </c>
       <c r="G137" s="11"/>
@@ -4697,13 +4704,13 @@
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
-      <c r="D138" s="25">
+      <c r="D138" s="24">
         <v>102</v>
       </c>
-      <c r="E138" s="25" t="s">
+      <c r="E138" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="F138" s="25" t="s">
+      <c r="F138" s="24" t="s">
         <v>145</v>
       </c>
       <c r="G138" s="11"/>
@@ -4721,13 +4728,13 @@
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
-      <c r="D139" s="25">
+      <c r="D139" s="24">
         <v>103</v>
       </c>
-      <c r="E139" s="25" t="s">
+      <c r="E139" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="F139" s="25" t="s">
+      <c r="F139" s="24" t="s">
         <v>146</v>
       </c>
       <c r="G139" s="11"/>
@@ -4745,13 +4752,13 @@
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
-      <c r="D140" s="25">
+      <c r="D140" s="24">
         <v>104</v>
       </c>
-      <c r="E140" s="25" t="s">
+      <c r="E140" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="F140" s="25" t="s">
+      <c r="F140" s="24" t="s">
         <v>147</v>
       </c>
       <c r="G140" s="11"/>
@@ -4769,13 +4776,13 @@
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
-      <c r="D141" s="25">
+      <c r="D141" s="24">
         <v>105</v>
       </c>
-      <c r="E141" s="25" t="s">
+      <c r="E141" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="F141" s="25" t="s">
+      <c r="F141" s="24" t="s">
         <v>148</v>
       </c>
       <c r="G141" s="11"/>
@@ -4793,13 +4800,13 @@
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
-      <c r="D142" s="25">
+      <c r="D142" s="24">
         <v>106</v>
       </c>
-      <c r="E142" s="25" t="s">
+      <c r="E142" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="F142" s="25" t="s">
+      <c r="F142" s="24" t="s">
         <v>149</v>
       </c>
       <c r="G142" s="11"/>
@@ -4817,13 +4824,13 @@
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
-      <c r="D143" s="25">
+      <c r="D143" s="24">
         <v>107</v>
       </c>
-      <c r="E143" s="25" t="s">
+      <c r="E143" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F143" s="25" t="s">
+      <c r="F143" s="24" t="s">
         <v>150</v>
       </c>
       <c r="G143" s="11"/>
@@ -4890,10 +4897,10 @@
       <c r="D146" s="16">
         <v>1</v>
       </c>
-      <c r="E146" s="25" t="s">
+      <c r="E146" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F146" s="25" t="s">
+      <c r="F146" s="24" t="s">
         <v>151</v>
       </c>
       <c r="G146" s="11"/>
@@ -4914,10 +4921,10 @@
       <c r="D147" s="16">
         <v>2</v>
       </c>
-      <c r="E147" s="25" t="s">
+      <c r="E147" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F147" s="25" t="s">
+      <c r="F147" s="24" t="s">
         <v>209</v>
       </c>
       <c r="G147" s="11"/>
@@ -4938,10 +4945,10 @@
       <c r="D148" s="16">
         <v>3</v>
       </c>
-      <c r="E148" s="25" t="s">
+      <c r="E148" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F148" s="25" t="s">
+      <c r="F148" s="24" t="s">
         <v>152</v>
       </c>
       <c r="G148" s="11"/>
@@ -4962,10 +4969,10 @@
       <c r="D149" s="16">
         <v>4</v>
       </c>
-      <c r="E149" s="25" t="s">
+      <c r="E149" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F149" s="25" t="s">
+      <c r="F149" s="24" t="s">
         <v>153</v>
       </c>
       <c r="G149" s="11"/>
@@ -4986,10 +4993,10 @@
       <c r="D150" s="16">
         <v>5</v>
       </c>
-      <c r="E150" s="25" t="s">
+      <c r="E150" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F150" s="25" t="s">
+      <c r="F150" s="24" t="s">
         <v>210</v>
       </c>
       <c r="G150" s="11"/>
@@ -5010,10 +5017,10 @@
       <c r="D151" s="16">
         <v>6</v>
       </c>
-      <c r="E151" s="25" t="s">
+      <c r="E151" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="F151" s="25" t="s">
+      <c r="F151" s="24" t="s">
         <v>154</v>
       </c>
       <c r="G151" s="11"/>
@@ -5034,10 +5041,10 @@
       <c r="D152" s="16">
         <v>7</v>
       </c>
-      <c r="E152" s="25" t="s">
+      <c r="E152" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F152" s="25" t="s">
+      <c r="F152" s="24" t="s">
         <v>155</v>
       </c>
       <c r="G152" s="11"/>
@@ -5058,10 +5065,10 @@
       <c r="D153" s="16">
         <v>8</v>
       </c>
-      <c r="E153" s="25" t="s">
+      <c r="E153" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F153" s="25" t="s">
+      <c r="F153" s="24" t="s">
         <v>156</v>
       </c>
       <c r="G153" s="11"/>
@@ -5082,10 +5089,10 @@
       <c r="D154" s="16">
         <v>9</v>
       </c>
-      <c r="E154" s="25" t="s">
+      <c r="E154" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F154" s="25" t="s">
+      <c r="F154" s="24" t="s">
         <v>157</v>
       </c>
       <c r="G154" s="11"/>
@@ -5106,10 +5113,10 @@
       <c r="D155" s="16">
         <v>10</v>
       </c>
-      <c r="E155" s="25" t="s">
+      <c r="E155" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F155" s="25" t="s">
+      <c r="F155" s="24" t="s">
         <v>158</v>
       </c>
       <c r="G155" s="11"/>
@@ -5130,10 +5137,10 @@
       <c r="D156" s="16">
         <v>11</v>
       </c>
-      <c r="E156" s="25" t="s">
+      <c r="E156" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F156" s="25" t="s">
+      <c r="F156" s="24" t="s">
         <v>159</v>
       </c>
       <c r="G156" s="11"/>
@@ -5154,10 +5161,10 @@
       <c r="D157" s="16">
         <v>12</v>
       </c>
-      <c r="E157" s="25" t="s">
+      <c r="E157" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F157" s="25" t="s">
+      <c r="F157" s="24" t="s">
         <v>160</v>
       </c>
       <c r="G157" s="11"/>
@@ -5178,10 +5185,10 @@
       <c r="D158" s="16">
         <v>13</v>
       </c>
-      <c r="E158" s="25" t="s">
+      <c r="E158" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="F158" s="25" t="s">
+      <c r="F158" s="24" t="s">
         <v>163</v>
       </c>
       <c r="G158" s="11"/>
@@ -5202,11 +5209,11 @@
       <c r="D159" s="16">
         <v>14</v>
       </c>
-      <c r="E159" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="F159" s="25" t="s">
-        <v>161</v>
+      <c r="E159" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="F159" s="24" t="s">
+        <v>212</v>
       </c>
       <c r="G159" s="11"/>
       <c r="H159" s="11"/>
@@ -5226,11 +5233,11 @@
       <c r="D160" s="16">
         <v>15</v>
       </c>
-      <c r="E160" s="25" t="s">
+      <c r="E160" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F160" s="25" t="s">
-        <v>162</v>
+      <c r="F160" s="24" t="s">
+        <v>161</v>
       </c>
       <c r="G160" s="11"/>
       <c r="H160" s="11"/>
@@ -5250,11 +5257,11 @@
       <c r="D161" s="16">
         <v>16</v>
       </c>
-      <c r="E161" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="F161" s="25" t="s">
-        <v>164</v>
+      <c r="E161" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="F161" s="24" t="s">
+        <v>162</v>
       </c>
       <c r="G161" s="11"/>
       <c r="H161" s="11"/>
@@ -5274,11 +5281,11 @@
       <c r="D162" s="16">
         <v>17</v>
       </c>
-      <c r="E162" s="25" t="s">
+      <c r="E162" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F162" s="25" t="s">
-        <v>165</v>
+      <c r="F162" s="24" t="s">
+        <v>164</v>
       </c>
       <c r="G162" s="11"/>
       <c r="H162" s="11"/>
@@ -5298,11 +5305,11 @@
       <c r="D163" s="16">
         <v>18</v>
       </c>
-      <c r="E163" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="F163" s="25" t="s">
-        <v>166</v>
+      <c r="E163" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F163" s="24" t="s">
+        <v>165</v>
       </c>
       <c r="G163" s="11"/>
       <c r="H163" s="11"/>
@@ -5322,11 +5329,11 @@
       <c r="D164" s="16">
         <v>19</v>
       </c>
-      <c r="E164" s="25" t="s">
+      <c r="E164" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F164" s="25" t="s">
-        <v>167</v>
+      <c r="F164" s="24" t="s">
+        <v>166</v>
       </c>
       <c r="G164" s="11"/>
       <c r="H164" s="11"/>
@@ -5346,11 +5353,11 @@
       <c r="D165" s="16">
         <v>20</v>
       </c>
-      <c r="E165" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="F165" s="25" t="s">
-        <v>168</v>
+      <c r="E165" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="F165" s="24" t="s">
+        <v>167</v>
       </c>
       <c r="G165" s="11"/>
       <c r="H165" s="11"/>
@@ -5370,11 +5377,11 @@
       <c r="D166" s="16">
         <v>21</v>
       </c>
-      <c r="E166" s="25" t="s">
+      <c r="E166" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F166" s="25" t="s">
-        <v>169</v>
+      <c r="F166" s="24" t="s">
+        <v>168</v>
       </c>
       <c r="G166" s="11"/>
       <c r="H166" s="11"/>
@@ -5394,11 +5401,11 @@
       <c r="D167" s="16">
         <v>22</v>
       </c>
-      <c r="E167" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="F167" s="25" t="s">
-        <v>170</v>
+      <c r="E167" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F167" s="24" t="s">
+        <v>169</v>
       </c>
       <c r="G167" s="11"/>
       <c r="H167" s="11"/>
@@ -5418,11 +5425,11 @@
       <c r="D168" s="16">
         <v>23</v>
       </c>
-      <c r="E168" s="25" t="s">
+      <c r="E168" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F168" s="25" t="s">
-        <v>171</v>
+      <c r="F168" s="24" t="s">
+        <v>170</v>
       </c>
       <c r="G168" s="11"/>
       <c r="H168" s="11"/>
@@ -5442,11 +5449,11 @@
       <c r="D169" s="16">
         <v>24</v>
       </c>
-      <c r="E169" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="F169" s="25" t="s">
-        <v>172</v>
+      <c r="E169" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="F169" s="24" t="s">
+        <v>171</v>
       </c>
       <c r="G169" s="11"/>
       <c r="H169" s="11"/>
@@ -5466,11 +5473,11 @@
       <c r="D170" s="16">
         <v>25</v>
       </c>
-      <c r="E170" s="25" t="s">
+      <c r="E170" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F170" s="25" t="s">
-        <v>173</v>
+      <c r="F170" s="24" t="s">
+        <v>172</v>
       </c>
       <c r="G170" s="11"/>
       <c r="H170" s="11"/>
@@ -5490,11 +5497,11 @@
       <c r="D171" s="16">
         <v>26</v>
       </c>
-      <c r="E171" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="F171" s="25" t="s">
-        <v>174</v>
+      <c r="E171" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F171" s="24" t="s">
+        <v>173</v>
       </c>
       <c r="G171" s="11"/>
       <c r="H171" s="11"/>
@@ -5514,11 +5521,11 @@
       <c r="D172" s="16">
         <v>27</v>
       </c>
-      <c r="E172" s="25" t="s">
+      <c r="E172" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F172" s="25" t="s">
-        <v>175</v>
+      <c r="F172" s="24" t="s">
+        <v>174</v>
       </c>
       <c r="G172" s="11"/>
       <c r="H172" s="11"/>
@@ -5538,11 +5545,11 @@
       <c r="D173" s="16">
         <v>28</v>
       </c>
-      <c r="E173" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="F173" s="25" t="s">
-        <v>176</v>
+      <c r="E173" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="F173" s="24" t="s">
+        <v>175</v>
       </c>
       <c r="G173" s="11"/>
       <c r="H173" s="11"/>
@@ -5562,11 +5569,11 @@
       <c r="D174" s="16">
         <v>29</v>
       </c>
-      <c r="E174" s="25" t="s">
+      <c r="E174" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F174" s="25" t="s">
-        <v>177</v>
+      <c r="F174" s="24" t="s">
+        <v>176</v>
       </c>
       <c r="G174" s="11"/>
       <c r="H174" s="11"/>
@@ -5586,11 +5593,11 @@
       <c r="D175" s="16">
         <v>30</v>
       </c>
-      <c r="E175" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="F175" s="25" t="s">
-        <v>178</v>
+      <c r="E175" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F175" s="24" t="s">
+        <v>177</v>
       </c>
       <c r="G175" s="11"/>
       <c r="H175" s="11"/>
@@ -5610,11 +5617,11 @@
       <c r="D176" s="16">
         <v>31</v>
       </c>
-      <c r="E176" s="25" t="s">
+      <c r="E176" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F176" s="25" t="s">
-        <v>179</v>
+      <c r="F176" s="24" t="s">
+        <v>178</v>
       </c>
       <c r="G176" s="11"/>
       <c r="H176" s="11"/>
@@ -5634,11 +5641,11 @@
       <c r="D177" s="16">
         <v>32</v>
       </c>
-      <c r="E177" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="F177" s="25" t="s">
-        <v>190</v>
+      <c r="E177" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="F177" s="24" t="s">
+        <v>179</v>
       </c>
       <c r="G177" s="11"/>
       <c r="H177" s="11"/>
@@ -5658,11 +5665,11 @@
       <c r="D178" s="16">
         <v>33</v>
       </c>
-      <c r="E178" s="25" t="s">
+      <c r="E178" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F178" s="25" t="s">
-        <v>211</v>
+      <c r="F178" s="24" t="s">
+        <v>190</v>
       </c>
       <c r="G178" s="11"/>
       <c r="H178" s="11"/>
@@ -5682,11 +5689,11 @@
       <c r="D179" s="16">
         <v>34</v>
       </c>
-      <c r="E179" s="25" t="s">
+      <c r="E179" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F179" s="25" t="s">
-        <v>180</v>
+      <c r="F179" s="24" t="s">
+        <v>211</v>
       </c>
       <c r="G179" s="11"/>
       <c r="H179" s="11"/>
@@ -5706,11 +5713,11 @@
       <c r="D180" s="16">
         <v>35</v>
       </c>
-      <c r="E180" s="25" t="s">
+      <c r="E180" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F180" s="25" t="s">
-        <v>181</v>
+      <c r="F180" s="24" t="s">
+        <v>180</v>
       </c>
       <c r="G180" s="11"/>
       <c r="H180" s="11"/>
@@ -5730,11 +5737,11 @@
       <c r="D181" s="16">
         <v>36</v>
       </c>
-      <c r="E181" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="F181" s="25" t="s">
-        <v>182</v>
+      <c r="E181" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F181" s="24" t="s">
+        <v>181</v>
       </c>
       <c r="G181" s="11"/>
       <c r="H181" s="11"/>
@@ -5754,11 +5761,11 @@
       <c r="D182" s="16">
         <v>37</v>
       </c>
-      <c r="E182" s="25" t="s">
+      <c r="E182" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F182" s="25" t="s">
-        <v>183</v>
+      <c r="F182" s="24" t="s">
+        <v>182</v>
       </c>
       <c r="G182" s="11"/>
       <c r="H182" s="11"/>
@@ -5778,11 +5785,11 @@
       <c r="D183" s="16">
         <v>38</v>
       </c>
-      <c r="E183" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="F183" s="25" t="s">
-        <v>184</v>
+      <c r="E183" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="F183" s="24" t="s">
+        <v>183</v>
       </c>
       <c r="G183" s="11"/>
       <c r="H183" s="11"/>
@@ -5802,11 +5809,11 @@
       <c r="D184" s="16">
         <v>39</v>
       </c>
-      <c r="E184" s="25" t="s">
+      <c r="E184" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F184" s="25" t="s">
-        <v>185</v>
+      <c r="F184" s="24" t="s">
+        <v>184</v>
       </c>
       <c r="G184" s="11"/>
       <c r="H184" s="11"/>
@@ -5826,11 +5833,11 @@
       <c r="D185" s="16">
         <v>40</v>
       </c>
-      <c r="E185" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="F185" s="25" t="s">
-        <v>186</v>
+      <c r="E185" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F185" s="24" t="s">
+        <v>185</v>
       </c>
       <c r="G185" s="11"/>
       <c r="H185" s="11"/>
@@ -5850,11 +5857,11 @@
       <c r="D186" s="16">
         <v>41</v>
       </c>
-      <c r="E186" s="25" t="s">
+      <c r="E186" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F186" s="25" t="s">
-        <v>187</v>
+      <c r="F186" s="24" t="s">
+        <v>186</v>
       </c>
       <c r="G186" s="11"/>
       <c r="H186" s="11"/>
@@ -5874,11 +5881,11 @@
       <c r="D187" s="16">
         <v>42</v>
       </c>
-      <c r="E187" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="F187" s="25" t="s">
-        <v>188</v>
+      <c r="E187" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="F187" s="24" t="s">
+        <v>187</v>
       </c>
       <c r="G187" s="11"/>
       <c r="H187" s="11"/>
@@ -5898,11 +5905,11 @@
       <c r="D188" s="16">
         <v>43</v>
       </c>
-      <c r="E188" s="25" t="s">
+      <c r="E188" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F188" s="25" t="s">
-        <v>189</v>
+      <c r="F188" s="24" t="s">
+        <v>188</v>
       </c>
       <c r="G188" s="11"/>
       <c r="H188" s="11"/>
@@ -5915,45 +5922,51 @@
       <c r="O188" s="3"/>
       <c r="P188" s="11"/>
     </row>
-    <row r="189" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="11"/>
-      <c r="B189" s="17" t="s">
+    <row r="189" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="3"/>
+      <c r="B189" s="3"/>
+      <c r="C189" s="3"/>
+      <c r="D189" s="16">
+        <v>44</v>
+      </c>
+      <c r="E189" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F189" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="G189" s="11"/>
+      <c r="H189" s="11"/>
+      <c r="I189" s="11"/>
+      <c r="J189" s="3"/>
+      <c r="K189" s="3"/>
+      <c r="L189" s="3"/>
+      <c r="M189" s="3"/>
+      <c r="N189" s="3"/>
+      <c r="O189" s="3"/>
+      <c r="P189" s="11"/>
+    </row>
+    <row r="190" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="11"/>
+      <c r="B190" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C189" s="17" t="s">
+      <c r="C190" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="D189" s="17"/>
-      <c r="E189" s="17"/>
-      <c r="F189" s="18"/>
-      <c r="G189" s="17"/>
-      <c r="H189" s="17"/>
-      <c r="I189" s="17"/>
-      <c r="J189" s="17"/>
-      <c r="K189" s="17"/>
-      <c r="L189" s="17"/>
-      <c r="M189" s="17"/>
-      <c r="N189" s="17"/>
-      <c r="O189" s="17"/>
-      <c r="P189" s="17"/>
-    </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A190" s="3"/>
-      <c r="B190" s="3"/>
-      <c r="C190" s="3"/>
-      <c r="D190" s="16"/>
-      <c r="E190" s="11"/>
-      <c r="F190" s="11"/>
-      <c r="G190" s="11"/>
-      <c r="H190" s="11"/>
-      <c r="I190" s="11"/>
-      <c r="J190" s="3"/>
-      <c r="K190" s="3"/>
-      <c r="L190" s="3"/>
-      <c r="M190" s="3"/>
-      <c r="N190" s="3"/>
-      <c r="O190" s="3"/>
-      <c r="P190" s="11"/>
+      <c r="D190" s="17"/>
+      <c r="E190" s="17"/>
+      <c r="F190" s="18"/>
+      <c r="G190" s="17"/>
+      <c r="H190" s="17"/>
+      <c r="I190" s="17"/>
+      <c r="J190" s="17"/>
+      <c r="K190" s="17"/>
+      <c r="L190" s="17"/>
+      <c r="M190" s="17"/>
+      <c r="N190" s="17"/>
+      <c r="O190" s="17"/>
+      <c r="P190" s="17"/>
     </row>
     <row r="191" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A191" s="3"/>
@@ -5973,45 +5986,45 @@
       <c r="O191" s="3"/>
       <c r="P191" s="11"/>
     </row>
-    <row r="192" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="11"/>
-      <c r="B192" s="17" t="s">
+    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A192" s="3"/>
+      <c r="B192" s="3"/>
+      <c r="C192" s="3"/>
+      <c r="D192" s="16"/>
+      <c r="E192" s="11"/>
+      <c r="F192" s="11"/>
+      <c r="G192" s="11"/>
+      <c r="H192" s="11"/>
+      <c r="I192" s="11"/>
+      <c r="J192" s="3"/>
+      <c r="K192" s="3"/>
+      <c r="L192" s="3"/>
+      <c r="M192" s="3"/>
+      <c r="N192" s="3"/>
+      <c r="O192" s="3"/>
+      <c r="P192" s="11"/>
+    </row>
+    <row r="193" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A193" s="11"/>
+      <c r="B193" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="C192" s="17" t="s">
+      <c r="C193" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="D192" s="17"/>
-      <c r="E192" s="17"/>
-      <c r="F192" s="11"/>
-      <c r="G192" s="17"/>
-      <c r="H192" s="17"/>
-      <c r="I192" s="17"/>
-      <c r="J192" s="17"/>
-      <c r="K192" s="17"/>
-      <c r="L192" s="17"/>
-      <c r="M192" s="17"/>
-      <c r="N192" s="17"/>
-      <c r="O192" s="17"/>
-      <c r="P192" s="17"/>
-    </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A193" s="3"/>
-      <c r="B193" s="3"/>
-      <c r="C193" s="3"/>
-      <c r="D193" s="16"/>
-      <c r="E193" s="11"/>
+      <c r="D193" s="17"/>
+      <c r="E193" s="17"/>
       <c r="F193" s="11"/>
-      <c r="G193" s="11"/>
-      <c r="H193" s="11"/>
-      <c r="I193" s="11"/>
-      <c r="J193" s="3"/>
-      <c r="K193" s="3"/>
-      <c r="L193" s="3"/>
-      <c r="M193" s="3"/>
-      <c r="N193" s="3"/>
-      <c r="O193" s="3"/>
-      <c r="P193" s="11"/>
+      <c r="G193" s="17"/>
+      <c r="H193" s="17"/>
+      <c r="I193" s="17"/>
+      <c r="J193" s="17"/>
+      <c r="K193" s="17"/>
+      <c r="L193" s="17"/>
+      <c r="M193" s="17"/>
+      <c r="N193" s="17"/>
+      <c r="O193" s="17"/>
+      <c r="P193" s="17"/>
     </row>
     <row r="194" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A194" s="3"/>
@@ -6031,45 +6044,45 @@
       <c r="O194" s="3"/>
       <c r="P194" s="11"/>
     </row>
-    <row r="195" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A195" s="11"/>
-      <c r="B195" s="17" t="s">
+    <row r="195" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A195" s="3"/>
+      <c r="B195" s="3"/>
+      <c r="C195" s="3"/>
+      <c r="D195" s="16"/>
+      <c r="E195" s="11"/>
+      <c r="F195" s="11"/>
+      <c r="G195" s="11"/>
+      <c r="H195" s="11"/>
+      <c r="I195" s="11"/>
+      <c r="J195" s="3"/>
+      <c r="K195" s="3"/>
+      <c r="L195" s="3"/>
+      <c r="M195" s="3"/>
+      <c r="N195" s="3"/>
+      <c r="O195" s="3"/>
+      <c r="P195" s="11"/>
+    </row>
+    <row r="196" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A196" s="11"/>
+      <c r="B196" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="C195" s="17" t="s">
+      <c r="C196" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="D195" s="17"/>
-      <c r="E195" s="17"/>
-      <c r="F195" s="17"/>
-      <c r="G195" s="17"/>
-      <c r="H195" s="17"/>
-      <c r="I195" s="17"/>
-      <c r="J195" s="17"/>
-      <c r="K195" s="17"/>
-      <c r="L195" s="17"/>
-      <c r="M195" s="17"/>
-      <c r="N195" s="17"/>
-      <c r="O195" s="17"/>
-      <c r="P195" s="17"/>
-    </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A196" s="3"/>
-      <c r="B196" s="3"/>
-      <c r="C196" s="3"/>
-      <c r="D196" s="16"/>
-      <c r="E196" s="11"/>
-      <c r="F196" s="11"/>
-      <c r="G196" s="11"/>
-      <c r="H196" s="11"/>
-      <c r="I196" s="11"/>
-      <c r="J196" s="3"/>
-      <c r="K196" s="3"/>
-      <c r="L196" s="3"/>
-      <c r="M196" s="3"/>
-      <c r="N196" s="3"/>
-      <c r="O196" s="3"/>
-      <c r="P196" s="11"/>
+      <c r="D196" s="17"/>
+      <c r="E196" s="17"/>
+      <c r="F196" s="17"/>
+      <c r="G196" s="17"/>
+      <c r="H196" s="17"/>
+      <c r="I196" s="17"/>
+      <c r="J196" s="17"/>
+      <c r="K196" s="17"/>
+      <c r="L196" s="17"/>
+      <c r="M196" s="17"/>
+      <c r="N196" s="17"/>
+      <c r="O196" s="17"/>
+      <c r="P196" s="17"/>
     </row>
     <row r="197" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A197" s="3"/>
@@ -6093,19 +6106,19 @@
       <c r="A198" s="3"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
-      <c r="D198" s="3"/>
-      <c r="E198" s="3"/>
-      <c r="F198" s="17"/>
-      <c r="G198" s="3"/>
-      <c r="H198" s="3"/>
-      <c r="I198" s="3"/>
+      <c r="D198" s="16"/>
+      <c r="E198" s="11"/>
+      <c r="F198" s="11"/>
+      <c r="G198" s="11"/>
+      <c r="H198" s="11"/>
+      <c r="I198" s="11"/>
       <c r="J198" s="3"/>
       <c r="K198" s="3"/>
       <c r="L198" s="3"/>
       <c r="M198" s="3"/>
       <c r="N198" s="3"/>
       <c r="O198" s="3"/>
-      <c r="P198" s="3"/>
+      <c r="P198" s="11"/>
     </row>
     <row r="199" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A199" s="3"/>
@@ -6113,7 +6126,7 @@
       <c r="C199" s="3"/>
       <c r="D199" s="3"/>
       <c r="E199" s="3"/>
-      <c r="F199" s="11"/>
+      <c r="F199" s="17"/>
       <c r="G199" s="3"/>
       <c r="H199" s="3"/>
       <c r="I199" s="3"/>
@@ -6149,7 +6162,7 @@
       <c r="C201" s="3"/>
       <c r="D201" s="3"/>
       <c r="E201" s="3"/>
-      <c r="F201" s="17"/>
+      <c r="F201" s="11"/>
       <c r="G201" s="3"/>
       <c r="H201" s="3"/>
       <c r="I201" s="3"/>
@@ -6167,7 +6180,7 @@
       <c r="C202" s="3"/>
       <c r="D202" s="3"/>
       <c r="E202" s="3"/>
-      <c r="F202" s="11"/>
+      <c r="F202" s="17"/>
       <c r="G202" s="3"/>
       <c r="H202" s="3"/>
       <c r="I202" s="3"/>
@@ -6203,7 +6216,7 @@
       <c r="C204" s="3"/>
       <c r="D204" s="3"/>
       <c r="E204" s="3"/>
-      <c r="F204" s="3"/>
+      <c r="F204" s="11"/>
       <c r="G204" s="3"/>
       <c r="H204" s="3"/>
       <c r="I204" s="3"/>
@@ -6287,58 +6300,73 @@
       <c r="O208" s="3"/>
       <c r="P208" s="3"/>
     </row>
-    <row r="209" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A209" s="3"/>
+      <c r="B209" s="3"/>
       <c r="C209" s="3"/>
+      <c r="D209" s="3"/>
+      <c r="E209" s="3"/>
       <c r="F209" s="3"/>
-    </row>
-    <row r="210" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="G209" s="3"/>
+      <c r="H209" s="3"/>
+      <c r="I209" s="3"/>
+      <c r="J209" s="3"/>
+      <c r="K209" s="3"/>
+      <c r="L209" s="3"/>
+      <c r="M209" s="3"/>
+      <c r="N209" s="3"/>
+      <c r="O209" s="3"/>
+      <c r="P209" s="3"/>
+    </row>
+    <row r="210" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C210" s="3"/>
       <c r="F210" s="3"/>
     </row>
-    <row r="211" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C211" s="3"/>
       <c r="F211" s="3"/>
     </row>
-    <row r="212" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C212" s="3"/>
       <c r="F212" s="3"/>
     </row>
-    <row r="213" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C213" s="3"/>
       <c r="F213" s="3"/>
     </row>
-    <row r="214" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C214" s="3"/>
       <c r="F214" s="3"/>
     </row>
-    <row r="215" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C215" s="3"/>
-    </row>
-    <row r="216" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="F215" s="3"/>
+    </row>
+    <row r="216" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C216" s="3"/>
     </row>
-    <row r="217" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C217" s="3"/>
     </row>
-    <row r="218" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C218" s="3"/>
     </row>
-    <row r="219" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C219" s="3"/>
     </row>
-    <row r="220" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C220" s="3"/>
     </row>
-    <row r="221" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C221" s="3"/>
     </row>
-    <row r="222" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C222" s="3"/>
     </row>
-    <row r="223" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C223" s="3"/>
     </row>
-    <row r="224" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C224" s="3"/>
     </row>
     <row r="225" spans="3:3" x14ac:dyDescent="0.25">
@@ -8813,28 +8841,31 @@
     <row r="1048" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C1048" s="3"/>
     </row>
+    <row r="1049" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C1049" s="3"/>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatRows="0" insertRows="0" insertHyperlinks="0" deleteRows="0" sort="0" autoFilter="0"/>
-  <autoFilter ref="B10:P197" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="B10:P198" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="F1:P6"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="9">
-    <dataValidation allowBlank="1" showInputMessage="1" sqref="C11 C14 C17 C20 C23 C26 C29 C32 C35 C144 C189 C192 C195" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Object Code value" error="The Object code value shall be:_x000a_VARIABLE_x000a_RECORD_x000a_ARRAY" sqref="C12:C13 C15:C16 C18:C19 C21:C22 C24:C25 C27:C28 C30:C31 C33:C34 C36:C143 C145:C188 C190:C191 C193:C194 C196:C208" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation allowBlank="1" showInputMessage="1" sqref="C11 C14 C17 C20 C23 C26 C29 C32 C35 C144 C190 C193 C196" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Object Code value" error="The Object code value shall be:_x000a_VARIABLE_x000a_RECORD_x000a_ARRAY" sqref="C12:C13 C15:C16 C18:C19 C21:C22 C24:C25 C27:C28 C30:C31 C33:C34 C36:C143 C145:C189 C191:C192 C194:C195 C197:C209" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Category" error="The value for the entry category shall be _x000a_M : (mandatory)_x000a_O : (optional) _x000a_C : (conditional)" sqref="J36 J193:J194 J196:J208 J12:J13 J15:J16 J18:J19 J21:J22 J24:J25 J27:J28 J30:J31 J33:J34 J40:J143 J145:J188 J190:J191" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Category" error="The value for the entry category shall be _x000a_M : (mandatory)_x000a_O : (optional) _x000a_C : (conditional)" sqref="J36 J194:J195 J197:J209 J12:J13 J15:J16 J18:J19 J21:J22 J24:J25 J27:J28 J30:J31 J33:J34 J40:J143 J145:J189 J191:J192" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"M,O,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Backup/Setting Flag" error="The entry flag shall be_x000a_B : (Backup)_x000a_S : (Setting)" sqref="K36 K193:K194 K196:K208 K12:K13 K15:K16 K18:K19 K21:K22 K24:K25 K27:K28 K30:K31 K33:K34 K40:K143 K145:K188 K190:K191" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Backup/Setting Flag" error="The entry flag shall be_x000a_B : (Backup)_x000a_S : (Setting)" sqref="K36 K194:K195 K197:K209 K12:K13 K15:K16 K18:K19 K21:K22 K24:K25 K27:K28 K30:K31 K33:K34 K40:K143 K145:K189 K191:K192" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"B,S"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M36:O36 M193:O194 M12:O13 M18:O19 M24:O25 M30:O31 M40:O143 M190:O191 M196:O197 M15:O16 M21:O22 M27:O28 M33:O34 M145:O188" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M36:O36 M194:O195 M12:O13 M18:O19 M24:O25 M30:O31 M40:O143 M191:O192 M197:O198 M15:O16 M21:O22 M27:O28 M33:O34 M145:O189" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"rx,tx"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C209:C1048" xr:uid="{00000000-0002-0000-0000-000005000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C210:C1049" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J37:J39" xr:uid="{20805EC6-BF85-484F-8728-8A67EE77DC8F}">

--- a/ArmCoreV1_QSPI/SSCProject/lan9252_app.xlsx
+++ b/ArmCoreV1_QSPI/SSCProject/lan9252_app.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SI\project\RTM_OFF_NEW\FW-ArmCore\ArmCoreV1_QSPI\SSCProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C03307-4F26-4A08-B0C7-459A3BEF98FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D9FCF4C-31ED-4DC3-9C73-2270C865D881}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-38510" yWindow="-7730" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -17,8 +17,8 @@
     <sheet name="Profile" sheetId="11" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Profile!$B$10:$P$127</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Profile!$B$1:$P$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Profile!$B$10:$P$131</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Profile!$B$1:$P$132</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="144">
   <si>
     <t>Device Profile:</t>
   </si>
@@ -701,12 +701,31 @@
     <t>OutU8_reserved5</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
+  <si>
+    <t>UNSIGNED8</t>
+  </si>
+  <si>
+    <t>InU8_fault_clear</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>InU8_ethercat_Link_state</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>OutU8_ethercat_Link_state</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>OutU8_reserved2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -768,6 +787,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -819,10 +853,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
       <protection locked="0"/>
@@ -877,15 +912,35 @@
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 3" xfId="1" xr:uid="{BEC44B3C-D034-4371-B354-A1BBB74B7237}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1187,7 +1242,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T978"/>
+  <dimension ref="A1:T982"/>
   <sheetFormatPr defaultColWidth="10.7265625" defaultRowHeight="14" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.81640625" style="2" customWidth="1"/>
@@ -1219,19 +1274,19 @@
         <v>1</v>
       </c>
       <c r="E1" s="4"/>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
       <c r="Q1" s="20"/>
       <c r="R1" s="20"/>
       <c r="S1" s="20"/>
@@ -1247,17 +1302,17 @@
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25"/>
       <c r="Q2" s="20"/>
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
@@ -1269,17 +1324,17 @@
       <c r="C3" s="5"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25"/>
       <c r="Q3" s="20"/>
       <c r="R3" s="20"/>
       <c r="S3" s="20"/>
@@ -1291,17 +1346,17 @@
       <c r="C4" s="5"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="24"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="24"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
+      <c r="N4" s="25"/>
+      <c r="O4" s="25"/>
+      <c r="P4" s="25"/>
       <c r="Q4" s="20"/>
       <c r="R4" s="20"/>
       <c r="S4" s="20"/>
@@ -1313,17 +1368,17 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="24"/>
-      <c r="M5" s="24"/>
-      <c r="N5" s="24"/>
-      <c r="O5" s="24"/>
-      <c r="P5" s="24"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="25"/>
+      <c r="O5" s="25"/>
+      <c r="P5" s="25"/>
       <c r="Q5" s="20"/>
       <c r="R5" s="20"/>
       <c r="S5" s="20"/>
@@ -1335,17 +1390,17 @@
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="24"/>
-      <c r="N6" s="24"/>
-      <c r="O6" s="24"/>
-      <c r="P6" s="24"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="25"/>
+      <c r="P6" s="25"/>
       <c r="Q6" s="20"/>
       <c r="R6" s="20"/>
       <c r="S6" s="20"/>
@@ -1973,13 +2028,13 @@
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
-      <c r="D37" s="25">
+      <c r="D37" s="24">
         <v>1</v>
       </c>
-      <c r="E37" s="25" t="s">
+      <c r="E37" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="F37" s="25" t="s">
+      <c r="F37" s="24" t="s">
         <v>55</v>
       </c>
       <c r="G37" s="22"/>
@@ -1999,13 +2054,13 @@
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
-      <c r="D38" s="25">
+      <c r="D38" s="24">
         <v>2</v>
       </c>
-      <c r="E38" s="25" t="s">
+      <c r="E38" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="F38" s="25" t="s">
+      <c r="F38" s="24" t="s">
         <v>56</v>
       </c>
       <c r="G38" s="22"/>
@@ -2023,13 +2078,13 @@
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
-      <c r="D39" s="25">
+      <c r="D39" s="24">
         <v>3</v>
       </c>
-      <c r="E39" s="25" t="s">
+      <c r="E39" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="F39" s="25" t="s">
+      <c r="F39" s="24" t="s">
         <v>58</v>
       </c>
       <c r="G39" s="22"/>
@@ -2049,13 +2104,13 @@
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
-      <c r="D40" s="25">
+      <c r="D40" s="24">
         <v>4</v>
       </c>
-      <c r="E40" s="25" t="s">
+      <c r="E40" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="F40" s="25" t="s">
+      <c r="F40" s="24" t="s">
         <v>59</v>
       </c>
       <c r="G40" s="1"/>
@@ -2075,13 +2130,13 @@
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
-      <c r="D41" s="25">
+      <c r="D41" s="24">
         <v>5</v>
       </c>
-      <c r="E41" s="25" t="s">
+      <c r="E41" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="F41" s="25" t="s">
+      <c r="F41" s="24" t="s">
         <v>60</v>
       </c>
       <c r="G41" s="1"/>
@@ -2099,13 +2154,13 @@
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
-      <c r="D42" s="25">
+      <c r="D42" s="24">
         <v>6</v>
       </c>
-      <c r="E42" s="25" t="s">
+      <c r="E42" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F42" s="25" t="s">
+      <c r="F42" s="24" t="s">
         <v>62</v>
       </c>
       <c r="G42" s="1"/>
@@ -2123,16 +2178,16 @@
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
-      <c r="D43" s="25">
+      <c r="D43" s="26">
         <v>7</v>
       </c>
-      <c r="E43" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="F43" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="G43" s="1"/>
+      <c r="E43" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="F43" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="G43" s="27"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
       <c r="J43" s="2"/>
@@ -2147,16 +2202,16 @@
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
-      <c r="D44" s="25">
+      <c r="D44" s="24">
         <v>8</v>
       </c>
-      <c r="E44" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="F44" s="25" t="s">
-        <v>67</v>
-      </c>
-      <c r="G44" s="1"/>
+      <c r="E44" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="F44" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="G44" s="28"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
       <c r="J44" s="2"/>
@@ -2171,14 +2226,14 @@
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
-      <c r="D45" s="25">
+      <c r="D45" s="24">
         <v>9</v>
       </c>
-      <c r="E45" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="F45" s="25" t="s">
-        <v>68</v>
+      <c r="E45" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="F45" s="24" t="s">
+        <v>66</v>
       </c>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
@@ -2195,14 +2250,14 @@
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
-      <c r="D46" s="25">
+      <c r="D46" s="24">
         <v>10</v>
       </c>
-      <c r="E46" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="F46" s="25" t="s">
-        <v>69</v>
+      <c r="E46" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="F46" s="24" t="s">
+        <v>67</v>
       </c>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
@@ -2219,14 +2274,14 @@
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
-      <c r="D47" s="25">
+      <c r="D47" s="24">
         <v>11</v>
       </c>
-      <c r="E47" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="F47" s="25" t="s">
-        <v>87</v>
+      <c r="E47" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="F47" s="24" t="s">
+        <v>68</v>
       </c>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
@@ -2243,14 +2298,14 @@
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
-      <c r="D48" s="25">
+      <c r="D48" s="24">
         <v>12</v>
       </c>
-      <c r="E48" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="F48" s="25" t="s">
-        <v>88</v>
+      <c r="E48" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="F48" s="24" t="s">
+        <v>69</v>
       </c>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
@@ -2267,14 +2322,14 @@
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
-      <c r="D49" s="25">
+      <c r="D49" s="24">
         <v>13</v>
       </c>
-      <c r="E49" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="F49" s="25" t="s">
-        <v>89</v>
+      <c r="E49" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="F49" s="24" t="s">
+        <v>87</v>
       </c>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
@@ -2291,14 +2346,14 @@
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
-      <c r="D50" s="25">
+      <c r="D50" s="26">
         <v>14</v>
       </c>
-      <c r="E50" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="F50" s="25" t="s">
-        <v>126</v>
+      <c r="E50" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="F50" s="24" t="s">
+        <v>88</v>
       </c>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
@@ -2315,14 +2370,14 @@
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
-      <c r="D51" s="25">
+      <c r="D51" s="24">
         <v>15</v>
       </c>
-      <c r="E51" s="25" t="s">
+      <c r="E51" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="F51" s="25" t="s">
-        <v>127</v>
+      <c r="F51" s="24" t="s">
+        <v>89</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
@@ -2339,14 +2394,14 @@
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
-      <c r="D52" s="25">
+      <c r="D52" s="24">
         <v>16</v>
       </c>
-      <c r="E52" s="25" t="s">
+      <c r="E52" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="F52" s="25" t="s">
-        <v>128</v>
+      <c r="F52" s="24" t="s">
+        <v>126</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
@@ -2363,14 +2418,14 @@
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
-      <c r="D53" s="25">
+      <c r="D53" s="24">
         <v>17</v>
       </c>
-      <c r="E53" s="25" t="s">
+      <c r="E53" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="F53" s="25" t="s">
-        <v>70</v>
+      <c r="F53" s="24" t="s">
+        <v>127</v>
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
@@ -2387,14 +2442,14 @@
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
-      <c r="D54" s="25">
+      <c r="D54" s="24">
         <v>18</v>
       </c>
-      <c r="E54" s="25" t="s">
+      <c r="E54" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="F54" s="25" t="s">
-        <v>71</v>
+      <c r="F54" s="24" t="s">
+        <v>128</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
@@ -2411,14 +2466,14 @@
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
-      <c r="D55" s="25">
+      <c r="D55" s="24">
         <v>19</v>
       </c>
-      <c r="E55" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="F55" s="25" t="s">
-        <v>72</v>
+      <c r="E55" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="F55" s="24" t="s">
+        <v>70</v>
       </c>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
@@ -2435,14 +2490,14 @@
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
-      <c r="D56" s="25">
+      <c r="D56" s="24">
         <v>20</v>
       </c>
-      <c r="E56" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="F56" s="25" t="s">
-        <v>73</v>
+      <c r="E56" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="F56" s="24" t="s">
+        <v>71</v>
       </c>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
@@ -2459,14 +2514,14 @@
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
-      <c r="D57" s="25">
+      <c r="D57" s="26">
         <v>21</v>
       </c>
-      <c r="E57" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="F57" s="25" t="s">
-        <v>90</v>
+      <c r="E57" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="F57" s="24" t="s">
+        <v>72</v>
       </c>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
@@ -2483,14 +2538,14 @@
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
-      <c r="D58" s="25">
+      <c r="D58" s="24">
         <v>22</v>
       </c>
-      <c r="E58" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="F58" s="25" t="s">
-        <v>91</v>
+      <c r="E58" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="F58" s="24" t="s">
+        <v>73</v>
       </c>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
@@ -2507,14 +2562,14 @@
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
-      <c r="D59" s="25">
+      <c r="D59" s="24">
         <v>23</v>
       </c>
-      <c r="E59" s="25" t="s">
+      <c r="E59" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="F59" s="25" t="s">
-        <v>83</v>
+      <c r="F59" s="24" t="s">
+        <v>90</v>
       </c>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
@@ -2531,14 +2586,14 @@
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
-      <c r="D60" s="25">
+      <c r="D60" s="24">
         <v>24</v>
       </c>
-      <c r="E60" s="25" t="s">
+      <c r="E60" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="F60" s="25" t="s">
-        <v>92</v>
+      <c r="F60" s="24" t="s">
+        <v>91</v>
       </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
@@ -2555,14 +2610,14 @@
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
-      <c r="D61" s="25">
+      <c r="D61" s="24">
         <v>25</v>
       </c>
-      <c r="E61" s="25" t="s">
+      <c r="E61" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="F61" s="25" t="s">
-        <v>84</v>
+      <c r="F61" s="24" t="s">
+        <v>83</v>
       </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
@@ -2579,14 +2634,14 @@
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
-      <c r="D62" s="25">
+      <c r="D62" s="24">
         <v>26</v>
       </c>
-      <c r="E62" s="25" t="s">
+      <c r="E62" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="F62" s="25" t="s">
-        <v>93</v>
+      <c r="F62" s="24" t="s">
+        <v>92</v>
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
@@ -2603,14 +2658,14 @@
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
-      <c r="D63" s="25">
+      <c r="D63" s="24">
         <v>27</v>
       </c>
-      <c r="E63" s="25" t="s">
+      <c r="E63" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="F63" s="25" t="s">
-        <v>94</v>
+      <c r="F63" s="24" t="s">
+        <v>84</v>
       </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
@@ -2627,14 +2682,14 @@
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
-      <c r="D64" s="25">
+      <c r="D64" s="26">
         <v>28</v>
       </c>
-      <c r="E64" s="25" t="s">
+      <c r="E64" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="F64" s="25" t="s">
-        <v>95</v>
+      <c r="F64" s="24" t="s">
+        <v>93</v>
       </c>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
@@ -2651,14 +2706,14 @@
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
-      <c r="D65" s="25">
+      <c r="D65" s="24">
         <v>29</v>
       </c>
-      <c r="E65" s="25" t="s">
+      <c r="E65" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="F65" s="25" t="s">
-        <v>96</v>
+      <c r="F65" s="24" t="s">
+        <v>94</v>
       </c>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
@@ -2675,14 +2730,14 @@
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
-      <c r="D66" s="25">
+      <c r="D66" s="24">
         <v>30</v>
       </c>
-      <c r="E66" s="25" t="s">
+      <c r="E66" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="F66" s="25" t="s">
-        <v>97</v>
+      <c r="F66" s="24" t="s">
+        <v>95</v>
       </c>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
@@ -2699,14 +2754,14 @@
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
-      <c r="D67" s="25">
+      <c r="D67" s="24">
         <v>31</v>
       </c>
-      <c r="E67" s="25" t="s">
+      <c r="E67" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="F67" s="25" t="s">
-        <v>98</v>
+      <c r="F67" s="24" t="s">
+        <v>96</v>
       </c>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
@@ -2723,14 +2778,14 @@
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
-      <c r="D68" s="25">
+      <c r="D68" s="24">
         <v>32</v>
       </c>
-      <c r="E68" s="25" t="s">
+      <c r="E68" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="F68" s="25" t="s">
-        <v>99</v>
+      <c r="F68" s="24" t="s">
+        <v>97</v>
       </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
@@ -2747,14 +2802,14 @@
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
-      <c r="D69" s="25">
+      <c r="D69" s="24">
         <v>33</v>
       </c>
-      <c r="E69" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="F69" s="25" t="s">
-        <v>100</v>
+      <c r="E69" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="F69" s="24" t="s">
+        <v>98</v>
       </c>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
@@ -2771,14 +2826,14 @@
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
-      <c r="D70" s="25">
+      <c r="D70" s="24">
         <v>34</v>
       </c>
-      <c r="E70" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="F70" s="25" t="s">
-        <v>129</v>
+      <c r="E70" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="F70" s="24" t="s">
+        <v>99</v>
       </c>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
@@ -2795,14 +2850,14 @@
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
-      <c r="D71" s="25">
+      <c r="D71" s="26">
         <v>35</v>
       </c>
-      <c r="E71" s="25" t="s">
+      <c r="E71" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="F71" s="25" t="s">
-        <v>130</v>
+      <c r="F71" s="24" t="s">
+        <v>100</v>
       </c>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
@@ -2819,14 +2874,14 @@
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
-      <c r="D72" s="25">
+      <c r="D72" s="24">
         <v>36</v>
       </c>
-      <c r="E72" s="25" t="s">
+      <c r="E72" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="F72" s="25" t="s">
-        <v>131</v>
+      <c r="F72" s="24" t="s">
+        <v>129</v>
       </c>
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
@@ -2843,14 +2898,14 @@
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
-      <c r="D73" s="25">
+      <c r="D73" s="24">
         <v>37</v>
       </c>
-      <c r="E73" s="25" t="s">
-        <v>101</v>
-      </c>
-      <c r="F73" s="25" t="s">
-        <v>85</v>
+      <c r="E73" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="F73" s="24" t="s">
+        <v>130</v>
       </c>
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
@@ -2867,14 +2922,14 @@
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
-      <c r="D74" s="25">
+      <c r="D74" s="24">
         <v>38</v>
       </c>
-      <c r="E74" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="F74" s="25" t="s">
-        <v>102</v>
+      <c r="E74" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="F74" s="24" t="s">
+        <v>131</v>
       </c>
       <c r="G74" s="1"/>
       <c r="H74" s="1"/>
@@ -2887,88 +2942,88 @@
       <c r="O74" s="2"/>
       <c r="P74" s="1"/>
     </row>
-    <row r="75" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="11"/>
-      <c r="B75" s="17" t="s">
+    <row r="75" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="3"/>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="24">
+        <v>39</v>
+      </c>
+      <c r="E75" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="F75" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="2"/>
+      <c r="K75" s="2"/>
+      <c r="L75" s="2"/>
+      <c r="M75" s="2"/>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" s="1"/>
+    </row>
+    <row r="76" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="3"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="24">
+        <v>40</v>
+      </c>
+      <c r="E76" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="F76" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="2"/>
+      <c r="K76" s="2"/>
+      <c r="L76" s="2"/>
+      <c r="M76" s="2"/>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+      <c r="P76" s="1"/>
+    </row>
+    <row r="77" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="11"/>
+      <c r="B77" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C75" s="17" t="s">
+      <c r="C77" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D75" s="17"/>
-      <c r="E75" s="17"/>
-      <c r="F75" s="17"/>
-      <c r="G75" s="17"/>
-      <c r="H75" s="17"/>
-      <c r="I75" s="17"/>
-      <c r="J75" s="17"/>
-      <c r="K75" s="17"/>
-      <c r="L75" s="17"/>
-      <c r="M75" s="17"/>
-      <c r="N75" s="17"/>
-      <c r="O75" s="17"/>
-      <c r="P75" s="17"/>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A76" s="3"/>
-      <c r="B76" s="3" t="s">
+      <c r="D77" s="17"/>
+      <c r="E77" s="17"/>
+      <c r="F77" s="17"/>
+      <c r="G77" s="17"/>
+      <c r="H77" s="17"/>
+      <c r="I77" s="17"/>
+      <c r="J77" s="17"/>
+      <c r="K77" s="17"/>
+      <c r="L77" s="17"/>
+      <c r="M77" s="17"/>
+      <c r="N77" s="17"/>
+      <c r="O77" s="17"/>
+      <c r="P77" s="17"/>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A78" s="3"/>
+      <c r="B78" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C78" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D76" s="16"/>
-      <c r="E76" s="11"/>
-      <c r="F76" s="11" t="s">
+      <c r="D78" s="16"/>
+      <c r="E78" s="11"/>
+      <c r="F78" s="11" t="s">
         <v>45</v>
-      </c>
-      <c r="G76" s="11"/>
-      <c r="H76" s="11"/>
-      <c r="I76" s="11"/>
-      <c r="J76" s="3"/>
-      <c r="K76" s="3"/>
-      <c r="L76" s="3"/>
-      <c r="M76" s="3"/>
-      <c r="N76" s="3"/>
-      <c r="O76" s="3"/>
-      <c r="P76" s="11"/>
-    </row>
-    <row r="77" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="3"/>
-      <c r="B77" s="3"/>
-      <c r="C77" s="3"/>
-      <c r="D77" s="25">
-        <v>1</v>
-      </c>
-      <c r="E77" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="F77" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="G77" s="11"/>
-      <c r="H77" s="11"/>
-      <c r="I77" s="11"/>
-      <c r="J77" s="3"/>
-      <c r="K77" s="3"/>
-      <c r="L77" s="3"/>
-      <c r="M77" s="3"/>
-      <c r="N77" s="3"/>
-      <c r="O77" s="3"/>
-      <c r="P77" s="11"/>
-    </row>
-    <row r="78" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="3"/>
-      <c r="B78" s="3"/>
-      <c r="C78" s="3"/>
-      <c r="D78" s="25">
-        <v>2</v>
-      </c>
-      <c r="E78" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="F78" s="25" t="s">
-        <v>64</v>
       </c>
       <c r="G78" s="11"/>
       <c r="H78" s="11"/>
@@ -2985,14 +3040,14 @@
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
-      <c r="D79" s="25">
-        <v>3</v>
-      </c>
-      <c r="E79" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="F79" s="25" t="s">
-        <v>65</v>
+      <c r="D79" s="24">
+        <v>1</v>
+      </c>
+      <c r="E79" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="F79" s="24" t="s">
+        <v>63</v>
       </c>
       <c r="G79" s="11"/>
       <c r="H79" s="11"/>
@@ -3009,14 +3064,14 @@
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
-      <c r="D80" s="25">
-        <v>4</v>
-      </c>
-      <c r="E80" s="25" t="s">
+      <c r="D80" s="24">
+        <v>2</v>
+      </c>
+      <c r="E80" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="F80" s="25" t="s">
-        <v>132</v>
+      <c r="F80" s="24" t="s">
+        <v>64</v>
       </c>
       <c r="G80" s="11"/>
       <c r="H80" s="11"/>
@@ -3033,14 +3088,14 @@
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
-      <c r="D81" s="25">
-        <v>5</v>
-      </c>
-      <c r="E81" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="F81" s="25" t="s">
-        <v>134</v>
+      <c r="D81" s="24">
+        <v>3</v>
+      </c>
+      <c r="E81" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="F81" s="24" t="s">
+        <v>65</v>
       </c>
       <c r="G81" s="11"/>
       <c r="H81" s="11"/>
@@ -3057,14 +3112,14 @@
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
-      <c r="D82" s="25">
-        <v>6</v>
-      </c>
-      <c r="E82" s="25" t="s">
-        <v>101</v>
-      </c>
-      <c r="F82" s="25" t="s">
-        <v>133</v>
+      <c r="D82" s="24">
+        <v>4</v>
+      </c>
+      <c r="E82" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="F82" s="24" t="s">
+        <v>132</v>
       </c>
       <c r="G82" s="11"/>
       <c r="H82" s="11"/>
@@ -3081,14 +3136,14 @@
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
-      <c r="D83" s="25">
-        <v>7</v>
-      </c>
-      <c r="E83" s="25" t="s">
+      <c r="D83" s="24">
+        <v>5</v>
+      </c>
+      <c r="E83" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="F83" s="25" t="s">
-        <v>74</v>
+      <c r="F83" s="24" t="s">
+        <v>134</v>
       </c>
       <c r="G83" s="11"/>
       <c r="H83" s="11"/>
@@ -3105,14 +3160,14 @@
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
-      <c r="D84" s="25">
-        <v>8</v>
-      </c>
-      <c r="E84" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="F84" s="25" t="s">
-        <v>75</v>
+      <c r="D84" s="24">
+        <v>6</v>
+      </c>
+      <c r="E84" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="F84" s="24" t="s">
+        <v>133</v>
       </c>
       <c r="G84" s="11"/>
       <c r="H84" s="11"/>
@@ -3129,16 +3184,16 @@
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
-      <c r="D85" s="25">
-        <v>9</v>
-      </c>
-      <c r="E85" s="25" t="s">
-        <v>101</v>
-      </c>
-      <c r="F85" s="25" t="s">
-        <v>135</v>
-      </c>
-      <c r="G85" s="11"/>
+      <c r="D85" s="26">
+        <v>7</v>
+      </c>
+      <c r="E85" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="F85" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="G85" s="29"/>
       <c r="H85" s="11"/>
       <c r="I85" s="11"/>
       <c r="J85" s="3"/>
@@ -3153,16 +3208,16 @@
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
-      <c r="D86" s="25">
-        <v>10</v>
-      </c>
-      <c r="E86" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="F86" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="G86" s="11"/>
+      <c r="D86" s="26">
+        <v>8</v>
+      </c>
+      <c r="E86" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="F86" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="G86" s="30"/>
       <c r="H86" s="11"/>
       <c r="I86" s="11"/>
       <c r="J86" s="3"/>
@@ -3177,14 +3232,14 @@
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
-      <c r="D87" s="25">
-        <v>11</v>
-      </c>
-      <c r="E87" s="25" t="s">
+      <c r="D87" s="24">
+        <v>9</v>
+      </c>
+      <c r="E87" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="F87" s="25" t="s">
-        <v>136</v>
+      <c r="F87" s="24" t="s">
+        <v>74</v>
       </c>
       <c r="G87" s="11"/>
       <c r="H87" s="11"/>
@@ -3201,14 +3256,14 @@
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
-      <c r="D88" s="25">
-        <v>12</v>
-      </c>
-      <c r="E88" s="25" t="s">
-        <v>101</v>
-      </c>
-      <c r="F88" s="25" t="s">
-        <v>77</v>
+      <c r="D88" s="24">
+        <v>10</v>
+      </c>
+      <c r="E88" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="F88" s="24" t="s">
+        <v>75</v>
       </c>
       <c r="G88" s="11"/>
       <c r="H88" s="11"/>
@@ -3225,14 +3280,14 @@
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
-      <c r="D89" s="25">
-        <v>13</v>
-      </c>
-      <c r="E89" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="F89" s="25" t="s">
-        <v>78</v>
+      <c r="D89" s="24">
+        <v>11</v>
+      </c>
+      <c r="E89" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="F89" s="24" t="s">
+        <v>135</v>
       </c>
       <c r="G89" s="11"/>
       <c r="H89" s="11"/>
@@ -3249,14 +3304,14 @@
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
-      <c r="D90" s="25">
-        <v>14</v>
-      </c>
-      <c r="E90" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="F90" s="25" t="s">
-        <v>79</v>
+      <c r="D90" s="24">
+        <v>12</v>
+      </c>
+      <c r="E90" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="F90" s="24" t="s">
+        <v>76</v>
       </c>
       <c r="G90" s="11"/>
       <c r="H90" s="11"/>
@@ -3273,14 +3328,14 @@
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
-      <c r="D91" s="25">
-        <v>15</v>
-      </c>
-      <c r="E91" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="F91" s="25" t="s">
-        <v>80</v>
+      <c r="D91" s="24">
+        <v>13</v>
+      </c>
+      <c r="E91" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="F91" s="24" t="s">
+        <v>136</v>
       </c>
       <c r="G91" s="11"/>
       <c r="H91" s="11"/>
@@ -3297,14 +3352,14 @@
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
-      <c r="D92" s="25">
-        <v>16</v>
-      </c>
-      <c r="E92" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="F92" s="25" t="s">
-        <v>81</v>
+      <c r="D92" s="24">
+        <v>14</v>
+      </c>
+      <c r="E92" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="F92" s="24" t="s">
+        <v>77</v>
       </c>
       <c r="G92" s="11"/>
       <c r="H92" s="11"/>
@@ -3321,14 +3376,14 @@
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
-      <c r="D93" s="25">
-        <v>17</v>
-      </c>
-      <c r="E93" s="25" t="s">
+      <c r="D93" s="26">
+        <v>15</v>
+      </c>
+      <c r="E93" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="F93" s="25" t="s">
-        <v>82</v>
+      <c r="F93" s="24" t="s">
+        <v>78</v>
       </c>
       <c r="G93" s="11"/>
       <c r="H93" s="11"/>
@@ -3345,14 +3400,14 @@
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
-      <c r="D94" s="25">
-        <v>18</v>
-      </c>
-      <c r="E94" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="F94" s="25" t="s">
-        <v>103</v>
+      <c r="D94" s="26">
+        <v>16</v>
+      </c>
+      <c r="E94" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="F94" s="24" t="s">
+        <v>79</v>
       </c>
       <c r="G94" s="11"/>
       <c r="H94" s="11"/>
@@ -3369,14 +3424,14 @@
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
-      <c r="D95" s="25">
-        <v>19</v>
-      </c>
-      <c r="E95" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="F95" s="25" t="s">
-        <v>104</v>
+      <c r="D95" s="24">
+        <v>17</v>
+      </c>
+      <c r="E95" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="F95" s="24" t="s">
+        <v>80</v>
       </c>
       <c r="G95" s="11"/>
       <c r="H95" s="11"/>
@@ -3393,14 +3448,14 @@
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
-      <c r="D96" s="25">
-        <v>20</v>
-      </c>
-      <c r="E96" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="F96" s="25" t="s">
-        <v>105</v>
+      <c r="D96" s="24">
+        <v>18</v>
+      </c>
+      <c r="E96" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="F96" s="24" t="s">
+        <v>81</v>
       </c>
       <c r="G96" s="11"/>
       <c r="H96" s="11"/>
@@ -3417,16 +3472,16 @@
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
-      <c r="D97" s="25">
-        <v>21</v>
-      </c>
-      <c r="E97" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="F97" s="25" t="s">
-        <v>106</v>
-      </c>
-      <c r="G97" s="25"/>
+      <c r="D97" s="24">
+        <v>19</v>
+      </c>
+      <c r="E97" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="F97" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="G97" s="11"/>
       <c r="H97" s="11"/>
       <c r="I97" s="11"/>
       <c r="J97" s="3"/>
@@ -3441,16 +3496,16 @@
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
-      <c r="D98" s="25">
-        <v>22</v>
-      </c>
-      <c r="E98" s="25" t="s">
-        <v>101</v>
-      </c>
-      <c r="F98" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="G98" s="25"/>
+      <c r="D98" s="24">
+        <v>20</v>
+      </c>
+      <c r="E98" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="F98" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="G98" s="11"/>
       <c r="H98" s="11"/>
       <c r="I98" s="11"/>
       <c r="J98" s="3"/>
@@ -3465,16 +3520,16 @@
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
-      <c r="D99" s="25">
-        <v>23</v>
-      </c>
-      <c r="E99" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="F99" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="G99" s="25"/>
+      <c r="D99" s="24">
+        <v>21</v>
+      </c>
+      <c r="E99" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="F99" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="G99" s="11"/>
       <c r="H99" s="11"/>
       <c r="I99" s="11"/>
       <c r="J99" s="3"/>
@@ -3489,14 +3544,14 @@
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
-      <c r="D100" s="25">
-        <v>24</v>
-      </c>
-      <c r="E100" s="25" t="s">
+      <c r="D100" s="24">
+        <v>22</v>
+      </c>
+      <c r="E100" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="F100" s="25" t="s">
-        <v>138</v>
+      <c r="F100" s="24" t="s">
+        <v>105</v>
       </c>
       <c r="G100" s="11"/>
       <c r="H100" s="11"/>
@@ -3513,16 +3568,16 @@
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
-      <c r="D101" s="25">
-        <v>25</v>
-      </c>
-      <c r="E101" s="25" t="s">
-        <v>101</v>
-      </c>
-      <c r="F101" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="G101" s="11"/>
+      <c r="D101" s="26">
+        <v>23</v>
+      </c>
+      <c r="E101" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="F101" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="G101" s="24"/>
       <c r="H101" s="11"/>
       <c r="I101" s="11"/>
       <c r="J101" s="3"/>
@@ -3537,16 +3592,16 @@
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
-      <c r="D102" s="25">
-        <v>26</v>
-      </c>
-      <c r="E102" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="F102" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="G102" s="11"/>
+      <c r="D102" s="26">
+        <v>24</v>
+      </c>
+      <c r="E102" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="F102" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="G102" s="24"/>
       <c r="H102" s="11"/>
       <c r="I102" s="11"/>
       <c r="J102" s="3"/>
@@ -3561,16 +3616,16 @@
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
-      <c r="D103" s="25">
-        <v>27</v>
-      </c>
-      <c r="E103" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="F103" s="25" t="s">
-        <v>110</v>
-      </c>
-      <c r="G103" s="11"/>
+      <c r="D103" s="24">
+        <v>25</v>
+      </c>
+      <c r="E103" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="F103" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="G103" s="24"/>
       <c r="H103" s="11"/>
       <c r="I103" s="11"/>
       <c r="J103" s="3"/>
@@ -3585,14 +3640,14 @@
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
-      <c r="D104" s="25">
-        <v>28</v>
-      </c>
-      <c r="E104" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="F104" s="25" t="s">
-        <v>111</v>
+      <c r="D104" s="24">
+        <v>26</v>
+      </c>
+      <c r="E104" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="F104" s="24" t="s">
+        <v>138</v>
       </c>
       <c r="G104" s="11"/>
       <c r="H104" s="11"/>
@@ -3609,14 +3664,14 @@
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
-      <c r="D105" s="25">
-        <v>29</v>
-      </c>
-      <c r="E105" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="F105" s="25" t="s">
-        <v>112</v>
+      <c r="D105" s="24">
+        <v>27</v>
+      </c>
+      <c r="E105" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="F105" s="24" t="s">
+        <v>108</v>
       </c>
       <c r="G105" s="11"/>
       <c r="H105" s="11"/>
@@ -3633,14 +3688,14 @@
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
-      <c r="D106" s="25">
-        <v>30</v>
-      </c>
-      <c r="E106" s="25" t="s">
+      <c r="D106" s="24">
+        <v>28</v>
+      </c>
+      <c r="E106" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="F106" s="25" t="s">
-        <v>113</v>
+      <c r="F106" s="24" t="s">
+        <v>109</v>
       </c>
       <c r="G106" s="11"/>
       <c r="H106" s="11"/>
@@ -3657,14 +3712,14 @@
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
-      <c r="D107" s="25">
-        <v>31</v>
-      </c>
-      <c r="E107" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="F107" s="25" t="s">
-        <v>114</v>
+      <c r="D107" s="24">
+        <v>29</v>
+      </c>
+      <c r="E107" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="F107" s="24" t="s">
+        <v>110</v>
       </c>
       <c r="G107" s="11"/>
       <c r="H107" s="11"/>
@@ -3681,14 +3736,14 @@
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
-      <c r="D108" s="25">
-        <v>32</v>
-      </c>
-      <c r="E108" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="F108" s="25" t="s">
-        <v>115</v>
+      <c r="D108" s="24">
+        <v>30</v>
+      </c>
+      <c r="E108" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="F108" s="24" t="s">
+        <v>111</v>
       </c>
       <c r="G108" s="11"/>
       <c r="H108" s="11"/>
@@ -3705,14 +3760,14 @@
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
-      <c r="D109" s="25">
-        <v>33</v>
-      </c>
-      <c r="E109" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="F109" s="25" t="s">
-        <v>116</v>
+      <c r="D109" s="26">
+        <v>31</v>
+      </c>
+      <c r="E109" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="F109" s="24" t="s">
+        <v>112</v>
       </c>
       <c r="G109" s="11"/>
       <c r="H109" s="11"/>
@@ -3729,14 +3784,14 @@
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
-      <c r="D110" s="25">
-        <v>34</v>
-      </c>
-      <c r="E110" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="F110" s="25" t="s">
-        <v>117</v>
+      <c r="D110" s="26">
+        <v>32</v>
+      </c>
+      <c r="E110" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="F110" s="24" t="s">
+        <v>113</v>
       </c>
       <c r="G110" s="11"/>
       <c r="H110" s="11"/>
@@ -3753,14 +3808,14 @@
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
-      <c r="D111" s="25">
-        <v>35</v>
-      </c>
-      <c r="E111" s="25" t="s">
+      <c r="D111" s="24">
+        <v>33</v>
+      </c>
+      <c r="E111" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="F111" s="25" t="s">
-        <v>118</v>
+      <c r="F111" s="24" t="s">
+        <v>114</v>
       </c>
       <c r="G111" s="11"/>
       <c r="H111" s="11"/>
@@ -3777,14 +3832,14 @@
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
-      <c r="D112" s="25">
-        <v>36</v>
-      </c>
-      <c r="E112" s="25" t="s">
+      <c r="D112" s="24">
+        <v>34</v>
+      </c>
+      <c r="E112" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="F112" s="25" t="s">
-        <v>119</v>
+      <c r="F112" s="24" t="s">
+        <v>115</v>
       </c>
       <c r="G112" s="11"/>
       <c r="H112" s="11"/>
@@ -3801,14 +3856,14 @@
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
-      <c r="D113" s="25">
-        <v>37</v>
-      </c>
-      <c r="E113" s="25" t="s">
+      <c r="D113" s="24">
+        <v>35</v>
+      </c>
+      <c r="E113" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="F113" s="25" t="s">
-        <v>120</v>
+      <c r="F113" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="G113" s="11"/>
       <c r="H113" s="11"/>
@@ -3825,14 +3880,14 @@
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
-      <c r="D114" s="25">
-        <v>38</v>
-      </c>
-      <c r="E114" s="25" t="s">
+      <c r="D114" s="24">
+        <v>36</v>
+      </c>
+      <c r="E114" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="F114" s="25" t="s">
-        <v>121</v>
+      <c r="F114" s="24" t="s">
+        <v>117</v>
       </c>
       <c r="G114" s="11"/>
       <c r="H114" s="11"/>
@@ -3849,14 +3904,14 @@
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
-      <c r="D115" s="25">
-        <v>39</v>
-      </c>
-      <c r="E115" s="25" t="s">
+      <c r="D115" s="24">
+        <v>37</v>
+      </c>
+      <c r="E115" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="F115" s="25" t="s">
-        <v>122</v>
+      <c r="F115" s="24" t="s">
+        <v>118</v>
       </c>
       <c r="G115" s="11"/>
       <c r="H115" s="11"/>
@@ -3873,14 +3928,14 @@
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
-      <c r="D116" s="25">
-        <v>40</v>
-      </c>
-      <c r="E116" s="25" t="s">
+      <c r="D116" s="24">
+        <v>38</v>
+      </c>
+      <c r="E116" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="F116" s="25" t="s">
-        <v>123</v>
+      <c r="F116" s="24" t="s">
+        <v>119</v>
       </c>
       <c r="G116" s="11"/>
       <c r="H116" s="11"/>
@@ -3897,14 +3952,14 @@
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
-      <c r="D117" s="25">
-        <v>41</v>
-      </c>
-      <c r="E117" s="25" t="s">
+      <c r="D117" s="26">
+        <v>39</v>
+      </c>
+      <c r="E117" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="F117" s="25" t="s">
-        <v>124</v>
+      <c r="F117" s="24" t="s">
+        <v>120</v>
       </c>
       <c r="G117" s="11"/>
       <c r="H117" s="11"/>
@@ -3921,14 +3976,14 @@
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
-      <c r="D118" s="25">
-        <v>42</v>
-      </c>
-      <c r="E118" s="25" t="s">
+      <c r="D118" s="26">
+        <v>40</v>
+      </c>
+      <c r="E118" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="F118" s="25" t="s">
-        <v>125</v>
+      <c r="F118" s="24" t="s">
+        <v>121</v>
       </c>
       <c r="G118" s="11"/>
       <c r="H118" s="11"/>
@@ -3941,35 +3996,43 @@
       <c r="O118" s="3"/>
       <c r="P118" s="11"/>
     </row>
-    <row r="119" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="11"/>
-      <c r="B119" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="C119" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="D119" s="17"/>
-      <c r="E119" s="17"/>
-      <c r="F119" s="18"/>
-      <c r="G119" s="17"/>
-      <c r="H119" s="17"/>
-      <c r="I119" s="17"/>
-      <c r="J119" s="17"/>
-      <c r="K119" s="17"/>
-      <c r="L119" s="17"/>
-      <c r="M119" s="17"/>
-      <c r="N119" s="17"/>
-      <c r="O119" s="17"/>
-      <c r="P119" s="17"/>
-    </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="3"/>
+      <c r="B119" s="3"/>
+      <c r="C119" s="3"/>
+      <c r="D119" s="24">
+        <v>41</v>
+      </c>
+      <c r="E119" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="F119" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="G119" s="11"/>
+      <c r="H119" s="11"/>
+      <c r="I119" s="11"/>
+      <c r="J119" s="3"/>
+      <c r="K119" s="3"/>
+      <c r="L119" s="3"/>
+      <c r="M119" s="3"/>
+      <c r="N119" s="3"/>
+      <c r="O119" s="3"/>
+      <c r="P119" s="11"/>
+    </row>
+    <row r="120" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
-      <c r="D120" s="16"/>
-      <c r="E120" s="11"/>
-      <c r="F120" s="11"/>
+      <c r="D120" s="24">
+        <v>42</v>
+      </c>
+      <c r="E120" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="F120" s="24" t="s">
+        <v>123</v>
+      </c>
       <c r="G120" s="11"/>
       <c r="H120" s="11"/>
       <c r="I120" s="11"/>
@@ -3981,13 +4044,19 @@
       <c r="O120" s="3"/>
       <c r="P120" s="11"/>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
-      <c r="D121" s="16"/>
-      <c r="E121" s="11"/>
-      <c r="F121" s="11"/>
+      <c r="D121" s="24">
+        <v>43</v>
+      </c>
+      <c r="E121" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="F121" s="24" t="s">
+        <v>124</v>
+      </c>
       <c r="G121" s="11"/>
       <c r="H121" s="11"/>
       <c r="I121" s="11"/>
@@ -3999,45 +4068,51 @@
       <c r="O121" s="3"/>
       <c r="P121" s="11"/>
     </row>
-    <row r="122" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="11"/>
-      <c r="B122" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="C122" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="D122" s="17"/>
-      <c r="E122" s="17"/>
-      <c r="F122" s="11"/>
-      <c r="G122" s="17"/>
-      <c r="H122" s="17"/>
-      <c r="I122" s="17"/>
-      <c r="J122" s="17"/>
-      <c r="K122" s="17"/>
-      <c r="L122" s="17"/>
-      <c r="M122" s="17"/>
-      <c r="N122" s="17"/>
-      <c r="O122" s="17"/>
-      <c r="P122" s="17"/>
-    </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A123" s="3"/>
-      <c r="B123" s="3"/>
-      <c r="C123" s="3"/>
-      <c r="D123" s="16"/>
-      <c r="E123" s="11"/>
-      <c r="F123" s="11"/>
-      <c r="G123" s="11"/>
-      <c r="H123" s="11"/>
-      <c r="I123" s="11"/>
-      <c r="J123" s="3"/>
-      <c r="K123" s="3"/>
-      <c r="L123" s="3"/>
-      <c r="M123" s="3"/>
-      <c r="N123" s="3"/>
-      <c r="O123" s="3"/>
-      <c r="P123" s="11"/>
+    <row r="122" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="3"/>
+      <c r="B122" s="3"/>
+      <c r="C122" s="3"/>
+      <c r="D122" s="24">
+        <v>44</v>
+      </c>
+      <c r="E122" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="F122" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="G122" s="11"/>
+      <c r="H122" s="11"/>
+      <c r="I122" s="11"/>
+      <c r="J122" s="3"/>
+      <c r="K122" s="3"/>
+      <c r="L122" s="3"/>
+      <c r="M122" s="3"/>
+      <c r="N122" s="3"/>
+      <c r="O122" s="3"/>
+      <c r="P122" s="11"/>
+    </row>
+    <row r="123" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="11"/>
+      <c r="B123" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C123" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D123" s="17"/>
+      <c r="E123" s="17"/>
+      <c r="F123" s="18"/>
+      <c r="G123" s="17"/>
+      <c r="H123" s="17"/>
+      <c r="I123" s="17"/>
+      <c r="J123" s="17"/>
+      <c r="K123" s="17"/>
+      <c r="L123" s="17"/>
+      <c r="M123" s="17"/>
+      <c r="N123" s="17"/>
+      <c r="O123" s="17"/>
+      <c r="P123" s="17"/>
     </row>
     <row r="124" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A124" s="3"/>
@@ -4057,45 +4132,45 @@
       <c r="O124" s="3"/>
       <c r="P124" s="11"/>
     </row>
-    <row r="125" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="11"/>
-      <c r="B125" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C125" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D125" s="17"/>
-      <c r="E125" s="17"/>
-      <c r="F125" s="17"/>
-      <c r="G125" s="17"/>
-      <c r="H125" s="17"/>
-      <c r="I125" s="17"/>
-      <c r="J125" s="17"/>
-      <c r="K125" s="17"/>
-      <c r="L125" s="17"/>
-      <c r="M125" s="17"/>
-      <c r="N125" s="17"/>
-      <c r="O125" s="17"/>
-      <c r="P125" s="17"/>
-    </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A126" s="3"/>
-      <c r="B126" s="3"/>
-      <c r="C126" s="3"/>
-      <c r="D126" s="16"/>
-      <c r="E126" s="11"/>
+    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A125" s="3"/>
+      <c r="B125" s="3"/>
+      <c r="C125" s="3"/>
+      <c r="D125" s="16"/>
+      <c r="E125" s="11"/>
+      <c r="F125" s="11"/>
+      <c r="G125" s="11"/>
+      <c r="H125" s="11"/>
+      <c r="I125" s="11"/>
+      <c r="J125" s="3"/>
+      <c r="K125" s="3"/>
+      <c r="L125" s="3"/>
+      <c r="M125" s="3"/>
+      <c r="N125" s="3"/>
+      <c r="O125" s="3"/>
+      <c r="P125" s="11"/>
+    </row>
+    <row r="126" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="11"/>
+      <c r="B126" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C126" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D126" s="17"/>
+      <c r="E126" s="17"/>
       <c r="F126" s="11"/>
-      <c r="G126" s="11"/>
-      <c r="H126" s="11"/>
-      <c r="I126" s="11"/>
-      <c r="J126" s="3"/>
-      <c r="K126" s="3"/>
-      <c r="L126" s="3"/>
-      <c r="M126" s="3"/>
-      <c r="N126" s="3"/>
-      <c r="O126" s="3"/>
-      <c r="P126" s="11"/>
+      <c r="G126" s="17"/>
+      <c r="H126" s="17"/>
+      <c r="I126" s="17"/>
+      <c r="J126" s="17"/>
+      <c r="K126" s="17"/>
+      <c r="L126" s="17"/>
+      <c r="M126" s="17"/>
+      <c r="N126" s="17"/>
+      <c r="O126" s="17"/>
+      <c r="P126" s="17"/>
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A127" s="3"/>
@@ -4119,73 +4194,77 @@
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
-      <c r="D128" s="3"/>
-      <c r="E128" s="3"/>
-      <c r="F128" s="17"/>
-      <c r="G128" s="3"/>
-      <c r="H128" s="3"/>
-      <c r="I128" s="3"/>
+      <c r="D128" s="16"/>
+      <c r="E128" s="11"/>
+      <c r="F128" s="11"/>
+      <c r="G128" s="11"/>
+      <c r="H128" s="11"/>
+      <c r="I128" s="11"/>
       <c r="J128" s="3"/>
       <c r="K128" s="3"/>
       <c r="L128" s="3"/>
       <c r="M128" s="3"/>
       <c r="N128" s="3"/>
       <c r="O128" s="3"/>
-      <c r="P128" s="3"/>
-    </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A129" s="3"/>
-      <c r="B129" s="3"/>
-      <c r="C129" s="3"/>
-      <c r="D129" s="3"/>
-      <c r="E129" s="3"/>
-      <c r="F129" s="11"/>
-      <c r="G129" s="3"/>
-      <c r="H129" s="3"/>
-      <c r="I129" s="3"/>
-      <c r="J129" s="3"/>
-      <c r="K129" s="3"/>
-      <c r="L129" s="3"/>
-      <c r="M129" s="3"/>
-      <c r="N129" s="3"/>
-      <c r="O129" s="3"/>
-      <c r="P129" s="3"/>
+      <c r="P128" s="11"/>
+    </row>
+    <row r="129" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="11"/>
+      <c r="B129" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C129" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D129" s="17"/>
+      <c r="E129" s="17"/>
+      <c r="F129" s="17"/>
+      <c r="G129" s="17"/>
+      <c r="H129" s="17"/>
+      <c r="I129" s="17"/>
+      <c r="J129" s="17"/>
+      <c r="K129" s="17"/>
+      <c r="L129" s="17"/>
+      <c r="M129" s="17"/>
+      <c r="N129" s="17"/>
+      <c r="O129" s="17"/>
+      <c r="P129" s="17"/>
     </row>
     <row r="130" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
-      <c r="D130" s="3"/>
-      <c r="E130" s="3"/>
+      <c r="D130" s="16"/>
+      <c r="E130" s="11"/>
       <c r="F130" s="11"/>
-      <c r="G130" s="3"/>
-      <c r="H130" s="3"/>
-      <c r="I130" s="3"/>
+      <c r="G130" s="11"/>
+      <c r="H130" s="11"/>
+      <c r="I130" s="11"/>
       <c r="J130" s="3"/>
       <c r="K130" s="3"/>
       <c r="L130" s="3"/>
       <c r="M130" s="3"/>
       <c r="N130" s="3"/>
       <c r="O130" s="3"/>
-      <c r="P130" s="3"/>
+      <c r="P130" s="11"/>
     </row>
     <row r="131" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
-      <c r="D131" s="3"/>
-      <c r="E131" s="3"/>
-      <c r="F131" s="17"/>
-      <c r="G131" s="3"/>
-      <c r="H131" s="3"/>
-      <c r="I131" s="3"/>
+      <c r="D131" s="16"/>
+      <c r="E131" s="11"/>
+      <c r="F131" s="11"/>
+      <c r="G131" s="11"/>
+      <c r="H131" s="11"/>
+      <c r="I131" s="11"/>
       <c r="J131" s="3"/>
       <c r="K131" s="3"/>
       <c r="L131" s="3"/>
       <c r="M131" s="3"/>
       <c r="N131" s="3"/>
       <c r="O131" s="3"/>
-      <c r="P131" s="3"/>
+      <c r="P131" s="11"/>
     </row>
     <row r="132" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A132" s="3"/>
@@ -4193,7 +4272,7 @@
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
-      <c r="F132" s="11"/>
+      <c r="F132" s="17"/>
       <c r="G132" s="3"/>
       <c r="H132" s="3"/>
       <c r="I132" s="3"/>
@@ -4229,7 +4308,7 @@
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
-      <c r="F134" s="3"/>
+      <c r="F134" s="11"/>
       <c r="G134" s="3"/>
       <c r="H134" s="3"/>
       <c r="I134" s="3"/>
@@ -4247,7 +4326,7 @@
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
-      <c r="F135" s="3"/>
+      <c r="F135" s="17"/>
       <c r="G135" s="3"/>
       <c r="H135" s="3"/>
       <c r="I135" s="3"/>
@@ -4265,7 +4344,7 @@
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
-      <c r="F136" s="3"/>
+      <c r="F136" s="11"/>
       <c r="G136" s="3"/>
       <c r="H136" s="3"/>
       <c r="I136" s="3"/>
@@ -4283,7 +4362,7 @@
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
-      <c r="F137" s="3"/>
+      <c r="F137" s="11"/>
       <c r="G137" s="3"/>
       <c r="H137" s="3"/>
       <c r="I137" s="3"/>
@@ -4314,20 +4393,76 @@
       <c r="P138" s="3"/>
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A139" s="3"/>
+      <c r="B139" s="3"/>
       <c r="C139" s="3"/>
+      <c r="D139" s="3"/>
+      <c r="E139" s="3"/>
       <c r="F139" s="3"/>
+      <c r="G139" s="3"/>
+      <c r="H139" s="3"/>
+      <c r="I139" s="3"/>
+      <c r="J139" s="3"/>
+      <c r="K139" s="3"/>
+      <c r="L139" s="3"/>
+      <c r="M139" s="3"/>
+      <c r="N139" s="3"/>
+      <c r="O139" s="3"/>
+      <c r="P139" s="3"/>
     </row>
     <row r="140" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A140" s="3"/>
+      <c r="B140" s="3"/>
       <c r="C140" s="3"/>
+      <c r="D140" s="3"/>
+      <c r="E140" s="3"/>
       <c r="F140" s="3"/>
+      <c r="G140" s="3"/>
+      <c r="H140" s="3"/>
+      <c r="I140" s="3"/>
+      <c r="J140" s="3"/>
+      <c r="K140" s="3"/>
+      <c r="L140" s="3"/>
+      <c r="M140" s="3"/>
+      <c r="N140" s="3"/>
+      <c r="O140" s="3"/>
+      <c r="P140" s="3"/>
     </row>
     <row r="141" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A141" s="3"/>
+      <c r="B141" s="3"/>
       <c r="C141" s="3"/>
+      <c r="D141" s="3"/>
+      <c r="E141" s="3"/>
       <c r="F141" s="3"/>
+      <c r="G141" s="3"/>
+      <c r="H141" s="3"/>
+      <c r="I141" s="3"/>
+      <c r="J141" s="3"/>
+      <c r="K141" s="3"/>
+      <c r="L141" s="3"/>
+      <c r="M141" s="3"/>
+      <c r="N141" s="3"/>
+      <c r="O141" s="3"/>
+      <c r="P141" s="3"/>
     </row>
     <row r="142" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A142" s="3"/>
+      <c r="B142" s="3"/>
       <c r="C142" s="3"/>
+      <c r="D142" s="3"/>
+      <c r="E142" s="3"/>
       <c r="F142" s="3"/>
+      <c r="G142" s="3"/>
+      <c r="H142" s="3"/>
+      <c r="I142" s="3"/>
+      <c r="J142" s="3"/>
+      <c r="K142" s="3"/>
+      <c r="L142" s="3"/>
+      <c r="M142" s="3"/>
+      <c r="N142" s="3"/>
+      <c r="O142" s="3"/>
+      <c r="P142" s="3"/>
     </row>
     <row r="143" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C143" s="3"/>
@@ -4337,52 +4472,56 @@
       <c r="C144" s="3"/>
       <c r="F144" s="3"/>
     </row>
-    <row r="145" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C145" s="3"/>
-    </row>
-    <row r="146" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="F145" s="3"/>
+    </row>
+    <row r="146" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C146" s="3"/>
-    </row>
-    <row r="147" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="F146" s="3"/>
+    </row>
+    <row r="147" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C147" s="3"/>
-    </row>
-    <row r="148" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="F147" s="3"/>
+    </row>
+    <row r="148" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C148" s="3"/>
-    </row>
-    <row r="149" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="F148" s="3"/>
+    </row>
+    <row r="149" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C149" s="3"/>
     </row>
-    <row r="150" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C150" s="3"/>
     </row>
-    <row r="151" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C151" s="3"/>
     </row>
-    <row r="152" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C152" s="3"/>
     </row>
-    <row r="153" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C153" s="3"/>
     </row>
-    <row r="154" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C154" s="3"/>
     </row>
-    <row r="155" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C155" s="3"/>
     </row>
-    <row r="156" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C156" s="3"/>
     </row>
-    <row r="157" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C157" s="3"/>
     </row>
-    <row r="158" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C158" s="3"/>
     </row>
-    <row r="159" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C159" s="3"/>
     </row>
-    <row r="160" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C160" s="3"/>
     </row>
     <row r="161" spans="3:3" x14ac:dyDescent="0.25">
@@ -6839,28 +6978,40 @@
     <row r="978" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C978" s="3"/>
     </row>
+    <row r="979" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C979" s="3"/>
+    </row>
+    <row r="980" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C980" s="3"/>
+    </row>
+    <row r="981" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C981" s="3"/>
+    </row>
+    <row r="982" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C982" s="3"/>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatRows="0" insertRows="0" insertHyperlinks="0" deleteRows="0" sort="0" autoFilter="0"/>
-  <autoFilter ref="B10:P127" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="B10:P131" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="F1:P6"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="9">
-    <dataValidation allowBlank="1" showInputMessage="1" sqref="C11 C14 C17 C20 C23 C26 C29 C32 C35 C75 C119 C122 C125" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Object Code value" error="The Object code value shall be:_x000a_VARIABLE_x000a_RECORD_x000a_ARRAY" sqref="C12:C13 C15:C16 C18:C19 C21:C22 C24:C25 C27:C28 C30:C31 C33:C34 C36:C74 C76:C118 C120:C121 C123:C124 C126:C138" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation allowBlank="1" showInputMessage="1" sqref="C11 C14 C17 C20 C23 C26 C29 C32 C35 C77 C123 C126 C129" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Object Code value" error="The Object code value shall be:_x000a_VARIABLE_x000a_RECORD_x000a_ARRAY" sqref="C12:C13 C15:C16 C18:C19 C21:C22 C24:C25 C27:C28 C30:C31 C33:C34 C36:C76 C78:C122 C124:C125 C127:C128 C130:C142" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Category" error="The value for the entry category shall be _x000a_M : (mandatory)_x000a_O : (optional) _x000a_C : (conditional)" sqref="J36 J123:J124 J126:J138 J12:J13 J15:J16 J18:J19 J21:J22 J24:J25 J27:J28 J30:J31 J33:J34 J120:J121 J76:J118 J40:J74" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Category" error="The value for the entry category shall be _x000a_M : (mandatory)_x000a_O : (optional) _x000a_C : (conditional)" sqref="J36 J127:J128 J130:J142 J12:J13 J15:J16 J18:J19 J21:J22 J24:J25 J27:J28 J30:J31 J33:J34 J124:J125 J78:J122 J40:J76" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"M,O,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Backup/Setting Flag" error="The entry flag shall be_x000a_B : (Backup)_x000a_S : (Setting)" sqref="K36 K123:K124 K126:K138 K12:K13 K15:K16 K18:K19 K21:K22 K24:K25 K27:K28 K30:K31 K33:K34 K120:K121 K76:K118 K40:K74" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Backup/Setting Flag" error="The entry flag shall be_x000a_B : (Backup)_x000a_S : (Setting)" sqref="K36 K127:K128 K130:K142 K12:K13 K15:K16 K18:K19 K21:K22 K24:K25 K27:K28 K30:K31 K33:K34 K124:K125 K78:K122 K40:K76" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"B,S"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M36:O36 M123:O124 M12:O13 M18:O19 M24:O25 M30:O31 M76:O118 M120:O121 M126:O127 M15:O16 M21:O22 M27:O28 M33:O34 M40:O74" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M36:O36 M127:O128 M12:O13 M18:O19 M24:O25 M30:O31 M78:O122 M124:O125 M130:O131 M15:O16 M21:O22 M27:O28 M33:O34 M40:O76" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"rx,tx"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C139:C978" xr:uid="{00000000-0002-0000-0000-000005000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C143:C982" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J37:J39" xr:uid="{EA22EA21-8D48-45F2-A48B-5451B78F87F1}">

--- a/ArmCoreV1_QSPI/SSCProject/lan9252_app.xlsx
+++ b/ArmCoreV1_QSPI/SSCProject/lan9252_app.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SI\project\RTM_ON_NEW\FW-ArmCore\ArmCoreV1_QSPI\SSCProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A209D8DA-B5D9-4902-9B15-B19E1D529420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B45208-0198-4BA4-8E28-2AB224D37EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-36960" yWindow="-6180" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-7730" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Profile" sheetId="11" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Profile!$B$10:$P$198</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Profile!$B$1:$P$199</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Profile!$B$10:$P$203</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Profile!$B$1:$P$204</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="220">
   <si>
     <t>Device Profile:</t>
   </si>
@@ -915,10 +915,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>InU16_reserved2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>InU8_reserved3</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -996,13 +992,41 @@
   </si>
   <si>
     <t>REAL</t>
+  </si>
+  <si>
+    <t>InU8_reserved2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>UNSIGNED8</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>InU8_ethercat_Link_state</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>OutU8_fault_clear</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>OutU8_ethercat_Link_state</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>OutU8_fkp_vibration</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>OutU8_cpg_vibration</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1064,6 +1088,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1119,7 +1151,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
       <protection locked="0"/>
@@ -1182,6 +1214,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1488,7 +1523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T1049"/>
+  <dimension ref="A1:T1054"/>
   <sheetFormatPr defaultColWidth="10.7265625" defaultRowHeight="14" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.81640625" style="2" customWidth="1"/>
@@ -2475,11 +2510,11 @@
       <c r="D45" s="24">
         <v>9</v>
       </c>
-      <c r="E45" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="F45" s="24" t="s">
-        <v>193</v>
+      <c r="E45" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="F45" s="27" t="s">
+        <v>215</v>
       </c>
       <c r="G45" s="11"/>
       <c r="H45" s="11"/>
@@ -2503,7 +2538,7 @@
         <v>58</v>
       </c>
       <c r="F46" s="24" t="s">
-        <v>67</v>
+        <v>213</v>
       </c>
       <c r="G46" s="11"/>
       <c r="H46" s="11"/>
@@ -2527,7 +2562,7 @@
         <v>58</v>
       </c>
       <c r="F47" s="24" t="s">
-        <v>194</v>
+        <v>67</v>
       </c>
       <c r="G47" s="11"/>
       <c r="H47" s="11"/>
@@ -2548,10 +2583,10 @@
         <v>12</v>
       </c>
       <c r="E48" s="24" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F48" s="24" t="s">
-        <v>68</v>
+        <v>193</v>
       </c>
       <c r="G48" s="11"/>
       <c r="H48" s="11"/>
@@ -2572,10 +2607,10 @@
         <v>13</v>
       </c>
       <c r="E49" s="24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F49" s="24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G49" s="11"/>
       <c r="H49" s="11"/>
@@ -2599,7 +2634,7 @@
         <v>61</v>
       </c>
       <c r="F50" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G50" s="11"/>
       <c r="H50" s="11"/>
@@ -2623,7 +2658,7 @@
         <v>61</v>
       </c>
       <c r="F51" s="24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G51" s="11"/>
       <c r="H51" s="11"/>
@@ -2647,7 +2682,7 @@
         <v>61</v>
       </c>
       <c r="F52" s="24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G52" s="11"/>
       <c r="H52" s="11"/>
@@ -2668,10 +2703,10 @@
         <v>17</v>
       </c>
       <c r="E53" s="24" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F53" s="24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G53" s="11"/>
       <c r="H53" s="11"/>
@@ -2695,7 +2730,7 @@
         <v>58</v>
       </c>
       <c r="F54" s="24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G54" s="11"/>
       <c r="H54" s="11"/>
@@ -2716,10 +2751,10 @@
         <v>19</v>
       </c>
       <c r="E55" s="24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F55" s="24" t="s">
-        <v>195</v>
+        <v>74</v>
       </c>
       <c r="G55" s="11"/>
       <c r="H55" s="11"/>
@@ -2740,10 +2775,10 @@
         <v>20</v>
       </c>
       <c r="E56" s="24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F56" s="24" t="s">
-        <v>75</v>
+        <v>194</v>
       </c>
       <c r="G56" s="11"/>
       <c r="H56" s="11"/>
@@ -2767,7 +2802,7 @@
         <v>58</v>
       </c>
       <c r="F57" s="24" t="s">
-        <v>196</v>
+        <v>75</v>
       </c>
       <c r="G57" s="11"/>
       <c r="H57" s="11"/>
@@ -2788,10 +2823,10 @@
         <v>22</v>
       </c>
       <c r="E58" s="24" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F58" s="24" t="s">
-        <v>76</v>
+        <v>195</v>
       </c>
       <c r="G58" s="11"/>
       <c r="H58" s="11"/>
@@ -2812,10 +2847,10 @@
         <v>23</v>
       </c>
       <c r="E59" s="24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F59" s="24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G59" s="11"/>
       <c r="H59" s="11"/>
@@ -2839,7 +2874,7 @@
         <v>61</v>
       </c>
       <c r="F60" s="24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G60" s="11"/>
       <c r="H60" s="11"/>
@@ -2863,7 +2898,7 @@
         <v>61</v>
       </c>
       <c r="F61" s="24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G61" s="11"/>
       <c r="H61" s="11"/>
@@ -2887,7 +2922,7 @@
         <v>61</v>
       </c>
       <c r="F62" s="24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G62" s="11"/>
       <c r="H62" s="11"/>
@@ -2907,11 +2942,11 @@
       <c r="D63" s="24">
         <v>27</v>
       </c>
-      <c r="E63" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="F63" s="25" t="s">
-        <v>81</v>
+      <c r="E63" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="F63" s="24" t="s">
+        <v>80</v>
       </c>
       <c r="G63" s="11"/>
       <c r="H63" s="11"/>
@@ -2935,7 +2970,7 @@
         <v>53</v>
       </c>
       <c r="F64" s="25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G64" s="11"/>
       <c r="H64" s="11"/>
@@ -2955,11 +2990,11 @@
       <c r="D65" s="24">
         <v>29</v>
       </c>
-      <c r="E65" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="F65" s="24" t="s">
-        <v>197</v>
+      <c r="E65" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="F65" s="25" t="s">
+        <v>82</v>
       </c>
       <c r="G65" s="11"/>
       <c r="H65" s="11"/>
@@ -2979,11 +3014,11 @@
       <c r="D66" s="24">
         <v>30</v>
       </c>
-      <c r="E66" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="F66" s="25" t="s">
-        <v>83</v>
+      <c r="E66" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="F66" s="24" t="s">
+        <v>196</v>
       </c>
       <c r="G66" s="11"/>
       <c r="H66" s="11"/>
@@ -3004,10 +3039,10 @@
         <v>31</v>
       </c>
       <c r="E67" s="25" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F67" s="25" t="s">
-        <v>198</v>
+        <v>83</v>
       </c>
       <c r="G67" s="11"/>
       <c r="H67" s="11"/>
@@ -3028,10 +3063,10 @@
         <v>32</v>
       </c>
       <c r="E68" s="25" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="F68" s="25" t="s">
-        <v>84</v>
+        <v>197</v>
       </c>
       <c r="G68" s="11"/>
       <c r="H68" s="11"/>
@@ -3052,10 +3087,10 @@
         <v>33</v>
       </c>
       <c r="E69" s="25" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="F69" s="25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G69" s="11"/>
       <c r="H69" s="11"/>
@@ -3079,7 +3114,7 @@
         <v>55</v>
       </c>
       <c r="F70" s="25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G70" s="11"/>
       <c r="H70" s="11"/>
@@ -3103,7 +3138,7 @@
         <v>55</v>
       </c>
       <c r="F71" s="25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G71" s="11"/>
       <c r="H71" s="11"/>
@@ -3127,7 +3162,7 @@
         <v>55</v>
       </c>
       <c r="F72" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G72" s="11"/>
       <c r="H72" s="11"/>
@@ -3147,11 +3182,11 @@
       <c r="D73" s="24">
         <v>37</v>
       </c>
-      <c r="E73" s="24" t="s">
-        <v>89</v>
+      <c r="E73" s="25" t="s">
+        <v>55</v>
       </c>
       <c r="F73" s="25" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G73" s="11"/>
       <c r="H73" s="11"/>
@@ -3175,7 +3210,7 @@
         <v>89</v>
       </c>
       <c r="F74" s="25" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G74" s="11"/>
       <c r="H74" s="11"/>
@@ -3199,7 +3234,7 @@
         <v>89</v>
       </c>
       <c r="F75" s="25" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G75" s="11"/>
       <c r="H75" s="11"/>
@@ -3220,10 +3255,10 @@
         <v>40</v>
       </c>
       <c r="E76" s="24" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="F76" s="25" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G76" s="11"/>
       <c r="H76" s="11"/>
@@ -3247,7 +3282,7 @@
         <v>58</v>
       </c>
       <c r="F77" s="25" t="s">
-        <v>199</v>
+        <v>93</v>
       </c>
       <c r="G77" s="11"/>
       <c r="H77" s="11"/>
@@ -3268,10 +3303,10 @@
         <v>42</v>
       </c>
       <c r="E78" s="24" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F78" s="25" t="s">
-        <v>94</v>
+        <v>198</v>
       </c>
       <c r="G78" s="11"/>
       <c r="H78" s="11"/>
@@ -3292,10 +3327,10 @@
         <v>43</v>
       </c>
       <c r="E79" s="24" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="F79" s="25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G79" s="11"/>
       <c r="H79" s="11"/>
@@ -3319,7 +3354,7 @@
         <v>89</v>
       </c>
       <c r="F80" s="25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G80" s="11"/>
       <c r="H80" s="11"/>
@@ -3340,10 +3375,10 @@
         <v>45</v>
       </c>
       <c r="E81" s="24" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="F81" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G81" s="11"/>
       <c r="H81" s="11"/>
@@ -3367,7 +3402,7 @@
         <v>58</v>
       </c>
       <c r="F82" s="25" t="s">
-        <v>200</v>
+        <v>97</v>
       </c>
       <c r="G82" s="11"/>
       <c r="H82" s="11"/>
@@ -3388,10 +3423,10 @@
         <v>47</v>
       </c>
       <c r="E83" s="24" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F83" s="25" t="s">
-        <v>98</v>
+        <v>199</v>
       </c>
       <c r="G83" s="11"/>
       <c r="H83" s="11"/>
@@ -3415,7 +3450,7 @@
         <v>61</v>
       </c>
       <c r="F84" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G84" s="11"/>
       <c r="H84" s="11"/>
@@ -3436,10 +3471,10 @@
         <v>49</v>
       </c>
       <c r="E85" s="24" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="F85" s="25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G85" s="11"/>
       <c r="H85" s="11"/>
@@ -3460,10 +3495,10 @@
         <v>50</v>
       </c>
       <c r="E86" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="F86" s="24" t="s">
-        <v>101</v>
+        <v>89</v>
+      </c>
+      <c r="F86" s="25" t="s">
+        <v>100</v>
       </c>
       <c r="G86" s="11"/>
       <c r="H86" s="11"/>
@@ -3487,7 +3522,7 @@
         <v>58</v>
       </c>
       <c r="F87" s="24" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G87" s="11"/>
       <c r="H87" s="11"/>
@@ -3508,10 +3543,10 @@
         <v>52</v>
       </c>
       <c r="E88" s="24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F88" s="24" t="s">
-        <v>201</v>
+        <v>102</v>
       </c>
       <c r="G88" s="11"/>
       <c r="H88" s="11"/>
@@ -3532,10 +3567,10 @@
         <v>53</v>
       </c>
       <c r="E89" s="24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F89" s="24" t="s">
-        <v>103</v>
+        <v>200</v>
       </c>
       <c r="G89" s="11"/>
       <c r="H89" s="11"/>
@@ -3559,7 +3594,7 @@
         <v>58</v>
       </c>
       <c r="F90" s="24" t="s">
-        <v>202</v>
+        <v>103</v>
       </c>
       <c r="G90" s="11"/>
       <c r="H90" s="11"/>
@@ -3580,10 +3615,10 @@
         <v>55</v>
       </c>
       <c r="E91" s="24" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F91" s="24" t="s">
-        <v>104</v>
+        <v>201</v>
       </c>
       <c r="G91" s="11"/>
       <c r="H91" s="11"/>
@@ -3604,10 +3639,10 @@
         <v>56</v>
       </c>
       <c r="E92" s="24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F92" s="24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G92" s="11"/>
       <c r="H92" s="11"/>
@@ -3631,7 +3666,7 @@
         <v>61</v>
       </c>
       <c r="F93" s="24" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G93" s="11"/>
       <c r="H93" s="11"/>
@@ -3655,7 +3690,7 @@
         <v>61</v>
       </c>
       <c r="F94" s="24" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G94" s="11"/>
       <c r="H94" s="11"/>
@@ -3679,7 +3714,7 @@
         <v>61</v>
       </c>
       <c r="F95" s="24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G95" s="11"/>
       <c r="H95" s="11"/>
@@ -3700,10 +3735,10 @@
         <v>60</v>
       </c>
       <c r="E96" s="24" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F96" s="24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G96" s="11"/>
       <c r="H96" s="11"/>
@@ -3727,7 +3762,7 @@
         <v>58</v>
       </c>
       <c r="F97" s="24" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G97" s="11"/>
       <c r="H97" s="11"/>
@@ -3748,10 +3783,10 @@
         <v>62</v>
       </c>
       <c r="E98" s="24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F98" s="24" t="s">
-        <v>203</v>
+        <v>110</v>
       </c>
       <c r="G98" s="11"/>
       <c r="H98" s="11"/>
@@ -3772,10 +3807,10 @@
         <v>63</v>
       </c>
       <c r="E99" s="24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F99" s="24" t="s">
-        <v>111</v>
+        <v>202</v>
       </c>
       <c r="G99" s="11"/>
       <c r="H99" s="11"/>
@@ -3799,7 +3834,7 @@
         <v>58</v>
       </c>
       <c r="F100" s="24" t="s">
-        <v>204</v>
+        <v>111</v>
       </c>
       <c r="G100" s="11"/>
       <c r="H100" s="11"/>
@@ -3820,10 +3855,10 @@
         <v>65</v>
       </c>
       <c r="E101" s="24" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F101" s="24" t="s">
-        <v>112</v>
+        <v>203</v>
       </c>
       <c r="G101" s="11"/>
       <c r="H101" s="11"/>
@@ -3844,10 +3879,10 @@
         <v>66</v>
       </c>
       <c r="E102" s="24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F102" s="24" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G102" s="11"/>
       <c r="H102" s="11"/>
@@ -3871,7 +3906,7 @@
         <v>61</v>
       </c>
       <c r="F103" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G103" s="11"/>
       <c r="H103" s="11"/>
@@ -3895,7 +3930,7 @@
         <v>61</v>
       </c>
       <c r="F104" s="24" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G104" s="11"/>
       <c r="H104" s="11"/>
@@ -3919,7 +3954,7 @@
         <v>61</v>
       </c>
       <c r="F105" s="24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G105" s="11"/>
       <c r="H105" s="11"/>
@@ -3940,10 +3975,10 @@
         <v>70</v>
       </c>
       <c r="E106" s="24" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F106" s="24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G106" s="11"/>
       <c r="H106" s="11"/>
@@ -3967,7 +4002,7 @@
         <v>58</v>
       </c>
       <c r="F107" s="24" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G107" s="11"/>
       <c r="H107" s="11"/>
@@ -3988,10 +4023,10 @@
         <v>72</v>
       </c>
       <c r="E108" s="24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F108" s="24" t="s">
-        <v>205</v>
+        <v>118</v>
       </c>
       <c r="G108" s="11"/>
       <c r="H108" s="11"/>
@@ -4012,10 +4047,10 @@
         <v>73</v>
       </c>
       <c r="E109" s="24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F109" s="24" t="s">
-        <v>119</v>
+        <v>204</v>
       </c>
       <c r="G109" s="11"/>
       <c r="H109" s="11"/>
@@ -4039,7 +4074,7 @@
         <v>58</v>
       </c>
       <c r="F110" s="24" t="s">
-        <v>206</v>
+        <v>119</v>
       </c>
       <c r="G110" s="11"/>
       <c r="H110" s="11"/>
@@ -4060,10 +4095,10 @@
         <v>75</v>
       </c>
       <c r="E111" s="24" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F111" s="24" t="s">
-        <v>120</v>
+        <v>205</v>
       </c>
       <c r="G111" s="11"/>
       <c r="H111" s="11"/>
@@ -4084,10 +4119,10 @@
         <v>76</v>
       </c>
       <c r="E112" s="24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F112" s="24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G112" s="11"/>
       <c r="H112" s="11"/>
@@ -4111,7 +4146,7 @@
         <v>61</v>
       </c>
       <c r="F113" s="24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G113" s="11"/>
       <c r="H113" s="11"/>
@@ -4135,7 +4170,7 @@
         <v>61</v>
       </c>
       <c r="F114" s="24" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G114" s="11"/>
       <c r="H114" s="11"/>
@@ -4159,7 +4194,7 @@
         <v>61</v>
       </c>
       <c r="F115" s="24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G115" s="11"/>
       <c r="H115" s="11"/>
@@ -4183,7 +4218,7 @@
         <v>61</v>
       </c>
       <c r="F116" s="24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G116" s="11"/>
       <c r="H116" s="11"/>
@@ -4204,10 +4239,10 @@
         <v>81</v>
       </c>
       <c r="E117" s="24" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="F117" s="24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G117" s="11"/>
       <c r="H117" s="11"/>
@@ -4231,7 +4266,7 @@
         <v>89</v>
       </c>
       <c r="F118" s="24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G118" s="11"/>
       <c r="H118" s="11"/>
@@ -4252,10 +4287,10 @@
         <v>83</v>
       </c>
       <c r="E119" s="24" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="F119" s="24" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G119" s="11"/>
       <c r="H119" s="11"/>
@@ -4279,7 +4314,7 @@
         <v>58</v>
       </c>
       <c r="F120" s="24" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G120" s="11"/>
       <c r="H120" s="11"/>
@@ -4300,10 +4335,10 @@
         <v>85</v>
       </c>
       <c r="E121" s="24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F121" s="24" t="s">
-        <v>207</v>
+        <v>129</v>
       </c>
       <c r="G121" s="11"/>
       <c r="H121" s="11"/>
@@ -4324,10 +4359,10 @@
         <v>86</v>
       </c>
       <c r="E122" s="24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F122" s="24" t="s">
-        <v>130</v>
+        <v>206</v>
       </c>
       <c r="G122" s="11"/>
       <c r="H122" s="11"/>
@@ -4351,7 +4386,7 @@
         <v>58</v>
       </c>
       <c r="F123" s="24" t="s">
-        <v>208</v>
+        <v>130</v>
       </c>
       <c r="G123" s="11"/>
       <c r="H123" s="11"/>
@@ -4372,10 +4407,10 @@
         <v>88</v>
       </c>
       <c r="E124" s="24" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F124" s="24" t="s">
-        <v>131</v>
+        <v>207</v>
       </c>
       <c r="G124" s="11"/>
       <c r="H124" s="11"/>
@@ -4396,10 +4431,10 @@
         <v>89</v>
       </c>
       <c r="E125" s="24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F125" s="24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G125" s="11"/>
       <c r="H125" s="11"/>
@@ -4423,7 +4458,7 @@
         <v>61</v>
       </c>
       <c r="F126" s="24" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G126" s="11"/>
       <c r="H126" s="11"/>
@@ -4447,7 +4482,7 @@
         <v>61</v>
       </c>
       <c r="F127" s="24" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G127" s="11"/>
       <c r="H127" s="11"/>
@@ -4471,7 +4506,7 @@
         <v>61</v>
       </c>
       <c r="F128" s="24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G128" s="11"/>
       <c r="H128" s="11"/>
@@ -4495,7 +4530,7 @@
         <v>61</v>
       </c>
       <c r="F129" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G129" s="11"/>
       <c r="H129" s="11"/>
@@ -4516,10 +4551,10 @@
         <v>94</v>
       </c>
       <c r="E130" s="24" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="F130" s="24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G130" s="11"/>
       <c r="H130" s="11"/>
@@ -4543,7 +4578,7 @@
         <v>89</v>
       </c>
       <c r="F131" s="24" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G131" s="11"/>
       <c r="H131" s="11"/>
@@ -4567,7 +4602,7 @@
         <v>89</v>
       </c>
       <c r="F132" s="24" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G132" s="11"/>
       <c r="H132" s="11"/>
@@ -4591,7 +4626,7 @@
         <v>89</v>
       </c>
       <c r="F133" s="24" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G133" s="11"/>
       <c r="H133" s="11"/>
@@ -4615,7 +4650,7 @@
         <v>89</v>
       </c>
       <c r="F134" s="24" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G134" s="11"/>
       <c r="H134" s="11"/>
@@ -4639,7 +4674,7 @@
         <v>89</v>
       </c>
       <c r="F135" s="24" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G135" s="11"/>
       <c r="H135" s="11"/>
@@ -4663,7 +4698,7 @@
         <v>89</v>
       </c>
       <c r="F136" s="24" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G136" s="11"/>
       <c r="H136" s="11"/>
@@ -4687,7 +4722,7 @@
         <v>89</v>
       </c>
       <c r="F137" s="24" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G137" s="11"/>
       <c r="H137" s="11"/>
@@ -4711,7 +4746,7 @@
         <v>89</v>
       </c>
       <c r="F138" s="24" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G138" s="11"/>
       <c r="H138" s="11"/>
@@ -4735,7 +4770,7 @@
         <v>89</v>
       </c>
       <c r="F139" s="24" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G139" s="11"/>
       <c r="H139" s="11"/>
@@ -4759,7 +4794,7 @@
         <v>89</v>
       </c>
       <c r="F140" s="24" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G140" s="11"/>
       <c r="H140" s="11"/>
@@ -4783,7 +4818,7 @@
         <v>89</v>
       </c>
       <c r="F141" s="24" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G141" s="11"/>
       <c r="H141" s="11"/>
@@ -4804,10 +4839,10 @@
         <v>106</v>
       </c>
       <c r="E142" s="24" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="F142" s="24" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G142" s="11"/>
       <c r="H142" s="11"/>
@@ -4828,10 +4863,10 @@
         <v>107</v>
       </c>
       <c r="E143" s="24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F143" s="24" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G143" s="11"/>
       <c r="H143" s="11"/>
@@ -4844,64 +4879,64 @@
       <c r="O143" s="3"/>
       <c r="P143" s="11"/>
     </row>
-    <row r="144" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="11"/>
-      <c r="B144" s="17" t="s">
+    <row r="144" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="3"/>
+      <c r="B144" s="3"/>
+      <c r="C144" s="3"/>
+      <c r="D144" s="24">
+        <v>108</v>
+      </c>
+      <c r="E144" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="F144" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="G144" s="11"/>
+      <c r="H144" s="11"/>
+      <c r="I144" s="11"/>
+      <c r="J144" s="3"/>
+      <c r="K144" s="3"/>
+      <c r="L144" s="3"/>
+      <c r="M144" s="3"/>
+      <c r="N144" s="3"/>
+      <c r="O144" s="3"/>
+      <c r="P144" s="11"/>
+    </row>
+    <row r="145" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="11"/>
+      <c r="B145" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C144" s="17" t="s">
+      <c r="C145" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D144" s="17"/>
-      <c r="E144" s="17"/>
-      <c r="F144" s="17"/>
-      <c r="G144" s="17"/>
-      <c r="H144" s="17"/>
-      <c r="I144" s="17"/>
-      <c r="J144" s="17"/>
-      <c r="K144" s="17"/>
-      <c r="L144" s="17"/>
-      <c r="M144" s="17"/>
-      <c r="N144" s="17"/>
-      <c r="O144" s="17"/>
-      <c r="P144" s="17"/>
-    </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A145" s="3"/>
-      <c r="B145" s="3" t="s">
+      <c r="D145" s="17"/>
+      <c r="E145" s="17"/>
+      <c r="F145" s="17"/>
+      <c r="G145" s="17"/>
+      <c r="H145" s="17"/>
+      <c r="I145" s="17"/>
+      <c r="J145" s="17"/>
+      <c r="K145" s="17"/>
+      <c r="L145" s="17"/>
+      <c r="M145" s="17"/>
+      <c r="N145" s="17"/>
+      <c r="O145" s="17"/>
+      <c r="P145" s="17"/>
+    </row>
+    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A146" s="3"/>
+      <c r="B146" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C145" s="3" t="s">
+      <c r="C146" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D145" s="16"/>
-      <c r="E145" s="11"/>
-      <c r="F145" s="11" t="s">
+      <c r="D146" s="16"/>
+      <c r="E146" s="11"/>
+      <c r="F146" s="11" t="s">
         <v>46</v>
-      </c>
-      <c r="G145" s="11"/>
-      <c r="H145" s="11"/>
-      <c r="I145" s="11"/>
-      <c r="J145" s="3"/>
-      <c r="K145" s="3"/>
-      <c r="L145" s="3"/>
-      <c r="M145" s="3"/>
-      <c r="N145" s="3"/>
-      <c r="O145" s="3"/>
-      <c r="P145" s="11"/>
-    </row>
-    <row r="146" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="3"/>
-      <c r="B146" s="3"/>
-      <c r="C146" s="3"/>
-      <c r="D146" s="16">
-        <v>1</v>
-      </c>
-      <c r="E146" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="F146" s="24" t="s">
-        <v>151</v>
       </c>
       <c r="G146" s="11"/>
       <c r="H146" s="11"/>
@@ -4919,13 +4954,13 @@
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
       <c r="D147" s="16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E147" s="24" t="s">
         <v>58</v>
       </c>
       <c r="F147" s="24" t="s">
-        <v>209</v>
+        <v>151</v>
       </c>
       <c r="G147" s="11"/>
       <c r="H147" s="11"/>
@@ -4943,13 +4978,13 @@
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
       <c r="D148" s="16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E148" s="24" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F148" s="24" t="s">
-        <v>152</v>
+        <v>208</v>
       </c>
       <c r="G148" s="11"/>
       <c r="H148" s="11"/>
@@ -4967,13 +5002,13 @@
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
       <c r="D149" s="16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E149" s="24" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F149" s="24" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G149" s="11"/>
       <c r="H149" s="11"/>
@@ -4991,13 +5026,13 @@
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
       <c r="D150" s="16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E150" s="24" t="s">
         <v>58</v>
       </c>
       <c r="F150" s="24" t="s">
-        <v>210</v>
+        <v>153</v>
       </c>
       <c r="G150" s="11"/>
       <c r="H150" s="11"/>
@@ -5015,13 +5050,13 @@
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
       <c r="D151" s="16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E151" s="24" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F151" s="24" t="s">
-        <v>154</v>
+        <v>209</v>
       </c>
       <c r="G151" s="11"/>
       <c r="H151" s="11"/>
@@ -5039,13 +5074,13 @@
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
       <c r="D152" s="16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E152" s="24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F152" s="24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G152" s="11"/>
       <c r="H152" s="11"/>
@@ -5063,13 +5098,13 @@
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
       <c r="D153" s="16">
-        <v>8</v>
-      </c>
-      <c r="E153" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="F153" s="24" t="s">
-        <v>156</v>
+        <v>7</v>
+      </c>
+      <c r="E153" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="F153" s="27" t="s">
+        <v>216</v>
       </c>
       <c r="G153" s="11"/>
       <c r="H153" s="11"/>
@@ -5087,13 +5122,13 @@
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
       <c r="D154" s="16">
-        <v>9</v>
-      </c>
-      <c r="E154" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="F154" s="24" t="s">
-        <v>157</v>
+        <v>8</v>
+      </c>
+      <c r="E154" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="F154" s="27" t="s">
+        <v>217</v>
       </c>
       <c r="G154" s="11"/>
       <c r="H154" s="11"/>
@@ -5111,13 +5146,13 @@
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
       <c r="D155" s="16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E155" s="24" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F155" s="24" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G155" s="11"/>
       <c r="H155" s="11"/>
@@ -5135,13 +5170,13 @@
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
       <c r="D156" s="16">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E156" s="24" t="s">
         <v>58</v>
       </c>
       <c r="F156" s="24" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G156" s="11"/>
       <c r="H156" s="11"/>
@@ -5159,13 +5194,13 @@
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
       <c r="D157" s="16">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E157" s="24" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F157" s="24" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G157" s="11"/>
       <c r="H157" s="11"/>
@@ -5183,13 +5218,13 @@
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
       <c r="D158" s="16">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E158" s="24" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F158" s="24" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="G158" s="11"/>
       <c r="H158" s="11"/>
@@ -5207,13 +5242,13 @@
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
       <c r="D159" s="16">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E159" s="24" t="s">
-        <v>213</v>
+        <v>58</v>
       </c>
       <c r="F159" s="24" t="s">
-        <v>212</v>
+        <v>159</v>
       </c>
       <c r="G159" s="11"/>
       <c r="H159" s="11"/>
@@ -5231,13 +5266,13 @@
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
       <c r="D160" s="16">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E160" s="24" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F160" s="24" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G160" s="11"/>
       <c r="H160" s="11"/>
@@ -5255,13 +5290,13 @@
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
       <c r="D161" s="16">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E161" s="24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F161" s="24" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G161" s="11"/>
       <c r="H161" s="11"/>
@@ -5279,13 +5314,13 @@
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
       <c r="D162" s="16">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E162" s="24" t="s">
-        <v>58</v>
+        <v>212</v>
       </c>
       <c r="F162" s="24" t="s">
-        <v>164</v>
+        <v>211</v>
       </c>
       <c r="G162" s="11"/>
       <c r="H162" s="11"/>
@@ -5303,13 +5338,13 @@
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
       <c r="D163" s="16">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E163" s="24" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F163" s="24" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G163" s="11"/>
       <c r="H163" s="11"/>
@@ -5327,13 +5362,13 @@
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
       <c r="D164" s="16">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E164" s="24" t="s">
         <v>61</v>
       </c>
       <c r="F164" s="24" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G164" s="11"/>
       <c r="H164" s="11"/>
@@ -5351,13 +5386,13 @@
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
       <c r="D165" s="16">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E165" s="24" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F165" s="24" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G165" s="11"/>
       <c r="H165" s="11"/>
@@ -5375,13 +5410,13 @@
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
       <c r="D166" s="16">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E166" s="24" t="s">
         <v>58</v>
       </c>
       <c r="F166" s="24" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G166" s="11"/>
       <c r="H166" s="11"/>
@@ -5399,13 +5434,13 @@
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
       <c r="D167" s="16">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E167" s="24" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F167" s="24" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G167" s="11"/>
       <c r="H167" s="11"/>
@@ -5423,13 +5458,13 @@
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
       <c r="D168" s="16">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E168" s="24" t="s">
         <v>61</v>
       </c>
       <c r="F168" s="24" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G168" s="11"/>
       <c r="H168" s="11"/>
@@ -5447,13 +5482,13 @@
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
       <c r="D169" s="16">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E169" s="24" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F169" s="24" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G169" s="11"/>
       <c r="H169" s="11"/>
@@ -5471,13 +5506,13 @@
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
       <c r="D170" s="16">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E170" s="24" t="s">
         <v>58</v>
       </c>
       <c r="F170" s="24" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G170" s="11"/>
       <c r="H170" s="11"/>
@@ -5495,13 +5530,13 @@
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
       <c r="D171" s="16">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E171" s="24" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F171" s="24" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G171" s="11"/>
       <c r="H171" s="11"/>
@@ -5519,13 +5554,13 @@
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
       <c r="D172" s="16">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E172" s="24" t="s">
         <v>61</v>
       </c>
       <c r="F172" s="24" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G172" s="11"/>
       <c r="H172" s="11"/>
@@ -5543,13 +5578,13 @@
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
       <c r="D173" s="16">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E173" s="24" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F173" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G173" s="11"/>
       <c r="H173" s="11"/>
@@ -5567,13 +5602,13 @@
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
       <c r="D174" s="16">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E174" s="24" t="s">
         <v>58</v>
       </c>
       <c r="F174" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G174" s="11"/>
       <c r="H174" s="11"/>
@@ -5591,13 +5626,13 @@
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
       <c r="D175" s="16">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E175" s="24" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F175" s="24" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G175" s="11"/>
       <c r="H175" s="11"/>
@@ -5615,13 +5650,13 @@
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
       <c r="D176" s="16">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E176" s="24" t="s">
         <v>61</v>
       </c>
       <c r="F176" s="24" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G176" s="11"/>
       <c r="H176" s="11"/>
@@ -5639,13 +5674,13 @@
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
       <c r="D177" s="16">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E177" s="24" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F177" s="24" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G177" s="11"/>
       <c r="H177" s="11"/>
@@ -5663,13 +5698,13 @@
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
       <c r="D178" s="16">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E178" s="24" t="s">
         <v>58</v>
       </c>
       <c r="F178" s="24" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="G178" s="11"/>
       <c r="H178" s="11"/>
@@ -5687,13 +5722,13 @@
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
       <c r="D179" s="16">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E179" s="24" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F179" s="24" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="G179" s="11"/>
       <c r="H179" s="11"/>
@@ -5711,13 +5746,13 @@
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
       <c r="D180" s="16">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E180" s="24" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F180" s="24" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G180" s="11"/>
       <c r="H180" s="11"/>
@@ -5735,13 +5770,13 @@
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
       <c r="D181" s="16">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E181" s="24" t="s">
         <v>58</v>
       </c>
       <c r="F181" s="24" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="G181" s="11"/>
       <c r="H181" s="11"/>
@@ -5759,13 +5794,13 @@
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
       <c r="D182" s="16">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E182" s="24" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F182" s="24" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="G182" s="11"/>
       <c r="H182" s="11"/>
@@ -5783,13 +5818,13 @@
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
       <c r="D183" s="16">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E183" s="24" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F183" s="24" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G183" s="11"/>
       <c r="H183" s="11"/>
@@ -5807,13 +5842,13 @@
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
       <c r="D184" s="16">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E184" s="24" t="s">
         <v>58</v>
       </c>
       <c r="F184" s="24" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G184" s="11"/>
       <c r="H184" s="11"/>
@@ -5831,13 +5866,13 @@
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
       <c r="D185" s="16">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E185" s="24" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F185" s="24" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G185" s="11"/>
       <c r="H185" s="11"/>
@@ -5855,13 +5890,13 @@
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
       <c r="D186" s="16">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E186" s="24" t="s">
         <v>61</v>
       </c>
       <c r="F186" s="24" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G186" s="11"/>
       <c r="H186" s="11"/>
@@ -5879,13 +5914,13 @@
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
       <c r="D187" s="16">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E187" s="24" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F187" s="24" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G187" s="11"/>
       <c r="H187" s="11"/>
@@ -5903,13 +5938,13 @@
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
       <c r="D188" s="16">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E188" s="24" t="s">
         <v>58</v>
       </c>
       <c r="F188" s="24" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G188" s="11"/>
       <c r="H188" s="11"/>
@@ -5927,13 +5962,13 @@
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
       <c r="D189" s="16">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E189" s="24" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F189" s="24" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G189" s="11"/>
       <c r="H189" s="11"/>
@@ -5946,35 +5981,43 @@
       <c r="O189" s="3"/>
       <c r="P189" s="11"/>
     </row>
-    <row r="190" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A190" s="11"/>
-      <c r="B190" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="C190" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D190" s="17"/>
-      <c r="E190" s="17"/>
-      <c r="F190" s="18"/>
-      <c r="G190" s="17"/>
-      <c r="H190" s="17"/>
-      <c r="I190" s="17"/>
-      <c r="J190" s="17"/>
-      <c r="K190" s="17"/>
-      <c r="L190" s="17"/>
-      <c r="M190" s="17"/>
-      <c r="N190" s="17"/>
-      <c r="O190" s="17"/>
-      <c r="P190" s="17"/>
-    </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="3"/>
+      <c r="B190" s="3"/>
+      <c r="C190" s="3"/>
+      <c r="D190" s="16">
+        <v>44</v>
+      </c>
+      <c r="E190" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="F190" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="G190" s="11"/>
+      <c r="H190" s="11"/>
+      <c r="I190" s="11"/>
+      <c r="J190" s="3"/>
+      <c r="K190" s="3"/>
+      <c r="L190" s="3"/>
+      <c r="M190" s="3"/>
+      <c r="N190" s="3"/>
+      <c r="O190" s="3"/>
+      <c r="P190" s="11"/>
+    </row>
+    <row r="191" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A191" s="3"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
-      <c r="D191" s="16"/>
-      <c r="E191" s="11"/>
-      <c r="F191" s="11"/>
+      <c r="D191" s="16">
+        <v>45</v>
+      </c>
+      <c r="E191" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F191" s="24" t="s">
+        <v>188</v>
+      </c>
       <c r="G191" s="11"/>
       <c r="H191" s="11"/>
       <c r="I191" s="11"/>
@@ -5986,13 +6029,19 @@
       <c r="O191" s="3"/>
       <c r="P191" s="11"/>
     </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A192" s="3"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
-      <c r="D192" s="16"/>
-      <c r="E192" s="11"/>
-      <c r="F192" s="11"/>
+      <c r="D192" s="16">
+        <v>46</v>
+      </c>
+      <c r="E192" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="F192" s="27" t="s">
+        <v>218</v>
+      </c>
       <c r="G192" s="11"/>
       <c r="H192" s="11"/>
       <c r="I192" s="11"/>
@@ -6004,35 +6053,43 @@
       <c r="O192" s="3"/>
       <c r="P192" s="11"/>
     </row>
-    <row r="193" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A193" s="11"/>
-      <c r="B193" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="C193" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="D193" s="17"/>
-      <c r="E193" s="17"/>
-      <c r="F193" s="11"/>
-      <c r="G193" s="17"/>
-      <c r="H193" s="17"/>
-      <c r="I193" s="17"/>
-      <c r="J193" s="17"/>
-      <c r="K193" s="17"/>
-      <c r="L193" s="17"/>
-      <c r="M193" s="17"/>
-      <c r="N193" s="17"/>
-      <c r="O193" s="17"/>
-      <c r="P193" s="17"/>
-    </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A193" s="3"/>
+      <c r="B193" s="3"/>
+      <c r="C193" s="3"/>
+      <c r="D193" s="16">
+        <v>47</v>
+      </c>
+      <c r="E193" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F193" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="G193" s="11"/>
+      <c r="H193" s="11"/>
+      <c r="I193" s="11"/>
+      <c r="J193" s="3"/>
+      <c r="K193" s="3"/>
+      <c r="L193" s="3"/>
+      <c r="M193" s="3"/>
+      <c r="N193" s="3"/>
+      <c r="O193" s="3"/>
+      <c r="P193" s="11"/>
+    </row>
+    <row r="194" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A194" s="3"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
-      <c r="D194" s="16"/>
-      <c r="E194" s="11"/>
-      <c r="F194" s="11"/>
+      <c r="D194" s="16">
+        <v>48</v>
+      </c>
+      <c r="E194" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="F194" s="27" t="s">
+        <v>219</v>
+      </c>
       <c r="G194" s="11"/>
       <c r="H194" s="11"/>
       <c r="I194" s="11"/>
@@ -6044,45 +6101,45 @@
       <c r="O194" s="3"/>
       <c r="P194" s="11"/>
     </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A195" s="3"/>
-      <c r="B195" s="3"/>
-      <c r="C195" s="3"/>
-      <c r="D195" s="16"/>
-      <c r="E195" s="11"/>
-      <c r="F195" s="11"/>
-      <c r="G195" s="11"/>
-      <c r="H195" s="11"/>
-      <c r="I195" s="11"/>
-      <c r="J195" s="3"/>
-      <c r="K195" s="3"/>
-      <c r="L195" s="3"/>
-      <c r="M195" s="3"/>
-      <c r="N195" s="3"/>
-      <c r="O195" s="3"/>
-      <c r="P195" s="11"/>
-    </row>
-    <row r="196" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="11"/>
-      <c r="B196" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="C196" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D196" s="17"/>
-      <c r="E196" s="17"/>
-      <c r="F196" s="17"/>
-      <c r="G196" s="17"/>
-      <c r="H196" s="17"/>
-      <c r="I196" s="17"/>
-      <c r="J196" s="17"/>
-      <c r="K196" s="17"/>
-      <c r="L196" s="17"/>
-      <c r="M196" s="17"/>
-      <c r="N196" s="17"/>
-      <c r="O196" s="17"/>
-      <c r="P196" s="17"/>
+    <row r="195" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A195" s="11"/>
+      <c r="B195" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C195" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D195" s="17"/>
+      <c r="E195" s="17"/>
+      <c r="F195" s="18"/>
+      <c r="G195" s="17"/>
+      <c r="H195" s="17"/>
+      <c r="I195" s="17"/>
+      <c r="J195" s="17"/>
+      <c r="K195" s="17"/>
+      <c r="L195" s="17"/>
+      <c r="M195" s="17"/>
+      <c r="N195" s="17"/>
+      <c r="O195" s="17"/>
+      <c r="P195" s="17"/>
+    </row>
+    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A196" s="3"/>
+      <c r="B196" s="3"/>
+      <c r="C196" s="3"/>
+      <c r="D196" s="16"/>
+      <c r="E196" s="11"/>
+      <c r="F196" s="11"/>
+      <c r="G196" s="11"/>
+      <c r="H196" s="11"/>
+      <c r="I196" s="11"/>
+      <c r="J196" s="3"/>
+      <c r="K196" s="3"/>
+      <c r="L196" s="3"/>
+      <c r="M196" s="3"/>
+      <c r="N196" s="3"/>
+      <c r="O196" s="3"/>
+      <c r="P196" s="11"/>
     </row>
     <row r="197" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A197" s="3"/>
@@ -6102,113 +6159,121 @@
       <c r="O197" s="3"/>
       <c r="P197" s="11"/>
     </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A198" s="3"/>
-      <c r="B198" s="3"/>
-      <c r="C198" s="3"/>
-      <c r="D198" s="16"/>
-      <c r="E198" s="11"/>
+    <row r="198" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A198" s="11"/>
+      <c r="B198" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C198" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D198" s="17"/>
+      <c r="E198" s="17"/>
       <c r="F198" s="11"/>
-      <c r="G198" s="11"/>
-      <c r="H198" s="11"/>
-      <c r="I198" s="11"/>
-      <c r="J198" s="3"/>
-      <c r="K198" s="3"/>
-      <c r="L198" s="3"/>
-      <c r="M198" s="3"/>
-      <c r="N198" s="3"/>
-      <c r="O198" s="3"/>
-      <c r="P198" s="11"/>
+      <c r="G198" s="17"/>
+      <c r="H198" s="17"/>
+      <c r="I198" s="17"/>
+      <c r="J198" s="17"/>
+      <c r="K198" s="17"/>
+      <c r="L198" s="17"/>
+      <c r="M198" s="17"/>
+      <c r="N198" s="17"/>
+      <c r="O198" s="17"/>
+      <c r="P198" s="17"/>
     </row>
     <row r="199" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A199" s="3"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
-      <c r="D199" s="3"/>
-      <c r="E199" s="3"/>
-      <c r="F199" s="17"/>
-      <c r="G199" s="3"/>
-      <c r="H199" s="3"/>
-      <c r="I199" s="3"/>
+      <c r="D199" s="16"/>
+      <c r="E199" s="11"/>
+      <c r="F199" s="11"/>
+      <c r="G199" s="11"/>
+      <c r="H199" s="11"/>
+      <c r="I199" s="11"/>
       <c r="J199" s="3"/>
       <c r="K199" s="3"/>
       <c r="L199" s="3"/>
       <c r="M199" s="3"/>
       <c r="N199" s="3"/>
       <c r="O199" s="3"/>
-      <c r="P199" s="3"/>
+      <c r="P199" s="11"/>
     </row>
     <row r="200" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A200" s="3"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
-      <c r="D200" s="3"/>
-      <c r="E200" s="3"/>
+      <c r="D200" s="16"/>
+      <c r="E200" s="11"/>
       <c r="F200" s="11"/>
-      <c r="G200" s="3"/>
-      <c r="H200" s="3"/>
-      <c r="I200" s="3"/>
+      <c r="G200" s="11"/>
+      <c r="H200" s="11"/>
+      <c r="I200" s="11"/>
       <c r="J200" s="3"/>
       <c r="K200" s="3"/>
       <c r="L200" s="3"/>
       <c r="M200" s="3"/>
       <c r="N200" s="3"/>
       <c r="O200" s="3"/>
-      <c r="P200" s="3"/>
-    </row>
-    <row r="201" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A201" s="3"/>
-      <c r="B201" s="3"/>
-      <c r="C201" s="3"/>
-      <c r="D201" s="3"/>
-      <c r="E201" s="3"/>
-      <c r="F201" s="11"/>
-      <c r="G201" s="3"/>
-      <c r="H201" s="3"/>
-      <c r="I201" s="3"/>
-      <c r="J201" s="3"/>
-      <c r="K201" s="3"/>
-      <c r="L201" s="3"/>
-      <c r="M201" s="3"/>
-      <c r="N201" s="3"/>
-      <c r="O201" s="3"/>
-      <c r="P201" s="3"/>
+      <c r="P200" s="11"/>
+    </row>
+    <row r="201" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A201" s="11"/>
+      <c r="B201" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C201" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D201" s="17"/>
+      <c r="E201" s="17"/>
+      <c r="F201" s="17"/>
+      <c r="G201" s="17"/>
+      <c r="H201" s="17"/>
+      <c r="I201" s="17"/>
+      <c r="J201" s="17"/>
+      <c r="K201" s="17"/>
+      <c r="L201" s="17"/>
+      <c r="M201" s="17"/>
+      <c r="N201" s="17"/>
+      <c r="O201" s="17"/>
+      <c r="P201" s="17"/>
     </row>
     <row r="202" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A202" s="3"/>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
-      <c r="D202" s="3"/>
-      <c r="E202" s="3"/>
-      <c r="F202" s="17"/>
-      <c r="G202" s="3"/>
-      <c r="H202" s="3"/>
-      <c r="I202" s="3"/>
+      <c r="D202" s="16"/>
+      <c r="E202" s="11"/>
+      <c r="F202" s="11"/>
+      <c r="G202" s="11"/>
+      <c r="H202" s="11"/>
+      <c r="I202" s="11"/>
       <c r="J202" s="3"/>
       <c r="K202" s="3"/>
       <c r="L202" s="3"/>
       <c r="M202" s="3"/>
       <c r="N202" s="3"/>
       <c r="O202" s="3"/>
-      <c r="P202" s="3"/>
+      <c r="P202" s="11"/>
     </row>
     <row r="203" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A203" s="3"/>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
-      <c r="D203" s="3"/>
-      <c r="E203" s="3"/>
+      <c r="D203" s="16"/>
+      <c r="E203" s="11"/>
       <c r="F203" s="11"/>
-      <c r="G203" s="3"/>
-      <c r="H203" s="3"/>
-      <c r="I203" s="3"/>
+      <c r="G203" s="11"/>
+      <c r="H203" s="11"/>
+      <c r="I203" s="11"/>
       <c r="J203" s="3"/>
       <c r="K203" s="3"/>
       <c r="L203" s="3"/>
       <c r="M203" s="3"/>
       <c r="N203" s="3"/>
       <c r="O203" s="3"/>
-      <c r="P203" s="3"/>
+      <c r="P203" s="11"/>
     </row>
     <row r="204" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A204" s="3"/>
@@ -6216,7 +6281,7 @@
       <c r="C204" s="3"/>
       <c r="D204" s="3"/>
       <c r="E204" s="3"/>
-      <c r="F204" s="11"/>
+      <c r="F204" s="17"/>
       <c r="G204" s="3"/>
       <c r="H204" s="3"/>
       <c r="I204" s="3"/>
@@ -6234,7 +6299,7 @@
       <c r="C205" s="3"/>
       <c r="D205" s="3"/>
       <c r="E205" s="3"/>
-      <c r="F205" s="3"/>
+      <c r="F205" s="11"/>
       <c r="G205" s="3"/>
       <c r="H205" s="3"/>
       <c r="I205" s="3"/>
@@ -6252,7 +6317,7 @@
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
       <c r="E206" s="3"/>
-      <c r="F206" s="3"/>
+      <c r="F206" s="11"/>
       <c r="G206" s="3"/>
       <c r="H206" s="3"/>
       <c r="I206" s="3"/>
@@ -6270,7 +6335,7 @@
       <c r="C207" s="3"/>
       <c r="D207" s="3"/>
       <c r="E207" s="3"/>
-      <c r="F207" s="3"/>
+      <c r="F207" s="17"/>
       <c r="G207" s="3"/>
       <c r="H207" s="3"/>
       <c r="I207" s="3"/>
@@ -6288,7 +6353,7 @@
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
       <c r="E208" s="3"/>
-      <c r="F208" s="3"/>
+      <c r="F208" s="11"/>
       <c r="G208" s="3"/>
       <c r="H208" s="3"/>
       <c r="I208" s="3"/>
@@ -6306,7 +6371,7 @@
       <c r="C209" s="3"/>
       <c r="D209" s="3"/>
       <c r="E209" s="3"/>
-      <c r="F209" s="3"/>
+      <c r="F209" s="11"/>
       <c r="G209" s="3"/>
       <c r="H209" s="3"/>
       <c r="I209" s="3"/>
@@ -6319,24 +6384,94 @@
       <c r="P209" s="3"/>
     </row>
     <row r="210" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A210" s="3"/>
+      <c r="B210" s="3"/>
       <c r="C210" s="3"/>
+      <c r="D210" s="3"/>
+      <c r="E210" s="3"/>
       <c r="F210" s="3"/>
+      <c r="G210" s="3"/>
+      <c r="H210" s="3"/>
+      <c r="I210" s="3"/>
+      <c r="J210" s="3"/>
+      <c r="K210" s="3"/>
+      <c r="L210" s="3"/>
+      <c r="M210" s="3"/>
+      <c r="N210" s="3"/>
+      <c r="O210" s="3"/>
+      <c r="P210" s="3"/>
     </row>
     <row r="211" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A211" s="3"/>
+      <c r="B211" s="3"/>
       <c r="C211" s="3"/>
+      <c r="D211" s="3"/>
+      <c r="E211" s="3"/>
       <c r="F211" s="3"/>
+      <c r="G211" s="3"/>
+      <c r="H211" s="3"/>
+      <c r="I211" s="3"/>
+      <c r="J211" s="3"/>
+      <c r="K211" s="3"/>
+      <c r="L211" s="3"/>
+      <c r="M211" s="3"/>
+      <c r="N211" s="3"/>
+      <c r="O211" s="3"/>
+      <c r="P211" s="3"/>
     </row>
     <row r="212" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A212" s="3"/>
+      <c r="B212" s="3"/>
       <c r="C212" s="3"/>
+      <c r="D212" s="3"/>
+      <c r="E212" s="3"/>
       <c r="F212" s="3"/>
+      <c r="G212" s="3"/>
+      <c r="H212" s="3"/>
+      <c r="I212" s="3"/>
+      <c r="J212" s="3"/>
+      <c r="K212" s="3"/>
+      <c r="L212" s="3"/>
+      <c r="M212" s="3"/>
+      <c r="N212" s="3"/>
+      <c r="O212" s="3"/>
+      <c r="P212" s="3"/>
     </row>
     <row r="213" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A213" s="3"/>
+      <c r="B213" s="3"/>
       <c r="C213" s="3"/>
+      <c r="D213" s="3"/>
+      <c r="E213" s="3"/>
       <c r="F213" s="3"/>
+      <c r="G213" s="3"/>
+      <c r="H213" s="3"/>
+      <c r="I213" s="3"/>
+      <c r="J213" s="3"/>
+      <c r="K213" s="3"/>
+      <c r="L213" s="3"/>
+      <c r="M213" s="3"/>
+      <c r="N213" s="3"/>
+      <c r="O213" s="3"/>
+      <c r="P213" s="3"/>
     </row>
     <row r="214" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A214" s="3"/>
+      <c r="B214" s="3"/>
       <c r="C214" s="3"/>
+      <c r="D214" s="3"/>
+      <c r="E214" s="3"/>
       <c r="F214" s="3"/>
+      <c r="G214" s="3"/>
+      <c r="H214" s="3"/>
+      <c r="I214" s="3"/>
+      <c r="J214" s="3"/>
+      <c r="K214" s="3"/>
+      <c r="L214" s="3"/>
+      <c r="M214" s="3"/>
+      <c r="N214" s="3"/>
+      <c r="O214" s="3"/>
+      <c r="P214" s="3"/>
     </row>
     <row r="215" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C215" s="3"/>
@@ -6344,18 +6479,23 @@
     </row>
     <row r="216" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C216" s="3"/>
+      <c r="F216" s="3"/>
     </row>
     <row r="217" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C217" s="3"/>
+      <c r="F217" s="3"/>
     </row>
     <row r="218" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C218" s="3"/>
+      <c r="F218" s="3"/>
     </row>
     <row r="219" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C219" s="3"/>
+      <c r="F219" s="3"/>
     </row>
     <row r="220" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C220" s="3"/>
+      <c r="F220" s="3"/>
     </row>
     <row r="221" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C221" s="3"/>
@@ -8844,28 +8984,43 @@
     <row r="1049" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C1049" s="3"/>
     </row>
+    <row r="1050" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C1050" s="3"/>
+    </row>
+    <row r="1051" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C1051" s="3"/>
+    </row>
+    <row r="1052" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C1052" s="3"/>
+    </row>
+    <row r="1053" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C1053" s="3"/>
+    </row>
+    <row r="1054" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C1054" s="3"/>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatRows="0" insertRows="0" insertHyperlinks="0" deleteRows="0" sort="0" autoFilter="0"/>
-  <autoFilter ref="B10:P198" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="B10:P203" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="F1:P6"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="9">
-    <dataValidation allowBlank="1" showInputMessage="1" sqref="C11 C14 C17 C20 C23 C26 C29 C32 C35 C144 C190 C193 C196" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Object Code value" error="The Object code value shall be:_x000a_VARIABLE_x000a_RECORD_x000a_ARRAY" sqref="C12:C13 C15:C16 C18:C19 C21:C22 C24:C25 C27:C28 C30:C31 C33:C34 C36:C143 C145:C189 C191:C192 C194:C195 C197:C209" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation allowBlank="1" showInputMessage="1" sqref="C11 C14 C17 C20 C23 C26 C29 C32 C35 C145 C195 C198 C201" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Object Code value" error="The Object code value shall be:_x000a_VARIABLE_x000a_RECORD_x000a_ARRAY" sqref="C12:C13 C15:C16 C18:C19 C21:C22 C24:C25 C27:C28 C30:C31 C33:C34 C36:C144 C146:C194 C196:C197 C199:C200 C202:C214" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Category" error="The value for the entry category shall be _x000a_M : (mandatory)_x000a_O : (optional) _x000a_C : (conditional)" sqref="J36 J194:J195 J197:J209 J12:J13 J15:J16 J18:J19 J21:J22 J24:J25 J27:J28 J30:J31 J33:J34 J40:J143 J145:J189 J191:J192" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Category" error="The value for the entry category shall be _x000a_M : (mandatory)_x000a_O : (optional) _x000a_C : (conditional)" sqref="J36 J199:J200 J202:J214 J12:J13 J15:J16 J18:J19 J21:J22 J24:J25 J27:J28 J30:J31 J33:J34 J40:J144 J146:J194 J196:J197" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"M,O,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Backup/Setting Flag" error="The entry flag shall be_x000a_B : (Backup)_x000a_S : (Setting)" sqref="K36 K194:K195 K197:K209 K12:K13 K15:K16 K18:K19 K21:K22 K24:K25 K27:K28 K30:K31 K33:K34 K40:K143 K145:K189 K191:K192" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Backup/Setting Flag" error="The entry flag shall be_x000a_B : (Backup)_x000a_S : (Setting)" sqref="K36 K199:K200 K202:K214 K12:K13 K15:K16 K18:K19 K21:K22 K24:K25 K27:K28 K30:K31 K33:K34 K40:K144 K146:K194 K196:K197" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"B,S"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M36:O36 M194:O195 M12:O13 M18:O19 M24:O25 M30:O31 M40:O143 M191:O192 M197:O198 M15:O16 M21:O22 M27:O28 M33:O34 M145:O189" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M36:O36 M199:O200 M12:O13 M18:O19 M24:O25 M30:O31 M40:O144 M196:O197 M202:O203 M15:O16 M21:O22 M27:O28 M33:O34 M146:O194" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"rx,tx"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C210:C1049" xr:uid="{00000000-0002-0000-0000-000005000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C215:C1054" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J37:J39" xr:uid="{20805EC6-BF85-484F-8728-8A67EE77DC8F}">

--- a/ArmCoreV1_QSPI/SSCProject/lan9252_app.xlsx
+++ b/ArmCoreV1_QSPI/SSCProject/lan9252_app.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SI\project\RTM_OFF_NEW\FW-ArmCore\ArmCoreV1_QSPI\SSCProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D9FCF4C-31ED-4DC3-9C73-2270C865D881}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF2F73E-A1FD-4BDB-9240-C7A9131AC541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-7730" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Profile" sheetId="11" r:id="rId1"/>
@@ -386,10 +386,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>InU8_reserved1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>UINT</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -718,6 +714,10 @@
   </si>
   <si>
     <t>OutU8_reserved2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>InU8_state_sync</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -915,9 +915,6 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -936,6 +933,9 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1274,19 +1274,19 @@
         <v>1</v>
       </c>
       <c r="E1" s="4"/>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
       <c r="Q1" s="20"/>
       <c r="R1" s="20"/>
       <c r="S1" s="20"/>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
       <c r="Q2" s="20"/>
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
@@ -1324,17 +1324,17 @@
       <c r="C3" s="5"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
-      <c r="P3" s="25"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="31"/>
+      <c r="N3" s="31"/>
+      <c r="O3" s="31"/>
+      <c r="P3" s="31"/>
       <c r="Q3" s="20"/>
       <c r="R3" s="20"/>
       <c r="S3" s="20"/>
@@ -1346,17 +1346,17 @@
       <c r="C4" s="5"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="25"/>
-      <c r="P4" s="25"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
+      <c r="O4" s="31"/>
+      <c r="P4" s="31"/>
       <c r="Q4" s="20"/>
       <c r="R4" s="20"/>
       <c r="S4" s="20"/>
@@ -1368,17 +1368,17 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="25"/>
-      <c r="P5" s="25"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31"/>
+      <c r="M5" s="31"/>
+      <c r="N5" s="31"/>
+      <c r="O5" s="31"/>
+      <c r="P5" s="31"/>
       <c r="Q5" s="20"/>
       <c r="R5" s="20"/>
       <c r="S5" s="20"/>
@@ -1390,17 +1390,17 @@
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="25"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="25"/>
-      <c r="P6" s="25"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="31"/>
+      <c r="P6" s="31"/>
       <c r="Q6" s="20"/>
       <c r="R6" s="20"/>
       <c r="S6" s="20"/>
@@ -2137,7 +2137,7 @@
         <v>54</v>
       </c>
       <c r="F41" s="24" t="s">
-        <v>60</v>
+        <v>143</v>
       </c>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
@@ -2158,10 +2158,10 @@
         <v>6</v>
       </c>
       <c r="E42" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="F42" s="24" t="s">
         <v>61</v>
-      </c>
-      <c r="F42" s="24" t="s">
-        <v>62</v>
       </c>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
@@ -2178,16 +2178,16 @@
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
-      <c r="D43" s="26">
+      <c r="D43" s="25">
         <v>7</v>
       </c>
       <c r="E43" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="F43" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="F43" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="G43" s="27"/>
+      <c r="G43" s="26"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
       <c r="J43" s="2"/>
@@ -2206,12 +2206,12 @@
         <v>8</v>
       </c>
       <c r="E44" s="24" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F44" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="G44" s="28"/>
+        <v>140</v>
+      </c>
+      <c r="G44" s="27"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
       <c r="J44" s="2"/>
@@ -2233,7 +2233,7 @@
         <v>54</v>
       </c>
       <c r="F45" s="24" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
@@ -2257,7 +2257,7 @@
         <v>54</v>
       </c>
       <c r="F46" s="24" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
@@ -2281,7 +2281,7 @@
         <v>57</v>
       </c>
       <c r="F47" s="24" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
@@ -2305,7 +2305,7 @@
         <v>57</v>
       </c>
       <c r="F48" s="24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
@@ -2326,10 +2326,10 @@
         <v>13</v>
       </c>
       <c r="E49" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="F49" s="24" t="s">
         <v>86</v>
-      </c>
-      <c r="F49" s="24" t="s">
-        <v>87</v>
       </c>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
@@ -2346,14 +2346,14 @@
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
-      <c r="D50" s="26">
+      <c r="D50" s="25">
         <v>14</v>
       </c>
       <c r="E50" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F50" s="24" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
@@ -2377,7 +2377,7 @@
         <v>54</v>
       </c>
       <c r="F51" s="24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
@@ -2401,7 +2401,7 @@
         <v>54</v>
       </c>
       <c r="F52" s="24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
@@ -2425,7 +2425,7 @@
         <v>54</v>
       </c>
       <c r="F53" s="24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
@@ -2449,7 +2449,7 @@
         <v>54</v>
       </c>
       <c r="F54" s="24" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
@@ -2473,7 +2473,7 @@
         <v>54</v>
       </c>
       <c r="F55" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
@@ -2497,7 +2497,7 @@
         <v>54</v>
       </c>
       <c r="F56" s="24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
@@ -2514,14 +2514,14 @@
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
-      <c r="D57" s="26">
+      <c r="D57" s="25">
         <v>21</v>
       </c>
       <c r="E57" s="24" t="s">
         <v>57</v>
       </c>
       <c r="F57" s="24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
@@ -2545,7 +2545,7 @@
         <v>57</v>
       </c>
       <c r="F58" s="24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
@@ -2566,10 +2566,10 @@
         <v>23</v>
       </c>
       <c r="E59" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F59" s="24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
@@ -2590,10 +2590,10 @@
         <v>24</v>
       </c>
       <c r="E60" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F60" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
@@ -2614,10 +2614,10 @@
         <v>25</v>
       </c>
       <c r="E61" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F61" s="24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
@@ -2638,10 +2638,10 @@
         <v>26</v>
       </c>
       <c r="E62" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F62" s="24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
@@ -2662,10 +2662,10 @@
         <v>27</v>
       </c>
       <c r="E63" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F63" s="24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
@@ -2682,14 +2682,14 @@
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
-      <c r="D64" s="26">
+      <c r="D64" s="25">
         <v>28</v>
       </c>
       <c r="E64" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F64" s="24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
@@ -2710,10 +2710,10 @@
         <v>29</v>
       </c>
       <c r="E65" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F65" s="24" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
@@ -2734,10 +2734,10 @@
         <v>30</v>
       </c>
       <c r="E66" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F66" s="24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
@@ -2758,10 +2758,10 @@
         <v>31</v>
       </c>
       <c r="E67" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F67" s="24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
@@ -2782,10 +2782,10 @@
         <v>32</v>
       </c>
       <c r="E68" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F68" s="24" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
@@ -2806,10 +2806,10 @@
         <v>33</v>
       </c>
       <c r="E69" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F69" s="24" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
@@ -2830,10 +2830,10 @@
         <v>34</v>
       </c>
       <c r="E70" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F70" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
@@ -2850,14 +2850,14 @@
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
-      <c r="D71" s="26">
+      <c r="D71" s="25">
         <v>35</v>
       </c>
       <c r="E71" s="24" t="s">
         <v>54</v>
       </c>
       <c r="F71" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
@@ -2881,7 +2881,7 @@
         <v>54</v>
       </c>
       <c r="F72" s="24" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
@@ -2905,7 +2905,7 @@
         <v>54</v>
       </c>
       <c r="F73" s="24" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
@@ -2929,7 +2929,7 @@
         <v>54</v>
       </c>
       <c r="F74" s="24" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G74" s="1"/>
       <c r="H74" s="1"/>
@@ -2950,10 +2950,10 @@
         <v>39</v>
       </c>
       <c r="E75" s="24" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F75" s="24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
@@ -2977,7 +2977,7 @@
         <v>57</v>
       </c>
       <c r="F76" s="24" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
@@ -3047,7 +3047,7 @@
         <v>54</v>
       </c>
       <c r="F79" s="24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G79" s="11"/>
       <c r="H79" s="11"/>
@@ -3071,7 +3071,7 @@
         <v>54</v>
       </c>
       <c r="F80" s="24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G80" s="11"/>
       <c r="H80" s="11"/>
@@ -3095,7 +3095,7 @@
         <v>57</v>
       </c>
       <c r="F81" s="24" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G81" s="11"/>
       <c r="H81" s="11"/>
@@ -3119,7 +3119,7 @@
         <v>54</v>
       </c>
       <c r="F82" s="24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G82" s="11"/>
       <c r="H82" s="11"/>
@@ -3143,7 +3143,7 @@
         <v>54</v>
       </c>
       <c r="F83" s="24" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G83" s="11"/>
       <c r="H83" s="11"/>
@@ -3164,10 +3164,10 @@
         <v>6</v>
       </c>
       <c r="E84" s="24" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F84" s="24" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G84" s="11"/>
       <c r="H84" s="11"/>
@@ -3184,16 +3184,16 @@
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
-      <c r="D85" s="26">
+      <c r="D85" s="25">
         <v>7</v>
       </c>
-      <c r="E85" s="31" t="s">
-        <v>139</v>
-      </c>
-      <c r="F85" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="G85" s="29"/>
+      <c r="E85" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="F85" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="G85" s="28"/>
       <c r="H85" s="11"/>
       <c r="I85" s="11"/>
       <c r="J85" s="3"/>
@@ -3208,16 +3208,16 @@
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
-      <c r="D86" s="26">
+      <c r="D86" s="25">
         <v>8</v>
       </c>
-      <c r="E86" s="31" t="s">
-        <v>139</v>
-      </c>
-      <c r="F86" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="G86" s="30"/>
+      <c r="E86" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="F86" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="G86" s="29"/>
       <c r="H86" s="11"/>
       <c r="I86" s="11"/>
       <c r="J86" s="3"/>
@@ -3239,7 +3239,7 @@
         <v>54</v>
       </c>
       <c r="F87" s="24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G87" s="11"/>
       <c r="H87" s="11"/>
@@ -3263,7 +3263,7 @@
         <v>54</v>
       </c>
       <c r="F88" s="24" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G88" s="11"/>
       <c r="H88" s="11"/>
@@ -3284,10 +3284,10 @@
         <v>11</v>
       </c>
       <c r="E89" s="24" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F89" s="24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G89" s="11"/>
       <c r="H89" s="11"/>
@@ -3311,7 +3311,7 @@
         <v>54</v>
       </c>
       <c r="F90" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G90" s="11"/>
       <c r="H90" s="11"/>
@@ -3335,7 +3335,7 @@
         <v>54</v>
       </c>
       <c r="F91" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G91" s="11"/>
       <c r="H91" s="11"/>
@@ -3356,10 +3356,10 @@
         <v>14</v>
       </c>
       <c r="E92" s="24" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F92" s="24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G92" s="11"/>
       <c r="H92" s="11"/>
@@ -3376,14 +3376,14 @@
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
-      <c r="D93" s="26">
+      <c r="D93" s="25">
         <v>15</v>
       </c>
       <c r="E93" s="24" t="s">
         <v>57</v>
       </c>
       <c r="F93" s="24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G93" s="11"/>
       <c r="H93" s="11"/>
@@ -3400,14 +3400,14 @@
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
-      <c r="D94" s="26">
+      <c r="D94" s="25">
         <v>16</v>
       </c>
       <c r="E94" s="24" t="s">
         <v>57</v>
       </c>
       <c r="F94" s="24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G94" s="11"/>
       <c r="H94" s="11"/>
@@ -3431,7 +3431,7 @@
         <v>57</v>
       </c>
       <c r="F95" s="24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G95" s="11"/>
       <c r="H95" s="11"/>
@@ -3455,7 +3455,7 @@
         <v>57</v>
       </c>
       <c r="F96" s="24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G96" s="11"/>
       <c r="H96" s="11"/>
@@ -3479,7 +3479,7 @@
         <v>57</v>
       </c>
       <c r="F97" s="24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G97" s="11"/>
       <c r="H97" s="11"/>
@@ -3500,10 +3500,10 @@
         <v>20</v>
       </c>
       <c r="E98" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F98" s="24" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G98" s="11"/>
       <c r="H98" s="11"/>
@@ -3524,10 +3524,10 @@
         <v>21</v>
       </c>
       <c r="E99" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F99" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G99" s="11"/>
       <c r="H99" s="11"/>
@@ -3551,7 +3551,7 @@
         <v>54</v>
       </c>
       <c r="F100" s="24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G100" s="11"/>
       <c r="H100" s="11"/>
@@ -3568,14 +3568,14 @@
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
-      <c r="D101" s="26">
+      <c r="D101" s="25">
         <v>23</v>
       </c>
       <c r="E101" s="24" t="s">
         <v>54</v>
       </c>
       <c r="F101" s="24" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G101" s="24"/>
       <c r="H101" s="11"/>
@@ -3592,14 +3592,14 @@
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
-      <c r="D102" s="26">
+      <c r="D102" s="25">
         <v>24</v>
       </c>
       <c r="E102" s="24" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F102" s="24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G102" s="24"/>
       <c r="H102" s="11"/>
@@ -3623,7 +3623,7 @@
         <v>54</v>
       </c>
       <c r="F103" s="24" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G103" s="24"/>
       <c r="H103" s="11"/>
@@ -3647,7 +3647,7 @@
         <v>54</v>
       </c>
       <c r="F104" s="24" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G104" s="11"/>
       <c r="H104" s="11"/>
@@ -3668,10 +3668,10 @@
         <v>27</v>
       </c>
       <c r="E105" s="24" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F105" s="24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G105" s="11"/>
       <c r="H105" s="11"/>
@@ -3695,7 +3695,7 @@
         <v>57</v>
       </c>
       <c r="F106" s="24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G106" s="11"/>
       <c r="H106" s="11"/>
@@ -3719,7 +3719,7 @@
         <v>57</v>
       </c>
       <c r="F107" s="24" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G107" s="11"/>
       <c r="H107" s="11"/>
@@ -3743,7 +3743,7 @@
         <v>57</v>
       </c>
       <c r="F108" s="24" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G108" s="11"/>
       <c r="H108" s="11"/>
@@ -3760,14 +3760,14 @@
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
-      <c r="D109" s="26">
+      <c r="D109" s="25">
         <v>31</v>
       </c>
       <c r="E109" s="24" t="s">
         <v>57</v>
       </c>
       <c r="F109" s="24" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G109" s="11"/>
       <c r="H109" s="11"/>
@@ -3784,14 +3784,14 @@
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
-      <c r="D110" s="26">
+      <c r="D110" s="25">
         <v>32</v>
       </c>
       <c r="E110" s="24" t="s">
         <v>57</v>
       </c>
       <c r="F110" s="24" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G110" s="11"/>
       <c r="H110" s="11"/>
@@ -3812,10 +3812,10 @@
         <v>33</v>
       </c>
       <c r="E111" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F111" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G111" s="11"/>
       <c r="H111" s="11"/>
@@ -3836,10 +3836,10 @@
         <v>34</v>
       </c>
       <c r="E112" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F112" s="24" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G112" s="11"/>
       <c r="H112" s="11"/>
@@ -3860,10 +3860,10 @@
         <v>35</v>
       </c>
       <c r="E113" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F113" s="24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G113" s="11"/>
       <c r="H113" s="11"/>
@@ -3884,10 +3884,10 @@
         <v>36</v>
       </c>
       <c r="E114" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F114" s="24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G114" s="11"/>
       <c r="H114" s="11"/>
@@ -3908,10 +3908,10 @@
         <v>37</v>
       </c>
       <c r="E115" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F115" s="24" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G115" s="11"/>
       <c r="H115" s="11"/>
@@ -3932,10 +3932,10 @@
         <v>38</v>
       </c>
       <c r="E116" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F116" s="24" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G116" s="11"/>
       <c r="H116" s="11"/>
@@ -3952,14 +3952,14 @@
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
-      <c r="D117" s="26">
+      <c r="D117" s="25">
         <v>39</v>
       </c>
       <c r="E117" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F117" s="24" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G117" s="11"/>
       <c r="H117" s="11"/>
@@ -3976,14 +3976,14 @@
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
-      <c r="D118" s="26">
+      <c r="D118" s="25">
         <v>40</v>
       </c>
       <c r="E118" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F118" s="24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G118" s="11"/>
       <c r="H118" s="11"/>
@@ -4004,10 +4004,10 @@
         <v>41</v>
       </c>
       <c r="E119" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F119" s="24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G119" s="11"/>
       <c r="H119" s="11"/>
@@ -4028,10 +4028,10 @@
         <v>42</v>
       </c>
       <c r="E120" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F120" s="24" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G120" s="11"/>
       <c r="H120" s="11"/>
@@ -4052,10 +4052,10 @@
         <v>43</v>
       </c>
       <c r="E121" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F121" s="24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G121" s="11"/>
       <c r="H121" s="11"/>
@@ -4076,10 +4076,10 @@
         <v>44</v>
       </c>
       <c r="E122" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F122" s="24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G122" s="11"/>
       <c r="H122" s="11"/>

--- a/ArmCoreV1_QSPI/SSCProject/lan9252_app.xlsx
+++ b/ArmCoreV1_QSPI/SSCProject/lan9252_app.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SI\project\RTM_ON_NEW\FW-ArmCore\ArmCoreV1_QSPI\SSCProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B45208-0198-4BA4-8E28-2AB224D37EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5F76DF8-0A96-40CC-BBB4-17D40DC87D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-7730" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Profile" sheetId="11" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Profile!$B$10:$P$203</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Profile!$B$1:$P$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Profile!$B$10:$P$210</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Profile!$B$1:$P$211</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="229">
   <si>
     <t>Device Profile:</t>
   </si>
@@ -979,10 +979,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>OutU8_reserved1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>OutU8_reserved2</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -1019,6 +1015,46 @@
   </si>
   <si>
     <t>OutU8_cpg_vibration</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>OutU16_fkp_year</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>OutU8_fkp_month</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>OutU8_fkp_day</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>OutU8_fkp_hour</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>OutU8_fkp_minute</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>OutU8_fkp_fractions</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>OutU8_fkp_systemCurrentState</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>UNSIGNED16</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>UNSIGNED8</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>OutU8_state_sync</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -1026,7 +1062,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1096,6 +1132,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1151,7 +1195,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
       <protection locked="0"/>
@@ -1212,12 +1256,25 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1523,7 +1580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T1054"/>
+  <dimension ref="A1:T1061"/>
   <sheetFormatPr defaultColWidth="10.7265625" defaultRowHeight="14" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.81640625" style="2" customWidth="1"/>
@@ -1555,19 +1612,19 @@
         <v>1</v>
       </c>
       <c r="E1" s="4"/>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
       <c r="Q1" s="20"/>
       <c r="R1" s="20"/>
       <c r="S1" s="20"/>
@@ -1583,17 +1640,17 @@
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
       <c r="Q2" s="20"/>
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
@@ -1605,17 +1662,17 @@
       <c r="C3" s="5"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="27"/>
       <c r="Q3" s="20"/>
       <c r="R3" s="20"/>
       <c r="S3" s="20"/>
@@ -1627,17 +1684,17 @@
       <c r="C4" s="5"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
       <c r="Q4" s="20"/>
       <c r="R4" s="20"/>
       <c r="S4" s="20"/>
@@ -1649,17 +1706,17 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
-      <c r="M5" s="26"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="26"/>
-      <c r="P5" s="26"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="27"/>
+      <c r="P5" s="27"/>
       <c r="Q5" s="20"/>
       <c r="R5" s="20"/>
       <c r="S5" s="20"/>
@@ -1671,17 +1728,17 @@
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="26"/>
-      <c r="M6" s="26"/>
-      <c r="N6" s="26"/>
-      <c r="O6" s="26"/>
-      <c r="P6" s="26"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="27"/>
+      <c r="P6" s="27"/>
       <c r="Q6" s="20"/>
       <c r="R6" s="20"/>
       <c r="S6" s="20"/>
@@ -2510,11 +2567,11 @@
       <c r="D45" s="24">
         <v>9</v>
       </c>
-      <c r="E45" s="27" t="s">
+      <c r="E45" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="F45" s="26" t="s">
         <v>214</v>
-      </c>
-      <c r="F45" s="27" t="s">
-        <v>215</v>
       </c>
       <c r="G45" s="11"/>
       <c r="H45" s="11"/>
@@ -2538,7 +2595,7 @@
         <v>58</v>
       </c>
       <c r="F46" s="24" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G46" s="11"/>
       <c r="H46" s="11"/>
@@ -5045,29 +5102,29 @@
       <c r="O150" s="3"/>
       <c r="P150" s="11"/>
     </row>
-    <row r="151" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="3"/>
-      <c r="B151" s="3"/>
-      <c r="C151" s="3"/>
-      <c r="D151" s="16">
+    <row r="151" spans="1:16" s="32" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="29"/>
+      <c r="B151" s="29"/>
+      <c r="C151" s="29"/>
+      <c r="D151" s="30">
         <v>5</v>
       </c>
-      <c r="E151" s="24" t="s">
+      <c r="E151" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="F151" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="G151" s="11"/>
-      <c r="H151" s="11"/>
-      <c r="I151" s="11"/>
-      <c r="J151" s="3"/>
-      <c r="K151" s="3"/>
-      <c r="L151" s="3"/>
-      <c r="M151" s="3"/>
-      <c r="N151" s="3"/>
-      <c r="O151" s="3"/>
-      <c r="P151" s="11"/>
+      <c r="F151" s="31" t="s">
+        <v>228</v>
+      </c>
+      <c r="G151" s="31"/>
+      <c r="H151" s="31"/>
+      <c r="I151" s="31"/>
+      <c r="J151" s="29"/>
+      <c r="K151" s="29"/>
+      <c r="L151" s="29"/>
+      <c r="M151" s="29"/>
+      <c r="N151" s="29"/>
+      <c r="O151" s="29"/>
+      <c r="P151" s="31"/>
     </row>
     <row r="152" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="3"/>
@@ -5100,11 +5157,11 @@
       <c r="D153" s="16">
         <v>7</v>
       </c>
-      <c r="E153" s="27" t="s">
+      <c r="E153" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="F153" s="27" t="s">
-        <v>216</v>
+      <c r="F153" s="26" t="s">
+        <v>215</v>
       </c>
       <c r="G153" s="11"/>
       <c r="H153" s="11"/>
@@ -5124,11 +5181,11 @@
       <c r="D154" s="16">
         <v>8</v>
       </c>
-      <c r="E154" s="27" t="s">
+      <c r="E154" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="F154" s="27" t="s">
-        <v>217</v>
+      <c r="F154" s="26" t="s">
+        <v>216</v>
       </c>
       <c r="G154" s="11"/>
       <c r="H154" s="11"/>
@@ -5317,10 +5374,10 @@
         <v>16</v>
       </c>
       <c r="E162" s="24" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F162" s="24" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G162" s="11"/>
       <c r="H162" s="11"/>
@@ -5800,7 +5857,7 @@
         <v>58</v>
       </c>
       <c r="F182" s="24" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G182" s="11"/>
       <c r="H182" s="11"/>
@@ -6036,11 +6093,11 @@
       <c r="D192" s="16">
         <v>46</v>
       </c>
-      <c r="E192" s="27" t="s">
+      <c r="E192" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="F192" s="27" t="s">
-        <v>218</v>
+      <c r="F192" s="26" t="s">
+        <v>217</v>
       </c>
       <c r="G192" s="11"/>
       <c r="H192" s="11"/>
@@ -6060,11 +6117,11 @@
       <c r="D193" s="16">
         <v>47</v>
       </c>
-      <c r="E193" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="F193" s="24" t="s">
-        <v>189</v>
+      <c r="E193" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="F193" s="28" t="s">
+        <v>219</v>
       </c>
       <c r="G193" s="11"/>
       <c r="H193" s="11"/>
@@ -6084,11 +6141,11 @@
       <c r="D194" s="16">
         <v>48</v>
       </c>
-      <c r="E194" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="F194" s="27" t="s">
-        <v>219</v>
+      <c r="E194" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="F194" s="28" t="s">
+        <v>220</v>
       </c>
       <c r="G194" s="11"/>
       <c r="H194" s="11"/>
@@ -6101,35 +6158,43 @@
       <c r="O194" s="3"/>
       <c r="P194" s="11"/>
     </row>
-    <row r="195" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A195" s="11"/>
-      <c r="B195" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="C195" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D195" s="17"/>
-      <c r="E195" s="17"/>
-      <c r="F195" s="18"/>
-      <c r="G195" s="17"/>
-      <c r="H195" s="17"/>
-      <c r="I195" s="17"/>
-      <c r="J195" s="17"/>
-      <c r="K195" s="17"/>
-      <c r="L195" s="17"/>
-      <c r="M195" s="17"/>
-      <c r="N195" s="17"/>
-      <c r="O195" s="17"/>
-      <c r="P195" s="17"/>
-    </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A195" s="3"/>
+      <c r="B195" s="3"/>
+      <c r="C195" s="3"/>
+      <c r="D195" s="16">
+        <v>49</v>
+      </c>
+      <c r="E195" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="F195" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="G195" s="11"/>
+      <c r="H195" s="11"/>
+      <c r="I195" s="11"/>
+      <c r="J195" s="3"/>
+      <c r="K195" s="3"/>
+      <c r="L195" s="3"/>
+      <c r="M195" s="3"/>
+      <c r="N195" s="3"/>
+      <c r="O195" s="3"/>
+      <c r="P195" s="11"/>
+    </row>
+    <row r="196" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A196" s="3"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
-      <c r="D196" s="16"/>
-      <c r="E196" s="11"/>
-      <c r="F196" s="11"/>
+      <c r="D196" s="16">
+        <v>50</v>
+      </c>
+      <c r="E196" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="F196" s="28" t="s">
+        <v>222</v>
+      </c>
       <c r="G196" s="11"/>
       <c r="H196" s="11"/>
       <c r="I196" s="11"/>
@@ -6141,13 +6206,19 @@
       <c r="O196" s="3"/>
       <c r="P196" s="11"/>
     </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A197" s="3"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
-      <c r="D197" s="16"/>
-      <c r="E197" s="11"/>
-      <c r="F197" s="11"/>
+      <c r="D197" s="16">
+        <v>51</v>
+      </c>
+      <c r="E197" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="F197" s="28" t="s">
+        <v>223</v>
+      </c>
       <c r="G197" s="11"/>
       <c r="H197" s="11"/>
       <c r="I197" s="11"/>
@@ -6159,35 +6230,43 @@
       <c r="O197" s="3"/>
       <c r="P197" s="11"/>
     </row>
-    <row r="198" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A198" s="11"/>
-      <c r="B198" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="C198" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="D198" s="17"/>
-      <c r="E198" s="17"/>
-      <c r="F198" s="11"/>
-      <c r="G198" s="17"/>
-      <c r="H198" s="17"/>
-      <c r="I198" s="17"/>
-      <c r="J198" s="17"/>
-      <c r="K198" s="17"/>
-      <c r="L198" s="17"/>
-      <c r="M198" s="17"/>
-      <c r="N198" s="17"/>
-      <c r="O198" s="17"/>
-      <c r="P198" s="17"/>
-    </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A198" s="3"/>
+      <c r="B198" s="3"/>
+      <c r="C198" s="3"/>
+      <c r="D198" s="16">
+        <v>52</v>
+      </c>
+      <c r="E198" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="F198" s="28" t="s">
+        <v>224</v>
+      </c>
+      <c r="G198" s="11"/>
+      <c r="H198" s="11"/>
+      <c r="I198" s="11"/>
+      <c r="J198" s="3"/>
+      <c r="K198" s="3"/>
+      <c r="L198" s="3"/>
+      <c r="M198" s="3"/>
+      <c r="N198" s="3"/>
+      <c r="O198" s="3"/>
+      <c r="P198" s="11"/>
+    </row>
+    <row r="199" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="3"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
-      <c r="D199" s="16"/>
-      <c r="E199" s="11"/>
-      <c r="F199" s="11"/>
+      <c r="D199" s="16">
+        <v>53</v>
+      </c>
+      <c r="E199" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="F199" s="28" t="s">
+        <v>225</v>
+      </c>
       <c r="G199" s="11"/>
       <c r="H199" s="11"/>
       <c r="I199" s="11"/>
@@ -6199,13 +6278,19 @@
       <c r="O199" s="3"/>
       <c r="P199" s="11"/>
     </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="3"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
-      <c r="D200" s="16"/>
-      <c r="E200" s="11"/>
-      <c r="F200" s="11"/>
+      <c r="D200" s="16">
+        <v>54</v>
+      </c>
+      <c r="E200" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F200" s="24" t="s">
+        <v>189</v>
+      </c>
       <c r="G200" s="11"/>
       <c r="H200" s="11"/>
       <c r="I200" s="11"/>
@@ -6217,45 +6302,51 @@
       <c r="O200" s="3"/>
       <c r="P200" s="11"/>
     </row>
-    <row r="201" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A201" s="11"/>
-      <c r="B201" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="C201" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D201" s="17"/>
-      <c r="E201" s="17"/>
-      <c r="F201" s="17"/>
-      <c r="G201" s="17"/>
-      <c r="H201" s="17"/>
-      <c r="I201" s="17"/>
-      <c r="J201" s="17"/>
-      <c r="K201" s="17"/>
-      <c r="L201" s="17"/>
-      <c r="M201" s="17"/>
-      <c r="N201" s="17"/>
-      <c r="O201" s="17"/>
-      <c r="P201" s="17"/>
-    </row>
-    <row r="202" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A202" s="3"/>
-      <c r="B202" s="3"/>
-      <c r="C202" s="3"/>
-      <c r="D202" s="16"/>
-      <c r="E202" s="11"/>
-      <c r="F202" s="11"/>
-      <c r="G202" s="11"/>
-      <c r="H202" s="11"/>
-      <c r="I202" s="11"/>
-      <c r="J202" s="3"/>
-      <c r="K202" s="3"/>
-      <c r="L202" s="3"/>
-      <c r="M202" s="3"/>
-      <c r="N202" s="3"/>
-      <c r="O202" s="3"/>
-      <c r="P202" s="11"/>
+    <row r="201" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A201" s="3"/>
+      <c r="B201" s="3"/>
+      <c r="C201" s="3"/>
+      <c r="D201" s="16">
+        <v>55</v>
+      </c>
+      <c r="E201" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="F201" s="26" t="s">
+        <v>218</v>
+      </c>
+      <c r="G201" s="11"/>
+      <c r="H201" s="11"/>
+      <c r="I201" s="11"/>
+      <c r="J201" s="3"/>
+      <c r="K201" s="3"/>
+      <c r="L201" s="3"/>
+      <c r="M201" s="3"/>
+      <c r="N201" s="3"/>
+      <c r="O201" s="3"/>
+      <c r="P201" s="11"/>
+    </row>
+    <row r="202" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A202" s="11"/>
+      <c r="B202" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C202" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D202" s="17"/>
+      <c r="E202" s="17"/>
+      <c r="F202" s="18"/>
+      <c r="G202" s="17"/>
+      <c r="H202" s="17"/>
+      <c r="I202" s="17"/>
+      <c r="J202" s="17"/>
+      <c r="K202" s="17"/>
+      <c r="L202" s="17"/>
+      <c r="M202" s="17"/>
+      <c r="N202" s="17"/>
+      <c r="O202" s="17"/>
+      <c r="P202" s="17"/>
     </row>
     <row r="203" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A203" s="3"/>
@@ -6279,127 +6370,135 @@
       <c r="A204" s="3"/>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
-      <c r="D204" s="3"/>
-      <c r="E204" s="3"/>
-      <c r="F204" s="17"/>
-      <c r="G204" s="3"/>
-      <c r="H204" s="3"/>
-      <c r="I204" s="3"/>
+      <c r="D204" s="16"/>
+      <c r="E204" s="11"/>
+      <c r="F204" s="11"/>
+      <c r="G204" s="11"/>
+      <c r="H204" s="11"/>
+      <c r="I204" s="11"/>
       <c r="J204" s="3"/>
       <c r="K204" s="3"/>
       <c r="L204" s="3"/>
       <c r="M204" s="3"/>
       <c r="N204" s="3"/>
       <c r="O204" s="3"/>
-      <c r="P204" s="3"/>
-    </row>
-    <row r="205" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A205" s="3"/>
-      <c r="B205" s="3"/>
-      <c r="C205" s="3"/>
-      <c r="D205" s="3"/>
-      <c r="E205" s="3"/>
+      <c r="P204" s="11"/>
+    </row>
+    <row r="205" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A205" s="11"/>
+      <c r="B205" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C205" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D205" s="17"/>
+      <c r="E205" s="17"/>
       <c r="F205" s="11"/>
-      <c r="G205" s="3"/>
-      <c r="H205" s="3"/>
-      <c r="I205" s="3"/>
-      <c r="J205" s="3"/>
-      <c r="K205" s="3"/>
-      <c r="L205" s="3"/>
-      <c r="M205" s="3"/>
-      <c r="N205" s="3"/>
-      <c r="O205" s="3"/>
-      <c r="P205" s="3"/>
+      <c r="G205" s="17"/>
+      <c r="H205" s="17"/>
+      <c r="I205" s="17"/>
+      <c r="J205" s="17"/>
+      <c r="K205" s="17"/>
+      <c r="L205" s="17"/>
+      <c r="M205" s="17"/>
+      <c r="N205" s="17"/>
+      <c r="O205" s="17"/>
+      <c r="P205" s="17"/>
     </row>
     <row r="206" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A206" s="3"/>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
-      <c r="D206" s="3"/>
-      <c r="E206" s="3"/>
+      <c r="D206" s="16"/>
+      <c r="E206" s="11"/>
       <c r="F206" s="11"/>
-      <c r="G206" s="3"/>
-      <c r="H206" s="3"/>
-      <c r="I206" s="3"/>
+      <c r="G206" s="11"/>
+      <c r="H206" s="11"/>
+      <c r="I206" s="11"/>
       <c r="J206" s="3"/>
       <c r="K206" s="3"/>
       <c r="L206" s="3"/>
       <c r="M206" s="3"/>
       <c r="N206" s="3"/>
       <c r="O206" s="3"/>
-      <c r="P206" s="3"/>
+      <c r="P206" s="11"/>
     </row>
     <row r="207" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A207" s="3"/>
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
-      <c r="D207" s="3"/>
-      <c r="E207" s="3"/>
-      <c r="F207" s="17"/>
-      <c r="G207" s="3"/>
-      <c r="H207" s="3"/>
-      <c r="I207" s="3"/>
+      <c r="D207" s="16"/>
+      <c r="E207" s="11"/>
+      <c r="F207" s="11"/>
+      <c r="G207" s="11"/>
+      <c r="H207" s="11"/>
+      <c r="I207" s="11"/>
       <c r="J207" s="3"/>
       <c r="K207" s="3"/>
       <c r="L207" s="3"/>
       <c r="M207" s="3"/>
       <c r="N207" s="3"/>
       <c r="O207" s="3"/>
-      <c r="P207" s="3"/>
-    </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A208" s="3"/>
-      <c r="B208" s="3"/>
-      <c r="C208" s="3"/>
-      <c r="D208" s="3"/>
-      <c r="E208" s="3"/>
-      <c r="F208" s="11"/>
-      <c r="G208" s="3"/>
-      <c r="H208" s="3"/>
-      <c r="I208" s="3"/>
-      <c r="J208" s="3"/>
-      <c r="K208" s="3"/>
-      <c r="L208" s="3"/>
-      <c r="M208" s="3"/>
-      <c r="N208" s="3"/>
-      <c r="O208" s="3"/>
-      <c r="P208" s="3"/>
+      <c r="P207" s="11"/>
+    </row>
+    <row r="208" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A208" s="11"/>
+      <c r="B208" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C208" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D208" s="17"/>
+      <c r="E208" s="17"/>
+      <c r="F208" s="17"/>
+      <c r="G208" s="17"/>
+      <c r="H208" s="17"/>
+      <c r="I208" s="17"/>
+      <c r="J208" s="17"/>
+      <c r="K208" s="17"/>
+      <c r="L208" s="17"/>
+      <c r="M208" s="17"/>
+      <c r="N208" s="17"/>
+      <c r="O208" s="17"/>
+      <c r="P208" s="17"/>
     </row>
     <row r="209" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A209" s="3"/>
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
-      <c r="D209" s="3"/>
-      <c r="E209" s="3"/>
+      <c r="D209" s="16"/>
+      <c r="E209" s="11"/>
       <c r="F209" s="11"/>
-      <c r="G209" s="3"/>
-      <c r="H209" s="3"/>
-      <c r="I209" s="3"/>
+      <c r="G209" s="11"/>
+      <c r="H209" s="11"/>
+      <c r="I209" s="11"/>
       <c r="J209" s="3"/>
       <c r="K209" s="3"/>
       <c r="L209" s="3"/>
       <c r="M209" s="3"/>
       <c r="N209" s="3"/>
       <c r="O209" s="3"/>
-      <c r="P209" s="3"/>
+      <c r="P209" s="11"/>
     </row>
     <row r="210" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A210" s="3"/>
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
-      <c r="D210" s="3"/>
-      <c r="E210" s="3"/>
-      <c r="F210" s="3"/>
-      <c r="G210" s="3"/>
-      <c r="H210" s="3"/>
-      <c r="I210" s="3"/>
+      <c r="D210" s="16"/>
+      <c r="E210" s="11"/>
+      <c r="F210" s="11"/>
+      <c r="G210" s="11"/>
+      <c r="H210" s="11"/>
+      <c r="I210" s="11"/>
       <c r="J210" s="3"/>
       <c r="K210" s="3"/>
       <c r="L210" s="3"/>
       <c r="M210" s="3"/>
       <c r="N210" s="3"/>
       <c r="O210" s="3"/>
-      <c r="P210" s="3"/>
+      <c r="P210" s="11"/>
     </row>
     <row r="211" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A211" s="3"/>
@@ -6407,7 +6506,7 @@
       <c r="C211" s="3"/>
       <c r="D211" s="3"/>
       <c r="E211" s="3"/>
-      <c r="F211" s="3"/>
+      <c r="F211" s="17"/>
       <c r="G211" s="3"/>
       <c r="H211" s="3"/>
       <c r="I211" s="3"/>
@@ -6425,7 +6524,7 @@
       <c r="C212" s="3"/>
       <c r="D212" s="3"/>
       <c r="E212" s="3"/>
-      <c r="F212" s="3"/>
+      <c r="F212" s="11"/>
       <c r="G212" s="3"/>
       <c r="H212" s="3"/>
       <c r="I212" s="3"/>
@@ -6443,7 +6542,7 @@
       <c r="C213" s="3"/>
       <c r="D213" s="3"/>
       <c r="E213" s="3"/>
-      <c r="F213" s="3"/>
+      <c r="F213" s="11"/>
       <c r="G213" s="3"/>
       <c r="H213" s="3"/>
       <c r="I213" s="3"/>
@@ -6461,7 +6560,7 @@
       <c r="C214" s="3"/>
       <c r="D214" s="3"/>
       <c r="E214" s="3"/>
-      <c r="F214" s="3"/>
+      <c r="F214" s="17"/>
       <c r="G214" s="3"/>
       <c r="H214" s="3"/>
       <c r="I214" s="3"/>
@@ -6474,87 +6573,192 @@
       <c r="P214" s="3"/>
     </row>
     <row r="215" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A215" s="3"/>
+      <c r="B215" s="3"/>
       <c r="C215" s="3"/>
-      <c r="F215" s="3"/>
+      <c r="D215" s="3"/>
+      <c r="E215" s="3"/>
+      <c r="F215" s="11"/>
+      <c r="G215" s="3"/>
+      <c r="H215" s="3"/>
+      <c r="I215" s="3"/>
+      <c r="J215" s="3"/>
+      <c r="K215" s="3"/>
+      <c r="L215" s="3"/>
+      <c r="M215" s="3"/>
+      <c r="N215" s="3"/>
+      <c r="O215" s="3"/>
+      <c r="P215" s="3"/>
     </row>
     <row r="216" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A216" s="3"/>
+      <c r="B216" s="3"/>
       <c r="C216" s="3"/>
-      <c r="F216" s="3"/>
+      <c r="D216" s="3"/>
+      <c r="E216" s="3"/>
+      <c r="F216" s="11"/>
+      <c r="G216" s="3"/>
+      <c r="H216" s="3"/>
+      <c r="I216" s="3"/>
+      <c r="J216" s="3"/>
+      <c r="K216" s="3"/>
+      <c r="L216" s="3"/>
+      <c r="M216" s="3"/>
+      <c r="N216" s="3"/>
+      <c r="O216" s="3"/>
+      <c r="P216" s="3"/>
     </row>
     <row r="217" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A217" s="3"/>
+      <c r="B217" s="3"/>
       <c r="C217" s="3"/>
+      <c r="D217" s="3"/>
+      <c r="E217" s="3"/>
       <c r="F217" s="3"/>
+      <c r="G217" s="3"/>
+      <c r="H217" s="3"/>
+      <c r="I217" s="3"/>
+      <c r="J217" s="3"/>
+      <c r="K217" s="3"/>
+      <c r="L217" s="3"/>
+      <c r="M217" s="3"/>
+      <c r="N217" s="3"/>
+      <c r="O217" s="3"/>
+      <c r="P217" s="3"/>
     </row>
     <row r="218" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A218" s="3"/>
+      <c r="B218" s="3"/>
       <c r="C218" s="3"/>
+      <c r="D218" s="3"/>
+      <c r="E218" s="3"/>
       <c r="F218" s="3"/>
+      <c r="G218" s="3"/>
+      <c r="H218" s="3"/>
+      <c r="I218" s="3"/>
+      <c r="J218" s="3"/>
+      <c r="K218" s="3"/>
+      <c r="L218" s="3"/>
+      <c r="M218" s="3"/>
+      <c r="N218" s="3"/>
+      <c r="O218" s="3"/>
+      <c r="P218" s="3"/>
     </row>
     <row r="219" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A219" s="3"/>
+      <c r="B219" s="3"/>
       <c r="C219" s="3"/>
+      <c r="D219" s="3"/>
+      <c r="E219" s="3"/>
       <c r="F219" s="3"/>
+      <c r="G219" s="3"/>
+      <c r="H219" s="3"/>
+      <c r="I219" s="3"/>
+      <c r="J219" s="3"/>
+      <c r="K219" s="3"/>
+      <c r="L219" s="3"/>
+      <c r="M219" s="3"/>
+      <c r="N219" s="3"/>
+      <c r="O219" s="3"/>
+      <c r="P219" s="3"/>
     </row>
     <row r="220" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A220" s="3"/>
+      <c r="B220" s="3"/>
       <c r="C220" s="3"/>
+      <c r="D220" s="3"/>
+      <c r="E220" s="3"/>
       <c r="F220" s="3"/>
+      <c r="G220" s="3"/>
+      <c r="H220" s="3"/>
+      <c r="I220" s="3"/>
+      <c r="J220" s="3"/>
+      <c r="K220" s="3"/>
+      <c r="L220" s="3"/>
+      <c r="M220" s="3"/>
+      <c r="N220" s="3"/>
+      <c r="O220" s="3"/>
+      <c r="P220" s="3"/>
     </row>
     <row r="221" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A221" s="3"/>
+      <c r="B221" s="3"/>
       <c r="C221" s="3"/>
+      <c r="D221" s="3"/>
+      <c r="E221" s="3"/>
+      <c r="F221" s="3"/>
+      <c r="G221" s="3"/>
+      <c r="H221" s="3"/>
+      <c r="I221" s="3"/>
+      <c r="J221" s="3"/>
+      <c r="K221" s="3"/>
+      <c r="L221" s="3"/>
+      <c r="M221" s="3"/>
+      <c r="N221" s="3"/>
+      <c r="O221" s="3"/>
+      <c r="P221" s="3"/>
     </row>
     <row r="222" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C222" s="3"/>
+      <c r="F222" s="3"/>
     </row>
     <row r="223" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C223" s="3"/>
+      <c r="F223" s="3"/>
     </row>
     <row r="224" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C224" s="3"/>
-    </row>
-    <row r="225" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="F224" s="3"/>
+    </row>
+    <row r="225" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C225" s="3"/>
-    </row>
-    <row r="226" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="F225" s="3"/>
+    </row>
+    <row r="226" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C226" s="3"/>
-    </row>
-    <row r="227" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="F226" s="3"/>
+    </row>
+    <row r="227" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C227" s="3"/>
-    </row>
-    <row r="228" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="F227" s="3"/>
+    </row>
+    <row r="228" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C228" s="3"/>
     </row>
-    <row r="229" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="229" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C229" s="3"/>
     </row>
-    <row r="230" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="230" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C230" s="3"/>
     </row>
-    <row r="231" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="231" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C231" s="3"/>
     </row>
-    <row r="232" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="232" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C232" s="3"/>
     </row>
-    <row r="233" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="233" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C233" s="3"/>
     </row>
-    <row r="234" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="234" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C234" s="3"/>
     </row>
-    <row r="235" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="235" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C235" s="3"/>
     </row>
-    <row r="236" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="236" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C236" s="3"/>
     </row>
-    <row r="237" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="237" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C237" s="3"/>
     </row>
-    <row r="238" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="238" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C238" s="3"/>
     </row>
-    <row r="239" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="239" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C239" s="3"/>
     </row>
-    <row r="240" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="240" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C240" s="3"/>
     </row>
     <row r="241" spans="3:3" x14ac:dyDescent="0.25">
@@ -8999,28 +9203,49 @@
     <row r="1054" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C1054" s="3"/>
     </row>
+    <row r="1055" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C1055" s="3"/>
+    </row>
+    <row r="1056" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C1056" s="3"/>
+    </row>
+    <row r="1057" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C1057" s="3"/>
+    </row>
+    <row r="1058" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C1058" s="3"/>
+    </row>
+    <row r="1059" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C1059" s="3"/>
+    </row>
+    <row r="1060" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C1060" s="3"/>
+    </row>
+    <row r="1061" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C1061" s="3"/>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatRows="0" insertRows="0" insertHyperlinks="0" deleteRows="0" sort="0" autoFilter="0"/>
-  <autoFilter ref="B10:P203" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="B10:P210" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="F1:P6"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="9">
-    <dataValidation allowBlank="1" showInputMessage="1" sqref="C11 C14 C17 C20 C23 C26 C29 C32 C35 C145 C195 C198 C201" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Object Code value" error="The Object code value shall be:_x000a_VARIABLE_x000a_RECORD_x000a_ARRAY" sqref="C12:C13 C15:C16 C18:C19 C21:C22 C24:C25 C27:C28 C30:C31 C33:C34 C36:C144 C146:C194 C196:C197 C199:C200 C202:C214" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation allowBlank="1" showInputMessage="1" sqref="C11 C14 C17 C20 C23 C26 C29 C32 C35 C145 C202 C205 C208" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Object Code value" error="The Object code value shall be:_x000a_VARIABLE_x000a_RECORD_x000a_ARRAY" sqref="C12:C13 C15:C16 C18:C19 C21:C22 C24:C25 C27:C28 C30:C31 C33:C34 C36:C144 C146:C201 C203:C204 C206:C207 C209:C221" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Category" error="The value for the entry category shall be _x000a_M : (mandatory)_x000a_O : (optional) _x000a_C : (conditional)" sqref="J36 J199:J200 J202:J214 J12:J13 J15:J16 J18:J19 J21:J22 J24:J25 J27:J28 J30:J31 J33:J34 J40:J144 J146:J194 J196:J197" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Category" error="The value for the entry category shall be _x000a_M : (mandatory)_x000a_O : (optional) _x000a_C : (conditional)" sqref="J36 J206:J207 J209:J221 J12:J13 J15:J16 J18:J19 J21:J22 J24:J25 J27:J28 J30:J31 J33:J34 J40:J144 J146:J201 J203:J204" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"M,O,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Backup/Setting Flag" error="The entry flag shall be_x000a_B : (Backup)_x000a_S : (Setting)" sqref="K36 K199:K200 K202:K214 K12:K13 K15:K16 K18:K19 K21:K22 K24:K25 K27:K28 K30:K31 K33:K34 K40:K144 K146:K194 K196:K197" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Backup/Setting Flag" error="The entry flag shall be_x000a_B : (Backup)_x000a_S : (Setting)" sqref="K36 K206:K207 K209:K221 K12:K13 K15:K16 K18:K19 K21:K22 K24:K25 K27:K28 K30:K31 K33:K34 K40:K144 K146:K201 K203:K204" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"B,S"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M36:O36 M199:O200 M12:O13 M18:O19 M24:O25 M30:O31 M40:O144 M196:O197 M202:O203 M15:O16 M21:O22 M27:O28 M33:O34 M146:O194" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M36:O36 M206:O207 M12:O13 M18:O19 M24:O25 M30:O31 M40:O144 M203:O204 M209:O210 M15:O16 M21:O22 M27:O28 M33:O34 M146:O201" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"rx,tx"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C215:C1054" xr:uid="{00000000-0002-0000-0000-000005000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C222:C1061" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J37:J39" xr:uid="{20805EC6-BF85-484F-8728-8A67EE77DC8F}">

--- a/ArmCoreV1_QSPI/SSCProject/lan9252_app.xlsx
+++ b/ArmCoreV1_QSPI/SSCProject/lan9252_app.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SI\project\RTM_ON_NEW\FW-ArmCore\ArmCoreV1_QSPI\SSCProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F04498C-E3A9-4CD8-AF68-ADD2A30564CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0985C63B-39BB-406F-9388-1F39211CE0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33480" yWindow="4590" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Profile" sheetId="11" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="323">
   <si>
     <t>Device Profile:</t>
   </si>
@@ -1223,9 +1223,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>OutU8_cpg_led_blink</t>
-  </si>
-  <si>
     <t>OutU8_cpg_vibration</t>
   </si>
   <si>
@@ -1254,6 +1251,26 @@
   </si>
   <si>
     <t>InU8_OFF_DO_reserve8</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>UNSIGNED16</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>OutU16_rtm_on_plc_info</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>OutU16_rtm_off_plc_info</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>OutU32_cpg_led_blink</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>UNSIGNED32</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1453,9 +1470,6 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -1545,6 +1559,9 @@
     </xf>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1851,7 +1868,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T305"/>
+  <dimension ref="A1:T307"/>
   <sheetFormatPr defaultColWidth="10.7265625" defaultRowHeight="14" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.81640625" style="2" customWidth="1"/>
@@ -1883,19 +1900,19 @@
         <v>1</v>
       </c>
       <c r="E1"/>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40"/>
       <c r="Q1" s="3"/>
       <c r="R1" s="3"/>
       <c r="S1" s="3"/>
@@ -1905,63 +1922,63 @@
       <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>4</v>
       </c>
       <c r="E2"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="40"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
       <c r="T2" s="3"/>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B3" s="9"/>
+      <c r="B3" s="8"/>
       <c r="C3" s="6"/>
       <c r="D3"/>
       <c r="E3"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
     </row>
     <row r="4" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B4" s="9"/>
+      <c r="B4" s="8"/>
       <c r="C4" s="6"/>
       <c r="D4"/>
       <c r="E4"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="40"/>
+      <c r="O4" s="40"/>
+      <c r="P4" s="40"/>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
@@ -1972,17 +1989,17 @@
       <c r="C5"/>
       <c r="D5"/>
       <c r="E5"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="40"/>
+      <c r="N5" s="40"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="40"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
@@ -1993,17 +2010,17 @@
       <c r="C6"/>
       <c r="D6"/>
       <c r="E6"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="40"/>
+      <c r="N6" s="40"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="40"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
@@ -2014,24 +2031,24 @@
       <c r="C7"/>
       <c r="D7"/>
       <c r="E7"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
       <c r="T7" s="3"/>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="10" t="s">
         <v>5</v>
       </c>
       <c r="C8"/>
@@ -2067,92 +2084,92 @@
       <c r="P9"/>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="J10" s="12" t="s">
+      <c r="J10" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="K10" s="12" t="s">
+      <c r="K10" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="L10" s="12" t="s">
+      <c r="L10" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="M10" s="12" t="s">
+      <c r="M10" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="N10" s="12" t="s">
+      <c r="N10" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="O10" s="12" t="s">
+      <c r="O10" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="P10" s="12" t="s">
+      <c r="P10" s="11" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="13"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="12"/>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B12"/>
       <c r="C12"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
       <c r="J12"/>
       <c r="K12"/>
       <c r="L12"/>
       <c r="M12"/>
       <c r="N12"/>
       <c r="O12"/>
-      <c r="P12" s="15"/>
+      <c r="P12" s="14"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="D13" s="16"/>
+      <c r="D13" s="15"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -2161,28 +2178,28 @@
       <c r="P13" s="1"/>
     </row>
     <row r="14" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
-      <c r="O14" s="13"/>
-      <c r="P14" s="13"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="12"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="D15" s="16"/>
+      <c r="D15" s="15"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -2191,7 +2208,7 @@
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="2:20" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="D16" s="16"/>
+      <c r="D16" s="15"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -2200,28 +2217,28 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="2:16" s="1" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13"/>
-      <c r="P17" s="13"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="12"/>
+      <c r="P17" s="12"/>
     </row>
     <row r="18" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="D18" s="16"/>
+      <c r="D18" s="15"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -2230,7 +2247,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="D19" s="16"/>
+      <c r="D19" s="15"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -2239,28 +2256,28 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="2:16" s="1" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
-      <c r="N20" s="13"/>
-      <c r="O20" s="13"/>
-      <c r="P20" s="13"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+      <c r="O20" s="12"/>
+      <c r="P20" s="12"/>
     </row>
     <row r="21" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="D21" s="16"/>
+      <c r="D21" s="15"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
@@ -2269,7 +2286,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="D22" s="16"/>
+      <c r="D22" s="15"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
@@ -2278,28 +2295,28 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="2:16" s="1" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="13"/>
-      <c r="M23" s="13"/>
-      <c r="N23" s="13"/>
-      <c r="O23" s="13"/>
-      <c r="P23" s="13"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="12"/>
+      <c r="N23" s="12"/>
+      <c r="O23" s="12"/>
+      <c r="P23" s="12"/>
     </row>
     <row r="24" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="D24" s="16"/>
+      <c r="D24" s="15"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -2308,7 +2325,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="D25" s="16"/>
+      <c r="D25" s="15"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -2317,28 +2334,28 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="2:16" s="1" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="13"/>
-      <c r="M26" s="13"/>
-      <c r="N26" s="13"/>
-      <c r="O26" s="13"/>
-      <c r="P26" s="13"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="12"/>
+      <c r="M26" s="12"/>
+      <c r="N26" s="12"/>
+      <c r="O26" s="12"/>
+      <c r="P26" s="12"/>
     </row>
     <row r="27" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="D27" s="16"/>
+      <c r="D27" s="15"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
@@ -2347,7 +2364,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="D28" s="16"/>
+      <c r="D28" s="15"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
@@ -2356,28 +2373,28 @@
       <c r="P28" s="1"/>
     </row>
     <row r="29" spans="2:16" s="1" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
-      <c r="L29" s="13"/>
-      <c r="M29" s="13"/>
-      <c r="N29" s="13"/>
-      <c r="O29" s="13"/>
-      <c r="P29" s="13"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+      <c r="N29" s="12"/>
+      <c r="O29" s="12"/>
+      <c r="P29" s="12"/>
     </row>
     <row r="30" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="D30" s="16"/>
+      <c r="D30" s="15"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
@@ -2386,7 +2403,7 @@
       <c r="P30" s="1"/>
     </row>
     <row r="31" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="D31" s="16"/>
+      <c r="D31" s="15"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
@@ -2395,28 +2412,28 @@
       <c r="P31" s="1"/>
     </row>
     <row r="32" spans="2:16" s="1" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
-      <c r="K32" s="13"/>
-      <c r="L32" s="13"/>
-      <c r="M32" s="13"/>
-      <c r="N32" s="13"/>
-      <c r="O32" s="13"/>
-      <c r="P32" s="13"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="12"/>
+      <c r="N32" s="12"/>
+      <c r="O32" s="12"/>
+      <c r="P32" s="12"/>
     </row>
     <row r="33" spans="1:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="D33" s="16"/>
+      <c r="D33" s="15"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
@@ -2425,7 +2442,7 @@
       <c r="P33" s="1"/>
     </row>
     <row r="34" spans="1:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="D34" s="16"/>
+      <c r="D34" s="15"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -2434,25 +2451,25 @@
       <c r="P34" s="1"/>
     </row>
     <row r="35" spans="1:16" s="1" customFormat="1" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
-      <c r="K35" s="13"/>
-      <c r="L35" s="13"/>
-      <c r="M35" s="13"/>
-      <c r="N35" s="13"/>
-      <c r="O35" s="13"/>
-      <c r="P35" s="13"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="12"/>
+      <c r="K35" s="12"/>
+      <c r="L35" s="12"/>
+      <c r="M35" s="12"/>
+      <c r="N35" s="12"/>
+      <c r="O35" s="12"/>
+      <c r="P35" s="12"/>
     </row>
     <row r="36" spans="1:16" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="2" t="s">
@@ -2461,7 +2478,7 @@
       <c r="C36" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D36" s="16"/>
+      <c r="D36" s="15"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1" t="s">
         <v>41</v>
@@ -2475,25 +2492,25 @@
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
-      <c r="D37" s="17">
+      <c r="D37" s="16">
         <v>1</v>
       </c>
-      <c r="E37" s="17" t="s">
+      <c r="E37" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F37" s="17" t="s">
+      <c r="F37" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="G37" s="18"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="19"/>
-      <c r="K37" s="19"/>
-      <c r="L37" s="19"/>
-      <c r="M37" s="19"/>
-      <c r="N37" s="19"/>
-      <c r="O37" s="19"/>
-      <c r="P37" s="20" t="s">
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="18"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18"/>
+      <c r="M37" s="18"/>
+      <c r="N37" s="18"/>
+      <c r="O37" s="18"/>
+      <c r="P37" s="19" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2501,49 +2518,49 @@
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
-      <c r="D38" s="17">
+      <c r="D38" s="16">
         <v>2</v>
       </c>
-      <c r="E38" s="17" t="s">
+      <c r="E38" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F38" s="17" t="s">
+      <c r="F38" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="19"/>
-      <c r="K38" s="19"/>
-      <c r="L38" s="19"/>
-      <c r="M38" s="19"/>
-      <c r="N38" s="19"/>
-      <c r="O38" s="19"/>
-      <c r="P38" s="20"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+      <c r="M38" s="18"/>
+      <c r="N38" s="18"/>
+      <c r="O38" s="18"/>
+      <c r="P38" s="19"/>
     </row>
     <row r="39" spans="1:16" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
-      <c r="D39" s="17">
+      <c r="D39" s="16">
         <v>3</v>
       </c>
-      <c r="E39" s="17" t="s">
+      <c r="E39" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F39" s="17" t="s">
+      <c r="F39" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18"/>
-      <c r="I39" s="18"/>
-      <c r="J39" s="19"/>
-      <c r="K39" s="19"/>
-      <c r="L39" s="19"/>
-      <c r="M39" s="19"/>
-      <c r="N39" s="19"/>
-      <c r="O39" s="19"/>
-      <c r="P39" s="20" t="s">
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="18"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+      <c r="M39" s="18"/>
+      <c r="N39" s="18"/>
+      <c r="O39" s="18"/>
+      <c r="P39" s="19" t="s">
         <v>56</v>
       </c>
     </row>
@@ -2551,13 +2568,13 @@
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
-      <c r="D40" s="17">
+      <c r="D40" s="16">
         <v>4</v>
       </c>
-      <c r="E40" s="17" t="s">
+      <c r="E40" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F40" s="17" t="s">
+      <c r="F40" s="16" t="s">
         <v>66</v>
       </c>
       <c r="G40" s="1"/>
@@ -2577,13 +2594,13 @@
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
-      <c r="D41" s="17">
+      <c r="D41" s="16">
         <v>5</v>
       </c>
-      <c r="E41" s="17" t="s">
+      <c r="E41" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F41" s="17" t="s">
+      <c r="F41" s="16" t="s">
         <v>67</v>
       </c>
       <c r="G41" s="1"/>
@@ -2601,13 +2618,13 @@
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
-      <c r="D42" s="17">
+      <c r="D42" s="16">
         <v>6</v>
       </c>
-      <c r="E42" s="17" t="s">
+      <c r="E42" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="F42" s="17" t="s">
+      <c r="F42" s="16" t="s">
         <v>68</v>
       </c>
       <c r="G42" s="1"/>
@@ -2625,13 +2642,13 @@
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
-      <c r="D43" s="17">
+      <c r="D43" s="16">
         <v>7</v>
       </c>
-      <c r="E43" s="17" t="s">
+      <c r="E43" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F43" s="17" t="s">
+      <c r="F43" s="16" t="s">
         <v>69</v>
       </c>
       <c r="G43" s="1"/>
@@ -2649,13 +2666,13 @@
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
-      <c r="D44" s="17">
+      <c r="D44" s="16">
         <v>8</v>
       </c>
-      <c r="E44" s="17" t="s">
+      <c r="E44" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F44" s="17" t="s">
+      <c r="F44" s="16" t="s">
         <v>70</v>
       </c>
       <c r="G44" s="1"/>
@@ -2672,14 +2689,14 @@
     <row r="45" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
-      <c r="C45" s="21"/>
-      <c r="D45" s="17">
+      <c r="C45" s="20"/>
+      <c r="D45" s="16">
         <v>9</v>
       </c>
-      <c r="E45" s="17" t="s">
+      <c r="E45" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F45" s="17" t="s">
+      <c r="F45" s="16" t="s">
         <v>71</v>
       </c>
       <c r="G45" s="1"/>
@@ -2696,14 +2713,14 @@
     <row r="46" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
-      <c r="C46" s="21"/>
-      <c r="D46" s="17">
+      <c r="C46" s="20"/>
+      <c r="D46" s="16">
         <v>10</v>
       </c>
-      <c r="E46" s="17" t="s">
+      <c r="E46" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F46" s="17" t="s">
+      <c r="F46" s="16" t="s">
         <v>72</v>
       </c>
       <c r="G46" s="1"/>
@@ -2721,13 +2738,13 @@
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
-      <c r="D47" s="17">
+      <c r="D47" s="16">
         <v>11</v>
       </c>
-      <c r="E47" s="17" t="s">
+      <c r="E47" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F47" s="17" t="s">
+      <c r="F47" s="16" t="s">
         <v>73</v>
       </c>
       <c r="G47" s="1"/>
@@ -2745,13 +2762,13 @@
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
-      <c r="D48" s="17">
+      <c r="D48" s="16">
         <v>12</v>
       </c>
-      <c r="E48" s="17" t="s">
+      <c r="E48" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F48" s="17" t="s">
+      <c r="F48" s="16" t="s">
         <v>74</v>
       </c>
       <c r="G48" s="1"/>
@@ -2769,13 +2786,13 @@
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
-      <c r="D49" s="17">
+      <c r="D49" s="16">
         <v>13</v>
       </c>
-      <c r="E49" s="17" t="s">
+      <c r="E49" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="F49" s="17" t="s">
+      <c r="F49" s="16" t="s">
         <v>75</v>
       </c>
       <c r="G49" s="1"/>
@@ -2793,13 +2810,13 @@
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
-      <c r="D50" s="17">
+      <c r="D50" s="16">
         <v>14</v>
       </c>
-      <c r="E50" s="17" t="s">
+      <c r="E50" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F50" s="17" t="s">
+      <c r="F50" s="16" t="s">
         <v>76</v>
       </c>
       <c r="G50" s="1"/>
@@ -2817,13 +2834,13 @@
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
-      <c r="D51" s="17">
+      <c r="D51" s="16">
         <v>15</v>
       </c>
-      <c r="E51" s="17" t="s">
+      <c r="E51" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F51" s="17" t="s">
+      <c r="F51" s="16" t="s">
         <v>77</v>
       </c>
       <c r="G51" s="1"/>
@@ -2841,13 +2858,13 @@
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
-      <c r="D52" s="17">
+      <c r="D52" s="16">
         <v>16</v>
       </c>
-      <c r="E52" s="17" t="s">
+      <c r="E52" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F52" s="17" t="s">
+      <c r="F52" s="16" t="s">
         <v>78</v>
       </c>
       <c r="G52" s="1"/>
@@ -2865,16 +2882,16 @@
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
-      <c r="D53" s="17">
+      <c r="D53" s="16">
         <v>17</v>
       </c>
-      <c r="E53" s="17" t="s">
+      <c r="E53" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F53" s="17" t="s">
+      <c r="F53" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="G53" s="22"/>
+      <c r="G53" s="21"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
       <c r="J53" s="2"/>
@@ -2889,7 +2906,7 @@
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
-      <c r="D54" s="17">
+      <c r="D54" s="16">
         <v>18</v>
       </c>
       <c r="E54" s="4" t="s">
@@ -2898,7 +2915,7 @@
       <c r="F54" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="G54" s="22"/>
+      <c r="G54" s="21"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
       <c r="J54" s="2"/>
@@ -2913,7 +2930,7 @@
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
-      <c r="D55" s="17">
+      <c r="D55" s="16">
         <v>19</v>
       </c>
       <c r="E55" s="4" t="s">
@@ -2922,7 +2939,7 @@
       <c r="F55" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="G55" s="22"/>
+      <c r="G55" s="21"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
       <c r="J55" s="2"/>
@@ -2937,7 +2954,7 @@
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
-      <c r="D56" s="17">
+      <c r="D56" s="16">
         <v>20</v>
       </c>
       <c r="E56" s="4" t="s">
@@ -2946,7 +2963,7 @@
       <c r="F56" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="G56" s="22"/>
+      <c r="G56" s="21"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
       <c r="J56" s="2"/>
@@ -2961,7 +2978,7 @@
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
-      <c r="D57" s="17">
+      <c r="D57" s="16">
         <v>21</v>
       </c>
       <c r="E57" s="4" t="s">
@@ -2970,7 +2987,7 @@
       <c r="F57" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="G57" s="22"/>
+      <c r="G57" s="21"/>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
       <c r="J57" s="2"/>
@@ -2985,7 +3002,7 @@
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
-      <c r="D58" s="17">
+      <c r="D58" s="16">
         <v>22</v>
       </c>
       <c r="E58" s="4" t="s">
@@ -2994,7 +3011,7 @@
       <c r="F58" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="G58" s="22"/>
+      <c r="G58" s="21"/>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
       <c r="J58" s="2"/>
@@ -3009,7 +3026,7 @@
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
-      <c r="D59" s="17">
+      <c r="D59" s="16">
         <v>23</v>
       </c>
       <c r="E59" s="4" t="s">
@@ -3018,7 +3035,7 @@
       <c r="F59" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="G59" s="22"/>
+      <c r="G59" s="21"/>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
       <c r="J59" s="2"/>
@@ -3033,7 +3050,7 @@
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
-      <c r="D60" s="17">
+      <c r="D60" s="16">
         <v>24</v>
       </c>
       <c r="E60" s="4" t="s">
@@ -3042,7 +3059,7 @@
       <c r="F60" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="G60" s="22"/>
+      <c r="G60" s="21"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
       <c r="J60" s="2"/>
@@ -3057,7 +3074,7 @@
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
-      <c r="D61" s="17">
+      <c r="D61" s="16">
         <v>25</v>
       </c>
       <c r="E61" s="4" t="s">
@@ -3066,7 +3083,7 @@
       <c r="F61" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="G61" s="22"/>
+      <c r="G61" s="21"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
       <c r="J61" s="2"/>
@@ -3081,7 +3098,7 @@
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
-      <c r="D62" s="17">
+      <c r="D62" s="16">
         <v>26</v>
       </c>
       <c r="E62" s="4" t="s">
@@ -3090,7 +3107,7 @@
       <c r="F62" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="G62" s="22"/>
+      <c r="G62" s="21"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
       <c r="J62" s="2"/>
@@ -3105,7 +3122,7 @@
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
-      <c r="D63" s="17">
+      <c r="D63" s="16">
         <v>27</v>
       </c>
       <c r="E63" s="4" t="s">
@@ -3114,7 +3131,7 @@
       <c r="F63" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="G63" s="22"/>
+      <c r="G63" s="21"/>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
       <c r="J63" s="2"/>
@@ -3129,7 +3146,7 @@
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
-      <c r="D64" s="17">
+      <c r="D64" s="16">
         <v>28</v>
       </c>
       <c r="E64" s="4" t="s">
@@ -3138,7 +3155,7 @@
       <c r="F64" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="G64" s="22"/>
+      <c r="G64" s="21"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
       <c r="J64" s="2"/>
@@ -3153,7 +3170,7 @@
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
-      <c r="D65" s="17">
+      <c r="D65" s="16">
         <v>29</v>
       </c>
       <c r="E65" s="4" t="s">
@@ -3162,7 +3179,7 @@
       <c r="F65" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="G65" s="22"/>
+      <c r="G65" s="21"/>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
       <c r="J65" s="2"/>
@@ -3177,7 +3194,7 @@
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
-      <c r="D66" s="17">
+      <c r="D66" s="16">
         <v>30</v>
       </c>
       <c r="E66" s="4" t="s">
@@ -3186,7 +3203,7 @@
       <c r="F66" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G66" s="22"/>
+      <c r="G66" s="21"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
       <c r="J66" s="2"/>
@@ -3201,7 +3218,7 @@
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
-      <c r="D67" s="17">
+      <c r="D67" s="16">
         <v>31</v>
       </c>
       <c r="E67" s="4" t="s">
@@ -3210,7 +3227,7 @@
       <c r="F67" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="G67" s="22"/>
+      <c r="G67" s="21"/>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
       <c r="J67" s="2"/>
@@ -3225,7 +3242,7 @@
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
-      <c r="D68" s="17">
+      <c r="D68" s="16">
         <v>32</v>
       </c>
       <c r="E68" s="4" t="s">
@@ -3234,7 +3251,7 @@
       <c r="F68" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="G68" s="22"/>
+      <c r="G68" s="21"/>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
       <c r="J68" s="2"/>
@@ -3249,7 +3266,7 @@
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
-      <c r="D69" s="17">
+      <c r="D69" s="16">
         <v>33</v>
       </c>
       <c r="E69" s="4" t="s">
@@ -3258,7 +3275,7 @@
       <c r="F69" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="G69" s="22"/>
+      <c r="G69" s="21"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
       <c r="J69" s="2"/>
@@ -3273,7 +3290,7 @@
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
-      <c r="D70" s="17">
+      <c r="D70" s="16">
         <v>34</v>
       </c>
       <c r="E70" s="4" t="s">
@@ -3282,7 +3299,7 @@
       <c r="F70" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="G70" s="22"/>
+      <c r="G70" s="21"/>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
       <c r="J70" s="2"/>
@@ -3297,7 +3314,7 @@
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
-      <c r="D71" s="17">
+      <c r="D71" s="16">
         <v>35</v>
       </c>
       <c r="E71" s="4" t="s">
@@ -3306,7 +3323,7 @@
       <c r="F71" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="G71" s="22"/>
+      <c r="G71" s="21"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
       <c r="J71" s="2"/>
@@ -3321,7 +3338,7 @@
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
-      <c r="D72" s="17">
+      <c r="D72" s="16">
         <v>36</v>
       </c>
       <c r="E72" s="4" t="s">
@@ -3330,7 +3347,7 @@
       <c r="F72" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="G72" s="22"/>
+      <c r="G72" s="21"/>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
       <c r="J72" s="2"/>
@@ -3345,7 +3362,7 @@
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
-      <c r="D73" s="17">
+      <c r="D73" s="16">
         <v>37</v>
       </c>
       <c r="E73" s="4" t="s">
@@ -3354,7 +3371,7 @@
       <c r="F73" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="G73" s="22"/>
+      <c r="G73" s="21"/>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
       <c r="J73" s="2"/>
@@ -3369,7 +3386,7 @@
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
-      <c r="D74" s="17">
+      <c r="D74" s="16">
         <v>38</v>
       </c>
       <c r="E74" s="4" t="s">
@@ -3378,7 +3395,7 @@
       <c r="F74" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="G74" s="22"/>
+      <c r="G74" s="21"/>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
       <c r="J74" s="2"/>
@@ -3393,7 +3410,7 @@
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
-      <c r="D75" s="17">
+      <c r="D75" s="16">
         <v>39</v>
       </c>
       <c r="E75" s="4" t="s">
@@ -3402,7 +3419,7 @@
       <c r="F75" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="G75" s="22"/>
+      <c r="G75" s="21"/>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
       <c r="J75" s="2"/>
@@ -3417,7 +3434,7 @@
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
-      <c r="D76" s="17">
+      <c r="D76" s="16">
         <v>40</v>
       </c>
       <c r="E76" s="4" t="s">
@@ -3426,7 +3443,7 @@
       <c r="F76" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="G76" s="22"/>
+      <c r="G76" s="21"/>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
       <c r="J76" s="2"/>
@@ -3441,7 +3458,7 @@
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
-      <c r="D77" s="17">
+      <c r="D77" s="16">
         <v>41</v>
       </c>
       <c r="E77" s="4" t="s">
@@ -3450,7 +3467,7 @@
       <c r="F77" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="G77" s="22"/>
+      <c r="G77" s="21"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
       <c r="J77" s="2"/>
@@ -3465,7 +3482,7 @@
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
-      <c r="D78" s="17">
+      <c r="D78" s="16">
         <v>42</v>
       </c>
       <c r="E78" s="4" t="s">
@@ -3474,7 +3491,7 @@
       <c r="F78" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="G78" s="22"/>
+      <c r="G78" s="21"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
       <c r="J78" s="2"/>
@@ -3489,7 +3506,7 @@
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
-      <c r="D79" s="17">
+      <c r="D79" s="16">
         <v>43</v>
       </c>
       <c r="E79" s="4" t="s">
@@ -3498,7 +3515,7 @@
       <c r="F79" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G79" s="22"/>
+      <c r="G79" s="21"/>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
       <c r="J79" s="2"/>
@@ -3513,7 +3530,7 @@
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
-      <c r="D80" s="17">
+      <c r="D80" s="16">
         <v>44</v>
       </c>
       <c r="E80" s="4" t="s">
@@ -3522,7 +3539,7 @@
       <c r="F80" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="G80" s="22"/>
+      <c r="G80" s="21"/>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
       <c r="J80" s="2"/>
@@ -3537,7 +3554,7 @@
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
-      <c r="D81" s="17">
+      <c r="D81" s="16">
         <v>45</v>
       </c>
       <c r="E81" s="4" t="s">
@@ -3546,7 +3563,7 @@
       <c r="F81" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="G81" s="22"/>
+      <c r="G81" s="21"/>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
       <c r="J81" s="2"/>
@@ -3561,7 +3578,7 @@
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
-      <c r="D82" s="17">
+      <c r="D82" s="16">
         <v>46</v>
       </c>
       <c r="E82" s="4" t="s">
@@ -3570,7 +3587,7 @@
       <c r="F82" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="G82" s="22"/>
+      <c r="G82" s="21"/>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
       <c r="J82" s="2"/>
@@ -3585,7 +3602,7 @@
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
-      <c r="D83" s="17">
+      <c r="D83" s="16">
         <v>47</v>
       </c>
       <c r="E83" s="4" t="s">
@@ -3594,7 +3611,7 @@
       <c r="F83" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="G83" s="22"/>
+      <c r="G83" s="21"/>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
       <c r="J83" s="2"/>
@@ -3609,7 +3626,7 @@
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
-      <c r="D84" s="17">
+      <c r="D84" s="16">
         <v>48</v>
       </c>
       <c r="E84" s="4" t="s">
@@ -3618,7 +3635,7 @@
       <c r="F84" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="G84" s="22"/>
+      <c r="G84" s="21"/>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
       <c r="J84" s="2"/>
@@ -3633,7 +3650,7 @@
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
-      <c r="D85" s="17">
+      <c r="D85" s="16">
         <v>49</v>
       </c>
       <c r="E85" s="4" t="s">
@@ -3642,7 +3659,7 @@
       <c r="F85" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="G85" s="22"/>
+      <c r="G85" s="21"/>
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
       <c r="J85" s="2"/>
@@ -3657,7 +3674,7 @@
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
-      <c r="D86" s="17">
+      <c r="D86" s="16">
         <v>50</v>
       </c>
       <c r="E86" s="4" t="s">
@@ -3666,7 +3683,7 @@
       <c r="F86" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="G86" s="22"/>
+      <c r="G86" s="21"/>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
       <c r="J86" s="2"/>
@@ -3681,7 +3698,7 @@
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
-      <c r="D87" s="17">
+      <c r="D87" s="16">
         <v>51</v>
       </c>
       <c r="E87" s="4" t="s">
@@ -3690,7 +3707,7 @@
       <c r="F87" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="G87" s="22"/>
+      <c r="G87" s="21"/>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
       <c r="J87" s="2"/>
@@ -3705,7 +3722,7 @@
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
-      <c r="D88" s="17">
+      <c r="D88" s="16">
         <v>52</v>
       </c>
       <c r="E88" s="4" t="s">
@@ -3714,7 +3731,7 @@
       <c r="F88" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="G88" s="22"/>
+      <c r="G88" s="21"/>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
       <c r="J88" s="2"/>
@@ -3729,7 +3746,7 @@
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
-      <c r="D89" s="17">
+      <c r="D89" s="16">
         <v>53</v>
       </c>
       <c r="E89" s="4" t="s">
@@ -3738,7 +3755,7 @@
       <c r="F89" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="G89" s="22"/>
+      <c r="G89" s="21"/>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
       <c r="J89" s="2"/>
@@ -3753,7 +3770,7 @@
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
-      <c r="D90" s="17">
+      <c r="D90" s="16">
         <v>54</v>
       </c>
       <c r="E90" s="4" t="s">
@@ -3762,7 +3779,7 @@
       <c r="F90" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="G90" s="22"/>
+      <c r="G90" s="21"/>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
       <c r="J90" s="2"/>
@@ -3777,7 +3794,7 @@
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
-      <c r="D91" s="17">
+      <c r="D91" s="16">
         <v>55</v>
       </c>
       <c r="E91" s="4" t="s">
@@ -3786,7 +3803,7 @@
       <c r="F91" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="G91" s="22"/>
+      <c r="G91" s="21"/>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
       <c r="J91" s="2"/>
@@ -3801,7 +3818,7 @@
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
-      <c r="D92" s="17">
+      <c r="D92" s="16">
         <v>56</v>
       </c>
       <c r="E92" s="4" t="s">
@@ -3810,7 +3827,7 @@
       <c r="F92" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="G92" s="22"/>
+      <c r="G92" s="21"/>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
       <c r="J92" s="2"/>
@@ -3825,7 +3842,7 @@
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
-      <c r="D93" s="17">
+      <c r="D93" s="16">
         <v>57</v>
       </c>
       <c r="E93" s="4" t="s">
@@ -3834,7 +3851,7 @@
       <c r="F93" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="G93" s="22"/>
+      <c r="G93" s="21"/>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
       <c r="J93" s="2"/>
@@ -3849,7 +3866,7 @@
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
-      <c r="D94" s="17">
+      <c r="D94" s="16">
         <v>58</v>
       </c>
       <c r="E94" s="4" t="s">
@@ -3858,7 +3875,7 @@
       <c r="F94" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="G94" s="22"/>
+      <c r="G94" s="21"/>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
       <c r="J94" s="2"/>
@@ -3873,7 +3890,7 @@
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
-      <c r="D95" s="17">
+      <c r="D95" s="16">
         <v>59</v>
       </c>
       <c r="E95" s="4" t="s">
@@ -3882,7 +3899,7 @@
       <c r="F95" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="G95" s="22"/>
+      <c r="G95" s="21"/>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
       <c r="J95" s="2"/>
@@ -3897,7 +3914,7 @@
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
-      <c r="D96" s="17">
+      <c r="D96" s="16">
         <v>60</v>
       </c>
       <c r="E96" s="4" t="s">
@@ -3906,7 +3923,7 @@
       <c r="F96" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="G96" s="22"/>
+      <c r="G96" s="21"/>
       <c r="H96" s="1"/>
       <c r="I96" s="1"/>
       <c r="J96" s="2"/>
@@ -3921,7 +3938,7 @@
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
-      <c r="D97" s="17">
+      <c r="D97" s="16">
         <v>61</v>
       </c>
       <c r="E97" s="4" t="s">
@@ -3930,7 +3947,7 @@
       <c r="F97" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="G97" s="22"/>
+      <c r="G97" s="21"/>
       <c r="H97" s="1"/>
       <c r="I97" s="1"/>
       <c r="J97" s="2"/>
@@ -3945,7 +3962,7 @@
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
-      <c r="D98" s="17">
+      <c r="D98" s="16">
         <v>62</v>
       </c>
       <c r="E98" s="4" t="s">
@@ -3954,7 +3971,7 @@
       <c r="F98" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="G98" s="22"/>
+      <c r="G98" s="21"/>
       <c r="H98" s="1"/>
       <c r="I98" s="1"/>
       <c r="J98" s="2"/>
@@ -3969,7 +3986,7 @@
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
-      <c r="D99" s="17">
+      <c r="D99" s="16">
         <v>63</v>
       </c>
       <c r="E99" s="4" t="s">
@@ -3978,7 +3995,7 @@
       <c r="F99" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="G99" s="22"/>
+      <c r="G99" s="21"/>
       <c r="H99" s="1"/>
       <c r="I99" s="1"/>
       <c r="J99" s="2"/>
@@ -3993,7 +4010,7 @@
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
-      <c r="D100" s="17">
+      <c r="D100" s="16">
         <v>64</v>
       </c>
       <c r="E100" s="4" t="s">
@@ -4002,7 +4019,7 @@
       <c r="F100" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="G100" s="22"/>
+      <c r="G100" s="21"/>
       <c r="H100" s="1"/>
       <c r="I100" s="1"/>
       <c r="J100" s="2"/>
@@ -4017,7 +4034,7 @@
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
-      <c r="D101" s="17">
+      <c r="D101" s="16">
         <v>65</v>
       </c>
       <c r="E101" s="4" t="s">
@@ -4026,7 +4043,7 @@
       <c r="F101" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="G101" s="22"/>
+      <c r="G101" s="21"/>
       <c r="H101" s="1"/>
       <c r="I101" s="1"/>
       <c r="J101" s="2"/>
@@ -4041,7 +4058,7 @@
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
-      <c r="D102" s="17">
+      <c r="D102" s="16">
         <v>66</v>
       </c>
       <c r="E102" s="4" t="s">
@@ -4050,7 +4067,7 @@
       <c r="F102" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="G102" s="22"/>
+      <c r="G102" s="21"/>
       <c r="H102" s="1"/>
       <c r="I102" s="1"/>
       <c r="J102" s="2"/>
@@ -4065,7 +4082,7 @@
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
-      <c r="D103" s="17">
+      <c r="D103" s="16">
         <v>67</v>
       </c>
       <c r="E103" s="4" t="s">
@@ -4074,7 +4091,7 @@
       <c r="F103" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="G103" s="22"/>
+      <c r="G103" s="21"/>
       <c r="H103" s="1"/>
       <c r="I103" s="1"/>
       <c r="J103" s="2"/>
@@ -4089,7 +4106,7 @@
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
-      <c r="D104" s="17">
+      <c r="D104" s="16">
         <v>68</v>
       </c>
       <c r="E104" s="4" t="s">
@@ -4098,7 +4115,7 @@
       <c r="F104" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="G104" s="22"/>
+      <c r="G104" s="21"/>
       <c r="H104" s="1"/>
       <c r="I104" s="1"/>
       <c r="J104" s="2"/>
@@ -4113,7 +4130,7 @@
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
-      <c r="D105" s="17">
+      <c r="D105" s="16">
         <v>69</v>
       </c>
       <c r="E105" s="4" t="s">
@@ -4122,7 +4139,7 @@
       <c r="F105" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="G105" s="22"/>
+      <c r="G105" s="21"/>
       <c r="H105" s="1"/>
       <c r="I105" s="1"/>
       <c r="J105" s="2"/>
@@ -4137,7 +4154,7 @@
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
-      <c r="D106" s="17">
+      <c r="D106" s="16">
         <v>70</v>
       </c>
       <c r="E106" s="4" t="s">
@@ -4146,7 +4163,7 @@
       <c r="F106" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="G106" s="22"/>
+      <c r="G106" s="21"/>
       <c r="H106" s="1"/>
       <c r="I106" s="1"/>
       <c r="J106" s="2"/>
@@ -4161,7 +4178,7 @@
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
-      <c r="D107" s="17">
+      <c r="D107" s="16">
         <v>71</v>
       </c>
       <c r="E107" s="4" t="s">
@@ -4170,7 +4187,7 @@
       <c r="F107" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="G107" s="22"/>
+      <c r="G107" s="21"/>
       <c r="H107" s="1"/>
       <c r="I107" s="1"/>
       <c r="J107" s="2"/>
@@ -4185,7 +4202,7 @@
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
-      <c r="D108" s="17">
+      <c r="D108" s="16">
         <v>72</v>
       </c>
       <c r="E108" s="4" t="s">
@@ -4194,7 +4211,7 @@
       <c r="F108" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="G108" s="22"/>
+      <c r="G108" s="21"/>
       <c r="H108" s="1"/>
       <c r="I108" s="1"/>
       <c r="J108" s="2"/>
@@ -4209,7 +4226,7 @@
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
-      <c r="D109" s="17">
+      <c r="D109" s="16">
         <v>73</v>
       </c>
       <c r="E109" s="4" t="s">
@@ -4218,7 +4235,7 @@
       <c r="F109" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G109" s="22"/>
+      <c r="G109" s="21"/>
       <c r="H109" s="1"/>
       <c r="I109" s="1"/>
       <c r="J109" s="2"/>
@@ -4233,7 +4250,7 @@
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
-      <c r="D110" s="17">
+      <c r="D110" s="16">
         <v>74</v>
       </c>
       <c r="E110" s="4" t="s">
@@ -4242,7 +4259,7 @@
       <c r="F110" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="G110" s="22"/>
+      <c r="G110" s="21"/>
       <c r="H110" s="1"/>
       <c r="I110" s="1"/>
       <c r="J110" s="2"/>
@@ -4257,7 +4274,7 @@
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
-      <c r="D111" s="17">
+      <c r="D111" s="16">
         <v>75</v>
       </c>
       <c r="E111" s="4" t="s">
@@ -4266,7 +4283,7 @@
       <c r="F111" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="G111" s="22"/>
+      <c r="G111" s="21"/>
       <c r="H111" s="1"/>
       <c r="I111" s="1"/>
       <c r="J111" s="2"/>
@@ -4281,7 +4298,7 @@
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
-      <c r="D112" s="17">
+      <c r="D112" s="16">
         <v>76</v>
       </c>
       <c r="E112" s="4" t="s">
@@ -4290,7 +4307,7 @@
       <c r="F112" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="G112" s="22"/>
+      <c r="G112" s="21"/>
       <c r="H112" s="1"/>
       <c r="I112" s="1"/>
       <c r="J112" s="2"/>
@@ -4305,7 +4322,7 @@
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
-      <c r="D113" s="17">
+      <c r="D113" s="16">
         <v>77</v>
       </c>
       <c r="E113" s="4" t="s">
@@ -4314,7 +4331,7 @@
       <c r="F113" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="G113" s="22"/>
+      <c r="G113" s="21"/>
       <c r="H113" s="1"/>
       <c r="I113" s="1"/>
       <c r="J113" s="2"/>
@@ -4329,7 +4346,7 @@
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
-      <c r="D114" s="17">
+      <c r="D114" s="16">
         <v>78</v>
       </c>
       <c r="E114" s="4" t="s">
@@ -4338,7 +4355,7 @@
       <c r="F114" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="G114" s="22"/>
+      <c r="G114" s="21"/>
       <c r="H114" s="1"/>
       <c r="I114" s="1"/>
       <c r="J114" s="2"/>
@@ -4353,7 +4370,7 @@
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
-      <c r="D115" s="17">
+      <c r="D115" s="16">
         <v>79</v>
       </c>
       <c r="E115" s="4" t="s">
@@ -4362,7 +4379,7 @@
       <c r="F115" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="G115" s="22"/>
+      <c r="G115" s="21"/>
       <c r="H115" s="1"/>
       <c r="I115" s="1"/>
       <c r="J115" s="2"/>
@@ -4377,7 +4394,7 @@
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
-      <c r="D116" s="17">
+      <c r="D116" s="16">
         <v>80</v>
       </c>
       <c r="E116" s="4" t="s">
@@ -4386,7 +4403,7 @@
       <c r="F116" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G116" s="22"/>
+      <c r="G116" s="21"/>
       <c r="H116" s="1"/>
       <c r="I116" s="1"/>
       <c r="J116" s="2"/>
@@ -4401,7 +4418,7 @@
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
-      <c r="D117" s="17">
+      <c r="D117" s="16">
         <v>81</v>
       </c>
       <c r="E117" s="4" t="s">
@@ -4410,7 +4427,7 @@
       <c r="F117" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="G117" s="22"/>
+      <c r="G117" s="21"/>
       <c r="H117" s="1"/>
       <c r="I117" s="1"/>
       <c r="J117" s="2"/>
@@ -4425,7 +4442,7 @@
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
-      <c r="D118" s="17">
+      <c r="D118" s="16">
         <v>82</v>
       </c>
       <c r="E118" s="4" t="s">
@@ -4434,7 +4451,7 @@
       <c r="F118" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="G118" s="22"/>
+      <c r="G118" s="21"/>
       <c r="H118" s="1"/>
       <c r="I118" s="1"/>
       <c r="J118" s="2"/>
@@ -4449,16 +4466,16 @@
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
-      <c r="D119" s="17">
+      <c r="D119" s="16">
         <v>83</v>
       </c>
       <c r="E119" s="4" t="s">
         <v>90</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="G119" s="22"/>
+        <v>311</v>
+      </c>
+      <c r="G119" s="21"/>
       <c r="H119" s="1"/>
       <c r="I119" s="1"/>
       <c r="J119" s="2"/>
@@ -4473,16 +4490,16 @@
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
-      <c r="D120" s="17">
+      <c r="D120" s="16">
         <v>84</v>
       </c>
       <c r="E120" s="4" t="s">
         <v>57</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="G120" s="22"/>
+        <v>312</v>
+      </c>
+      <c r="G120" s="21"/>
       <c r="H120" s="1"/>
       <c r="I120" s="1"/>
       <c r="J120" s="2"/>
@@ -4497,7 +4514,7 @@
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
-      <c r="D121" s="17">
+      <c r="D121" s="16">
         <v>85</v>
       </c>
       <c r="E121" s="4" t="s">
@@ -4506,7 +4523,7 @@
       <c r="F121" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="G121" s="22"/>
+      <c r="G121" s="21"/>
       <c r="H121" s="1"/>
       <c r="I121" s="1"/>
       <c r="J121" s="2"/>
@@ -4521,7 +4538,7 @@
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
-      <c r="D122" s="17">
+      <c r="D122" s="16">
         <v>86</v>
       </c>
       <c r="E122" s="4" t="s">
@@ -4530,7 +4547,7 @@
       <c r="F122" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="G122" s="22"/>
+      <c r="G122" s="21"/>
       <c r="H122" s="1"/>
       <c r="I122" s="1"/>
       <c r="J122" s="2"/>
@@ -4545,7 +4562,7 @@
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
-      <c r="D123" s="17">
+      <c r="D123" s="16">
         <v>87</v>
       </c>
       <c r="E123" s="4" t="s">
@@ -4554,7 +4571,7 @@
       <c r="F123" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="G123" s="22"/>
+      <c r="G123" s="21"/>
       <c r="H123" s="1"/>
       <c r="I123" s="1"/>
       <c r="J123" s="2"/>
@@ -4569,7 +4586,7 @@
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
-      <c r="D124" s="17">
+      <c r="D124" s="16">
         <v>88</v>
       </c>
       <c r="E124" s="4" t="s">
@@ -4578,7 +4595,7 @@
       <c r="F124" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="G124" s="22"/>
+      <c r="G124" s="21"/>
       <c r="H124" s="1"/>
       <c r="I124" s="1"/>
       <c r="J124" s="2"/>
@@ -4593,7 +4610,7 @@
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
-      <c r="D125" s="17">
+      <c r="D125" s="16">
         <v>89</v>
       </c>
       <c r="E125" s="4" t="s">
@@ -4602,7 +4619,7 @@
       <c r="F125" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="G125" s="22"/>
+      <c r="G125" s="21"/>
       <c r="H125" s="1"/>
       <c r="I125" s="1"/>
       <c r="J125" s="2"/>
@@ -4617,7 +4634,7 @@
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
-      <c r="D126" s="17">
+      <c r="D126" s="16">
         <v>90</v>
       </c>
       <c r="E126" s="4" t="s">
@@ -4626,7 +4643,7 @@
       <c r="F126" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="G126" s="22"/>
+      <c r="G126" s="21"/>
       <c r="H126" s="1"/>
       <c r="I126" s="1"/>
       <c r="J126" s="2"/>
@@ -4641,7 +4658,7 @@
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
-      <c r="D127" s="17">
+      <c r="D127" s="16">
         <v>91</v>
       </c>
       <c r="E127" s="4" t="s">
@@ -4650,7 +4667,7 @@
       <c r="F127" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="G127" s="22"/>
+      <c r="G127" s="21"/>
       <c r="H127" s="1"/>
       <c r="I127" s="1"/>
       <c r="J127" s="2"/>
@@ -4665,16 +4682,16 @@
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
-      <c r="D128" s="17">
+      <c r="D128" s="16">
         <v>92</v>
       </c>
       <c r="E128" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="G128" s="22"/>
+        <v>313</v>
+      </c>
+      <c r="G128" s="21"/>
       <c r="H128" s="1"/>
       <c r="I128" s="1"/>
       <c r="J128" s="2"/>
@@ -4689,16 +4706,16 @@
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
-      <c r="D129" s="17">
+      <c r="D129" s="16">
         <v>93</v>
       </c>
       <c r="E129" s="4" t="s">
         <v>57</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="G129" s="22"/>
+        <v>314</v>
+      </c>
+      <c r="G129" s="21"/>
       <c r="H129" s="1"/>
       <c r="I129" s="1"/>
       <c r="J129" s="2"/>
@@ -4713,16 +4730,16 @@
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
-      <c r="D130" s="17">
+      <c r="D130" s="16">
         <v>94</v>
       </c>
       <c r="E130" s="4" t="s">
         <v>58</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="G130" s="22"/>
+        <v>315</v>
+      </c>
+      <c r="G130" s="21"/>
       <c r="H130" s="1"/>
       <c r="I130" s="1"/>
       <c r="J130" s="2"/>
@@ -4737,7 +4754,7 @@
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
-      <c r="D131" s="17">
+      <c r="D131" s="16">
         <v>95</v>
       </c>
       <c r="E131" s="4" t="s">
@@ -4746,7 +4763,7 @@
       <c r="F131" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="G131" s="22"/>
+      <c r="G131" s="21"/>
       <c r="H131" s="1"/>
       <c r="I131" s="1"/>
       <c r="J131" s="2"/>
@@ -4761,7 +4778,7 @@
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
-      <c r="D132" s="17">
+      <c r="D132" s="16">
         <v>96</v>
       </c>
       <c r="E132" s="4" t="s">
@@ -4770,7 +4787,7 @@
       <c r="F132" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="G132" s="22"/>
+      <c r="G132" s="21"/>
       <c r="H132" s="1"/>
       <c r="I132" s="1"/>
       <c r="J132" s="2"/>
@@ -4785,7 +4802,7 @@
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
-      <c r="D133" s="17">
+      <c r="D133" s="16">
         <v>97</v>
       </c>
       <c r="E133" s="4" t="s">
@@ -4794,7 +4811,7 @@
       <c r="F133" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="G133" s="22"/>
+      <c r="G133" s="21"/>
       <c r="H133" s="1"/>
       <c r="I133" s="1"/>
       <c r="J133" s="2"/>
@@ -4809,7 +4826,7 @@
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
-      <c r="D134" s="17">
+      <c r="D134" s="16">
         <v>98</v>
       </c>
       <c r="E134" s="4" t="s">
@@ -4818,7 +4835,7 @@
       <c r="F134" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="G134" s="22"/>
+      <c r="G134" s="21"/>
       <c r="H134" s="1"/>
       <c r="I134" s="1"/>
       <c r="J134" s="2"/>
@@ -4833,7 +4850,7 @@
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
-      <c r="D135" s="17">
+      <c r="D135" s="16">
         <v>99</v>
       </c>
       <c r="E135" s="4" t="s">
@@ -4842,7 +4859,7 @@
       <c r="F135" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G135" s="22"/>
+      <c r="G135" s="21"/>
       <c r="H135" s="1"/>
       <c r="I135" s="1"/>
       <c r="J135" s="2"/>
@@ -4857,7 +4874,7 @@
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
-      <c r="D136" s="17">
+      <c r="D136" s="16">
         <v>100</v>
       </c>
       <c r="E136" s="4" t="s">
@@ -4866,7 +4883,7 @@
       <c r="F136" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="G136" s="22"/>
+      <c r="G136" s="21"/>
       <c r="H136" s="1"/>
       <c r="I136" s="1"/>
       <c r="J136" s="2"/>
@@ -4881,7 +4898,7 @@
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
-      <c r="D137" s="17">
+      <c r="D137" s="16">
         <v>101</v>
       </c>
       <c r="E137" s="4" t="s">
@@ -4890,7 +4907,7 @@
       <c r="F137" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="G137" s="22"/>
+      <c r="G137" s="21"/>
       <c r="H137" s="1"/>
       <c r="I137" s="1"/>
       <c r="J137" s="2"/>
@@ -4905,16 +4922,16 @@
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
-      <c r="D138" s="17">
+      <c r="D138" s="16">
         <v>102</v>
       </c>
       <c r="E138" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="G138" s="22"/>
+        <v>316</v>
+      </c>
+      <c r="G138" s="21"/>
       <c r="H138" s="1"/>
       <c r="I138" s="1"/>
       <c r="J138" s="2"/>
@@ -4929,16 +4946,16 @@
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
-      <c r="D139" s="17">
+      <c r="D139" s="16">
         <v>103</v>
       </c>
       <c r="E139" s="4" t="s">
         <v>57</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="G139" s="22"/>
+        <v>317</v>
+      </c>
+      <c r="G139" s="21"/>
       <c r="H139" s="1"/>
       <c r="I139" s="1"/>
       <c r="J139" s="2"/>
@@ -4953,13 +4970,13 @@
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
-      <c r="D140" s="17">
+      <c r="D140" s="16">
         <v>104</v>
       </c>
-      <c r="E140" s="17" t="s">
+      <c r="E140" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F140" s="17" t="s">
+      <c r="F140" s="16" t="s">
         <v>164</v>
       </c>
       <c r="G140" s="1"/>
@@ -4977,13 +4994,13 @@
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
-      <c r="D141" s="17">
+      <c r="D141" s="16">
         <v>105</v>
       </c>
-      <c r="E141" s="17" t="s">
+      <c r="E141" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F141" s="17" t="s">
+      <c r="F141" s="16" t="s">
         <v>165</v>
       </c>
       <c r="G141" s="1"/>
@@ -5001,13 +5018,13 @@
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
-      <c r="D142" s="17">
+      <c r="D142" s="16">
         <v>106</v>
       </c>
-      <c r="E142" s="17" t="s">
+      <c r="E142" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="F142" s="17" t="s">
+      <c r="F142" s="16" t="s">
         <v>167</v>
       </c>
       <c r="G142" s="1"/>
@@ -5025,13 +5042,13 @@
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
-      <c r="D143" s="17">
+      <c r="D143" s="16">
         <v>107</v>
       </c>
-      <c r="E143" s="17" t="s">
+      <c r="E143" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F143" s="17" t="s">
+      <c r="F143" s="16" t="s">
         <v>168</v>
       </c>
       <c r="G143" s="1"/>
@@ -5049,13 +5066,13 @@
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
-      <c r="D144" s="17">
+      <c r="D144" s="16">
         <v>108</v>
       </c>
-      <c r="E144" s="17" t="s">
+      <c r="E144" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F144" s="17" t="s">
+      <c r="F144" s="16" t="s">
         <v>169</v>
       </c>
       <c r="G144" s="1"/>
@@ -5073,13 +5090,13 @@
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
-      <c r="D145" s="17">
+      <c r="D145" s="16">
         <v>109</v>
       </c>
-      <c r="E145" s="17" t="s">
+      <c r="E145" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="F145" s="17" t="s">
+      <c r="F145" s="16" t="s">
         <v>170</v>
       </c>
       <c r="G145" s="1"/>
@@ -5097,16 +5114,16 @@
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
-      <c r="D146" s="17">
+      <c r="D146" s="16">
         <v>110</v>
       </c>
-      <c r="E146" s="17" t="s">
+      <c r="E146" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F146" s="17" t="s">
+      <c r="F146" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="G146" s="23"/>
+      <c r="G146" s="22"/>
       <c r="H146" s="1"/>
       <c r="I146" s="1"/>
       <c r="J146" s="2"/>
@@ -5121,13 +5138,13 @@
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
-      <c r="D147" s="17">
+      <c r="D147" s="16">
         <v>111</v>
       </c>
-      <c r="E147" s="17" t="s">
+      <c r="E147" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F147" s="17" t="s">
+      <c r="F147" s="16" t="s">
         <v>172</v>
       </c>
       <c r="G147" s="1"/>
@@ -5145,13 +5162,13 @@
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
-      <c r="D148" s="17">
+      <c r="D148" s="16">
         <v>112</v>
       </c>
-      <c r="E148" s="17" t="s">
+      <c r="E148" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F148" s="17" t="s">
+      <c r="F148" s="16" t="s">
         <v>173</v>
       </c>
       <c r="G148" s="1"/>
@@ -5169,13 +5186,13 @@
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
-      <c r="D149" s="17">
+      <c r="D149" s="16">
         <v>113</v>
       </c>
-      <c r="E149" s="17" t="s">
+      <c r="E149" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F149" s="17" t="s">
+      <c r="F149" s="16" t="s">
         <v>174</v>
       </c>
       <c r="G149" s="1"/>
@@ -5193,13 +5210,13 @@
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
-      <c r="D150" s="17">
+      <c r="D150" s="16">
         <v>114</v>
       </c>
-      <c r="E150" s="24" t="s">
+      <c r="E150" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="F150" s="17" t="s">
+      <c r="F150" s="16" t="s">
         <v>175</v>
       </c>
       <c r="G150" s="1"/>
@@ -5217,13 +5234,13 @@
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
-      <c r="D151" s="17">
+      <c r="D151" s="16">
         <v>115</v>
       </c>
-      <c r="E151" s="24" t="s">
+      <c r="E151" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="F151" s="17" t="s">
+      <c r="F151" s="16" t="s">
         <v>176</v>
       </c>
       <c r="G151" s="1"/>
@@ -5241,13 +5258,13 @@
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
-      <c r="D152" s="17">
+      <c r="D152" s="16">
         <v>116</v>
       </c>
-      <c r="E152" s="17" t="s">
+      <c r="E152" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="F152" s="17" t="s">
+      <c r="F152" s="16" t="s">
         <v>177</v>
       </c>
       <c r="G152" s="1"/>
@@ -5265,13 +5282,13 @@
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
-      <c r="D153" s="17">
+      <c r="D153" s="16">
         <v>117</v>
       </c>
-      <c r="E153" s="24" t="s">
+      <c r="E153" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="F153" s="17" t="s">
+      <c r="F153" s="16" t="s">
         <v>178</v>
       </c>
       <c r="G153" s="1"/>
@@ -5289,13 +5306,13 @@
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
-      <c r="D154" s="17">
+      <c r="D154" s="16">
         <v>118</v>
       </c>
-      <c r="E154" s="24" t="s">
+      <c r="E154" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="F154" s="17" t="s">
+      <c r="F154" s="16" t="s">
         <v>179</v>
       </c>
       <c r="G154" s="1"/>
@@ -5313,13 +5330,13 @@
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
-      <c r="D155" s="17">
+      <c r="D155" s="16">
         <v>119</v>
       </c>
-      <c r="E155" s="24" t="s">
+      <c r="E155" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="F155" s="17" t="s">
+      <c r="F155" s="16" t="s">
         <v>180</v>
       </c>
       <c r="G155" s="1"/>
@@ -5337,13 +5354,13 @@
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
-      <c r="D156" s="17">
+      <c r="D156" s="16">
         <v>120</v>
       </c>
-      <c r="E156" s="24" t="s">
+      <c r="E156" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="F156" s="17" t="s">
+      <c r="F156" s="16" t="s">
         <v>181</v>
       </c>
       <c r="G156" s="1"/>
@@ -5361,13 +5378,13 @@
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
-      <c r="D157" s="17">
+      <c r="D157" s="16">
         <v>121</v>
       </c>
-      <c r="E157" s="24" t="s">
+      <c r="E157" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="F157" s="17" t="s">
+      <c r="F157" s="16" t="s">
         <v>182</v>
       </c>
       <c r="G157" s="1"/>
@@ -5385,13 +5402,13 @@
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
-      <c r="D158" s="17">
+      <c r="D158" s="16">
         <v>122</v>
       </c>
-      <c r="E158" s="24" t="s">
+      <c r="E158" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="F158" s="17" t="s">
+      <c r="F158" s="16" t="s">
         <v>183</v>
       </c>
       <c r="G158" s="1"/>
@@ -5409,13 +5426,13 @@
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
-      <c r="D159" s="17">
+      <c r="D159" s="16">
         <v>123</v>
       </c>
-      <c r="E159" s="24" t="s">
+      <c r="E159" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="F159" s="17" t="s">
+      <c r="F159" s="16" t="s">
         <v>184</v>
       </c>
       <c r="G159" s="1"/>
@@ -5433,13 +5450,13 @@
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
-      <c r="D160" s="17">
+      <c r="D160" s="16">
         <v>124</v>
       </c>
-      <c r="E160" s="17" t="s">
+      <c r="E160" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="F160" s="17" t="s">
+      <c r="F160" s="16" t="s">
         <v>185</v>
       </c>
       <c r="G160" s="1"/>
@@ -5457,13 +5474,13 @@
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
-      <c r="D161" s="17">
+      <c r="D161" s="16">
         <v>125</v>
       </c>
-      <c r="E161" s="17" t="s">
+      <c r="E161" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="F161" s="17" t="s">
+      <c r="F161" s="16" t="s">
         <v>186</v>
       </c>
       <c r="G161" s="1"/>
@@ -5481,13 +5498,13 @@
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
-      <c r="D162" s="17">
+      <c r="D162" s="16">
         <v>126</v>
       </c>
-      <c r="E162" s="17" t="s">
+      <c r="E162" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="F162" s="17" t="s">
+      <c r="F162" s="16" t="s">
         <v>187</v>
       </c>
       <c r="G162" s="1"/>
@@ -5505,13 +5522,13 @@
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
-      <c r="D163" s="17">
+      <c r="D163" s="16">
         <v>127</v>
       </c>
-      <c r="E163" s="17" t="s">
+      <c r="E163" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F163" s="17" t="s">
+      <c r="F163" s="16" t="s">
         <v>188</v>
       </c>
       <c r="G163" s="1"/>
@@ -5529,13 +5546,13 @@
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
-      <c r="D164" s="17">
+      <c r="D164" s="16">
         <v>128</v>
       </c>
-      <c r="E164" s="17" t="s">
+      <c r="E164" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F164" s="17" t="s">
+      <c r="F164" s="16" t="s">
         <v>189</v>
       </c>
       <c r="G164" s="1"/>
@@ -5553,13 +5570,13 @@
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
-      <c r="D165" s="17">
+      <c r="D165" s="16">
         <v>129</v>
       </c>
-      <c r="E165" s="17" t="s">
+      <c r="E165" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F165" s="17" t="s">
+      <c r="F165" s="16" t="s">
         <v>190</v>
       </c>
       <c r="G165" s="1"/>
@@ -5577,13 +5594,13 @@
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
-      <c r="D166" s="17">
+      <c r="D166" s="16">
         <v>130</v>
       </c>
-      <c r="E166" s="17" t="s">
+      <c r="E166" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="F166" s="17" t="s">
+      <c r="F166" s="16" t="s">
         <v>191</v>
       </c>
       <c r="G166" s="1"/>
@@ -5601,13 +5618,13 @@
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
-      <c r="D167" s="17">
+      <c r="D167" s="16">
         <v>131</v>
       </c>
-      <c r="E167" s="17" t="s">
+      <c r="E167" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="F167" s="17" t="s">
+      <c r="F167" s="16" t="s">
         <v>192</v>
       </c>
       <c r="G167" s="1"/>
@@ -5625,13 +5642,13 @@
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
-      <c r="D168" s="17">
+      <c r="D168" s="16">
         <v>132</v>
       </c>
-      <c r="E168" s="17" t="s">
+      <c r="E168" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F168" s="17" t="s">
+      <c r="F168" s="16" t="s">
         <v>193</v>
       </c>
       <c r="G168" s="1"/>
@@ -5649,13 +5666,13 @@
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
-      <c r="D169" s="17">
+      <c r="D169" s="16">
         <v>133</v>
       </c>
-      <c r="E169" s="17" t="s">
+      <c r="E169" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F169" s="17" t="s">
+      <c r="F169" s="16" t="s">
         <v>194</v>
       </c>
       <c r="G169" s="1"/>
@@ -5673,13 +5690,13 @@
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
-      <c r="D170" s="17">
+      <c r="D170" s="16">
         <v>134</v>
       </c>
-      <c r="E170" s="17" t="s">
+      <c r="E170" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F170" s="17" t="s">
+      <c r="F170" s="16" t="s">
         <v>195</v>
       </c>
       <c r="G170" s="1"/>
@@ -5697,13 +5714,13 @@
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
-      <c r="D171" s="17">
+      <c r="D171" s="16">
         <v>135</v>
       </c>
-      <c r="E171" s="17" t="s">
+      <c r="E171" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F171" s="17" t="s">
+      <c r="F171" s="16" t="s">
         <v>196</v>
       </c>
       <c r="G171" s="1"/>
@@ -5721,13 +5738,13 @@
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
-      <c r="D172" s="17">
+      <c r="D172" s="16">
         <v>136</v>
       </c>
-      <c r="E172" s="17" t="s">
+      <c r="E172" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="F172" s="17" t="s">
+      <c r="F172" s="16" t="s">
         <v>197</v>
       </c>
       <c r="G172" s="1"/>
@@ -5745,13 +5762,13 @@
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
-      <c r="D173" s="17">
+      <c r="D173" s="16">
         <v>137</v>
       </c>
-      <c r="E173" s="17" t="s">
+      <c r="E173" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F173" s="17" t="s">
+      <c r="F173" s="16" t="s">
         <v>198</v>
       </c>
       <c r="G173" s="1"/>
@@ -5769,13 +5786,13 @@
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
-      <c r="D174" s="17">
+      <c r="D174" s="16">
         <v>138</v>
       </c>
-      <c r="E174" s="17" t="s">
+      <c r="E174" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F174" s="17" t="s">
+      <c r="F174" s="16" t="s">
         <v>199</v>
       </c>
       <c r="G174" s="1"/>
@@ -5793,13 +5810,13 @@
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
-      <c r="D175" s="17">
+      <c r="D175" s="16">
         <v>139</v>
       </c>
-      <c r="E175" s="17" t="s">
+      <c r="E175" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="F175" s="17" t="s">
+      <c r="F175" s="16" t="s">
         <v>200</v>
       </c>
       <c r="G175" s="1"/>
@@ -5817,13 +5834,13 @@
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
-      <c r="D176" s="17">
+      <c r="D176" s="16">
         <v>140</v>
       </c>
-      <c r="E176" s="17" t="s">
+      <c r="E176" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F176" s="17" t="s">
+      <c r="F176" s="16" t="s">
         <v>201</v>
       </c>
       <c r="G176" s="1"/>
@@ -5841,13 +5858,13 @@
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
-      <c r="D177" s="17">
+      <c r="D177" s="16">
         <v>141</v>
       </c>
-      <c r="E177" s="17" t="s">
+      <c r="E177" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F177" s="17" t="s">
+      <c r="F177" s="16" t="s">
         <v>202</v>
       </c>
       <c r="G177" s="1"/>
@@ -5865,13 +5882,13 @@
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
-      <c r="D178" s="17">
+      <c r="D178" s="16">
         <v>142</v>
       </c>
-      <c r="E178" s="17" t="s">
+      <c r="E178" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="F178" s="17" t="s">
+      <c r="F178" s="16" t="s">
         <v>203</v>
       </c>
       <c r="G178" s="1"/>
@@ -5889,16 +5906,16 @@
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
-      <c r="D179" s="17">
+      <c r="D179" s="16">
         <v>143</v>
       </c>
-      <c r="E179" s="17" t="s">
+      <c r="E179" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F179" s="17" t="s">
+      <c r="F179" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="G179" s="23"/>
+      <c r="G179" s="22"/>
       <c r="H179" s="1"/>
       <c r="I179" s="1"/>
       <c r="J179" s="2"/>
@@ -5913,13 +5930,13 @@
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
-      <c r="D180" s="17">
+      <c r="D180" s="16">
         <v>144</v>
       </c>
-      <c r="E180" s="17" t="s">
+      <c r="E180" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F180" s="17" t="s">
+      <c r="F180" s="16" t="s">
         <v>205</v>
       </c>
       <c r="G180" s="1"/>
@@ -5937,13 +5954,13 @@
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
-      <c r="D181" s="17">
+      <c r="D181" s="16">
         <v>145</v>
       </c>
-      <c r="E181" s="17" t="s">
+      <c r="E181" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F181" s="17" t="s">
+      <c r="F181" s="16" t="s">
         <v>206</v>
       </c>
       <c r="G181" s="1"/>
@@ -5961,13 +5978,13 @@
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
-      <c r="D182" s="17">
+      <c r="D182" s="16">
         <v>146</v>
       </c>
-      <c r="E182" s="17" t="s">
+      <c r="E182" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F182" s="17" t="s">
+      <c r="F182" s="16" t="s">
         <v>207</v>
       </c>
       <c r="G182" s="1"/>
@@ -5985,13 +6002,13 @@
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
-      <c r="D183" s="17">
+      <c r="D183" s="16">
         <v>147</v>
       </c>
-      <c r="E183" s="17" t="s">
+      <c r="E183" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F183" s="17" t="s">
+      <c r="F183" s="16" t="s">
         <v>208</v>
       </c>
       <c r="G183" s="1"/>
@@ -6009,13 +6026,13 @@
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
-      <c r="D184" s="17">
+      <c r="D184" s="16">
         <v>148</v>
       </c>
-      <c r="E184" s="17" t="s">
+      <c r="E184" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F184" s="17" t="s">
+      <c r="F184" s="16" t="s">
         <v>209</v>
       </c>
       <c r="G184" s="1"/>
@@ -6033,13 +6050,13 @@
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
-      <c r="D185" s="17">
+      <c r="D185" s="16">
         <v>149</v>
       </c>
-      <c r="E185" s="17" t="s">
+      <c r="E185" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="F185" s="17" t="s">
+      <c r="F185" s="16" t="s">
         <v>210</v>
       </c>
       <c r="G185" s="1"/>
@@ -6057,13 +6074,13 @@
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
-      <c r="D186" s="17">
+      <c r="D186" s="16">
         <v>150</v>
       </c>
-      <c r="E186" s="17" t="s">
+      <c r="E186" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F186" s="17" t="s">
+      <c r="F186" s="16" t="s">
         <v>211</v>
       </c>
       <c r="G186" s="1"/>
@@ -6081,13 +6098,13 @@
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
-      <c r="D187" s="17">
+      <c r="D187" s="16">
         <v>151</v>
       </c>
-      <c r="E187" s="17" t="s">
+      <c r="E187" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F187" s="17" t="s">
+      <c r="F187" s="16" t="s">
         <v>212</v>
       </c>
       <c r="G187" s="1"/>
@@ -6105,13 +6122,13 @@
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
-      <c r="D188" s="17">
+      <c r="D188" s="16">
         <v>152</v>
       </c>
-      <c r="E188" s="17" t="s">
+      <c r="E188" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="F188" s="17" t="s">
+      <c r="F188" s="16" t="s">
         <v>213</v>
       </c>
       <c r="G188" s="1"/>
@@ -6129,16 +6146,16 @@
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
-      <c r="D189" s="17">
+      <c r="D189" s="16">
         <v>153</v>
       </c>
-      <c r="E189" s="17" t="s">
+      <c r="E189" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F189" s="17" t="s">
+      <c r="F189" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="G189" s="22"/>
+      <c r="G189" s="21"/>
       <c r="H189" s="1"/>
       <c r="I189" s="1"/>
       <c r="J189" s="2"/>
@@ -6153,13 +6170,13 @@
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
-      <c r="D190" s="17">
+      <c r="D190" s="16">
         <v>154</v>
       </c>
-      <c r="E190" s="17" t="s">
+      <c r="E190" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F190" s="17" t="s">
+      <c r="F190" s="16" t="s">
         <v>215</v>
       </c>
       <c r="G190" s="1"/>
@@ -6177,13 +6194,13 @@
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
-      <c r="D191" s="17">
+      <c r="D191" s="16">
         <v>155</v>
       </c>
-      <c r="E191" s="17" t="s">
+      <c r="E191" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F191" s="17" t="s">
+      <c r="F191" s="16" t="s">
         <v>216</v>
       </c>
       <c r="G191" s="1"/>
@@ -6201,16 +6218,16 @@
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
-      <c r="D192" s="17">
+      <c r="D192" s="16">
         <v>156</v>
       </c>
-      <c r="E192" s="17" t="s">
+      <c r="E192" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F192" s="17" t="s">
+      <c r="F192" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="G192" s="22"/>
+      <c r="G192" s="21"/>
       <c r="H192" s="1"/>
       <c r="I192" s="1"/>
       <c r="J192" s="2"/>
@@ -6225,13 +6242,13 @@
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
-      <c r="D193" s="17">
+      <c r="D193" s="16">
         <v>157</v>
       </c>
-      <c r="E193" s="17" t="s">
+      <c r="E193" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F193" s="17" t="s">
+      <c r="F193" s="16" t="s">
         <v>218</v>
       </c>
       <c r="G193" s="1"/>
@@ -6249,13 +6266,13 @@
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
-      <c r="D194" s="17">
+      <c r="D194" s="16">
         <v>158</v>
       </c>
-      <c r="E194" s="17" t="s">
+      <c r="E194" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F194" s="17" t="s">
+      <c r="F194" s="16" t="s">
         <v>219</v>
       </c>
       <c r="G194" s="1"/>
@@ -6273,13 +6290,13 @@
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
-      <c r="D195" s="17">
+      <c r="D195" s="16">
         <v>159</v>
       </c>
-      <c r="E195" s="17" t="s">
+      <c r="E195" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="F195" s="17" t="s">
+      <c r="F195" s="16" t="s">
         <v>220</v>
       </c>
       <c r="G195" s="1"/>
@@ -6297,13 +6314,13 @@
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
-      <c r="D196" s="17">
+      <c r="D196" s="16">
         <v>160</v>
       </c>
-      <c r="E196" s="17" t="s">
+      <c r="E196" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F196" s="17" t="s">
+      <c r="F196" s="16" t="s">
         <v>221</v>
       </c>
       <c r="G196" s="1"/>
@@ -6321,13 +6338,13 @@
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
-      <c r="D197" s="17">
+      <c r="D197" s="16">
         <v>161</v>
       </c>
-      <c r="E197" s="17" t="s">
+      <c r="E197" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F197" s="17" t="s">
+      <c r="F197" s="16" t="s">
         <v>222</v>
       </c>
       <c r="G197" s="1"/>
@@ -6345,13 +6362,13 @@
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
-      <c r="D198" s="17">
+      <c r="D198" s="16">
         <v>162</v>
       </c>
-      <c r="E198" s="17" t="s">
+      <c r="E198" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="F198" s="17" t="s">
+      <c r="F198" s="16" t="s">
         <v>223</v>
       </c>
       <c r="G198" s="1"/>
@@ -6369,16 +6386,16 @@
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
-      <c r="D199" s="17">
+      <c r="D199" s="16">
         <v>163</v>
       </c>
-      <c r="E199" s="17" t="s">
+      <c r="E199" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F199" s="17" t="s">
+      <c r="F199" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="G199" s="23"/>
+      <c r="G199" s="22"/>
       <c r="H199" s="1"/>
       <c r="I199" s="1"/>
       <c r="J199" s="2"/>
@@ -6393,13 +6410,13 @@
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
-      <c r="D200" s="17">
+      <c r="D200" s="16">
         <v>164</v>
       </c>
-      <c r="E200" s="17" t="s">
+      <c r="E200" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F200" s="17" t="s">
+      <c r="F200" s="16" t="s">
         <v>225</v>
       </c>
       <c r="G200" s="1"/>
@@ -6417,13 +6434,13 @@
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
-      <c r="D201" s="17">
+      <c r="D201" s="16">
         <v>165</v>
       </c>
-      <c r="E201" s="17" t="s">
+      <c r="E201" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F201" s="17" t="s">
+      <c r="F201" s="16" t="s">
         <v>226</v>
       </c>
       <c r="G201" s="1"/>
@@ -6441,13 +6458,13 @@
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
-      <c r="D202" s="17">
+      <c r="D202" s="16">
         <v>166</v>
       </c>
-      <c r="E202" s="17" t="s">
+      <c r="E202" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F202" s="17" t="s">
+      <c r="F202" s="16" t="s">
         <v>227</v>
       </c>
       <c r="G202" s="1"/>
@@ -6465,13 +6482,13 @@
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
-      <c r="D203" s="17">
+      <c r="D203" s="16">
         <v>167</v>
       </c>
-      <c r="E203" s="17" t="s">
+      <c r="E203" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F203" s="17" t="s">
+      <c r="F203" s="16" t="s">
         <v>228</v>
       </c>
       <c r="G203" s="1"/>
@@ -6489,13 +6506,13 @@
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
-      <c r="D204" s="17">
+      <c r="D204" s="16">
         <v>168</v>
       </c>
-      <c r="E204" s="17" t="s">
+      <c r="E204" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="F204" s="17" t="s">
+      <c r="F204" s="16" t="s">
         <v>229</v>
       </c>
       <c r="G204" s="1"/>
@@ -6513,13 +6530,13 @@
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
-      <c r="D205" s="17">
+      <c r="D205" s="16">
         <v>169</v>
       </c>
-      <c r="E205" s="17" t="s">
+      <c r="E205" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="F205" s="17" t="s">
+      <c r="F205" s="16" t="s">
         <v>230</v>
       </c>
       <c r="G205" s="1"/>
@@ -6537,13 +6554,13 @@
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
-      <c r="D206" s="17">
+      <c r="D206" s="16">
         <v>170</v>
       </c>
-      <c r="E206" s="17" t="s">
+      <c r="E206" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F206" s="17" t="s">
+      <c r="F206" s="16" t="s">
         <v>231</v>
       </c>
       <c r="G206" s="1"/>
@@ -6561,13 +6578,13 @@
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
-      <c r="D207" s="17">
+      <c r="D207" s="16">
         <v>171</v>
       </c>
-      <c r="E207" s="17" t="s">
+      <c r="E207" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F207" s="17" t="s">
+      <c r="F207" s="16" t="s">
         <v>232</v>
       </c>
       <c r="G207" s="1"/>
@@ -6585,13 +6602,13 @@
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
-      <c r="D208" s="17">
+      <c r="D208" s="16">
         <v>172</v>
       </c>
-      <c r="E208" s="17" t="s">
+      <c r="E208" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="F208" s="17" t="s">
+      <c r="F208" s="16" t="s">
         <v>233</v>
       </c>
       <c r="G208" s="1"/>
@@ -6609,13 +6626,13 @@
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
-      <c r="D209" s="17">
+      <c r="D209" s="16">
         <v>173</v>
       </c>
-      <c r="E209" s="17" t="s">
+      <c r="E209" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F209" s="17" t="s">
+      <c r="F209" s="16" t="s">
         <v>234</v>
       </c>
       <c r="G209" s="1"/>
@@ -6633,13 +6650,13 @@
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
-      <c r="D210" s="17">
+      <c r="D210" s="16">
         <v>174</v>
       </c>
-      <c r="E210" s="17" t="s">
+      <c r="E210" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F210" s="17" t="s">
+      <c r="F210" s="16" t="s">
         <v>235</v>
       </c>
       <c r="G210" s="1"/>
@@ -6657,13 +6674,13 @@
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
-      <c r="D211" s="17">
+      <c r="D211" s="16">
         <v>175</v>
       </c>
-      <c r="E211" s="17" t="s">
+      <c r="E211" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="F211" s="17" t="s">
+      <c r="F211" s="16" t="s">
         <v>236</v>
       </c>
       <c r="G211" s="1"/>
@@ -6681,16 +6698,16 @@
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
-      <c r="D212" s="17">
+      <c r="D212" s="16">
         <v>176</v>
       </c>
-      <c r="E212" s="17" t="s">
+      <c r="E212" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F212" s="17" t="s">
+      <c r="F212" s="16" t="s">
         <v>237</v>
       </c>
-      <c r="G212" s="23"/>
+      <c r="G212" s="22"/>
       <c r="H212" s="1"/>
       <c r="I212" s="1"/>
       <c r="J212" s="2"/>
@@ -6705,13 +6722,13 @@
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
-      <c r="D213" s="17">
+      <c r="D213" s="16">
         <v>177</v>
       </c>
-      <c r="E213" s="17" t="s">
+      <c r="E213" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F213" s="17" t="s">
+      <c r="F213" s="16" t="s">
         <v>238</v>
       </c>
       <c r="G213" s="1"/>
@@ -6729,13 +6746,13 @@
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
-      <c r="D214" s="17">
+      <c r="D214" s="16">
         <v>178</v>
       </c>
-      <c r="E214" s="17" t="s">
+      <c r="E214" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F214" s="17" t="s">
+      <c r="F214" s="16" t="s">
         <v>239</v>
       </c>
       <c r="G214" s="1"/>
@@ -6753,13 +6770,13 @@
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
-      <c r="D215" s="17">
+      <c r="D215" s="16">
         <v>179</v>
       </c>
-      <c r="E215" s="17" t="s">
+      <c r="E215" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F215" s="17" t="s">
+      <c r="F215" s="16" t="s">
         <v>240</v>
       </c>
       <c r="G215" s="1"/>
@@ -6777,13 +6794,13 @@
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
-      <c r="D216" s="17">
+      <c r="D216" s="16">
         <v>180</v>
       </c>
-      <c r="E216" s="17" t="s">
+      <c r="E216" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F216" s="17" t="s">
+      <c r="F216" s="16" t="s">
         <v>241</v>
       </c>
       <c r="G216" s="1"/>
@@ -6801,13 +6818,13 @@
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
-      <c r="D217" s="17">
+      <c r="D217" s="16">
         <v>181</v>
       </c>
-      <c r="E217" s="17" t="s">
+      <c r="E217" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="F217" s="17" t="s">
+      <c r="F217" s="16" t="s">
         <v>242</v>
       </c>
       <c r="G217" s="1"/>
@@ -6825,13 +6842,13 @@
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
-      <c r="D218" s="17">
+      <c r="D218" s="16">
         <v>182</v>
       </c>
-      <c r="E218" s="17" t="s">
+      <c r="E218" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="F218" s="17" t="s">
+      <c r="F218" s="16" t="s">
         <v>243</v>
       </c>
       <c r="G218" s="1"/>
@@ -6849,13 +6866,13 @@
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
-      <c r="D219" s="17">
+      <c r="D219" s="16">
         <v>183</v>
       </c>
-      <c r="E219" s="17" t="s">
+      <c r="E219" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="F219" s="17" t="s">
+      <c r="F219" s="16" t="s">
         <v>244</v>
       </c>
       <c r="G219" s="1"/>
@@ -6873,13 +6890,13 @@
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
-      <c r="D220" s="17">
+      <c r="D220" s="16">
         <v>184</v>
       </c>
-      <c r="E220" s="17" t="s">
+      <c r="E220" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="F220" s="17" t="s">
+      <c r="F220" s="16" t="s">
         <v>245</v>
       </c>
       <c r="G220" s="1"/>
@@ -6897,13 +6914,13 @@
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
-      <c r="D221" s="17">
+      <c r="D221" s="16">
         <v>185</v>
       </c>
-      <c r="E221" s="17" t="s">
+      <c r="E221" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="F221" s="17" t="s">
+      <c r="F221" s="16" t="s">
         <v>246</v>
       </c>
       <c r="G221" s="1"/>
@@ -6921,13 +6938,13 @@
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
       <c r="C222" s="2"/>
-      <c r="D222" s="17">
+      <c r="D222" s="16">
         <v>186</v>
       </c>
-      <c r="E222" s="17" t="s">
+      <c r="E222" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="F222" s="17" t="s">
+      <c r="F222" s="16" t="s">
         <v>247</v>
       </c>
       <c r="G222" s="1"/>
@@ -6945,13 +6962,13 @@
       <c r="A223" s="2"/>
       <c r="B223" s="2"/>
       <c r="C223" s="2"/>
-      <c r="D223" s="17">
+      <c r="D223" s="16">
         <v>187</v>
       </c>
-      <c r="E223" s="17" t="s">
+      <c r="E223" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="F223" s="17" t="s">
+      <c r="F223" s="16" t="s">
         <v>248</v>
       </c>
       <c r="G223" s="1"/>
@@ -6969,13 +6986,13 @@
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="2"/>
-      <c r="D224" s="17">
+      <c r="D224" s="16">
         <v>188</v>
       </c>
-      <c r="E224" s="17" t="s">
+      <c r="E224" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="F224" s="17" t="s">
+      <c r="F224" s="16" t="s">
         <v>249</v>
       </c>
       <c r="G224" s="1"/>
@@ -6993,13 +7010,13 @@
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
       <c r="C225" s="2"/>
-      <c r="D225" s="17">
+      <c r="D225" s="16">
         <v>189</v>
       </c>
-      <c r="E225" s="17" t="s">
+      <c r="E225" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="F225" s="17" t="s">
+      <c r="F225" s="16" t="s">
         <v>250</v>
       </c>
       <c r="G225" s="1"/>
@@ -7017,13 +7034,13 @@
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
-      <c r="D226" s="17">
+      <c r="D226" s="16">
         <v>190</v>
       </c>
-      <c r="E226" s="17" t="s">
+      <c r="E226" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="F226" s="17" t="s">
+      <c r="F226" s="16" t="s">
         <v>251</v>
       </c>
       <c r="G226" s="1"/>
@@ -7041,13 +7058,13 @@
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
-      <c r="D227" s="17">
+      <c r="D227" s="16">
         <v>191</v>
       </c>
-      <c r="E227" s="17" t="s">
+      <c r="E227" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="F227" s="17" t="s">
+      <c r="F227" s="16" t="s">
         <v>252</v>
       </c>
       <c r="G227" s="1"/>
@@ -7065,13 +7082,13 @@
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="2"/>
-      <c r="D228" s="17">
+      <c r="D228" s="16">
         <v>192</v>
       </c>
-      <c r="E228" s="17" t="s">
+      <c r="E228" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="F228" s="17" t="s">
+      <c r="F228" s="16" t="s">
         <v>253</v>
       </c>
       <c r="G228" s="1"/>
@@ -7089,13 +7106,13 @@
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
-      <c r="D229" s="17">
+      <c r="D229" s="16">
         <v>193</v>
       </c>
-      <c r="E229" s="17" t="s">
+      <c r="E229" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="F229" s="17" t="s">
+      <c r="F229" s="16" t="s">
         <v>254</v>
       </c>
       <c r="G229" s="1"/>
@@ -7113,13 +7130,13 @@
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
-      <c r="D230" s="17">
+      <c r="D230" s="16">
         <v>194</v>
       </c>
-      <c r="E230" s="17" t="s">
+      <c r="E230" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F230" s="17" t="s">
+      <c r="F230" s="16" t="s">
         <v>255</v>
       </c>
       <c r="G230" s="1"/>
@@ -7134,25 +7151,25 @@
       <c r="P230" s="1"/>
     </row>
     <row r="231" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B231" s="13" t="s">
+      <c r="B231" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C231" s="13" t="s">
+      <c r="C231" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="D231" s="13"/>
-      <c r="E231" s="13"/>
-      <c r="F231" s="13"/>
-      <c r="G231" s="13"/>
-      <c r="H231" s="13"/>
-      <c r="I231" s="13"/>
-      <c r="J231" s="13"/>
-      <c r="K231" s="13"/>
-      <c r="L231" s="13"/>
-      <c r="M231" s="13"/>
-      <c r="N231" s="13"/>
-      <c r="O231" s="13"/>
-      <c r="P231" s="13"/>
+      <c r="D231" s="12"/>
+      <c r="E231" s="12"/>
+      <c r="F231" s="12"/>
+      <c r="G231" s="12"/>
+      <c r="H231" s="12"/>
+      <c r="I231" s="12"/>
+      <c r="J231" s="12"/>
+      <c r="K231" s="12"/>
+      <c r="L231" s="12"/>
+      <c r="M231" s="12"/>
+      <c r="N231" s="12"/>
+      <c r="O231" s="12"/>
+      <c r="P231" s="12"/>
     </row>
     <row r="232" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B232" s="2" t="s">
@@ -7161,7 +7178,7 @@
       <c r="C232" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D232" s="16"/>
+      <c r="D232" s="15"/>
       <c r="E232" s="1"/>
       <c r="F232" s="1" t="s">
         <v>46</v>
@@ -7175,13 +7192,13 @@
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="2"/>
-      <c r="D233" s="16">
+      <c r="D233" s="15">
         <v>1</v>
       </c>
-      <c r="E233" s="17" t="s">
+      <c r="E233" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F233" s="17" t="s">
+      <c r="F233" s="16" t="s">
         <v>256</v>
       </c>
       <c r="G233" s="1"/>
@@ -7199,16 +7216,16 @@
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
-      <c r="D234" s="16">
+      <c r="D234" s="15">
         <v>2</v>
       </c>
-      <c r="E234" s="25" t="s">
+      <c r="E234" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="F234" s="25" t="s">
+      <c r="F234" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="G234" s="26"/>
+      <c r="G234" s="25"/>
       <c r="H234" s="1"/>
       <c r="I234" s="1"/>
       <c r="J234" s="2"/>
@@ -7223,13 +7240,13 @@
       <c r="A235" s="2"/>
       <c r="B235" s="2"/>
       <c r="C235" s="2"/>
-      <c r="D235" s="16">
+      <c r="D235" s="15">
         <v>3</v>
       </c>
-      <c r="E235" s="25" t="s">
+      <c r="E235" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="F235" s="25" t="s">
+      <c r="F235" s="24" t="s">
         <v>257</v>
       </c>
       <c r="G235" s="1"/>
@@ -7247,13 +7264,13 @@
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
       <c r="C236" s="2"/>
-      <c r="D236" s="16">
+      <c r="D236" s="15">
         <v>4</v>
       </c>
-      <c r="E236" s="17" t="s">
+      <c r="E236" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F236" s="17" t="s">
+      <c r="F236" s="16" t="s">
         <v>258</v>
       </c>
       <c r="G236" s="1"/>
@@ -7267,41 +7284,41 @@
       <c r="O236" s="2"/>
       <c r="P236" s="1"/>
     </row>
-    <row r="237" spans="1:16" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A237" s="21"/>
-      <c r="B237" s="21"/>
-      <c r="C237" s="21"/>
-      <c r="D237" s="16">
+    <row r="237" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A237" s="20"/>
+      <c r="B237" s="20"/>
+      <c r="C237" s="20"/>
+      <c r="D237" s="15">
         <v>5</v>
       </c>
-      <c r="E237" s="17" t="s">
+      <c r="E237" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F237" s="17" t="s">
+      <c r="F237" s="16" t="s">
         <v>259</v>
       </c>
-      <c r="G237" s="22"/>
-      <c r="H237" s="27"/>
-      <c r="I237" s="27"/>
-      <c r="J237" s="21"/>
-      <c r="K237" s="21"/>
-      <c r="L237" s="21"/>
-      <c r="M237" s="21"/>
-      <c r="N237" s="21"/>
-      <c r="O237" s="21"/>
-      <c r="P237" s="27"/>
+      <c r="G237" s="21"/>
+      <c r="H237" s="26"/>
+      <c r="I237" s="26"/>
+      <c r="J237" s="20"/>
+      <c r="K237" s="20"/>
+      <c r="L237" s="20"/>
+      <c r="M237" s="20"/>
+      <c r="N237" s="20"/>
+      <c r="O237" s="20"/>
+      <c r="P237" s="26"/>
     </row>
     <row r="238" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="2"/>
-      <c r="D238" s="16">
+      <c r="D238" s="15">
         <v>6</v>
       </c>
-      <c r="E238" s="17" t="s">
+      <c r="E238" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="F238" s="17" t="s">
+      <c r="F238" s="16" t="s">
         <v>260</v>
       </c>
       <c r="G238" s="1"/>
@@ -7319,16 +7336,16 @@
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
       <c r="C239" s="2"/>
-      <c r="D239" s="16">
+      <c r="D239" s="15">
         <v>7</v>
       </c>
-      <c r="E239" s="17" t="s">
+      <c r="E239" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F239" s="17" t="s">
+      <c r="F239" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="G239" s="22"/>
+      <c r="G239" s="21"/>
       <c r="H239" s="1"/>
       <c r="I239" s="1"/>
       <c r="J239" s="2"/>
@@ -7339,11 +7356,11 @@
       <c r="O239" s="2"/>
       <c r="P239" s="1"/>
     </row>
-    <row r="240" spans="1:16" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A240" s="21"/>
-      <c r="B240" s="21"/>
-      <c r="C240" s="21"/>
-      <c r="D240" s="16">
+    <row r="240" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A240" s="20"/>
+      <c r="B240" s="20"/>
+      <c r="C240" s="20"/>
+      <c r="D240" s="15">
         <v>8</v>
       </c>
       <c r="E240" s="4" t="s">
@@ -7352,22 +7369,22 @@
       <c r="F240" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="G240" s="26"/>
-      <c r="H240" s="27"/>
-      <c r="I240" s="27"/>
-      <c r="J240" s="21"/>
-      <c r="K240" s="21"/>
-      <c r="L240" s="21"/>
-      <c r="M240" s="21"/>
-      <c r="N240" s="21"/>
-      <c r="O240" s="21"/>
-      <c r="P240" s="27"/>
-    </row>
-    <row r="241" spans="1:16" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="21"/>
-      <c r="B241" s="21"/>
-      <c r="C241" s="21"/>
-      <c r="D241" s="16">
+      <c r="G240" s="25"/>
+      <c r="H240" s="26"/>
+      <c r="I240" s="26"/>
+      <c r="J240" s="20"/>
+      <c r="K240" s="20"/>
+      <c r="L240" s="20"/>
+      <c r="M240" s="20"/>
+      <c r="N240" s="20"/>
+      <c r="O240" s="20"/>
+      <c r="P240" s="26"/>
+    </row>
+    <row r="241" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A241" s="20"/>
+      <c r="B241" s="20"/>
+      <c r="C241" s="20"/>
+      <c r="D241" s="15">
         <v>9</v>
       </c>
       <c r="E241" s="4" t="s">
@@ -7376,22 +7393,22 @@
       <c r="F241" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="G241" s="26"/>
-      <c r="H241" s="27"/>
-      <c r="I241" s="27"/>
-      <c r="J241" s="21"/>
-      <c r="K241" s="21"/>
-      <c r="L241" s="21"/>
-      <c r="M241" s="21"/>
-      <c r="N241" s="21"/>
-      <c r="O241" s="21"/>
-      <c r="P241" s="27"/>
-    </row>
-    <row r="242" spans="1:16" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A242" s="21"/>
-      <c r="B242" s="21"/>
-      <c r="C242" s="21"/>
-      <c r="D242" s="16">
+      <c r="G241" s="25"/>
+      <c r="H241" s="26"/>
+      <c r="I241" s="26"/>
+      <c r="J241" s="20"/>
+      <c r="K241" s="20"/>
+      <c r="L241" s="20"/>
+      <c r="M241" s="20"/>
+      <c r="N241" s="20"/>
+      <c r="O241" s="20"/>
+      <c r="P241" s="26"/>
+    </row>
+    <row r="242" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A242" s="20"/>
+      <c r="B242" s="20"/>
+      <c r="C242" s="20"/>
+      <c r="D242" s="15">
         <v>10</v>
       </c>
       <c r="E242" s="4" t="s">
@@ -7400,31 +7417,31 @@
       <c r="F242" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="G242" s="26"/>
-      <c r="H242" s="27"/>
-      <c r="I242" s="27"/>
-      <c r="J242" s="21"/>
-      <c r="K242" s="21"/>
-      <c r="L242" s="21"/>
-      <c r="M242" s="21"/>
-      <c r="N242" s="21"/>
-      <c r="O242" s="21"/>
-      <c r="P242" s="27"/>
+      <c r="G242" s="25"/>
+      <c r="H242" s="26"/>
+      <c r="I242" s="26"/>
+      <c r="J242" s="20"/>
+      <c r="K242" s="20"/>
+      <c r="L242" s="20"/>
+      <c r="M242" s="20"/>
+      <c r="N242" s="20"/>
+      <c r="O242" s="20"/>
+      <c r="P242" s="26"/>
     </row>
     <row r="243" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="2"/>
-      <c r="D243" s="16">
+      <c r="D243" s="15">
         <v>11</v>
       </c>
-      <c r="E243" s="17" t="s">
+      <c r="E243" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F243" s="17" t="s">
+      <c r="F243" s="16" t="s">
         <v>264</v>
       </c>
-      <c r="G243" s="29"/>
+      <c r="G243" s="28"/>
       <c r="H243" s="1"/>
       <c r="I243" s="1"/>
       <c r="J243" s="2"/>
@@ -7439,13 +7456,13 @@
       <c r="A244" s="2"/>
       <c r="B244" s="2"/>
       <c r="C244" s="2"/>
-      <c r="D244" s="16">
+      <c r="D244" s="15">
         <v>12</v>
       </c>
-      <c r="E244" s="17" t="s">
+      <c r="E244" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F244" s="17" t="s">
+      <c r="F244" s="16" t="s">
         <v>265</v>
       </c>
       <c r="G244" s="1"/>
@@ -7463,13 +7480,13 @@
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
       <c r="C245" s="2"/>
-      <c r="D245" s="16">
+      <c r="D245" s="15">
         <v>13</v>
       </c>
-      <c r="E245" s="17" t="s">
+      <c r="E245" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F245" s="17" t="s">
+      <c r="F245" s="16" t="s">
         <v>266</v>
       </c>
       <c r="G245" s="1"/>
@@ -7487,16 +7504,16 @@
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="2"/>
-      <c r="D246" s="16">
+      <c r="D246" s="15">
         <v>14</v>
       </c>
-      <c r="E246" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="F246" s="17" t="s">
-        <v>267</v>
-      </c>
-      <c r="G246" s="1"/>
+      <c r="E246" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="F246" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="G246" s="25"/>
       <c r="H246" s="1"/>
       <c r="I246" s="1"/>
       <c r="J246" s="2"/>
@@ -7511,14 +7528,14 @@
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
       <c r="C247" s="2"/>
-      <c r="D247" s="16">
+      <c r="D247" s="15">
         <v>15</v>
       </c>
-      <c r="E247" s="17" t="s">
+      <c r="E247" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F247" s="17" t="s">
-        <v>268</v>
+      <c r="F247" s="16" t="s">
+        <v>267</v>
       </c>
       <c r="G247" s="1"/>
       <c r="H247" s="1"/>
@@ -7535,14 +7552,14 @@
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
       <c r="C248" s="2"/>
-      <c r="D248" s="16">
+      <c r="D248" s="15">
         <v>16</v>
       </c>
-      <c r="E248" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F248" s="17" t="s">
-        <v>269</v>
+      <c r="E248" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F248" s="16" t="s">
+        <v>268</v>
       </c>
       <c r="G248" s="1"/>
       <c r="H248" s="1"/>
@@ -7559,14 +7576,14 @@
       <c r="A249" s="2"/>
       <c r="B249" s="2"/>
       <c r="C249" s="2"/>
-      <c r="D249" s="16">
+      <c r="D249" s="15">
         <v>17</v>
       </c>
-      <c r="E249" s="17" t="s">
+      <c r="E249" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F249" s="17" t="s">
-        <v>270</v>
+      <c r="F249" s="16" t="s">
+        <v>269</v>
       </c>
       <c r="G249" s="1"/>
       <c r="H249" s="1"/>
@@ -7583,14 +7600,14 @@
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
       <c r="C250" s="2"/>
-      <c r="D250" s="16">
+      <c r="D250" s="15">
         <v>18</v>
       </c>
-      <c r="E250" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="F250" s="17" t="s">
-        <v>271</v>
+      <c r="E250" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F250" s="16" t="s">
+        <v>270</v>
       </c>
       <c r="G250" s="1"/>
       <c r="H250" s="1"/>
@@ -7603,66 +7620,66 @@
       <c r="O250" s="2"/>
       <c r="P250" s="1"/>
     </row>
-    <row r="251" spans="1:16" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A251" s="21"/>
-      <c r="B251" s="21"/>
-      <c r="C251" s="21"/>
-      <c r="D251" s="16">
+    <row r="251" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A251" s="2"/>
+      <c r="B251" s="2"/>
+      <c r="C251" s="2"/>
+      <c r="D251" s="15">
         <v>19</v>
       </c>
-      <c r="E251" s="25" t="s">
+      <c r="E251" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="F251" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="G251" s="1"/>
+      <c r="H251" s="1"/>
+      <c r="I251" s="1"/>
+      <c r="J251" s="2"/>
+      <c r="K251" s="2"/>
+      <c r="L251" s="2"/>
+      <c r="M251" s="2"/>
+      <c r="N251" s="2"/>
+      <c r="O251" s="2"/>
+      <c r="P251" s="1"/>
+    </row>
+    <row r="252" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A252" s="20"/>
+      <c r="B252" s="20"/>
+      <c r="C252" s="20"/>
+      <c r="D252" s="15">
+        <v>20</v>
+      </c>
+      <c r="E252" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F251" s="25" t="s">
+      <c r="F252" s="24" t="s">
         <v>272</v>
       </c>
-      <c r="G251" s="27"/>
-      <c r="H251" s="27"/>
-      <c r="I251" s="27"/>
-      <c r="J251" s="21"/>
-      <c r="K251" s="21"/>
-      <c r="L251" s="21"/>
-      <c r="M251" s="21"/>
-      <c r="N251" s="21"/>
-      <c r="O251" s="21"/>
-      <c r="P251" s="27"/>
-    </row>
-    <row r="252" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A252" s="2"/>
-      <c r="B252" s="2"/>
-      <c r="C252" s="2"/>
-      <c r="D252" s="16">
-        <v>20</v>
-      </c>
-      <c r="E252" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="F252" s="17" t="s">
-        <v>273</v>
-      </c>
-      <c r="G252" s="1"/>
-      <c r="H252" s="1"/>
-      <c r="I252" s="1"/>
-      <c r="J252" s="2"/>
-      <c r="K252" s="2"/>
-      <c r="L252" s="2"/>
-      <c r="M252" s="2"/>
-      <c r="N252" s="2"/>
-      <c r="O252" s="2"/>
-      <c r="P252" s="1"/>
+      <c r="G252" s="26"/>
+      <c r="H252" s="26"/>
+      <c r="I252" s="26"/>
+      <c r="J252" s="20"/>
+      <c r="K252" s="20"/>
+      <c r="L252" s="20"/>
+      <c r="M252" s="20"/>
+      <c r="N252" s="20"/>
+      <c r="O252" s="20"/>
+      <c r="P252" s="26"/>
     </row>
     <row r="253" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="2"/>
-      <c r="D253" s="16">
+      <c r="D253" s="15">
         <v>21</v>
       </c>
-      <c r="E253" s="17" t="s">
+      <c r="E253" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F253" s="17" t="s">
-        <v>274</v>
+      <c r="F253" s="16" t="s">
+        <v>273</v>
       </c>
       <c r="G253" s="1"/>
       <c r="H253" s="1"/>
@@ -7679,14 +7696,14 @@
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="2"/>
-      <c r="D254" s="16">
+      <c r="D254" s="15">
         <v>22</v>
       </c>
-      <c r="E254" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F254" s="17" t="s">
-        <v>275</v>
+      <c r="E254" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F254" s="16" t="s">
+        <v>274</v>
       </c>
       <c r="G254" s="1"/>
       <c r="H254" s="1"/>
@@ -7703,14 +7720,14 @@
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="2"/>
-      <c r="D255" s="16">
+      <c r="D255" s="15">
         <v>23</v>
       </c>
-      <c r="E255" s="17" t="s">
+      <c r="E255" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F255" s="17" t="s">
-        <v>276</v>
+      <c r="F255" s="16" t="s">
+        <v>275</v>
       </c>
       <c r="G255" s="1"/>
       <c r="H255" s="1"/>
@@ -7727,14 +7744,14 @@
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="2"/>
-      <c r="D256" s="16">
+      <c r="D256" s="15">
         <v>24</v>
       </c>
-      <c r="E256" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="F256" s="17" t="s">
-        <v>277</v>
+      <c r="E256" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F256" s="16" t="s">
+        <v>276</v>
       </c>
       <c r="G256" s="1"/>
       <c r="H256" s="1"/>
@@ -7751,14 +7768,14 @@
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="2"/>
-      <c r="D257" s="16">
+      <c r="D257" s="15">
         <v>25</v>
       </c>
-      <c r="E257" s="17" t="s">
+      <c r="E257" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F257" s="17" t="s">
-        <v>278</v>
+      <c r="F257" s="16" t="s">
+        <v>277</v>
       </c>
       <c r="G257" s="1"/>
       <c r="H257" s="1"/>
@@ -7775,14 +7792,14 @@
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="2"/>
-      <c r="D258" s="16">
+      <c r="D258" s="15">
         <v>26</v>
       </c>
-      <c r="E258" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F258" s="17" t="s">
-        <v>279</v>
+      <c r="E258" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F258" s="16" t="s">
+        <v>278</v>
       </c>
       <c r="G258" s="1"/>
       <c r="H258" s="1"/>
@@ -7799,14 +7816,14 @@
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
       <c r="C259" s="2"/>
-      <c r="D259" s="16">
+      <c r="D259" s="15">
         <v>27</v>
       </c>
-      <c r="E259" s="17" t="s">
+      <c r="E259" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F259" s="17" t="s">
-        <v>280</v>
+      <c r="F259" s="16" t="s">
+        <v>279</v>
       </c>
       <c r="G259" s="1"/>
       <c r="H259" s="1"/>
@@ -7823,14 +7840,14 @@
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
       <c r="C260" s="2"/>
-      <c r="D260" s="16">
+      <c r="D260" s="15">
         <v>28</v>
       </c>
-      <c r="E260" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="F260" s="17" t="s">
-        <v>281</v>
+      <c r="E260" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F260" s="16" t="s">
+        <v>280</v>
       </c>
       <c r="G260" s="1"/>
       <c r="H260" s="1"/>
@@ -7847,14 +7864,14 @@
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
       <c r="C261" s="2"/>
-      <c r="D261" s="16">
+      <c r="D261" s="15">
         <v>29</v>
       </c>
-      <c r="E261" s="17" t="s">
+      <c r="E261" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F261" s="17" t="s">
-        <v>282</v>
+      <c r="F261" s="16" t="s">
+        <v>281</v>
       </c>
       <c r="G261" s="1"/>
       <c r="H261" s="1"/>
@@ -7871,14 +7888,14 @@
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
       <c r="C262" s="2"/>
-      <c r="D262" s="16">
+      <c r="D262" s="15">
         <v>30</v>
       </c>
-      <c r="E262" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F262" s="17" t="s">
-        <v>283</v>
+      <c r="E262" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F262" s="16" t="s">
+        <v>282</v>
       </c>
       <c r="G262" s="1"/>
       <c r="H262" s="1"/>
@@ -7895,14 +7912,14 @@
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
       <c r="C263" s="2"/>
-      <c r="D263" s="16">
+      <c r="D263" s="15">
         <v>31</v>
       </c>
-      <c r="E263" s="17" t="s">
+      <c r="E263" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F263" s="17" t="s">
-        <v>284</v>
+      <c r="F263" s="16" t="s">
+        <v>283</v>
       </c>
       <c r="G263" s="1"/>
       <c r="H263" s="1"/>
@@ -7919,14 +7936,14 @@
       <c r="A264" s="2"/>
       <c r="B264" s="2"/>
       <c r="C264" s="2"/>
-      <c r="D264" s="16">
+      <c r="D264" s="15">
         <v>32</v>
       </c>
-      <c r="E264" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="F264" s="17" t="s">
-        <v>285</v>
+      <c r="E264" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F264" s="16" t="s">
+        <v>284</v>
       </c>
       <c r="G264" s="1"/>
       <c r="H264" s="1"/>
@@ -7943,14 +7960,14 @@
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
       <c r="C265" s="2"/>
-      <c r="D265" s="16">
+      <c r="D265" s="15">
         <v>33</v>
       </c>
-      <c r="E265" s="17" t="s">
+      <c r="E265" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F265" s="17" t="s">
-        <v>286</v>
+      <c r="F265" s="16" t="s">
+        <v>285</v>
       </c>
       <c r="G265" s="1"/>
       <c r="H265" s="1"/>
@@ -7967,14 +7984,14 @@
       <c r="A266" s="2"/>
       <c r="B266" s="2"/>
       <c r="C266" s="2"/>
-      <c r="D266" s="16">
+      <c r="D266" s="15">
         <v>34</v>
       </c>
-      <c r="E266" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F266" s="17" t="s">
-        <v>287</v>
+      <c r="E266" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F266" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="G266" s="1"/>
       <c r="H266" s="1"/>
@@ -7991,14 +8008,14 @@
       <c r="A267" s="2"/>
       <c r="B267" s="2"/>
       <c r="C267" s="2"/>
-      <c r="D267" s="16">
+      <c r="D267" s="15">
         <v>35</v>
       </c>
-      <c r="E267" s="17" t="s">
+      <c r="E267" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F267" s="17" t="s">
-        <v>288</v>
+      <c r="F267" s="16" t="s">
+        <v>287</v>
       </c>
       <c r="G267" s="1"/>
       <c r="H267" s="1"/>
@@ -8015,14 +8032,14 @@
       <c r="A268" s="2"/>
       <c r="B268" s="2"/>
       <c r="C268" s="2"/>
-      <c r="D268" s="16">
+      <c r="D268" s="15">
         <v>36</v>
       </c>
-      <c r="E268" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="F268" s="17" t="s">
-        <v>289</v>
+      <c r="E268" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F268" s="16" t="s">
+        <v>288</v>
       </c>
       <c r="G268" s="1"/>
       <c r="H268" s="1"/>
@@ -8039,14 +8056,14 @@
       <c r="A269" s="2"/>
       <c r="B269" s="2"/>
       <c r="C269" s="2"/>
-      <c r="D269" s="16">
+      <c r="D269" s="15">
         <v>37</v>
       </c>
-      <c r="E269" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="F269" s="17" t="s">
-        <v>290</v>
+      <c r="E269" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="F269" s="4" t="s">
+        <v>320</v>
       </c>
       <c r="G269" s="1"/>
       <c r="H269" s="1"/>
@@ -8063,14 +8080,14 @@
       <c r="A270" s="2"/>
       <c r="B270" s="2"/>
       <c r="C270" s="2"/>
-      <c r="D270" s="16">
+      <c r="D270" s="15">
         <v>38</v>
       </c>
-      <c r="E270" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F270" s="17" t="s">
-        <v>291</v>
+      <c r="E270" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F270" s="16" t="s">
+        <v>289</v>
       </c>
       <c r="G270" s="1"/>
       <c r="H270" s="1"/>
@@ -8083,42 +8100,42 @@
       <c r="O270" s="2"/>
       <c r="P270" s="1"/>
     </row>
-    <row r="271" spans="1:16" s="33" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A271" s="30"/>
-      <c r="B271" s="30"/>
-      <c r="C271" s="30"/>
-      <c r="D271" s="16">
+    <row r="271" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A271" s="2"/>
+      <c r="B271" s="2"/>
+      <c r="C271" s="2"/>
+      <c r="D271" s="15">
         <v>39</v>
       </c>
-      <c r="E271" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="F271" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="G271" s="31"/>
-      <c r="H271" s="32"/>
-      <c r="I271" s="32"/>
-      <c r="J271" s="30"/>
-      <c r="K271" s="30"/>
-      <c r="L271" s="30"/>
-      <c r="M271" s="30"/>
-      <c r="N271" s="30"/>
-      <c r="O271" s="30"/>
-      <c r="P271" s="32"/>
+      <c r="E271" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F271" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="G271" s="1"/>
+      <c r="H271" s="1"/>
+      <c r="I271" s="1"/>
+      <c r="J271" s="2"/>
+      <c r="K271" s="2"/>
+      <c r="L271" s="2"/>
+      <c r="M271" s="2"/>
+      <c r="N271" s="2"/>
+      <c r="O271" s="2"/>
+      <c r="P271" s="1"/>
     </row>
     <row r="272" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2"/>
       <c r="B272" s="2"/>
       <c r="C272" s="2"/>
-      <c r="D272" s="16">
+      <c r="D272" s="15">
         <v>40</v>
       </c>
-      <c r="E272" s="17" t="s">
+      <c r="E272" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F272" s="17" t="s">
-        <v>293</v>
+      <c r="F272" s="16" t="s">
+        <v>291</v>
       </c>
       <c r="G272" s="1"/>
       <c r="H272" s="1"/>
@@ -8131,45 +8148,45 @@
       <c r="O272" s="2"/>
       <c r="P272" s="1"/>
     </row>
-    <row r="273" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="2"/>
-      <c r="B273" s="2"/>
-      <c r="C273" s="2"/>
-      <c r="D273" s="16">
+    <row r="273" spans="1:16" s="32" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A273" s="29"/>
+      <c r="B273" s="29"/>
+      <c r="C273" s="29"/>
+      <c r="D273" s="15">
         <v>41</v>
       </c>
-      <c r="E273" s="17" t="s">
+      <c r="E273" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="F273" s="17" t="s">
-        <v>294</v>
-      </c>
-      <c r="G273" s="1"/>
-      <c r="H273" s="1"/>
-      <c r="I273" s="1"/>
-      <c r="J273" s="2"/>
-      <c r="K273" s="2"/>
-      <c r="L273" s="2"/>
-      <c r="M273" s="2"/>
-      <c r="N273" s="2"/>
-      <c r="O273" s="2"/>
-      <c r="P273" s="1"/>
+      <c r="F273" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="G273" s="30"/>
+      <c r="H273" s="31"/>
+      <c r="I273" s="31"/>
+      <c r="J273" s="29"/>
+      <c r="K273" s="29"/>
+      <c r="L273" s="29"/>
+      <c r="M273" s="29"/>
+      <c r="N273" s="29"/>
+      <c r="O273" s="29"/>
+      <c r="P273" s="31"/>
     </row>
     <row r="274" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2"/>
       <c r="B274" s="2"/>
       <c r="C274" s="2"/>
-      <c r="D274" s="16">
+      <c r="D274" s="15">
         <v>42</v>
       </c>
-      <c r="E274" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="F274" s="17" t="s">
-        <v>295</v>
+      <c r="E274" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F274" s="16" t="s">
+        <v>293</v>
       </c>
       <c r="G274" s="1"/>
-      <c r="H274" s="34"/>
+      <c r="H274" s="1"/>
       <c r="I274" s="1"/>
       <c r="J274" s="2"/>
       <c r="K274" s="2"/>
@@ -8183,17 +8200,17 @@
       <c r="A275" s="2"/>
       <c r="B275" s="2"/>
       <c r="C275" s="2"/>
-      <c r="D275" s="16">
+      <c r="D275" s="15">
         <v>43</v>
       </c>
-      <c r="E275" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="F275" s="17" t="s">
-        <v>296</v>
+      <c r="E275" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F275" s="16" t="s">
+        <v>294</v>
       </c>
       <c r="G275" s="1"/>
-      <c r="H275" s="35"/>
+      <c r="H275" s="1"/>
       <c r="I275" s="1"/>
       <c r="J275" s="2"/>
       <c r="K275" s="2"/>
@@ -8207,17 +8224,17 @@
       <c r="A276" s="2"/>
       <c r="B276" s="2"/>
       <c r="C276" s="2"/>
-      <c r="D276" s="16">
+      <c r="D276" s="15">
         <v>44</v>
       </c>
-      <c r="E276" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F276" s="17" t="s">
-        <v>297</v>
+      <c r="E276" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F276" s="16" t="s">
+        <v>295</v>
       </c>
       <c r="G276" s="1"/>
-      <c r="H276" s="35"/>
+      <c r="H276" s="33"/>
       <c r="I276" s="1"/>
       <c r="J276" s="2"/>
       <c r="K276" s="2"/>
@@ -8231,17 +8248,17 @@
       <c r="A277" s="2"/>
       <c r="B277" s="2"/>
       <c r="C277" s="2"/>
-      <c r="D277" s="16">
+      <c r="D277" s="15">
         <v>45</v>
       </c>
-      <c r="E277" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F277" s="17" t="s">
-        <v>298</v>
+      <c r="E277" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F277" s="16" t="s">
+        <v>296</v>
       </c>
       <c r="G277" s="1"/>
-      <c r="H277" s="35"/>
+      <c r="H277" s="34"/>
       <c r="I277" s="1"/>
       <c r="J277" s="2"/>
       <c r="K277" s="2"/>
@@ -8255,17 +8272,17 @@
       <c r="A278" s="2"/>
       <c r="B278" s="2"/>
       <c r="C278" s="2"/>
-      <c r="D278" s="16">
+      <c r="D278" s="15">
         <v>46</v>
       </c>
-      <c r="E278" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="F278" s="17" t="s">
-        <v>299</v>
+      <c r="E278" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F278" s="16" t="s">
+        <v>297</v>
       </c>
       <c r="G278" s="1"/>
-      <c r="H278" s="35"/>
+      <c r="H278" s="34"/>
       <c r="I278" s="1"/>
       <c r="J278" s="2"/>
       <c r="K278" s="2"/>
@@ -8279,17 +8296,17 @@
       <c r="A279" s="2"/>
       <c r="B279" s="2"/>
       <c r="C279" s="2"/>
-      <c r="D279" s="16">
+      <c r="D279" s="15">
         <v>47</v>
       </c>
-      <c r="E279" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="F279" s="17" t="s">
-        <v>300</v>
+      <c r="E279" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F279" s="16" t="s">
+        <v>298</v>
       </c>
       <c r="G279" s="1"/>
-      <c r="H279" s="35"/>
+      <c r="H279" s="34"/>
       <c r="I279" s="1"/>
       <c r="J279" s="2"/>
       <c r="K279" s="2"/>
@@ -8303,17 +8320,17 @@
       <c r="A280" s="2"/>
       <c r="B280" s="2"/>
       <c r="C280" s="2"/>
-      <c r="D280" s="16">
+      <c r="D280" s="15">
         <v>48</v>
       </c>
-      <c r="E280" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F280" s="17" t="s">
-        <v>301</v>
+      <c r="E280" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F280" s="16" t="s">
+        <v>299</v>
       </c>
       <c r="G280" s="1"/>
-      <c r="H280" s="35"/>
+      <c r="H280" s="34"/>
       <c r="I280" s="1"/>
       <c r="J280" s="2"/>
       <c r="K280" s="2"/>
@@ -8323,45 +8340,45 @@
       <c r="O280" s="2"/>
       <c r="P280" s="1"/>
     </row>
-    <row r="281" spans="1:16" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A281" s="21"/>
-      <c r="B281" s="21"/>
-      <c r="C281" s="21"/>
-      <c r="D281" s="16">
+    <row r="281" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A281" s="2"/>
+      <c r="B281" s="2"/>
+      <c r="C281" s="2"/>
+      <c r="D281" s="15">
         <v>49</v>
       </c>
-      <c r="E281" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F281" s="36" t="s">
-        <v>302</v>
-      </c>
-      <c r="G281" s="26"/>
-      <c r="H281" s="37"/>
-      <c r="I281" s="27"/>
-      <c r="J281" s="21"/>
-      <c r="K281" s="21"/>
-      <c r="L281" s="21"/>
-      <c r="M281" s="21"/>
-      <c r="N281" s="21"/>
-      <c r="O281" s="21"/>
-      <c r="P281" s="27"/>
+      <c r="E281" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F281" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="G281" s="1"/>
+      <c r="H281" s="34"/>
+      <c r="I281" s="1"/>
+      <c r="J281" s="2"/>
+      <c r="K281" s="2"/>
+      <c r="L281" s="2"/>
+      <c r="M281" s="2"/>
+      <c r="N281" s="2"/>
+      <c r="O281" s="2"/>
+      <c r="P281" s="1"/>
     </row>
     <row r="282" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2"/>
       <c r="B282" s="2"/>
       <c r="C282" s="2"/>
-      <c r="D282" s="16">
+      <c r="D282" s="15">
         <v>50</v>
       </c>
-      <c r="E282" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="F282" s="38" t="s">
-        <v>303</v>
-      </c>
-      <c r="G282" s="22"/>
-      <c r="H282" s="35"/>
+      <c r="E282" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F282" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="G282" s="1"/>
+      <c r="H282" s="34"/>
       <c r="I282" s="1"/>
       <c r="J282" s="2"/>
       <c r="K282" s="2"/>
@@ -8371,45 +8388,45 @@
       <c r="O282" s="2"/>
       <c r="P282" s="1"/>
     </row>
-    <row r="283" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A283" s="2"/>
-      <c r="B283" s="2"/>
-      <c r="C283" s="2"/>
-      <c r="D283" s="16">
+    <row r="283" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A283" s="20"/>
+      <c r="B283" s="20"/>
+      <c r="C283" s="20"/>
+      <c r="D283" s="15">
         <v>51</v>
       </c>
-      <c r="E283" s="17" t="s">
+      <c r="E283" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F283" s="38" t="s">
-        <v>304</v>
-      </c>
-      <c r="G283" s="22"/>
-      <c r="H283" s="35"/>
-      <c r="I283" s="1"/>
-      <c r="J283" s="2"/>
-      <c r="K283" s="2"/>
-      <c r="L283" s="2"/>
-      <c r="M283" s="2"/>
-      <c r="N283" s="2"/>
-      <c r="O283" s="2"/>
-      <c r="P283" s="1"/>
+      <c r="F283" s="35" t="s">
+        <v>302</v>
+      </c>
+      <c r="G283" s="25"/>
+      <c r="H283" s="36"/>
+      <c r="I283" s="26"/>
+      <c r="J283" s="20"/>
+      <c r="K283" s="20"/>
+      <c r="L283" s="20"/>
+      <c r="M283" s="20"/>
+      <c r="N283" s="20"/>
+      <c r="O283" s="20"/>
+      <c r="P283" s="26"/>
     </row>
     <row r="284" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2"/>
       <c r="B284" s="2"/>
       <c r="C284" s="2"/>
-      <c r="D284" s="16">
+      <c r="D284" s="15">
         <v>52</v>
       </c>
-      <c r="E284" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F284" s="38" t="s">
-        <v>305</v>
-      </c>
-      <c r="G284" s="22"/>
-      <c r="H284" s="35"/>
+      <c r="E284" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="F284" s="37" t="s">
+        <v>303</v>
+      </c>
+      <c r="G284" s="21"/>
+      <c r="H284" s="34"/>
       <c r="I284" s="1"/>
       <c r="J284" s="2"/>
       <c r="K284" s="2"/>
@@ -8423,17 +8440,17 @@
       <c r="A285" s="2"/>
       <c r="B285" s="2"/>
       <c r="C285" s="2"/>
-      <c r="D285" s="16">
+      <c r="D285" s="15">
         <v>53</v>
       </c>
-      <c r="E285" s="17" t="s">
+      <c r="E285" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F285" s="38" t="s">
-        <v>306</v>
-      </c>
-      <c r="G285" s="22"/>
-      <c r="H285" s="35"/>
+      <c r="F285" s="37" t="s">
+        <v>304</v>
+      </c>
+      <c r="G285" s="21"/>
+      <c r="H285" s="34"/>
       <c r="I285" s="1"/>
       <c r="J285" s="2"/>
       <c r="K285" s="2"/>
@@ -8447,17 +8464,17 @@
       <c r="A286" s="2"/>
       <c r="B286" s="2"/>
       <c r="C286" s="2"/>
-      <c r="D286" s="16">
+      <c r="D286" s="15">
         <v>54</v>
       </c>
-      <c r="E286" s="17" t="s">
+      <c r="E286" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F286" s="38" t="s">
-        <v>307</v>
-      </c>
-      <c r="G286" s="22"/>
-      <c r="H286" s="35"/>
+      <c r="F286" s="37" t="s">
+        <v>305</v>
+      </c>
+      <c r="G286" s="21"/>
+      <c r="H286" s="34"/>
       <c r="I286" s="1"/>
       <c r="J286" s="2"/>
       <c r="K286" s="2"/>
@@ -8471,17 +8488,17 @@
       <c r="A287" s="2"/>
       <c r="B287" s="2"/>
       <c r="C287" s="2"/>
-      <c r="D287" s="16">
+      <c r="D287" s="15">
         <v>55</v>
       </c>
-      <c r="E287" s="17" t="s">
+      <c r="E287" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F287" s="38" t="s">
-        <v>308</v>
-      </c>
-      <c r="G287" s="22"/>
-      <c r="H287" s="35"/>
+      <c r="F287" s="37" t="s">
+        <v>306</v>
+      </c>
+      <c r="G287" s="21"/>
+      <c r="H287" s="34"/>
       <c r="I287" s="1"/>
       <c r="J287" s="2"/>
       <c r="K287" s="2"/>
@@ -8491,45 +8508,45 @@
       <c r="O287" s="2"/>
       <c r="P287" s="1"/>
     </row>
-    <row r="288" spans="1:16" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A288" s="21"/>
-      <c r="B288" s="21"/>
-      <c r="C288" s="21"/>
-      <c r="D288" s="16">
+    <row r="288" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A288" s="2"/>
+      <c r="B288" s="2"/>
+      <c r="C288" s="2"/>
+      <c r="D288" s="15">
         <v>56</v>
       </c>
-      <c r="E288" s="4" t="s">
+      <c r="E288" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F288" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="G288" s="26"/>
-      <c r="H288" s="37"/>
-      <c r="I288" s="27"/>
-      <c r="J288" s="21"/>
-      <c r="K288" s="21"/>
-      <c r="L288" s="21"/>
-      <c r="M288" s="21"/>
-      <c r="N288" s="21"/>
-      <c r="O288" s="21"/>
-      <c r="P288" s="27"/>
+      <c r="F288" s="37" t="s">
+        <v>307</v>
+      </c>
+      <c r="G288" s="21"/>
+      <c r="H288" s="34"/>
+      <c r="I288" s="1"/>
+      <c r="J288" s="2"/>
+      <c r="K288" s="2"/>
+      <c r="L288" s="2"/>
+      <c r="M288" s="2"/>
+      <c r="N288" s="2"/>
+      <c r="O288" s="2"/>
+      <c r="P288" s="1"/>
     </row>
     <row r="289" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2"/>
       <c r="B289" s="2"/>
       <c r="C289" s="2"/>
-      <c r="D289" s="16">
+      <c r="D289" s="15">
         <v>57</v>
       </c>
-      <c r="E289" s="17" t="s">
+      <c r="E289" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F289" s="17" t="s">
-        <v>310</v>
-      </c>
-      <c r="G289" s="1"/>
-      <c r="H289" s="35"/>
+      <c r="F289" s="37" t="s">
+        <v>308</v>
+      </c>
+      <c r="G289" s="21"/>
+      <c r="H289" s="34"/>
       <c r="I289" s="1"/>
       <c r="J289" s="2"/>
       <c r="K289" s="2"/>
@@ -8539,163 +8556,211 @@
       <c r="O289" s="2"/>
       <c r="P289" s="1"/>
     </row>
-    <row r="290" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A290" s="2"/>
-      <c r="B290" s="2"/>
-      <c r="C290" s="2"/>
-      <c r="D290" s="16">
+    <row r="290" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A290" s="20"/>
+      <c r="B290" s="20"/>
+      <c r="C290" s="20"/>
+      <c r="D290" s="15">
         <v>58</v>
       </c>
-      <c r="E290" s="17" t="s">
+      <c r="E290" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F290" s="17" t="s">
-        <v>311</v>
-      </c>
-      <c r="G290" s="22"/>
-      <c r="H290" s="35"/>
-      <c r="I290" s="1"/>
-      <c r="J290" s="2"/>
-      <c r="K290" s="2"/>
-      <c r="L290" s="2"/>
-      <c r="M290" s="2"/>
-      <c r="N290" s="2"/>
-      <c r="O290" s="2"/>
-      <c r="P290" s="1"/>
-    </row>
-    <row r="291" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B291" s="13" t="s">
+      <c r="F290" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G290" s="25"/>
+      <c r="H290" s="36"/>
+      <c r="I290" s="26"/>
+      <c r="J290" s="20"/>
+      <c r="K290" s="20"/>
+      <c r="L290" s="20"/>
+      <c r="M290" s="20"/>
+      <c r="N290" s="20"/>
+      <c r="O290" s="20"/>
+      <c r="P290" s="26"/>
+    </row>
+    <row r="291" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A291" s="2"/>
+      <c r="B291" s="2"/>
+      <c r="C291" s="2"/>
+      <c r="D291" s="15">
+        <v>59</v>
+      </c>
+      <c r="E291" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="F291" s="16" t="s">
+        <v>321</v>
+      </c>
+      <c r="G291" s="1"/>
+      <c r="H291" s="34"/>
+      <c r="I291" s="1"/>
+      <c r="J291" s="2"/>
+      <c r="K291" s="2"/>
+      <c r="L291" s="2"/>
+      <c r="M291" s="2"/>
+      <c r="N291" s="2"/>
+      <c r="O291" s="2"/>
+      <c r="P291" s="1"/>
+    </row>
+    <row r="292" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A292" s="2"/>
+      <c r="B292" s="2"/>
+      <c r="C292" s="2"/>
+      <c r="D292" s="15">
+        <v>60</v>
+      </c>
+      <c r="E292" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F292" s="16" t="s">
+        <v>310</v>
+      </c>
+      <c r="G292" s="21"/>
+      <c r="H292" s="34"/>
+      <c r="I292" s="1"/>
+      <c r="J292" s="2"/>
+      <c r="K292" s="2"/>
+      <c r="L292" s="2"/>
+      <c r="M292" s="2"/>
+      <c r="N292" s="2"/>
+      <c r="O292" s="2"/>
+      <c r="P292" s="1"/>
+    </row>
+    <row r="293" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B293" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C291" s="13" t="s">
+      <c r="C293" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="D291" s="13"/>
-      <c r="E291" s="13"/>
-      <c r="F291" s="39"/>
-      <c r="G291" s="13"/>
-      <c r="H291" s="40"/>
-      <c r="I291" s="13"/>
-      <c r="J291" s="13"/>
-      <c r="K291" s="13"/>
-      <c r="L291" s="13"/>
-      <c r="M291" s="13"/>
-      <c r="N291" s="13"/>
-      <c r="O291" s="13"/>
-      <c r="P291" s="13"/>
-    </row>
-    <row r="292" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D292" s="16"/>
-      <c r="E292" s="1"/>
-      <c r="F292" s="1"/>
-      <c r="G292" s="1"/>
-      <c r="H292" s="40"/>
-      <c r="I292" s="1"/>
-      <c r="P292" s="1"/>
-    </row>
-    <row r="293" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D293" s="16"/>
-      <c r="E293" s="1"/>
-      <c r="F293" s="1"/>
-      <c r="G293" s="1"/>
-      <c r="H293" s="40"/>
-      <c r="I293" s="1"/>
-      <c r="P293" s="1"/>
-    </row>
-    <row r="294" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B294" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C294" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D294" s="13"/>
-      <c r="E294" s="13"/>
-      <c r="G294" s="13"/>
-      <c r="H294" s="35"/>
-      <c r="I294" s="13"/>
-      <c r="J294" s="13"/>
-      <c r="K294" s="13"/>
-      <c r="L294" s="13"/>
-      <c r="M294" s="13"/>
-      <c r="N294" s="13"/>
-      <c r="O294" s="13"/>
-      <c r="P294" s="13"/>
+      <c r="D293" s="12"/>
+      <c r="E293" s="12"/>
+      <c r="F293" s="38"/>
+      <c r="G293" s="12"/>
+      <c r="H293" s="39"/>
+      <c r="I293" s="12"/>
+      <c r="J293" s="12"/>
+      <c r="K293" s="12"/>
+      <c r="L293" s="12"/>
+      <c r="M293" s="12"/>
+      <c r="N293" s="12"/>
+      <c r="O293" s="12"/>
+      <c r="P293" s="12"/>
+    </row>
+    <row r="294" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D294" s="15"/>
+      <c r="E294" s="1"/>
+      <c r="F294" s="1"/>
+      <c r="G294" s="1"/>
+      <c r="H294" s="39"/>
+      <c r="I294" s="1"/>
+      <c r="P294" s="1"/>
     </row>
     <row r="295" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D295" s="16"/>
+      <c r="D295" s="15"/>
       <c r="E295" s="1"/>
       <c r="F295" s="1"/>
       <c r="G295" s="1"/>
-      <c r="H295" s="35"/>
+      <c r="H295" s="39"/>
       <c r="I295" s="1"/>
       <c r="P295" s="1"/>
     </row>
-    <row r="296" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D296" s="16"/>
-      <c r="E296" s="1"/>
-      <c r="F296" s="1"/>
-      <c r="G296" s="1"/>
+    <row r="296" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B296" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C296" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D296" s="12"/>
+      <c r="E296" s="12"/>
+      <c r="G296" s="12"/>
       <c r="H296" s="34"/>
-      <c r="I296" s="1"/>
-      <c r="P296" s="1"/>
-    </row>
-    <row r="297" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B297" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C297" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D297" s="13"/>
-      <c r="E297" s="13"/>
-      <c r="F297" s="13"/>
-      <c r="G297" s="13"/>
-      <c r="H297" s="13"/>
-      <c r="I297" s="13"/>
-      <c r="J297" s="13"/>
-      <c r="K297" s="13"/>
-      <c r="L297" s="13"/>
-      <c r="M297" s="13"/>
-      <c r="N297" s="13"/>
-      <c r="O297" s="13"/>
-      <c r="P297" s="13"/>
+      <c r="I296" s="12"/>
+      <c r="J296" s="12"/>
+      <c r="K296" s="12"/>
+      <c r="L296" s="12"/>
+      <c r="M296" s="12"/>
+      <c r="N296" s="12"/>
+      <c r="O296" s="12"/>
+      <c r="P296" s="12"/>
+    </row>
+    <row r="297" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D297" s="15"/>
+      <c r="E297" s="1"/>
+      <c r="F297" s="1"/>
+      <c r="G297" s="1"/>
+      <c r="H297" s="34"/>
+      <c r="I297" s="1"/>
+      <c r="P297" s="1"/>
     </row>
     <row r="298" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D298" s="16"/>
+      <c r="D298" s="15"/>
       <c r="E298" s="1"/>
       <c r="F298" s="1"/>
       <c r="G298" s="1"/>
-      <c r="H298" s="1"/>
+      <c r="H298" s="33"/>
       <c r="I298" s="1"/>
       <c r="P298" s="1"/>
     </row>
-    <row r="299" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D299" s="16"/>
-      <c r="E299" s="1"/>
-      <c r="F299" s="1"/>
-      <c r="G299" s="1"/>
-      <c r="H299" s="1"/>
-      <c r="I299" s="1"/>
-      <c r="P299" s="1"/>
+    <row r="299" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B299" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C299" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D299" s="12"/>
+      <c r="E299" s="12"/>
+      <c r="F299" s="12"/>
+      <c r="G299" s="12"/>
+      <c r="H299" s="12"/>
+      <c r="I299" s="12"/>
+      <c r="J299" s="12"/>
+      <c r="K299" s="12"/>
+      <c r="L299" s="12"/>
+      <c r="M299" s="12"/>
+      <c r="N299" s="12"/>
+      <c r="O299" s="12"/>
+      <c r="P299" s="12"/>
     </row>
     <row r="300" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="F300" s="13"/>
+      <c r="D300" s="15"/>
+      <c r="E300" s="1"/>
+      <c r="F300" s="1"/>
+      <c r="G300" s="1"/>
+      <c r="H300" s="1"/>
+      <c r="I300" s="1"/>
+      <c r="P300" s="1"/>
     </row>
     <row r="301" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D301" s="15"/>
+      <c r="E301" s="1"/>
       <c r="F301" s="1"/>
+      <c r="G301" s="1"/>
+      <c r="H301" s="1"/>
+      <c r="I301" s="1"/>
+      <c r="P301" s="1"/>
     </row>
     <row r="302" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="F302" s="1"/>
+      <c r="F302" s="12"/>
     </row>
     <row r="303" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="F303" s="13"/>
+      <c r="F303" s="1"/>
     </row>
     <row r="304" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F304" s="1"/>
     </row>
     <row r="305" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F305" s="1"/>
+      <c r="F305" s="12"/>
+    </row>
+    <row r="306" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F306" s="1"/>
+    </row>
+    <row r="307" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F307" s="1"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatRows="0" insertRows="0" insertHyperlinks="0" deleteRows="0" sort="0" autoFilter="0"/>
@@ -8705,20 +8770,20 @@
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="9">
-    <dataValidation allowBlank="1" showInputMessage="1" sqref="C11 C14 C17 C20 C23 C26 C29 C32 C35 C231 C291 C294 C297" xr:uid="{5DA7423F-1D1C-4F75-8AE0-92D87965AC10}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Object Code value" error="The Object code value shall be:_x000a_VARIABLE_x000a_RECORD_x000a_ARRAY" sqref="C12:C13 C15:C16 C18:C19 C21:C22 C24:C25 C27:C28 C30:C31 C33:C34 C292:C293 C295:C296 C298:C310 C36:C230 C232:C290" xr:uid="{702A3A7B-BC29-40EC-81C7-6AA43C36CDFB}">
+    <dataValidation allowBlank="1" showInputMessage="1" sqref="C11 C14 C17 C20 C23 C26 C29 C32 C35 C231 C293 C296 C299" xr:uid="{5DA7423F-1D1C-4F75-8AE0-92D87965AC10}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Object Code value" error="The Object code value shall be:_x000a_VARIABLE_x000a_RECORD_x000a_ARRAY" sqref="C12:C13 C15:C16 C18:C19 C21:C22 C24:C25 C27:C28 C30:C31 C33:C34 C294:C295 C297:C298 C300:C312 C36:C230 C232:C292" xr:uid="{702A3A7B-BC29-40EC-81C7-6AA43C36CDFB}">
       <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Category" error="The value for the entry category shall be _x000a_M : (mandatory)_x000a_O : (optional) _x000a_C : (conditional)" sqref="J36 J12:J13 J15:J16 J18:J19 J21:J22 J24:J25 J27:J28 J30:J31 J33:J34 J292:J293 J295:J296 J298:J310 J40:J230 J232:J290" xr:uid="{123B347C-1D31-4802-ADF4-E512D1B26BF5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Category" error="The value for the entry category shall be _x000a_M : (mandatory)_x000a_O : (optional) _x000a_C : (conditional)" sqref="J36 J12:J13 J15:J16 J18:J19 J21:J22 J24:J25 J27:J28 J30:J31 J33:J34 J294:J295 J297:J298 J300:J312 J40:J230 J232:J292" xr:uid="{123B347C-1D31-4802-ADF4-E512D1B26BF5}">
       <formula1>"M,O,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Backup/Setting Flag" error="The entry flag shall be_x000a_B : (Backup)_x000a_S : (Setting)" sqref="K36 K12:K13 K15:K16 K18:K19 K21:K22 K24:K25 K27:K28 K30:K31 K33:K34 K292:K293 K295:K296 K298:K310 K40:K230 K232:K290" xr:uid="{F8545A4C-2A61-48E3-A0E1-A9DBE93A4389}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Backup/Setting Flag" error="The entry flag shall be_x000a_B : (Backup)_x000a_S : (Setting)" sqref="K36 K12:K13 K15:K16 K18:K19 K21:K22 K24:K25 K27:K28 K30:K31 K33:K34 K294:K295 K297:K298 K300:K312 K40:K230 K232:K292" xr:uid="{F8545A4C-2A61-48E3-A0E1-A9DBE93A4389}">
       <formula1>"B,S"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M36:O36 M12:O13 M18:O19 M24:O25 M30:O31 M295:O296 M15:O16 M21:O22 M27:O28 M33:O34 M292:O293 M298:O299 M40:O230 M232:O290" xr:uid="{FBDEAF93-3444-4530-B6BC-26E68F08C5ED}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M36:O36 M12:O13 M18:O19 M24:O25 M30:O31 M297:O298 M15:O16 M21:O22 M27:O28 M33:O34 M294:O295 M300:O301 M40:O230 M232:O292" xr:uid="{FBDEAF93-3444-4530-B6BC-26E68F08C5ED}">
       <formula1>"rx,tx"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C311:C1150" xr:uid="{DF92CF7D-AAE5-412D-9103-46A0E14DD1A7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C313:C1152" xr:uid="{DF92CF7D-AAE5-412D-9103-46A0E14DD1A7}">
       <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J37:J39" xr:uid="{426C70AC-64DA-4983-8043-0BFDAA70072A}">

--- a/ArmCoreV1_QSPI/SSCProject/lan9252_app.xlsx
+++ b/ArmCoreV1_QSPI/SSCProject/lan9252_app.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SI\project\RTM_ON_NEW\FW-ArmCore\ArmCoreV1_QSPI\SSCProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0985C63B-39BB-406F-9388-1F39211CE0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B91C03C-95EF-424A-8973-56DD2D50FF74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="33480" yWindow="4590" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-7730" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Profile" sheetId="11" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="324">
   <si>
     <t>Device Profile:</t>
   </si>
@@ -371,27 +371,7 @@
     <t>固件版本，"00.00.00.01"</t>
   </si>
   <si>
-    <t>UNSIGNED8</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>UNSIGNED16</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>UINT</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>OutU8_Reserved0</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>REAL</t>
-  </si>
-  <si>
-    <t>OutU8_fault_clear</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>InU8_BoardID</t>
@@ -449,18 +429,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>InB1_ON_DI_RTMON_CONTACTOR_FB</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>InB1_ON_DI_Emergency_Reserve</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>InB1_ON_DI_HVEN</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>InB1_ON_DI_BSM_NOT_READY</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -473,805 +441,755 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>BIT2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>InB2_ON_DI_reserve0</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>InB1_ON_DI_DI_GATING</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>BIT7</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>InB7_ON_DI_reserve1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>BIT4</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>InB4_ON_DO_reserve0</t>
+    <t>BOOLEAN</t>
+  </si>
+  <si>
+    <t>InU8_icm_fsm_state_current</t>
+  </si>
+  <si>
+    <t>InU8_icm_ctrl_mode_cur</t>
+  </si>
+  <si>
+    <t>UNSIGNED16</t>
+  </si>
+  <si>
+    <t>InU16_reserved4</t>
+  </si>
+  <si>
+    <t>InU8_icm_beam_id</t>
+  </si>
+  <si>
+    <t>InU8_reserved5</t>
+  </si>
+  <si>
+    <t>InU16_icm_radiation_index</t>
+  </si>
+  <si>
+    <t>InU32_icm_not_ready_event</t>
+  </si>
+  <si>
+    <t>InU32_icm_warning_interlock</t>
+  </si>
+  <si>
+    <t>InU32_icm_minor_interlock</t>
+  </si>
+  <si>
+    <t>InU32_icm_serious_interlock</t>
+  </si>
+  <si>
+    <t>InU8_bgm_fsm_state_current</t>
+  </si>
+  <si>
+    <t>InU8_bgm_ctrl_mode_cur</t>
+  </si>
+  <si>
+    <t>InU16_reserved6</t>
+  </si>
+  <si>
+    <t>InU8_bgm_beam_id</t>
+  </si>
+  <si>
+    <t>InU8_reserved7</t>
+  </si>
+  <si>
+    <t>InU16_bgm_radiation_index</t>
+  </si>
+  <si>
+    <t>InU32_bgm_not_ready_event</t>
+  </si>
+  <si>
+    <t>InU32_bgm_warning_interlock</t>
+  </si>
+  <si>
+    <t>InU32_bgm_minor_interlock</t>
+  </si>
+  <si>
+    <t>InU32_bgm_serious_interlock</t>
+  </si>
+  <si>
+    <t>InF_beam_on_time</t>
+  </si>
+  <si>
+    <t>InF_primary_dose_current</t>
+  </si>
+  <si>
+    <t>InF_primary_dose_rate_current</t>
+  </si>
+  <si>
+    <t>InU8_primary_dose_fsm_state</t>
+  </si>
+  <si>
+    <t>InU8_reserved8</t>
+  </si>
+  <si>
+    <t>InU32_primary_dose_interlock</t>
+  </si>
+  <si>
+    <t>InF_second_dose_current</t>
+  </si>
+  <si>
+    <t>InF_secondry_dose_rate_current</t>
+  </si>
+  <si>
+    <t>InU8_secondry_dose_fsm_rate</t>
+  </si>
+  <si>
+    <t>InU8_reserved9</t>
+  </si>
+  <si>
+    <t>InU32_secondry_dose_interlock</t>
+  </si>
+  <si>
+    <t>InU32_afc_interlock</t>
+  </si>
+  <si>
+    <t>InF_afc_position_current</t>
+  </si>
+  <si>
+    <t>InU8_qam_fsm_state_current</t>
+  </si>
+  <si>
+    <t>InU8_qam_ctrl_mode_cur</t>
+  </si>
+  <si>
+    <t>InU16_reserved10</t>
+  </si>
+  <si>
+    <t>InU8_qam_beam_id</t>
+  </si>
+  <si>
+    <t>InU8_reserved11</t>
+  </si>
+  <si>
+    <t>InU16_qam_radiation_index</t>
+  </si>
+  <si>
+    <t>InU32_qam_not_ready_event</t>
+  </si>
+  <si>
+    <t>InU32_qam_warning_interlock</t>
+  </si>
+  <si>
+    <t>InU32_qam_minor_interlock</t>
+  </si>
+  <si>
+    <t>InU32_qam_serious_interlock</t>
+  </si>
+  <si>
+    <t>InU8_rtm_off_fsm_state_current</t>
+  </si>
+  <si>
+    <t>InU8_rtm_off_ctrl_mode_cur</t>
+  </si>
+  <si>
+    <t>InU16_reserved12</t>
+  </si>
+  <si>
+    <t>InU8_rtm_off_beam_id</t>
+  </si>
+  <si>
+    <t>InU8_reserved13</t>
+  </si>
+  <si>
+    <t>InU16_rtm_off_radiation_index</t>
+  </si>
+  <si>
+    <t>InU32_rtm_off_not_ready_event</t>
+  </si>
+  <si>
+    <t>InU32_rtm_off_warning_interlock</t>
+  </si>
+  <si>
+    <t>InU32_rtm_off_minor_interlock</t>
+  </si>
+  <si>
+    <t>InU32_rtm_off_serious_interlock</t>
+  </si>
+  <si>
+    <t>InU8_gmm_fsm_state_current</t>
+  </si>
+  <si>
+    <t>InU8_gmm_ctrl_mode_cur</t>
+  </si>
+  <si>
+    <t>InU16_reserved14</t>
+  </si>
+  <si>
+    <t>InU8_gmm_beam_id</t>
+  </si>
+  <si>
+    <t>InU8_reserved15</t>
+  </si>
+  <si>
+    <t>InU16_gmm_radiation_index</t>
+  </si>
+  <si>
+    <t>InU32_gmm_not_ready_event</t>
+  </si>
+  <si>
+    <t>InU32_gmm_warning_interlock</t>
+  </si>
+  <si>
+    <t>InU32_gmm_minor_interlock</t>
+  </si>
+  <si>
+    <t>InU32_gmm_serious_interlock</t>
+  </si>
+  <si>
+    <t>InU32_gmm_move_status</t>
+  </si>
+  <si>
+    <t>InF_gmm_position_cur</t>
+  </si>
+  <si>
+    <t>InF_gmm_velocity_cur</t>
+  </si>
+  <si>
+    <t>InU8_psm_fsm_state_current</t>
+  </si>
+  <si>
+    <t>InU8_psm_ctrl_mode_cur</t>
+  </si>
+  <si>
+    <t>InU16_reserved16</t>
+  </si>
+  <si>
+    <t>InU8_psm_beam_id</t>
+  </si>
+  <si>
+    <t>InU8_reserved17</t>
+  </si>
+  <si>
+    <t>InU16_psm_radiation_index</t>
+  </si>
+  <si>
+    <t>InU32_psm_not_ready_event</t>
+  </si>
+  <si>
+    <t>InU32_psm_warning_interlock</t>
+  </si>
+  <si>
+    <t>InU32_psm_minor_interlock</t>
+  </si>
+  <si>
+    <t>InU32_psm_serious_interlock</t>
+  </si>
+  <si>
+    <t>InU32_psm_move_status</t>
+  </si>
+  <si>
+    <t>InF_psm_position_x_cur</t>
+  </si>
+  <si>
+    <t>InF_psm_position_y_cur</t>
+  </si>
+  <si>
+    <t>InF_psm_position_z_cur</t>
+  </si>
+  <si>
+    <t>InF_psm_position_x_r_cur</t>
+  </si>
+  <si>
+    <t>InF_psm_position_y_r_cur</t>
+  </si>
+  <si>
+    <t>InF_psm_position_z_r_cur</t>
+  </si>
+  <si>
+    <t>InF_psm_velocity_x_cur</t>
+  </si>
+  <si>
+    <t>InF_psm_velocity_y_cur</t>
+  </si>
+  <si>
+    <t>InF_psm_velocity_z_cur</t>
+  </si>
+  <si>
+    <t>InF_psm_velocity_x_r_cur</t>
+  </si>
+  <si>
+    <t>InF_psm_velocity_y_r_cur</t>
+  </si>
+  <si>
+    <t>InF_psm_velocity_z_r_cur</t>
+  </si>
+  <si>
+    <t>InU16_FkpButton</t>
+  </si>
+  <si>
+    <t>InU32_CpgButton</t>
+  </si>
+  <si>
+    <t>OutU8_BoardID</t>
+  </si>
+  <si>
+    <t>OutU32_FirmWareVersion</t>
+  </si>
+  <si>
+    <t>OutU8_beam_id</t>
+  </si>
+  <si>
+    <t>OutU8_state_sync</t>
+  </si>
+  <si>
+    <t>OutU16_radiation_index</t>
+  </si>
+  <si>
+    <t>OutU8_ethercat_Link_state</t>
+  </si>
+  <si>
+    <t>OutU8_rtm_on_require_state</t>
+  </si>
+  <si>
+    <t>OutU8_rtm_on_require_ctrl_mode</t>
+  </si>
+  <si>
+    <t>OutU32_rtm_on_interlock_override</t>
+  </si>
+  <si>
+    <t>OutU32_rtm_on_unready_override</t>
+  </si>
+  <si>
+    <t>OutU8_icm_require_state</t>
+  </si>
+  <si>
+    <t>OutU8_icm_require_ctrl_mode</t>
+  </si>
+  <si>
+    <t>OutU16_ct_status</t>
+  </si>
+  <si>
+    <t>OutF_gantry_velocity_prepare</t>
+  </si>
+  <si>
+    <t>OutU32_icm_interlock_override</t>
+  </si>
+  <si>
+    <t>OutU32_icm_unready_override</t>
+  </si>
+  <si>
+    <t>OutU8_bgm_require_state</t>
+  </si>
+  <si>
+    <t>OutU8_bgm_require_ctrl_mode</t>
+  </si>
+  <si>
+    <t>OutU32_bgm_interlock_override</t>
+  </si>
+  <si>
+    <t>OutU32_bgm_unready_override</t>
+  </si>
+  <si>
+    <t>OutU8_qam_require_state</t>
+  </si>
+  <si>
+    <t>OutU8_qam_require_ctrl_mode</t>
+  </si>
+  <si>
+    <t>OutU32_qam_interlock_override</t>
+  </si>
+  <si>
+    <t>OutU32_qam_unready_override</t>
+  </si>
+  <si>
+    <t>OutU8_bsm_require_state</t>
+  </si>
+  <si>
+    <t>OutU8_bsm_require_ctrl_mode</t>
+  </si>
+  <si>
+    <t>OutU32_bsm_interlock_override</t>
+  </si>
+  <si>
+    <t>OutU32_bsm_unready_override</t>
+  </si>
+  <si>
+    <t>OutU8_rtm_off_require_state</t>
+  </si>
+  <si>
+    <t>OutU8_rtm_off_require_ctrl_mode</t>
+  </si>
+  <si>
+    <t>OutU32_rtm_off_interlock_override</t>
+  </si>
+  <si>
+    <t>OutU32_rtm_off_unready_override</t>
+  </si>
+  <si>
+    <t>OutU8_led_belt</t>
+  </si>
+  <si>
+    <t>OutU8_reserved2</t>
+  </si>
+  <si>
+    <t>OutU8_gmm_require_state</t>
+  </si>
+  <si>
+    <t>OutU8_gmm_require_ctrl_mode</t>
+  </si>
+  <si>
+    <t>OutU32_gmm_interlock_override</t>
+  </si>
+  <si>
+    <t>OutU32_gmm_unready_override</t>
+  </si>
+  <si>
+    <t>OutU8_psm_require_state</t>
+  </si>
+  <si>
+    <t>OutU8_psm_require_ctrl_mode</t>
+  </si>
+  <si>
+    <t>OutU32_psm_interlock_override</t>
+  </si>
+  <si>
+    <t>OutU32_psm_unready_override</t>
+  </si>
+  <si>
+    <t>OutU8_fkp_led_blink</t>
+  </si>
+  <si>
+    <t>OutU16_fkp_year</t>
+  </si>
+  <si>
+    <t>OutU8_fkp_month</t>
+  </si>
+  <si>
+    <t>OutU8_fkp_day</t>
+  </si>
+  <si>
+    <t>OutU8_fkp_hour</t>
+  </si>
+  <si>
+    <t>OutU8_fkp_minute</t>
+  </si>
+  <si>
+    <t>OutU8_fkp_fractions</t>
+  </si>
+  <si>
+    <t>OutU8_cpg_vibration</t>
+  </si>
+  <si>
+    <t>InB1_ON_DI_RTC_WD_OK_IN</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
+    <t>InB1_ON_DI_Reserve0</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>InB1_ON_DI_DI_HVEN</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>InB1_ON_DI_Pulse_Inhibit</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>InB1_ON_DI_Power_cut_FB</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>InB1_ON_DI_GATING_IN</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>InB1_ON_DI_Slipring_HVEN_IN</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>InB1_ON_DI_Slipring_KV_TreatmentEN_IN</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>InB1_ON_DI_Slipring_MV_TreatmentEN_IN</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>InB4_ON_DI_reserve1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>InB1_ON_DO_reserve0</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t>InB1_ON_DO_MV_TreatmentEN</t>
+  </si>
+  <si>
+    <t>InB1_ON_DO_KV_TreatmentEN</t>
+  </si>
+  <si>
+    <t>InB1_ON_DO_Emergency</t>
+  </si>
+  <si>
+    <t>InB1_ON_DO_Pulse_Inhibit</t>
+  </si>
+  <si>
+    <t>InB1_ON_DO_HVEN</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>InB1_ON_DO_KV_TreatmentEN</t>
+    <t>InB1_ON_DO_PowerCut</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>InB1_ON_DO_Emergency</t>
+    <t>InB1_ON_DO_reserve1</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>BOOLEAN</t>
-  </si>
-  <si>
-    <t>InB1_ON_DO_Pulse_Inhibit</t>
+    <t>InU8_ON_DO_reserve2</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>InU8_ON_DO_reserve1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>InB1_OFF_DI_STAND_BREAKER1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>InB1_OFF_DI_STAND_BREAKER2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>InB1_OFF_DI_STAND_BREAKER7</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_TREATMENT_ROOM_DOOR_READY </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_CONTROL_ROOM_EMERGENCY </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_CITB_TREATMENT_ROOM_DOOR2 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_CITB_EMERGENCY4 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_CONTROL_ROOM_BREAKER1 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_UserTreatmentEnable </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_UserHvEnable </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_UserMoveEnable </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_STAND_RESERVE </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_STAND_EMERGENCY </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_STAND_BREAKER4 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_TouchGuard </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_reserve0 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_STAND_BREAKER3 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_COVER_EMERGENCY4 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_STAND_CONTACTOR1 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_COVER_EMERGENCY1 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_CONTROL_ROOM_BREAKER3 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_UPS_LOAD_PORT </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_CITB_TREATMENT_ROOM_DOOR1 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_CITB_EMERGENCY2 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_COVER_DOOR </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_HvKey </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_CONTROL_ROOM_CONTACTOR1 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_CITB_EMERGENCY3 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_STAND_CONTACTOR2 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_COVER_EMERGENCY3 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_CONTROL_ROOM_BREAKER5 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_UPS_ON_BYPASS </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_STAND_BREAKER5 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_COVER_RESERVE </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_CONTROL_ROOM_CONTACTOR2 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_CITB_EMERGENCY5 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_CITB_SEARCH_TREATMENT_ROOM </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_CITB_EXTERNAL_TERMINATE </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_UPS_LOW_BATT </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_CONTROL_ROOM_BREAKER2 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_CONTROL_ROOM_BREAKER4 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_UPS_ON_BATT </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_CITB_EMERGENCY1 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_COVER_EMERGENCY2 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_STAND_BREAKER6 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_HvEn </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_MV_TreatmentEN </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_KV_TreatmentEN </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>InU16_OFF_DI_tca9535_di_reserve1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DI_GATING </t>
-    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>BIT7</t>
+  </si>
+  <si>
+    <t>InB7_OFF_DI_reserve2</t>
+  </si>
+  <si>
+    <t>InU8_OFF_DI_reserve3</t>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DO_TreatmentRoomLight </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DO_STAND_RESERVE </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DO_Laser </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DO_RadiationIndicator </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DO_ReadyIndicator </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DO_SearchTreatmentRoomRelay </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DO_softwareTouchGuard </t>
-    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>InB1_OFF_DO_reserve4</t>
+  </si>
+  <si>
+    <t>InU8_OFF_DO_reserve5</t>
+  </si>
+  <si>
+    <t>InU16_OFF_DO_tca9535_do_reserve6</t>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DO_SoftwareMVTreatmentEn </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DO_SoftwareKVTreatmentEn </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DO_softwareMoveEN </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DO_SoftwareHvEn </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DO_TreatmentMotionEnable </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DO_ThreePhasePowerOn </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">InB1_OFF_DO_AsuMotionEnable </t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>InU8_icm_fsm_state_current</t>
-  </si>
-  <si>
-    <t>InU8_icm_ctrl_mode_cur</t>
-  </si>
-  <si>
-    <t>UNSIGNED16</t>
-  </si>
-  <si>
-    <t>InU16_reserved4</t>
-  </si>
-  <si>
-    <t>InU8_icm_beam_id</t>
-  </si>
-  <si>
-    <t>InU8_reserved5</t>
-  </si>
-  <si>
-    <t>InU16_icm_radiation_index</t>
-  </si>
-  <si>
-    <t>InU32_icm_not_ready_event</t>
-  </si>
-  <si>
-    <t>InU32_icm_warning_interlock</t>
-  </si>
-  <si>
-    <t>InU32_icm_minor_interlock</t>
-  </si>
-  <si>
-    <t>InU32_icm_serious_interlock</t>
-  </si>
-  <si>
-    <t>InU8_bgm_fsm_state_current</t>
-  </si>
-  <si>
-    <t>InU8_bgm_ctrl_mode_cur</t>
-  </si>
-  <si>
-    <t>InU16_reserved6</t>
-  </si>
-  <si>
-    <t>InU8_bgm_beam_id</t>
-  </si>
-  <si>
-    <t>InU8_reserved7</t>
-  </si>
-  <si>
-    <t>InU16_bgm_radiation_index</t>
-  </si>
-  <si>
-    <t>InU32_bgm_not_ready_event</t>
-  </si>
-  <si>
-    <t>InU32_bgm_warning_interlock</t>
-  </si>
-  <si>
-    <t>InU32_bgm_minor_interlock</t>
-  </si>
-  <si>
-    <t>InU32_bgm_serious_interlock</t>
-  </si>
-  <si>
-    <t>InF_beam_on_time</t>
-  </si>
-  <si>
-    <t>InF_primary_dose_current</t>
-  </si>
-  <si>
-    <t>InF_primary_dose_rate_current</t>
-  </si>
-  <si>
-    <t>InU8_primary_dose_fsm_state</t>
-  </si>
-  <si>
-    <t>InU8_reserved8</t>
-  </si>
-  <si>
-    <t>InU32_primary_dose_interlock</t>
-  </si>
-  <si>
-    <t>InF_second_dose_current</t>
-  </si>
-  <si>
-    <t>InF_secondry_dose_rate_current</t>
-  </si>
-  <si>
-    <t>InU8_secondry_dose_fsm_rate</t>
-  </si>
-  <si>
-    <t>InU8_reserved9</t>
-  </si>
-  <si>
-    <t>InU32_secondry_dose_interlock</t>
-  </si>
-  <si>
-    <t>InU32_afc_interlock</t>
-  </si>
-  <si>
-    <t>InF_afc_position_current</t>
-  </si>
-  <si>
-    <t>InU8_qam_fsm_state_current</t>
-  </si>
-  <si>
-    <t>InU8_qam_ctrl_mode_cur</t>
-  </si>
-  <si>
-    <t>InU16_reserved10</t>
-  </si>
-  <si>
-    <t>InU8_qam_beam_id</t>
-  </si>
-  <si>
-    <t>InU8_reserved11</t>
-  </si>
-  <si>
-    <t>InU16_qam_radiation_index</t>
-  </si>
-  <si>
-    <t>InU32_qam_not_ready_event</t>
-  </si>
-  <si>
-    <t>InU32_qam_warning_interlock</t>
-  </si>
-  <si>
-    <t>InU32_qam_minor_interlock</t>
-  </si>
-  <si>
-    <t>InU32_qam_serious_interlock</t>
-  </si>
-  <si>
-    <t>InU8_rtm_off_fsm_state_current</t>
-  </si>
-  <si>
-    <t>InU8_rtm_off_ctrl_mode_cur</t>
-  </si>
-  <si>
-    <t>InU16_reserved12</t>
-  </si>
-  <si>
-    <t>InU8_rtm_off_beam_id</t>
-  </si>
-  <si>
-    <t>InU8_reserved13</t>
-  </si>
-  <si>
-    <t>InU16_rtm_off_radiation_index</t>
-  </si>
-  <si>
-    <t>InU32_rtm_off_not_ready_event</t>
-  </si>
-  <si>
-    <t>InU32_rtm_off_warning_interlock</t>
-  </si>
-  <si>
-    <t>InU32_rtm_off_minor_interlock</t>
-  </si>
-  <si>
-    <t>InU32_rtm_off_serious_interlock</t>
-  </si>
-  <si>
-    <t>InU8_gmm_fsm_state_current</t>
-  </si>
-  <si>
-    <t>InU8_gmm_ctrl_mode_cur</t>
-  </si>
-  <si>
-    <t>InU16_reserved14</t>
-  </si>
-  <si>
-    <t>InU8_gmm_beam_id</t>
-  </si>
-  <si>
-    <t>InU8_reserved15</t>
-  </si>
-  <si>
-    <t>InU16_gmm_radiation_index</t>
-  </si>
-  <si>
-    <t>InU32_gmm_not_ready_event</t>
-  </si>
-  <si>
-    <t>InU32_gmm_warning_interlock</t>
-  </si>
-  <si>
-    <t>InU32_gmm_minor_interlock</t>
-  </si>
-  <si>
-    <t>InU32_gmm_serious_interlock</t>
-  </si>
-  <si>
-    <t>InU32_gmm_move_status</t>
-  </si>
-  <si>
-    <t>InF_gmm_position_cur</t>
-  </si>
-  <si>
-    <t>InF_gmm_velocity_cur</t>
-  </si>
-  <si>
-    <t>InU8_psm_fsm_state_current</t>
-  </si>
-  <si>
-    <t>InU8_psm_ctrl_mode_cur</t>
-  </si>
-  <si>
-    <t>InU16_reserved16</t>
-  </si>
-  <si>
-    <t>InU8_psm_beam_id</t>
-  </si>
-  <si>
-    <t>InU8_reserved17</t>
-  </si>
-  <si>
-    <t>InU16_psm_radiation_index</t>
-  </si>
-  <si>
-    <t>InU32_psm_not_ready_event</t>
-  </si>
-  <si>
-    <t>InU32_psm_warning_interlock</t>
-  </si>
-  <si>
-    <t>InU32_psm_minor_interlock</t>
-  </si>
-  <si>
-    <t>InU32_psm_serious_interlock</t>
-  </si>
-  <si>
-    <t>InU32_psm_move_status</t>
-  </si>
-  <si>
-    <t>InF_psm_position_x_cur</t>
-  </si>
-  <si>
-    <t>InF_psm_position_y_cur</t>
-  </si>
-  <si>
-    <t>InF_psm_position_z_cur</t>
-  </si>
-  <si>
-    <t>InF_psm_position_x_r_cur</t>
-  </si>
-  <si>
-    <t>InF_psm_position_y_r_cur</t>
-  </si>
-  <si>
-    <t>InF_psm_position_z_r_cur</t>
-  </si>
-  <si>
-    <t>InF_psm_velocity_x_cur</t>
-  </si>
-  <si>
-    <t>InF_psm_velocity_y_cur</t>
-  </si>
-  <si>
-    <t>InF_psm_velocity_z_cur</t>
-  </si>
-  <si>
-    <t>InF_psm_velocity_x_r_cur</t>
-  </si>
-  <si>
-    <t>InF_psm_velocity_y_r_cur</t>
-  </si>
-  <si>
-    <t>InF_psm_velocity_z_r_cur</t>
-  </si>
-  <si>
-    <t>InU16_FkpButton</t>
-  </si>
-  <si>
-    <t>InU32_CpgButton</t>
-  </si>
-  <si>
-    <t>OutU8_BoardID</t>
-  </si>
-  <si>
-    <t>OutU32_FirmWareVersion</t>
-  </si>
-  <si>
-    <t>OutU8_beam_id</t>
-  </si>
-  <si>
-    <t>OutU8_state_sync</t>
-  </si>
-  <si>
-    <t>OutU16_radiation_index</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DO_reserve7</t>
+  </si>
+  <si>
+    <t>InU8_OFF_DO_reserve8</t>
+  </si>
+  <si>
+    <t>OutU8_Reserved0</t>
+  </si>
+  <si>
+    <t>OutU8_fault_clear</t>
   </si>
   <si>
     <t>OutU8_systemCurrentState</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>OutU16_reboot</t>
   </si>
   <si>
     <t>OutU8_Reserved1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>OutU16_reboot</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>OutU8_ethercat_Link_state</t>
-  </si>
-  <si>
-    <t>OutU8_rtm_on_require_state</t>
-  </si>
-  <si>
-    <t>OutU8_rtm_on_require_ctrl_mode</t>
-  </si>
-  <si>
-    <t>OutU32_rtm_on_interlock_override</t>
-  </si>
-  <si>
-    <t>OutU32_rtm_on_unready_override</t>
-  </si>
-  <si>
-    <t>OutU8_icm_require_state</t>
-  </si>
-  <si>
-    <t>OutU8_icm_require_ctrl_mode</t>
-  </si>
-  <si>
-    <t>OutU16_ct_status</t>
-  </si>
-  <si>
-    <t>OutF_gantry_velocity_prepare</t>
-  </si>
-  <si>
-    <t>OutU32_icm_interlock_override</t>
-  </si>
-  <si>
-    <t>OutU32_icm_unready_override</t>
-  </si>
-  <si>
-    <t>OutU8_bgm_require_state</t>
-  </si>
-  <si>
-    <t>OutU8_bgm_require_ctrl_mode</t>
-  </si>
-  <si>
-    <t>OutU32_bgm_interlock_override</t>
-  </si>
-  <si>
-    <t>OutU32_bgm_unready_override</t>
-  </si>
-  <si>
-    <t>OutU8_qam_require_state</t>
-  </si>
-  <si>
-    <t>OutU8_qam_require_ctrl_mode</t>
-  </si>
-  <si>
-    <t>OutU32_qam_interlock_override</t>
-  </si>
-  <si>
-    <t>OutU32_qam_unready_override</t>
-  </si>
-  <si>
-    <t>OutU8_bsm_require_state</t>
-  </si>
-  <si>
-    <t>OutU8_bsm_require_ctrl_mode</t>
-  </si>
-  <si>
-    <t>OutU32_bsm_interlock_override</t>
-  </si>
-  <si>
-    <t>OutU32_bsm_unready_override</t>
-  </si>
-  <si>
-    <t>OutU8_rtm_off_require_state</t>
-  </si>
-  <si>
-    <t>OutU8_rtm_off_require_ctrl_mode</t>
-  </si>
-  <si>
-    <t>OutU32_rtm_off_interlock_override</t>
-  </si>
-  <si>
-    <t>OutU32_rtm_off_unready_override</t>
-  </si>
-  <si>
-    <t>OutU8_led_belt</t>
-  </si>
-  <si>
-    <t>OutU8_reserved2</t>
-  </si>
-  <si>
-    <t>OutU8_gmm_require_state</t>
-  </si>
-  <si>
-    <t>OutU8_gmm_require_ctrl_mode</t>
-  </si>
-  <si>
-    <t>OutU32_gmm_interlock_override</t>
-  </si>
-  <si>
-    <t>OutU32_gmm_unready_override</t>
-  </si>
-  <si>
-    <t>OutU8_psm_require_state</t>
-  </si>
-  <si>
-    <t>OutU8_psm_require_ctrl_mode</t>
-  </si>
-  <si>
-    <t>OutU32_psm_interlock_override</t>
-  </si>
-  <si>
-    <t>OutU32_psm_unready_override</t>
-  </si>
-  <si>
-    <t>OutU8_fkp_led_blink</t>
+  </si>
+  <si>
+    <t>OutU16_rtm_on_plc_info</t>
+  </si>
+  <si>
+    <t>OutU16_rtm_off_plc_info</t>
   </si>
   <si>
     <t>OutU8_fkp_userPrompt</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>OutU16_fkp_year</t>
-  </si>
-  <si>
-    <t>OutU8_fkp_month</t>
-  </si>
-  <si>
-    <t>OutU8_fkp_day</t>
-  </si>
-  <si>
-    <t>OutU8_fkp_hour</t>
-  </si>
-  <si>
-    <t>OutU8_fkp_minute</t>
-  </si>
-  <si>
-    <t>OutU8_fkp_fractions</t>
   </si>
   <si>
     <t>OutU8_reserved3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>OutU8_cpg_vibration</t>
-  </si>
-  <si>
-    <t>InB7_OFF_DI_reserve2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>InU8_OFF_DI_reserve3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>InB1_OFF_DO_reserve4</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>InU8_OFF_DO_reserve5</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>InU16_OFF_DO_tca9535_do_reserve6</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>InB1_OFF_DO_reserve7</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>InU8_OFF_DO_reserve8</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>UNSIGNED16</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>OutU16_rtm_on_plc_info</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>OutU16_rtm_off_plc_info</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>OutU32_cpg_led_blink</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>UNSIGNED32</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1416,7 +1334,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14990691854609822"/>
+        <fgColor theme="0" tint="-0.1498458815271462"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1449,7 +1367,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
       <protection locked="0"/>
@@ -1484,7 +1402,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
@@ -1554,14 +1471,18 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1868,7 +1789,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T307"/>
+  <dimension ref="A1:T314"/>
   <sheetFormatPr defaultColWidth="10.7265625" defaultRowHeight="14" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.81640625" style="2" customWidth="1"/>
@@ -1900,19 +1821,19 @@
         <v>1</v>
       </c>
       <c r="E1"/>
-      <c r="F1" s="40" t="s">
+      <c r="F1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
-      <c r="N1" s="40"/>
-      <c r="O1" s="40"/>
-      <c r="P1" s="40"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
       <c r="Q1" s="3"/>
       <c r="R1" s="3"/>
       <c r="S1" s="3"/>
@@ -1926,17 +1847,17 @@
         <v>4</v>
       </c>
       <c r="E2"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="40"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
@@ -1947,17 +1868,17 @@
       <c r="C3" s="6"/>
       <c r="D3"/>
       <c r="E3"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="38"/>
+      <c r="N3" s="38"/>
+      <c r="O3" s="38"/>
+      <c r="P3" s="38"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
@@ -1968,17 +1889,17 @@
       <c r="C4" s="6"/>
       <c r="D4"/>
       <c r="E4"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="40"/>
-      <c r="M4" s="40"/>
-      <c r="N4" s="40"/>
-      <c r="O4" s="40"/>
-      <c r="P4" s="40"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="38"/>
+      <c r="O4" s="38"/>
+      <c r="P4" s="38"/>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
@@ -1989,17 +1910,17 @@
       <c r="C5"/>
       <c r="D5"/>
       <c r="E5"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="40"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="40"/>
-      <c r="N5" s="40"/>
-      <c r="O5" s="40"/>
-      <c r="P5" s="40"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
+      <c r="J5" s="38"/>
+      <c r="K5" s="38"/>
+      <c r="L5" s="38"/>
+      <c r="M5" s="38"/>
+      <c r="N5" s="38"/>
+      <c r="O5" s="38"/>
+      <c r="P5" s="38"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
@@ -2010,17 +1931,17 @@
       <c r="C6"/>
       <c r="D6"/>
       <c r="E6"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="40"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="40"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="L6" s="38"/>
+      <c r="M6" s="38"/>
+      <c r="N6" s="38"/>
+      <c r="O6" s="38"/>
+      <c r="P6" s="38"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
@@ -2131,45 +2052,45 @@
       </c>
     </row>
     <row r="11" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="12"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="39"/>
+      <c r="M11" s="39"/>
+      <c r="N11" s="39"/>
+      <c r="O11" s="39"/>
+      <c r="P11" s="39"/>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B12"/>
       <c r="C12"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
       <c r="J12"/>
       <c r="K12"/>
       <c r="L12"/>
       <c r="M12"/>
       <c r="N12"/>
       <c r="O12"/>
-      <c r="P12" s="14"/>
+      <c r="P12" s="13"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="D13" s="15"/>
+      <c r="D13" s="14"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -2178,28 +2099,28 @@
       <c r="P13" s="1"/>
     </row>
     <row r="14" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="12"/>
-      <c r="P14" s="12"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="39"/>
+      <c r="L14" s="39"/>
+      <c r="M14" s="39"/>
+      <c r="N14" s="39"/>
+      <c r="O14" s="39"/>
+      <c r="P14" s="39"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="D15" s="15"/>
+      <c r="D15" s="14"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -2208,7 +2129,7 @@
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="2:20" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="D16" s="15"/>
+      <c r="D16" s="14"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -2217,28 +2138,28 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="2:16" s="1" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
-      <c r="O17" s="12"/>
-      <c r="P17" s="12"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="39"/>
+      <c r="L17" s="39"/>
+      <c r="M17" s="39"/>
+      <c r="N17" s="39"/>
+      <c r="O17" s="39"/>
+      <c r="P17" s="39"/>
     </row>
     <row r="18" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="D18" s="15"/>
+      <c r="D18" s="14"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -2247,7 +2168,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="D19" s="15"/>
+      <c r="D19" s="14"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -2256,28 +2177,28 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="2:16" s="1" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="12"/>
-      <c r="M20" s="12"/>
-      <c r="N20" s="12"/>
-      <c r="O20" s="12"/>
-      <c r="P20" s="12"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="39"/>
+      <c r="L20" s="39"/>
+      <c r="M20" s="39"/>
+      <c r="N20" s="39"/>
+      <c r="O20" s="39"/>
+      <c r="P20" s="39"/>
     </row>
     <row r="21" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="D21" s="15"/>
+      <c r="D21" s="14"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
@@ -2286,7 +2207,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="D22" s="15"/>
+      <c r="D22" s="14"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
@@ -2295,28 +2216,28 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="2:16" s="1" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="12"/>
-      <c r="M23" s="12"/>
-      <c r="N23" s="12"/>
-      <c r="O23" s="12"/>
-      <c r="P23" s="12"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="39"/>
+      <c r="L23" s="39"/>
+      <c r="M23" s="39"/>
+      <c r="N23" s="39"/>
+      <c r="O23" s="39"/>
+      <c r="P23" s="39"/>
     </row>
     <row r="24" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="D24" s="15"/>
+      <c r="D24" s="14"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -2325,7 +2246,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="D25" s="15"/>
+      <c r="D25" s="14"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -2334,28 +2255,28 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="2:16" s="1" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="12"/>
-      <c r="M26" s="12"/>
-      <c r="N26" s="12"/>
-      <c r="O26" s="12"/>
-      <c r="P26" s="12"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="39"/>
+      <c r="K26" s="39"/>
+      <c r="L26" s="39"/>
+      <c r="M26" s="39"/>
+      <c r="N26" s="39"/>
+      <c r="O26" s="39"/>
+      <c r="P26" s="39"/>
     </row>
     <row r="27" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="D27" s="15"/>
+      <c r="D27" s="14"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
@@ -2364,7 +2285,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="D28" s="15"/>
+      <c r="D28" s="14"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
@@ -2373,28 +2294,28 @@
       <c r="P28" s="1"/>
     </row>
     <row r="29" spans="2:16" s="1" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="12"/>
-      <c r="O29" s="12"/>
-      <c r="P29" s="12"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="39"/>
+      <c r="J29" s="39"/>
+      <c r="K29" s="39"/>
+      <c r="L29" s="39"/>
+      <c r="M29" s="39"/>
+      <c r="N29" s="39"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="39"/>
     </row>
     <row r="30" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="D30" s="15"/>
+      <c r="D30" s="14"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
@@ -2403,7 +2324,7 @@
       <c r="P30" s="1"/>
     </row>
     <row r="31" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="D31" s="15"/>
+      <c r="D31" s="14"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
@@ -2412,28 +2333,28 @@
       <c r="P31" s="1"/>
     </row>
     <row r="32" spans="2:16" s="1" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
-      <c r="M32" s="12"/>
-      <c r="N32" s="12"/>
-      <c r="O32" s="12"/>
-      <c r="P32" s="12"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="39"/>
+      <c r="H32" s="39"/>
+      <c r="I32" s="39"/>
+      <c r="J32" s="39"/>
+      <c r="K32" s="39"/>
+      <c r="L32" s="39"/>
+      <c r="M32" s="39"/>
+      <c r="N32" s="39"/>
+      <c r="O32" s="39"/>
+      <c r="P32" s="39"/>
     </row>
     <row r="33" spans="1:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="D33" s="15"/>
+      <c r="D33" s="14"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
@@ -2442,7 +2363,7 @@
       <c r="P33" s="1"/>
     </row>
     <row r="34" spans="1:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="D34" s="15"/>
+      <c r="D34" s="14"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -2451,25 +2372,25 @@
       <c r="P34" s="1"/>
     </row>
     <row r="35" spans="1:16" s="1" customFormat="1" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="12"/>
-      <c r="M35" s="12"/>
-      <c r="N35" s="12"/>
-      <c r="O35" s="12"/>
-      <c r="P35" s="12"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="39"/>
+      <c r="H35" s="39"/>
+      <c r="I35" s="39"/>
+      <c r="J35" s="39"/>
+      <c r="K35" s="39"/>
+      <c r="L35" s="39"/>
+      <c r="M35" s="39"/>
+      <c r="N35" s="39"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="39"/>
     </row>
     <row r="36" spans="1:16" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="2" t="s">
@@ -2478,7 +2399,7 @@
       <c r="C36" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D36" s="15"/>
+      <c r="D36" s="14"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1" t="s">
         <v>41</v>
@@ -2492,25 +2413,25 @@
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
-      <c r="D37" s="16">
+      <c r="D37" s="15">
         <v>1</v>
       </c>
-      <c r="E37" s="16" t="s">
+      <c r="E37" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F37" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="18"/>
-      <c r="K37" s="18"/>
-      <c r="L37" s="18"/>
-      <c r="M37" s="18"/>
-      <c r="N37" s="18"/>
-      <c r="O37" s="18"/>
-      <c r="P37" s="19" t="s">
+      <c r="F37" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="16"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="17"/>
+      <c r="M37" s="17"/>
+      <c r="N37" s="17"/>
+      <c r="O37" s="17"/>
+      <c r="P37" s="18" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2518,49 +2439,49 @@
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
-      <c r="D38" s="16">
+      <c r="D38" s="15">
         <v>2</v>
       </c>
-      <c r="E38" s="16" t="s">
+      <c r="E38" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F38" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="G38" s="17"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="17"/>
-      <c r="J38" s="18"/>
-      <c r="K38" s="18"/>
-      <c r="L38" s="18"/>
-      <c r="M38" s="18"/>
-      <c r="N38" s="18"/>
-      <c r="O38" s="18"/>
-      <c r="P38" s="19"/>
+      <c r="F38" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="16"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
+      <c r="L38" s="17"/>
+      <c r="M38" s="17"/>
+      <c r="N38" s="17"/>
+      <c r="O38" s="17"/>
+      <c r="P38" s="18"/>
     </row>
     <row r="39" spans="1:16" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
-      <c r="D39" s="16">
+      <c r="D39" s="15">
         <v>3</v>
       </c>
-      <c r="E39" s="16" t="s">
+      <c r="E39" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="F39" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="G39" s="17"/>
-      <c r="H39" s="17"/>
-      <c r="I39" s="17"/>
-      <c r="J39" s="18"/>
-      <c r="K39" s="18"/>
-      <c r="L39" s="18"/>
-      <c r="M39" s="18"/>
-      <c r="N39" s="18"/>
-      <c r="O39" s="18"/>
-      <c r="P39" s="19" t="s">
+      <c r="F39" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="G39" s="16"/>
+      <c r="H39" s="16"/>
+      <c r="I39" s="16"/>
+      <c r="J39" s="17"/>
+      <c r="K39" s="17"/>
+      <c r="L39" s="17"/>
+      <c r="M39" s="17"/>
+      <c r="N39" s="17"/>
+      <c r="O39" s="17"/>
+      <c r="P39" s="18" t="s">
         <v>56</v>
       </c>
     </row>
@@ -2568,14 +2489,14 @@
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
-      <c r="D40" s="16">
+      <c r="D40" s="15">
         <v>4</v>
       </c>
-      <c r="E40" s="16" t="s">
+      <c r="E40" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F40" s="16" t="s">
-        <v>66</v>
+      <c r="F40" s="15" t="s">
+        <v>61</v>
       </c>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
@@ -2594,14 +2515,14 @@
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
-      <c r="D41" s="16">
+      <c r="D41" s="15">
         <v>5</v>
       </c>
-      <c r="E41" s="16" t="s">
+      <c r="E41" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F41" s="16" t="s">
-        <v>67</v>
+      <c r="F41" s="15" t="s">
+        <v>62</v>
       </c>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
@@ -2618,14 +2539,14 @@
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
-      <c r="D42" s="16">
+      <c r="D42" s="15">
         <v>6</v>
       </c>
-      <c r="E42" s="16" t="s">
+      <c r="E42" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="F42" s="16" t="s">
-        <v>68</v>
+      <c r="F42" s="15" t="s">
+        <v>63</v>
       </c>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
@@ -2642,14 +2563,14 @@
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
-      <c r="D43" s="16">
+      <c r="D43" s="15">
         <v>7</v>
       </c>
-      <c r="E43" s="16" t="s">
+      <c r="E43" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F43" s="16" t="s">
-        <v>69</v>
+      <c r="F43" s="15" t="s">
+        <v>64</v>
       </c>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
@@ -2666,14 +2587,14 @@
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
-      <c r="D44" s="16">
+      <c r="D44" s="15">
         <v>8</v>
       </c>
-      <c r="E44" s="16" t="s">
+      <c r="E44" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F44" s="16" t="s">
-        <v>70</v>
+      <c r="F44" s="15" t="s">
+        <v>65</v>
       </c>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
@@ -2689,15 +2610,15 @@
     <row r="45" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
-      <c r="C45" s="20"/>
-      <c r="D45" s="16">
+      <c r="C45" s="19"/>
+      <c r="D45" s="15">
         <v>9</v>
       </c>
-      <c r="E45" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="F45" s="16" t="s">
-        <v>71</v>
+      <c r="E45" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F45" s="15" t="s">
+        <v>66</v>
       </c>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
@@ -2713,15 +2634,15 @@
     <row r="46" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
-      <c r="C46" s="20"/>
-      <c r="D46" s="16">
+      <c r="C46" s="19"/>
+      <c r="D46" s="15">
         <v>10</v>
       </c>
-      <c r="E46" s="16" t="s">
+      <c r="E46" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F46" s="16" t="s">
-        <v>72</v>
+      <c r="F46" s="15" t="s">
+        <v>67</v>
       </c>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
@@ -2738,14 +2659,14 @@
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
-      <c r="D47" s="16">
+      <c r="D47" s="15">
         <v>11</v>
       </c>
-      <c r="E47" s="16" t="s">
+      <c r="E47" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F47" s="16" t="s">
-        <v>73</v>
+      <c r="F47" s="15" t="s">
+        <v>68</v>
       </c>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
@@ -2762,14 +2683,14 @@
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
-      <c r="D48" s="16">
+      <c r="D48" s="15">
         <v>12</v>
       </c>
-      <c r="E48" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="F48" s="16" t="s">
-        <v>74</v>
+      <c r="E48" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F48" s="15" t="s">
+        <v>69</v>
       </c>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
@@ -2786,14 +2707,14 @@
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
-      <c r="D49" s="16">
+      <c r="D49" s="15">
         <v>13</v>
       </c>
-      <c r="E49" s="16" t="s">
+      <c r="E49" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="F49" s="16" t="s">
-        <v>75</v>
+      <c r="F49" s="15" t="s">
+        <v>70</v>
       </c>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
@@ -2810,14 +2731,14 @@
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
-      <c r="D50" s="16">
+      <c r="D50" s="15">
         <v>14</v>
       </c>
-      <c r="E50" s="16" t="s">
+      <c r="E50" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="F50" s="16" t="s">
-        <v>76</v>
+      <c r="F50" s="15" t="s">
+        <v>71</v>
       </c>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
@@ -2834,14 +2755,14 @@
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
-      <c r="D51" s="16">
+      <c r="D51" s="15">
         <v>15</v>
       </c>
-      <c r="E51" s="16" t="s">
+      <c r="E51" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="F51" s="16" t="s">
-        <v>77</v>
+      <c r="F51" s="15" t="s">
+        <v>72</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
@@ -2858,14 +2779,14 @@
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
-      <c r="D52" s="16">
+      <c r="D52" s="15">
         <v>16</v>
       </c>
-      <c r="E52" s="16" t="s">
+      <c r="E52" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="F52" s="16" t="s">
-        <v>78</v>
+      <c r="F52" s="15" t="s">
+        <v>73</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
@@ -2882,16 +2803,16 @@
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
-      <c r="D53" s="16">
+      <c r="D53" s="15">
         <v>17</v>
       </c>
-      <c r="E53" s="16" t="s">
+      <c r="E53" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="F53" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="G53" s="21"/>
+      <c r="F53" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="G53" s="20"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
       <c r="J53" s="2"/>
@@ -2906,16 +2827,16 @@
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
-      <c r="D54" s="16">
+      <c r="D54" s="15">
         <v>18</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G54" s="21"/>
+        <v>223</v>
+      </c>
+      <c r="G54" s="20"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
       <c r="J54" s="2"/>
@@ -2930,16 +2851,16 @@
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
-      <c r="D55" s="16">
+      <c r="D55" s="15">
         <v>19</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G55" s="21"/>
+        <v>224</v>
+      </c>
+      <c r="G55" s="20"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
       <c r="J55" s="2"/>
@@ -2954,16 +2875,16 @@
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
-      <c r="D56" s="16">
+      <c r="D56" s="15">
         <v>20</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="G56" s="21"/>
+        <v>76</v>
+      </c>
+      <c r="G56" s="20"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
       <c r="J56" s="2"/>
@@ -2978,16 +2899,16 @@
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
-      <c r="D57" s="16">
+      <c r="D57" s="15">
         <v>21</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="G57" s="21"/>
+        <v>78</v>
+      </c>
+      <c r="G57" s="20"/>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
       <c r="J57" s="2"/>
@@ -3002,16 +2923,16 @@
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
-      <c r="D58" s="16">
+      <c r="D58" s="15">
         <v>22</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="G58" s="21"/>
+        <v>225</v>
+      </c>
+      <c r="G58" s="20"/>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
       <c r="J58" s="2"/>
@@ -3026,16 +2947,16 @@
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
-      <c r="D59" s="16">
+      <c r="D59" s="15">
         <v>23</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="G59" s="21"/>
+        <v>226</v>
+      </c>
+      <c r="G59" s="20"/>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
       <c r="J59" s="2"/>
@@ -3050,16 +2971,16 @@
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
-      <c r="D60" s="16">
+      <c r="D60" s="15">
         <v>24</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="G60" s="21"/>
+        <v>77</v>
+      </c>
+      <c r="G60" s="20"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
       <c r="J60" s="2"/>
@@ -3074,16 +2995,16 @@
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
-      <c r="D61" s="16">
+      <c r="D61" s="15">
         <v>25</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="G61" s="21"/>
+        <v>227</v>
+      </c>
+      <c r="G61" s="20"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
       <c r="J61" s="2"/>
@@ -3098,16 +3019,16 @@
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
-      <c r="D62" s="16">
+      <c r="D62" s="15">
         <v>26</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="G62" s="21"/>
+        <v>228</v>
+      </c>
+      <c r="G62" s="20"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
       <c r="J62" s="2"/>
@@ -3122,16 +3043,16 @@
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
-      <c r="D63" s="16">
+      <c r="D63" s="15">
         <v>27</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="G63" s="21"/>
+        <v>229</v>
+      </c>
+      <c r="G63" s="20"/>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
       <c r="J63" s="2"/>
@@ -3146,16 +3067,16 @@
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
-      <c r="D64" s="16">
+      <c r="D64" s="15">
         <v>28</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G64" s="21"/>
+        <v>230</v>
+      </c>
+      <c r="G64" s="20"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
       <c r="J64" s="2"/>
@@ -3170,16 +3091,16 @@
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
-      <c r="D65" s="16">
+      <c r="D65" s="15">
         <v>29</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="G65" s="21"/>
+        <v>231</v>
+      </c>
+      <c r="G65" s="20"/>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
       <c r="J65" s="2"/>
@@ -3194,16 +3115,16 @@
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
-      <c r="D66" s="16">
+      <c r="D66" s="15">
         <v>30</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G66" s="21"/>
+        <v>232</v>
+      </c>
+      <c r="G66" s="20"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
       <c r="J66" s="2"/>
@@ -3218,16 +3139,16 @@
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
-      <c r="D67" s="16">
+      <c r="D67" s="15">
         <v>31</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G67" s="21"/>
+        <v>233</v>
+      </c>
+      <c r="G67" s="20"/>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
       <c r="J67" s="2"/>
@@ -3242,16 +3163,16 @@
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
-      <c r="D68" s="16">
+      <c r="D68" s="15">
         <v>32</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="G68" s="21"/>
+        <v>234</v>
+      </c>
+      <c r="G68" s="20"/>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
       <c r="J68" s="2"/>
@@ -3266,16 +3187,16 @@
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
-      <c r="D69" s="16">
+      <c r="D69" s="15">
         <v>33</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="G69" s="21"/>
+        <v>235</v>
+      </c>
+      <c r="G69" s="20"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
       <c r="J69" s="2"/>
@@ -3290,16 +3211,16 @@
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
-      <c r="D70" s="16">
+      <c r="D70" s="15">
         <v>34</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="G70" s="21"/>
+        <v>236</v>
+      </c>
+      <c r="G70" s="20"/>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
       <c r="J70" s="2"/>
@@ -3314,16 +3235,16 @@
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
-      <c r="D71" s="16">
+      <c r="D71" s="15">
         <v>35</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="G71" s="21"/>
+        <v>237</v>
+      </c>
+      <c r="G71" s="20"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
       <c r="J71" s="2"/>
@@ -3338,16 +3259,16 @@
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
-      <c r="D72" s="16">
+      <c r="D72" s="15">
         <v>36</v>
       </c>
       <c r="E72" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="G72" s="21"/>
+        <v>238</v>
+      </c>
+      <c r="G72" s="20"/>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
       <c r="J72" s="2"/>
@@ -3362,16 +3283,16 @@
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
-      <c r="D73" s="16">
+      <c r="D73" s="15">
         <v>37</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="G73" s="21"/>
+        <v>239</v>
+      </c>
+      <c r="G73" s="20"/>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
       <c r="J73" s="2"/>
@@ -3386,16 +3307,16 @@
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
-      <c r="D74" s="16">
+      <c r="D74" s="15">
         <v>38</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="G74" s="21"/>
+        <v>240</v>
+      </c>
+      <c r="G74" s="20"/>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
       <c r="J74" s="2"/>
@@ -3410,16 +3331,16 @@
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
-      <c r="D75" s="16">
+      <c r="D75" s="15">
         <v>39</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="G75" s="21"/>
+        <v>241</v>
+      </c>
+      <c r="G75" s="20"/>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
       <c r="J75" s="2"/>
@@ -3434,16 +3355,16 @@
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
-      <c r="D76" s="16">
+      <c r="D76" s="15">
         <v>40</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="G76" s="21"/>
+        <v>242</v>
+      </c>
+      <c r="G76" s="20"/>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
       <c r="J76" s="2"/>
@@ -3458,16 +3379,16 @@
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
-      <c r="D77" s="16">
+      <c r="D77" s="15">
         <v>41</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="G77" s="21"/>
+        <v>243</v>
+      </c>
+      <c r="G77" s="20"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
       <c r="J77" s="2"/>
@@ -3482,16 +3403,16 @@
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
-      <c r="D78" s="16">
+      <c r="D78" s="15">
         <v>42</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="G78" s="21"/>
+        <v>244</v>
+      </c>
+      <c r="G78" s="20"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
       <c r="J78" s="2"/>
@@ -3506,16 +3427,16 @@
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
-      <c r="D79" s="16">
+      <c r="D79" s="15">
         <v>43</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G79" s="21"/>
+        <v>245</v>
+      </c>
+      <c r="G79" s="20"/>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
       <c r="J79" s="2"/>
@@ -3530,16 +3451,16 @@
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
-      <c r="D80" s="16">
+      <c r="D80" s="15">
         <v>44</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="G80" s="21"/>
+        <v>246</v>
+      </c>
+      <c r="G80" s="20"/>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
       <c r="J80" s="2"/>
@@ -3554,16 +3475,16 @@
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
-      <c r="D81" s="16">
+      <c r="D81" s="15">
         <v>45</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="G81" s="21"/>
+        <v>247</v>
+      </c>
+      <c r="G81" s="20"/>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
       <c r="J81" s="2"/>
@@ -3578,16 +3499,16 @@
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
-      <c r="D82" s="16">
+      <c r="D82" s="15">
         <v>46</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G82" s="21"/>
+        <v>248</v>
+      </c>
+      <c r="G82" s="20"/>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
       <c r="J82" s="2"/>
@@ -3602,16 +3523,16 @@
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
-      <c r="D83" s="16">
+      <c r="D83" s="15">
         <v>47</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="G83" s="21"/>
+        <v>249</v>
+      </c>
+      <c r="G83" s="20"/>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
       <c r="J83" s="2"/>
@@ -3626,16 +3547,16 @@
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
-      <c r="D84" s="16">
+      <c r="D84" s="15">
         <v>48</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="G84" s="21"/>
+        <v>250</v>
+      </c>
+      <c r="G84" s="20"/>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
       <c r="J84" s="2"/>
@@ -3650,16 +3571,16 @@
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
-      <c r="D85" s="16">
+      <c r="D85" s="15">
         <v>49</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G85" s="21"/>
+        <v>251</v>
+      </c>
+      <c r="G85" s="20"/>
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
       <c r="J85" s="2"/>
@@ -3674,16 +3595,16 @@
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
-      <c r="D86" s="16">
+      <c r="D86" s="15">
         <v>50</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G86" s="21"/>
+        <v>252</v>
+      </c>
+      <c r="G86" s="20"/>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
       <c r="J86" s="2"/>
@@ -3698,16 +3619,16 @@
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
-      <c r="D87" s="16">
+      <c r="D87" s="15">
         <v>51</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="G87" s="21"/>
+        <v>253</v>
+      </c>
+      <c r="G87" s="20"/>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
       <c r="J87" s="2"/>
@@ -3722,16 +3643,16 @@
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
-      <c r="D88" s="16">
+      <c r="D88" s="15">
         <v>52</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="G88" s="21"/>
+        <v>254</v>
+      </c>
+      <c r="G88" s="20"/>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
       <c r="J88" s="2"/>
@@ -3746,16 +3667,16 @@
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
-      <c r="D89" s="16">
+      <c r="D89" s="15">
         <v>53</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="G89" s="21"/>
+        <v>255</v>
+      </c>
+      <c r="G89" s="20"/>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
       <c r="J89" s="2"/>
@@ -3770,16 +3691,16 @@
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
-      <c r="D90" s="16">
+      <c r="D90" s="15">
         <v>54</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="G90" s="21"/>
+        <v>256</v>
+      </c>
+      <c r="G90" s="20"/>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
       <c r="J90" s="2"/>
@@ -3794,16 +3715,16 @@
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
-      <c r="D91" s="16">
+      <c r="D91" s="15">
         <v>55</v>
       </c>
       <c r="E91" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="G91" s="21"/>
+        <v>257</v>
+      </c>
+      <c r="G91" s="20"/>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
       <c r="J91" s="2"/>
@@ -3818,16 +3739,16 @@
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
-      <c r="D92" s="16">
+      <c r="D92" s="15">
         <v>56</v>
       </c>
       <c r="E92" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="G92" s="21"/>
+        <v>258</v>
+      </c>
+      <c r="G92" s="20"/>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
       <c r="J92" s="2"/>
@@ -3842,16 +3763,16 @@
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
-      <c r="D93" s="16">
+      <c r="D93" s="15">
         <v>57</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="G93" s="21"/>
+        <v>259</v>
+      </c>
+      <c r="G93" s="20"/>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
       <c r="J93" s="2"/>
@@ -3866,16 +3787,16 @@
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
-      <c r="D94" s="16">
+      <c r="D94" s="15">
         <v>58</v>
       </c>
       <c r="E94" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="G94" s="21"/>
+        <v>260</v>
+      </c>
+      <c r="G94" s="20"/>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
       <c r="J94" s="2"/>
@@ -3890,16 +3811,16 @@
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
-      <c r="D95" s="16">
+      <c r="D95" s="15">
         <v>59</v>
       </c>
       <c r="E95" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="G95" s="21"/>
+        <v>261</v>
+      </c>
+      <c r="G95" s="20"/>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
       <c r="J95" s="2"/>
@@ -3914,16 +3835,16 @@
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
-      <c r="D96" s="16">
+      <c r="D96" s="15">
         <v>60</v>
       </c>
       <c r="E96" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="G96" s="21"/>
+        <v>262</v>
+      </c>
+      <c r="G96" s="20"/>
       <c r="H96" s="1"/>
       <c r="I96" s="1"/>
       <c r="J96" s="2"/>
@@ -3938,16 +3859,16 @@
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
-      <c r="D97" s="16">
+      <c r="D97" s="15">
         <v>61</v>
       </c>
       <c r="E97" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="G97" s="21"/>
+        <v>263</v>
+      </c>
+      <c r="G97" s="20"/>
       <c r="H97" s="1"/>
       <c r="I97" s="1"/>
       <c r="J97" s="2"/>
@@ -3962,16 +3883,16 @@
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
-      <c r="D98" s="16">
+      <c r="D98" s="15">
         <v>62</v>
       </c>
       <c r="E98" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="G98" s="21"/>
+        <v>264</v>
+      </c>
+      <c r="G98" s="20"/>
       <c r="H98" s="1"/>
       <c r="I98" s="1"/>
       <c r="J98" s="2"/>
@@ -3986,16 +3907,16 @@
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
-      <c r="D99" s="16">
+      <c r="D99" s="15">
         <v>63</v>
       </c>
       <c r="E99" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="G99" s="21"/>
+        <v>265</v>
+      </c>
+      <c r="G99" s="20"/>
       <c r="H99" s="1"/>
       <c r="I99" s="1"/>
       <c r="J99" s="2"/>
@@ -4010,16 +3931,16 @@
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
-      <c r="D100" s="16">
+      <c r="D100" s="15">
         <v>64</v>
       </c>
       <c r="E100" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="G100" s="21"/>
+        <v>266</v>
+      </c>
+      <c r="G100" s="20"/>
       <c r="H100" s="1"/>
       <c r="I100" s="1"/>
       <c r="J100" s="2"/>
@@ -4034,16 +3955,16 @@
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
-      <c r="D101" s="16">
+      <c r="D101" s="15">
         <v>65</v>
       </c>
       <c r="E101" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="G101" s="21"/>
+        <v>267</v>
+      </c>
+      <c r="G101" s="20"/>
       <c r="H101" s="1"/>
       <c r="I101" s="1"/>
       <c r="J101" s="2"/>
@@ -4058,16 +3979,16 @@
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
-      <c r="D102" s="16">
+      <c r="D102" s="15">
         <v>66</v>
       </c>
       <c r="E102" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G102" s="21"/>
+        <v>268</v>
+      </c>
+      <c r="G102" s="20"/>
       <c r="H102" s="1"/>
       <c r="I102" s="1"/>
       <c r="J102" s="2"/>
@@ -4082,16 +4003,16 @@
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
-      <c r="D103" s="16">
+      <c r="D103" s="15">
         <v>67</v>
       </c>
       <c r="E103" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="G103" s="21"/>
+        <v>269</v>
+      </c>
+      <c r="G103" s="20"/>
       <c r="H103" s="1"/>
       <c r="I103" s="1"/>
       <c r="J103" s="2"/>
@@ -4106,16 +4027,16 @@
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
-      <c r="D104" s="16">
+      <c r="D104" s="15">
         <v>68</v>
       </c>
       <c r="E104" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="G104" s="21"/>
+        <v>270</v>
+      </c>
+      <c r="G104" s="20"/>
       <c r="H104" s="1"/>
       <c r="I104" s="1"/>
       <c r="J104" s="2"/>
@@ -4130,16 +4051,16 @@
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
-      <c r="D105" s="16">
+      <c r="D105" s="15">
         <v>69</v>
       </c>
       <c r="E105" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="G105" s="21"/>
+        <v>271</v>
+      </c>
+      <c r="G105" s="20"/>
       <c r="H105" s="1"/>
       <c r="I105" s="1"/>
       <c r="J105" s="2"/>
@@ -4154,16 +4075,16 @@
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
-      <c r="D106" s="16">
+      <c r="D106" s="15">
         <v>70</v>
       </c>
       <c r="E106" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="G106" s="21"/>
+        <v>272</v>
+      </c>
+      <c r="G106" s="20"/>
       <c r="H106" s="1"/>
       <c r="I106" s="1"/>
       <c r="J106" s="2"/>
@@ -4178,16 +4099,16 @@
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
-      <c r="D107" s="16">
+      <c r="D107" s="15">
         <v>71</v>
       </c>
       <c r="E107" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="G107" s="21"/>
+        <v>273</v>
+      </c>
+      <c r="G107" s="20"/>
       <c r="H107" s="1"/>
       <c r="I107" s="1"/>
       <c r="J107" s="2"/>
@@ -4202,16 +4123,16 @@
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
-      <c r="D108" s="16">
+      <c r="D108" s="15">
         <v>72</v>
       </c>
       <c r="E108" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="G108" s="21"/>
+        <v>274</v>
+      </c>
+      <c r="G108" s="20"/>
       <c r="H108" s="1"/>
       <c r="I108" s="1"/>
       <c r="J108" s="2"/>
@@ -4226,16 +4147,16 @@
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
-      <c r="D109" s="16">
+      <c r="D109" s="15">
         <v>73</v>
       </c>
       <c r="E109" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="G109" s="21"/>
+        <v>275</v>
+      </c>
+      <c r="G109" s="20"/>
       <c r="H109" s="1"/>
       <c r="I109" s="1"/>
       <c r="J109" s="2"/>
@@ -4250,16 +4171,16 @@
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
-      <c r="D110" s="16">
+      <c r="D110" s="15">
         <v>74</v>
       </c>
       <c r="E110" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="G110" s="21"/>
+        <v>276</v>
+      </c>
+      <c r="G110" s="20"/>
       <c r="H110" s="1"/>
       <c r="I110" s="1"/>
       <c r="J110" s="2"/>
@@ -4274,16 +4195,16 @@
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
-      <c r="D111" s="16">
+      <c r="D111" s="15">
         <v>75</v>
       </c>
       <c r="E111" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="G111" s="21"/>
+        <v>277</v>
+      </c>
+      <c r="G111" s="20"/>
       <c r="H111" s="1"/>
       <c r="I111" s="1"/>
       <c r="J111" s="2"/>
@@ -4298,16 +4219,16 @@
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
-      <c r="D112" s="16">
+      <c r="D112" s="15">
         <v>76</v>
       </c>
       <c r="E112" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="G112" s="21"/>
+        <v>278</v>
+      </c>
+      <c r="G112" s="20"/>
       <c r="H112" s="1"/>
       <c r="I112" s="1"/>
       <c r="J112" s="2"/>
@@ -4322,16 +4243,16 @@
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
-      <c r="D113" s="16">
+      <c r="D113" s="15">
         <v>77</v>
       </c>
       <c r="E113" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="G113" s="21"/>
+        <v>279</v>
+      </c>
+      <c r="G113" s="20"/>
       <c r="H113" s="1"/>
       <c r="I113" s="1"/>
       <c r="J113" s="2"/>
@@ -4346,16 +4267,16 @@
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
-      <c r="D114" s="16">
+      <c r="D114" s="15">
         <v>78</v>
       </c>
       <c r="E114" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="G114" s="21"/>
+        <v>280</v>
+      </c>
+      <c r="G114" s="20"/>
       <c r="H114" s="1"/>
       <c r="I114" s="1"/>
       <c r="J114" s="2"/>
@@ -4370,16 +4291,16 @@
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
-      <c r="D115" s="16">
+      <c r="D115" s="15">
         <v>79</v>
       </c>
       <c r="E115" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="G115" s="21"/>
+        <v>281</v>
+      </c>
+      <c r="G115" s="20"/>
       <c r="H115" s="1"/>
       <c r="I115" s="1"/>
       <c r="J115" s="2"/>
@@ -4394,16 +4315,16 @@
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
-      <c r="D116" s="16">
+      <c r="D116" s="15">
         <v>80</v>
       </c>
       <c r="E116" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G116" s="21"/>
+        <v>282</v>
+      </c>
+      <c r="G116" s="20"/>
       <c r="H116" s="1"/>
       <c r="I116" s="1"/>
       <c r="J116" s="2"/>
@@ -4418,16 +4339,16 @@
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
-      <c r="D117" s="16">
+      <c r="D117" s="15">
         <v>81</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="G117" s="21"/>
+        <v>283</v>
+      </c>
+      <c r="G117" s="20"/>
       <c r="H117" s="1"/>
       <c r="I117" s="1"/>
       <c r="J117" s="2"/>
@@ -4442,16 +4363,16 @@
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
-      <c r="D118" s="16">
+      <c r="D118" s="15">
         <v>82</v>
       </c>
       <c r="E118" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="G118" s="21"/>
+        <v>284</v>
+      </c>
+      <c r="G118" s="20"/>
       <c r="H118" s="1"/>
       <c r="I118" s="1"/>
       <c r="J118" s="2"/>
@@ -4466,16 +4387,16 @@
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
-      <c r="D119" s="16">
+      <c r="D119" s="15">
         <v>83</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="G119" s="21"/>
+        <v>285</v>
+      </c>
+      <c r="G119" s="20"/>
       <c r="H119" s="1"/>
       <c r="I119" s="1"/>
       <c r="J119" s="2"/>
@@ -4490,16 +4411,16 @@
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
-      <c r="D120" s="16">
+      <c r="D120" s="15">
         <v>84</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="G120" s="21"/>
+        <v>286</v>
+      </c>
+      <c r="G120" s="20"/>
       <c r="H120" s="1"/>
       <c r="I120" s="1"/>
       <c r="J120" s="2"/>
@@ -4514,16 +4435,16 @@
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
-      <c r="D121" s="16">
+      <c r="D121" s="15">
         <v>85</v>
       </c>
       <c r="E121" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="G121" s="21"/>
+        <v>287</v>
+      </c>
+      <c r="G121" s="20"/>
       <c r="H121" s="1"/>
       <c r="I121" s="1"/>
       <c r="J121" s="2"/>
@@ -4538,16 +4459,16 @@
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
-      <c r="D122" s="16">
+      <c r="D122" s="15">
         <v>86</v>
       </c>
       <c r="E122" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="G122" s="21"/>
+        <v>288</v>
+      </c>
+      <c r="G122" s="20"/>
       <c r="H122" s="1"/>
       <c r="I122" s="1"/>
       <c r="J122" s="2"/>
@@ -4562,16 +4483,16 @@
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
-      <c r="D123" s="16">
+      <c r="D123" s="15">
         <v>87</v>
       </c>
       <c r="E123" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="G123" s="21"/>
+        <v>289</v>
+      </c>
+      <c r="G123" s="20"/>
       <c r="H123" s="1"/>
       <c r="I123" s="1"/>
       <c r="J123" s="2"/>
@@ -4586,16 +4507,16 @@
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
-      <c r="D124" s="16">
+      <c r="D124" s="15">
         <v>88</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="G124" s="21"/>
+        <v>290</v>
+      </c>
+      <c r="G124" s="20"/>
       <c r="H124" s="1"/>
       <c r="I124" s="1"/>
       <c r="J124" s="2"/>
@@ -4610,16 +4531,16 @@
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
-      <c r="D125" s="16">
+      <c r="D125" s="15">
         <v>89</v>
       </c>
       <c r="E125" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="G125" s="21"/>
+        <v>291</v>
+      </c>
+      <c r="G125" s="20"/>
       <c r="H125" s="1"/>
       <c r="I125" s="1"/>
       <c r="J125" s="2"/>
@@ -4634,16 +4555,16 @@
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
-      <c r="D126" s="16">
+      <c r="D126" s="15">
         <v>90</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>80</v>
+        <v>292</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="G126" s="21"/>
+        <v>293</v>
+      </c>
+      <c r="G126" s="20"/>
       <c r="H126" s="1"/>
       <c r="I126" s="1"/>
       <c r="J126" s="2"/>
@@ -4658,16 +4579,16 @@
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
-      <c r="D127" s="16">
+      <c r="D127" s="15">
         <v>91</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="G127" s="21"/>
+        <v>294</v>
+      </c>
+      <c r="G127" s="20"/>
       <c r="H127" s="1"/>
       <c r="I127" s="1"/>
       <c r="J127" s="2"/>
@@ -4682,16 +4603,16 @@
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
-      <c r="D128" s="16">
+      <c r="D128" s="15">
         <v>92</v>
       </c>
       <c r="E128" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="G128" s="21"/>
+        <v>295</v>
+      </c>
+      <c r="G128" s="20"/>
       <c r="H128" s="1"/>
       <c r="I128" s="1"/>
       <c r="J128" s="2"/>
@@ -4706,16 +4627,16 @@
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
-      <c r="D129" s="16">
+      <c r="D129" s="15">
         <v>93</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="G129" s="21"/>
+        <v>296</v>
+      </c>
+      <c r="G129" s="20"/>
       <c r="H129" s="1"/>
       <c r="I129" s="1"/>
       <c r="J129" s="2"/>
@@ -4730,16 +4651,16 @@
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
-      <c r="D130" s="16">
+      <c r="D130" s="15">
         <v>94</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="G130" s="21"/>
+        <v>297</v>
+      </c>
+      <c r="G130" s="20"/>
       <c r="H130" s="1"/>
       <c r="I130" s="1"/>
       <c r="J130" s="2"/>
@@ -4754,16 +4675,16 @@
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
-      <c r="D131" s="16">
+      <c r="D131" s="15">
         <v>95</v>
       </c>
       <c r="E131" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G131" s="21"/>
+        <v>298</v>
+      </c>
+      <c r="G131" s="20"/>
       <c r="H131" s="1"/>
       <c r="I131" s="1"/>
       <c r="J131" s="2"/>
@@ -4778,16 +4699,16 @@
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
-      <c r="D132" s="16">
+      <c r="D132" s="15">
         <v>96</v>
       </c>
       <c r="E132" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="G132" s="21"/>
+        <v>299</v>
+      </c>
+      <c r="G132" s="20"/>
       <c r="H132" s="1"/>
       <c r="I132" s="1"/>
       <c r="J132" s="2"/>
@@ -4802,16 +4723,16 @@
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
-      <c r="D133" s="16">
+      <c r="D133" s="15">
         <v>97</v>
       </c>
       <c r="E133" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="G133" s="21"/>
+        <v>300</v>
+      </c>
+      <c r="G133" s="20"/>
       <c r="H133" s="1"/>
       <c r="I133" s="1"/>
       <c r="J133" s="2"/>
@@ -4826,16 +4747,16 @@
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
-      <c r="D134" s="16">
+      <c r="D134" s="15">
         <v>98</v>
       </c>
       <c r="E134" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="G134" s="21"/>
+        <v>301</v>
+      </c>
+      <c r="G134" s="20"/>
       <c r="H134" s="1"/>
       <c r="I134" s="1"/>
       <c r="J134" s="2"/>
@@ -4850,16 +4771,16 @@
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
-      <c r="D135" s="16">
+      <c r="D135" s="15">
         <v>99</v>
       </c>
       <c r="E135" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="G135" s="21"/>
+        <v>302</v>
+      </c>
+      <c r="G135" s="20"/>
       <c r="H135" s="1"/>
       <c r="I135" s="1"/>
       <c r="J135" s="2"/>
@@ -4874,16 +4795,16 @@
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
-      <c r="D136" s="16">
+      <c r="D136" s="15">
         <v>100</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="G136" s="21"/>
+        <v>303</v>
+      </c>
+      <c r="G136" s="20"/>
       <c r="H136" s="1"/>
       <c r="I136" s="1"/>
       <c r="J136" s="2"/>
@@ -4898,16 +4819,16 @@
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
-      <c r="D137" s="16">
+      <c r="D137" s="15">
         <v>101</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="G137" s="21"/>
+        <v>304</v>
+      </c>
+      <c r="G137" s="20"/>
       <c r="H137" s="1"/>
       <c r="I137" s="1"/>
       <c r="J137" s="2"/>
@@ -4922,16 +4843,16 @@
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
-      <c r="D138" s="16">
+      <c r="D138" s="15">
         <v>102</v>
       </c>
       <c r="E138" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="G138" s="21"/>
+        <v>305</v>
+      </c>
+      <c r="G138" s="20"/>
       <c r="H138" s="1"/>
       <c r="I138" s="1"/>
       <c r="J138" s="2"/>
@@ -4946,16 +4867,16 @@
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
-      <c r="D139" s="16">
+      <c r="D139" s="15">
         <v>103</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="G139" s="21"/>
+        <v>306</v>
+      </c>
+      <c r="G139" s="20"/>
       <c r="H139" s="1"/>
       <c r="I139" s="1"/>
       <c r="J139" s="2"/>
@@ -4970,16 +4891,16 @@
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
-      <c r="D140" s="16">
+      <c r="D140" s="15">
         <v>104</v>
       </c>
-      <c r="E140" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F140" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="G140" s="1"/>
+      <c r="E140" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F140" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="G140" s="20"/>
       <c r="H140" s="1"/>
       <c r="I140" s="1"/>
       <c r="J140" s="2"/>
@@ -4994,16 +4915,16 @@
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
-      <c r="D141" s="16">
+      <c r="D141" s="15">
         <v>105</v>
       </c>
-      <c r="E141" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F141" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="G141" s="1"/>
+      <c r="E141" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="G141" s="20"/>
       <c r="H141" s="1"/>
       <c r="I141" s="1"/>
       <c r="J141" s="2"/>
@@ -5018,16 +4939,16 @@
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
-      <c r="D142" s="16">
+      <c r="D142" s="15">
         <v>106</v>
       </c>
-      <c r="E142" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="F142" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="G142" s="1"/>
+      <c r="E142" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F142" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="G142" s="20"/>
       <c r="H142" s="1"/>
       <c r="I142" s="1"/>
       <c r="J142" s="2"/>
@@ -5042,16 +4963,16 @@
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
-      <c r="D143" s="16">
+      <c r="D143" s="15">
         <v>107</v>
       </c>
-      <c r="E143" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F143" s="16" t="s">
-        <v>168</v>
-      </c>
-      <c r="G143" s="1"/>
+      <c r="E143" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="G143" s="20"/>
       <c r="H143" s="1"/>
       <c r="I143" s="1"/>
       <c r="J143" s="2"/>
@@ -5066,16 +4987,16 @@
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
-      <c r="D144" s="16">
+      <c r="D144" s="15">
         <v>108</v>
       </c>
-      <c r="E144" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F144" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="G144" s="1"/>
+      <c r="E144" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F144" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="G144" s="20"/>
       <c r="H144" s="1"/>
       <c r="I144" s="1"/>
       <c r="J144" s="2"/>
@@ -5090,16 +5011,16 @@
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
-      <c r="D145" s="16">
+      <c r="D145" s="15">
         <v>109</v>
       </c>
-      <c r="E145" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="F145" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="G145" s="1"/>
+      <c r="E145" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="G145" s="20"/>
       <c r="H145" s="1"/>
       <c r="I145" s="1"/>
       <c r="J145" s="2"/>
@@ -5114,16 +5035,16 @@
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
-      <c r="D146" s="16">
+      <c r="D146" s="15">
         <v>110</v>
       </c>
-      <c r="E146" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F146" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="G146" s="22"/>
+      <c r="E146" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F146" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="G146" s="20"/>
       <c r="H146" s="1"/>
       <c r="I146" s="1"/>
       <c r="J146" s="2"/>
@@ -5138,14 +5059,14 @@
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
-      <c r="D147" s="16">
+      <c r="D147" s="15">
         <v>111</v>
       </c>
-      <c r="E147" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F147" s="16" t="s">
-        <v>172</v>
+      <c r="E147" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F147" s="15" t="s">
+        <v>81</v>
       </c>
       <c r="G147" s="1"/>
       <c r="H147" s="1"/>
@@ -5162,14 +5083,14 @@
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
-      <c r="D148" s="16">
+      <c r="D148" s="15">
         <v>112</v>
       </c>
-      <c r="E148" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F148" s="16" t="s">
-        <v>173</v>
+      <c r="E148" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F148" s="15" t="s">
+        <v>82</v>
       </c>
       <c r="G148" s="1"/>
       <c r="H148" s="1"/>
@@ -5186,14 +5107,14 @@
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
-      <c r="D149" s="16">
+      <c r="D149" s="15">
         <v>113</v>
       </c>
-      <c r="E149" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F149" s="16" t="s">
-        <v>174</v>
+      <c r="E149" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="F149" s="15" t="s">
+        <v>84</v>
       </c>
       <c r="G149" s="1"/>
       <c r="H149" s="1"/>
@@ -5210,14 +5131,14 @@
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
-      <c r="D150" s="16">
+      <c r="D150" s="15">
         <v>114</v>
       </c>
-      <c r="E150" s="23" t="s">
+      <c r="E150" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F150" s="16" t="s">
-        <v>175</v>
+      <c r="F150" s="15" t="s">
+        <v>85</v>
       </c>
       <c r="G150" s="1"/>
       <c r="H150" s="1"/>
@@ -5234,14 +5155,14 @@
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
-      <c r="D151" s="16">
+      <c r="D151" s="15">
         <v>115</v>
       </c>
-      <c r="E151" s="23" t="s">
+      <c r="E151" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F151" s="16" t="s">
-        <v>176</v>
+      <c r="F151" s="15" t="s">
+        <v>86</v>
       </c>
       <c r="G151" s="1"/>
       <c r="H151" s="1"/>
@@ -5258,14 +5179,14 @@
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
-      <c r="D152" s="16">
+      <c r="D152" s="15">
         <v>116</v>
       </c>
-      <c r="E152" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="F152" s="16" t="s">
-        <v>177</v>
+      <c r="E152" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F152" s="15" t="s">
+        <v>87</v>
       </c>
       <c r="G152" s="1"/>
       <c r="H152" s="1"/>
@@ -5282,16 +5203,16 @@
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
-      <c r="D153" s="16">
+      <c r="D153" s="15">
         <v>117</v>
       </c>
-      <c r="E153" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="F153" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="G153" s="1"/>
+      <c r="E153" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F153" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="G153" s="21"/>
       <c r="H153" s="1"/>
       <c r="I153" s="1"/>
       <c r="J153" s="2"/>
@@ -5306,14 +5227,14 @@
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
-      <c r="D154" s="16">
+      <c r="D154" s="15">
         <v>118</v>
       </c>
-      <c r="E154" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="F154" s="16" t="s">
-        <v>179</v>
+      <c r="E154" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F154" s="15" t="s">
+        <v>89</v>
       </c>
       <c r="G154" s="1"/>
       <c r="H154" s="1"/>
@@ -5330,14 +5251,14 @@
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
-      <c r="D155" s="16">
+      <c r="D155" s="15">
         <v>119</v>
       </c>
-      <c r="E155" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="F155" s="16" t="s">
-        <v>180</v>
+      <c r="E155" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F155" s="15" t="s">
+        <v>90</v>
       </c>
       <c r="G155" s="1"/>
       <c r="H155" s="1"/>
@@ -5354,14 +5275,14 @@
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
-      <c r="D156" s="16">
+      <c r="D156" s="15">
         <v>120</v>
       </c>
-      <c r="E156" s="23" t="s">
+      <c r="E156" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="F156" s="16" t="s">
-        <v>181</v>
+      <c r="F156" s="15" t="s">
+        <v>91</v>
       </c>
       <c r="G156" s="1"/>
       <c r="H156" s="1"/>
@@ -5378,14 +5299,14 @@
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
-      <c r="D157" s="16">
+      <c r="D157" s="15">
         <v>121</v>
       </c>
-      <c r="E157" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="F157" s="16" t="s">
-        <v>182</v>
+      <c r="E157" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="F157" s="15" t="s">
+        <v>92</v>
       </c>
       <c r="G157" s="1"/>
       <c r="H157" s="1"/>
@@ -5402,14 +5323,14 @@
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
-      <c r="D158" s="16">
+      <c r="D158" s="15">
         <v>122</v>
       </c>
-      <c r="E158" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="F158" s="16" t="s">
-        <v>183</v>
+      <c r="E158" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="F158" s="15" t="s">
+        <v>93</v>
       </c>
       <c r="G158" s="1"/>
       <c r="H158" s="1"/>
@@ -5426,14 +5347,14 @@
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
-      <c r="D159" s="16">
+      <c r="D159" s="15">
         <v>123</v>
       </c>
-      <c r="E159" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="F159" s="16" t="s">
-        <v>184</v>
+      <c r="E159" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="F159" s="15" t="s">
+        <v>94</v>
       </c>
       <c r="G159" s="1"/>
       <c r="H159" s="1"/>
@@ -5450,14 +5371,14 @@
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
-      <c r="D160" s="16">
+      <c r="D160" s="15">
         <v>124</v>
       </c>
-      <c r="E160" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F160" s="16" t="s">
-        <v>185</v>
+      <c r="E160" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="F160" s="15" t="s">
+        <v>95</v>
       </c>
       <c r="G160" s="1"/>
       <c r="H160" s="1"/>
@@ -5474,14 +5395,14 @@
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
-      <c r="D161" s="16">
+      <c r="D161" s="15">
         <v>125</v>
       </c>
-      <c r="E161" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F161" s="16" t="s">
-        <v>186</v>
+      <c r="E161" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="F161" s="15" t="s">
+        <v>96</v>
       </c>
       <c r="G161" s="1"/>
       <c r="H161" s="1"/>
@@ -5498,14 +5419,14 @@
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
-      <c r="D162" s="16">
+      <c r="D162" s="15">
         <v>126</v>
       </c>
-      <c r="E162" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F162" s="16" t="s">
-        <v>187</v>
+      <c r="E162" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="F162" s="15" t="s">
+        <v>97</v>
       </c>
       <c r="G162" s="1"/>
       <c r="H162" s="1"/>
@@ -5522,14 +5443,14 @@
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
-      <c r="D163" s="16">
+      <c r="D163" s="15">
         <v>127</v>
       </c>
-      <c r="E163" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F163" s="16" t="s">
-        <v>188</v>
+      <c r="E163" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="F163" s="15" t="s">
+        <v>98</v>
       </c>
       <c r="G163" s="1"/>
       <c r="H163" s="1"/>
@@ -5546,14 +5467,14 @@
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
-      <c r="D164" s="16">
+      <c r="D164" s="15">
         <v>128</v>
       </c>
-      <c r="E164" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F164" s="16" t="s">
-        <v>189</v>
+      <c r="E164" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="F164" s="15" t="s">
+        <v>99</v>
       </c>
       <c r="G164" s="1"/>
       <c r="H164" s="1"/>
@@ -5570,14 +5491,14 @@
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
-      <c r="D165" s="16">
+      <c r="D165" s="15">
         <v>129</v>
       </c>
-      <c r="E165" s="16" t="s">
+      <c r="E165" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="F165" s="16" t="s">
-        <v>190</v>
+      <c r="F165" s="15" t="s">
+        <v>100</v>
       </c>
       <c r="G165" s="1"/>
       <c r="H165" s="1"/>
@@ -5594,14 +5515,14 @@
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
-      <c r="D166" s="16">
+      <c r="D166" s="15">
         <v>130</v>
       </c>
-      <c r="E166" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F166" s="16" t="s">
-        <v>191</v>
+      <c r="E166" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="F166" s="15" t="s">
+        <v>101</v>
       </c>
       <c r="G166" s="1"/>
       <c r="H166" s="1"/>
@@ -5618,14 +5539,14 @@
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
-      <c r="D167" s="16">
+      <c r="D167" s="15">
         <v>131</v>
       </c>
-      <c r="E167" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F167" s="16" t="s">
-        <v>192</v>
+      <c r="E167" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F167" s="15" t="s">
+        <v>102</v>
       </c>
       <c r="G167" s="1"/>
       <c r="H167" s="1"/>
@@ -5642,14 +5563,14 @@
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
-      <c r="D168" s="16">
+      <c r="D168" s="15">
         <v>132</v>
       </c>
-      <c r="E168" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F168" s="16" t="s">
-        <v>193</v>
+      <c r="E168" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F168" s="15" t="s">
+        <v>103</v>
       </c>
       <c r="G168" s="1"/>
       <c r="H168" s="1"/>
@@ -5666,14 +5587,14 @@
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
-      <c r="D169" s="16">
+      <c r="D169" s="15">
         <v>133</v>
       </c>
-      <c r="E169" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F169" s="16" t="s">
-        <v>194</v>
+      <c r="E169" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F169" s="15" t="s">
+        <v>104</v>
       </c>
       <c r="G169" s="1"/>
       <c r="H169" s="1"/>
@@ -5690,14 +5611,14 @@
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
-      <c r="D170" s="16">
+      <c r="D170" s="15">
         <v>134</v>
       </c>
-      <c r="E170" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F170" s="16" t="s">
-        <v>195</v>
+      <c r="E170" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F170" s="15" t="s">
+        <v>105</v>
       </c>
       <c r="G170" s="1"/>
       <c r="H170" s="1"/>
@@ -5714,14 +5635,14 @@
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
-      <c r="D171" s="16">
+      <c r="D171" s="15">
         <v>135</v>
       </c>
-      <c r="E171" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F171" s="16" t="s">
-        <v>196</v>
+      <c r="E171" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F171" s="15" t="s">
+        <v>106</v>
       </c>
       <c r="G171" s="1"/>
       <c r="H171" s="1"/>
@@ -5738,14 +5659,14 @@
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
-      <c r="D172" s="16">
+      <c r="D172" s="15">
         <v>136</v>
       </c>
-      <c r="E172" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F172" s="16" t="s">
-        <v>197</v>
+      <c r="E172" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F172" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="G172" s="1"/>
       <c r="H172" s="1"/>
@@ -5762,14 +5683,14 @@
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
-      <c r="D173" s="16">
+      <c r="D173" s="15">
         <v>137</v>
       </c>
-      <c r="E173" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F173" s="16" t="s">
-        <v>198</v>
+      <c r="E173" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F173" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="G173" s="1"/>
       <c r="H173" s="1"/>
@@ -5786,14 +5707,14 @@
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
-      <c r="D174" s="16">
+      <c r="D174" s="15">
         <v>138</v>
       </c>
-      <c r="E174" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F174" s="16" t="s">
-        <v>199</v>
+      <c r="E174" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F174" s="15" t="s">
+        <v>109</v>
       </c>
       <c r="G174" s="1"/>
       <c r="H174" s="1"/>
@@ -5810,14 +5731,14 @@
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
-      <c r="D175" s="16">
+      <c r="D175" s="15">
         <v>139</v>
       </c>
-      <c r="E175" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="F175" s="16" t="s">
-        <v>200</v>
+      <c r="E175" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F175" s="15" t="s">
+        <v>110</v>
       </c>
       <c r="G175" s="1"/>
       <c r="H175" s="1"/>
@@ -5834,14 +5755,14 @@
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
-      <c r="D176" s="16">
+      <c r="D176" s="15">
         <v>140</v>
       </c>
-      <c r="E176" s="16" t="s">
+      <c r="E176" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F176" s="16" t="s">
-        <v>201</v>
+      <c r="F176" s="15" t="s">
+        <v>111</v>
       </c>
       <c r="G176" s="1"/>
       <c r="H176" s="1"/>
@@ -5858,14 +5779,14 @@
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
-      <c r="D177" s="16">
+      <c r="D177" s="15">
         <v>141</v>
       </c>
-      <c r="E177" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F177" s="16" t="s">
-        <v>202</v>
+      <c r="E177" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F177" s="15" t="s">
+        <v>112</v>
       </c>
       <c r="G177" s="1"/>
       <c r="H177" s="1"/>
@@ -5882,14 +5803,14 @@
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
-      <c r="D178" s="16">
+      <c r="D178" s="15">
         <v>142</v>
       </c>
-      <c r="E178" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="F178" s="16" t="s">
-        <v>203</v>
+      <c r="E178" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F178" s="15" t="s">
+        <v>113</v>
       </c>
       <c r="G178" s="1"/>
       <c r="H178" s="1"/>
@@ -5902,20 +5823,20 @@
       <c r="O178" s="2"/>
       <c r="P178" s="1"/>
     </row>
-    <row r="179" spans="1:16" customFormat="1" ht="48.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
-      <c r="D179" s="16">
+      <c r="D179" s="15">
         <v>143</v>
       </c>
-      <c r="E179" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F179" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="G179" s="22"/>
+      <c r="E179" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F179" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="G179" s="1"/>
       <c r="H179" s="1"/>
       <c r="I179" s="1"/>
       <c r="J179" s="2"/>
@@ -5930,14 +5851,14 @@
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
-      <c r="D180" s="16">
+      <c r="D180" s="15">
         <v>144</v>
       </c>
-      <c r="E180" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F180" s="16" t="s">
-        <v>205</v>
+      <c r="E180" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F180" s="15" t="s">
+        <v>115</v>
       </c>
       <c r="G180" s="1"/>
       <c r="H180" s="1"/>
@@ -5954,14 +5875,14 @@
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
-      <c r="D181" s="16">
+      <c r="D181" s="15">
         <v>145</v>
       </c>
-      <c r="E181" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F181" s="16" t="s">
-        <v>206</v>
+      <c r="E181" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F181" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="G181" s="1"/>
       <c r="H181" s="1"/>
@@ -5978,14 +5899,14 @@
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
-      <c r="D182" s="16">
+      <c r="D182" s="15">
         <v>146</v>
       </c>
-      <c r="E182" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F182" s="16" t="s">
-        <v>207</v>
+      <c r="E182" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="F182" s="15" t="s">
+        <v>117</v>
       </c>
       <c r="G182" s="1"/>
       <c r="H182" s="1"/>
@@ -6002,14 +5923,14 @@
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
-      <c r="D183" s="16">
+      <c r="D183" s="15">
         <v>147</v>
       </c>
-      <c r="E183" s="16" t="s">
+      <c r="E183" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F183" s="16" t="s">
-        <v>208</v>
+      <c r="F183" s="15" t="s">
+        <v>118</v>
       </c>
       <c r="G183" s="1"/>
       <c r="H183" s="1"/>
@@ -6026,14 +5947,14 @@
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
-      <c r="D184" s="16">
+      <c r="D184" s="15">
         <v>148</v>
       </c>
-      <c r="E184" s="16" t="s">
+      <c r="E184" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F184" s="16" t="s">
-        <v>209</v>
+      <c r="F184" s="15" t="s">
+        <v>119</v>
       </c>
       <c r="G184" s="1"/>
       <c r="H184" s="1"/>
@@ -6050,14 +5971,14 @@
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
-      <c r="D185" s="16">
+      <c r="D185" s="15">
         <v>149</v>
       </c>
-      <c r="E185" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="F185" s="16" t="s">
-        <v>210</v>
+      <c r="E185" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F185" s="15" t="s">
+        <v>120</v>
       </c>
       <c r="G185" s="1"/>
       <c r="H185" s="1"/>
@@ -6070,20 +5991,20 @@
       <c r="O185" s="2"/>
       <c r="P185" s="1"/>
     </row>
-    <row r="186" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:16" customFormat="1" ht="48.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
-      <c r="D186" s="16">
+      <c r="D186" s="15">
         <v>150</v>
       </c>
-      <c r="E186" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F186" s="16" t="s">
-        <v>211</v>
-      </c>
-      <c r="G186" s="1"/>
+      <c r="E186" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F186" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="G186" s="21"/>
       <c r="H186" s="1"/>
       <c r="I186" s="1"/>
       <c r="J186" s="2"/>
@@ -6098,14 +6019,14 @@
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
-      <c r="D187" s="16">
+      <c r="D187" s="15">
         <v>151</v>
       </c>
-      <c r="E187" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F187" s="16" t="s">
-        <v>212</v>
+      <c r="E187" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F187" s="15" t="s">
+        <v>122</v>
       </c>
       <c r="G187" s="1"/>
       <c r="H187" s="1"/>
@@ -6122,14 +6043,14 @@
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
-      <c r="D188" s="16">
+      <c r="D188" s="15">
         <v>152</v>
       </c>
-      <c r="E188" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="F188" s="16" t="s">
-        <v>213</v>
+      <c r="E188" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F188" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="G188" s="1"/>
       <c r="H188" s="1"/>
@@ -6146,16 +6067,16 @@
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
-      <c r="D189" s="16">
+      <c r="D189" s="15">
         <v>153</v>
       </c>
-      <c r="E189" s="16" t="s">
+      <c r="E189" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="F189" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="G189" s="21"/>
+      <c r="F189" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="G189" s="1"/>
       <c r="H189" s="1"/>
       <c r="I189" s="1"/>
       <c r="J189" s="2"/>
@@ -6170,14 +6091,14 @@
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
-      <c r="D190" s="16">
+      <c r="D190" s="15">
         <v>154</v>
       </c>
-      <c r="E190" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F190" s="16" t="s">
-        <v>215</v>
+      <c r="E190" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F190" s="15" t="s">
+        <v>125</v>
       </c>
       <c r="G190" s="1"/>
       <c r="H190" s="1"/>
@@ -6194,14 +6115,14 @@
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
-      <c r="D191" s="16">
+      <c r="D191" s="15">
         <v>155</v>
       </c>
-      <c r="E191" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F191" s="16" t="s">
-        <v>216</v>
+      <c r="E191" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F191" s="15" t="s">
+        <v>126</v>
       </c>
       <c r="G191" s="1"/>
       <c r="H191" s="1"/>
@@ -6218,16 +6139,16 @@
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
-      <c r="D192" s="16">
+      <c r="D192" s="15">
         <v>156</v>
       </c>
-      <c r="E192" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F192" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="G192" s="21"/>
+      <c r="E192" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="F192" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="G192" s="1"/>
       <c r="H192" s="1"/>
       <c r="I192" s="1"/>
       <c r="J192" s="2"/>
@@ -6242,14 +6163,14 @@
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
-      <c r="D193" s="16">
+      <c r="D193" s="15">
         <v>157</v>
       </c>
-      <c r="E193" s="16" t="s">
+      <c r="E193" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F193" s="16" t="s">
-        <v>218</v>
+      <c r="F193" s="15" t="s">
+        <v>128</v>
       </c>
       <c r="G193" s="1"/>
       <c r="H193" s="1"/>
@@ -6266,14 +6187,14 @@
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
-      <c r="D194" s="16">
+      <c r="D194" s="15">
         <v>158</v>
       </c>
-      <c r="E194" s="16" t="s">
+      <c r="E194" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F194" s="16" t="s">
-        <v>219</v>
+      <c r="F194" s="15" t="s">
+        <v>129</v>
       </c>
       <c r="G194" s="1"/>
       <c r="H194" s="1"/>
@@ -6290,14 +6211,14 @@
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
-      <c r="D195" s="16">
+      <c r="D195" s="15">
         <v>159</v>
       </c>
-      <c r="E195" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="F195" s="16" t="s">
-        <v>220</v>
+      <c r="E195" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F195" s="15" t="s">
+        <v>130</v>
       </c>
       <c r="G195" s="1"/>
       <c r="H195" s="1"/>
@@ -6314,16 +6235,16 @@
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
-      <c r="D196" s="16">
+      <c r="D196" s="15">
         <v>160</v>
       </c>
-      <c r="E196" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F196" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="G196" s="1"/>
+      <c r="E196" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F196" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="G196" s="20"/>
       <c r="H196" s="1"/>
       <c r="I196" s="1"/>
       <c r="J196" s="2"/>
@@ -6338,14 +6259,14 @@
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
-      <c r="D197" s="16">
+      <c r="D197" s="15">
         <v>161</v>
       </c>
-      <c r="E197" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F197" s="16" t="s">
-        <v>222</v>
+      <c r="E197" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F197" s="15" t="s">
+        <v>132</v>
       </c>
       <c r="G197" s="1"/>
       <c r="H197" s="1"/>
@@ -6362,14 +6283,14 @@
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
-      <c r="D198" s="16">
+      <c r="D198" s="15">
         <v>162</v>
       </c>
-      <c r="E198" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="F198" s="16" t="s">
-        <v>223</v>
+      <c r="E198" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F198" s="15" t="s">
+        <v>133</v>
       </c>
       <c r="G198" s="1"/>
       <c r="H198" s="1"/>
@@ -6382,20 +6303,20 @@
       <c r="O198" s="2"/>
       <c r="P198" s="1"/>
     </row>
-    <row r="199" spans="1:16" customFormat="1" ht="78.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
-      <c r="D199" s="16">
+      <c r="D199" s="15">
         <v>163</v>
       </c>
-      <c r="E199" s="16" t="s">
+      <c r="E199" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="F199" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="G199" s="22"/>
+      <c r="F199" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="G199" s="20"/>
       <c r="H199" s="1"/>
       <c r="I199" s="1"/>
       <c r="J199" s="2"/>
@@ -6410,14 +6331,14 @@
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
-      <c r="D200" s="16">
+      <c r="D200" s="15">
         <v>164</v>
       </c>
-      <c r="E200" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F200" s="16" t="s">
-        <v>225</v>
+      <c r="E200" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F200" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="G200" s="1"/>
       <c r="H200" s="1"/>
@@ -6434,14 +6355,14 @@
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
-      <c r="D201" s="16">
+      <c r="D201" s="15">
         <v>165</v>
       </c>
-      <c r="E201" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F201" s="16" t="s">
-        <v>226</v>
+      <c r="E201" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F201" s="15" t="s">
+        <v>136</v>
       </c>
       <c r="G201" s="1"/>
       <c r="H201" s="1"/>
@@ -6458,14 +6379,14 @@
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
-      <c r="D202" s="16">
+      <c r="D202" s="15">
         <v>166</v>
       </c>
-      <c r="E202" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F202" s="16" t="s">
-        <v>227</v>
+      <c r="E202" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="F202" s="15" t="s">
+        <v>137</v>
       </c>
       <c r="G202" s="1"/>
       <c r="H202" s="1"/>
@@ -6482,14 +6403,14 @@
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
-      <c r="D203" s="16">
+      <c r="D203" s="15">
         <v>167</v>
       </c>
-      <c r="E203" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F203" s="16" t="s">
-        <v>228</v>
+      <c r="E203" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F203" s="15" t="s">
+        <v>138</v>
       </c>
       <c r="G203" s="1"/>
       <c r="H203" s="1"/>
@@ -6506,14 +6427,14 @@
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
-      <c r="D204" s="16">
+      <c r="D204" s="15">
         <v>168</v>
       </c>
-      <c r="E204" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F204" s="16" t="s">
-        <v>229</v>
+      <c r="E204" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F204" s="15" t="s">
+        <v>139</v>
       </c>
       <c r="G204" s="1"/>
       <c r="H204" s="1"/>
@@ -6530,14 +6451,14 @@
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
-      <c r="D205" s="16">
+      <c r="D205" s="15">
         <v>169</v>
       </c>
-      <c r="E205" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F205" s="16" t="s">
-        <v>230</v>
+      <c r="E205" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F205" s="15" t="s">
+        <v>140</v>
       </c>
       <c r="G205" s="1"/>
       <c r="H205" s="1"/>
@@ -6550,20 +6471,20 @@
       <c r="O205" s="2"/>
       <c r="P205" s="1"/>
     </row>
-    <row r="206" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:16" customFormat="1" ht="78.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
-      <c r="D206" s="16">
+      <c r="D206" s="15">
         <v>170</v>
       </c>
-      <c r="E206" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F206" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="G206" s="1"/>
+      <c r="E206" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F206" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="G206" s="21"/>
       <c r="H206" s="1"/>
       <c r="I206" s="1"/>
       <c r="J206" s="2"/>
@@ -6578,14 +6499,14 @@
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
-      <c r="D207" s="16">
+      <c r="D207" s="15">
         <v>171</v>
       </c>
-      <c r="E207" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F207" s="16" t="s">
-        <v>232</v>
+      <c r="E207" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F207" s="15" t="s">
+        <v>142</v>
       </c>
       <c r="G207" s="1"/>
       <c r="H207" s="1"/>
@@ -6602,14 +6523,14 @@
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
-      <c r="D208" s="16">
+      <c r="D208" s="15">
         <v>172</v>
       </c>
-      <c r="E208" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="F208" s="16" t="s">
-        <v>233</v>
+      <c r="E208" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F208" s="15" t="s">
+        <v>143</v>
       </c>
       <c r="G208" s="1"/>
       <c r="H208" s="1"/>
@@ -6626,14 +6547,14 @@
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
-      <c r="D209" s="16">
+      <c r="D209" s="15">
         <v>173</v>
       </c>
-      <c r="E209" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F209" s="16" t="s">
-        <v>234</v>
+      <c r="E209" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F209" s="15" t="s">
+        <v>144</v>
       </c>
       <c r="G209" s="1"/>
       <c r="H209" s="1"/>
@@ -6650,14 +6571,14 @@
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
-      <c r="D210" s="16">
+      <c r="D210" s="15">
         <v>174</v>
       </c>
-      <c r="E210" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F210" s="16" t="s">
-        <v>235</v>
+      <c r="E210" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F210" s="15" t="s">
+        <v>145</v>
       </c>
       <c r="G210" s="1"/>
       <c r="H210" s="1"/>
@@ -6674,14 +6595,14 @@
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
-      <c r="D211" s="16">
+      <c r="D211" s="15">
         <v>175</v>
       </c>
-      <c r="E211" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="F211" s="16" t="s">
-        <v>236</v>
+      <c r="E211" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F211" s="15" t="s">
+        <v>146</v>
       </c>
       <c r="G211" s="1"/>
       <c r="H211" s="1"/>
@@ -6694,20 +6615,20 @@
       <c r="O211" s="2"/>
       <c r="P211" s="1"/>
     </row>
-    <row r="212" spans="1:16" customFormat="1" ht="128.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
-      <c r="D212" s="16">
+      <c r="D212" s="15">
         <v>176</v>
       </c>
-      <c r="E212" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F212" s="16" t="s">
-        <v>237</v>
-      </c>
-      <c r="G212" s="22"/>
+      <c r="E212" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F212" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="G212" s="1"/>
       <c r="H212" s="1"/>
       <c r="I212" s="1"/>
       <c r="J212" s="2"/>
@@ -6722,14 +6643,14 @@
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
-      <c r="D213" s="16">
+      <c r="D213" s="15">
         <v>177</v>
       </c>
-      <c r="E213" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F213" s="16" t="s">
-        <v>238</v>
+      <c r="E213" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F213" s="15" t="s">
+        <v>148</v>
       </c>
       <c r="G213" s="1"/>
       <c r="H213" s="1"/>
@@ -6746,14 +6667,14 @@
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
-      <c r="D214" s="16">
+      <c r="D214" s="15">
         <v>178</v>
       </c>
-      <c r="E214" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F214" s="16" t="s">
-        <v>239</v>
+      <c r="E214" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F214" s="15" t="s">
+        <v>149</v>
       </c>
       <c r="G214" s="1"/>
       <c r="H214" s="1"/>
@@ -6770,14 +6691,14 @@
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
-      <c r="D215" s="16">
+      <c r="D215" s="15">
         <v>179</v>
       </c>
-      <c r="E215" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F215" s="16" t="s">
-        <v>240</v>
+      <c r="E215" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="F215" s="15" t="s">
+        <v>150</v>
       </c>
       <c r="G215" s="1"/>
       <c r="H215" s="1"/>
@@ -6794,14 +6715,14 @@
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
-      <c r="D216" s="16">
+      <c r="D216" s="15">
         <v>180</v>
       </c>
-      <c r="E216" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F216" s="16" t="s">
-        <v>241</v>
+      <c r="E216" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F216" s="15" t="s">
+        <v>151</v>
       </c>
       <c r="G216" s="1"/>
       <c r="H216" s="1"/>
@@ -6818,14 +6739,14 @@
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
-      <c r="D217" s="16">
+      <c r="D217" s="15">
         <v>181</v>
       </c>
-      <c r="E217" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F217" s="16" t="s">
-        <v>242</v>
+      <c r="E217" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F217" s="15" t="s">
+        <v>152</v>
       </c>
       <c r="G217" s="1"/>
       <c r="H217" s="1"/>
@@ -6842,14 +6763,14 @@
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
-      <c r="D218" s="16">
+      <c r="D218" s="15">
         <v>182</v>
       </c>
-      <c r="E218" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F218" s="16" t="s">
-        <v>243</v>
+      <c r="E218" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F218" s="15" t="s">
+        <v>153</v>
       </c>
       <c r="G218" s="1"/>
       <c r="H218" s="1"/>
@@ -6862,20 +6783,20 @@
       <c r="O218" s="2"/>
       <c r="P218" s="1"/>
     </row>
-    <row r="219" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:16" customFormat="1" ht="128.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
-      <c r="D219" s="16">
+      <c r="D219" s="15">
         <v>183</v>
       </c>
-      <c r="E219" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F219" s="16" t="s">
-        <v>244</v>
-      </c>
-      <c r="G219" s="1"/>
+      <c r="E219" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F219" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="G219" s="21"/>
       <c r="H219" s="1"/>
       <c r="I219" s="1"/>
       <c r="J219" s="2"/>
@@ -6890,14 +6811,14 @@
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
-      <c r="D220" s="16">
+      <c r="D220" s="15">
         <v>184</v>
       </c>
-      <c r="E220" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F220" s="16" t="s">
-        <v>245</v>
+      <c r="E220" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F220" s="15" t="s">
+        <v>155</v>
       </c>
       <c r="G220" s="1"/>
       <c r="H220" s="1"/>
@@ -6914,14 +6835,14 @@
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
-      <c r="D221" s="16">
+      <c r="D221" s="15">
         <v>185</v>
       </c>
-      <c r="E221" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F221" s="16" t="s">
-        <v>246</v>
+      <c r="E221" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F221" s="15" t="s">
+        <v>156</v>
       </c>
       <c r="G221" s="1"/>
       <c r="H221" s="1"/>
@@ -6938,14 +6859,14 @@
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
       <c r="C222" s="2"/>
-      <c r="D222" s="16">
+      <c r="D222" s="15">
         <v>186</v>
       </c>
-      <c r="E222" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F222" s="16" t="s">
-        <v>247</v>
+      <c r="E222" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F222" s="15" t="s">
+        <v>157</v>
       </c>
       <c r="G222" s="1"/>
       <c r="H222" s="1"/>
@@ -6962,14 +6883,14 @@
       <c r="A223" s="2"/>
       <c r="B223" s="2"/>
       <c r="C223" s="2"/>
-      <c r="D223" s="16">
+      <c r="D223" s="15">
         <v>187</v>
       </c>
-      <c r="E223" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F223" s="16" t="s">
-        <v>248</v>
+      <c r="E223" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F223" s="15" t="s">
+        <v>158</v>
       </c>
       <c r="G223" s="1"/>
       <c r="H223" s="1"/>
@@ -6986,14 +6907,14 @@
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="2"/>
-      <c r="D224" s="16">
+      <c r="D224" s="15">
         <v>188</v>
       </c>
-      <c r="E224" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F224" s="16" t="s">
-        <v>249</v>
+      <c r="E224" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F224" s="15" t="s">
+        <v>159</v>
       </c>
       <c r="G224" s="1"/>
       <c r="H224" s="1"/>
@@ -7010,14 +6931,14 @@
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
       <c r="C225" s="2"/>
-      <c r="D225" s="16">
+      <c r="D225" s="15">
         <v>189</v>
       </c>
-      <c r="E225" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F225" s="16" t="s">
-        <v>250</v>
+      <c r="E225" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F225" s="15" t="s">
+        <v>160</v>
       </c>
       <c r="G225" s="1"/>
       <c r="H225" s="1"/>
@@ -7034,14 +6955,14 @@
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
-      <c r="D226" s="16">
+      <c r="D226" s="15">
         <v>190</v>
       </c>
-      <c r="E226" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F226" s="16" t="s">
-        <v>251</v>
+      <c r="E226" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F226" s="15" t="s">
+        <v>161</v>
       </c>
       <c r="G226" s="1"/>
       <c r="H226" s="1"/>
@@ -7058,14 +6979,14 @@
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
-      <c r="D227" s="16">
+      <c r="D227" s="15">
         <v>191</v>
       </c>
-      <c r="E227" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F227" s="16" t="s">
-        <v>252</v>
+      <c r="E227" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F227" s="15" t="s">
+        <v>162</v>
       </c>
       <c r="G227" s="1"/>
       <c r="H227" s="1"/>
@@ -7082,14 +7003,14 @@
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="2"/>
-      <c r="D228" s="16">
+      <c r="D228" s="15">
         <v>192</v>
       </c>
-      <c r="E228" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F228" s="16" t="s">
-        <v>253</v>
+      <c r="E228" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F228" s="15" t="s">
+        <v>163</v>
       </c>
       <c r="G228" s="1"/>
       <c r="H228" s="1"/>
@@ -7106,14 +7027,14 @@
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
-      <c r="D229" s="16">
+      <c r="D229" s="15">
         <v>193</v>
       </c>
-      <c r="E229" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="F229" s="16" t="s">
-        <v>254</v>
+      <c r="E229" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F229" s="15" t="s">
+        <v>164</v>
       </c>
       <c r="G229" s="1"/>
       <c r="H229" s="1"/>
@@ -7130,14 +7051,14 @@
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
-      <c r="D230" s="16">
+      <c r="D230" s="15">
         <v>194</v>
       </c>
-      <c r="E230" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F230" s="16" t="s">
-        <v>255</v>
+      <c r="E230" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F230" s="15" t="s">
+        <v>165</v>
       </c>
       <c r="G230" s="1"/>
       <c r="H230" s="1"/>
@@ -7150,42 +7071,52 @@
       <c r="O230" s="2"/>
       <c r="P230" s="1"/>
     </row>
-    <row r="231" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B231" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C231" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D231" s="12"/>
-      <c r="E231" s="12"/>
-      <c r="F231" s="12"/>
-      <c r="G231" s="12"/>
-      <c r="H231" s="12"/>
-      <c r="I231" s="12"/>
-      <c r="J231" s="12"/>
-      <c r="K231" s="12"/>
-      <c r="L231" s="12"/>
-      <c r="M231" s="12"/>
-      <c r="N231" s="12"/>
-      <c r="O231" s="12"/>
-      <c r="P231" s="12"/>
-    </row>
-    <row r="232" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B232" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C232" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D232" s="15"/>
-      <c r="E232" s="1"/>
-      <c r="F232" s="1" t="s">
-        <v>46</v>
+    <row r="231" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A231" s="2"/>
+      <c r="B231" s="2"/>
+      <c r="C231" s="2"/>
+      <c r="D231" s="15">
+        <v>195</v>
+      </c>
+      <c r="E231" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F231" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="G231" s="1"/>
+      <c r="H231" s="1"/>
+      <c r="I231" s="1"/>
+      <c r="J231" s="2"/>
+      <c r="K231" s="2"/>
+      <c r="L231" s="2"/>
+      <c r="M231" s="2"/>
+      <c r="N231" s="2"/>
+      <c r="O231" s="2"/>
+      <c r="P231" s="1"/>
+    </row>
+    <row r="232" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A232" s="2"/>
+      <c r="B232" s="2"/>
+      <c r="C232" s="2"/>
+      <c r="D232" s="15">
+        <v>196</v>
+      </c>
+      <c r="E232" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F232" s="15" t="s">
+        <v>167</v>
       </c>
       <c r="G232" s="1"/>
       <c r="H232" s="1"/>
       <c r="I232" s="1"/>
+      <c r="J232" s="2"/>
+      <c r="K232" s="2"/>
+      <c r="L232" s="2"/>
+      <c r="M232" s="2"/>
+      <c r="N232" s="2"/>
+      <c r="O232" s="2"/>
       <c r="P232" s="1"/>
     </row>
     <row r="233" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
@@ -7193,13 +7124,13 @@
       <c r="B233" s="2"/>
       <c r="C233" s="2"/>
       <c r="D233" s="15">
-        <v>1</v>
-      </c>
-      <c r="E233" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F233" s="16" t="s">
-        <v>256</v>
+        <v>197</v>
+      </c>
+      <c r="E233" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F233" s="15" t="s">
+        <v>168</v>
       </c>
       <c r="G233" s="1"/>
       <c r="H233" s="1"/>
@@ -7217,15 +7148,15 @@
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
       <c r="D234" s="15">
-        <v>2</v>
-      </c>
-      <c r="E234" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="F234" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="G234" s="25"/>
+        <v>198</v>
+      </c>
+      <c r="E234" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F234" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="G234" s="1"/>
       <c r="H234" s="1"/>
       <c r="I234" s="1"/>
       <c r="J234" s="2"/>
@@ -7241,13 +7172,13 @@
       <c r="B235" s="2"/>
       <c r="C235" s="2"/>
       <c r="D235" s="15">
-        <v>3</v>
-      </c>
-      <c r="E235" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="F235" s="24" t="s">
-        <v>257</v>
+        <v>199</v>
+      </c>
+      <c r="E235" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F235" s="15" t="s">
+        <v>170</v>
       </c>
       <c r="G235" s="1"/>
       <c r="H235" s="1"/>
@@ -7265,15 +7196,15 @@
       <c r="B236" s="2"/>
       <c r="C236" s="2"/>
       <c r="D236" s="15">
-        <v>4</v>
-      </c>
-      <c r="E236" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F236" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="G236" s="1"/>
+        <v>200</v>
+      </c>
+      <c r="E236" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="F236" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="G236" s="20"/>
       <c r="H236" s="1"/>
       <c r="I236" s="1"/>
       <c r="J236" s="2"/>
@@ -7284,164 +7215,154 @@
       <c r="O236" s="2"/>
       <c r="P236" s="1"/>
     </row>
-    <row r="237" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A237" s="20"/>
-      <c r="B237" s="20"/>
-      <c r="C237" s="20"/>
+    <row r="237" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A237" s="2"/>
+      <c r="B237" s="2"/>
+      <c r="C237" s="2"/>
       <c r="D237" s="15">
-        <v>5</v>
-      </c>
-      <c r="E237" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F237" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="G237" s="21"/>
-      <c r="H237" s="26"/>
-      <c r="I237" s="26"/>
-      <c r="J237" s="20"/>
-      <c r="K237" s="20"/>
-      <c r="L237" s="20"/>
-      <c r="M237" s="20"/>
-      <c r="N237" s="20"/>
-      <c r="O237" s="20"/>
-      <c r="P237" s="26"/>
-    </row>
-    <row r="238" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A238" s="2"/>
-      <c r="B238" s="2"/>
-      <c r="C238" s="2"/>
-      <c r="D238" s="15">
-        <v>6</v>
-      </c>
-      <c r="E238" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="F238" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="G238" s="1"/>
-      <c r="H238" s="1"/>
-      <c r="I238" s="1"/>
-      <c r="J238" s="2"/>
-      <c r="K238" s="2"/>
-      <c r="L238" s="2"/>
-      <c r="M238" s="2"/>
-      <c r="N238" s="2"/>
-      <c r="O238" s="2"/>
-      <c r="P238" s="1"/>
-    </row>
-    <row r="239" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A239" s="2"/>
-      <c r="B239" s="2"/>
-      <c r="C239" s="2"/>
-      <c r="D239" s="15">
-        <v>7</v>
-      </c>
-      <c r="E239" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="F239" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="G239" s="21"/>
+        <v>201</v>
+      </c>
+      <c r="E237" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F237" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="G237" s="20"/>
+      <c r="H237" s="1"/>
+      <c r="I237" s="1"/>
+      <c r="J237" s="2"/>
+      <c r="K237" s="2"/>
+      <c r="L237" s="2"/>
+      <c r="M237" s="2"/>
+      <c r="N237" s="2"/>
+      <c r="O237" s="2"/>
+      <c r="P237" s="1"/>
+    </row>
+    <row r="238" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B238" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="C238" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="D238" s="39"/>
+      <c r="E238" s="39"/>
+      <c r="F238" s="39"/>
+      <c r="G238" s="39"/>
+      <c r="H238" s="39"/>
+      <c r="I238" s="39"/>
+      <c r="J238" s="39"/>
+      <c r="K238" s="39"/>
+      <c r="L238" s="39"/>
+      <c r="M238" s="39"/>
+      <c r="N238" s="39"/>
+      <c r="O238" s="39"/>
+      <c r="P238" s="39"/>
+    </row>
+    <row r="239" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B239" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D239" s="14"/>
+      <c r="E239" s="1"/>
+      <c r="F239" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G239" s="1"/>
       <c r="H239" s="1"/>
       <c r="I239" s="1"/>
-      <c r="J239" s="2"/>
-      <c r="K239" s="2"/>
-      <c r="L239" s="2"/>
-      <c r="M239" s="2"/>
-      <c r="N239" s="2"/>
-      <c r="O239" s="2"/>
       <c r="P239" s="1"/>
     </row>
-    <row r="240" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A240" s="20"/>
-      <c r="B240" s="20"/>
-      <c r="C240" s="20"/>
-      <c r="D240" s="15">
-        <v>8</v>
-      </c>
-      <c r="E240" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F240" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="G240" s="25"/>
-      <c r="H240" s="26"/>
-      <c r="I240" s="26"/>
-      <c r="J240" s="20"/>
-      <c r="K240" s="20"/>
-      <c r="L240" s="20"/>
-      <c r="M240" s="20"/>
-      <c r="N240" s="20"/>
-      <c r="O240" s="20"/>
-      <c r="P240" s="26"/>
-    </row>
-    <row r="241" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="20"/>
-      <c r="B241" s="20"/>
-      <c r="C241" s="20"/>
-      <c r="D241" s="15">
-        <v>9</v>
-      </c>
-      <c r="E241" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F241" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="G241" s="25"/>
-      <c r="H241" s="26"/>
-      <c r="I241" s="26"/>
-      <c r="J241" s="20"/>
-      <c r="K241" s="20"/>
-      <c r="L241" s="20"/>
-      <c r="M241" s="20"/>
-      <c r="N241" s="20"/>
-      <c r="O241" s="20"/>
-      <c r="P241" s="26"/>
-    </row>
-    <row r="242" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A242" s="20"/>
-      <c r="B242" s="20"/>
-      <c r="C242" s="20"/>
-      <c r="D242" s="15">
-        <v>10</v>
-      </c>
-      <c r="E242" s="4" t="s">
+    <row r="240" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A240" s="2"/>
+      <c r="B240" s="2"/>
+      <c r="C240" s="2"/>
+      <c r="D240" s="14">
+        <v>1</v>
+      </c>
+      <c r="E240" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F242" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="G242" s="25"/>
-      <c r="H242" s="26"/>
-      <c r="I242" s="26"/>
-      <c r="J242" s="20"/>
-      <c r="K242" s="20"/>
-      <c r="L242" s="20"/>
-      <c r="M242" s="20"/>
-      <c r="N242" s="20"/>
-      <c r="O242" s="20"/>
-      <c r="P242" s="26"/>
+      <c r="F240" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="G240" s="1"/>
+      <c r="H240" s="1"/>
+      <c r="I240" s="1"/>
+      <c r="J240" s="2"/>
+      <c r="K240" s="2"/>
+      <c r="L240" s="2"/>
+      <c r="M240" s="2"/>
+      <c r="N240" s="2"/>
+      <c r="O240" s="2"/>
+      <c r="P240" s="1"/>
+    </row>
+    <row r="241" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A241" s="2"/>
+      <c r="B241" s="2"/>
+      <c r="C241" s="2"/>
+      <c r="D241" s="14">
+        <v>2</v>
+      </c>
+      <c r="E241" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="F241" s="23" t="s">
+        <v>314</v>
+      </c>
+      <c r="G241" s="24"/>
+      <c r="H241" s="1"/>
+      <c r="I241" s="1"/>
+      <c r="J241" s="2"/>
+      <c r="K241" s="2"/>
+      <c r="L241" s="2"/>
+      <c r="M241" s="2"/>
+      <c r="N241" s="2"/>
+      <c r="O241" s="2"/>
+      <c r="P241" s="1"/>
+    </row>
+    <row r="242" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A242" s="2"/>
+      <c r="B242" s="2"/>
+      <c r="C242" s="2"/>
+      <c r="D242" s="14">
+        <v>3</v>
+      </c>
+      <c r="E242" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="F242" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="G242" s="1"/>
+      <c r="H242" s="1"/>
+      <c r="I242" s="1"/>
+      <c r="J242" s="2"/>
+      <c r="K242" s="2"/>
+      <c r="L242" s="2"/>
+      <c r="M242" s="2"/>
+      <c r="N242" s="2"/>
+      <c r="O242" s="2"/>
+      <c r="P242" s="1"/>
     </row>
     <row r="243" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="2"/>
-      <c r="D243" s="15">
-        <v>11</v>
-      </c>
-      <c r="E243" s="16" t="s">
+      <c r="D243" s="14">
+        <v>4</v>
+      </c>
+      <c r="E243" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F243" s="16" t="s">
-        <v>264</v>
-      </c>
-      <c r="G243" s="28"/>
+      <c r="F243" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="G243" s="1"/>
       <c r="H243" s="1"/>
       <c r="I243" s="1"/>
       <c r="J243" s="2"/>
@@ -7452,42 +7373,42 @@
       <c r="O243" s="2"/>
       <c r="P243" s="1"/>
     </row>
-    <row r="244" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A244" s="2"/>
-      <c r="B244" s="2"/>
-      <c r="C244" s="2"/>
-      <c r="D244" s="15">
-        <v>12</v>
-      </c>
-      <c r="E244" s="16" t="s">
+    <row r="244" spans="1:16" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A244" s="19"/>
+      <c r="B244" s="19"/>
+      <c r="C244" s="19"/>
+      <c r="D244" s="14">
+        <v>5</v>
+      </c>
+      <c r="E244" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F244" s="16" t="s">
-        <v>265</v>
-      </c>
-      <c r="G244" s="1"/>
-      <c r="H244" s="1"/>
-      <c r="I244" s="1"/>
-      <c r="J244" s="2"/>
-      <c r="K244" s="2"/>
-      <c r="L244" s="2"/>
-      <c r="M244" s="2"/>
-      <c r="N244" s="2"/>
-      <c r="O244" s="2"/>
-      <c r="P244" s="1"/>
+      <c r="F244" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="G244" s="20"/>
+      <c r="H244" s="25"/>
+      <c r="I244" s="25"/>
+      <c r="J244" s="19"/>
+      <c r="K244" s="19"/>
+      <c r="L244" s="19"/>
+      <c r="M244" s="19"/>
+      <c r="N244" s="19"/>
+      <c r="O244" s="19"/>
+      <c r="P244" s="25"/>
     </row>
     <row r="245" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
       <c r="C245" s="2"/>
-      <c r="D245" s="15">
-        <v>13</v>
-      </c>
-      <c r="E245" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F245" s="16" t="s">
-        <v>266</v>
+      <c r="D245" s="14">
+        <v>6</v>
+      </c>
+      <c r="E245" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F245" s="15" t="s">
+        <v>177</v>
       </c>
       <c r="G245" s="1"/>
       <c r="H245" s="1"/>
@@ -7504,16 +7425,16 @@
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="2"/>
-      <c r="D246" s="15">
-        <v>14</v>
-      </c>
-      <c r="E246" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="F246" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="G246" s="25"/>
+      <c r="D246" s="14">
+        <v>7</v>
+      </c>
+      <c r="E246" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F246" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="G246" s="20"/>
       <c r="H246" s="1"/>
       <c r="I246" s="1"/>
       <c r="J246" s="2"/>
@@ -7524,92 +7445,92 @@
       <c r="O246" s="2"/>
       <c r="P246" s="1"/>
     </row>
-    <row r="247" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A247" s="2"/>
-      <c r="B247" s="2"/>
-      <c r="C247" s="2"/>
-      <c r="D247" s="15">
-        <v>15</v>
-      </c>
-      <c r="E247" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F247" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="G247" s="1"/>
-      <c r="H247" s="1"/>
-      <c r="I247" s="1"/>
-      <c r="J247" s="2"/>
-      <c r="K247" s="2"/>
-      <c r="L247" s="2"/>
-      <c r="M247" s="2"/>
-      <c r="N247" s="2"/>
-      <c r="O247" s="2"/>
-      <c r="P247" s="1"/>
-    </row>
-    <row r="248" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A248" s="2"/>
-      <c r="B248" s="2"/>
-      <c r="C248" s="2"/>
-      <c r="D248" s="15">
-        <v>16</v>
-      </c>
-      <c r="E248" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F248" s="16" t="s">
-        <v>268</v>
-      </c>
-      <c r="G248" s="1"/>
-      <c r="H248" s="1"/>
-      <c r="I248" s="1"/>
-      <c r="J248" s="2"/>
-      <c r="K248" s="2"/>
-      <c r="L248" s="2"/>
-      <c r="M248" s="2"/>
-      <c r="N248" s="2"/>
-      <c r="O248" s="2"/>
-      <c r="P248" s="1"/>
-    </row>
-    <row r="249" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A249" s="2"/>
-      <c r="B249" s="2"/>
-      <c r="C249" s="2"/>
-      <c r="D249" s="15">
-        <v>17</v>
-      </c>
-      <c r="E249" s="16" t="s">
+    <row r="247" spans="1:16" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A247" s="19"/>
+      <c r="B247" s="19"/>
+      <c r="C247" s="19"/>
+      <c r="D247" s="14">
+        <v>8</v>
+      </c>
+      <c r="E247" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F249" s="16" t="s">
-        <v>269</v>
-      </c>
-      <c r="G249" s="1"/>
-      <c r="H249" s="1"/>
-      <c r="I249" s="1"/>
-      <c r="J249" s="2"/>
-      <c r="K249" s="2"/>
-      <c r="L249" s="2"/>
-      <c r="M249" s="2"/>
-      <c r="N249" s="2"/>
-      <c r="O249" s="2"/>
-      <c r="P249" s="1"/>
+      <c r="F247" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="G247" s="24"/>
+      <c r="H247" s="25"/>
+      <c r="I247" s="25"/>
+      <c r="J247" s="19"/>
+      <c r="K247" s="19"/>
+      <c r="L247" s="19"/>
+      <c r="M247" s="19"/>
+      <c r="N247" s="19"/>
+      <c r="O247" s="19"/>
+      <c r="P247" s="25"/>
+    </row>
+    <row r="248" spans="1:16" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A248" s="19"/>
+      <c r="B248" s="19"/>
+      <c r="C248" s="19"/>
+      <c r="D248" s="14">
+        <v>9</v>
+      </c>
+      <c r="E248" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F248" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="G248" s="24"/>
+      <c r="H248" s="25"/>
+      <c r="I248" s="25"/>
+      <c r="J248" s="19"/>
+      <c r="K248" s="19"/>
+      <c r="L248" s="19"/>
+      <c r="M248" s="19"/>
+      <c r="N248" s="19"/>
+      <c r="O248" s="19"/>
+      <c r="P248" s="25"/>
+    </row>
+    <row r="249" spans="1:16" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A249" s="19"/>
+      <c r="B249" s="19"/>
+      <c r="C249" s="19"/>
+      <c r="D249" s="14">
+        <v>10</v>
+      </c>
+      <c r="E249" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F249" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="G249" s="24"/>
+      <c r="H249" s="25"/>
+      <c r="I249" s="25"/>
+      <c r="J249" s="19"/>
+      <c r="K249" s="19"/>
+      <c r="L249" s="19"/>
+      <c r="M249" s="19"/>
+      <c r="N249" s="19"/>
+      <c r="O249" s="19"/>
+      <c r="P249" s="25"/>
     </row>
     <row r="250" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
       <c r="C250" s="2"/>
-      <c r="D250" s="15">
-        <v>18</v>
-      </c>
-      <c r="E250" s="16" t="s">
+      <c r="D250" s="14">
+        <v>11</v>
+      </c>
+      <c r="E250" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F250" s="16" t="s">
-        <v>270</v>
-      </c>
-      <c r="G250" s="1"/>
+      <c r="F250" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="G250" s="27"/>
       <c r="H250" s="1"/>
       <c r="I250" s="1"/>
       <c r="J250" s="2"/>
@@ -7624,14 +7545,14 @@
       <c r="A251" s="2"/>
       <c r="B251" s="2"/>
       <c r="C251" s="2"/>
-      <c r="D251" s="15">
-        <v>19</v>
-      </c>
-      <c r="E251" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="F251" s="16" t="s">
-        <v>271</v>
+      <c r="D251" s="14">
+        <v>12</v>
+      </c>
+      <c r="E251" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F251" s="15" t="s">
+        <v>179</v>
       </c>
       <c r="G251" s="1"/>
       <c r="H251" s="1"/>
@@ -7644,66 +7565,66 @@
       <c r="O251" s="2"/>
       <c r="P251" s="1"/>
     </row>
-    <row r="252" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A252" s="20"/>
-      <c r="B252" s="20"/>
-      <c r="C252" s="20"/>
-      <c r="D252" s="15">
-        <v>20</v>
-      </c>
-      <c r="E252" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="F252" s="24" t="s">
-        <v>272</v>
-      </c>
-      <c r="G252" s="26"/>
-      <c r="H252" s="26"/>
-      <c r="I252" s="26"/>
-      <c r="J252" s="20"/>
-      <c r="K252" s="20"/>
-      <c r="L252" s="20"/>
-      <c r="M252" s="20"/>
-      <c r="N252" s="20"/>
-      <c r="O252" s="20"/>
-      <c r="P252" s="26"/>
-    </row>
-    <row r="253" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A253" s="2"/>
-      <c r="B253" s="2"/>
-      <c r="C253" s="2"/>
-      <c r="D253" s="15">
-        <v>21</v>
-      </c>
-      <c r="E253" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F253" s="16" t="s">
-        <v>273</v>
-      </c>
-      <c r="G253" s="1"/>
-      <c r="H253" s="1"/>
-      <c r="I253" s="1"/>
-      <c r="J253" s="2"/>
-      <c r="K253" s="2"/>
-      <c r="L253" s="2"/>
-      <c r="M253" s="2"/>
-      <c r="N253" s="2"/>
-      <c r="O253" s="2"/>
-      <c r="P253" s="1"/>
+    <row r="252" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A252" s="2"/>
+      <c r="B252" s="2"/>
+      <c r="C252" s="2"/>
+      <c r="D252" s="14">
+        <v>13</v>
+      </c>
+      <c r="E252" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F252" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="G252" s="1"/>
+      <c r="H252" s="1"/>
+      <c r="I252" s="1"/>
+      <c r="J252" s="2"/>
+      <c r="K252" s="2"/>
+      <c r="L252" s="2"/>
+      <c r="M252" s="2"/>
+      <c r="N252" s="2"/>
+      <c r="O252" s="2"/>
+      <c r="P252" s="1"/>
+    </row>
+    <row r="253" spans="1:16" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A253" s="19"/>
+      <c r="B253" s="19"/>
+      <c r="C253" s="19"/>
+      <c r="D253" s="14">
+        <v>14</v>
+      </c>
+      <c r="E253" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F253" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="G253" s="24"/>
+      <c r="H253" s="25"/>
+      <c r="I253" s="25"/>
+      <c r="J253" s="19"/>
+      <c r="K253" s="19"/>
+      <c r="L253" s="19"/>
+      <c r="M253" s="19"/>
+      <c r="N253" s="19"/>
+      <c r="O253" s="19"/>
+      <c r="P253" s="25"/>
     </row>
     <row r="254" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="2"/>
-      <c r="D254" s="15">
-        <v>22</v>
-      </c>
-      <c r="E254" s="16" t="s">
+      <c r="D254" s="14">
+        <v>15</v>
+      </c>
+      <c r="E254" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="F254" s="16" t="s">
-        <v>274</v>
+      <c r="F254" s="15" t="s">
+        <v>181</v>
       </c>
       <c r="G254" s="1"/>
       <c r="H254" s="1"/>
@@ -7720,14 +7641,14 @@
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="2"/>
-      <c r="D255" s="15">
-        <v>23</v>
-      </c>
-      <c r="E255" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F255" s="16" t="s">
-        <v>275</v>
+      <c r="D255" s="14">
+        <v>16</v>
+      </c>
+      <c r="E255" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F255" s="15" t="s">
+        <v>182</v>
       </c>
       <c r="G255" s="1"/>
       <c r="H255" s="1"/>
@@ -7744,14 +7665,14 @@
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="2"/>
-      <c r="D256" s="15">
-        <v>24</v>
-      </c>
-      <c r="E256" s="16" t="s">
+      <c r="D256" s="14">
+        <v>17</v>
+      </c>
+      <c r="E256" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F256" s="16" t="s">
-        <v>276</v>
+      <c r="F256" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="G256" s="1"/>
       <c r="H256" s="1"/>
@@ -7768,14 +7689,14 @@
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="2"/>
-      <c r="D257" s="15">
-        <v>25</v>
-      </c>
-      <c r="E257" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F257" s="16" t="s">
-        <v>277</v>
+      <c r="D257" s="14">
+        <v>18</v>
+      </c>
+      <c r="E257" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F257" s="15" t="s">
+        <v>184</v>
       </c>
       <c r="G257" s="1"/>
       <c r="H257" s="1"/>
@@ -7792,14 +7713,14 @@
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="2"/>
-      <c r="D258" s="15">
-        <v>26</v>
-      </c>
-      <c r="E258" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F258" s="16" t="s">
-        <v>278</v>
+      <c r="D258" s="14">
+        <v>19</v>
+      </c>
+      <c r="E258" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F258" s="15" t="s">
+        <v>185</v>
       </c>
       <c r="G258" s="1"/>
       <c r="H258" s="1"/>
@@ -7812,42 +7733,42 @@
       <c r="O258" s="2"/>
       <c r="P258" s="1"/>
     </row>
-    <row r="259" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A259" s="2"/>
-      <c r="B259" s="2"/>
-      <c r="C259" s="2"/>
-      <c r="D259" s="15">
-        <v>27</v>
-      </c>
-      <c r="E259" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F259" s="16" t="s">
-        <v>279</v>
-      </c>
-      <c r="G259" s="1"/>
-      <c r="H259" s="1"/>
-      <c r="I259" s="1"/>
-      <c r="J259" s="2"/>
-      <c r="K259" s="2"/>
-      <c r="L259" s="2"/>
-      <c r="M259" s="2"/>
-      <c r="N259" s="2"/>
-      <c r="O259" s="2"/>
-      <c r="P259" s="1"/>
+    <row r="259" spans="1:16" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A259" s="19"/>
+      <c r="B259" s="19"/>
+      <c r="C259" s="19"/>
+      <c r="D259" s="14">
+        <v>20</v>
+      </c>
+      <c r="E259" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="F259" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="G259" s="25"/>
+      <c r="H259" s="25"/>
+      <c r="I259" s="25"/>
+      <c r="J259" s="19"/>
+      <c r="K259" s="19"/>
+      <c r="L259" s="19"/>
+      <c r="M259" s="19"/>
+      <c r="N259" s="19"/>
+      <c r="O259" s="19"/>
+      <c r="P259" s="25"/>
     </row>
     <row r="260" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
       <c r="C260" s="2"/>
-      <c r="D260" s="15">
-        <v>28</v>
-      </c>
-      <c r="E260" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F260" s="16" t="s">
-        <v>280</v>
+      <c r="D260" s="14">
+        <v>21</v>
+      </c>
+      <c r="E260" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F260" s="15" t="s">
+        <v>187</v>
       </c>
       <c r="G260" s="1"/>
       <c r="H260" s="1"/>
@@ -7864,14 +7785,14 @@
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
       <c r="C261" s="2"/>
-      <c r="D261" s="15">
-        <v>29</v>
-      </c>
-      <c r="E261" s="16" t="s">
+      <c r="D261" s="14">
+        <v>22</v>
+      </c>
+      <c r="E261" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="F261" s="16" t="s">
-        <v>281</v>
+      <c r="F261" s="15" t="s">
+        <v>188</v>
       </c>
       <c r="G261" s="1"/>
       <c r="H261" s="1"/>
@@ -7888,14 +7809,14 @@
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
       <c r="C262" s="2"/>
-      <c r="D262" s="15">
-        <v>30</v>
-      </c>
-      <c r="E262" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F262" s="16" t="s">
-        <v>282</v>
+      <c r="D262" s="14">
+        <v>23</v>
+      </c>
+      <c r="E262" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F262" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="G262" s="1"/>
       <c r="H262" s="1"/>
@@ -7912,14 +7833,14 @@
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
       <c r="C263" s="2"/>
-      <c r="D263" s="15">
-        <v>31</v>
-      </c>
-      <c r="E263" s="16" t="s">
+      <c r="D263" s="14">
+        <v>24</v>
+      </c>
+      <c r="E263" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F263" s="16" t="s">
-        <v>283</v>
+      <c r="F263" s="15" t="s">
+        <v>190</v>
       </c>
       <c r="G263" s="1"/>
       <c r="H263" s="1"/>
@@ -7936,14 +7857,14 @@
       <c r="A264" s="2"/>
       <c r="B264" s="2"/>
       <c r="C264" s="2"/>
-      <c r="D264" s="15">
-        <v>32</v>
-      </c>
-      <c r="E264" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F264" s="16" t="s">
-        <v>284</v>
+      <c r="D264" s="14">
+        <v>25</v>
+      </c>
+      <c r="E264" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F264" s="15" t="s">
+        <v>191</v>
       </c>
       <c r="G264" s="1"/>
       <c r="H264" s="1"/>
@@ -7960,14 +7881,14 @@
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
       <c r="C265" s="2"/>
-      <c r="D265" s="15">
-        <v>33</v>
-      </c>
-      <c r="E265" s="16" t="s">
+      <c r="D265" s="14">
+        <v>26</v>
+      </c>
+      <c r="E265" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="F265" s="16" t="s">
-        <v>285</v>
+      <c r="F265" s="15" t="s">
+        <v>192</v>
       </c>
       <c r="G265" s="1"/>
       <c r="H265" s="1"/>
@@ -7984,14 +7905,14 @@
       <c r="A266" s="2"/>
       <c r="B266" s="2"/>
       <c r="C266" s="2"/>
-      <c r="D266" s="15">
-        <v>34</v>
-      </c>
-      <c r="E266" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F266" s="16" t="s">
-        <v>286</v>
+      <c r="D266" s="14">
+        <v>27</v>
+      </c>
+      <c r="E266" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F266" s="15" t="s">
+        <v>193</v>
       </c>
       <c r="G266" s="1"/>
       <c r="H266" s="1"/>
@@ -8008,14 +7929,14 @@
       <c r="A267" s="2"/>
       <c r="B267" s="2"/>
       <c r="C267" s="2"/>
-      <c r="D267" s="15">
-        <v>35</v>
-      </c>
-      <c r="E267" s="16" t="s">
+      <c r="D267" s="14">
+        <v>28</v>
+      </c>
+      <c r="E267" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F267" s="16" t="s">
-        <v>287</v>
+      <c r="F267" s="15" t="s">
+        <v>194</v>
       </c>
       <c r="G267" s="1"/>
       <c r="H267" s="1"/>
@@ -8032,14 +7953,14 @@
       <c r="A268" s="2"/>
       <c r="B268" s="2"/>
       <c r="C268" s="2"/>
-      <c r="D268" s="15">
-        <v>36</v>
-      </c>
-      <c r="E268" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F268" s="16" t="s">
-        <v>288</v>
+      <c r="D268" s="14">
+        <v>29</v>
+      </c>
+      <c r="E268" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F268" s="15" t="s">
+        <v>195</v>
       </c>
       <c r="G268" s="1"/>
       <c r="H268" s="1"/>
@@ -8056,14 +7977,14 @@
       <c r="A269" s="2"/>
       <c r="B269" s="2"/>
       <c r="C269" s="2"/>
-      <c r="D269" s="15">
-        <v>37</v>
-      </c>
-      <c r="E269" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="F269" s="4" t="s">
-        <v>320</v>
+      <c r="D269" s="14">
+        <v>30</v>
+      </c>
+      <c r="E269" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F269" s="15" t="s">
+        <v>196</v>
       </c>
       <c r="G269" s="1"/>
       <c r="H269" s="1"/>
@@ -8080,14 +8001,14 @@
       <c r="A270" s="2"/>
       <c r="B270" s="2"/>
       <c r="C270" s="2"/>
-      <c r="D270" s="15">
-        <v>38</v>
-      </c>
-      <c r="E270" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F270" s="16" t="s">
-        <v>289</v>
+      <c r="D270" s="14">
+        <v>31</v>
+      </c>
+      <c r="E270" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F270" s="15" t="s">
+        <v>197</v>
       </c>
       <c r="G270" s="1"/>
       <c r="H270" s="1"/>
@@ -8104,14 +8025,14 @@
       <c r="A271" s="2"/>
       <c r="B271" s="2"/>
       <c r="C271" s="2"/>
-      <c r="D271" s="15">
-        <v>39</v>
-      </c>
-      <c r="E271" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F271" s="16" t="s">
-        <v>290</v>
+      <c r="D271" s="14">
+        <v>32</v>
+      </c>
+      <c r="E271" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F271" s="15" t="s">
+        <v>198</v>
       </c>
       <c r="G271" s="1"/>
       <c r="H271" s="1"/>
@@ -8128,14 +8049,14 @@
       <c r="A272" s="2"/>
       <c r="B272" s="2"/>
       <c r="C272" s="2"/>
-      <c r="D272" s="15">
-        <v>40</v>
-      </c>
-      <c r="E272" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F272" s="16" t="s">
-        <v>291</v>
+      <c r="D272" s="14">
+        <v>33</v>
+      </c>
+      <c r="E272" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F272" s="15" t="s">
+        <v>199</v>
       </c>
       <c r="G272" s="1"/>
       <c r="H272" s="1"/>
@@ -8148,42 +8069,42 @@
       <c r="O272" s="2"/>
       <c r="P272" s="1"/>
     </row>
-    <row r="273" spans="1:16" s="32" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="29"/>
-      <c r="B273" s="29"/>
-      <c r="C273" s="29"/>
-      <c r="D273" s="15">
-        <v>41</v>
-      </c>
-      <c r="E273" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="F273" s="24" t="s">
-        <v>292</v>
-      </c>
-      <c r="G273" s="30"/>
-      <c r="H273" s="31"/>
-      <c r="I273" s="31"/>
-      <c r="J273" s="29"/>
-      <c r="K273" s="29"/>
-      <c r="L273" s="29"/>
-      <c r="M273" s="29"/>
-      <c r="N273" s="29"/>
-      <c r="O273" s="29"/>
-      <c r="P273" s="31"/>
+    <row r="273" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A273" s="2"/>
+      <c r="B273" s="2"/>
+      <c r="C273" s="2"/>
+      <c r="D273" s="14">
+        <v>34</v>
+      </c>
+      <c r="E273" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F273" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="G273" s="1"/>
+      <c r="H273" s="1"/>
+      <c r="I273" s="1"/>
+      <c r="J273" s="2"/>
+      <c r="K273" s="2"/>
+      <c r="L273" s="2"/>
+      <c r="M273" s="2"/>
+      <c r="N273" s="2"/>
+      <c r="O273" s="2"/>
+      <c r="P273" s="1"/>
     </row>
     <row r="274" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2"/>
       <c r="B274" s="2"/>
       <c r="C274" s="2"/>
-      <c r="D274" s="15">
-        <v>42</v>
-      </c>
-      <c r="E274" s="16" t="s">
+      <c r="D274" s="14">
+        <v>35</v>
+      </c>
+      <c r="E274" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F274" s="16" t="s">
-        <v>293</v>
+      <c r="F274" s="15" t="s">
+        <v>201</v>
       </c>
       <c r="G274" s="1"/>
       <c r="H274" s="1"/>
@@ -8200,14 +8121,14 @@
       <c r="A275" s="2"/>
       <c r="B275" s="2"/>
       <c r="C275" s="2"/>
-      <c r="D275" s="15">
-        <v>43</v>
-      </c>
-      <c r="E275" s="16" t="s">
+      <c r="D275" s="14">
+        <v>36</v>
+      </c>
+      <c r="E275" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F275" s="16" t="s">
-        <v>294</v>
+      <c r="F275" s="15" t="s">
+        <v>202</v>
       </c>
       <c r="G275" s="1"/>
       <c r="H275" s="1"/>
@@ -8220,45 +8141,45 @@
       <c r="O275" s="2"/>
       <c r="P275" s="1"/>
     </row>
-    <row r="276" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A276" s="2"/>
-      <c r="B276" s="2"/>
-      <c r="C276" s="2"/>
-      <c r="D276" s="15">
-        <v>44</v>
-      </c>
-      <c r="E276" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F276" s="16" t="s">
-        <v>295</v>
-      </c>
-      <c r="G276" s="1"/>
-      <c r="H276" s="33"/>
-      <c r="I276" s="1"/>
-      <c r="J276" s="2"/>
-      <c r="K276" s="2"/>
-      <c r="L276" s="2"/>
-      <c r="M276" s="2"/>
-      <c r="N276" s="2"/>
-      <c r="O276" s="2"/>
-      <c r="P276" s="1"/>
+    <row r="276" spans="1:16" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A276" s="19"/>
+      <c r="B276" s="19"/>
+      <c r="C276" s="19"/>
+      <c r="D276" s="14">
+        <v>37</v>
+      </c>
+      <c r="E276" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F276" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="G276" s="24"/>
+      <c r="H276" s="25"/>
+      <c r="I276" s="25"/>
+      <c r="J276" s="19"/>
+      <c r="K276" s="19"/>
+      <c r="L276" s="19"/>
+      <c r="M276" s="19"/>
+      <c r="N276" s="19"/>
+      <c r="O276" s="19"/>
+      <c r="P276" s="25"/>
     </row>
     <row r="277" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2"/>
       <c r="B277" s="2"/>
       <c r="C277" s="2"/>
-      <c r="D277" s="15">
-        <v>45</v>
-      </c>
-      <c r="E277" s="16" t="s">
+      <c r="D277" s="14">
+        <v>38</v>
+      </c>
+      <c r="E277" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="F277" s="16" t="s">
-        <v>296</v>
+      <c r="F277" s="15" t="s">
+        <v>203</v>
       </c>
       <c r="G277" s="1"/>
-      <c r="H277" s="34"/>
+      <c r="H277" s="1"/>
       <c r="I277" s="1"/>
       <c r="J277" s="2"/>
       <c r="K277" s="2"/>
@@ -8272,17 +8193,17 @@
       <c r="A278" s="2"/>
       <c r="B278" s="2"/>
       <c r="C278" s="2"/>
-      <c r="D278" s="15">
-        <v>46</v>
-      </c>
-      <c r="E278" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F278" s="16" t="s">
-        <v>297</v>
+      <c r="D278" s="14">
+        <v>39</v>
+      </c>
+      <c r="E278" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F278" s="15" t="s">
+        <v>204</v>
       </c>
       <c r="G278" s="1"/>
-      <c r="H278" s="34"/>
+      <c r="H278" s="1"/>
       <c r="I278" s="1"/>
       <c r="J278" s="2"/>
       <c r="K278" s="2"/>
@@ -8296,17 +8217,17 @@
       <c r="A279" s="2"/>
       <c r="B279" s="2"/>
       <c r="C279" s="2"/>
-      <c r="D279" s="15">
-        <v>47</v>
-      </c>
-      <c r="E279" s="16" t="s">
+      <c r="D279" s="14">
+        <v>40</v>
+      </c>
+      <c r="E279" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F279" s="16" t="s">
-        <v>298</v>
+      <c r="F279" s="15" t="s">
+        <v>205</v>
       </c>
       <c r="G279" s="1"/>
-      <c r="H279" s="34"/>
+      <c r="H279" s="1"/>
       <c r="I279" s="1"/>
       <c r="J279" s="2"/>
       <c r="K279" s="2"/>
@@ -8316,45 +8237,45 @@
       <c r="O279" s="2"/>
       <c r="P279" s="1"/>
     </row>
-    <row r="280" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A280" s="2"/>
-      <c r="B280" s="2"/>
-      <c r="C280" s="2"/>
-      <c r="D280" s="15">
-        <v>48</v>
-      </c>
-      <c r="E280" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F280" s="16" t="s">
-        <v>299</v>
-      </c>
-      <c r="G280" s="1"/>
-      <c r="H280" s="34"/>
-      <c r="I280" s="1"/>
-      <c r="J280" s="2"/>
-      <c r="K280" s="2"/>
-      <c r="L280" s="2"/>
-      <c r="M280" s="2"/>
-      <c r="N280" s="2"/>
-      <c r="O280" s="2"/>
-      <c r="P280" s="1"/>
+    <row r="280" spans="1:16" s="31" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A280" s="28"/>
+      <c r="B280" s="28"/>
+      <c r="C280" s="28"/>
+      <c r="D280" s="14">
+        <v>41</v>
+      </c>
+      <c r="E280" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="F280" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="G280" s="29"/>
+      <c r="H280" s="30"/>
+      <c r="I280" s="30"/>
+      <c r="J280" s="28"/>
+      <c r="K280" s="28"/>
+      <c r="L280" s="28"/>
+      <c r="M280" s="28"/>
+      <c r="N280" s="28"/>
+      <c r="O280" s="28"/>
+      <c r="P280" s="30"/>
     </row>
     <row r="281" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2"/>
       <c r="B281" s="2"/>
       <c r="C281" s="2"/>
-      <c r="D281" s="15">
-        <v>49</v>
-      </c>
-      <c r="E281" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F281" s="16" t="s">
-        <v>300</v>
+      <c r="D281" s="14">
+        <v>42</v>
+      </c>
+      <c r="E281" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F281" s="15" t="s">
+        <v>207</v>
       </c>
       <c r="G281" s="1"/>
-      <c r="H281" s="34"/>
+      <c r="H281" s="1"/>
       <c r="I281" s="1"/>
       <c r="J281" s="2"/>
       <c r="K281" s="2"/>
@@ -8368,17 +8289,17 @@
       <c r="A282" s="2"/>
       <c r="B282" s="2"/>
       <c r="C282" s="2"/>
-      <c r="D282" s="15">
-        <v>50</v>
-      </c>
-      <c r="E282" s="16" t="s">
+      <c r="D282" s="14">
+        <v>43</v>
+      </c>
+      <c r="E282" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F282" s="16" t="s">
-        <v>301</v>
+      <c r="F282" s="15" t="s">
+        <v>208</v>
       </c>
       <c r="G282" s="1"/>
-      <c r="H282" s="34"/>
+      <c r="H282" s="1"/>
       <c r="I282" s="1"/>
       <c r="J282" s="2"/>
       <c r="K282" s="2"/>
@@ -8388,45 +8309,45 @@
       <c r="O282" s="2"/>
       <c r="P282" s="1"/>
     </row>
-    <row r="283" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A283" s="20"/>
-      <c r="B283" s="20"/>
-      <c r="C283" s="20"/>
-      <c r="D283" s="15">
-        <v>51</v>
-      </c>
-      <c r="E283" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F283" s="35" t="s">
-        <v>302</v>
-      </c>
-      <c r="G283" s="25"/>
-      <c r="H283" s="36"/>
-      <c r="I283" s="26"/>
-      <c r="J283" s="20"/>
-      <c r="K283" s="20"/>
-      <c r="L283" s="20"/>
-      <c r="M283" s="20"/>
-      <c r="N283" s="20"/>
-      <c r="O283" s="20"/>
-      <c r="P283" s="26"/>
+    <row r="283" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A283" s="2"/>
+      <c r="B283" s="2"/>
+      <c r="C283" s="2"/>
+      <c r="D283" s="14">
+        <v>44</v>
+      </c>
+      <c r="E283" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F283" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="G283" s="1"/>
+      <c r="H283" s="32"/>
+      <c r="I283" s="1"/>
+      <c r="J283" s="2"/>
+      <c r="K283" s="2"/>
+      <c r="L283" s="2"/>
+      <c r="M283" s="2"/>
+      <c r="N283" s="2"/>
+      <c r="O283" s="2"/>
+      <c r="P283" s="1"/>
     </row>
     <row r="284" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2"/>
       <c r="B284" s="2"/>
       <c r="C284" s="2"/>
-      <c r="D284" s="15">
-        <v>52</v>
-      </c>
-      <c r="E284" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="F284" s="37" t="s">
-        <v>303</v>
-      </c>
-      <c r="G284" s="21"/>
-      <c r="H284" s="34"/>
+      <c r="D284" s="14">
+        <v>45</v>
+      </c>
+      <c r="E284" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F284" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="G284" s="1"/>
+      <c r="H284" s="33"/>
       <c r="I284" s="1"/>
       <c r="J284" s="2"/>
       <c r="K284" s="2"/>
@@ -8440,17 +8361,17 @@
       <c r="A285" s="2"/>
       <c r="B285" s="2"/>
       <c r="C285" s="2"/>
-      <c r="D285" s="15">
+      <c r="D285" s="14">
+        <v>46</v>
+      </c>
+      <c r="E285" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="E285" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F285" s="37" t="s">
-        <v>304</v>
-      </c>
-      <c r="G285" s="21"/>
-      <c r="H285" s="34"/>
+      <c r="F285" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="G285" s="1"/>
+      <c r="H285" s="33"/>
       <c r="I285" s="1"/>
       <c r="J285" s="2"/>
       <c r="K285" s="2"/>
@@ -8464,17 +8385,17 @@
       <c r="A286" s="2"/>
       <c r="B286" s="2"/>
       <c r="C286" s="2"/>
-      <c r="D286" s="15">
-        <v>54</v>
-      </c>
-      <c r="E286" s="16" t="s">
+      <c r="D286" s="14">
+        <v>47</v>
+      </c>
+      <c r="E286" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F286" s="37" t="s">
-        <v>305</v>
-      </c>
-      <c r="G286" s="21"/>
-      <c r="H286" s="34"/>
+      <c r="F286" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="G286" s="1"/>
+      <c r="H286" s="33"/>
       <c r="I286" s="1"/>
       <c r="J286" s="2"/>
       <c r="K286" s="2"/>
@@ -8488,17 +8409,17 @@
       <c r="A287" s="2"/>
       <c r="B287" s="2"/>
       <c r="C287" s="2"/>
-      <c r="D287" s="15">
+      <c r="D287" s="14">
+        <v>48</v>
+      </c>
+      <c r="E287" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="E287" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F287" s="37" t="s">
-        <v>306</v>
-      </c>
-      <c r="G287" s="21"/>
-      <c r="H287" s="34"/>
+      <c r="F287" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="G287" s="1"/>
+      <c r="H287" s="33"/>
       <c r="I287" s="1"/>
       <c r="J287" s="2"/>
       <c r="K287" s="2"/>
@@ -8512,17 +8433,17 @@
       <c r="A288" s="2"/>
       <c r="B288" s="2"/>
       <c r="C288" s="2"/>
-      <c r="D288" s="15">
-        <v>56</v>
-      </c>
-      <c r="E288" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F288" s="37" t="s">
-        <v>307</v>
-      </c>
-      <c r="G288" s="21"/>
-      <c r="H288" s="34"/>
+      <c r="D288" s="14">
+        <v>49</v>
+      </c>
+      <c r="E288" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F288" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="G288" s="1"/>
+      <c r="H288" s="33"/>
       <c r="I288" s="1"/>
       <c r="J288" s="2"/>
       <c r="K288" s="2"/>
@@ -8536,17 +8457,17 @@
       <c r="A289" s="2"/>
       <c r="B289" s="2"/>
       <c r="C289" s="2"/>
-      <c r="D289" s="15">
-        <v>57</v>
-      </c>
-      <c r="E289" s="16" t="s">
+      <c r="D289" s="14">
+        <v>50</v>
+      </c>
+      <c r="E289" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F289" s="37" t="s">
-        <v>308</v>
-      </c>
-      <c r="G289" s="21"/>
-      <c r="H289" s="34"/>
+      <c r="F289" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="G289" s="20"/>
+      <c r="H289" s="33"/>
       <c r="I289" s="1"/>
       <c r="J289" s="2"/>
       <c r="K289" s="2"/>
@@ -8556,45 +8477,45 @@
       <c r="O289" s="2"/>
       <c r="P289" s="1"/>
     </row>
-    <row r="290" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A290" s="20"/>
-      <c r="B290" s="20"/>
-      <c r="C290" s="20"/>
-      <c r="D290" s="15">
-        <v>58</v>
+    <row r="290" spans="1:16" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A290" s="19"/>
+      <c r="B290" s="19"/>
+      <c r="C290" s="19"/>
+      <c r="D290" s="14">
+        <v>51</v>
       </c>
       <c r="E290" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F290" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="G290" s="25"/>
-      <c r="H290" s="36"/>
-      <c r="I290" s="26"/>
-      <c r="J290" s="20"/>
-      <c r="K290" s="20"/>
-      <c r="L290" s="20"/>
-      <c r="M290" s="20"/>
-      <c r="N290" s="20"/>
-      <c r="O290" s="20"/>
-      <c r="P290" s="26"/>
+      <c r="F290" s="34" t="s">
+        <v>321</v>
+      </c>
+      <c r="G290" s="24"/>
+      <c r="H290" s="35"/>
+      <c r="I290" s="25"/>
+      <c r="J290" s="19"/>
+      <c r="K290" s="19"/>
+      <c r="L290" s="19"/>
+      <c r="M290" s="19"/>
+      <c r="N290" s="19"/>
+      <c r="O290" s="19"/>
+      <c r="P290" s="25"/>
     </row>
     <row r="291" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="2"/>
-      <c r="D291" s="15">
-        <v>59</v>
-      </c>
-      <c r="E291" s="16" t="s">
-        <v>322</v>
-      </c>
-      <c r="F291" s="16" t="s">
-        <v>321</v>
-      </c>
-      <c r="G291" s="1"/>
-      <c r="H291" s="34"/>
+      <c r="D291" s="14">
+        <v>52</v>
+      </c>
+      <c r="E291" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="F291" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="G291" s="20"/>
+      <c r="H291" s="33"/>
       <c r="I291" s="1"/>
       <c r="J291" s="2"/>
       <c r="K291" s="2"/>
@@ -8608,17 +8529,17 @@
       <c r="A292" s="2"/>
       <c r="B292" s="2"/>
       <c r="C292" s="2"/>
-      <c r="D292" s="15">
-        <v>60</v>
-      </c>
-      <c r="E292" s="16" t="s">
+      <c r="D292" s="14">
         <v>53</v>
       </c>
-      <c r="F292" s="16" t="s">
-        <v>310</v>
-      </c>
-      <c r="G292" s="21"/>
-      <c r="H292" s="34"/>
+      <c r="E292" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F292" s="36" t="s">
+        <v>217</v>
+      </c>
+      <c r="G292" s="20"/>
+      <c r="H292" s="33"/>
       <c r="I292" s="1"/>
       <c r="J292" s="2"/>
       <c r="K292" s="2"/>
@@ -8628,139 +8549,307 @@
       <c r="O292" s="2"/>
       <c r="P292" s="1"/>
     </row>
-    <row r="293" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B293" s="12" t="s">
+    <row r="293" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A293" s="2"/>
+      <c r="B293" s="2"/>
+      <c r="C293" s="2"/>
+      <c r="D293" s="14">
+        <v>54</v>
+      </c>
+      <c r="E293" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F293" s="36" t="s">
+        <v>218</v>
+      </c>
+      <c r="G293" s="20"/>
+      <c r="H293" s="33"/>
+      <c r="I293" s="1"/>
+      <c r="J293" s="2"/>
+      <c r="K293" s="2"/>
+      <c r="L293" s="2"/>
+      <c r="M293" s="2"/>
+      <c r="N293" s="2"/>
+      <c r="O293" s="2"/>
+      <c r="P293" s="1"/>
+    </row>
+    <row r="294" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A294" s="2"/>
+      <c r="B294" s="2"/>
+      <c r="C294" s="2"/>
+      <c r="D294" s="14">
+        <v>55</v>
+      </c>
+      <c r="E294" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F294" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="G294" s="20"/>
+      <c r="H294" s="33"/>
+      <c r="I294" s="1"/>
+      <c r="J294" s="2"/>
+      <c r="K294" s="2"/>
+      <c r="L294" s="2"/>
+      <c r="M294" s="2"/>
+      <c r="N294" s="2"/>
+      <c r="O294" s="2"/>
+      <c r="P294" s="1"/>
+    </row>
+    <row r="295" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A295" s="2"/>
+      <c r="B295" s="2"/>
+      <c r="C295" s="2"/>
+      <c r="D295" s="14">
+        <v>56</v>
+      </c>
+      <c r="E295" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F295" s="36" t="s">
+        <v>220</v>
+      </c>
+      <c r="G295" s="20"/>
+      <c r="H295" s="33"/>
+      <c r="I295" s="1"/>
+      <c r="J295" s="2"/>
+      <c r="K295" s="2"/>
+      <c r="L295" s="2"/>
+      <c r="M295" s="2"/>
+      <c r="N295" s="2"/>
+      <c r="O295" s="2"/>
+      <c r="P295" s="1"/>
+    </row>
+    <row r="296" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A296" s="2"/>
+      <c r="B296" s="2"/>
+      <c r="C296" s="2"/>
+      <c r="D296" s="14">
+        <v>57</v>
+      </c>
+      <c r="E296" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F296" s="36" t="s">
+        <v>221</v>
+      </c>
+      <c r="G296" s="20"/>
+      <c r="H296" s="33"/>
+      <c r="I296" s="1"/>
+      <c r="J296" s="2"/>
+      <c r="K296" s="2"/>
+      <c r="L296" s="2"/>
+      <c r="M296" s="2"/>
+      <c r="N296" s="2"/>
+      <c r="O296" s="2"/>
+      <c r="P296" s="1"/>
+    </row>
+    <row r="297" spans="1:16" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A297" s="19"/>
+      <c r="B297" s="19"/>
+      <c r="C297" s="19"/>
+      <c r="D297" s="14">
+        <v>58</v>
+      </c>
+      <c r="E297" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F297" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="G297" s="24"/>
+      <c r="H297" s="35"/>
+      <c r="I297" s="25"/>
+      <c r="J297" s="19"/>
+      <c r="K297" s="19"/>
+      <c r="L297" s="19"/>
+      <c r="M297" s="19"/>
+      <c r="N297" s="19"/>
+      <c r="O297" s="19"/>
+      <c r="P297" s="25"/>
+    </row>
+    <row r="298" spans="1:16" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A298" s="19"/>
+      <c r="B298" s="19"/>
+      <c r="C298" s="19"/>
+      <c r="D298" s="40">
+        <v>59</v>
+      </c>
+      <c r="E298" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F298" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="G298" s="24"/>
+      <c r="H298" s="35"/>
+      <c r="I298" s="25"/>
+      <c r="J298" s="19"/>
+      <c r="K298" s="19"/>
+      <c r="L298" s="19"/>
+      <c r="M298" s="19"/>
+      <c r="N298" s="19"/>
+      <c r="O298" s="19"/>
+      <c r="P298" s="25"/>
+    </row>
+    <row r="299" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A299" s="2"/>
+      <c r="B299" s="2"/>
+      <c r="C299" s="2"/>
+      <c r="D299" s="14">
+        <v>60</v>
+      </c>
+      <c r="E299" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F299" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="G299" s="20"/>
+      <c r="H299" s="33"/>
+      <c r="I299" s="1"/>
+      <c r="J299" s="2"/>
+      <c r="K299" s="2"/>
+      <c r="L299" s="2"/>
+      <c r="M299" s="2"/>
+      <c r="N299" s="2"/>
+      <c r="O299" s="2"/>
+      <c r="P299" s="1"/>
+    </row>
+    <row r="300" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B300" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="C293" s="12" t="s">
+      <c r="C300" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="D293" s="12"/>
-      <c r="E293" s="12"/>
-      <c r="F293" s="38"/>
-      <c r="G293" s="12"/>
-      <c r="H293" s="39"/>
-      <c r="I293" s="12"/>
-      <c r="J293" s="12"/>
-      <c r="K293" s="12"/>
-      <c r="L293" s="12"/>
-      <c r="M293" s="12"/>
-      <c r="N293" s="12"/>
-      <c r="O293" s="12"/>
-      <c r="P293" s="12"/>
-    </row>
-    <row r="294" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D294" s="15"/>
-      <c r="E294" s="1"/>
-      <c r="F294" s="1"/>
-      <c r="G294" s="1"/>
-      <c r="H294" s="39"/>
-      <c r="I294" s="1"/>
-      <c r="P294" s="1"/>
-    </row>
-    <row r="295" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D295" s="15"/>
-      <c r="E295" s="1"/>
-      <c r="F295" s="1"/>
-      <c r="G295" s="1"/>
-      <c r="H295" s="39"/>
-      <c r="I295" s="1"/>
-      <c r="P295" s="1"/>
-    </row>
-    <row r="296" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B296" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C296" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="D296" s="12"/>
-      <c r="E296" s="12"/>
-      <c r="G296" s="12"/>
-      <c r="H296" s="34"/>
-      <c r="I296" s="12"/>
-      <c r="J296" s="12"/>
-      <c r="K296" s="12"/>
-      <c r="L296" s="12"/>
-      <c r="M296" s="12"/>
-      <c r="N296" s="12"/>
-      <c r="O296" s="12"/>
-      <c r="P296" s="12"/>
-    </row>
-    <row r="297" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D297" s="15"/>
-      <c r="E297" s="1"/>
-      <c r="F297" s="1"/>
-      <c r="G297" s="1"/>
-      <c r="H297" s="34"/>
-      <c r="I297" s="1"/>
-      <c r="P297" s="1"/>
-    </row>
-    <row r="298" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D298" s="15"/>
-      <c r="E298" s="1"/>
-      <c r="F298" s="1"/>
-      <c r="G298" s="1"/>
-      <c r="H298" s="33"/>
-      <c r="I298" s="1"/>
-      <c r="P298" s="1"/>
-    </row>
-    <row r="299" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B299" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C299" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D299" s="12"/>
-      <c r="E299" s="12"/>
-      <c r="F299" s="12"/>
-      <c r="G299" s="12"/>
-      <c r="H299" s="12"/>
-      <c r="I299" s="12"/>
-      <c r="J299" s="12"/>
-      <c r="K299" s="12"/>
-      <c r="L299" s="12"/>
-      <c r="M299" s="12"/>
-      <c r="N299" s="12"/>
-      <c r="O299" s="12"/>
-      <c r="P299" s="12"/>
-    </row>
-    <row r="300" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D300" s="15"/>
-      <c r="E300" s="1"/>
-      <c r="F300" s="1"/>
-      <c r="G300" s="1"/>
-      <c r="H300" s="1"/>
-      <c r="I300" s="1"/>
-      <c r="P300" s="1"/>
+      <c r="D300" s="39"/>
+      <c r="E300" s="39"/>
+      <c r="F300" s="41"/>
+      <c r="G300" s="39"/>
+      <c r="H300" s="37"/>
+      <c r="I300" s="39"/>
+      <c r="J300" s="39"/>
+      <c r="K300" s="39"/>
+      <c r="L300" s="39"/>
+      <c r="M300" s="39"/>
+      <c r="N300" s="39"/>
+      <c r="O300" s="39"/>
+      <c r="P300" s="39"/>
     </row>
     <row r="301" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D301" s="15"/>
+      <c r="D301" s="14"/>
       <c r="E301" s="1"/>
       <c r="F301" s="1"/>
       <c r="G301" s="1"/>
-      <c r="H301" s="1"/>
+      <c r="H301" s="37"/>
       <c r="I301" s="1"/>
       <c r="P301" s="1"/>
     </row>
     <row r="302" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="F302" s="12"/>
-    </row>
-    <row r="303" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="F303" s="1"/>
+      <c r="D302" s="14"/>
+      <c r="E302" s="1"/>
+      <c r="F302" s="1"/>
+      <c r="G302" s="1"/>
+      <c r="H302" s="37"/>
+      <c r="I302" s="1"/>
+      <c r="P302" s="1"/>
+    </row>
+    <row r="303" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B303" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C303" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="D303" s="39"/>
+      <c r="E303" s="39"/>
+      <c r="G303" s="39"/>
+      <c r="H303" s="33"/>
+      <c r="I303" s="39"/>
+      <c r="J303" s="39"/>
+      <c r="K303" s="39"/>
+      <c r="L303" s="39"/>
+      <c r="M303" s="39"/>
+      <c r="N303" s="39"/>
+      <c r="O303" s="39"/>
+      <c r="P303" s="39"/>
     </row>
     <row r="304" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D304" s="14"/>
+      <c r="E304" s="1"/>
       <c r="F304" s="1"/>
-    </row>
-    <row r="305" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F305" s="12"/>
-    </row>
-    <row r="306" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F306" s="1"/>
-    </row>
-    <row r="307" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="G304" s="1"/>
+      <c r="H304" s="33"/>
+      <c r="I304" s="1"/>
+      <c r="P304" s="1"/>
+    </row>
+    <row r="305" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D305" s="14"/>
+      <c r="E305" s="1"/>
+      <c r="F305" s="1"/>
+      <c r="G305" s="1"/>
+      <c r="H305" s="32"/>
+      <c r="I305" s="1"/>
+      <c r="P305" s="1"/>
+    </row>
+    <row r="306" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B306" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="C306" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="D306" s="39"/>
+      <c r="E306" s="39"/>
+      <c r="F306" s="39"/>
+      <c r="G306" s="39"/>
+      <c r="H306" s="39"/>
+      <c r="I306" s="39"/>
+      <c r="J306" s="39"/>
+      <c r="K306" s="39"/>
+      <c r="L306" s="39"/>
+      <c r="M306" s="39"/>
+      <c r="N306" s="39"/>
+      <c r="O306" s="39"/>
+      <c r="P306" s="39"/>
+    </row>
+    <row r="307" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D307" s="14"/>
+      <c r="E307" s="1"/>
       <c r="F307" s="1"/>
+      <c r="G307" s="1"/>
+      <c r="H307" s="1"/>
+      <c r="I307" s="1"/>
+      <c r="P307" s="1"/>
+    </row>
+    <row r="308" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D308" s="14"/>
+      <c r="E308" s="1"/>
+      <c r="F308" s="1"/>
+      <c r="G308" s="1"/>
+      <c r="H308" s="1"/>
+      <c r="I308" s="1"/>
+      <c r="P308" s="1"/>
+    </row>
+    <row r="309" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="F309" s="39"/>
+    </row>
+    <row r="310" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="F310" s="1"/>
+    </row>
+    <row r="311" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="F311" s="1"/>
+    </row>
+    <row r="312" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="F312" s="39"/>
+    </row>
+    <row r="313" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="F313" s="1"/>
+    </row>
+    <row r="314" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="F314" s="1"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatRows="0" insertRows="0" insertHyperlinks="0" deleteRows="0" sort="0" autoFilter="0"/>
@@ -8770,29 +8859,29 @@
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="9">
-    <dataValidation allowBlank="1" showInputMessage="1" sqref="C11 C14 C17 C20 C23 C26 C29 C32 C35 C231 C293 C296 C299" xr:uid="{5DA7423F-1D1C-4F75-8AE0-92D87965AC10}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Object Code value" error="The Object code value shall be:_x000a_VARIABLE_x000a_RECORD_x000a_ARRAY" sqref="C12:C13 C15:C16 C18:C19 C21:C22 C24:C25 C27:C28 C30:C31 C33:C34 C294:C295 C297:C298 C300:C312 C36:C230 C232:C292" xr:uid="{702A3A7B-BC29-40EC-81C7-6AA43C36CDFB}">
+    <dataValidation allowBlank="1" showInputMessage="1" sqref="C11 C14 C17 C20 C23 C26 C29 C32 C35 C238 C300 C303 C306" xr:uid="{41153E27-09CA-4044-BD99-80B678CECC68}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Object Code value" error="The Object code value shall be:_x000a_VARIABLE_x000a_RECORD_x000a_ARRAY" sqref="C12:C13 C15:C16 C18:C19 C21:C22 C24:C25 C27:C28 C30:C31 C33:C34 C239:C299 C301:C302 C304:C305 C307:C319 C36:C237" xr:uid="{3D7375DF-EBAC-4EE7-9718-D9778BD47EA1}">
       <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Category" error="The value for the entry category shall be _x000a_M : (mandatory)_x000a_O : (optional) _x000a_C : (conditional)" sqref="J36 J12:J13 J15:J16 J18:J19 J21:J22 J24:J25 J27:J28 J30:J31 J33:J34 J294:J295 J297:J298 J300:J312 J40:J230 J232:J292" xr:uid="{123B347C-1D31-4802-ADF4-E512D1B26BF5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Category" error="The value for the entry category shall be _x000a_M : (mandatory)_x000a_O : (optional) _x000a_C : (conditional)" sqref="J36 J12:J13 J15:J16 J18:J19 J21:J22 J24:J25 J27:J28 J30:J31 J33:J34 J239:J299 J301:J302 J304:J305 J307:J319 J40:J237" xr:uid="{67B41DFD-B19D-484F-BB98-77E21A371F35}">
       <formula1>"M,O,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Backup/Setting Flag" error="The entry flag shall be_x000a_B : (Backup)_x000a_S : (Setting)" sqref="K36 K12:K13 K15:K16 K18:K19 K21:K22 K24:K25 K27:K28 K30:K31 K33:K34 K294:K295 K297:K298 K300:K312 K40:K230 K232:K292" xr:uid="{F8545A4C-2A61-48E3-A0E1-A9DBE93A4389}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Backup/Setting Flag" error="The entry flag shall be_x000a_B : (Backup)_x000a_S : (Setting)" sqref="K36 K12:K13 K15:K16 K18:K19 K21:K22 K24:K25 K27:K28 K30:K31 K33:K34 K239:K299 K301:K302 K304:K305 K307:K319 K40:K237" xr:uid="{41BF57B2-2710-42E6-B6F2-B25DBB151446}">
       <formula1>"B,S"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M36:O36 M12:O13 M18:O19 M24:O25 M30:O31 M297:O298 M15:O16 M21:O22 M27:O28 M33:O34 M294:O295 M300:O301 M40:O230 M232:O292" xr:uid="{FBDEAF93-3444-4530-B6BC-26E68F08C5ED}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M36:O36 M12:O13 M18:O19 M24:O25 M30:O31 M301:O302 M307:O308 M15:O16 M21:O22 M27:O28 M33:O34 M304:O305 M239:O299 M40:O237" xr:uid="{F39DA7B7-CC86-47FA-90CD-799CDF9A8874}">
       <formula1>"rx,tx"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C313:C1152" xr:uid="{DF92CF7D-AAE5-412D-9103-46A0E14DD1A7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C320:C1159" xr:uid="{3F0E3A1C-3554-40C8-8339-F93563CD6D55}">
       <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J37:J39" xr:uid="{426C70AC-64DA-4983-8043-0BFDAA70072A}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J37:J39" xr:uid="{92A7682C-F1B4-4AA7-89F4-A1DFCC4F81E2}">
       <formula1>"M,O,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K37:K39" xr:uid="{FABB97B0-E68D-44B3-A0F8-862624A747E6}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K37:K39" xr:uid="{5B70A601-E042-4390-B9AF-AE47631C2108}">
       <formula1>"B,S"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M37:O39" xr:uid="{B9DC3126-34A9-4A84-9926-A3097CCAFE5F}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M37:O39" xr:uid="{55E9B94C-F9C0-4ADF-9C15-8621DB4A435C}">
       <formula1>"rx,tx"</formula1>
     </dataValidation>
   </dataValidations>

--- a/ArmCoreV1_QSPI/SSCProject/lan9252_app.xlsx
+++ b/ArmCoreV1_QSPI/SSCProject/lan9252_app.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WORK\arm_core_develop\bgm_arm_io_develop\FW-ArmCore\ArmCoreV1_QSPI\SSCProject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhong\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <workbookProtection lockStructure="1"/>
@@ -16,8 +16,8 @@
     <sheet name="Profile" sheetId="11" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Profile!$B$10:$P$76</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Profile!$B$1:$P$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Profile!$B$10:$P$93</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Profile!$B$1:$P$94</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="119">
   <si>
     <t>Device Profile:</t>
   </si>
@@ -385,6 +385,423 @@
   </si>
   <si>
     <r>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nU16_NotReadyEvent</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>U</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DINT</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>In</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>U32_WaringInterlock</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nU32_MinorInterlock</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InU32_SeriousInterlock</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EAL</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nF_PrimaryDoseTotalActual</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nF_SecondaryDoseTotalActual</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nF_PrimaryDoseRateActual</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nF_SecondaryDoseRateActual</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RM IO FSM State</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RM IO Interlock</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InU32_DoseAInterlock</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>InU32_Dose</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Interlock</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>DOSEA</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>DOSEB</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>DOSEB</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>REAL</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InU8_DoseAFsmState</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InU8_DoseBFsmState</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>U</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DINT</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EAL</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>OutU8_RequireState</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>O</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>utU8_BeamId</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>InU8_BeamI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>d</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>O</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>utU16_RadiationIndex</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EAL</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>O</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>utF_GantryPosition</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>UDINT</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>UDINT</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>OutU32_InterlockOverride</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>OutU32_UnreadyOveride</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>REAL</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InF_BeamOnTime</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ARM IO First Trigger Out start count </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>UDINT</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InU32_AfcState</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>UDINT</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InU32_DoseAErrorCode</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InU32_DoseBErrorCode</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
       <t>U</t>
     </r>
     <r>
@@ -402,7 +819,7 @@
   </si>
   <si>
     <r>
-      <t>I</t>
+      <t>U</t>
     </r>
     <r>
       <rPr>
@@ -413,13 +830,21 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>nU16_NotReadyEvent</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>U</t>
+      <t>SINT</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>USINT</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InF_AfcPositionCurrent</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>0</t>
     </r>
     <r>
       <rPr>
@@ -430,13 +855,13 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>DINT</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>In</t>
+      <t>: stop  1: run</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>0</t>
     </r>
     <r>
       <rPr>
@@ -447,9 +872,28 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>U32_WaringInterlock</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+      <t>: no fault  1: fault</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InU8_EpsFaultStop</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InU32_EpsFaultCode</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InF_EpsCurrentOutput</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InF_EpsPowerOutput</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>REAL</t>
   </si>
   <si>
     <r>
@@ -464,17 +908,13 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>nU32_MinorInterlock</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>InU32_SeriousInterlock</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>R</t>
+      <t>nF_EpsVersion</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>InF_</t>
     </r>
     <r>
       <rPr>
@@ -485,13 +925,55 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>EAL</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>I</t>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>psVersion</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InU8_EpsRunStatus</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InU8_VpsRunStatus</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InU8_VpsFaultStop</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InU32_VpsFaultCode</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InF_EpsVoltageOutput</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InF_VpsVoltageOutput</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InF_VpsCurrentOutput</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InF_VpsPowerVoltage</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>In</t>
     </r>
     <r>
       <rPr>
@@ -502,311 +984,8 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>nF_PrimaryDoseTotalActual</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>I</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>nF_SecondaryDoseTotalActual</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>I</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>nF_PrimaryDoseRateActual</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>I</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>nF_SecondaryDoseRateActual</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RM IO FSM State</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RM IO Interlock</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>InU32_DoseAInterlock</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>InU32_Dose</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Interlock</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>DOSEA</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>DOSEB</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>DOSEB</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>REAL</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>InU8_DoseAFsmState</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>InU8_DoseBFsmState</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>U</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>DINT</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>EAL</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>InF_AfcPositionCurrent</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>OutU8_RequireState</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>O</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>utU8_BeamId</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>InU8_BeamI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>d</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>O</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>utU16_RadiationIndex</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>EAL</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>O</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>utF_GantryPosition</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>UDINT</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>UDINT</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>OutU32_InterlockOverride</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>OutU32_UnreadyOveride</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>REAL</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>InF_BeamOnTime</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">ARM IO First Trigger Out start count </t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>UDINT</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>InU32_AfcState</t>
+      <t>F_SF6Pressure</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1257,7 +1436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T927"/>
+  <dimension ref="A1:T944"/>
   <sheetFormatPr defaultColWidth="10.7265625" defaultRowHeight="14" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="3.81640625" style="2" customWidth="1"/>
@@ -2062,7 +2241,7 @@
       <c r="N37" s="3"/>
       <c r="O37" s="3"/>
       <c r="P37" s="21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38" spans="1:16" customFormat="1">
@@ -2076,7 +2255,7 @@
         <v>42</v>
       </c>
       <c r="F38" s="21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G38" s="11"/>
       <c r="H38" s="11"/>
@@ -2121,10 +2300,10 @@
         <v>4</v>
       </c>
       <c r="E40" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="F40" s="21" t="s">
         <v>57</v>
-      </c>
-      <c r="F40" s="21" t="s">
-        <v>58</v>
       </c>
       <c r="G40" s="11"/>
       <c r="H40" s="11"/>
@@ -2145,10 +2324,10 @@
         <v>5</v>
       </c>
       <c r="E41" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="F41" s="21" t="s">
         <v>59</v>
-      </c>
-      <c r="F41" s="21" t="s">
-        <v>60</v>
       </c>
       <c r="G41" s="11"/>
       <c r="H41" s="11"/>
@@ -2169,10 +2348,10 @@
         <v>6</v>
       </c>
       <c r="E42" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F42" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G42" s="11"/>
       <c r="H42" s="11"/>
@@ -2193,10 +2372,10 @@
         <v>7</v>
       </c>
       <c r="E43" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F43" s="21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G43" s="11"/>
       <c r="H43" s="11"/>
@@ -2208,7 +2387,7 @@
       <c r="N43" s="3"/>
       <c r="O43" s="3"/>
       <c r="P43" s="21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44" spans="1:16" customFormat="1">
@@ -2219,10 +2398,10 @@
         <v>8</v>
       </c>
       <c r="E44" s="21" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F44" s="21" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G44" s="11"/>
       <c r="H44" s="11"/>
@@ -2234,7 +2413,7 @@
       <c r="N44" s="3"/>
       <c r="O44" s="3"/>
       <c r="P44" s="21" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="45" spans="1:16" customFormat="1">
@@ -2245,10 +2424,10 @@
         <v>9</v>
       </c>
       <c r="E45" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="F45" s="21" t="s">
         <v>63</v>
-      </c>
-      <c r="F45" s="21" t="s">
-        <v>64</v>
       </c>
       <c r="G45" s="11"/>
       <c r="H45" s="11"/>
@@ -2260,7 +2439,7 @@
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
       <c r="P45" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:16" customFormat="1">
@@ -2271,10 +2450,10 @@
         <v>10</v>
       </c>
       <c r="E46" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F46" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G46" s="11"/>
       <c r="H46" s="11"/>
@@ -2286,7 +2465,7 @@
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
       <c r="P46" s="21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47" spans="1:16" customFormat="1">
@@ -2297,10 +2476,10 @@
         <v>11</v>
       </c>
       <c r="E47" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F47" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G47" s="11"/>
       <c r="H47" s="11"/>
@@ -2312,7 +2491,7 @@
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
       <c r="P47" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="48" spans="1:16" customFormat="1">
@@ -2323,10 +2502,10 @@
         <v>12</v>
       </c>
       <c r="E48" s="21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F48" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G48" s="11"/>
       <c r="H48" s="11"/>
@@ -2338,7 +2517,7 @@
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
       <c r="P48" s="21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="49" spans="1:16" customFormat="1">
@@ -2349,10 +2528,10 @@
         <v>13</v>
       </c>
       <c r="E49" s="21" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="F49" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G49" s="11"/>
       <c r="H49" s="11"/>
@@ -2376,7 +2555,7 @@
         <v>55</v>
       </c>
       <c r="F50" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G50" s="11"/>
       <c r="H50" s="11"/>
@@ -2397,10 +2576,10 @@
         <v>15</v>
       </c>
       <c r="E51" s="21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F51" s="21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G51" s="11"/>
       <c r="H51" s="11"/>
@@ -2421,10 +2600,10 @@
         <v>16</v>
       </c>
       <c r="E52" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F52" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G52" s="11"/>
       <c r="H52" s="11"/>
@@ -2469,10 +2648,10 @@
         <v>18</v>
       </c>
       <c r="E54" s="21" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F54" s="21" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G54" s="11"/>
       <c r="H54" s="11"/>
@@ -2489,9 +2668,15 @@
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
-      <c r="D55" s="16"/>
-      <c r="E55" s="11"/>
-      <c r="F55" s="11"/>
+      <c r="D55" s="16">
+        <v>19</v>
+      </c>
+      <c r="E55" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="F55" s="21" t="s">
+        <v>93</v>
+      </c>
       <c r="G55" s="11"/>
       <c r="H55" s="11"/>
       <c r="I55" s="11"/>
@@ -2507,9 +2692,15 @@
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
-      <c r="D56" s="16"/>
-      <c r="E56" s="11"/>
-      <c r="F56" s="11"/>
+      <c r="D56" s="16">
+        <v>20</v>
+      </c>
+      <c r="E56" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="F56" s="21" t="s">
+        <v>100</v>
+      </c>
       <c r="G56" s="11"/>
       <c r="H56" s="11"/>
       <c r="I56" s="11"/>
@@ -2521,40 +2712,42 @@
       <c r="O56" s="3"/>
       <c r="P56" s="11"/>
     </row>
-    <row r="57" spans="1:16" s="1" customFormat="1">
-      <c r="A57" s="11"/>
-      <c r="B57" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="C57" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="D57" s="17"/>
-      <c r="E57" s="17"/>
-      <c r="F57" s="17"/>
-      <c r="G57" s="17"/>
-      <c r="H57" s="17"/>
-      <c r="I57" s="17"/>
-      <c r="J57" s="17"/>
-      <c r="K57" s="17"/>
-      <c r="L57" s="17"/>
-      <c r="M57" s="17"/>
-      <c r="N57" s="17"/>
-      <c r="O57" s="17"/>
-      <c r="P57" s="17"/>
-    </row>
-    <row r="58" spans="1:16">
+    <row r="57" spans="1:16" customFormat="1">
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="16">
+        <v>21</v>
+      </c>
+      <c r="E57" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="F57" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="G57" s="11"/>
+      <c r="H57" s="11"/>
+      <c r="I57" s="11"/>
+      <c r="J57" s="3"/>
+      <c r="K57" s="3"/>
+      <c r="L57" s="3"/>
+      <c r="M57" s="3"/>
+      <c r="N57" s="3"/>
+      <c r="O57" s="3"/>
+      <c r="P57" s="11"/>
+    </row>
+    <row r="58" spans="1:16" customFormat="1">
       <c r="A58" s="3"/>
-      <c r="B58" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D58" s="16"/>
-      <c r="E58" s="11"/>
-      <c r="F58" s="11" t="s">
-        <v>47</v>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="16">
+        <v>22</v>
+      </c>
+      <c r="E58" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="F58" s="21" t="s">
+        <v>110</v>
       </c>
       <c r="G58" s="11"/>
       <c r="H58" s="11"/>
@@ -2565,20 +2758,22 @@
       <c r="M58" s="3"/>
       <c r="N58" s="3"/>
       <c r="O58" s="3"/>
-      <c r="P58" s="11"/>
+      <c r="P58" s="21" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="59" spans="1:16" customFormat="1">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
       <c r="D59" s="16">
-        <v>1</v>
-      </c>
-      <c r="E59" s="11" t="s">
-        <v>42</v>
+        <v>23</v>
+      </c>
+      <c r="E59" s="21" t="s">
+        <v>99</v>
       </c>
       <c r="F59" s="21" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="G59" s="11"/>
       <c r="H59" s="11"/>
@@ -2589,20 +2784,22 @@
       <c r="M59" s="3"/>
       <c r="N59" s="3"/>
       <c r="O59" s="3"/>
-      <c r="P59" s="11"/>
+      <c r="P59" s="21" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="60" spans="1:16" customFormat="1">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
       <c r="D60" s="16">
-        <v>2</v>
-      </c>
-      <c r="E60" s="11" t="s">
-        <v>42</v>
+        <v>24</v>
+      </c>
+      <c r="E60" s="21" t="s">
+        <v>85</v>
       </c>
       <c r="F60" s="21" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="G60" s="11"/>
       <c r="H60" s="11"/>
@@ -2613,20 +2810,20 @@
       <c r="M60" s="3"/>
       <c r="N60" s="3"/>
       <c r="O60" s="3"/>
-      <c r="P60" s="11"/>
+      <c r="P60" s="21"/>
     </row>
     <row r="61" spans="1:16" customFormat="1">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
       <c r="D61" s="16">
-        <v>3</v>
-      </c>
-      <c r="E61" s="11" t="s">
-        <v>43</v>
+        <v>25</v>
+      </c>
+      <c r="E61" s="21" t="s">
+        <v>74</v>
       </c>
       <c r="F61" s="21" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="G61" s="11"/>
       <c r="H61" s="11"/>
@@ -2644,13 +2841,13 @@
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
       <c r="D62" s="16">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E62" s="21" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="F62" s="21" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="G62" s="11"/>
       <c r="H62" s="11"/>
@@ -2668,13 +2865,13 @@
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
       <c r="D63" s="16">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="E63" s="21" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="F63" s="21" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="G63" s="11"/>
       <c r="H63" s="11"/>
@@ -2692,13 +2889,13 @@
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
       <c r="D64" s="16">
-        <v>6</v>
-      </c>
-      <c r="E64" s="21" t="s">
-        <v>85</v>
+        <v>28</v>
+      </c>
+      <c r="E64" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="F64" s="21" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="G64" s="11"/>
       <c r="H64" s="11"/>
@@ -2715,9 +2912,15 @@
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
-      <c r="D65" s="16"/>
-      <c r="E65" s="11"/>
-      <c r="F65" s="11"/>
+      <c r="D65" s="16">
+        <v>29</v>
+      </c>
+      <c r="E65" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="F65" s="21" t="s">
+        <v>111</v>
+      </c>
       <c r="G65" s="11"/>
       <c r="H65" s="11"/>
       <c r="I65" s="11"/>
@@ -2733,9 +2936,15 @@
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
-      <c r="D66" s="16"/>
-      <c r="E66" s="11"/>
-      <c r="F66" s="11"/>
+      <c r="D66" s="16">
+        <v>30</v>
+      </c>
+      <c r="E66" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="F66" s="21" t="s">
+        <v>112</v>
+      </c>
       <c r="G66" s="11"/>
       <c r="H66" s="11"/>
       <c r="I66" s="11"/>
@@ -2751,9 +2960,15 @@
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
-      <c r="D67" s="16"/>
-      <c r="E67" s="11"/>
-      <c r="F67" s="11"/>
+      <c r="D67" s="16">
+        <v>31</v>
+      </c>
+      <c r="E67" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="F67" s="21" t="s">
+        <v>113</v>
+      </c>
       <c r="G67" s="11"/>
       <c r="H67" s="11"/>
       <c r="I67" s="11"/>
@@ -2765,35 +2980,43 @@
       <c r="O67" s="3"/>
       <c r="P67" s="11"/>
     </row>
-    <row r="68" spans="1:16" s="1" customFormat="1">
-      <c r="A68" s="11"/>
-      <c r="B68" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="C68" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="D68" s="17"/>
-      <c r="E68" s="17"/>
-      <c r="F68" s="18"/>
-      <c r="G68" s="17"/>
-      <c r="H68" s="17"/>
-      <c r="I68" s="17"/>
-      <c r="J68" s="17"/>
-      <c r="K68" s="17"/>
-      <c r="L68" s="17"/>
-      <c r="M68" s="17"/>
-      <c r="N68" s="17"/>
-      <c r="O68" s="17"/>
-      <c r="P68" s="17"/>
-    </row>
-    <row r="69" spans="1:16">
+    <row r="68" spans="1:16" customFormat="1">
+      <c r="A68" s="3"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="16">
+        <v>32</v>
+      </c>
+      <c r="E68" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="F68" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="G68" s="11"/>
+      <c r="H68" s="11"/>
+      <c r="I68" s="11"/>
+      <c r="J68" s="3"/>
+      <c r="K68" s="3"/>
+      <c r="L68" s="3"/>
+      <c r="M68" s="3"/>
+      <c r="N68" s="3"/>
+      <c r="O68" s="3"/>
+      <c r="P68" s="11"/>
+    </row>
+    <row r="69" spans="1:16" customFormat="1">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
-      <c r="D69" s="16"/>
-      <c r="E69" s="11"/>
-      <c r="F69" s="11"/>
+      <c r="D69" s="16">
+        <v>33</v>
+      </c>
+      <c r="E69" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="F69" s="21" t="s">
+        <v>116</v>
+      </c>
       <c r="G69" s="11"/>
       <c r="H69" s="11"/>
       <c r="I69" s="11"/>
@@ -2805,13 +3028,19 @@
       <c r="O69" s="3"/>
       <c r="P69" s="11"/>
     </row>
-    <row r="70" spans="1:16">
+    <row r="70" spans="1:16" customFormat="1">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
-      <c r="D70" s="16"/>
-      <c r="E70" s="11"/>
-      <c r="F70" s="11"/>
+      <c r="D70" s="16">
+        <v>34</v>
+      </c>
+      <c r="E70" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="F70" s="21" t="s">
+        <v>117</v>
+      </c>
       <c r="G70" s="11"/>
       <c r="H70" s="11"/>
       <c r="I70" s="11"/>
@@ -2823,34 +3052,36 @@
       <c r="O70" s="3"/>
       <c r="P70" s="11"/>
     </row>
-    <row r="71" spans="1:16" s="1" customFormat="1">
-      <c r="A71" s="11"/>
-      <c r="B71" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C71" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D71" s="17"/>
-      <c r="E71" s="17"/>
-      <c r="F71" s="11"/>
-      <c r="G71" s="17"/>
-      <c r="H71" s="17"/>
-      <c r="I71" s="17"/>
-      <c r="J71" s="17"/>
-      <c r="K71" s="17"/>
-      <c r="L71" s="17"/>
-      <c r="M71" s="17"/>
-      <c r="N71" s="17"/>
-      <c r="O71" s="17"/>
-      <c r="P71" s="17"/>
-    </row>
-    <row r="72" spans="1:16">
+    <row r="71" spans="1:16" customFormat="1">
+      <c r="A71" s="3"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="16">
+        <v>35</v>
+      </c>
+      <c r="E71" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="F71" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="G71" s="11"/>
+      <c r="H71" s="11"/>
+      <c r="I71" s="11"/>
+      <c r="J71" s="3"/>
+      <c r="K71" s="3"/>
+      <c r="L71" s="3"/>
+      <c r="M71" s="3"/>
+      <c r="N71" s="3"/>
+      <c r="O71" s="3"/>
+      <c r="P71" s="11"/>
+    </row>
+    <row r="72" spans="1:16" customFormat="1">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
       <c r="D72" s="16"/>
-      <c r="E72" s="11"/>
+      <c r="E72" s="21"/>
       <c r="F72" s="11"/>
       <c r="G72" s="11"/>
       <c r="H72" s="11"/>
@@ -2863,7 +3094,7 @@
       <c r="O72" s="3"/>
       <c r="P72" s="11"/>
     </row>
-    <row r="73" spans="1:16">
+    <row r="73" spans="1:16" customFormat="1">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -2884,10 +3115,10 @@
     <row r="74" spans="1:16" s="1" customFormat="1">
       <c r="A74" s="11"/>
       <c r="B74" s="17" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C74" s="17" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D74" s="17"/>
       <c r="E74" s="17"/>
@@ -2905,11 +3136,17 @@
     </row>
     <row r="75" spans="1:16">
       <c r="A75" s="3"/>
-      <c r="B75" s="3"/>
-      <c r="C75" s="3"/>
+      <c r="B75" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="D75" s="16"/>
       <c r="E75" s="11"/>
-      <c r="F75" s="11"/>
+      <c r="F75" s="11" t="s">
+        <v>47</v>
+      </c>
       <c r="G75" s="11"/>
       <c r="H75" s="11"/>
       <c r="I75" s="11"/>
@@ -2921,13 +3158,19 @@
       <c r="O75" s="3"/>
       <c r="P75" s="11"/>
     </row>
-    <row r="76" spans="1:16">
+    <row r="76" spans="1:16" customFormat="1">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
-      <c r="D76" s="16"/>
-      <c r="E76" s="11"/>
-      <c r="F76" s="11"/>
+      <c r="D76" s="16">
+        <v>1</v>
+      </c>
+      <c r="E76" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F76" s="21" t="s">
+        <v>79</v>
+      </c>
       <c r="G76" s="11"/>
       <c r="H76" s="11"/>
       <c r="I76" s="11"/>
@@ -2939,283 +3182,580 @@
       <c r="O76" s="3"/>
       <c r="P76" s="11"/>
     </row>
-    <row r="77" spans="1:16">
+    <row r="77" spans="1:16" customFormat="1">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
-      <c r="F77" s="17"/>
-      <c r="G77" s="3"/>
-      <c r="H77" s="3"/>
-      <c r="I77" s="3"/>
+      <c r="D77" s="16">
+        <v>2</v>
+      </c>
+      <c r="E77" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F77" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="G77" s="11"/>
+      <c r="H77" s="11"/>
+      <c r="I77" s="11"/>
       <c r="J77" s="3"/>
       <c r="K77" s="3"/>
       <c r="L77" s="3"/>
       <c r="M77" s="3"/>
       <c r="N77" s="3"/>
       <c r="O77" s="3"/>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="78" spans="1:16">
+      <c r="P77" s="11"/>
+    </row>
+    <row r="78" spans="1:16" customFormat="1">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
-      <c r="F78" s="11"/>
-      <c r="G78" s="3"/>
-      <c r="H78" s="3"/>
-      <c r="I78" s="3"/>
+      <c r="D78" s="16">
+        <v>3</v>
+      </c>
+      <c r="E78" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F78" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="G78" s="11"/>
+      <c r="H78" s="11"/>
+      <c r="I78" s="11"/>
       <c r="J78" s="3"/>
       <c r="K78" s="3"/>
       <c r="L78" s="3"/>
       <c r="M78" s="3"/>
       <c r="N78" s="3"/>
       <c r="O78" s="3"/>
-      <c r="P78" s="3"/>
-    </row>
-    <row r="79" spans="1:16">
+      <c r="P78" s="11"/>
+    </row>
+    <row r="79" spans="1:16" customFormat="1">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
-      <c r="D79" s="3"/>
-      <c r="E79" s="3"/>
-      <c r="F79" s="11"/>
-      <c r="G79" s="3"/>
-      <c r="H79" s="3"/>
-      <c r="I79" s="3"/>
+      <c r="D79" s="16">
+        <v>4</v>
+      </c>
+      <c r="E79" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="F79" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="G79" s="11"/>
+      <c r="H79" s="11"/>
+      <c r="I79" s="11"/>
       <c r="J79" s="3"/>
       <c r="K79" s="3"/>
       <c r="L79" s="3"/>
       <c r="M79" s="3"/>
       <c r="N79" s="3"/>
       <c r="O79" s="3"/>
-      <c r="P79" s="3"/>
-    </row>
-    <row r="80" spans="1:16">
+      <c r="P79" s="11"/>
+    </row>
+    <row r="80" spans="1:16" customFormat="1">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
-      <c r="D80" s="3"/>
-      <c r="E80" s="3"/>
-      <c r="F80" s="17"/>
-      <c r="G80" s="3"/>
-      <c r="H80" s="3"/>
-      <c r="I80" s="3"/>
+      <c r="D80" s="16">
+        <v>5</v>
+      </c>
+      <c r="E80" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="F80" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="G80" s="11"/>
+      <c r="H80" s="11"/>
+      <c r="I80" s="11"/>
       <c r="J80" s="3"/>
       <c r="K80" s="3"/>
       <c r="L80" s="3"/>
       <c r="M80" s="3"/>
       <c r="N80" s="3"/>
       <c r="O80" s="3"/>
-      <c r="P80" s="3"/>
-    </row>
-    <row r="81" spans="1:16">
+      <c r="P80" s="11"/>
+    </row>
+    <row r="81" spans="1:16" customFormat="1">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
-      <c r="D81" s="3"/>
-      <c r="E81" s="3"/>
-      <c r="F81" s="11"/>
-      <c r="G81" s="3"/>
-      <c r="H81" s="3"/>
-      <c r="I81" s="3"/>
+      <c r="D81" s="16">
+        <v>6</v>
+      </c>
+      <c r="E81" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="F81" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="G81" s="11"/>
+      <c r="H81" s="11"/>
+      <c r="I81" s="11"/>
       <c r="J81" s="3"/>
       <c r="K81" s="3"/>
       <c r="L81" s="3"/>
       <c r="M81" s="3"/>
       <c r="N81" s="3"/>
       <c r="O81" s="3"/>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="1:16">
+      <c r="P81" s="11"/>
+    </row>
+    <row r="82" spans="1:16" customFormat="1">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
-      <c r="D82" s="3"/>
-      <c r="E82" s="3"/>
+      <c r="D82" s="16"/>
+      <c r="E82" s="11"/>
       <c r="F82" s="11"/>
-      <c r="G82" s="3"/>
-      <c r="H82" s="3"/>
-      <c r="I82" s="3"/>
+      <c r="G82" s="11"/>
+      <c r="H82" s="11"/>
+      <c r="I82" s="11"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-      <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="1:16">
+      <c r="P82" s="11"/>
+    </row>
+    <row r="83" spans="1:16" customFormat="1">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
-      <c r="D83" s="3"/>
-      <c r="E83" s="3"/>
-      <c r="F83" s="3"/>
-      <c r="G83" s="3"/>
-      <c r="H83" s="3"/>
-      <c r="I83" s="3"/>
+      <c r="D83" s="16"/>
+      <c r="E83" s="11"/>
+      <c r="F83" s="11"/>
+      <c r="G83" s="11"/>
+      <c r="H83" s="11"/>
+      <c r="I83" s="11"/>
       <c r="J83" s="3"/>
       <c r="K83" s="3"/>
       <c r="L83" s="3"/>
       <c r="M83" s="3"/>
       <c r="N83" s="3"/>
       <c r="O83" s="3"/>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="1:16">
+      <c r="P83" s="11"/>
+    </row>
+    <row r="84" spans="1:16" customFormat="1">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
-      <c r="D84" s="3"/>
-      <c r="E84" s="3"/>
-      <c r="F84" s="3"/>
-      <c r="G84" s="3"/>
-      <c r="H84" s="3"/>
-      <c r="I84" s="3"/>
+      <c r="D84" s="16"/>
+      <c r="E84" s="11"/>
+      <c r="F84" s="11"/>
+      <c r="G84" s="11"/>
+      <c r="H84" s="11"/>
+      <c r="I84" s="11"/>
       <c r="J84" s="3"/>
       <c r="K84" s="3"/>
       <c r="L84" s="3"/>
       <c r="M84" s="3"/>
       <c r="N84" s="3"/>
       <c r="O84" s="3"/>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="1:16">
-      <c r="A85" s="3"/>
-      <c r="B85" s="3"/>
-      <c r="C85" s="3"/>
-      <c r="D85" s="3"/>
-      <c r="E85" s="3"/>
-      <c r="F85" s="3"/>
-      <c r="G85" s="3"/>
-      <c r="H85" s="3"/>
-      <c r="I85" s="3"/>
-      <c r="J85" s="3"/>
-      <c r="K85" s="3"/>
-      <c r="L85" s="3"/>
-      <c r="M85" s="3"/>
-      <c r="N85" s="3"/>
-      <c r="O85" s="3"/>
-      <c r="P85" s="3"/>
+      <c r="P84" s="11"/>
+    </row>
+    <row r="85" spans="1:16" s="1" customFormat="1">
+      <c r="A85" s="11"/>
+      <c r="B85" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C85" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D85" s="17"/>
+      <c r="E85" s="17"/>
+      <c r="F85" s="18"/>
+      <c r="G85" s="17"/>
+      <c r="H85" s="17"/>
+      <c r="I85" s="17"/>
+      <c r="J85" s="17"/>
+      <c r="K85" s="17"/>
+      <c r="L85" s="17"/>
+      <c r="M85" s="17"/>
+      <c r="N85" s="17"/>
+      <c r="O85" s="17"/>
+      <c r="P85" s="17"/>
     </row>
     <row r="86" spans="1:16">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
-      <c r="D86" s="3"/>
-      <c r="E86" s="3"/>
-      <c r="F86" s="3"/>
-      <c r="G86" s="3"/>
-      <c r="H86" s="3"/>
-      <c r="I86" s="3"/>
+      <c r="D86" s="16"/>
+      <c r="E86" s="11"/>
+      <c r="F86" s="11"/>
+      <c r="G86" s="11"/>
+      <c r="H86" s="11"/>
+      <c r="I86" s="11"/>
       <c r="J86" s="3"/>
       <c r="K86" s="3"/>
       <c r="L86" s="3"/>
       <c r="M86" s="3"/>
       <c r="N86" s="3"/>
       <c r="O86" s="3"/>
-      <c r="P86" s="3"/>
+      <c r="P86" s="11"/>
     </row>
     <row r="87" spans="1:16">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
-      <c r="D87" s="3"/>
-      <c r="E87" s="3"/>
-      <c r="F87" s="3"/>
-      <c r="G87" s="3"/>
-      <c r="H87" s="3"/>
-      <c r="I87" s="3"/>
+      <c r="D87" s="16"/>
+      <c r="E87" s="11"/>
+      <c r="F87" s="11"/>
+      <c r="G87" s="11"/>
+      <c r="H87" s="11"/>
+      <c r="I87" s="11"/>
       <c r="J87" s="3"/>
       <c r="K87" s="3"/>
       <c r="L87" s="3"/>
       <c r="M87" s="3"/>
       <c r="N87" s="3"/>
       <c r="O87" s="3"/>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="1:16">
-      <c r="C88" s="3"/>
-      <c r="F88" s="3"/>
+      <c r="P87" s="11"/>
+    </row>
+    <row r="88" spans="1:16" s="1" customFormat="1">
+      <c r="A88" s="11"/>
+      <c r="B88" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C88" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D88" s="17"/>
+      <c r="E88" s="17"/>
+      <c r="F88" s="11"/>
+      <c r="G88" s="17"/>
+      <c r="H88" s="17"/>
+      <c r="I88" s="17"/>
+      <c r="J88" s="17"/>
+      <c r="K88" s="17"/>
+      <c r="L88" s="17"/>
+      <c r="M88" s="17"/>
+      <c r="N88" s="17"/>
+      <c r="O88" s="17"/>
+      <c r="P88" s="17"/>
     </row>
     <row r="89" spans="1:16">
+      <c r="A89" s="3"/>
+      <c r="B89" s="3"/>
       <c r="C89" s="3"/>
-      <c r="F89" s="3"/>
+      <c r="D89" s="16"/>
+      <c r="E89" s="11"/>
+      <c r="F89" s="11"/>
+      <c r="G89" s="11"/>
+      <c r="H89" s="11"/>
+      <c r="I89" s="11"/>
+      <c r="J89" s="3"/>
+      <c r="K89" s="3"/>
+      <c r="L89" s="3"/>
+      <c r="M89" s="3"/>
+      <c r="N89" s="3"/>
+      <c r="O89" s="3"/>
+      <c r="P89" s="11"/>
     </row>
     <row r="90" spans="1:16">
+      <c r="A90" s="3"/>
+      <c r="B90" s="3"/>
       <c r="C90" s="3"/>
-      <c r="F90" s="3"/>
-    </row>
-    <row r="91" spans="1:16">
-      <c r="C91" s="3"/>
-      <c r="F91" s="3"/>
+      <c r="D90" s="16"/>
+      <c r="E90" s="11"/>
+      <c r="F90" s="11"/>
+      <c r="G90" s="11"/>
+      <c r="H90" s="11"/>
+      <c r="I90" s="11"/>
+      <c r="J90" s="3"/>
+      <c r="K90" s="3"/>
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+      <c r="P90" s="11"/>
+    </row>
+    <row r="91" spans="1:16" s="1" customFormat="1">
+      <c r="A91" s="11"/>
+      <c r="B91" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C91" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D91" s="17"/>
+      <c r="E91" s="17"/>
+      <c r="F91" s="17"/>
+      <c r="G91" s="17"/>
+      <c r="H91" s="17"/>
+      <c r="I91" s="17"/>
+      <c r="J91" s="17"/>
+      <c r="K91" s="17"/>
+      <c r="L91" s="17"/>
+      <c r="M91" s="17"/>
+      <c r="N91" s="17"/>
+      <c r="O91" s="17"/>
+      <c r="P91" s="17"/>
     </row>
     <row r="92" spans="1:16">
+      <c r="A92" s="3"/>
+      <c r="B92" s="3"/>
       <c r="C92" s="3"/>
-      <c r="F92" s="3"/>
+      <c r="D92" s="16"/>
+      <c r="E92" s="11"/>
+      <c r="F92" s="11"/>
+      <c r="G92" s="11"/>
+      <c r="H92" s="11"/>
+      <c r="I92" s="11"/>
+      <c r="J92" s="3"/>
+      <c r="K92" s="3"/>
+      <c r="L92" s="3"/>
+      <c r="M92" s="3"/>
+      <c r="N92" s="3"/>
+      <c r="O92" s="3"/>
+      <c r="P92" s="11"/>
     </row>
     <row r="93" spans="1:16">
+      <c r="A93" s="3"/>
+      <c r="B93" s="3"/>
       <c r="C93" s="3"/>
-      <c r="F93" s="3"/>
+      <c r="D93" s="16"/>
+      <c r="E93" s="11"/>
+      <c r="F93" s="11"/>
+      <c r="G93" s="11"/>
+      <c r="H93" s="11"/>
+      <c r="I93" s="11"/>
+      <c r="J93" s="3"/>
+      <c r="K93" s="3"/>
+      <c r="L93" s="3"/>
+      <c r="M93" s="3"/>
+      <c r="N93" s="3"/>
+      <c r="O93" s="3"/>
+      <c r="P93" s="11"/>
     </row>
     <row r="94" spans="1:16">
+      <c r="A94" s="3"/>
+      <c r="B94" s="3"/>
       <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="17"/>
+      <c r="G94" s="3"/>
+      <c r="H94" s="3"/>
+      <c r="I94" s="3"/>
+      <c r="J94" s="3"/>
+      <c r="K94" s="3"/>
+      <c r="L94" s="3"/>
+      <c r="M94" s="3"/>
+      <c r="N94" s="3"/>
+      <c r="O94" s="3"/>
+      <c r="P94" s="3"/>
     </row>
     <row r="95" spans="1:16">
+      <c r="A95" s="3"/>
+      <c r="B95" s="3"/>
       <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="11"/>
+      <c r="G95" s="3"/>
+      <c r="H95" s="3"/>
+      <c r="I95" s="3"/>
+      <c r="J95" s="3"/>
+      <c r="K95" s="3"/>
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
     </row>
     <row r="96" spans="1:16">
+      <c r="A96" s="3"/>
+      <c r="B96" s="3"/>
       <c r="C96" s="3"/>
-    </row>
-    <row r="97" spans="3:3">
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="11"/>
+      <c r="G96" s="3"/>
+      <c r="H96" s="3"/>
+      <c r="I96" s="3"/>
+      <c r="J96" s="3"/>
+      <c r="K96" s="3"/>
+      <c r="L96" s="3"/>
+      <c r="M96" s="3"/>
+      <c r="N96" s="3"/>
+      <c r="O96" s="3"/>
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="1:16">
+      <c r="A97" s="3"/>
+      <c r="B97" s="3"/>
       <c r="C97" s="3"/>
-    </row>
-    <row r="98" spans="3:3">
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="17"/>
+      <c r="G97" s="3"/>
+      <c r="H97" s="3"/>
+      <c r="I97" s="3"/>
+      <c r="J97" s="3"/>
+      <c r="K97" s="3"/>
+      <c r="L97" s="3"/>
+      <c r="M97" s="3"/>
+      <c r="N97" s="3"/>
+      <c r="O97" s="3"/>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="1:16">
+      <c r="A98" s="3"/>
+      <c r="B98" s="3"/>
       <c r="C98" s="3"/>
-    </row>
-    <row r="99" spans="3:3">
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="11"/>
+      <c r="G98" s="3"/>
+      <c r="H98" s="3"/>
+      <c r="I98" s="3"/>
+      <c r="J98" s="3"/>
+      <c r="K98" s="3"/>
+      <c r="L98" s="3"/>
+      <c r="M98" s="3"/>
+      <c r="N98" s="3"/>
+      <c r="O98" s="3"/>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="1:16">
+      <c r="A99" s="3"/>
+      <c r="B99" s="3"/>
       <c r="C99" s="3"/>
-    </row>
-    <row r="100" spans="3:3">
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="11"/>
+      <c r="G99" s="3"/>
+      <c r="H99" s="3"/>
+      <c r="I99" s="3"/>
+      <c r="J99" s="3"/>
+      <c r="K99" s="3"/>
+      <c r="L99" s="3"/>
+      <c r="M99" s="3"/>
+      <c r="N99" s="3"/>
+      <c r="O99" s="3"/>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="1:16">
+      <c r="A100" s="3"/>
+      <c r="B100" s="3"/>
       <c r="C100" s="3"/>
-    </row>
-    <row r="101" spans="3:3">
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
+      <c r="H100" s="3"/>
+      <c r="I100" s="3"/>
+      <c r="J100" s="3"/>
+      <c r="K100" s="3"/>
+      <c r="L100" s="3"/>
+      <c r="M100" s="3"/>
+      <c r="N100" s="3"/>
+      <c r="O100" s="3"/>
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="1:16">
+      <c r="A101" s="3"/>
+      <c r="B101" s="3"/>
       <c r="C101" s="3"/>
-    </row>
-    <row r="102" spans="3:3">
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3"/>
+      <c r="H101" s="3"/>
+      <c r="I101" s="3"/>
+      <c r="J101" s="3"/>
+      <c r="K101" s="3"/>
+      <c r="L101" s="3"/>
+      <c r="M101" s="3"/>
+      <c r="N101" s="3"/>
+      <c r="O101" s="3"/>
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="1:16">
+      <c r="A102" s="3"/>
+      <c r="B102" s="3"/>
       <c r="C102" s="3"/>
-    </row>
-    <row r="103" spans="3:3">
+      <c r="D102" s="3"/>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3"/>
+      <c r="H102" s="3"/>
+      <c r="I102" s="3"/>
+      <c r="J102" s="3"/>
+      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
+      <c r="N102" s="3"/>
+      <c r="O102" s="3"/>
+      <c r="P102" s="3"/>
+    </row>
+    <row r="103" spans="1:16">
+      <c r="A103" s="3"/>
+      <c r="B103" s="3"/>
       <c r="C103" s="3"/>
-    </row>
-    <row r="104" spans="3:3">
+      <c r="D103" s="3"/>
+      <c r="E103" s="3"/>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3"/>
+      <c r="H103" s="3"/>
+      <c r="I103" s="3"/>
+      <c r="J103" s="3"/>
+      <c r="K103" s="3"/>
+      <c r="L103" s="3"/>
+      <c r="M103" s="3"/>
+      <c r="N103" s="3"/>
+      <c r="O103" s="3"/>
+      <c r="P103" s="3"/>
+    </row>
+    <row r="104" spans="1:16">
+      <c r="A104" s="3"/>
+      <c r="B104" s="3"/>
       <c r="C104" s="3"/>
-    </row>
-    <row r="105" spans="3:3">
+      <c r="D104" s="3"/>
+      <c r="E104" s="3"/>
+      <c r="F104" s="3"/>
+      <c r="G104" s="3"/>
+      <c r="H104" s="3"/>
+      <c r="I104" s="3"/>
+      <c r="J104" s="3"/>
+      <c r="K104" s="3"/>
+      <c r="L104" s="3"/>
+      <c r="M104" s="3"/>
+      <c r="N104" s="3"/>
+      <c r="O104" s="3"/>
+      <c r="P104" s="3"/>
+    </row>
+    <row r="105" spans="1:16">
       <c r="C105" s="3"/>
-    </row>
-    <row r="106" spans="3:3">
+      <c r="F105" s="3"/>
+    </row>
+    <row r="106" spans="1:16">
       <c r="C106" s="3"/>
-    </row>
-    <row r="107" spans="3:3">
+      <c r="F106" s="3"/>
+    </row>
+    <row r="107" spans="1:16">
       <c r="C107" s="3"/>
-    </row>
-    <row r="108" spans="3:3">
+      <c r="F107" s="3"/>
+    </row>
+    <row r="108" spans="1:16">
       <c r="C108" s="3"/>
-    </row>
-    <row r="109" spans="3:3">
+      <c r="F108" s="3"/>
+    </row>
+    <row r="109" spans="1:16">
       <c r="C109" s="3"/>
-    </row>
-    <row r="110" spans="3:3">
+      <c r="F109" s="3"/>
+    </row>
+    <row r="110" spans="1:16">
       <c r="C110" s="3"/>
-    </row>
-    <row r="111" spans="3:3">
+      <c r="F110" s="3"/>
+    </row>
+    <row r="111" spans="1:16">
       <c r="C111" s="3"/>
     </row>
-    <row r="112" spans="3:3">
+    <row r="112" spans="1:16">
       <c r="C112" s="3"/>
     </row>
     <row r="113" spans="3:3">
@@ -5663,28 +6203,79 @@
     <row r="927" spans="3:3">
       <c r="C927" s="3"/>
     </row>
+    <row r="928" spans="3:3">
+      <c r="C928" s="3"/>
+    </row>
+    <row r="929" spans="3:3">
+      <c r="C929" s="3"/>
+    </row>
+    <row r="930" spans="3:3">
+      <c r="C930" s="3"/>
+    </row>
+    <row r="931" spans="3:3">
+      <c r="C931" s="3"/>
+    </row>
+    <row r="932" spans="3:3">
+      <c r="C932" s="3"/>
+    </row>
+    <row r="933" spans="3:3">
+      <c r="C933" s="3"/>
+    </row>
+    <row r="934" spans="3:3">
+      <c r="C934" s="3"/>
+    </row>
+    <row r="935" spans="3:3">
+      <c r="C935" s="3"/>
+    </row>
+    <row r="936" spans="3:3">
+      <c r="C936" s="3"/>
+    </row>
+    <row r="937" spans="3:3">
+      <c r="C937" s="3"/>
+    </row>
+    <row r="938" spans="3:3">
+      <c r="C938" s="3"/>
+    </row>
+    <row r="939" spans="3:3">
+      <c r="C939" s="3"/>
+    </row>
+    <row r="940" spans="3:3">
+      <c r="C940" s="3"/>
+    </row>
+    <row r="941" spans="3:3">
+      <c r="C941" s="3"/>
+    </row>
+    <row r="942" spans="3:3">
+      <c r="C942" s="3"/>
+    </row>
+    <row r="943" spans="3:3">
+      <c r="C943" s="3"/>
+    </row>
+    <row r="944" spans="3:3">
+      <c r="C944" s="3"/>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatRows="0" insertRows="0" insertHyperlinks="0" deleteRows="0" sort="0" autoFilter="0"/>
-  <autoFilter ref="B10:P76"/>
+  <autoFilter ref="B10:P93"/>
   <mergeCells count="1">
     <mergeCell ref="F1:P6"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="6">
-    <dataValidation allowBlank="1" showInputMessage="1" sqref="C11 C14 C17 C20 C23 C26 C29 C32 C35 C57 C68 C71 C74"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Object Code value" error="The Object code value shall be:_x000a_VARIABLE_x000a_RECORD_x000a_ARRAY" sqref="C12:C13 C15:C16 C18:C19 C21:C22 C24:C25 C27:C28 C30:C31 C33:C34 C58:C67 C69:C70 C72:C73 C75:C87 C36:C56">
+    <dataValidation allowBlank="1" showInputMessage="1" sqref="C11 C14 C17 C20 C23 C26 C29 C32 C35 C74 C85 C88 C91"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Object Code value" error="The Object code value shall be:_x000a_VARIABLE_x000a_RECORD_x000a_ARRAY" sqref="C12:C13 C15:C16 C18:C19 C21:C22 C24:C25 C27:C28 C30:C31 C33:C34 C75:C84 C86:C87 C89:C90 C92:C104 C36:C73">
       <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Category" error="The value for the entry category shall be _x000a_M : (mandatory)_x000a_O : (optional) _x000a_C : (conditional)" sqref="J12:J13 J15:J16 J18:J19 J21:J22 J24:J25 J27:J28 J30:J31 J33:J34 J58:J67 J69:J70 J72:J73 J75:J87 J36:J56">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Category" error="The value for the entry category shall be _x000a_M : (mandatory)_x000a_O : (optional) _x000a_C : (conditional)" sqref="J12:J13 J15:J16 J18:J19 J21:J22 J24:J25 J27:J28 J30:J31 J33:J34 J75:J84 J86:J87 J89:J90 J92:J104 J36:J73">
       <formula1>"M,O,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Backup/Setting Flag" error="The entry flag shall be_x000a_B : (Backup)_x000a_S : (Setting)" sqref="K12:K13 K15:K16 K18:K19 K21:K22 K24:K25 K27:K28 K30:K31 K33:K34 K58:K67 K69:K70 K72:K73 K75:K87 K36:K56">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Backup/Setting Flag" error="The entry flag shall be_x000a_B : (Backup)_x000a_S : (Setting)" sqref="K12:K13 K15:K16 K18:K19 K21:K22 K24:K25 K27:K28 K30:K31 K33:K34 K75:K84 K86:K87 K89:K90 K92:K104 K36:K73">
       <formula1>"B,S"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M12:O13 M18:O19 M24:O25 M30:O31 M69:O70 M75:O76 M15:O16 M21:O22 M27:O28 M33:O34 M72:O73 M58:O67 M36:O56">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M12:O13 M18:O19 M24:O25 M30:O31 M86:O87 M92:O93 M15:O16 M21:O22 M27:O28 M33:O34 M89:O90 M75:O84 M36:O73">
       <formula1>"rx,tx"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C88:C927">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C105:C944">
       <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
     </dataValidation>
   </dataValidations>

--- a/ArmCoreV1_QSPI/SSCProject/lan9252_app.xlsx
+++ b/ArmCoreV1_QSPI/SSCProject/lan9252_app.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SI\project\RTM_ON_NEW\FW-ArmCore\ArmCoreV1_QSPI\SSCProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1924E9D7-6469-48DB-B69E-87FD872B9E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A1685DD-E02A-46AB-94C6-88EFD05D0007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-7730" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="4590" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Profile" sheetId="11" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="328">
   <si>
     <t>Device Profile:</t>
   </si>
@@ -684,213 +684,6 @@
   </si>
   <si>
     <t>InB1_OFF_DI_STAND_BREAKER7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_TREATMENT_ROOM_DOOR_READY </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_CONTROL_ROOM_EMERGENCY </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_CITB_TREATMENT_ROOM_DOOR2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_CITB_EMERGENCY4 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_CONTROL_ROOM_BREAKER1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_UserTreatmentEnable </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_UserHvEnable </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_UserMoveEnable </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_STAND_RESERVE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_STAND_EMERGENCY </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_STAND_BREAKER4 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_TouchGuard </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_reserve0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_STAND_BREAKER3 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_COVER_EMERGENCY4 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_STAND_CONTACTOR1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_COVER_EMERGENCY1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_CONTROL_ROOM_BREAKER3 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_UPS_LOAD_PORT </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_CITB_TREATMENT_ROOM_DOOR1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_CITB_EMERGENCY2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_COVER_DOOR </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_HvKey </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_CONTROL_ROOM_CONTACTOR1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_CITB_EMERGENCY3 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_STAND_CONTACTOR2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_COVER_EMERGENCY3 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_CONTROL_ROOM_BREAKER5 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_UPS_ON_BYPASS </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_STAND_BREAKER5 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_COVER_RESERVE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_CONTROL_ROOM_CONTACTOR2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_CITB_EMERGENCY5 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_CITB_SEARCH_TREATMENT_ROOM </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_CITB_EXTERNAL_TERMINATE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_UPS_LOW_BATT </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_CONTROL_ROOM_BREAKER2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_CONTROL_ROOM_BREAKER4 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_UPS_ON_BATT </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_CITB_EMERGENCY1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_COVER_EMERGENCY2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_STAND_BREAKER6 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_HvEn </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_MV_TreatmentEN </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_KV_TreatmentEN </t>
-  </si>
-  <si>
-    <t>InU16_OFF_DI_tca9535_di_reserve1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DI_GATING </t>
-  </si>
-  <si>
-    <t>BIT7</t>
-  </si>
-  <si>
-    <t>InB7_OFF_DI_reserve2</t>
-  </si>
-  <si>
-    <t>InU8_OFF_DI_reserve3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DO_TreatmentRoomLight </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DO_STAND_RESERVE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DO_Laser </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DO_RadiationIndicator </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DO_ReadyIndicator </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DO_SearchTreatmentRoomRelay </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DO_softwareTouchGuard </t>
-  </si>
-  <si>
-    <t>InB1_OFF_DO_reserve4</t>
-  </si>
-  <si>
-    <t>InU8_OFF_DO_reserve5</t>
-  </si>
-  <si>
-    <t>InU16_OFF_DO_tca9535_do_reserve6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DO_SoftwareMVTreatmentEn </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DO_SoftwareKVTreatmentEn </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DO_softwareMoveEN </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DO_SoftwareHvEn </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DO_TreatmentMotionEnable </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DO_ThreePhasePowerOn </t>
-  </si>
-  <si>
-    <t xml:space="preserve">InB1_OFF_DO_AsuMotionEnable </t>
-  </si>
-  <si>
-    <t>InB1_OFF_DO_reserve7</t>
-  </si>
-  <si>
-    <t>InU8_OFF_DO_reserve8</t>
   </si>
   <si>
     <t>OutU8_Reserved0</t>
@@ -1196,10 +989,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>UNSIGNED8</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>InU8_trm_require_state</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1209,6 +998,219 @@
   </si>
   <si>
     <t>OutU8_reserved2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>InU8_OFF_reserve0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BOOLEAN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_CITB_EMERGENCY2</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_UPS_LOAD_PORT</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_STAND_EMERGENCY</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_TouchGuard</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_HvEn</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_MV_TreatmentEN</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_KV_TreatmentEN</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_STAND_BREAKER3</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_UPS_ON_BYPASS</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_STAND_BREAKER5</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_COVER3</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_POWER_CUT</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_STAND_BREAKER4</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_CITB_TREATMENT_ROOM_DOOR1</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_CITB_TREATMENT_ROOM_DOOR2</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_CITB_EMERGENCY1</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_CITB_SEARCH_TREATMENT_ROOM</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_CONTROL_ROOM_BREAKER1</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_UPS_ON_BATT</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_HvKey</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_STAND_CONTACTOR2</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_CITB_EMERGENCY5</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_UPS_LOW_BATT</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_CONTROL_ROOM_BREAKER2</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_CONTROL_ROOM_BREAKER4</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_COVER1</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_STAND_RESERVE</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_TREATMENT_ROOM_DOOR_READY</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_COVER2</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_STAND_CONTACTOR1</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_COVER4</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_CITB_EMERGENCY4</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_CONTROL_ROOM_BREAKER3</t>
+  </si>
+  <si>
+    <t>InB1_OFF_RTC_WD_OK_IN</t>
+  </si>
+  <si>
+    <t>InU16_OFF_mcp23017_di_reserve</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_GATING</t>
+  </si>
+  <si>
+    <t>BIT7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>InB7_OFF_reserve1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>InU8_OFF_reserve2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>InB1_OFF_DO_RTM_AutoPowerUp</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DO_SearchTreatmentRoomRelay</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DO_Laser</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DO_Power_CUT</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DO_STAND_RESERVE</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DO_TreatmentRoomLight</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DO_RadiationIndicator</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DO_ReadyIndicator</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DO_RTM_SystemShutDown</t>
+  </si>
+  <si>
+    <t>InB7_OFF_reserve3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>InU16_OFF_mcp23017_do_reserve</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>InB1_OFF_DO_SoftwareHvEn</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DO_SoftwareKVTreatmentEn</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DO_SoftwareMVTreatmentEn</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DO_ThreePhasePowerOn</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DO_softwareMoveEN</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DO_TreatmentMotionEnable</t>
+  </si>
+  <si>
+    <t>InB1_OFF_DO_AsuMotionEnable</t>
+  </si>
+  <si>
+    <t>InB1_OFF_reserve4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>InU8_OFF_reserve5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UNSIGNED32</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OutU32_rtm_off_search_timeout</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_CITB_EMERGENCY3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_CONTROL_ROOM_BREAKER5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>InB1_OFF_DI_STAND_BREAKER6</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1522,11 +1524,11 @@
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1837,7 +1839,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T319"/>
+  <dimension ref="A1:T1186"/>
   <sheetFormatPr defaultColWidth="10.7265625" defaultRowHeight="14" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.81640625" style="2" customWidth="1"/>
@@ -1869,19 +1871,19 @@
         <v>1</v>
       </c>
       <c r="E1"/>
-      <c r="F1" s="41" t="s">
-        <v>290</v>
-      </c>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
+      <c r="F1" s="42" t="s">
+        <v>221</v>
+      </c>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="42"/>
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
       <c r="S1" s="6"/>
@@ -1895,17 +1897,17 @@
         <v>3</v>
       </c>
       <c r="E2"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="42"/>
+      <c r="N2" s="42"/>
+      <c r="O2" s="42"/>
+      <c r="P2" s="42"/>
       <c r="Q2" s="6"/>
       <c r="R2" s="6"/>
       <c r="S2" s="6"/>
@@ -1916,17 +1918,17 @@
       <c r="C3" s="5"/>
       <c r="D3"/>
       <c r="E3"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
-      <c r="P3" s="41"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
+      <c r="N3" s="42"/>
+      <c r="O3" s="42"/>
+      <c r="P3" s="42"/>
       <c r="Q3" s="6"/>
       <c r="R3" s="6"/>
       <c r="S3" s="6"/>
@@ -1937,17 +1939,17 @@
       <c r="C4" s="5"/>
       <c r="D4"/>
       <c r="E4"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="41"/>
-      <c r="N4" s="41"/>
-      <c r="O4" s="41"/>
-      <c r="P4" s="41"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="42"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="42"/>
+      <c r="M4" s="42"/>
+      <c r="N4" s="42"/>
+      <c r="O4" s="42"/>
+      <c r="P4" s="42"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
       <c r="S4" s="6"/>
@@ -1958,17 +1960,17 @@
       <c r="C5"/>
       <c r="D5"/>
       <c r="E5"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="41"/>
-      <c r="L5" s="41"/>
-      <c r="M5" s="41"/>
-      <c r="N5" s="41"/>
-      <c r="O5" s="41"/>
-      <c r="P5" s="41"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="42"/>
+      <c r="M5" s="42"/>
+      <c r="N5" s="42"/>
+      <c r="O5" s="42"/>
+      <c r="P5" s="42"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
       <c r="S5" s="6"/>
@@ -1979,17 +1981,17 @@
       <c r="C6"/>
       <c r="D6"/>
       <c r="E6"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="41"/>
-      <c r="O6" s="41"/>
-      <c r="P6" s="41"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="42"/>
+      <c r="M6" s="42"/>
+      <c r="N6" s="42"/>
+      <c r="O6" s="42"/>
+      <c r="P6" s="42"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
       <c r="S6" s="6"/>
@@ -2229,7 +2231,7 @@
         <v>26</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>291</v>
+        <v>222</v>
       </c>
       <c r="D20" s="12"/>
       <c r="E20" s="12"/>
@@ -2307,7 +2309,7 @@
         <v>29</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>292</v>
+        <v>223</v>
       </c>
       <c r="D26" s="12"/>
       <c r="E26" s="12"/>
@@ -2346,7 +2348,7 @@
         <v>30</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>293</v>
+        <v>224</v>
       </c>
       <c r="D29" s="12"/>
       <c r="E29" s="12"/>
@@ -2385,7 +2387,7 @@
         <v>31</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>294</v>
+        <v>225</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="12"/>
@@ -2884,7 +2886,7 @@
         <v>70</v>
       </c>
       <c r="F54" s="20" t="s">
-        <v>295</v>
+        <v>226</v>
       </c>
       <c r="G54" s="26"/>
       <c r="H54" s="1"/>
@@ -2908,7 +2910,7 @@
         <v>70</v>
       </c>
       <c r="F55" s="20" t="s">
-        <v>296</v>
+        <v>227</v>
       </c>
       <c r="G55" s="26"/>
       <c r="H55" s="1"/>
@@ -2932,7 +2934,7 @@
         <v>70</v>
       </c>
       <c r="F56" s="20" t="s">
-        <v>297</v>
+        <v>228</v>
       </c>
       <c r="G56" s="26"/>
       <c r="H56" s="1"/>
@@ -2956,7 +2958,7 @@
         <v>70</v>
       </c>
       <c r="F57" s="20" t="s">
-        <v>298</v>
+        <v>229</v>
       </c>
       <c r="G57" s="26"/>
       <c r="H57" s="1"/>
@@ -2980,7 +2982,7 @@
         <v>70</v>
       </c>
       <c r="F58" s="20" t="s">
-        <v>299</v>
+        <v>230</v>
       </c>
       <c r="G58" s="26"/>
       <c r="H58" s="1"/>
@@ -3004,7 +3006,7 @@
         <v>70</v>
       </c>
       <c r="F59" s="20" t="s">
-        <v>300</v>
+        <v>231</v>
       </c>
       <c r="G59" s="26"/>
       <c r="H59" s="1"/>
@@ -3028,7 +3030,7 @@
         <v>70</v>
       </c>
       <c r="F60" s="20" t="s">
-        <v>301</v>
+        <v>232</v>
       </c>
       <c r="G60" s="26"/>
       <c r="H60" s="1"/>
@@ -3052,7 +3054,7 @@
         <v>70</v>
       </c>
       <c r="F61" s="20" t="s">
-        <v>302</v>
+        <v>233</v>
       </c>
       <c r="G61" s="26"/>
       <c r="H61" s="1"/>
@@ -3076,7 +3078,7 @@
         <v>70</v>
       </c>
       <c r="F62" s="20" t="s">
-        <v>303</v>
+        <v>234</v>
       </c>
       <c r="G62" s="26"/>
       <c r="H62" s="1"/>
@@ -3100,7 +3102,7 @@
         <v>70</v>
       </c>
       <c r="F63" s="20" t="s">
-        <v>304</v>
+        <v>235</v>
       </c>
       <c r="G63" s="26"/>
       <c r="H63" s="1"/>
@@ -3124,7 +3126,7 @@
         <v>70</v>
       </c>
       <c r="F64" s="20" t="s">
-        <v>305</v>
+        <v>236</v>
       </c>
       <c r="G64" s="26"/>
       <c r="H64" s="1"/>
@@ -3148,7 +3150,7 @@
         <v>70</v>
       </c>
       <c r="F65" s="20" t="s">
-        <v>306</v>
+        <v>237</v>
       </c>
       <c r="G65" s="26"/>
       <c r="H65" s="1"/>
@@ -3169,10 +3171,10 @@
         <v>30</v>
       </c>
       <c r="E66" s="20" t="s">
-        <v>307</v>
+        <v>238</v>
       </c>
       <c r="F66" s="20" t="s">
-        <v>308</v>
+        <v>239</v>
       </c>
       <c r="G66" s="26"/>
       <c r="H66" s="1"/>
@@ -3196,7 +3198,7 @@
         <v>70</v>
       </c>
       <c r="F67" s="20" t="s">
-        <v>309</v>
+        <v>240</v>
       </c>
       <c r="G67" s="26"/>
       <c r="H67" s="1"/>
@@ -3316,7 +3318,7 @@
         <v>70</v>
       </c>
       <c r="F72" s="20" t="s">
-        <v>310</v>
+        <v>241</v>
       </c>
       <c r="G72" s="26"/>
       <c r="H72" s="1"/>
@@ -3340,7 +3342,7 @@
         <v>70</v>
       </c>
       <c r="F73" s="20" t="s">
-        <v>311</v>
+        <v>242</v>
       </c>
       <c r="G73" s="26"/>
       <c r="H73" s="1"/>
@@ -3364,7 +3366,7 @@
         <v>70</v>
       </c>
       <c r="F74" s="20" t="s">
-        <v>312</v>
+        <v>243</v>
       </c>
       <c r="G74" s="26"/>
       <c r="H74" s="1"/>
@@ -3388,7 +3390,7 @@
         <v>48</v>
       </c>
       <c r="F75" s="20" t="s">
-        <v>313</v>
+        <v>244</v>
       </c>
       <c r="G75" s="26"/>
       <c r="H75" s="1"/>
@@ -3401,221 +3403,104 @@
       <c r="O75" s="2"/>
       <c r="P75" s="1"/>
     </row>
-    <row r="76" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="18"/>
-      <c r="B76" s="18"/>
-      <c r="C76" s="18"/>
+    <row r="76" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D76" s="20">
         <v>40</v>
       </c>
       <c r="E76" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F76" s="20" t="s">
-        <v>212</v>
-      </c>
-      <c r="G76" s="26"/>
-      <c r="H76" s="1"/>
-      <c r="I76" s="1"/>
-      <c r="J76" s="2"/>
-      <c r="K76" s="2"/>
-      <c r="L76" s="2"/>
-      <c r="M76" s="2"/>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
-      <c r="P76" s="1"/>
-    </row>
-    <row r="77" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="18"/>
-      <c r="B77" s="18"/>
-      <c r="C77" s="18"/>
+        <v>48</v>
+      </c>
+      <c r="F76" s="34" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D77" s="20">
         <v>41</v>
       </c>
       <c r="E77" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F77" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="G77" s="26"/>
-      <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
-      <c r="J77" s="2"/>
-      <c r="K77" s="2"/>
-      <c r="L77" s="2"/>
-      <c r="M77" s="2"/>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
-      <c r="P77" s="1"/>
-    </row>
-    <row r="78" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="18"/>
-      <c r="B78" s="18"/>
-      <c r="C78" s="18"/>
+        <v>263</v>
+      </c>
+      <c r="F77" s="34" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D78" s="20">
         <v>42</v>
       </c>
       <c r="E78" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F78" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="G78" s="26"/>
-      <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="2"/>
-      <c r="K78" s="2"/>
-      <c r="L78" s="2"/>
-      <c r="M78" s="2"/>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
-      <c r="P78" s="1"/>
-    </row>
-    <row r="79" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="18"/>
-      <c r="B79" s="18"/>
-      <c r="C79" s="18"/>
+        <v>263</v>
+      </c>
+      <c r="F78" s="34" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D79" s="20">
         <v>43</v>
       </c>
       <c r="E79" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F79" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="G79" s="26"/>
-      <c r="H79" s="1"/>
-      <c r="I79" s="1"/>
-      <c r="J79" s="2"/>
-      <c r="K79" s="2"/>
-      <c r="L79" s="2"/>
-      <c r="M79" s="2"/>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
-      <c r="P79" s="1"/>
-    </row>
-    <row r="80" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="18"/>
-      <c r="B80" s="18"/>
-      <c r="C80" s="18"/>
+        <v>263</v>
+      </c>
+      <c r="F79" s="34" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D80" s="20">
         <v>44</v>
       </c>
       <c r="E80" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F80" s="20" t="s">
-        <v>216</v>
-      </c>
-      <c r="G80" s="26"/>
-      <c r="H80" s="1"/>
-      <c r="I80" s="1"/>
-      <c r="J80" s="2"/>
-      <c r="K80" s="2"/>
-      <c r="L80" s="2"/>
-      <c r="M80" s="2"/>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
-      <c r="P80" s="1"/>
-    </row>
-    <row r="81" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="18"/>
-      <c r="B81" s="18"/>
-      <c r="C81" s="18"/>
+        <v>263</v>
+      </c>
+      <c r="F80" s="34" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D81" s="20">
         <v>45</v>
       </c>
       <c r="E81" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F81" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="G81" s="26"/>
-      <c r="H81" s="1"/>
-      <c r="I81" s="1"/>
-      <c r="J81" s="2"/>
-      <c r="K81" s="2"/>
-      <c r="L81" s="2"/>
-      <c r="M81" s="2"/>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
-      <c r="P81" s="1"/>
-    </row>
-    <row r="82" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="18"/>
-      <c r="B82" s="18"/>
-      <c r="C82" s="18"/>
+        <v>263</v>
+      </c>
+      <c r="F81" s="34" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D82" s="20">
         <v>46</v>
       </c>
       <c r="E82" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F82" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="G82" s="26"/>
-      <c r="H82" s="1"/>
-      <c r="I82" s="1"/>
-      <c r="J82" s="2"/>
-      <c r="K82" s="2"/>
-      <c r="L82" s="2"/>
-      <c r="M82" s="2"/>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
-      <c r="P82" s="1"/>
-    </row>
-    <row r="83" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="18"/>
-      <c r="B83" s="18"/>
-      <c r="C83" s="18"/>
+        <v>263</v>
+      </c>
+      <c r="F82" s="34" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D83" s="20">
         <v>47</v>
       </c>
       <c r="E83" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F83" s="20" t="s">
-        <v>219</v>
-      </c>
-      <c r="G83" s="26"/>
-      <c r="H83" s="1"/>
-      <c r="I83" s="1"/>
-      <c r="J83" s="2"/>
-      <c r="K83" s="2"/>
-      <c r="L83" s="2"/>
-      <c r="M83" s="2"/>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
-      <c r="P83" s="1"/>
-    </row>
-    <row r="84" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="18"/>
-      <c r="B84" s="18"/>
-      <c r="C84" s="18"/>
+        <v>263</v>
+      </c>
+      <c r="F83" s="34" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D84" s="20">
         <v>48</v>
       </c>
       <c r="E84" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F84" s="20" t="s">
-        <v>220</v>
-      </c>
-      <c r="G84" s="26"/>
-      <c r="H84" s="1"/>
-      <c r="I84" s="1"/>
-      <c r="J84" s="2"/>
-      <c r="K84" s="2"/>
-      <c r="L84" s="2"/>
-      <c r="M84" s="2"/>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
-      <c r="P84" s="1"/>
+        <v>263</v>
+      </c>
+      <c r="F84" s="34" t="s">
+        <v>270</v>
+      </c>
     </row>
     <row r="85" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="18"/>
@@ -3625,10 +3510,10 @@
         <v>49</v>
       </c>
       <c r="E85" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F85" s="20" t="s">
-        <v>221</v>
+        <v>263</v>
+      </c>
+      <c r="F85" s="34" t="s">
+        <v>214</v>
       </c>
       <c r="G85" s="26"/>
       <c r="H85" s="1"/>
@@ -3649,10 +3534,10 @@
         <v>50</v>
       </c>
       <c r="E86" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F86" s="20" t="s">
-        <v>222</v>
+        <v>263</v>
+      </c>
+      <c r="F86" s="34" t="s">
+        <v>271</v>
       </c>
       <c r="G86" s="26"/>
       <c r="H86" s="1"/>
@@ -3673,10 +3558,10 @@
         <v>51</v>
       </c>
       <c r="E87" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F87" s="20" t="s">
-        <v>223</v>
+        <v>263</v>
+      </c>
+      <c r="F87" s="34" t="s">
+        <v>272</v>
       </c>
       <c r="G87" s="26"/>
       <c r="H87" s="1"/>
@@ -3697,10 +3582,10 @@
         <v>52</v>
       </c>
       <c r="E88" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F88" s="20" t="s">
-        <v>224</v>
+        <v>263</v>
+      </c>
+      <c r="F88" s="34" t="s">
+        <v>273</v>
       </c>
       <c r="G88" s="26"/>
       <c r="H88" s="1"/>
@@ -3721,10 +3606,10 @@
         <v>53</v>
       </c>
       <c r="E89" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F89" s="20" t="s">
-        <v>225</v>
+        <v>263</v>
+      </c>
+      <c r="F89" s="34" t="s">
+        <v>325</v>
       </c>
       <c r="G89" s="26"/>
       <c r="H89" s="1"/>
@@ -3745,10 +3630,10 @@
         <v>54</v>
       </c>
       <c r="E90" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F90" s="20" t="s">
-        <v>226</v>
+        <v>263</v>
+      </c>
+      <c r="F90" s="34" t="s">
+        <v>274</v>
       </c>
       <c r="G90" s="26"/>
       <c r="H90" s="1"/>
@@ -3769,10 +3654,10 @@
         <v>55</v>
       </c>
       <c r="E91" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F91" s="20" t="s">
-        <v>227</v>
+        <v>263</v>
+      </c>
+      <c r="F91" s="34" t="s">
+        <v>275</v>
       </c>
       <c r="G91" s="26"/>
       <c r="H91" s="1"/>
@@ -3793,10 +3678,10 @@
         <v>56</v>
       </c>
       <c r="E92" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F92" s="20" t="s">
-        <v>228</v>
+        <v>263</v>
+      </c>
+      <c r="F92" s="34" t="s">
+        <v>276</v>
       </c>
       <c r="G92" s="26"/>
       <c r="H92" s="1"/>
@@ -3817,10 +3702,10 @@
         <v>57</v>
       </c>
       <c r="E93" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F93" s="20" t="s">
-        <v>229</v>
+        <v>263</v>
+      </c>
+      <c r="F93" s="34" t="s">
+        <v>277</v>
       </c>
       <c r="G93" s="26"/>
       <c r="H93" s="1"/>
@@ -3841,10 +3726,10 @@
         <v>58</v>
       </c>
       <c r="E94" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F94" s="20" t="s">
-        <v>230</v>
+        <v>263</v>
+      </c>
+      <c r="F94" s="34" t="s">
+        <v>278</v>
       </c>
       <c r="G94" s="26"/>
       <c r="H94" s="1"/>
@@ -3865,10 +3750,10 @@
         <v>59</v>
       </c>
       <c r="E95" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F95" s="20" t="s">
-        <v>231</v>
+        <v>263</v>
+      </c>
+      <c r="F95" s="34" t="s">
+        <v>279</v>
       </c>
       <c r="G95" s="26"/>
       <c r="H95" s="1"/>
@@ -3889,10 +3774,10 @@
         <v>60</v>
       </c>
       <c r="E96" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F96" s="20" t="s">
-        <v>232</v>
+        <v>263</v>
+      </c>
+      <c r="F96" s="34" t="s">
+        <v>280</v>
       </c>
       <c r="G96" s="26"/>
       <c r="H96" s="1"/>
@@ -3913,10 +3798,10 @@
         <v>61</v>
       </c>
       <c r="E97" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F97" s="20" t="s">
-        <v>233</v>
+        <v>263</v>
+      </c>
+      <c r="F97" s="34" t="s">
+        <v>281</v>
       </c>
       <c r="G97" s="26"/>
       <c r="H97" s="1"/>
@@ -3937,10 +3822,10 @@
         <v>62</v>
       </c>
       <c r="E98" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F98" s="20" t="s">
-        <v>234</v>
+        <v>263</v>
+      </c>
+      <c r="F98" s="34" t="s">
+        <v>282</v>
       </c>
       <c r="G98" s="26"/>
       <c r="H98" s="1"/>
@@ -3961,10 +3846,10 @@
         <v>63</v>
       </c>
       <c r="E99" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F99" s="20" t="s">
-        <v>235</v>
+        <v>263</v>
+      </c>
+      <c r="F99" s="34" t="s">
+        <v>326</v>
       </c>
       <c r="G99" s="26"/>
       <c r="H99" s="1"/>
@@ -3985,10 +3870,10 @@
         <v>64</v>
       </c>
       <c r="E100" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F100" s="20" t="s">
-        <v>236</v>
+        <v>263</v>
+      </c>
+      <c r="F100" s="34" t="s">
+        <v>327</v>
       </c>
       <c r="G100" s="26"/>
       <c r="H100" s="1"/>
@@ -4009,10 +3894,10 @@
         <v>65</v>
       </c>
       <c r="E101" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F101" s="20" t="s">
-        <v>237</v>
+        <v>263</v>
+      </c>
+      <c r="F101" s="34" t="s">
+        <v>285</v>
       </c>
       <c r="G101" s="26"/>
       <c r="H101" s="1"/>
@@ -4033,10 +3918,10 @@
         <v>66</v>
       </c>
       <c r="E102" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F102" s="20" t="s">
-        <v>238</v>
+        <v>263</v>
+      </c>
+      <c r="F102" s="34" t="s">
+        <v>289</v>
       </c>
       <c r="G102" s="26"/>
       <c r="H102" s="1"/>
@@ -4057,10 +3942,10 @@
         <v>67</v>
       </c>
       <c r="E103" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F103" s="20" t="s">
-        <v>239</v>
+        <v>263</v>
+      </c>
+      <c r="F103" s="34" t="s">
+        <v>290</v>
       </c>
       <c r="G103" s="26"/>
       <c r="H103" s="1"/>
@@ -4081,10 +3966,10 @@
         <v>68</v>
       </c>
       <c r="E104" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F104" s="20" t="s">
-        <v>240</v>
+        <v>263</v>
+      </c>
+      <c r="F104" s="34" t="s">
+        <v>291</v>
       </c>
       <c r="G104" s="26"/>
       <c r="H104" s="1"/>
@@ -4105,10 +3990,10 @@
         <v>69</v>
       </c>
       <c r="E105" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F105" s="20" t="s">
-        <v>241</v>
+        <v>263</v>
+      </c>
+      <c r="F105" s="34" t="s">
+        <v>292</v>
       </c>
       <c r="G105" s="26"/>
       <c r="H105" s="1"/>
@@ -4129,10 +4014,10 @@
         <v>70</v>
       </c>
       <c r="E106" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F106" s="20" t="s">
-        <v>242</v>
+        <v>263</v>
+      </c>
+      <c r="F106" s="34" t="s">
+        <v>287</v>
       </c>
       <c r="G106" s="26"/>
       <c r="H106" s="1"/>
@@ -4153,10 +4038,10 @@
         <v>71</v>
       </c>
       <c r="E107" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F107" s="20" t="s">
-        <v>243</v>
+        <v>263</v>
+      </c>
+      <c r="F107" s="34" t="s">
+        <v>288</v>
       </c>
       <c r="G107" s="26"/>
       <c r="H107" s="1"/>
@@ -4177,10 +4062,10 @@
         <v>72</v>
       </c>
       <c r="E108" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F108" s="20" t="s">
-        <v>244</v>
+        <v>263</v>
+      </c>
+      <c r="F108" s="34" t="s">
+        <v>284</v>
       </c>
       <c r="G108" s="26"/>
       <c r="H108" s="1"/>
@@ -4201,10 +4086,10 @@
         <v>73</v>
       </c>
       <c r="E109" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F109" s="20" t="s">
-        <v>245</v>
+        <v>263</v>
+      </c>
+      <c r="F109" s="34" t="s">
+        <v>293</v>
       </c>
       <c r="G109" s="26"/>
       <c r="H109" s="1"/>
@@ -4225,10 +4110,10 @@
         <v>74</v>
       </c>
       <c r="E110" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F110" s="20" t="s">
-        <v>246</v>
+        <v>263</v>
+      </c>
+      <c r="F110" s="34" t="s">
+        <v>286</v>
       </c>
       <c r="G110" s="26"/>
       <c r="H110" s="1"/>
@@ -4249,10 +4134,10 @@
         <v>75</v>
       </c>
       <c r="E111" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F111" s="20" t="s">
-        <v>247</v>
+        <v>263</v>
+      </c>
+      <c r="F111" s="34" t="s">
+        <v>283</v>
       </c>
       <c r="G111" s="26"/>
       <c r="H111" s="1"/>
@@ -4273,10 +4158,10 @@
         <v>76</v>
       </c>
       <c r="E112" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F112" s="20" t="s">
-        <v>248</v>
+        <v>263</v>
+      </c>
+      <c r="F112" s="34" t="s">
+        <v>294</v>
       </c>
       <c r="G112" s="26"/>
       <c r="H112" s="1"/>
@@ -4297,10 +4182,10 @@
         <v>77</v>
       </c>
       <c r="E113" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F113" s="20" t="s">
-        <v>249</v>
+        <v>263</v>
+      </c>
+      <c r="F113" s="34" t="s">
+        <v>295</v>
       </c>
       <c r="G113" s="26"/>
       <c r="H113" s="1"/>
@@ -4321,10 +4206,10 @@
         <v>78</v>
       </c>
       <c r="E114" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F114" s="20" t="s">
-        <v>250</v>
+        <v>263</v>
+      </c>
+      <c r="F114" s="34" t="s">
+        <v>296</v>
       </c>
       <c r="G114" s="26"/>
       <c r="H114" s="1"/>
@@ -4345,10 +4230,10 @@
         <v>79</v>
       </c>
       <c r="E115" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F115" s="20" t="s">
-        <v>251</v>
+        <v>263</v>
+      </c>
+      <c r="F115" s="34" t="s">
+        <v>213</v>
       </c>
       <c r="G115" s="26"/>
       <c r="H115" s="1"/>
@@ -4369,10 +4254,10 @@
         <v>80</v>
       </c>
       <c r="E116" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F116" s="20" t="s">
-        <v>252</v>
+        <v>263</v>
+      </c>
+      <c r="F116" s="34" t="s">
+        <v>297</v>
       </c>
       <c r="G116" s="26"/>
       <c r="H116" s="1"/>
@@ -4393,10 +4278,10 @@
         <v>81</v>
       </c>
       <c r="E117" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F117" s="20" t="s">
-        <v>253</v>
+        <v>251</v>
+      </c>
+      <c r="F117" s="34" t="s">
+        <v>298</v>
       </c>
       <c r="G117" s="26"/>
       <c r="H117" s="1"/>
@@ -4417,10 +4302,10 @@
         <v>82</v>
       </c>
       <c r="E118" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F118" s="20" t="s">
-        <v>254</v>
+        <v>263</v>
+      </c>
+      <c r="F118" s="34" t="s">
+        <v>299</v>
       </c>
       <c r="G118" s="26"/>
       <c r="H118" s="1"/>
@@ -4441,10 +4326,10 @@
         <v>83</v>
       </c>
       <c r="E119" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F119" s="20" t="s">
-        <v>255</v>
+        <v>300</v>
+      </c>
+      <c r="F119" s="34" t="s">
+        <v>301</v>
       </c>
       <c r="G119" s="26"/>
       <c r="H119" s="1"/>
@@ -4465,10 +4350,10 @@
         <v>84</v>
       </c>
       <c r="E120" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F120" s="20" t="s">
-        <v>256</v>
+        <v>246</v>
+      </c>
+      <c r="F120" s="34" t="s">
+        <v>302</v>
       </c>
       <c r="G120" s="26"/>
       <c r="H120" s="1"/>
@@ -4489,10 +4374,10 @@
         <v>85</v>
       </c>
       <c r="E121" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F121" s="20" t="s">
-        <v>257</v>
+        <v>263</v>
+      </c>
+      <c r="F121" s="34" t="s">
+        <v>303</v>
       </c>
       <c r="G121" s="26"/>
       <c r="H121" s="1"/>
@@ -4513,10 +4398,10 @@
         <v>86</v>
       </c>
       <c r="E122" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F122" s="20" t="s">
-        <v>258</v>
+        <v>263</v>
+      </c>
+      <c r="F122" s="34" t="s">
+        <v>304</v>
       </c>
       <c r="G122" s="26"/>
       <c r="H122" s="1"/>
@@ -4537,10 +4422,10 @@
         <v>87</v>
       </c>
       <c r="E123" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F123" s="20" t="s">
-        <v>259</v>
+        <v>263</v>
+      </c>
+      <c r="F123" s="34" t="s">
+        <v>305</v>
       </c>
       <c r="G123" s="26"/>
       <c r="H123" s="1"/>
@@ -4561,10 +4446,10 @@
         <v>88</v>
       </c>
       <c r="E124" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="F124" s="20" t="s">
-        <v>260</v>
+        <v>263</v>
+      </c>
+      <c r="F124" s="34" t="s">
+        <v>306</v>
       </c>
       <c r="G124" s="26"/>
       <c r="H124" s="1"/>
@@ -4585,10 +4470,10 @@
         <v>89</v>
       </c>
       <c r="E125" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F125" s="20" t="s">
-        <v>261</v>
+        <v>263</v>
+      </c>
+      <c r="F125" s="34" t="s">
+        <v>307</v>
       </c>
       <c r="G125" s="26"/>
       <c r="H125" s="1"/>
@@ -4609,10 +4494,10 @@
         <v>90</v>
       </c>
       <c r="E126" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="F126" s="20" t="s">
         <v>263</v>
+      </c>
+      <c r="F126" s="34" t="s">
+        <v>308</v>
       </c>
       <c r="G126" s="26"/>
       <c r="H126" s="1"/>
@@ -4633,10 +4518,10 @@
         <v>91</v>
       </c>
       <c r="E127" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="F127" s="20" t="s">
-        <v>264</v>
+        <v>263</v>
+      </c>
+      <c r="F127" s="34" t="s">
+        <v>309</v>
       </c>
       <c r="G127" s="26"/>
       <c r="H127" s="1"/>
@@ -4657,10 +4542,10 @@
         <v>92</v>
       </c>
       <c r="E128" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F128" s="20" t="s">
-        <v>265</v>
+        <v>263</v>
+      </c>
+      <c r="F128" s="34" t="s">
+        <v>310</v>
       </c>
       <c r="G128" s="26"/>
       <c r="H128" s="1"/>
@@ -4681,10 +4566,10 @@
         <v>93</v>
       </c>
       <c r="E129" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F129" s="20" t="s">
-        <v>266</v>
+        <v>263</v>
+      </c>
+      <c r="F129" s="34" t="s">
+        <v>311</v>
       </c>
       <c r="G129" s="26"/>
       <c r="H129" s="1"/>
@@ -4705,10 +4590,10 @@
         <v>94</v>
       </c>
       <c r="E130" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F130" s="20" t="s">
-        <v>267</v>
+        <v>300</v>
+      </c>
+      <c r="F130" s="34" t="s">
+        <v>312</v>
       </c>
       <c r="G130" s="26"/>
       <c r="H130" s="1"/>
@@ -4729,10 +4614,10 @@
         <v>95</v>
       </c>
       <c r="E131" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F131" s="20" t="s">
-        <v>268</v>
+        <v>251</v>
+      </c>
+      <c r="F131" s="34" t="s">
+        <v>313</v>
       </c>
       <c r="G131" s="26"/>
       <c r="H131" s="1"/>
@@ -4753,10 +4638,10 @@
         <v>96</v>
       </c>
       <c r="E132" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F132" s="20" t="s">
-        <v>269</v>
+        <v>263</v>
+      </c>
+      <c r="F132" s="34" t="s">
+        <v>314</v>
       </c>
       <c r="G132" s="26"/>
       <c r="H132" s="1"/>
@@ -4777,10 +4662,10 @@
         <v>97</v>
       </c>
       <c r="E133" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F133" s="20" t="s">
-        <v>270</v>
+        <v>263</v>
+      </c>
+      <c r="F133" s="34" t="s">
+        <v>315</v>
       </c>
       <c r="G133" s="26"/>
       <c r="H133" s="1"/>
@@ -4801,10 +4686,10 @@
         <v>98</v>
       </c>
       <c r="E134" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F134" s="20" t="s">
-        <v>271</v>
+        <v>263</v>
+      </c>
+      <c r="F134" s="34" t="s">
+        <v>316</v>
       </c>
       <c r="G134" s="26"/>
       <c r="H134" s="1"/>
@@ -4825,10 +4710,10 @@
         <v>99</v>
       </c>
       <c r="E135" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F135" s="20" t="s">
-        <v>272</v>
+        <v>263</v>
+      </c>
+      <c r="F135" s="34" t="s">
+        <v>317</v>
       </c>
       <c r="G135" s="26"/>
       <c r="H135" s="1"/>
@@ -4849,10 +4734,10 @@
         <v>100</v>
       </c>
       <c r="E136" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="F136" s="20" t="s">
-        <v>273</v>
+        <v>263</v>
+      </c>
+      <c r="F136" s="34" t="s">
+        <v>318</v>
       </c>
       <c r="G136" s="26"/>
       <c r="H136" s="1"/>
@@ -4873,10 +4758,10 @@
         <v>101</v>
       </c>
       <c r="E137" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="F137" s="20" t="s">
-        <v>274</v>
+        <v>263</v>
+      </c>
+      <c r="F137" s="34" t="s">
+        <v>319</v>
       </c>
       <c r="G137" s="26"/>
       <c r="H137" s="1"/>
@@ -4897,10 +4782,10 @@
         <v>102</v>
       </c>
       <c r="E138" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F138" s="20" t="s">
-        <v>275</v>
+        <v>263</v>
+      </c>
+      <c r="F138" s="34" t="s">
+        <v>320</v>
       </c>
       <c r="G138" s="26"/>
       <c r="H138" s="1"/>
@@ -4921,10 +4806,10 @@
         <v>103</v>
       </c>
       <c r="E139" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F139" s="20" t="s">
-        <v>276</v>
+        <v>263</v>
+      </c>
+      <c r="F139" s="34" t="s">
+        <v>321</v>
       </c>
       <c r="G139" s="26"/>
       <c r="H139" s="1"/>
@@ -4945,10 +4830,10 @@
         <v>104</v>
       </c>
       <c r="E140" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F140" s="20" t="s">
-        <v>277</v>
+        <v>246</v>
+      </c>
+      <c r="F140" s="34" t="s">
+        <v>322</v>
       </c>
       <c r="G140" s="26"/>
       <c r="H140" s="1"/>
@@ -4969,12 +4854,12 @@
         <v>105</v>
       </c>
       <c r="E141" s="20" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="F141" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="G141" s="26"/>
+        <v>71</v>
+      </c>
+      <c r="G141" s="16"/>
       <c r="H141" s="1"/>
       <c r="I141" s="1"/>
       <c r="J141" s="2"/>
@@ -4993,12 +4878,12 @@
         <v>106</v>
       </c>
       <c r="E142" s="20" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="F142" s="20" t="s">
-        <v>279</v>
-      </c>
-      <c r="G142" s="26"/>
+        <v>72</v>
+      </c>
+      <c r="G142" s="16"/>
       <c r="H142" s="1"/>
       <c r="I142" s="1"/>
       <c r="J142" s="2"/>
@@ -5017,12 +4902,12 @@
         <v>107</v>
       </c>
       <c r="E143" s="20" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F143" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="G143" s="26"/>
+        <v>74</v>
+      </c>
+      <c r="G143" s="16"/>
       <c r="H143" s="1"/>
       <c r="I143" s="1"/>
       <c r="J143" s="2"/>
@@ -5041,12 +4926,12 @@
         <v>108</v>
       </c>
       <c r="E144" s="20" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="F144" s="20" t="s">
-        <v>281</v>
-      </c>
-      <c r="G144" s="26"/>
+        <v>75</v>
+      </c>
+      <c r="G144" s="16"/>
       <c r="H144" s="1"/>
       <c r="I144" s="1"/>
       <c r="J144" s="2"/>
@@ -5065,12 +4950,12 @@
         <v>109</v>
       </c>
       <c r="E145" s="20" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="F145" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="G145" s="26"/>
+        <v>76</v>
+      </c>
+      <c r="G145" s="16"/>
       <c r="H145" s="1"/>
       <c r="I145" s="1"/>
       <c r="J145" s="2"/>
@@ -5089,12 +4974,12 @@
         <v>110</v>
       </c>
       <c r="E146" s="20" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F146" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="G146" s="26"/>
+        <v>77</v>
+      </c>
+      <c r="G146" s="16"/>
       <c r="H146" s="1"/>
       <c r="I146" s="1"/>
       <c r="J146" s="2"/>
@@ -5113,12 +4998,12 @@
         <v>111</v>
       </c>
       <c r="E147" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F147" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="G147" s="16"/>
+        <v>78</v>
+      </c>
+      <c r="G147" s="26"/>
       <c r="H147" s="1"/>
       <c r="I147" s="1"/>
       <c r="J147" s="2"/>
@@ -5137,10 +5022,10 @@
         <v>112</v>
       </c>
       <c r="E148" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F148" s="20" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="G148" s="16"/>
       <c r="H148" s="1"/>
@@ -5161,10 +5046,10 @@
         <v>113</v>
       </c>
       <c r="E149" s="20" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="F149" s="20" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G149" s="16"/>
       <c r="H149" s="1"/>
@@ -5185,10 +5070,10 @@
         <v>114</v>
       </c>
       <c r="E150" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F150" s="20" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G150" s="16"/>
       <c r="H150" s="1"/>
@@ -5208,11 +5093,11 @@
       <c r="D151" s="20">
         <v>115</v>
       </c>
-      <c r="E151" s="20" t="s">
+      <c r="E151" s="27" t="s">
         <v>48</v>
       </c>
       <c r="F151" s="20" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="G151" s="16"/>
       <c r="H151" s="1"/>
@@ -5232,11 +5117,11 @@
       <c r="D152" s="20">
         <v>116</v>
       </c>
-      <c r="E152" s="20" t="s">
-        <v>37</v>
+      <c r="E152" s="27" t="s">
+        <v>48</v>
       </c>
       <c r="F152" s="20" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G152" s="16"/>
       <c r="H152" s="1"/>
@@ -5257,12 +5142,12 @@
         <v>117</v>
       </c>
       <c r="E153" s="20" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="F153" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="G153" s="26"/>
+        <v>84</v>
+      </c>
+      <c r="G153" s="16"/>
       <c r="H153" s="1"/>
       <c r="I153" s="1"/>
       <c r="J153" s="2"/>
@@ -5280,11 +5165,11 @@
       <c r="D154" s="20">
         <v>118</v>
       </c>
-      <c r="E154" s="20" t="s">
-        <v>50</v>
+      <c r="E154" s="27" t="s">
+        <v>48</v>
       </c>
       <c r="F154" s="20" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G154" s="16"/>
       <c r="H154" s="1"/>
@@ -5304,11 +5189,11 @@
       <c r="D155" s="20">
         <v>119</v>
       </c>
-      <c r="E155" s="20" t="s">
-        <v>50</v>
+      <c r="E155" s="27" t="s">
+        <v>48</v>
       </c>
       <c r="F155" s="20" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G155" s="16"/>
       <c r="H155" s="1"/>
@@ -5328,11 +5213,11 @@
       <c r="D156" s="20">
         <v>120</v>
       </c>
-      <c r="E156" s="20" t="s">
-        <v>50</v>
+      <c r="E156" s="27" t="s">
+        <v>37</v>
       </c>
       <c r="F156" s="20" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G156" s="16"/>
       <c r="H156" s="1"/>
@@ -5353,10 +5238,10 @@
         <v>121</v>
       </c>
       <c r="E157" s="27" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F157" s="20" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G157" s="16"/>
       <c r="H157" s="1"/>
@@ -5377,10 +5262,10 @@
         <v>122</v>
       </c>
       <c r="E158" s="27" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F158" s="20" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="G158" s="16"/>
       <c r="H158" s="1"/>
@@ -5400,11 +5285,11 @@
       <c r="D159" s="20">
         <v>123</v>
       </c>
-      <c r="E159" s="20" t="s">
-        <v>73</v>
+      <c r="E159" s="27" t="s">
+        <v>50</v>
       </c>
       <c r="F159" s="20" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G159" s="16"/>
       <c r="H159" s="1"/>
@@ -5425,10 +5310,10 @@
         <v>124</v>
       </c>
       <c r="E160" s="27" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F160" s="20" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G160" s="16"/>
       <c r="H160" s="1"/>
@@ -5448,11 +5333,11 @@
       <c r="D161" s="20">
         <v>125</v>
       </c>
-      <c r="E161" s="27" t="s">
-        <v>48</v>
+      <c r="E161" s="20" t="s">
+        <v>52</v>
       </c>
       <c r="F161" s="20" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G161" s="16"/>
       <c r="H161" s="1"/>
@@ -5472,11 +5357,11 @@
       <c r="D162" s="20">
         <v>126</v>
       </c>
-      <c r="E162" s="27" t="s">
-        <v>37</v>
+      <c r="E162" s="20" t="s">
+        <v>52</v>
       </c>
       <c r="F162" s="20" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G162" s="16"/>
       <c r="H162" s="1"/>
@@ -5496,11 +5381,11 @@
       <c r="D163" s="20">
         <v>127</v>
       </c>
-      <c r="E163" s="27" t="s">
-        <v>50</v>
+      <c r="E163" s="20" t="s">
+        <v>52</v>
       </c>
       <c r="F163" s="20" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G163" s="16"/>
       <c r="H163" s="1"/>
@@ -5520,11 +5405,11 @@
       <c r="D164" s="20">
         <v>128</v>
       </c>
-      <c r="E164" s="27" t="s">
-        <v>50</v>
+      <c r="E164" s="20" t="s">
+        <v>48</v>
       </c>
       <c r="F164" s="20" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G164" s="16"/>
       <c r="H164" s="1"/>
@@ -5544,11 +5429,11 @@
       <c r="D165" s="20">
         <v>129</v>
       </c>
-      <c r="E165" s="27" t="s">
-        <v>50</v>
+      <c r="E165" s="20" t="s">
+        <v>48</v>
       </c>
       <c r="F165" s="20" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G165" s="16"/>
       <c r="H165" s="1"/>
@@ -5568,11 +5453,11 @@
       <c r="D166" s="20">
         <v>130</v>
       </c>
-      <c r="E166" s="27" t="s">
+      <c r="E166" s="20" t="s">
         <v>50</v>
       </c>
       <c r="F166" s="20" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G166" s="16"/>
       <c r="H166" s="1"/>
@@ -5596,7 +5481,7 @@
         <v>52</v>
       </c>
       <c r="F167" s="20" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G167" s="16"/>
       <c r="H167" s="1"/>
@@ -5620,7 +5505,7 @@
         <v>52</v>
       </c>
       <c r="F168" s="20" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G168" s="16"/>
       <c r="H168" s="1"/>
@@ -5641,10 +5526,10 @@
         <v>133</v>
       </c>
       <c r="E169" s="20" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F169" s="20" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="G169" s="16"/>
       <c r="H169" s="1"/>
@@ -5668,7 +5553,7 @@
         <v>48</v>
       </c>
       <c r="F170" s="20" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G170" s="16"/>
       <c r="H170" s="1"/>
@@ -5689,10 +5574,10 @@
         <v>135</v>
       </c>
       <c r="E171" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F171" s="20" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G171" s="16"/>
       <c r="H171" s="1"/>
@@ -5716,7 +5601,7 @@
         <v>50</v>
       </c>
       <c r="F172" s="20" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G172" s="16"/>
       <c r="H172" s="1"/>
@@ -5740,7 +5625,7 @@
         <v>52</v>
       </c>
       <c r="F173" s="20" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G173" s="16"/>
       <c r="H173" s="1"/>
@@ -5761,10 +5646,10 @@
         <v>138</v>
       </c>
       <c r="E174" s="20" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F174" s="20" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G174" s="16"/>
       <c r="H174" s="1"/>
@@ -5788,7 +5673,7 @@
         <v>48</v>
       </c>
       <c r="F175" s="20" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="G175" s="16"/>
       <c r="H175" s="1"/>
@@ -5809,10 +5694,10 @@
         <v>140</v>
       </c>
       <c r="E176" s="20" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="F176" s="20" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G176" s="16"/>
       <c r="H176" s="1"/>
@@ -5833,10 +5718,10 @@
         <v>141</v>
       </c>
       <c r="E177" s="20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F177" s="20" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="G177" s="16"/>
       <c r="H177" s="1"/>
@@ -5857,10 +5742,10 @@
         <v>142</v>
       </c>
       <c r="E178" s="20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F178" s="20" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="G178" s="16"/>
       <c r="H178" s="1"/>
@@ -5881,10 +5766,10 @@
         <v>143</v>
       </c>
       <c r="E179" s="20" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="F179" s="20" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="G179" s="16"/>
       <c r="H179" s="1"/>
@@ -5897,7 +5782,7 @@
       <c r="O179" s="2"/>
       <c r="P179" s="1"/>
     </row>
-    <row r="180" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:16" customFormat="1" ht="48.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="18"/>
       <c r="B180" s="18"/>
       <c r="C180" s="18"/>
@@ -5905,12 +5790,12 @@
         <v>144</v>
       </c>
       <c r="E180" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F180" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="G180" s="16"/>
+        <v>111</v>
+      </c>
+      <c r="G180" s="26"/>
       <c r="H180" s="1"/>
       <c r="I180" s="1"/>
       <c r="J180" s="2"/>
@@ -5929,10 +5814,10 @@
         <v>145</v>
       </c>
       <c r="E181" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F181" s="20" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G181" s="16"/>
       <c r="H181" s="1"/>
@@ -5953,10 +5838,10 @@
         <v>146</v>
       </c>
       <c r="E182" s="20" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="F182" s="20" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="G182" s="16"/>
       <c r="H182" s="1"/>
@@ -5977,10 +5862,10 @@
         <v>147</v>
       </c>
       <c r="E183" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F183" s="20" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="G183" s="16"/>
       <c r="H183" s="1"/>
@@ -6004,7 +5889,7 @@
         <v>48</v>
       </c>
       <c r="F184" s="20" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G184" s="16"/>
       <c r="H184" s="1"/>
@@ -6025,10 +5910,10 @@
         <v>149</v>
       </c>
       <c r="E185" s="20" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F185" s="20" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G185" s="16"/>
       <c r="H185" s="1"/>
@@ -6041,7 +5926,7 @@
       <c r="O185" s="2"/>
       <c r="P185" s="1"/>
     </row>
-    <row r="186" spans="1:16" customFormat="1" ht="48.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="18"/>
       <c r="B186" s="18"/>
       <c r="C186" s="18"/>
@@ -6049,12 +5934,12 @@
         <v>150</v>
       </c>
       <c r="E186" s="20" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="F186" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="G186" s="26"/>
+        <v>117</v>
+      </c>
+      <c r="G186" s="16"/>
       <c r="H186" s="1"/>
       <c r="I186" s="1"/>
       <c r="J186" s="2"/>
@@ -6073,10 +5958,10 @@
         <v>151</v>
       </c>
       <c r="E187" s="20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F187" s="20" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="G187" s="16"/>
       <c r="H187" s="1"/>
@@ -6097,10 +5982,10 @@
         <v>152</v>
       </c>
       <c r="E188" s="20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F188" s="20" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="G188" s="16"/>
       <c r="H188" s="1"/>
@@ -6121,10 +6006,10 @@
         <v>153</v>
       </c>
       <c r="E189" s="20" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F189" s="20" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G189" s="16"/>
       <c r="H189" s="1"/>
@@ -6145,12 +6030,12 @@
         <v>154</v>
       </c>
       <c r="E190" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F190" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="G190" s="16"/>
+        <v>121</v>
+      </c>
+      <c r="G190" s="26"/>
       <c r="H190" s="1"/>
       <c r="I190" s="1"/>
       <c r="J190" s="2"/>
@@ -6169,10 +6054,10 @@
         <v>155</v>
       </c>
       <c r="E191" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F191" s="20" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="G191" s="16"/>
       <c r="H191" s="1"/>
@@ -6193,12 +6078,12 @@
         <v>156</v>
       </c>
       <c r="E192" s="20" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="F192" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="G192" s="16"/>
+        <v>123</v>
+      </c>
+      <c r="G192" s="26"/>
       <c r="H192" s="1"/>
       <c r="I192" s="1"/>
       <c r="J192" s="2"/>
@@ -6217,12 +6102,12 @@
         <v>157</v>
       </c>
       <c r="E193" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F193" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="G193" s="16"/>
+        <v>124</v>
+      </c>
+      <c r="G193" s="26"/>
       <c r="H193" s="1"/>
       <c r="I193" s="1"/>
       <c r="J193" s="2"/>
@@ -6244,7 +6129,7 @@
         <v>48</v>
       </c>
       <c r="F194" s="20" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="G194" s="16"/>
       <c r="H194" s="1"/>
@@ -6265,10 +6150,10 @@
         <v>159</v>
       </c>
       <c r="E195" s="20" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F195" s="20" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="G195" s="16"/>
       <c r="H195" s="1"/>
@@ -6289,12 +6174,12 @@
         <v>160</v>
       </c>
       <c r="E196" s="20" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="F196" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="G196" s="26"/>
+        <v>127</v>
+      </c>
+      <c r="G196" s="16"/>
       <c r="H196" s="1"/>
       <c r="I196" s="1"/>
       <c r="J196" s="2"/>
@@ -6313,10 +6198,10 @@
         <v>161</v>
       </c>
       <c r="E197" s="20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F197" s="20" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="G197" s="16"/>
       <c r="H197" s="1"/>
@@ -6337,12 +6222,12 @@
         <v>162</v>
       </c>
       <c r="E198" s="20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F198" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="G198" s="26"/>
+        <v>129</v>
+      </c>
+      <c r="G198" s="16"/>
       <c r="H198" s="1"/>
       <c r="I198" s="1"/>
       <c r="J198" s="2"/>
@@ -6361,12 +6246,12 @@
         <v>163</v>
       </c>
       <c r="E199" s="20" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F199" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="G199" s="26"/>
+        <v>130</v>
+      </c>
+      <c r="G199" s="16"/>
       <c r="H199" s="1"/>
       <c r="I199" s="1"/>
       <c r="J199" s="2"/>
@@ -6377,7 +6262,7 @@
       <c r="O199" s="2"/>
       <c r="P199" s="1"/>
     </row>
-    <row r="200" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:16" customFormat="1" ht="78.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="18"/>
       <c r="B200" s="18"/>
       <c r="C200" s="18"/>
@@ -6385,12 +6270,12 @@
         <v>164</v>
       </c>
       <c r="E200" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F200" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="G200" s="16"/>
+        <v>131</v>
+      </c>
+      <c r="G200" s="26"/>
       <c r="H200" s="1"/>
       <c r="I200" s="1"/>
       <c r="J200" s="2"/>
@@ -6409,10 +6294,10 @@
         <v>165</v>
       </c>
       <c r="E201" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F201" s="20" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="G201" s="16"/>
       <c r="H201" s="1"/>
@@ -6433,10 +6318,10 @@
         <v>166</v>
       </c>
       <c r="E202" s="20" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="F202" s="20" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="G202" s="16"/>
       <c r="H202" s="1"/>
@@ -6457,10 +6342,10 @@
         <v>167</v>
       </c>
       <c r="E203" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F203" s="20" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="G203" s="16"/>
       <c r="H203" s="1"/>
@@ -6481,10 +6366,10 @@
         <v>168</v>
       </c>
       <c r="E204" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F204" s="20" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="G204" s="16"/>
       <c r="H204" s="1"/>
@@ -6505,10 +6390,10 @@
         <v>169</v>
       </c>
       <c r="E205" s="20" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="F205" s="20" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="G205" s="16"/>
       <c r="H205" s="1"/>
@@ -6521,7 +6406,7 @@
       <c r="O205" s="2"/>
       <c r="P205" s="1"/>
     </row>
-    <row r="206" spans="1:16" customFormat="1" ht="78.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A206" s="18"/>
       <c r="B206" s="18"/>
       <c r="C206" s="18"/>
@@ -6529,12 +6414,12 @@
         <v>170</v>
       </c>
       <c r="E206" s="20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F206" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="G206" s="26"/>
+        <v>137</v>
+      </c>
+      <c r="G206" s="16"/>
       <c r="H206" s="1"/>
       <c r="I206" s="1"/>
       <c r="J206" s="2"/>
@@ -6553,10 +6438,10 @@
         <v>171</v>
       </c>
       <c r="E207" s="20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F207" s="20" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="G207" s="16"/>
       <c r="H207" s="1"/>
@@ -6577,10 +6462,10 @@
         <v>172</v>
       </c>
       <c r="E208" s="20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F208" s="20" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G208" s="16"/>
       <c r="H208" s="1"/>
@@ -6601,10 +6486,10 @@
         <v>173</v>
       </c>
       <c r="E209" s="20" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="F209" s="20" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="G209" s="16"/>
       <c r="H209" s="1"/>
@@ -6625,10 +6510,10 @@
         <v>174</v>
       </c>
       <c r="E210" s="20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F210" s="20" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="G210" s="16"/>
       <c r="H210" s="1"/>
@@ -6649,10 +6534,10 @@
         <v>175</v>
       </c>
       <c r="E211" s="20" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F211" s="20" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="G211" s="16"/>
       <c r="H211" s="1"/>
@@ -6673,10 +6558,10 @@
         <v>176</v>
       </c>
       <c r="E212" s="20" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="F212" s="20" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G212" s="16"/>
       <c r="H212" s="1"/>
@@ -6689,7 +6574,7 @@
       <c r="O212" s="2"/>
       <c r="P212" s="1"/>
     </row>
-    <row r="213" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:16" customFormat="1" ht="128.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="18"/>
       <c r="B213" s="18"/>
       <c r="C213" s="18"/>
@@ -6697,12 +6582,12 @@
         <v>177</v>
       </c>
       <c r="E213" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F213" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="G213" s="16"/>
+        <v>144</v>
+      </c>
+      <c r="G213" s="26"/>
       <c r="H213" s="1"/>
       <c r="I213" s="1"/>
       <c r="J213" s="2"/>
@@ -6721,10 +6606,10 @@
         <v>178</v>
       </c>
       <c r="E214" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F214" s="20" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G214" s="16"/>
       <c r="H214" s="1"/>
@@ -6745,10 +6630,10 @@
         <v>179</v>
       </c>
       <c r="E215" s="20" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="F215" s="20" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="G215" s="16"/>
       <c r="H215" s="1"/>
@@ -6769,10 +6654,10 @@
         <v>180</v>
       </c>
       <c r="E216" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F216" s="20" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G216" s="16"/>
       <c r="H216" s="1"/>
@@ -6793,10 +6678,10 @@
         <v>181</v>
       </c>
       <c r="E217" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F217" s="20" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="G217" s="16"/>
       <c r="H217" s="1"/>
@@ -6817,10 +6702,10 @@
         <v>182</v>
       </c>
       <c r="E218" s="20" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="F218" s="20" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="G218" s="16"/>
       <c r="H218" s="1"/>
@@ -6833,7 +6718,7 @@
       <c r="O218" s="2"/>
       <c r="P218" s="1"/>
     </row>
-    <row r="219" spans="1:16" customFormat="1" ht="128.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A219" s="18"/>
       <c r="B219" s="18"/>
       <c r="C219" s="18"/>
@@ -6841,12 +6726,12 @@
         <v>183</v>
       </c>
       <c r="E219" s="20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F219" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="G219" s="26"/>
+        <v>150</v>
+      </c>
+      <c r="G219" s="16"/>
       <c r="H219" s="1"/>
       <c r="I219" s="1"/>
       <c r="J219" s="2"/>
@@ -6865,10 +6750,10 @@
         <v>184</v>
       </c>
       <c r="E220" s="20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F220" s="20" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="G220" s="16"/>
       <c r="H220" s="1"/>
@@ -6889,10 +6774,10 @@
         <v>185</v>
       </c>
       <c r="E221" s="20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F221" s="20" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="G221" s="16"/>
       <c r="H221" s="1"/>
@@ -6913,10 +6798,10 @@
         <v>186</v>
       </c>
       <c r="E222" s="20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F222" s="20" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="G222" s="16"/>
       <c r="H222" s="1"/>
@@ -6937,10 +6822,10 @@
         <v>187</v>
       </c>
       <c r="E223" s="20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F223" s="20" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="G223" s="16"/>
       <c r="H223" s="1"/>
@@ -6964,7 +6849,7 @@
         <v>52</v>
       </c>
       <c r="F224" s="20" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="G224" s="16"/>
       <c r="H224" s="1"/>
@@ -6988,7 +6873,7 @@
         <v>52</v>
       </c>
       <c r="F225" s="20" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="G225" s="16"/>
       <c r="H225" s="1"/>
@@ -7012,7 +6897,7 @@
         <v>52</v>
       </c>
       <c r="F226" s="20" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="G226" s="16"/>
       <c r="H226" s="1"/>
@@ -7036,7 +6921,7 @@
         <v>52</v>
       </c>
       <c r="F227" s="20" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="G227" s="16"/>
       <c r="H227" s="1"/>
@@ -7060,7 +6945,7 @@
         <v>52</v>
       </c>
       <c r="F228" s="20" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="G228" s="16"/>
       <c r="H228" s="1"/>
@@ -7081,10 +6966,10 @@
         <v>193</v>
       </c>
       <c r="E229" s="20" t="s">
-        <v>52</v>
+        <v>250</v>
       </c>
       <c r="F229" s="20" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="G229" s="16"/>
       <c r="H229" s="1"/>
@@ -7104,13 +6989,13 @@
       <c r="D230" s="20">
         <v>194</v>
       </c>
-      <c r="E230" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="F230" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="G230" s="16"/>
+      <c r="E230" s="28" t="s">
+        <v>246</v>
+      </c>
+      <c r="F230" s="28" t="s">
+        <v>247</v>
+      </c>
+      <c r="G230" s="29"/>
       <c r="H230" s="1"/>
       <c r="I230" s="1"/>
       <c r="J230" s="2"/>
@@ -7128,13 +7013,13 @@
       <c r="D231" s="20">
         <v>195</v>
       </c>
-      <c r="E231" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="F231" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="G231" s="16"/>
+      <c r="E231" s="28" t="s">
+        <v>246</v>
+      </c>
+      <c r="F231" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="G231" s="29"/>
       <c r="H231" s="1"/>
       <c r="I231" s="1"/>
       <c r="J231" s="2"/>
@@ -7152,13 +7037,13 @@
       <c r="D232" s="20">
         <v>196</v>
       </c>
-      <c r="E232" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="F232" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="G232" s="16"/>
+      <c r="E232" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="F232" s="38" t="s">
+        <v>252</v>
+      </c>
+      <c r="G232" s="39"/>
       <c r="H232" s="1"/>
       <c r="I232" s="1"/>
       <c r="J232" s="2"/>
@@ -7176,13 +7061,13 @@
       <c r="D233" s="20">
         <v>197</v>
       </c>
-      <c r="E233" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="F233" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="G233" s="16"/>
+      <c r="E233" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="F233" s="38" t="s">
+        <v>253</v>
+      </c>
+      <c r="G233" s="39"/>
       <c r="H233" s="1"/>
       <c r="I233" s="1"/>
       <c r="J233" s="2"/>
@@ -7200,13 +7085,13 @@
       <c r="D234" s="20">
         <v>198</v>
       </c>
-      <c r="E234" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="F234" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="G234" s="16"/>
+      <c r="E234" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="F234" s="38" t="s">
+        <v>254</v>
+      </c>
+      <c r="G234" s="39"/>
       <c r="H234" s="1"/>
       <c r="I234" s="1"/>
       <c r="J234" s="2"/>
@@ -7224,13 +7109,13 @@
       <c r="D235" s="20">
         <v>199</v>
       </c>
-      <c r="E235" s="20" t="s">
-        <v>319</v>
-      </c>
-      <c r="F235" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="G235" s="16"/>
+      <c r="E235" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="F235" s="38" t="s">
+        <v>255</v>
+      </c>
+      <c r="G235" s="39"/>
       <c r="H235" s="1"/>
       <c r="I235" s="1"/>
       <c r="J235" s="2"/>
@@ -7249,12 +7134,12 @@
         <v>200</v>
       </c>
       <c r="E236" s="28" t="s">
-        <v>315</v>
-      </c>
-      <c r="F236" s="28" t="s">
-        <v>316</v>
-      </c>
-      <c r="G236" s="29"/>
+        <v>250</v>
+      </c>
+      <c r="F236" s="38" t="s">
+        <v>256</v>
+      </c>
+      <c r="G236" s="39"/>
       <c r="H236" s="1"/>
       <c r="I236" s="1"/>
       <c r="J236" s="2"/>
@@ -7273,12 +7158,12 @@
         <v>201</v>
       </c>
       <c r="E237" s="28" t="s">
-        <v>315</v>
-      </c>
-      <c r="F237" s="28" t="s">
-        <v>317</v>
-      </c>
-      <c r="G237" s="29"/>
+        <v>250</v>
+      </c>
+      <c r="F237" s="38" t="s">
+        <v>257</v>
+      </c>
+      <c r="G237" s="39"/>
       <c r="H237" s="1"/>
       <c r="I237" s="1"/>
       <c r="J237" s="2"/>
@@ -7297,10 +7182,10 @@
         <v>202</v>
       </c>
       <c r="E238" s="28" t="s">
-        <v>320</v>
+        <v>250</v>
       </c>
       <c r="F238" s="38" t="s">
-        <v>321</v>
+        <v>258</v>
       </c>
       <c r="G238" s="39"/>
       <c r="H238" s="1"/>
@@ -7321,12 +7206,12 @@
         <v>203</v>
       </c>
       <c r="E239" s="28" t="s">
-        <v>319</v>
+        <v>246</v>
       </c>
       <c r="F239" s="38" t="s">
-        <v>322</v>
-      </c>
-      <c r="G239" s="39"/>
+        <v>259</v>
+      </c>
+      <c r="G239" s="41"/>
       <c r="H239" s="1"/>
       <c r="I239" s="1"/>
       <c r="J239" s="2"/>
@@ -7337,68 +7222,60 @@
       <c r="O239" s="2"/>
       <c r="P239" s="1"/>
     </row>
-    <row r="240" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A240" s="18"/>
-      <c r="B240" s="18"/>
-      <c r="C240" s="18"/>
-      <c r="D240" s="20">
-        <v>204</v>
-      </c>
-      <c r="E240" s="28" t="s">
-        <v>319</v>
-      </c>
-      <c r="F240" s="38" t="s">
-        <v>323</v>
-      </c>
-      <c r="G240" s="39"/>
-      <c r="H240" s="1"/>
-      <c r="I240" s="1"/>
-      <c r="J240" s="2"/>
-      <c r="K240" s="2"/>
-      <c r="L240" s="2"/>
-      <c r="M240" s="2"/>
-      <c r="N240" s="2"/>
-      <c r="O240" s="2"/>
-      <c r="P240" s="1"/>
-    </row>
-    <row r="241" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A240" s="16"/>
+      <c r="B240" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C240" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D240" s="17"/>
+      <c r="E240" s="17"/>
+      <c r="F240" s="17"/>
+      <c r="G240" s="17"/>
+      <c r="H240" s="12"/>
+      <c r="I240" s="12"/>
+      <c r="J240" s="12"/>
+      <c r="K240" s="12"/>
+      <c r="L240" s="12"/>
+      <c r="M240" s="12"/>
+      <c r="N240" s="12"/>
+      <c r="O240" s="12"/>
+      <c r="P240" s="12"/>
+    </row>
+    <row r="241" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A241" s="18"/>
-      <c r="B241" s="18"/>
-      <c r="C241" s="18"/>
-      <c r="D241" s="20">
-        <v>205</v>
-      </c>
-      <c r="E241" s="28" t="s">
-        <v>319</v>
-      </c>
-      <c r="F241" s="38" t="s">
-        <v>324</v>
-      </c>
-      <c r="G241" s="39"/>
+      <c r="B241" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C241" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D241" s="19"/>
+      <c r="E241" s="16"/>
+      <c r="F241" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="G241" s="16"/>
       <c r="H241" s="1"/>
       <c r="I241" s="1"/>
-      <c r="J241" s="2"/>
-      <c r="K241" s="2"/>
-      <c r="L241" s="2"/>
-      <c r="M241" s="2"/>
-      <c r="N241" s="2"/>
-      <c r="O241" s="2"/>
       <c r="P241" s="1"/>
     </row>
     <row r="242" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="18"/>
       <c r="B242" s="18"/>
       <c r="C242" s="18"/>
-      <c r="D242" s="20">
-        <v>206</v>
-      </c>
-      <c r="E242" s="28" t="s">
-        <v>319</v>
-      </c>
-      <c r="F242" s="38" t="s">
-        <v>325</v>
-      </c>
-      <c r="G242" s="39"/>
+      <c r="D242" s="19">
+        <v>1</v>
+      </c>
+      <c r="E242" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="F242" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="G242" s="16"/>
       <c r="H242" s="1"/>
       <c r="I242" s="1"/>
       <c r="J242" s="2"/>
@@ -7413,16 +7290,16 @@
       <c r="A243" s="18"/>
       <c r="B243" s="18"/>
       <c r="C243" s="18"/>
-      <c r="D243" s="20">
-        <v>207</v>
-      </c>
-      <c r="E243" s="28" t="s">
-        <v>319</v>
-      </c>
-      <c r="F243" s="38" t="s">
-        <v>326</v>
-      </c>
-      <c r="G243" s="39"/>
+      <c r="D243" s="19">
+        <v>2</v>
+      </c>
+      <c r="E243" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="F243" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="G243" s="26"/>
       <c r="H243" s="1"/>
       <c r="I243" s="1"/>
       <c r="J243" s="2"/>
@@ -7437,16 +7314,16 @@
       <c r="A244" s="18"/>
       <c r="B244" s="18"/>
       <c r="C244" s="18"/>
-      <c r="D244" s="20">
-        <v>208</v>
-      </c>
-      <c r="E244" s="28" t="s">
-        <v>319</v>
-      </c>
-      <c r="F244" s="38" t="s">
-        <v>327</v>
-      </c>
-      <c r="G244" s="39"/>
+      <c r="D244" s="19">
+        <v>3</v>
+      </c>
+      <c r="E244" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="F244" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G244" s="16"/>
       <c r="H244" s="1"/>
       <c r="I244" s="1"/>
       <c r="J244" s="2"/>
@@ -7461,16 +7338,16 @@
       <c r="A245" s="18"/>
       <c r="B245" s="18"/>
       <c r="C245" s="18"/>
-      <c r="D245" s="20">
-        <v>209</v>
-      </c>
-      <c r="E245" s="28" t="s">
-        <v>328</v>
-      </c>
-      <c r="F245" s="38" t="s">
-        <v>329</v>
-      </c>
-      <c r="G245" s="42"/>
+      <c r="D245" s="19">
+        <v>4</v>
+      </c>
+      <c r="E245" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="F245" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G245" s="16"/>
       <c r="H245" s="1"/>
       <c r="I245" s="1"/>
       <c r="J245" s="2"/>
@@ -7481,44 +7358,52 @@
       <c r="O245" s="2"/>
       <c r="P245" s="1"/>
     </row>
-    <row r="246" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A246" s="16"/>
-      <c r="B246" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="C246" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D246" s="17"/>
-      <c r="E246" s="17"/>
-      <c r="F246" s="17"/>
-      <c r="G246" s="17"/>
-      <c r="H246" s="12"/>
-      <c r="I246" s="12"/>
-      <c r="J246" s="12"/>
-      <c r="K246" s="12"/>
-      <c r="L246" s="12"/>
-      <c r="M246" s="12"/>
-      <c r="N246" s="12"/>
-      <c r="O246" s="12"/>
-      <c r="P246" s="12"/>
-    </row>
-    <row r="247" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A246" s="18"/>
+      <c r="B246" s="18"/>
+      <c r="C246" s="18"/>
+      <c r="D246" s="19">
+        <v>5</v>
+      </c>
+      <c r="E246" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="F246" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="G246" s="26"/>
+      <c r="H246" s="30"/>
+      <c r="I246" s="30"/>
+      <c r="J246" s="31"/>
+      <c r="K246" s="31"/>
+      <c r="L246" s="31"/>
+      <c r="M246" s="31"/>
+      <c r="N246" s="31"/>
+      <c r="O246" s="31"/>
+      <c r="P246" s="30"/>
+    </row>
+    <row r="247" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A247" s="18"/>
-      <c r="B247" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="C247" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D247" s="19"/>
-      <c r="E247" s="16"/>
-      <c r="F247" s="16" t="s">
-        <v>41</v>
+      <c r="B247" s="18"/>
+      <c r="C247" s="18"/>
+      <c r="D247" s="19">
+        <v>6</v>
+      </c>
+      <c r="E247" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="F247" s="20" t="s">
+        <v>165</v>
       </c>
       <c r="G247" s="16"/>
       <c r="H247" s="1"/>
       <c r="I247" s="1"/>
+      <c r="J247" s="2"/>
+      <c r="K247" s="2"/>
+      <c r="L247" s="2"/>
+      <c r="M247" s="2"/>
+      <c r="N247" s="2"/>
+      <c r="O247" s="2"/>
       <c r="P247" s="1"/>
     </row>
     <row r="248" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
@@ -7526,15 +7411,15 @@
       <c r="B248" s="18"/>
       <c r="C248" s="18"/>
       <c r="D248" s="19">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E248" s="20" t="s">
         <v>48</v>
       </c>
       <c r="F248" s="20" t="s">
-        <v>161</v>
-      </c>
-      <c r="G248" s="16"/>
+        <v>216</v>
+      </c>
+      <c r="G248" s="26"/>
       <c r="H248" s="1"/>
       <c r="I248" s="1"/>
       <c r="J248" s="2"/>
@@ -7545,114 +7430,114 @@
       <c r="O248" s="2"/>
       <c r="P248" s="1"/>
     </row>
-    <row r="249" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A249" s="18"/>
       <c r="B249" s="18"/>
       <c r="C249" s="18"/>
       <c r="D249" s="19">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E249" s="20" t="s">
         <v>48</v>
       </c>
       <c r="F249" s="20" t="s">
-        <v>284</v>
+        <v>217</v>
       </c>
       <c r="G249" s="26"/>
-      <c r="H249" s="1"/>
-      <c r="I249" s="1"/>
-      <c r="J249" s="2"/>
-      <c r="K249" s="2"/>
-      <c r="L249" s="2"/>
-      <c r="M249" s="2"/>
-      <c r="N249" s="2"/>
-      <c r="O249" s="2"/>
-      <c r="P249" s="1"/>
-    </row>
-    <row r="250" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H249" s="30"/>
+      <c r="I249" s="30"/>
+      <c r="J249" s="31"/>
+      <c r="K249" s="31"/>
+      <c r="L249" s="31"/>
+      <c r="M249" s="31"/>
+      <c r="N249" s="31"/>
+      <c r="O249" s="31"/>
+      <c r="P249" s="30"/>
+    </row>
+    <row r="250" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="18"/>
       <c r="B250" s="18"/>
       <c r="C250" s="18"/>
       <c r="D250" s="19">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E250" s="20" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F250" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="G250" s="16"/>
-      <c r="H250" s="1"/>
-      <c r="I250" s="1"/>
-      <c r="J250" s="2"/>
-      <c r="K250" s="2"/>
-      <c r="L250" s="2"/>
-      <c r="M250" s="2"/>
-      <c r="N250" s="2"/>
-      <c r="O250" s="2"/>
-      <c r="P250" s="1"/>
-    </row>
-    <row r="251" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A251" s="18"/>
-      <c r="B251" s="18"/>
-      <c r="C251" s="18"/>
-      <c r="D251" s="19">
-        <v>4</v>
-      </c>
-      <c r="E251" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="G250" s="26"/>
+      <c r="H250" s="30"/>
+      <c r="I250" s="30"/>
+      <c r="J250" s="31"/>
+      <c r="K250" s="31"/>
+      <c r="L250" s="31"/>
+      <c r="M250" s="31"/>
+      <c r="N250" s="31"/>
+      <c r="O250" s="31"/>
+      <c r="P250" s="30"/>
+    </row>
+    <row r="251" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A251" s="31"/>
+      <c r="B251" s="31"/>
+      <c r="C251" s="31"/>
+      <c r="D251" s="40">
+        <v>10</v>
+      </c>
+      <c r="E251" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="F251" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="G251" s="16"/>
-      <c r="H251" s="1"/>
-      <c r="I251" s="1"/>
-      <c r="J251" s="2"/>
-      <c r="K251" s="2"/>
-      <c r="L251" s="2"/>
-      <c r="M251" s="2"/>
-      <c r="N251" s="2"/>
-      <c r="O251" s="2"/>
-      <c r="P251" s="1"/>
-    </row>
-    <row r="252" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F251" s="34" t="s">
+        <v>260</v>
+      </c>
+      <c r="G251" s="25"/>
+      <c r="H251" s="30"/>
+      <c r="I251" s="30"/>
+      <c r="J251" s="31"/>
+      <c r="K251" s="31"/>
+      <c r="L251" s="31"/>
+      <c r="M251" s="31"/>
+      <c r="N251" s="31"/>
+      <c r="O251" s="31"/>
+      <c r="P251" s="30"/>
+    </row>
+    <row r="252" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="18"/>
       <c r="B252" s="18"/>
       <c r="C252" s="18"/>
       <c r="D252" s="19">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E252" s="20" t="s">
         <v>48</v>
       </c>
       <c r="F252" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="G252" s="26"/>
-      <c r="H252" s="30"/>
-      <c r="I252" s="30"/>
-      <c r="J252" s="31"/>
-      <c r="K252" s="31"/>
-      <c r="L252" s="31"/>
-      <c r="M252" s="31"/>
-      <c r="N252" s="31"/>
-      <c r="O252" s="31"/>
-      <c r="P252" s="30"/>
+        <v>166</v>
+      </c>
+      <c r="G252" s="16"/>
+      <c r="H252" s="1"/>
+      <c r="I252" s="1"/>
+      <c r="J252" s="2"/>
+      <c r="K252" s="2"/>
+      <c r="L252" s="2"/>
+      <c r="M252" s="2"/>
+      <c r="N252" s="2"/>
+      <c r="O252" s="2"/>
+      <c r="P252" s="1"/>
     </row>
     <row r="253" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="18"/>
       <c r="B253" s="18"/>
       <c r="C253" s="18"/>
       <c r="D253" s="19">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E253" s="20" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F253" s="20" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G253" s="16"/>
       <c r="H253" s="1"/>
@@ -7670,15 +7555,15 @@
       <c r="B254" s="18"/>
       <c r="C254" s="18"/>
       <c r="D254" s="19">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E254" s="20" t="s">
         <v>48</v>
       </c>
       <c r="F254" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="G254" s="26"/>
+        <v>168</v>
+      </c>
+      <c r="G254" s="16"/>
       <c r="H254" s="1"/>
       <c r="I254" s="1"/>
       <c r="J254" s="2"/>
@@ -7694,13 +7579,13 @@
       <c r="B255" s="18"/>
       <c r="C255" s="18"/>
       <c r="D255" s="19">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E255" s="20" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="F255" s="20" t="s">
-        <v>286</v>
+        <v>219</v>
       </c>
       <c r="G255" s="26"/>
       <c r="H255" s="30"/>
@@ -7713,66 +7598,66 @@
       <c r="O255" s="31"/>
       <c r="P255" s="30"/>
     </row>
-    <row r="256" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="18"/>
       <c r="B256" s="18"/>
       <c r="C256" s="18"/>
       <c r="D256" s="19">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E256" s="20" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="F256" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="G256" s="26"/>
-      <c r="H256" s="30"/>
-      <c r="I256" s="30"/>
-      <c r="J256" s="31"/>
-      <c r="K256" s="31"/>
-      <c r="L256" s="31"/>
-      <c r="M256" s="31"/>
-      <c r="N256" s="31"/>
-      <c r="O256" s="31"/>
-      <c r="P256" s="30"/>
-    </row>
-    <row r="257" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A257" s="31"/>
-      <c r="B257" s="31"/>
-      <c r="C257" s="31"/>
-      <c r="D257" s="40">
-        <v>10</v>
-      </c>
-      <c r="E257" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="F257" s="34" t="s">
-        <v>330</v>
-      </c>
-      <c r="G257" s="25"/>
-      <c r="H257" s="30"/>
-      <c r="I257" s="30"/>
-      <c r="J257" s="31"/>
-      <c r="K257" s="31"/>
-      <c r="L257" s="31"/>
-      <c r="M257" s="31"/>
-      <c r="N257" s="31"/>
-      <c r="O257" s="31"/>
-      <c r="P257" s="30"/>
+        <v>169</v>
+      </c>
+      <c r="G256" s="16"/>
+      <c r="H256" s="1"/>
+      <c r="I256" s="1"/>
+      <c r="J256" s="2"/>
+      <c r="K256" s="2"/>
+      <c r="L256" s="2"/>
+      <c r="M256" s="2"/>
+      <c r="N256" s="2"/>
+      <c r="O256" s="2"/>
+      <c r="P256" s="1"/>
+    </row>
+    <row r="257" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A257" s="18"/>
+      <c r="B257" s="18"/>
+      <c r="C257" s="18"/>
+      <c r="D257" s="19">
+        <v>16</v>
+      </c>
+      <c r="E257" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="F257" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="G257" s="16"/>
+      <c r="H257" s="1"/>
+      <c r="I257" s="1"/>
+      <c r="J257" s="2"/>
+      <c r="K257" s="2"/>
+      <c r="L257" s="2"/>
+      <c r="M257" s="2"/>
+      <c r="N257" s="2"/>
+      <c r="O257" s="2"/>
+      <c r="P257" s="1"/>
     </row>
     <row r="258" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="18"/>
       <c r="B258" s="18"/>
       <c r="C258" s="18"/>
       <c r="D258" s="19">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E258" s="20" t="s">
         <v>48</v>
       </c>
       <c r="F258" s="20" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="G258" s="16"/>
       <c r="H258" s="1"/>
@@ -7790,13 +7675,13 @@
       <c r="B259" s="18"/>
       <c r="C259" s="18"/>
       <c r="D259" s="19">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E259" s="20" t="s">
         <v>48</v>
       </c>
       <c r="F259" s="20" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="G259" s="16"/>
       <c r="H259" s="1"/>
@@ -7814,13 +7699,13 @@
       <c r="B260" s="18"/>
       <c r="C260" s="18"/>
       <c r="D260" s="19">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E260" s="20" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F260" s="20" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="G260" s="16"/>
       <c r="H260" s="1"/>
@@ -7838,15 +7723,15 @@
       <c r="B261" s="18"/>
       <c r="C261" s="18"/>
       <c r="D261" s="19">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E261" s="20" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="F261" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="G261" s="26"/>
+        <v>174</v>
+      </c>
+      <c r="G261" s="16"/>
       <c r="H261" s="30"/>
       <c r="I261" s="30"/>
       <c r="J261" s="31"/>
@@ -7862,13 +7747,13 @@
       <c r="B262" s="18"/>
       <c r="C262" s="18"/>
       <c r="D262" s="19">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E262" s="20" t="s">
         <v>50</v>
       </c>
       <c r="F262" s="20" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="G262" s="16"/>
       <c r="H262" s="1"/>
@@ -7886,13 +7771,13 @@
       <c r="B263" s="18"/>
       <c r="C263" s="18"/>
       <c r="D263" s="19">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E263" s="20" t="s">
         <v>50</v>
       </c>
       <c r="F263" s="20" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="G263" s="16"/>
       <c r="H263" s="1"/>
@@ -7910,13 +7795,13 @@
       <c r="B264" s="18"/>
       <c r="C264" s="18"/>
       <c r="D264" s="19">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E264" s="20" t="s">
         <v>48</v>
       </c>
       <c r="F264" s="20" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="G264" s="16"/>
       <c r="H264" s="1"/>
@@ -7934,13 +7819,13 @@
       <c r="B265" s="18"/>
       <c r="C265" s="18"/>
       <c r="D265" s="19">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E265" s="20" t="s">
         <v>48</v>
       </c>
       <c r="F265" s="20" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="G265" s="16"/>
       <c r="H265" s="1"/>
@@ -7958,13 +7843,13 @@
       <c r="B266" s="18"/>
       <c r="C266" s="18"/>
       <c r="D266" s="19">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E266" s="20" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="F266" s="20" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="G266" s="16"/>
       <c r="H266" s="1"/>
@@ -7977,42 +7862,42 @@
       <c r="O266" s="2"/>
       <c r="P266" s="1"/>
     </row>
-    <row r="267" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A267" s="18"/>
       <c r="B267" s="18"/>
       <c r="C267" s="18"/>
       <c r="D267" s="19">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E267" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F267" s="20" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="G267" s="16"/>
-      <c r="H267" s="30"/>
-      <c r="I267" s="30"/>
-      <c r="J267" s="31"/>
-      <c r="K267" s="31"/>
-      <c r="L267" s="31"/>
-      <c r="M267" s="31"/>
-      <c r="N267" s="31"/>
-      <c r="O267" s="31"/>
-      <c r="P267" s="30"/>
+      <c r="H267" s="1"/>
+      <c r="I267" s="1"/>
+      <c r="J267" s="2"/>
+      <c r="K267" s="2"/>
+      <c r="L267" s="2"/>
+      <c r="M267" s="2"/>
+      <c r="N267" s="2"/>
+      <c r="O267" s="2"/>
+      <c r="P267" s="1"/>
     </row>
     <row r="268" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="18"/>
       <c r="B268" s="18"/>
       <c r="C268" s="18"/>
       <c r="D268" s="19">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E268" s="20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F268" s="20" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="G268" s="16"/>
       <c r="H268" s="1"/>
@@ -8030,13 +7915,13 @@
       <c r="B269" s="18"/>
       <c r="C269" s="18"/>
       <c r="D269" s="19">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E269" s="20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F269" s="20" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="G269" s="16"/>
       <c r="H269" s="1"/>
@@ -8054,13 +7939,13 @@
       <c r="B270" s="18"/>
       <c r="C270" s="18"/>
       <c r="D270" s="19">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E270" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F270" s="20" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="G270" s="16"/>
       <c r="H270" s="1"/>
@@ -8078,13 +7963,13 @@
       <c r="B271" s="18"/>
       <c r="C271" s="18"/>
       <c r="D271" s="19">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E271" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F271" s="20" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="G271" s="16"/>
       <c r="H271" s="1"/>
@@ -8102,13 +7987,13 @@
       <c r="B272" s="18"/>
       <c r="C272" s="18"/>
       <c r="D272" s="19">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E272" s="20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F272" s="20" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="G272" s="16"/>
       <c r="H272" s="1"/>
@@ -8126,13 +8011,13 @@
       <c r="B273" s="18"/>
       <c r="C273" s="18"/>
       <c r="D273" s="19">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E273" s="20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F273" s="20" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="G273" s="16"/>
       <c r="H273" s="1"/>
@@ -8150,13 +8035,13 @@
       <c r="B274" s="18"/>
       <c r="C274" s="18"/>
       <c r="D274" s="19">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E274" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F274" s="20" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="G274" s="16"/>
       <c r="H274" s="1"/>
@@ -8174,13 +8059,13 @@
       <c r="B275" s="18"/>
       <c r="C275" s="18"/>
       <c r="D275" s="19">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E275" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F275" s="20" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="G275" s="16"/>
       <c r="H275" s="1"/>
@@ -8198,13 +8083,13 @@
       <c r="B276" s="18"/>
       <c r="C276" s="18"/>
       <c r="D276" s="19">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E276" s="20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F276" s="20" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G276" s="16"/>
       <c r="H276" s="1"/>
@@ -8222,13 +8107,13 @@
       <c r="B277" s="18"/>
       <c r="C277" s="18"/>
       <c r="D277" s="19">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E277" s="20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F277" s="20" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="G277" s="16"/>
       <c r="H277" s="1"/>
@@ -8241,42 +8126,42 @@
       <c r="O277" s="2"/>
       <c r="P277" s="1"/>
     </row>
-    <row r="278" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A278" s="18"/>
       <c r="B278" s="18"/>
       <c r="C278" s="18"/>
       <c r="D278" s="19">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E278" s="20" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="F278" s="20" t="s">
-        <v>185</v>
-      </c>
-      <c r="G278" s="16"/>
-      <c r="H278" s="1"/>
-      <c r="I278" s="1"/>
-      <c r="J278" s="2"/>
-      <c r="K278" s="2"/>
-      <c r="L278" s="2"/>
-      <c r="M278" s="2"/>
-      <c r="N278" s="2"/>
-      <c r="O278" s="2"/>
-      <c r="P278" s="1"/>
+        <v>220</v>
+      </c>
+      <c r="G278" s="26"/>
+      <c r="H278" s="30"/>
+      <c r="I278" s="30"/>
+      <c r="J278" s="31"/>
+      <c r="K278" s="31"/>
+      <c r="L278" s="31"/>
+      <c r="M278" s="31"/>
+      <c r="N278" s="31"/>
+      <c r="O278" s="31"/>
+      <c r="P278" s="30"/>
     </row>
     <row r="279" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A279" s="18"/>
       <c r="B279" s="18"/>
       <c r="C279" s="18"/>
       <c r="D279" s="19">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E279" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F279" s="20" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="G279" s="16"/>
       <c r="H279" s="1"/>
@@ -8294,13 +8179,13 @@
       <c r="B280" s="18"/>
       <c r="C280" s="18"/>
       <c r="D280" s="19">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E280" s="20" t="s">
         <v>50</v>
       </c>
       <c r="F280" s="20" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="G280" s="16"/>
       <c r="H280" s="1"/>
@@ -8318,13 +8203,13 @@
       <c r="B281" s="18"/>
       <c r="C281" s="18"/>
       <c r="D281" s="19">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E281" s="20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F281" s="20" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="G281" s="16"/>
       <c r="H281" s="1"/>
@@ -8337,90 +8222,90 @@
       <c r="O281" s="2"/>
       <c r="P281" s="1"/>
     </row>
-    <row r="282" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A282" s="18"/>
       <c r="B282" s="18"/>
       <c r="C282" s="18"/>
       <c r="D282" s="19">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E282" s="20" t="s">
         <v>48</v>
       </c>
       <c r="F282" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="G282" s="16"/>
-      <c r="H282" s="1"/>
-      <c r="I282" s="1"/>
-      <c r="J282" s="2"/>
-      <c r="K282" s="2"/>
-      <c r="L282" s="2"/>
-      <c r="M282" s="2"/>
-      <c r="N282" s="2"/>
-      <c r="O282" s="2"/>
-      <c r="P282" s="1"/>
-    </row>
-    <row r="283" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="G282" s="26"/>
+      <c r="H282" s="16"/>
+      <c r="I282" s="16"/>
+      <c r="J282" s="18"/>
+      <c r="K282" s="18"/>
+      <c r="L282" s="18"/>
+      <c r="M282" s="18"/>
+      <c r="N282" s="18"/>
+      <c r="O282" s="18"/>
+      <c r="P282" s="16"/>
+    </row>
+    <row r="283" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A283" s="18"/>
       <c r="B283" s="18"/>
       <c r="C283" s="18"/>
       <c r="D283" s="19">
-        <v>36</v>
-      </c>
-      <c r="E283" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="F283" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="G283" s="16"/>
-      <c r="H283" s="1"/>
-      <c r="I283" s="1"/>
-      <c r="J283" s="2"/>
-      <c r="K283" s="2"/>
-      <c r="L283" s="2"/>
-      <c r="M283" s="2"/>
-      <c r="N283" s="2"/>
-      <c r="O283" s="2"/>
-      <c r="P283" s="1"/>
-    </row>
-    <row r="284" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="E283" s="34" t="s">
+        <v>323</v>
+      </c>
+      <c r="F283" s="34" t="s">
+        <v>324</v>
+      </c>
+      <c r="G283" s="25"/>
+      <c r="H283" s="16"/>
+      <c r="I283" s="16"/>
+      <c r="J283" s="18"/>
+      <c r="K283" s="18"/>
+      <c r="L283" s="18"/>
+      <c r="M283" s="18"/>
+      <c r="N283" s="18"/>
+      <c r="O283" s="18"/>
+      <c r="P283" s="16"/>
+    </row>
+    <row r="284" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A284" s="18"/>
       <c r="B284" s="18"/>
       <c r="C284" s="18"/>
       <c r="D284" s="19">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E284" s="20" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="F284" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="G284" s="26"/>
-      <c r="H284" s="30"/>
-      <c r="I284" s="30"/>
-      <c r="J284" s="31"/>
-      <c r="K284" s="31"/>
-      <c r="L284" s="31"/>
-      <c r="M284" s="31"/>
-      <c r="N284" s="31"/>
-      <c r="O284" s="31"/>
-      <c r="P284" s="30"/>
+        <v>194</v>
+      </c>
+      <c r="G284" s="16"/>
+      <c r="H284" s="1"/>
+      <c r="I284" s="1"/>
+      <c r="J284" s="2"/>
+      <c r="K284" s="2"/>
+      <c r="L284" s="2"/>
+      <c r="M284" s="2"/>
+      <c r="N284" s="2"/>
+      <c r="O284" s="2"/>
+      <c r="P284" s="1"/>
     </row>
     <row r="285" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A285" s="18"/>
       <c r="B285" s="18"/>
       <c r="C285" s="18"/>
       <c r="D285" s="19">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E285" s="20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F285" s="20" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G285" s="16"/>
       <c r="H285" s="1"/>
@@ -8438,16 +8323,16 @@
       <c r="B286" s="18"/>
       <c r="C286" s="18"/>
       <c r="D286" s="19">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E286" s="20" t="s">
         <v>50</v>
       </c>
       <c r="F286" s="20" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="G286" s="16"/>
-      <c r="H286" s="1"/>
+      <c r="H286" s="32"/>
       <c r="I286" s="1"/>
       <c r="J286" s="2"/>
       <c r="K286" s="2"/>
@@ -8462,16 +8347,16 @@
       <c r="B287" s="18"/>
       <c r="C287" s="18"/>
       <c r="D287" s="19">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E287" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F287" s="20" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="G287" s="16"/>
-      <c r="H287" s="1"/>
+      <c r="H287" s="33"/>
       <c r="I287" s="1"/>
       <c r="J287" s="2"/>
       <c r="K287" s="2"/>
@@ -8481,45 +8366,45 @@
       <c r="O287" s="2"/>
       <c r="P287" s="1"/>
     </row>
-    <row r="288" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A288" s="18"/>
       <c r="B288" s="18"/>
       <c r="C288" s="18"/>
       <c r="D288" s="19">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E288" s="20" t="s">
         <v>48</v>
       </c>
       <c r="F288" s="20" t="s">
-        <v>331</v>
-      </c>
-      <c r="G288" s="26"/>
-      <c r="H288" s="16"/>
-      <c r="I288" s="16"/>
-      <c r="J288" s="18"/>
-      <c r="K288" s="18"/>
-      <c r="L288" s="18"/>
-      <c r="M288" s="18"/>
-      <c r="N288" s="18"/>
-      <c r="O288" s="18"/>
-      <c r="P288" s="16"/>
+        <v>198</v>
+      </c>
+      <c r="G288" s="16"/>
+      <c r="H288" s="33"/>
+      <c r="I288" s="1"/>
+      <c r="J288" s="2"/>
+      <c r="K288" s="2"/>
+      <c r="L288" s="2"/>
+      <c r="M288" s="2"/>
+      <c r="N288" s="2"/>
+      <c r="O288" s="2"/>
+      <c r="P288" s="1"/>
     </row>
     <row r="289" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A289" s="18"/>
       <c r="B289" s="18"/>
       <c r="C289" s="18"/>
       <c r="D289" s="19">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E289" s="20" t="s">
         <v>48</v>
       </c>
       <c r="F289" s="20" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="G289" s="16"/>
-      <c r="H289" s="1"/>
+      <c r="H289" s="33"/>
       <c r="I289" s="1"/>
       <c r="J289" s="2"/>
       <c r="K289" s="2"/>
@@ -8534,16 +8419,16 @@
       <c r="B290" s="18"/>
       <c r="C290" s="18"/>
       <c r="D290" s="19">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E290" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F290" s="20" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="G290" s="16"/>
-      <c r="H290" s="1"/>
+      <c r="H290" s="33"/>
       <c r="I290" s="1"/>
       <c r="J290" s="2"/>
       <c r="K290" s="2"/>
@@ -8558,16 +8443,16 @@
       <c r="B291" s="18"/>
       <c r="C291" s="18"/>
       <c r="D291" s="19">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E291" s="20" t="s">
         <v>50</v>
       </c>
       <c r="F291" s="20" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="G291" s="16"/>
-      <c r="H291" s="32"/>
+      <c r="H291" s="33"/>
       <c r="I291" s="1"/>
       <c r="J291" s="2"/>
       <c r="K291" s="2"/>
@@ -8582,15 +8467,15 @@
       <c r="B292" s="18"/>
       <c r="C292" s="18"/>
       <c r="D292" s="19">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E292" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="F292" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="G292" s="16"/>
+        <v>73</v>
+      </c>
+      <c r="F292" s="35" t="s">
+        <v>202</v>
+      </c>
+      <c r="G292" s="26"/>
       <c r="H292" s="33"/>
       <c r="I292" s="1"/>
       <c r="J292" s="2"/>
@@ -8606,15 +8491,15 @@
       <c r="B293" s="18"/>
       <c r="C293" s="18"/>
       <c r="D293" s="19">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E293" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F293" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="G293" s="16"/>
+      <c r="F293" s="35" t="s">
+        <v>203</v>
+      </c>
+      <c r="G293" s="26"/>
       <c r="H293" s="33"/>
       <c r="I293" s="1"/>
       <c r="J293" s="2"/>
@@ -8630,15 +8515,15 @@
       <c r="B294" s="18"/>
       <c r="C294" s="18"/>
       <c r="D294" s="19">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E294" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F294" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="G294" s="16"/>
+      <c r="F294" s="35" t="s">
+        <v>204</v>
+      </c>
+      <c r="G294" s="26"/>
       <c r="H294" s="33"/>
       <c r="I294" s="1"/>
       <c r="J294" s="2"/>
@@ -8654,15 +8539,15 @@
       <c r="B295" s="18"/>
       <c r="C295" s="18"/>
       <c r="D295" s="19">
+        <v>54</v>
+      </c>
+      <c r="E295" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="E295" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="F295" s="20" t="s">
-        <v>200</v>
-      </c>
-      <c r="G295" s="16"/>
+      <c r="F295" s="35" t="s">
+        <v>205</v>
+      </c>
+      <c r="G295" s="26"/>
       <c r="H295" s="33"/>
       <c r="I295" s="1"/>
       <c r="J295" s="2"/>
@@ -8678,15 +8563,15 @@
       <c r="B296" s="18"/>
       <c r="C296" s="18"/>
       <c r="D296" s="19">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E296" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="F296" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="G296" s="16"/>
+        <v>48</v>
+      </c>
+      <c r="F296" s="35" t="s">
+        <v>206</v>
+      </c>
+      <c r="G296" s="26"/>
       <c r="H296" s="33"/>
       <c r="I296" s="1"/>
       <c r="J296" s="2"/>
@@ -8697,42 +8582,42 @@
       <c r="O296" s="2"/>
       <c r="P296" s="1"/>
     </row>
-    <row r="297" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A297" s="18"/>
-      <c r="B297" s="18"/>
-      <c r="C297" s="18"/>
+    <row r="297" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A297" s="31"/>
+      <c r="B297" s="31"/>
+      <c r="C297" s="31"/>
       <c r="D297" s="19">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E297" s="20" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="F297" s="35" t="s">
-        <v>202</v>
-      </c>
-      <c r="G297" s="26"/>
-      <c r="H297" s="33"/>
-      <c r="I297" s="1"/>
-      <c r="J297" s="2"/>
-      <c r="K297" s="2"/>
-      <c r="L297" s="2"/>
-      <c r="M297" s="2"/>
-      <c r="N297" s="2"/>
-      <c r="O297" s="2"/>
-      <c r="P297" s="1"/>
+        <v>245</v>
+      </c>
+      <c r="G297" s="25"/>
+      <c r="H297" s="28"/>
+      <c r="I297" s="30"/>
+      <c r="J297" s="31"/>
+      <c r="K297" s="31"/>
+      <c r="L297" s="31"/>
+      <c r="M297" s="31"/>
+      <c r="N297" s="31"/>
+      <c r="O297" s="31"/>
+      <c r="P297" s="30"/>
     </row>
     <row r="298" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A298" s="18"/>
       <c r="B298" s="18"/>
       <c r="C298" s="18"/>
       <c r="D298" s="19">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E298" s="20" t="s">
         <v>48</v>
       </c>
       <c r="F298" s="35" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G298" s="26"/>
       <c r="H298" s="33"/>
@@ -8745,285 +8630,167 @@
       <c r="O298" s="2"/>
       <c r="P298" s="1"/>
     </row>
-    <row r="299" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A299" s="18"/>
       <c r="B299" s="18"/>
       <c r="C299" s="18"/>
       <c r="D299" s="19">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E299" s="20" t="s">
         <v>48</v>
       </c>
       <c r="F299" s="35" t="s">
-        <v>204</v>
+        <v>249</v>
       </c>
       <c r="G299" s="26"/>
-      <c r="H299" s="33"/>
-      <c r="I299" s="1"/>
-      <c r="J299" s="2"/>
-      <c r="K299" s="2"/>
-      <c r="L299" s="2"/>
-      <c r="M299" s="2"/>
-      <c r="N299" s="2"/>
-      <c r="O299" s="2"/>
-      <c r="P299" s="1"/>
-    </row>
-    <row r="300" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A300" s="18"/>
-      <c r="B300" s="18"/>
-      <c r="C300" s="18"/>
-      <c r="D300" s="19">
-        <v>53</v>
-      </c>
-      <c r="E300" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="F300" s="35" t="s">
-        <v>205</v>
-      </c>
-      <c r="G300" s="26"/>
-      <c r="H300" s="33"/>
-      <c r="I300" s="1"/>
-      <c r="J300" s="2"/>
-      <c r="K300" s="2"/>
-      <c r="L300" s="2"/>
-      <c r="M300" s="2"/>
-      <c r="N300" s="2"/>
-      <c r="O300" s="2"/>
-      <c r="P300" s="1"/>
-    </row>
-    <row r="301" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A301" s="18"/>
-      <c r="B301" s="18"/>
-      <c r="C301" s="18"/>
-      <c r="D301" s="19">
-        <v>54</v>
-      </c>
-      <c r="E301" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="F301" s="35" t="s">
-        <v>206</v>
-      </c>
-      <c r="G301" s="26"/>
-      <c r="H301" s="33"/>
+      <c r="H299" s="28"/>
+      <c r="I299" s="30"/>
+      <c r="J299" s="31"/>
+      <c r="K299" s="31"/>
+      <c r="L299" s="31"/>
+      <c r="M299" s="31"/>
+      <c r="N299" s="31"/>
+      <c r="O299" s="31"/>
+      <c r="P299" s="30"/>
+    </row>
+    <row r="300" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A300" s="16"/>
+      <c r="B300" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C300" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D300" s="17"/>
+      <c r="E300" s="17"/>
+      <c r="F300" s="36"/>
+      <c r="G300" s="17"/>
+      <c r="H300" s="37"/>
+      <c r="I300" s="12"/>
+      <c r="J300" s="12"/>
+      <c r="K300" s="12"/>
+      <c r="L300" s="12"/>
+      <c r="M300" s="12"/>
+      <c r="N300" s="12"/>
+      <c r="O300" s="12"/>
+      <c r="P300" s="12"/>
+    </row>
+    <row r="301" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D301" s="15"/>
+      <c r="E301" s="1"/>
+      <c r="F301" s="1"/>
+      <c r="G301" s="1"/>
+      <c r="H301" s="37"/>
       <c r="I301" s="1"/>
-      <c r="J301" s="2"/>
-      <c r="K301" s="2"/>
-      <c r="L301" s="2"/>
-      <c r="M301" s="2"/>
-      <c r="N301" s="2"/>
-      <c r="O301" s="2"/>
       <c r="P301" s="1"/>
     </row>
-    <row r="302" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A302" s="31"/>
-      <c r="B302" s="31"/>
-      <c r="C302" s="31"/>
-      <c r="D302" s="19">
-        <v>55</v>
-      </c>
-      <c r="E302" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="F302" s="35" t="s">
-        <v>314</v>
-      </c>
-      <c r="G302" s="25"/>
-      <c r="H302" s="28"/>
-      <c r="I302" s="30"/>
-      <c r="J302" s="31"/>
-      <c r="K302" s="31"/>
-      <c r="L302" s="31"/>
-      <c r="M302" s="31"/>
-      <c r="N302" s="31"/>
-      <c r="O302" s="31"/>
-      <c r="P302" s="30"/>
-    </row>
-    <row r="303" spans="1:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A303" s="18"/>
-      <c r="B303" s="18"/>
-      <c r="C303" s="18"/>
-      <c r="D303" s="19">
-        <v>56</v>
-      </c>
-      <c r="E303" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="F303" s="35" t="s">
-        <v>207</v>
-      </c>
-      <c r="G303" s="26"/>
+    <row r="302" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D302" s="15"/>
+      <c r="E302" s="1"/>
+      <c r="F302" s="1"/>
+      <c r="G302" s="1"/>
+      <c r="H302" s="37"/>
+      <c r="I302" s="1"/>
+      <c r="P302" s="1"/>
+    </row>
+    <row r="303" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B303" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C303" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D303" s="12"/>
+      <c r="E303" s="12"/>
+      <c r="G303" s="12"/>
       <c r="H303" s="33"/>
-      <c r="I303" s="1"/>
-      <c r="J303" s="2"/>
-      <c r="K303" s="2"/>
-      <c r="L303" s="2"/>
-      <c r="M303" s="2"/>
-      <c r="N303" s="2"/>
-      <c r="O303" s="2"/>
-      <c r="P303" s="1"/>
-    </row>
-    <row r="304" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A304" s="18"/>
-      <c r="B304" s="18"/>
-      <c r="C304" s="18"/>
-      <c r="D304" s="19">
-        <v>57</v>
-      </c>
-      <c r="E304" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="F304" s="35" t="s">
-        <v>318</v>
-      </c>
-      <c r="G304" s="26"/>
-      <c r="H304" s="28"/>
-      <c r="I304" s="30"/>
-      <c r="J304" s="31"/>
-      <c r="K304" s="31"/>
-      <c r="L304" s="31"/>
-      <c r="M304" s="31"/>
-      <c r="N304" s="31"/>
-      <c r="O304" s="31"/>
-      <c r="P304" s="30"/>
-    </row>
-    <row r="305" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A305" s="16"/>
-      <c r="B305" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="C305" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="D305" s="17"/>
-      <c r="E305" s="17"/>
-      <c r="F305" s="36"/>
-      <c r="G305" s="17"/>
-      <c r="H305" s="37"/>
-      <c r="I305" s="12"/>
-      <c r="J305" s="12"/>
-      <c r="K305" s="12"/>
-      <c r="L305" s="12"/>
-      <c r="M305" s="12"/>
-      <c r="N305" s="12"/>
-      <c r="O305" s="12"/>
-      <c r="P305" s="12"/>
-    </row>
-    <row r="306" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D306" s="15"/>
-      <c r="E306" s="1"/>
-      <c r="F306" s="1"/>
-      <c r="G306" s="1"/>
-      <c r="H306" s="37"/>
-      <c r="I306" s="1"/>
-      <c r="P306" s="1"/>
-    </row>
-    <row r="307" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I303" s="12"/>
+      <c r="J303" s="12"/>
+      <c r="K303" s="12"/>
+      <c r="L303" s="12"/>
+      <c r="M303" s="12"/>
+      <c r="N303" s="12"/>
+      <c r="O303" s="12"/>
+      <c r="P303" s="12"/>
+    </row>
+    <row r="304" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D304" s="15"/>
+      <c r="E304" s="1"/>
+      <c r="F304" s="1"/>
+      <c r="G304" s="1"/>
+      <c r="H304" s="33"/>
+      <c r="I304" s="1"/>
+      <c r="P304" s="1"/>
+    </row>
+    <row r="305" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D305" s="15"/>
+      <c r="E305" s="1"/>
+      <c r="F305" s="1"/>
+      <c r="G305" s="1"/>
+      <c r="H305" s="32"/>
+      <c r="I305" s="1"/>
+      <c r="P305" s="1"/>
+    </row>
+    <row r="306" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B306" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C306" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D306" s="12"/>
+      <c r="E306" s="12"/>
+      <c r="F306" s="12"/>
+      <c r="G306" s="12"/>
+      <c r="H306" s="12"/>
+      <c r="I306" s="12"/>
+      <c r="J306" s="12"/>
+      <c r="K306" s="12"/>
+      <c r="L306" s="12"/>
+      <c r="M306" s="12"/>
+      <c r="N306" s="12"/>
+      <c r="O306" s="12"/>
+      <c r="P306" s="12"/>
+    </row>
+    <row r="307" spans="2:16" x14ac:dyDescent="0.25">
       <c r="D307" s="15"/>
       <c r="E307" s="1"/>
       <c r="F307" s="1"/>
       <c r="G307" s="1"/>
-      <c r="H307" s="37"/>
+      <c r="H307" s="1"/>
       <c r="I307" s="1"/>
       <c r="P307" s="1"/>
     </row>
-    <row r="308" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B308" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C308" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D308" s="12"/>
-      <c r="E308" s="12"/>
-      <c r="G308" s="12"/>
-      <c r="H308" s="33"/>
-      <c r="I308" s="12"/>
-      <c r="J308" s="12"/>
-      <c r="K308" s="12"/>
-      <c r="L308" s="12"/>
-      <c r="M308" s="12"/>
-      <c r="N308" s="12"/>
-      <c r="O308" s="12"/>
-      <c r="P308" s="12"/>
-    </row>
-    <row r="309" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D309" s="15"/>
-      <c r="E309" s="1"/>
-      <c r="F309" s="1"/>
-      <c r="G309" s="1"/>
-      <c r="H309" s="33"/>
-      <c r="I309" s="1"/>
-      <c r="P309" s="1"/>
-    </row>
-    <row r="310" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D310" s="15"/>
-      <c r="E310" s="1"/>
+    <row r="308" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D308" s="15"/>
+      <c r="E308" s="1"/>
+      <c r="F308" s="1"/>
+      <c r="G308" s="1"/>
+      <c r="H308" s="1"/>
+      <c r="I308" s="1"/>
+      <c r="P308" s="1"/>
+    </row>
+    <row r="309" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="F309" s="12"/>
+    </row>
+    <row r="310" spans="2:16" x14ac:dyDescent="0.25">
       <c r="F310" s="1"/>
-      <c r="G310" s="1"/>
-      <c r="H310" s="32"/>
-      <c r="I310" s="1"/>
-      <c r="P310" s="1"/>
-    </row>
-    <row r="311" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B311" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C311" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D311" s="12"/>
-      <c r="E311" s="12"/>
-      <c r="F311" s="12"/>
-      <c r="G311" s="12"/>
-      <c r="H311" s="12"/>
-      <c r="I311" s="12"/>
-      <c r="J311" s="12"/>
-      <c r="K311" s="12"/>
-      <c r="L311" s="12"/>
-      <c r="M311" s="12"/>
-      <c r="N311" s="12"/>
-      <c r="O311" s="12"/>
-      <c r="P311" s="12"/>
-    </row>
-    <row r="312" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D312" s="15"/>
-      <c r="E312" s="1"/>
-      <c r="F312" s="1"/>
-      <c r="G312" s="1"/>
-      <c r="H312" s="1"/>
-      <c r="I312" s="1"/>
-      <c r="P312" s="1"/>
-    </row>
-    <row r="313" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D313" s="15"/>
-      <c r="E313" s="1"/>
+    </row>
+    <row r="311" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="F311" s="1"/>
+    </row>
+    <row r="312" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="F312" s="12"/>
+    </row>
+    <row r="313" spans="2:16" x14ac:dyDescent="0.25">
       <c r="F313" s="1"/>
-      <c r="G313" s="1"/>
-      <c r="H313" s="1"/>
-      <c r="I313" s="1"/>
-      <c r="P313" s="1"/>
-    </row>
-    <row r="314" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="F314" s="12"/>
-    </row>
-    <row r="315" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="F315" s="1"/>
-    </row>
-    <row r="316" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="F316" s="1"/>
-    </row>
-    <row r="317" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="F317" s="12"/>
-    </row>
-    <row r="318" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="F318" s="1"/>
-    </row>
-    <row r="319" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="F319" s="1"/>
-    </row>
+    </row>
+    <row r="314" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="F314" s="1"/>
+    </row>
+    <row r="1185" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="1186" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <sheetProtection formatCells="0" formatRows="0" insertRows="0" insertHyperlinks="0" deleteRows="0" sort="0" autoFilter="0"/>
   <autoFilter ref="B10:P210" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -9032,29 +8799,29 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="9">
-    <dataValidation allowBlank="1" showInputMessage="1" sqref="C11 C14 C17 C20 C23 C26 C29 C32 C35 C246 C305 C308 C311" xr:uid="{EB9C12FD-8334-4B4F-B7C9-4AD293EA6488}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Object Code value" error="The Object code value shall be:_x000a_VARIABLE_x000a_RECORD_x000a_ARRAY" sqref="C12:C13 C15:C16 C18:C19 C21:C22 C24:C25 C27:C28 C30:C31 C33:C34 C36:C245 C306:C307 C309:C310 C312:C324 C247:C304" xr:uid="{184AA84D-6823-428D-8003-7C8E9BFDFE4A}">
+    <dataValidation allowBlank="1" showInputMessage="1" sqref="C11 C14 C17 C20 C23 C26 C29 C32 C35 C240 C300 C303 C306" xr:uid="{04624C85-6872-4B97-88BB-D06A696ED408}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Object Code value" error="The Object code value shall be:_x000a_VARIABLE_x000a_RECORD_x000a_ARRAY" sqref="C12:C13 C15:C16 C18:C19 C21:C22 C24:C25 C27:C28 C30:C31 C33:C34 C241:C299 C301:C302 C304:C305 C307:C319 C36:C75 C85:C239" xr:uid="{FDC2CF25-BDB1-44CB-AAED-806E7BCF15DA}">
       <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Category" error="The value for the entry category shall be _x000a_M : (mandatory)_x000a_O : (optional) _x000a_C : (conditional)" sqref="J36 J12:J13 J15:J16 J18:J19 J21:J22 J24:J25 J27:J28 J30:J31 J33:J34 J40:J245 J306:J307 J309:J310 J312:J324 J247:J304" xr:uid="{AE32B420-A676-4C90-AFA3-F07C93BD9C44}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Category" error="The value for the entry category shall be _x000a_M : (mandatory)_x000a_O : (optional) _x000a_C : (conditional)" sqref="J36 J12:J13 J15:J16 J18:J19 J21:J22 J24:J25 J27:J28 J30:J31 J33:J34 J241:J299 J301:J302 J304:J305 J307:J319 J40:J75 J85:J239" xr:uid="{CF90A607-18C9-4B74-888E-F20807E53841}">
       <formula1>"M,O,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Backup/Setting Flag" error="The entry flag shall be_x000a_B : (Backup)_x000a_S : (Setting)" sqref="K36 K12:K13 K15:K16 K18:K19 K21:K22 K24:K25 K27:K28 K30:K31 K33:K34 K40:K245 K306:K307 K309:K310 K312:K324 K247:K304" xr:uid="{362B18B7-EE64-4501-A07E-5A13EF15F647}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Backup/Setting Flag" error="The entry flag shall be_x000a_B : (Backup)_x000a_S : (Setting)" sqref="K36 K12:K13 K15:K16 K18:K19 K21:K22 K24:K25 K27:K28 K30:K31 K33:K34 K241:K299 K301:K302 K304:K305 K307:K319 K40:K75 K85:K239" xr:uid="{82F784E9-AB3D-4B94-88D5-8A35418338A6}">
       <formula1>"B,S"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M36:O36 M12:O13 M18:O19 M24:O25 M30:O31 M306:O307 M312:O313 M15:O16 M21:O22 M27:O28 M33:O34 M309:O310 M40:O245 M247:O304" xr:uid="{C5FA5D07-25FC-420F-9AA3-869A1BF559CA}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M36:O36 M12:O13 M18:O19 M24:O25 M30:O31 M301:O302 M307:O308 M15:O16 M21:O22 M27:O28 M33:O34 M304:O305 M241:O299 M40:O75 M85:O239" xr:uid="{045DC1ED-1225-4D80-8A04-840B5CE43AA9}">
       <formula1>"rx,tx"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C325:C1164" xr:uid="{D858724E-8601-415C-8570-99CF1472ECB6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C320:C1159" xr:uid="{0C3870FE-B39E-4E87-B735-8356C325F1AE}">
       <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J37:J39" xr:uid="{B600F59E-272A-4B41-91C8-F5FC9903D8BC}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J37:J39" xr:uid="{4BEF505F-8FF0-41B6-B42B-C39F5C00D571}">
       <formula1>"M,O,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K37:K39" xr:uid="{E0B56AA1-26D7-4E6F-8C83-EC1A2241D48B}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K37:K39" xr:uid="{24B17AED-423A-4B38-A4B0-96D698A3C924}">
       <formula1>"B,S"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M37:O39" xr:uid="{1546D867-1948-4D67-A011-5AF2FD4957B0}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M37:O39" xr:uid="{4ADD644A-32D7-4DB9-B4EA-625954A50F3E}">
       <formula1>"rx,tx"</formula1>
     </dataValidation>
   </dataValidations>

--- a/ArmCoreV1_QSPI/SSCProject/lan9252_app.xlsx
+++ b/ArmCoreV1_QSPI/SSCProject/lan9252_app.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SI\project\RTM_ON_NEW\FW-ArmCore\ArmCoreV1_QSPI\SSCProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9BD2B12-9DA0-41A2-9D10-3F731D7B00BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9469E864-6D82-47E8-8BC2-912A62346D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="403">
   <si>
     <t>Device Profile:</t>
   </si>
@@ -1414,6 +1414,10 @@
   </si>
   <si>
     <t>OutU32_rtm_off_treatment_mode</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>InU32_rtm_off_search_timeout_cur</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1665,9 +1669,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection locked="0"/>
@@ -1686,6 +1687,9 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1996,7 +2000,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T392"/>
+  <dimension ref="A1:T393"/>
   <sheetFormatPr defaultColWidth="10.7265625" defaultRowHeight="13" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.81640625" style="4" customWidth="1"/>
@@ -2028,19 +2032,19 @@
         <v>1</v>
       </c>
       <c r="E1" s="1"/>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="33" t="s">
         <v>292</v>
       </c>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
       <c r="Q1" s="15"/>
       <c r="R1" s="15"/>
       <c r="S1" s="15"/>
@@ -2054,17 +2058,17 @@
         <v>3</v>
       </c>
       <c r="E2" s="1"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
       <c r="Q2" s="15"/>
       <c r="R2" s="15"/>
       <c r="S2" s="15"/>
@@ -2075,17 +2079,17 @@
       <c r="C3" s="14"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="33"/>
+      <c r="M3" s="33"/>
+      <c r="N3" s="33"/>
+      <c r="O3" s="33"/>
+      <c r="P3" s="33"/>
       <c r="Q3" s="15"/>
       <c r="R3" s="15"/>
       <c r="S3" s="15"/>
@@ -2096,17 +2100,17 @@
       <c r="C4" s="14"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="33"/>
+      <c r="M4" s="33"/>
+      <c r="N4" s="33"/>
+      <c r="O4" s="33"/>
+      <c r="P4" s="33"/>
       <c r="Q4" s="15"/>
       <c r="R4" s="15"/>
       <c r="S4" s="15"/>
@@ -2117,17 +2121,17 @@
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
-      <c r="M5" s="26"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="26"/>
-      <c r="P5" s="26"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="33"/>
+      <c r="M5" s="33"/>
+      <c r="N5" s="33"/>
+      <c r="O5" s="33"/>
+      <c r="P5" s="33"/>
       <c r="Q5" s="15"/>
       <c r="R5" s="15"/>
       <c r="S5" s="15"/>
@@ -2138,17 +2142,17 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="26"/>
-      <c r="M6" s="26"/>
-      <c r="N6" s="26"/>
-      <c r="O6" s="26"/>
-      <c r="P6" s="26"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="33"/>
+      <c r="M6" s="33"/>
+      <c r="N6" s="33"/>
+      <c r="O6" s="33"/>
+      <c r="P6" s="33"/>
       <c r="Q6" s="15"/>
       <c r="R6" s="15"/>
       <c r="S6" s="15"/>
@@ -2259,25 +2263,25 @@
       </c>
     </row>
     <row r="11" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="27"/>
-      <c r="K11" s="27"/>
-      <c r="L11" s="27"/>
-      <c r="M11" s="27"/>
-      <c r="N11" s="27"/>
-      <c r="O11" s="27"/>
-      <c r="P11" s="27"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="26"/>
+      <c r="M11" s="26"/>
+      <c r="N11" s="26"/>
+      <c r="O11" s="26"/>
+      <c r="P11" s="26"/>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B12" s="1"/>
@@ -2306,25 +2310,25 @@
       <c r="P13" s="3"/>
     </row>
     <row r="14" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="27" t="s">
+      <c r="C14" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="27"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="27"/>
-      <c r="L14" s="27"/>
-      <c r="M14" s="27"/>
-      <c r="N14" s="27"/>
-      <c r="O14" s="27"/>
-      <c r="P14" s="27"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="26"/>
+      <c r="M14" s="26"/>
+      <c r="N14" s="26"/>
+      <c r="O14" s="26"/>
+      <c r="P14" s="26"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.25">
       <c r="D15" s="5"/>
@@ -2345,25 +2349,25 @@
       <c r="P16" s="3"/>
     </row>
     <row r="17" spans="2:16" s="3" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="27"/>
-      <c r="J17" s="27"/>
-      <c r="K17" s="27"/>
-      <c r="L17" s="27"/>
-      <c r="M17" s="27"/>
-      <c r="N17" s="27"/>
-      <c r="O17" s="27"/>
-      <c r="P17" s="27"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="26"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="26"/>
+      <c r="M17" s="26"/>
+      <c r="N17" s="26"/>
+      <c r="O17" s="26"/>
+      <c r="P17" s="26"/>
     </row>
     <row r="18" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="D18" s="5"/>
@@ -2384,25 +2388,25 @@
       <c r="P19" s="3"/>
     </row>
     <row r="20" spans="2:16" s="3" customFormat="1" ht="14" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="27" t="s">
+      <c r="C20" s="26" t="s">
         <v>293</v>
       </c>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="27"/>
-      <c r="K20" s="27"/>
-      <c r="L20" s="27"/>
-      <c r="M20" s="27"/>
-      <c r="N20" s="27"/>
-      <c r="O20" s="27"/>
-      <c r="P20" s="27"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="26"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="26"/>
+      <c r="M20" s="26"/>
+      <c r="N20" s="26"/>
+      <c r="O20" s="26"/>
+      <c r="P20" s="26"/>
     </row>
     <row r="21" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="D21" s="5"/>
@@ -2423,25 +2427,25 @@
       <c r="P22" s="3"/>
     </row>
     <row r="23" spans="2:16" s="3" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="27" t="s">
+      <c r="C23" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="27"/>
-      <c r="M23" s="27"/>
-      <c r="N23" s="27"/>
-      <c r="O23" s="27"/>
-      <c r="P23" s="27"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="26"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="26"/>
     </row>
     <row r="24" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="D24" s="5"/>
@@ -2462,25 +2466,25 @@
       <c r="P25" s="3"/>
     </row>
     <row r="26" spans="2:16" s="3" customFormat="1" ht="14" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="27" t="s">
+      <c r="B26" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="27" t="s">
+      <c r="C26" s="26" t="s">
         <v>294</v>
       </c>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="27"/>
-      <c r="J26" s="27"/>
-      <c r="K26" s="27"/>
-      <c r="L26" s="27"/>
-      <c r="M26" s="27"/>
-      <c r="N26" s="27"/>
-      <c r="O26" s="27"/>
-      <c r="P26" s="27"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="26"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="26"/>
+      <c r="M26" s="26"/>
+      <c r="N26" s="26"/>
+      <c r="O26" s="26"/>
+      <c r="P26" s="26"/>
     </row>
     <row r="27" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="D27" s="5"/>
@@ -2501,25 +2505,25 @@
       <c r="P28" s="3"/>
     </row>
     <row r="29" spans="2:16" s="3" customFormat="1" ht="14" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="27" t="s">
+      <c r="B29" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C29" s="27" t="s">
+      <c r="C29" s="26" t="s">
         <v>295</v>
       </c>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27"/>
-      <c r="K29" s="27"/>
-      <c r="L29" s="27"/>
-      <c r="M29" s="27"/>
-      <c r="N29" s="27"/>
-      <c r="O29" s="27"/>
-      <c r="P29" s="27"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="26"/>
+      <c r="J29" s="26"/>
+      <c r="K29" s="26"/>
+      <c r="L29" s="26"/>
+      <c r="M29" s="26"/>
+      <c r="N29" s="26"/>
+      <c r="O29" s="26"/>
+      <c r="P29" s="26"/>
     </row>
     <row r="30" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="D30" s="5"/>
@@ -2540,25 +2544,25 @@
       <c r="P31" s="3"/>
     </row>
     <row r="32" spans="2:16" s="3" customFormat="1" ht="14" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="27" t="s">
+      <c r="C32" s="26" t="s">
         <v>296</v>
       </c>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="27"/>
-      <c r="J32" s="27"/>
-      <c r="K32" s="27"/>
-      <c r="L32" s="27"/>
-      <c r="M32" s="27"/>
-      <c r="N32" s="27"/>
-      <c r="O32" s="27"/>
-      <c r="P32" s="27"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="26"/>
+      <c r="J32" s="26"/>
+      <c r="K32" s="26"/>
+      <c r="L32" s="26"/>
+      <c r="M32" s="26"/>
+      <c r="N32" s="26"/>
+      <c r="O32" s="26"/>
+      <c r="P32" s="26"/>
     </row>
     <row r="33" spans="1:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="D33" s="5"/>
@@ -2579,25 +2583,25 @@
       <c r="P34" s="3"/>
     </row>
     <row r="35" spans="1:16" s="3" customFormat="1" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="27" t="s">
+      <c r="B35" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C35" s="27" t="s">
+      <c r="C35" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="D35" s="27"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
-      <c r="H35" s="27"/>
-      <c r="I35" s="27"/>
-      <c r="J35" s="27"/>
-      <c r="K35" s="27"/>
-      <c r="L35" s="27"/>
-      <c r="M35" s="27"/>
-      <c r="N35" s="27"/>
-      <c r="O35" s="27"/>
-      <c r="P35" s="27"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="26"/>
+      <c r="I35" s="26"/>
+      <c r="J35" s="26"/>
+      <c r="K35" s="26"/>
+      <c r="L35" s="26"/>
+      <c r="M35" s="26"/>
+      <c r="N35" s="26"/>
+      <c r="O35" s="26"/>
+      <c r="P35" s="26"/>
     </row>
     <row r="36" spans="1:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
@@ -7244,13 +7248,13 @@
       <c r="D245" s="6">
         <v>209</v>
       </c>
-      <c r="E245" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F245" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="G245" s="3"/>
+      <c r="E245" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F245" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="G245" s="8"/>
       <c r="H245" s="3"/>
       <c r="I245" s="3"/>
       <c r="J245" s="4"/>
@@ -7272,7 +7276,7 @@
         <v>48</v>
       </c>
       <c r="F246" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G246" s="3"/>
       <c r="H246" s="3"/>
@@ -7293,10 +7297,10 @@
         <v>211</v>
       </c>
       <c r="E247" s="6" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="F247" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G247" s="3"/>
       <c r="H247" s="3"/>
@@ -7317,10 +7321,10 @@
         <v>212</v>
       </c>
       <c r="E248" s="6" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="F248" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G248" s="3"/>
       <c r="H248" s="3"/>
@@ -7344,7 +7348,7 @@
         <v>48</v>
       </c>
       <c r="F249" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G249" s="3"/>
       <c r="H249" s="3"/>
@@ -7365,10 +7369,10 @@
         <v>214</v>
       </c>
       <c r="E250" s="6" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F250" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G250" s="3"/>
       <c r="H250" s="3"/>
@@ -7381,7 +7385,7 @@
       <c r="O250" s="4"/>
       <c r="P250" s="3"/>
     </row>
-    <row r="251" spans="1:16" s="1" customFormat="1" ht="78.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:16" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.25">
       <c r="A251" s="4"/>
       <c r="B251" s="4"/>
       <c r="C251" s="4"/>
@@ -7389,12 +7393,12 @@
         <v>215</v>
       </c>
       <c r="E251" s="6" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F251" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="G251" s="8"/>
+        <v>127</v>
+      </c>
+      <c r="G251" s="3"/>
       <c r="H251" s="3"/>
       <c r="I251" s="3"/>
       <c r="J251" s="4"/>
@@ -7405,7 +7409,7 @@
       <c r="O251" s="4"/>
       <c r="P251" s="3"/>
     </row>
-    <row r="252" spans="1:16" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:16" s="1" customFormat="1" ht="78.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="4"/>
       <c r="B252" s="4"/>
       <c r="C252" s="4"/>
@@ -7416,9 +7420,9 @@
         <v>50</v>
       </c>
       <c r="F252" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="G252" s="3"/>
+        <v>128</v>
+      </c>
+      <c r="G252" s="8"/>
       <c r="H252" s="3"/>
       <c r="I252" s="3"/>
       <c r="J252" s="4"/>
@@ -7440,7 +7444,7 @@
         <v>50</v>
       </c>
       <c r="F253" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G253" s="3"/>
       <c r="H253" s="3"/>
@@ -7464,7 +7468,7 @@
         <v>50</v>
       </c>
       <c r="F254" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G254" s="3"/>
       <c r="H254" s="3"/>
@@ -7485,10 +7489,10 @@
         <v>219</v>
       </c>
       <c r="E255" s="6" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F255" s="6" t="s">
-        <v>363</v>
+        <v>131</v>
       </c>
       <c r="G255" s="3"/>
       <c r="H255" s="3"/>
@@ -7512,7 +7516,7 @@
         <v>70</v>
       </c>
       <c r="F256" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G256" s="3"/>
       <c r="H256" s="3"/>
@@ -7536,7 +7540,7 @@
         <v>70</v>
       </c>
       <c r="F257" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G257" s="3"/>
       <c r="H257" s="3"/>
@@ -7557,10 +7561,10 @@
         <v>222</v>
       </c>
       <c r="E258" s="6" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="F258" s="6" t="s">
-        <v>132</v>
+        <v>365</v>
       </c>
       <c r="G258" s="3"/>
       <c r="H258" s="3"/>
@@ -7581,10 +7585,10 @@
         <v>223</v>
       </c>
       <c r="E259" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F259" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G259" s="3"/>
       <c r="H259" s="3"/>
@@ -7608,7 +7612,7 @@
         <v>52</v>
       </c>
       <c r="F260" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G260" s="3"/>
       <c r="H260" s="3"/>
@@ -7629,10 +7633,10 @@
         <v>225</v>
       </c>
       <c r="E261" s="6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F261" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G261" s="3"/>
       <c r="H261" s="3"/>
@@ -7656,7 +7660,7 @@
         <v>48</v>
       </c>
       <c r="F262" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G262" s="3"/>
       <c r="H262" s="3"/>
@@ -7677,10 +7681,10 @@
         <v>227</v>
       </c>
       <c r="E263" s="6" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="F263" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G263" s="3"/>
       <c r="H263" s="3"/>
@@ -7701,10 +7705,10 @@
         <v>228</v>
       </c>
       <c r="E264" s="6" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="F264" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G264" s="3"/>
       <c r="H264" s="3"/>
@@ -7728,7 +7732,7 @@
         <v>48</v>
       </c>
       <c r="F265" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G265" s="3"/>
       <c r="H265" s="3"/>
@@ -7749,10 +7753,10 @@
         <v>230</v>
       </c>
       <c r="E266" s="6" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F266" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G266" s="3"/>
       <c r="H266" s="3"/>
@@ -7765,7 +7769,7 @@
       <c r="O266" s="4"/>
       <c r="P266" s="3"/>
     </row>
-    <row r="267" spans="1:16" s="1" customFormat="1" ht="128.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:16" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.25">
       <c r="A267" s="4"/>
       <c r="B267" s="4"/>
       <c r="C267" s="4"/>
@@ -7773,12 +7777,12 @@
         <v>231</v>
       </c>
       <c r="E267" s="6" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F267" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="G267" s="8"/>
+        <v>140</v>
+      </c>
+      <c r="G267" s="3"/>
       <c r="H267" s="3"/>
       <c r="I267" s="3"/>
       <c r="J267" s="4"/>
@@ -7789,7 +7793,7 @@
       <c r="O267" s="4"/>
       <c r="P267" s="3"/>
     </row>
-    <row r="268" spans="1:16" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:16" s="1" customFormat="1" ht="128.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="4"/>
       <c r="B268" s="4"/>
       <c r="C268" s="4"/>
@@ -7800,9 +7804,9 @@
         <v>50</v>
       </c>
       <c r="F268" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G268" s="3"/>
+        <v>141</v>
+      </c>
+      <c r="G268" s="8"/>
       <c r="H268" s="3"/>
       <c r="I268" s="3"/>
       <c r="J268" s="4"/>
@@ -7824,7 +7828,7 @@
         <v>50</v>
       </c>
       <c r="F269" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G269" s="3"/>
       <c r="H269" s="3"/>
@@ -7848,7 +7852,7 @@
         <v>50</v>
       </c>
       <c r="F270" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G270" s="3"/>
       <c r="H270" s="3"/>
@@ -7869,10 +7873,10 @@
         <v>235</v>
       </c>
       <c r="E271" s="6" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F271" s="6" t="s">
-        <v>366</v>
+        <v>144</v>
       </c>
       <c r="G271" s="3"/>
       <c r="H271" s="3"/>
@@ -7896,7 +7900,7 @@
         <v>70</v>
       </c>
       <c r="F272" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G272" s="3"/>
       <c r="H272" s="3"/>
@@ -7920,7 +7924,7 @@
         <v>70</v>
       </c>
       <c r="F273" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G273" s="3"/>
       <c r="H273" s="3"/>
@@ -7941,10 +7945,10 @@
         <v>238</v>
       </c>
       <c r="E274" s="6" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="F274" s="6" t="s">
-        <v>145</v>
+        <v>368</v>
       </c>
       <c r="G274" s="3"/>
       <c r="H274" s="3"/>
@@ -7965,10 +7969,10 @@
         <v>239</v>
       </c>
       <c r="E275" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F275" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G275" s="3"/>
       <c r="H275" s="3"/>
@@ -7992,7 +7996,7 @@
         <v>52</v>
       </c>
       <c r="F276" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G276" s="3"/>
       <c r="H276" s="3"/>
@@ -8016,7 +8020,7 @@
         <v>52</v>
       </c>
       <c r="F277" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G277" s="3"/>
       <c r="H277" s="3"/>
@@ -8040,7 +8044,7 @@
         <v>52</v>
       </c>
       <c r="F278" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G278" s="3"/>
       <c r="H278" s="3"/>
@@ -8064,7 +8068,7 @@
         <v>52</v>
       </c>
       <c r="F279" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G279" s="3"/>
       <c r="H279" s="3"/>
@@ -8088,7 +8092,7 @@
         <v>52</v>
       </c>
       <c r="F280" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G280" s="3"/>
       <c r="H280" s="3"/>
@@ -8112,7 +8116,7 @@
         <v>52</v>
       </c>
       <c r="F281" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G281" s="3"/>
       <c r="H281" s="3"/>
@@ -8136,7 +8140,7 @@
         <v>52</v>
       </c>
       <c r="F282" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G282" s="3"/>
       <c r="H282" s="3"/>
@@ -8160,7 +8164,7 @@
         <v>52</v>
       </c>
       <c r="F283" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G283" s="3"/>
       <c r="H283" s="3"/>
@@ -8184,7 +8188,7 @@
         <v>52</v>
       </c>
       <c r="F284" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G284" s="3"/>
       <c r="H284" s="3"/>
@@ -8208,7 +8212,7 @@
         <v>52</v>
       </c>
       <c r="F285" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G285" s="3"/>
       <c r="H285" s="3"/>
@@ -8232,7 +8236,7 @@
         <v>52</v>
       </c>
       <c r="F286" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G286" s="3"/>
       <c r="H286" s="3"/>
@@ -8252,13 +8256,13 @@
       <c r="D287" s="6">
         <v>251</v>
       </c>
-      <c r="E287" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="F287" s="23" t="s">
-        <v>369</v>
-      </c>
-      <c r="G287" s="24"/>
+      <c r="E287" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F287" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="G287" s="3"/>
       <c r="H287" s="3"/>
       <c r="I287" s="3"/>
       <c r="J287" s="4"/>
@@ -8280,7 +8284,7 @@
         <v>48</v>
       </c>
       <c r="F288" s="23" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G288" s="24"/>
       <c r="H288" s="3"/>
@@ -8293,45 +8297,45 @@
       <c r="O288" s="4"/>
       <c r="P288" s="3"/>
     </row>
-    <row r="289" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B289" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="C289" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D289" s="5"/>
-      <c r="E289" s="3"/>
-      <c r="F289" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G289" s="3"/>
+    <row r="289" spans="1:16" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.25">
+      <c r="A289" s="4"/>
+      <c r="B289" s="4"/>
+      <c r="C289" s="4"/>
+      <c r="D289" s="6">
+        <v>253</v>
+      </c>
+      <c r="E289" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="F289" s="23" t="s">
+        <v>370</v>
+      </c>
+      <c r="G289" s="24"/>
       <c r="H289" s="3"/>
       <c r="I289" s="3"/>
+      <c r="J289" s="4"/>
+      <c r="K289" s="4"/>
+      <c r="L289" s="4"/>
+      <c r="M289" s="4"/>
+      <c r="N289" s="4"/>
+      <c r="O289" s="4"/>
       <c r="P289" s="3"/>
     </row>
-    <row r="290" spans="1:16" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.25">
-      <c r="A290" s="4"/>
-      <c r="B290" s="4"/>
-      <c r="C290" s="4"/>
-      <c r="D290" s="6">
-        <v>1</v>
-      </c>
-      <c r="E290" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="F290" s="29" t="s">
-        <v>376</v>
-      </c>
-      <c r="G290" s="25"/>
+    <row r="290" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B290" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="C290" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D290" s="5"/>
+      <c r="E290" s="3"/>
+      <c r="F290" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G290" s="3"/>
       <c r="H290" s="3"/>
       <c r="I290" s="3"/>
-      <c r="J290" s="4"/>
-      <c r="K290" s="4"/>
-      <c r="L290" s="4"/>
-      <c r="M290" s="4"/>
-      <c r="N290" s="4"/>
-      <c r="O290" s="4"/>
       <c r="P290" s="3"/>
     </row>
     <row r="291" spans="1:16" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.25">
@@ -8339,15 +8343,15 @@
       <c r="B291" s="4"/>
       <c r="C291" s="4"/>
       <c r="D291" s="6">
-        <v>2</v>
-      </c>
-      <c r="E291" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="F291" s="30" t="s">
-        <v>377</v>
-      </c>
-      <c r="G291" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="E291" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="F291" s="28" t="s">
+        <v>376</v>
+      </c>
+      <c r="G291" s="25"/>
       <c r="H291" s="3"/>
       <c r="I291" s="3"/>
       <c r="J291" s="4"/>
@@ -8363,13 +8367,13 @@
       <c r="B292" s="4"/>
       <c r="C292" s="4"/>
       <c r="D292" s="6">
-        <v>3</v>
-      </c>
-      <c r="E292" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="E292" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="F292" s="30" t="s">
-        <v>378</v>
+      <c r="F292" s="29" t="s">
+        <v>377</v>
       </c>
       <c r="G292" s="3"/>
       <c r="H292" s="3"/>
@@ -8387,13 +8391,13 @@
       <c r="B293" s="4"/>
       <c r="C293" s="4"/>
       <c r="D293" s="6">
-        <v>4</v>
-      </c>
-      <c r="E293" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="E293" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="F293" s="30" t="s">
-        <v>379</v>
+      <c r="F293" s="29" t="s">
+        <v>378</v>
       </c>
       <c r="G293" s="3"/>
       <c r="H293" s="3"/>
@@ -8411,15 +8415,15 @@
       <c r="B294" s="4"/>
       <c r="C294" s="4"/>
       <c r="D294" s="6">
-        <v>5</v>
-      </c>
-      <c r="E294" s="28" t="s">
-        <v>50</v>
+        <v>4</v>
+      </c>
+      <c r="E294" s="29" t="s">
+        <v>70</v>
       </c>
       <c r="F294" s="29" t="s">
-        <v>380</v>
-      </c>
-      <c r="G294" s="25"/>
+        <v>379</v>
+      </c>
+      <c r="G294" s="3"/>
       <c r="H294" s="3"/>
       <c r="I294" s="3"/>
       <c r="J294" s="4"/>
@@ -8435,15 +8439,15 @@
       <c r="B295" s="4"/>
       <c r="C295" s="4"/>
       <c r="D295" s="6">
-        <v>6</v>
-      </c>
-      <c r="E295" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="F295" s="30" t="s">
-        <v>381</v>
-      </c>
-      <c r="G295" s="3"/>
+        <v>5</v>
+      </c>
+      <c r="E295" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="F295" s="28" t="s">
+        <v>380</v>
+      </c>
+      <c r="G295" s="25"/>
       <c r="H295" s="3"/>
       <c r="I295" s="3"/>
       <c r="J295" s="4"/>
@@ -8459,13 +8463,13 @@
       <c r="B296" s="4"/>
       <c r="C296" s="4"/>
       <c r="D296" s="6">
-        <v>7</v>
-      </c>
-      <c r="E296" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="E296" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="F296" s="30" t="s">
-        <v>382</v>
+      <c r="F296" s="29" t="s">
+        <v>381</v>
       </c>
       <c r="G296" s="3"/>
       <c r="H296" s="3"/>
@@ -8483,13 +8487,13 @@
       <c r="B297" s="4"/>
       <c r="C297" s="4"/>
       <c r="D297" s="6">
-        <v>8</v>
-      </c>
-      <c r="E297" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="E297" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="F297" s="30" t="s">
-        <v>383</v>
+      <c r="F297" s="29" t="s">
+        <v>382</v>
       </c>
       <c r="G297" s="3"/>
       <c r="H297" s="3"/>
@@ -8507,15 +8511,15 @@
       <c r="B298" s="4"/>
       <c r="C298" s="4"/>
       <c r="D298" s="6">
-        <v>9</v>
-      </c>
-      <c r="E298" s="28" t="s">
-        <v>50</v>
+        <v>8</v>
+      </c>
+      <c r="E298" s="29" t="s">
+        <v>70</v>
       </c>
       <c r="F298" s="29" t="s">
-        <v>384</v>
-      </c>
-      <c r="G298" s="25"/>
+        <v>383</v>
+      </c>
+      <c r="G298" s="3"/>
       <c r="H298" s="3"/>
       <c r="I298" s="3"/>
       <c r="J298" s="4"/>
@@ -8531,15 +8535,15 @@
       <c r="B299" s="4"/>
       <c r="C299" s="4"/>
       <c r="D299" s="6">
-        <v>10</v>
-      </c>
-      <c r="E299" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="F299" s="30" t="s">
-        <v>385</v>
-      </c>
-      <c r="G299" s="3"/>
+        <v>9</v>
+      </c>
+      <c r="E299" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="F299" s="28" t="s">
+        <v>384</v>
+      </c>
+      <c r="G299" s="25"/>
       <c r="H299" s="3"/>
       <c r="I299" s="3"/>
       <c r="J299" s="4"/>
@@ -8555,13 +8559,13 @@
       <c r="B300" s="4"/>
       <c r="C300" s="4"/>
       <c r="D300" s="6">
-        <v>11</v>
-      </c>
-      <c r="E300" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="E300" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="F300" s="30" t="s">
-        <v>386</v>
+      <c r="F300" s="29" t="s">
+        <v>385</v>
       </c>
       <c r="G300" s="3"/>
       <c r="H300" s="3"/>
@@ -8579,13 +8583,13 @@
       <c r="B301" s="4"/>
       <c r="C301" s="4"/>
       <c r="D301" s="6">
-        <v>12</v>
-      </c>
-      <c r="E301" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E301" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="F301" s="30" t="s">
-        <v>387</v>
+      <c r="F301" s="29" t="s">
+        <v>386</v>
       </c>
       <c r="G301" s="3"/>
       <c r="H301" s="3"/>
@@ -8602,16 +8606,16 @@
       <c r="A302" s="4"/>
       <c r="B302" s="4"/>
       <c r="C302" s="4"/>
-      <c r="D302" s="11">
-        <v>13</v>
-      </c>
-      <c r="E302" s="10" t="s">
+      <c r="D302" s="6">
+        <v>12</v>
+      </c>
+      <c r="E302" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="F302" s="13" t="s">
-        <v>371</v>
-      </c>
-      <c r="G302" s="31"/>
+      <c r="F302" s="29" t="s">
+        <v>387</v>
+      </c>
+      <c r="G302" s="3"/>
       <c r="H302" s="3"/>
       <c r="I302" s="3"/>
       <c r="J302" s="4"/>
@@ -8627,15 +8631,15 @@
       <c r="B303" s="4"/>
       <c r="C303" s="4"/>
       <c r="D303" s="11">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E303" s="10" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="F303" s="13" t="s">
-        <v>372</v>
-      </c>
-      <c r="G303" s="31"/>
+        <v>371</v>
+      </c>
+      <c r="G303" s="30"/>
       <c r="H303" s="3"/>
       <c r="I303" s="3"/>
       <c r="J303" s="4"/>
@@ -8651,15 +8655,15 @@
       <c r="B304" s="4"/>
       <c r="C304" s="4"/>
       <c r="D304" s="11">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E304" s="10" t="s">
         <v>52</v>
       </c>
       <c r="F304" s="13" t="s">
-        <v>373</v>
-      </c>
-      <c r="G304" s="31"/>
+        <v>372</v>
+      </c>
+      <c r="G304" s="30"/>
       <c r="H304" s="3"/>
       <c r="I304" s="3"/>
       <c r="J304" s="4"/>
@@ -8675,15 +8679,15 @@
       <c r="B305" s="4"/>
       <c r="C305" s="4"/>
       <c r="D305" s="11">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E305" s="10" t="s">
         <v>52</v>
       </c>
       <c r="F305" s="13" t="s">
-        <v>374</v>
-      </c>
-      <c r="G305" s="31"/>
+        <v>373</v>
+      </c>
+      <c r="G305" s="30"/>
       <c r="H305" s="3"/>
       <c r="I305" s="3"/>
       <c r="J305" s="4"/>
@@ -8699,15 +8703,15 @@
       <c r="B306" s="4"/>
       <c r="C306" s="4"/>
       <c r="D306" s="11">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E306" s="10" t="s">
         <v>52</v>
       </c>
       <c r="F306" s="13" t="s">
-        <v>388</v>
-      </c>
-      <c r="G306" s="31"/>
+        <v>374</v>
+      </c>
+      <c r="G306" s="30"/>
       <c r="H306" s="3"/>
       <c r="I306" s="3"/>
       <c r="J306" s="4"/>
@@ -8723,15 +8727,15 @@
       <c r="B307" s="4"/>
       <c r="C307" s="4"/>
       <c r="D307" s="11">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E307" s="10" t="s">
         <v>52</v>
       </c>
       <c r="F307" s="13" t="s">
-        <v>389</v>
-      </c>
-      <c r="G307" s="31"/>
+        <v>388</v>
+      </c>
+      <c r="G307" s="30"/>
       <c r="H307" s="3"/>
       <c r="I307" s="3"/>
       <c r="J307" s="4"/>
@@ -8747,15 +8751,15 @@
       <c r="B308" s="4"/>
       <c r="C308" s="4"/>
       <c r="D308" s="11">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E308" s="10" t="s">
         <v>52</v>
       </c>
       <c r="F308" s="13" t="s">
-        <v>390</v>
-      </c>
-      <c r="G308" s="31"/>
+        <v>389</v>
+      </c>
+      <c r="G308" s="30"/>
       <c r="H308" s="3"/>
       <c r="I308" s="3"/>
       <c r="J308" s="4"/>
@@ -8771,15 +8775,15 @@
       <c r="B309" s="4"/>
       <c r="C309" s="4"/>
       <c r="D309" s="11">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E309" s="10" t="s">
         <v>52</v>
       </c>
       <c r="F309" s="13" t="s">
-        <v>391</v>
-      </c>
-      <c r="G309" s="31"/>
+        <v>390</v>
+      </c>
+      <c r="G309" s="30"/>
       <c r="H309" s="3"/>
       <c r="I309" s="3"/>
       <c r="J309" s="4"/>
@@ -8795,15 +8799,15 @@
       <c r="B310" s="4"/>
       <c r="C310" s="4"/>
       <c r="D310" s="11">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E310" s="10" t="s">
         <v>52</v>
       </c>
       <c r="F310" s="13" t="s">
-        <v>392</v>
-      </c>
-      <c r="G310" s="31"/>
+        <v>391</v>
+      </c>
+      <c r="G310" s="30"/>
       <c r="H310" s="3"/>
       <c r="I310" s="3"/>
       <c r="J310" s="4"/>
@@ -8819,15 +8823,15 @@
       <c r="B311" s="4"/>
       <c r="C311" s="4"/>
       <c r="D311" s="11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E311" s="10" t="s">
         <v>52</v>
       </c>
       <c r="F311" s="13" t="s">
-        <v>393</v>
-      </c>
-      <c r="G311" s="31"/>
+        <v>392</v>
+      </c>
+      <c r="G311" s="30"/>
       <c r="H311" s="3"/>
       <c r="I311" s="3"/>
       <c r="J311" s="4"/>
@@ -8843,15 +8847,15 @@
       <c r="B312" s="4"/>
       <c r="C312" s="4"/>
       <c r="D312" s="11">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E312" s="10" t="s">
         <v>52</v>
       </c>
       <c r="F312" s="13" t="s">
-        <v>394</v>
-      </c>
-      <c r="G312" s="31"/>
+        <v>393</v>
+      </c>
+      <c r="G312" s="30"/>
       <c r="H312" s="3"/>
       <c r="I312" s="3"/>
       <c r="J312" s="4"/>
@@ -8867,15 +8871,15 @@
       <c r="B313" s="4"/>
       <c r="C313" s="4"/>
       <c r="D313" s="11">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E313" s="10" t="s">
         <v>52</v>
       </c>
       <c r="F313" s="13" t="s">
-        <v>395</v>
-      </c>
-      <c r="G313" s="31"/>
+        <v>394</v>
+      </c>
+      <c r="G313" s="30"/>
       <c r="H313" s="3"/>
       <c r="I313" s="3"/>
       <c r="J313" s="4"/>
@@ -8891,15 +8895,15 @@
       <c r="B314" s="4"/>
       <c r="C314" s="4"/>
       <c r="D314" s="11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E314" s="10" t="s">
         <v>52</v>
       </c>
       <c r="F314" s="13" t="s">
-        <v>396</v>
-      </c>
-      <c r="G314" s="31"/>
+        <v>395</v>
+      </c>
+      <c r="G314" s="30"/>
       <c r="H314" s="3"/>
       <c r="I314" s="3"/>
       <c r="J314" s="4"/>
@@ -8915,15 +8919,15 @@
       <c r="B315" s="4"/>
       <c r="C315" s="4"/>
       <c r="D315" s="11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E315" s="10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F315" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="G315" s="32"/>
+        <v>396</v>
+      </c>
+      <c r="G315" s="30"/>
       <c r="H315" s="3"/>
       <c r="I315" s="3"/>
       <c r="J315" s="4"/>
@@ -8934,66 +8938,66 @@
       <c r="O315" s="4"/>
       <c r="P315" s="3"/>
     </row>
-    <row r="316" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B316" s="27" t="s">
+    <row r="316" spans="1:16" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.25">
+      <c r="A316" s="4"/>
+      <c r="B316" s="4"/>
+      <c r="C316" s="4"/>
+      <c r="D316" s="11">
+        <v>26</v>
+      </c>
+      <c r="E316" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F316" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="G316" s="31"/>
+      <c r="H316" s="3"/>
+      <c r="I316" s="3"/>
+      <c r="J316" s="4"/>
+      <c r="K316" s="4"/>
+      <c r="L316" s="4"/>
+      <c r="M316" s="4"/>
+      <c r="N316" s="4"/>
+      <c r="O316" s="4"/>
+      <c r="P316" s="3"/>
+    </row>
+    <row r="317" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B317" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="C316" s="27" t="s">
+      <c r="C317" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="D316" s="27"/>
-      <c r="E316" s="27"/>
-      <c r="F316" s="27"/>
-      <c r="G316" s="27"/>
-      <c r="H316" s="27"/>
-      <c r="I316" s="27"/>
-      <c r="J316" s="27"/>
-      <c r="K316" s="27"/>
-      <c r="L316" s="27"/>
-      <c r="M316" s="27"/>
-      <c r="N316" s="27"/>
-      <c r="O316" s="27"/>
-      <c r="P316" s="27"/>
-    </row>
-    <row r="317" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B317" s="4" t="s">
+      <c r="D317" s="26"/>
+      <c r="E317" s="26"/>
+      <c r="F317" s="26"/>
+      <c r="G317" s="26"/>
+      <c r="H317" s="26"/>
+      <c r="I317" s="26"/>
+      <c r="J317" s="26"/>
+      <c r="K317" s="26"/>
+      <c r="L317" s="26"/>
+      <c r="M317" s="26"/>
+      <c r="N317" s="26"/>
+      <c r="O317" s="26"/>
+      <c r="P317" s="26"/>
+    </row>
+    <row r="318" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B318" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C317" s="4" t="s">
+      <c r="C318" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D317" s="5"/>
-      <c r="E317" s="3"/>
-      <c r="F317" s="3" t="s">
+      <c r="D318" s="5"/>
+      <c r="E318" s="3"/>
+      <c r="F318" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="G317" s="3"/>
-      <c r="H317" s="3"/>
-      <c r="I317" s="3"/>
-      <c r="P317" s="3"/>
-    </row>
-    <row r="318" spans="1:16" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.25">
-      <c r="A318" s="4"/>
-      <c r="B318" s="4"/>
-      <c r="C318" s="4"/>
-      <c r="D318" s="5">
-        <v>1</v>
-      </c>
-      <c r="E318" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F318" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="G318" s="3"/>
       <c r="H318" s="3"/>
       <c r="I318" s="3"/>
-      <c r="J318" s="4"/>
-      <c r="K318" s="4"/>
-      <c r="L318" s="4"/>
-      <c r="M318" s="4"/>
-      <c r="N318" s="4"/>
-      <c r="O318" s="4"/>
       <c r="P318" s="3"/>
     </row>
     <row r="319" spans="1:16" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.25">
@@ -9001,15 +9005,15 @@
       <c r="B319" s="4"/>
       <c r="C319" s="4"/>
       <c r="D319" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E319" s="6" t="s">
         <v>48</v>
       </c>
       <c r="F319" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="G319" s="8"/>
+        <v>158</v>
+      </c>
+      <c r="G319" s="3"/>
       <c r="H319" s="3"/>
       <c r="I319" s="3"/>
       <c r="J319" s="4"/>
@@ -9025,15 +9029,15 @@
       <c r="B320" s="4"/>
       <c r="C320" s="4"/>
       <c r="D320" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E320" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F320" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="G320" s="3"/>
+        <v>212</v>
+      </c>
+      <c r="G320" s="8"/>
       <c r="H320" s="3"/>
       <c r="I320" s="3"/>
       <c r="J320" s="4"/>
@@ -9049,13 +9053,13 @@
       <c r="B321" s="4"/>
       <c r="C321" s="4"/>
       <c r="D321" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E321" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F321" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G321" s="3"/>
       <c r="H321" s="3"/>
@@ -9073,15 +9077,15 @@
       <c r="B322" s="4"/>
       <c r="C322" s="4"/>
       <c r="D322" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E322" s="6" t="s">
         <v>48</v>
       </c>
       <c r="F322" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="G322" s="8"/>
+        <v>160</v>
+      </c>
+      <c r="G322" s="3"/>
       <c r="H322" s="3"/>
       <c r="I322" s="3"/>
       <c r="J322" s="4"/>
@@ -9097,15 +9101,15 @@
       <c r="B323" s="4"/>
       <c r="C323" s="4"/>
       <c r="D323" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E323" s="6" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F323" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="G323" s="3"/>
+        <v>161</v>
+      </c>
+      <c r="G323" s="8"/>
       <c r="H323" s="3"/>
       <c r="I323" s="3"/>
       <c r="J323" s="4"/>
@@ -9121,15 +9125,15 @@
       <c r="B324" s="4"/>
       <c r="C324" s="4"/>
       <c r="D324" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E324" s="6" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F324" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="G324" s="8"/>
+        <v>162</v>
+      </c>
+      <c r="G324" s="3"/>
       <c r="H324" s="3"/>
       <c r="I324" s="3"/>
       <c r="J324" s="4"/>
@@ -9145,13 +9149,13 @@
       <c r="B325" s="4"/>
       <c r="C325" s="4"/>
       <c r="D325" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E325" s="6" t="s">
         <v>48</v>
       </c>
       <c r="F325" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G325" s="8"/>
       <c r="H325" s="3"/>
@@ -9169,13 +9173,13 @@
       <c r="B326" s="4"/>
       <c r="C326" s="4"/>
       <c r="D326" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E326" s="6" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F326" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G326" s="8"/>
       <c r="H326" s="3"/>
@@ -9193,13 +9197,13 @@
       <c r="B327" s="4"/>
       <c r="C327" s="4"/>
       <c r="D327" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E327" s="6" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F327" s="6" t="s">
-        <v>397</v>
+        <v>215</v>
       </c>
       <c r="G327" s="8"/>
       <c r="H327" s="3"/>
@@ -9217,15 +9221,15 @@
       <c r="B328" s="4"/>
       <c r="C328" s="4"/>
       <c r="D328" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E328" s="6" t="s">
         <v>48</v>
       </c>
       <c r="F328" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="G328" s="3"/>
+        <v>397</v>
+      </c>
+      <c r="G328" s="8"/>
       <c r="H328" s="3"/>
       <c r="I328" s="3"/>
       <c r="J328" s="4"/>
@@ -9241,13 +9245,13 @@
       <c r="B329" s="4"/>
       <c r="C329" s="4"/>
       <c r="D329" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E329" s="6" t="s">
         <v>48</v>
       </c>
       <c r="F329" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G329" s="3"/>
       <c r="H329" s="3"/>
@@ -9265,13 +9269,13 @@
       <c r="B330" s="4"/>
       <c r="C330" s="4"/>
       <c r="D330" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E330" s="6" t="s">
         <v>48</v>
       </c>
       <c r="F330" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G330" s="3"/>
       <c r="H330" s="3"/>
@@ -9289,15 +9293,15 @@
       <c r="B331" s="4"/>
       <c r="C331" s="4"/>
       <c r="D331" s="5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E331" s="6" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="F331" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="G331" s="8"/>
+        <v>165</v>
+      </c>
+      <c r="G331" s="3"/>
       <c r="H331" s="3"/>
       <c r="I331" s="3"/>
       <c r="J331" s="4"/>
@@ -9313,15 +9317,15 @@
       <c r="B332" s="4"/>
       <c r="C332" s="4"/>
       <c r="D332" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E332" s="6" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="F332" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="G332" s="3"/>
+        <v>216</v>
+      </c>
+      <c r="G332" s="8"/>
       <c r="H332" s="3"/>
       <c r="I332" s="3"/>
       <c r="J332" s="4"/>
@@ -9337,13 +9341,13 @@
       <c r="B333" s="4"/>
       <c r="C333" s="4"/>
       <c r="D333" s="5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E333" s="6" t="s">
         <v>50</v>
       </c>
       <c r="F333" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G333" s="3"/>
       <c r="H333" s="3"/>
@@ -9361,13 +9365,13 @@
       <c r="B334" s="4"/>
       <c r="C334" s="4"/>
       <c r="D334" s="5">
-        <v>17</v>
-      </c>
-      <c r="E334" s="11" t="s">
-        <v>291</v>
-      </c>
-      <c r="F334" s="11" t="s">
-        <v>400</v>
+        <v>16</v>
+      </c>
+      <c r="E334" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F334" s="6" t="s">
+        <v>167</v>
       </c>
       <c r="G334" s="3"/>
       <c r="H334" s="3"/>
@@ -9385,13 +9389,13 @@
       <c r="B335" s="4"/>
       <c r="C335" s="4"/>
       <c r="D335" s="5">
-        <v>18</v>
-      </c>
-      <c r="E335" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F335" s="6" t="s">
-        <v>168</v>
+        <v>17</v>
+      </c>
+      <c r="E335" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="F335" s="11" t="s">
+        <v>400</v>
       </c>
       <c r="G335" s="3"/>
       <c r="H335" s="3"/>
@@ -9409,13 +9413,13 @@
       <c r="B336" s="4"/>
       <c r="C336" s="4"/>
       <c r="D336" s="5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E336" s="6" t="s">
         <v>48</v>
       </c>
       <c r="F336" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G336" s="3"/>
       <c r="H336" s="3"/>
@@ -9433,13 +9437,13 @@
       <c r="B337" s="4"/>
       <c r="C337" s="4"/>
       <c r="D337" s="5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E337" s="6" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F337" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G337" s="3"/>
       <c r="H337" s="3"/>
@@ -9457,13 +9461,13 @@
       <c r="B338" s="4"/>
       <c r="C338" s="4"/>
       <c r="D338" s="5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E338" s="6" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="F338" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G338" s="3"/>
       <c r="H338" s="3"/>
@@ -9481,13 +9485,13 @@
       <c r="B339" s="4"/>
       <c r="C339" s="4"/>
       <c r="D339" s="5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E339" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F339" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G339" s="3"/>
       <c r="H339" s="3"/>
@@ -9505,13 +9509,13 @@
       <c r="B340" s="4"/>
       <c r="C340" s="4"/>
       <c r="D340" s="5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E340" s="6" t="s">
         <v>50</v>
       </c>
       <c r="F340" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G340" s="3"/>
       <c r="H340" s="3"/>
@@ -9529,13 +9533,13 @@
       <c r="B341" s="4"/>
       <c r="C341" s="4"/>
       <c r="D341" s="5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E341" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F341" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G341" s="3"/>
       <c r="H341" s="3"/>
@@ -9553,13 +9557,13 @@
       <c r="B342" s="4"/>
       <c r="C342" s="4"/>
       <c r="D342" s="5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E342" s="6" t="s">
         <v>48</v>
       </c>
       <c r="F342" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G342" s="3"/>
       <c r="H342" s="3"/>
@@ -9577,13 +9581,13 @@
       <c r="B343" s="4"/>
       <c r="C343" s="4"/>
       <c r="D343" s="5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E343" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F343" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G343" s="3"/>
       <c r="H343" s="3"/>
@@ -9601,13 +9605,13 @@
       <c r="B344" s="4"/>
       <c r="C344" s="4"/>
       <c r="D344" s="5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E344" s="6" t="s">
         <v>50</v>
       </c>
       <c r="F344" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G344" s="3"/>
       <c r="H344" s="3"/>
@@ -9625,13 +9629,13 @@
       <c r="B345" s="4"/>
       <c r="C345" s="4"/>
       <c r="D345" s="5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E345" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F345" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G345" s="3"/>
       <c r="H345" s="3"/>
@@ -9649,13 +9653,13 @@
       <c r="B346" s="4"/>
       <c r="C346" s="4"/>
       <c r="D346" s="5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E346" s="6" t="s">
         <v>48</v>
       </c>
       <c r="F346" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G346" s="3"/>
       <c r="H346" s="3"/>
@@ -9673,13 +9677,13 @@
       <c r="B347" s="4"/>
       <c r="C347" s="4"/>
       <c r="D347" s="5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E347" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F347" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G347" s="3"/>
       <c r="H347" s="3"/>
@@ -9697,13 +9701,13 @@
       <c r="B348" s="4"/>
       <c r="C348" s="4"/>
       <c r="D348" s="5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E348" s="6" t="s">
         <v>50</v>
       </c>
       <c r="F348" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G348" s="3"/>
       <c r="H348" s="3"/>
@@ -9721,13 +9725,13 @@
       <c r="B349" s="4"/>
       <c r="C349" s="4"/>
       <c r="D349" s="5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E349" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F349" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G349" s="3"/>
       <c r="H349" s="3"/>
@@ -9745,13 +9749,13 @@
       <c r="B350" s="4"/>
       <c r="C350" s="4"/>
       <c r="D350" s="5">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E350" s="6" t="s">
         <v>48</v>
       </c>
       <c r="F350" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G350" s="3"/>
       <c r="H350" s="3"/>
@@ -9769,13 +9773,13 @@
       <c r="B351" s="4"/>
       <c r="C351" s="4"/>
       <c r="D351" s="5">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E351" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F351" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G351" s="3"/>
       <c r="H351" s="3"/>
@@ -9793,13 +9797,13 @@
       <c r="B352" s="4"/>
       <c r="C352" s="4"/>
       <c r="D352" s="5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E352" s="6" t="s">
         <v>50</v>
       </c>
       <c r="F352" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G352" s="3"/>
       <c r="H352" s="3"/>
@@ -9817,13 +9821,13 @@
       <c r="B353" s="4"/>
       <c r="C353" s="4"/>
       <c r="D353" s="5">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E353" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F353" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G353" s="3"/>
       <c r="H353" s="3"/>
@@ -9841,13 +9845,13 @@
       <c r="B354" s="4"/>
       <c r="C354" s="4"/>
       <c r="D354" s="5">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E354" s="6" t="s">
         <v>48</v>
       </c>
       <c r="F354" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G354" s="3"/>
       <c r="H354" s="3"/>
@@ -9865,15 +9869,15 @@
       <c r="B355" s="4"/>
       <c r="C355" s="4"/>
       <c r="D355" s="5">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E355" s="6" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="F355" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="G355" s="8"/>
+        <v>187</v>
+      </c>
+      <c r="G355" s="3"/>
       <c r="H355" s="3"/>
       <c r="I355" s="3"/>
       <c r="J355" s="4"/>
@@ -9889,15 +9893,15 @@
       <c r="B356" s="4"/>
       <c r="C356" s="4"/>
       <c r="D356" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E356" s="6" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="F356" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="G356" s="3"/>
+        <v>217</v>
+      </c>
+      <c r="G356" s="8"/>
       <c r="H356" s="3"/>
       <c r="I356" s="3"/>
       <c r="J356" s="4"/>
@@ -9913,13 +9917,13 @@
       <c r="B357" s="4"/>
       <c r="C357" s="4"/>
       <c r="D357" s="5">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E357" s="6" t="s">
         <v>50</v>
       </c>
       <c r="F357" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G357" s="3"/>
       <c r="H357" s="3"/>
@@ -9937,13 +9941,13 @@
       <c r="B358" s="4"/>
       <c r="C358" s="4"/>
       <c r="D358" s="5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E358" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F358" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G358" s="3"/>
       <c r="H358" s="3"/>
@@ -9961,15 +9965,15 @@
       <c r="B359" s="4"/>
       <c r="C359" s="4"/>
       <c r="D359" s="5">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E359" s="6" t="s">
         <v>48</v>
       </c>
       <c r="F359" s="6" t="s">
-        <v>398</v>
-      </c>
-      <c r="G359" s="8"/>
+        <v>190</v>
+      </c>
+      <c r="G359" s="3"/>
       <c r="H359" s="3"/>
       <c r="I359" s="3"/>
       <c r="J359" s="4"/>
@@ -9985,13 +9989,13 @@
       <c r="B360" s="4"/>
       <c r="C360" s="4"/>
       <c r="D360" s="5">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E360" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F360" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G360" s="8"/>
       <c r="H360" s="3"/>
@@ -10009,13 +10013,13 @@
       <c r="B361" s="4"/>
       <c r="C361" s="4"/>
       <c r="D361" s="5">
-        <v>44</v>
-      </c>
-      <c r="E361" s="11" t="s">
-        <v>291</v>
-      </c>
-      <c r="F361" s="11" t="s">
-        <v>401</v>
+        <v>43</v>
+      </c>
+      <c r="E361" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F361" s="6" t="s">
+        <v>399</v>
       </c>
       <c r="G361" s="8"/>
       <c r="H361" s="3"/>
@@ -10033,15 +10037,15 @@
       <c r="B362" s="4"/>
       <c r="C362" s="4"/>
       <c r="D362" s="5">
-        <v>45</v>
-      </c>
-      <c r="E362" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F362" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="G362" s="3"/>
+        <v>44</v>
+      </c>
+      <c r="E362" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="F362" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="G362" s="8"/>
       <c r="H362" s="3"/>
       <c r="I362" s="3"/>
       <c r="J362" s="4"/>
@@ -10057,13 +10061,13 @@
       <c r="B363" s="4"/>
       <c r="C363" s="4"/>
       <c r="D363" s="5">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E363" s="6" t="s">
         <v>48</v>
       </c>
       <c r="F363" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G363" s="3"/>
       <c r="H363" s="3"/>
@@ -10081,16 +10085,16 @@
       <c r="B364" s="4"/>
       <c r="C364" s="4"/>
       <c r="D364" s="5">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E364" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F364" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G364" s="3"/>
-      <c r="H364" s="24"/>
+      <c r="H364" s="3"/>
       <c r="I364" s="3"/>
       <c r="J364" s="4"/>
       <c r="K364" s="4"/>
@@ -10105,16 +10109,16 @@
       <c r="B365" s="4"/>
       <c r="C365" s="4"/>
       <c r="D365" s="5">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E365" s="6" t="s">
         <v>50</v>
       </c>
       <c r="F365" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G365" s="3"/>
-      <c r="H365" s="23"/>
+      <c r="H365" s="24"/>
       <c r="I365" s="3"/>
       <c r="J365" s="4"/>
       <c r="K365" s="4"/>
@@ -10129,13 +10133,13 @@
       <c r="B366" s="4"/>
       <c r="C366" s="4"/>
       <c r="D366" s="5">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E366" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F366" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G366" s="3"/>
       <c r="H366" s="23"/>
@@ -10153,13 +10157,13 @@
       <c r="B367" s="4"/>
       <c r="C367" s="4"/>
       <c r="D367" s="5">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E367" s="6" t="s">
         <v>48</v>
       </c>
       <c r="F367" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G367" s="3"/>
       <c r="H367" s="23"/>
@@ -10177,13 +10181,13 @@
       <c r="B368" s="4"/>
       <c r="C368" s="4"/>
       <c r="D368" s="5">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E368" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F368" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G368" s="3"/>
       <c r="H368" s="23"/>
@@ -10201,13 +10205,13 @@
       <c r="B369" s="4"/>
       <c r="C369" s="4"/>
       <c r="D369" s="5">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E369" s="6" t="s">
         <v>50</v>
       </c>
       <c r="F369" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G369" s="3"/>
       <c r="H369" s="23"/>
@@ -10225,15 +10229,15 @@
       <c r="B370" s="4"/>
       <c r="C370" s="4"/>
       <c r="D370" s="5">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E370" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F370" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="G370" s="8"/>
+        <v>50</v>
+      </c>
+      <c r="F370" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="G370" s="3"/>
       <c r="H370" s="23"/>
       <c r="I370" s="3"/>
       <c r="J370" s="4"/>
@@ -10249,13 +10253,13 @@
       <c r="B371" s="4"/>
       <c r="C371" s="4"/>
       <c r="D371" s="5">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E371" s="6" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="F371" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G371" s="8"/>
       <c r="H371" s="23"/>
@@ -10273,13 +10277,13 @@
       <c r="B372" s="4"/>
       <c r="C372" s="4"/>
       <c r="D372" s="5">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E372" s="6" t="s">
         <v>48</v>
       </c>
       <c r="F372" s="12" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G372" s="8"/>
       <c r="H372" s="23"/>
@@ -10297,13 +10301,13 @@
       <c r="B373" s="4"/>
       <c r="C373" s="4"/>
       <c r="D373" s="5">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E373" s="6" t="s">
         <v>48</v>
       </c>
       <c r="F373" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G373" s="8"/>
       <c r="H373" s="23"/>
@@ -10321,13 +10325,13 @@
       <c r="B374" s="4"/>
       <c r="C374" s="4"/>
       <c r="D374" s="5">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E374" s="6" t="s">
         <v>48</v>
       </c>
       <c r="F374" s="12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G374" s="8"/>
       <c r="H374" s="23"/>
@@ -10345,13 +10349,13 @@
       <c r="B375" s="4"/>
       <c r="C375" s="4"/>
       <c r="D375" s="5">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E375" s="6" t="s">
         <v>48</v>
       </c>
       <c r="F375" s="12" t="s">
-        <v>237</v>
+        <v>203</v>
       </c>
       <c r="G375" s="8"/>
       <c r="H375" s="23"/>
@@ -10369,13 +10373,13 @@
       <c r="B376" s="4"/>
       <c r="C376" s="4"/>
       <c r="D376" s="5">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E376" s="6" t="s">
         <v>48</v>
       </c>
       <c r="F376" s="12" t="s">
-        <v>204</v>
+        <v>237</v>
       </c>
       <c r="G376" s="8"/>
       <c r="H376" s="23"/>
@@ -10393,13 +10397,13 @@
       <c r="B377" s="4"/>
       <c r="C377" s="4"/>
       <c r="D377" s="5">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E377" s="6" t="s">
         <v>48</v>
       </c>
       <c r="F377" s="12" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="G377" s="8"/>
       <c r="H377" s="23"/>
@@ -10412,35 +10416,50 @@
       <c r="O377" s="4"/>
       <c r="P377" s="3"/>
     </row>
-    <row r="378" spans="1:16" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.25">
-      <c r="B378" s="27" t="s">
+    <row r="378" spans="1:16" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.25">
+      <c r="A378" s="4"/>
+      <c r="B378" s="4"/>
+      <c r="C378" s="4"/>
+      <c r="D378" s="5">
+        <v>60</v>
+      </c>
+      <c r="E378" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F378" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="G378" s="8"/>
+      <c r="H378" s="23"/>
+      <c r="I378" s="3"/>
+      <c r="J378" s="4"/>
+      <c r="K378" s="4"/>
+      <c r="L378" s="4"/>
+      <c r="M378" s="4"/>
+      <c r="N378" s="4"/>
+      <c r="O378" s="4"/>
+      <c r="P378" s="3"/>
+    </row>
+    <row r="379" spans="1:16" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.25">
+      <c r="B379" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="C378" s="27" t="s">
+      <c r="C379" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="D378" s="27"/>
-      <c r="E378" s="27"/>
-      <c r="F378" s="33"/>
-      <c r="G378" s="27"/>
-      <c r="H378" s="23"/>
-      <c r="I378" s="27"/>
-      <c r="J378" s="27"/>
-      <c r="K378" s="27"/>
-      <c r="L378" s="27"/>
-      <c r="M378" s="27"/>
-      <c r="N378" s="27"/>
-      <c r="O378" s="27"/>
-      <c r="P378" s="27"/>
-    </row>
-    <row r="379" spans="1:16" ht="14" x14ac:dyDescent="0.25">
-      <c r="D379" s="5"/>
-      <c r="E379" s="3"/>
-      <c r="F379" s="3"/>
-      <c r="G379" s="3"/>
+      <c r="D379" s="26"/>
+      <c r="E379" s="26"/>
+      <c r="F379" s="32"/>
+      <c r="G379" s="26"/>
       <c r="H379" s="23"/>
-      <c r="I379" s="3"/>
-      <c r="P379" s="3"/>
+      <c r="I379" s="26"/>
+      <c r="J379" s="26"/>
+      <c r="K379" s="26"/>
+      <c r="L379" s="26"/>
+      <c r="M379" s="26"/>
+      <c r="N379" s="26"/>
+      <c r="O379" s="26"/>
+      <c r="P379" s="26"/>
     </row>
     <row r="380" spans="1:16" ht="14" x14ac:dyDescent="0.25">
       <c r="D380" s="5"/>
@@ -10451,75 +10470,75 @@
       <c r="I380" s="3"/>
       <c r="P380" s="3"/>
     </row>
-    <row r="381" spans="1:16" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.25">
-      <c r="B381" s="27" t="s">
+    <row r="381" spans="1:16" ht="14" x14ac:dyDescent="0.25">
+      <c r="D381" s="5"/>
+      <c r="E381" s="3"/>
+      <c r="F381" s="3"/>
+      <c r="G381" s="3"/>
+      <c r="H381" s="23"/>
+      <c r="I381" s="3"/>
+      <c r="P381" s="3"/>
+    </row>
+    <row r="382" spans="1:16" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.25">
+      <c r="B382" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="C381" s="27" t="s">
+      <c r="C382" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="D381" s="27"/>
-      <c r="E381" s="27"/>
-      <c r="G381" s="27"/>
-      <c r="H381" s="23"/>
-      <c r="I381" s="27"/>
-      <c r="J381" s="27"/>
-      <c r="K381" s="27"/>
-      <c r="L381" s="27"/>
-      <c r="M381" s="27"/>
-      <c r="N381" s="27"/>
-      <c r="O381" s="27"/>
-      <c r="P381" s="27"/>
-    </row>
-    <row r="382" spans="1:16" ht="14" x14ac:dyDescent="0.25">
-      <c r="D382" s="5"/>
-      <c r="E382" s="3"/>
-      <c r="F382" s="3"/>
-      <c r="G382" s="3"/>
+      <c r="D382" s="26"/>
+      <c r="E382" s="26"/>
+      <c r="G382" s="26"/>
       <c r="H382" s="23"/>
-      <c r="I382" s="3"/>
-      <c r="P382" s="3"/>
+      <c r="I382" s="26"/>
+      <c r="J382" s="26"/>
+      <c r="K382" s="26"/>
+      <c r="L382" s="26"/>
+      <c r="M382" s="26"/>
+      <c r="N382" s="26"/>
+      <c r="O382" s="26"/>
+      <c r="P382" s="26"/>
     </row>
     <row r="383" spans="1:16" ht="14" x14ac:dyDescent="0.25">
       <c r="D383" s="5"/>
       <c r="E383" s="3"/>
       <c r="F383" s="3"/>
       <c r="G383" s="3"/>
-      <c r="H383" s="24"/>
+      <c r="H383" s="23"/>
       <c r="I383" s="3"/>
       <c r="P383" s="3"/>
     </row>
-    <row r="384" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B384" s="27" t="s">
+    <row r="384" spans="1:16" ht="14" x14ac:dyDescent="0.25">
+      <c r="D384" s="5"/>
+      <c r="E384" s="3"/>
+      <c r="F384" s="3"/>
+      <c r="G384" s="3"/>
+      <c r="H384" s="24"/>
+      <c r="I384" s="3"/>
+      <c r="P384" s="3"/>
+    </row>
+    <row r="385" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B385" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="C384" s="27" t="s">
+      <c r="C385" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="D384" s="27"/>
-      <c r="E384" s="27"/>
-      <c r="F384" s="27"/>
-      <c r="G384" s="27"/>
-      <c r="H384" s="27"/>
-      <c r="I384" s="27"/>
-      <c r="J384" s="27"/>
-      <c r="K384" s="27"/>
-      <c r="L384" s="27"/>
-      <c r="M384" s="27"/>
-      <c r="N384" s="27"/>
-      <c r="O384" s="27"/>
-      <c r="P384" s="27"/>
-    </row>
-    <row r="385" spans="4:16" x14ac:dyDescent="0.25">
-      <c r="D385" s="5"/>
-      <c r="E385" s="3"/>
-      <c r="F385" s="3"/>
-      <c r="G385" s="3"/>
-      <c r="H385" s="3"/>
-      <c r="I385" s="3"/>
-      <c r="P385" s="3"/>
-    </row>
-    <row r="386" spans="4:16" x14ac:dyDescent="0.25">
+      <c r="D385" s="26"/>
+      <c r="E385" s="26"/>
+      <c r="F385" s="26"/>
+      <c r="G385" s="26"/>
+      <c r="H385" s="26"/>
+      <c r="I385" s="26"/>
+      <c r="J385" s="26"/>
+      <c r="K385" s="26"/>
+      <c r="L385" s="26"/>
+      <c r="M385" s="26"/>
+      <c r="N385" s="26"/>
+      <c r="O385" s="26"/>
+      <c r="P385" s="26"/>
+    </row>
+    <row r="386" spans="2:16" x14ac:dyDescent="0.25">
       <c r="D386" s="5"/>
       <c r="E386" s="3"/>
       <c r="F386" s="3"/>
@@ -10528,23 +10547,32 @@
       <c r="I386" s="3"/>
       <c r="P386" s="3"/>
     </row>
-    <row r="387" spans="4:16" x14ac:dyDescent="0.25">
-      <c r="F387" s="27"/>
-    </row>
-    <row r="388" spans="4:16" x14ac:dyDescent="0.25">
-      <c r="F388" s="3"/>
-    </row>
-    <row r="389" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="387" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D387" s="5"/>
+      <c r="E387" s="3"/>
+      <c r="F387" s="3"/>
+      <c r="G387" s="3"/>
+      <c r="H387" s="3"/>
+      <c r="I387" s="3"/>
+      <c r="P387" s="3"/>
+    </row>
+    <row r="388" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="F388" s="26"/>
+    </row>
+    <row r="389" spans="2:16" x14ac:dyDescent="0.25">
       <c r="F389" s="3"/>
     </row>
-    <row r="390" spans="4:16" x14ac:dyDescent="0.25">
-      <c r="F390" s="27"/>
-    </row>
-    <row r="391" spans="4:16" x14ac:dyDescent="0.25">
-      <c r="F391" s="3"/>
-    </row>
-    <row r="392" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="390" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="F390" s="3"/>
+    </row>
+    <row r="391" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="F391" s="26"/>
+    </row>
+    <row r="392" spans="2:16" x14ac:dyDescent="0.25">
       <c r="F392" s="3"/>
+    </row>
+    <row r="393" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="F393" s="3"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatRows="0" insertRows="0" insertHyperlinks="0" deleteRows="0" sort="0" autoFilter="0"/>
@@ -10554,20 +10582,20 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="9">
-    <dataValidation allowBlank="1" showInputMessage="1" sqref="C11 C14 C17 C20 C23 C26 C29 C32 C35 C316 C378 C381 C384" xr:uid="{272FABD7-8957-424B-B2A3-A7A4DF6C667B}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Object Code value" error="The Object code value shall be:_x000a_VARIABLE_x000a_RECORD_x000a_ARRAY" sqref="C12:C13 C15:C16 C18:C19 C21:C22 C24:C25 C27:C28 C30:C31 C33:C34 C36:C89 C91:C114 C124:C189 C317:C377 C379:C380 C382:C383 C385:C397 C191:C315" xr:uid="{18855550-EE63-4366-B60A-372E09E7EA03}">
+    <dataValidation allowBlank="1" showInputMessage="1" sqref="C11 C14 C17 C20 C23 C26 C29 C32 C35 C317 C379 C382 C385" xr:uid="{272FABD7-8957-424B-B2A3-A7A4DF6C667B}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Object Code value" error="The Object code value shall be:_x000a_VARIABLE_x000a_RECORD_x000a_ARRAY" sqref="C12:C13 C15:C16 C18:C19 C21:C22 C24:C25 C27:C28 C30:C31 C33:C34 C36:C89 C91:C114 C124:C189 C318:C378 C380:C381 C383:C384 C386:C398 C191:C316" xr:uid="{18855550-EE63-4366-B60A-372E09E7EA03}">
       <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Category" error="The value for the entry category shall be _x000a_M : (mandatory)_x000a_O : (optional) _x000a_C : (conditional)" sqref="J36 J12:J13 J15:J16 J18:J19 J21:J22 J24:J25 J27:J28 J30:J31 J33:J34 J76:J89 J91:J114 J124:J189 J317:J377 J379:J380 J382:J383 J385:J397 J191:J315" xr:uid="{47F580D9-654F-4B02-87DD-CDEE29719F97}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Category" error="The value for the entry category shall be _x000a_M : (mandatory)_x000a_O : (optional) _x000a_C : (conditional)" sqref="J36 J12:J13 J15:J16 J18:J19 J21:J22 J24:J25 J27:J28 J30:J31 J33:J34 J76:J89 J91:J114 J124:J189 J318:J378 J380:J381 J383:J384 J386:J398 J191:J316" xr:uid="{47F580D9-654F-4B02-87DD-CDEE29719F97}">
       <formula1>"M,O,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Backup/Setting Flag" error="The entry flag shall be_x000a_B : (Backup)_x000a_S : (Setting)" sqref="K36 K12:K13 K15:K16 K18:K19 K21:K22 K24:K25 K27:K28 K30:K31 K33:K34 K76:K89 K91:K114 K124:K189 K317:K377 K379:K380 K382:K383 K385:K397 K191:K315" xr:uid="{E5728F1C-24BF-4AFE-9375-6636E68DFCBD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Backup/Setting Flag" error="The entry flag shall be_x000a_B : (Backup)_x000a_S : (Setting)" sqref="K36 K12:K13 K15:K16 K18:K19 K21:K22 K24:K25 K27:K28 K30:K31 K33:K34 K76:K89 K91:K114 K124:K189 K318:K378 K380:K381 K383:K384 K386:K398 K191:K316" xr:uid="{E5728F1C-24BF-4AFE-9375-6636E68DFCBD}">
       <formula1>"B,S"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M36:O36 M12:O13 M18:O19 M24:O25 M30:O31 M379:O380 M385:O386 M15:O16 M21:O22 M27:O28 M33:O34 M382:O383 M76:O89 M124:O189 M317:O377 M91:O114 M191:O315" xr:uid="{4EBF5EA7-2742-4AF6-BACD-230FC3C4437C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M36:O36 M12:O13 M18:O19 M24:O25 M30:O31 M380:O381 M386:O387 M15:O16 M21:O22 M27:O28 M33:O34 M383:O384 M76:O89 M124:O189 M318:O378 M91:O114 M191:O316" xr:uid="{4EBF5EA7-2742-4AF6-BACD-230FC3C4437C}">
       <formula1>"rx,tx"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C398:C1237" xr:uid="{310E4F23-290B-4CFE-8269-7B6D85056FE7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C399:C1238" xr:uid="{310E4F23-290B-4CFE-8269-7B6D85056FE7}">
       <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J37:J75" xr:uid="{57863C58-C079-4676-BDE8-28BF71C1A604}">

--- a/ArmCoreV1_QSPI/SSCProject/lan9252_app.xlsx
+++ b/ArmCoreV1_QSPI/SSCProject/lan9252_app.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SI\project\RTM_ON_NEW\FW-ArmCore\ArmCoreV1_QSPI\SSCProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9469E864-6D82-47E8-8BC2-912A62346D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43F905A8-AB51-4DB8-A5A1-6DF0C4A10B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -913,10 +913,6 @@
   </si>
   <si>
     <t>InB1_OFF_DO_AsuMotionEnable</t>
-  </si>
-  <si>
-    <t>UNSIGNED32</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1409,15 +1405,19 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>OutU32_rtm_on_treatment_mode</t>
+    <t>InU32_rtm_off_search_timeout_cur</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>OutU32_rtm_off_treatment_mode</t>
+    <t>UNSIGNED16</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>InU32_rtm_off_search_timeout_cur</t>
+    <t>OutU16_rtm_on_treatment_mode</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OutU16_rtm_off_treatment_mode</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="33" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G1" s="33"/>
       <c r="H1" s="33"/>
@@ -2392,7 +2392,7 @@
         <v>26</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D20" s="26"/>
       <c r="E20" s="26"/>
@@ -2470,7 +2470,7 @@
         <v>29</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D26" s="26"/>
       <c r="E26" s="26"/>
@@ -2509,7 +2509,7 @@
         <v>30</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="26"/>
@@ -2548,7 +2548,7 @@
         <v>31</v>
       </c>
       <c r="C32" s="26" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D32" s="26"/>
       <c r="E32" s="26"/>
@@ -2631,7 +2631,7 @@
         <v>48</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G37" s="7"/>
       <c r="H37" s="7"/>
@@ -2651,7 +2651,7 @@
         <v>48</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G38" s="7"/>
       <c r="H38" s="7"/>
@@ -2669,7 +2669,7 @@
         <v>50</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G39" s="7"/>
       <c r="H39" s="7"/>
@@ -2689,7 +2689,7 @@
         <v>48</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
@@ -2707,7 +2707,7 @@
         <v>48</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G41" s="7"/>
       <c r="H41" s="7"/>
@@ -2725,7 +2725,7 @@
         <v>50</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G42" s="7"/>
       <c r="H42" s="7"/>
@@ -2743,7 +2743,7 @@
         <v>48</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G43" s="7"/>
       <c r="H43" s="7"/>
@@ -2761,7 +2761,7 @@
         <v>48</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G44" s="7"/>
       <c r="H44" s="7"/>
@@ -2779,7 +2779,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G45" s="7"/>
       <c r="H45" s="7"/>
@@ -2797,7 +2797,7 @@
         <v>48</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G46" s="7"/>
       <c r="H46" s="7"/>
@@ -2815,7 +2815,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G47" s="7"/>
       <c r="H47" s="7"/>
@@ -2833,7 +2833,7 @@
         <v>50</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G48" s="7"/>
       <c r="H48" s="7"/>
@@ -2851,7 +2851,7 @@
         <v>48</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G49" s="7"/>
       <c r="H49" s="7"/>
@@ -2869,7 +2869,7 @@
         <v>48</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
@@ -2887,7 +2887,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G51" s="7"/>
       <c r="H51" s="7"/>
@@ -2905,7 +2905,7 @@
         <v>48</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G52" s="7"/>
       <c r="H52" s="7"/>
@@ -2923,7 +2923,7 @@
         <v>48</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G53" s="7"/>
       <c r="H53" s="7"/>
@@ -2941,7 +2941,7 @@
         <v>50</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
@@ -2959,7 +2959,7 @@
         <v>48</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G55" s="7"/>
       <c r="H55" s="7"/>
@@ -2977,7 +2977,7 @@
         <v>48</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
@@ -2995,7 +2995,7 @@
         <v>50</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="7"/>
@@ -3013,7 +3013,7 @@
         <v>48</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G58" s="7"/>
       <c r="H58" s="7"/>
@@ -3031,7 +3031,7 @@
         <v>48</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G59" s="7"/>
       <c r="H59" s="7"/>
@@ -3049,7 +3049,7 @@
         <v>50</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
@@ -3067,7 +3067,7 @@
         <v>48</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G61" s="7"/>
       <c r="H61" s="7"/>
@@ -3085,7 +3085,7 @@
         <v>48</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G62" s="7"/>
       <c r="H62" s="7"/>
@@ -3103,7 +3103,7 @@
         <v>50</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G63" s="7"/>
       <c r="H63" s="7"/>
@@ -3121,7 +3121,7 @@
         <v>48</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G64" s="7"/>
       <c r="H64" s="7"/>
@@ -3139,7 +3139,7 @@
         <v>48</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G65" s="7"/>
       <c r="H65" s="7"/>
@@ -3157,7 +3157,7 @@
         <v>50</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G66" s="7"/>
       <c r="H66" s="7"/>
@@ -3175,7 +3175,7 @@
         <v>48</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G67" s="7"/>
       <c r="H67" s="7"/>
@@ -3193,7 +3193,7 @@
         <v>48</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G68" s="7"/>
       <c r="H68" s="7"/>
@@ -3211,7 +3211,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G69" s="7"/>
       <c r="H69" s="7"/>
@@ -3229,7 +3229,7 @@
         <v>48</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
@@ -3247,7 +3247,7 @@
         <v>48</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="7"/>
@@ -3265,7 +3265,7 @@
         <v>50</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G72" s="7"/>
       <c r="H72" s="7"/>
@@ -3283,7 +3283,7 @@
         <v>48</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G73" s="7"/>
       <c r="H73" s="7"/>
@@ -3301,7 +3301,7 @@
         <v>48</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G74" s="7"/>
       <c r="H74" s="7"/>
@@ -3319,7 +3319,7 @@
         <v>50</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G75" s="7"/>
       <c r="H75" s="7"/>
@@ -3672,7 +3672,7 @@
         <v>70</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="91" spans="1:16" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.25">
@@ -3686,7 +3686,7 @@
         <v>70</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G91" s="8"/>
       <c r="H91" s="3"/>
@@ -3710,7 +3710,7 @@
         <v>70</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G92" s="8"/>
       <c r="H92" s="3"/>
@@ -4259,7 +4259,7 @@
         <v>48</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="116" spans="1:16" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.25">
@@ -4457,7 +4457,7 @@
         <v>67</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G128" s="8"/>
       <c r="H128" s="3"/>
@@ -4697,7 +4697,7 @@
         <v>67</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G138" s="8"/>
       <c r="H138" s="3"/>
@@ -4721,7 +4721,7 @@
         <v>67</v>
       </c>
       <c r="F139" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G139" s="8"/>
       <c r="H139" s="3"/>
@@ -5129,7 +5129,7 @@
         <v>70</v>
       </c>
       <c r="F156" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G156" s="8"/>
       <c r="H156" s="3"/>
@@ -5174,10 +5174,10 @@
         <v>122</v>
       </c>
       <c r="E158" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="F158" s="6" t="s">
         <v>344</v>
-      </c>
-      <c r="F158" s="6" t="s">
-        <v>345</v>
       </c>
       <c r="G158" s="8"/>
       <c r="H158" s="3"/>
@@ -5201,7 +5201,7 @@
         <v>48</v>
       </c>
       <c r="F159" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G159" s="8"/>
       <c r="H159" s="3"/>
@@ -5438,10 +5438,10 @@
         <v>133</v>
       </c>
       <c r="E169" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F169" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G169" s="8"/>
       <c r="H169" s="3"/>
@@ -5465,7 +5465,7 @@
         <v>70</v>
       </c>
       <c r="F170" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G170" s="8"/>
       <c r="H170" s="3"/>
@@ -5657,7 +5657,7 @@
         <v>67</v>
       </c>
       <c r="F178" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G178" s="8"/>
       <c r="H178" s="3"/>
@@ -5681,7 +5681,7 @@
         <v>48</v>
       </c>
       <c r="F179" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G179" s="8"/>
       <c r="H179" s="3"/>
@@ -5942,7 +5942,7 @@
         <v>70</v>
       </c>
       <c r="F190" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="191" spans="1:16" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.25">
@@ -5956,7 +5956,7 @@
         <v>70</v>
       </c>
       <c r="F191" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G191" s="8"/>
       <c r="H191" s="3"/>
@@ -5980,7 +5980,7 @@
         <v>70</v>
       </c>
       <c r="F192" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G192" s="8"/>
       <c r="H192" s="3"/>
@@ -6244,7 +6244,7 @@
         <v>70</v>
       </c>
       <c r="F203" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G203" s="3"/>
       <c r="H203" s="3"/>
@@ -6268,7 +6268,7 @@
         <v>70</v>
       </c>
       <c r="F204" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G204" s="3"/>
       <c r="H204" s="3"/>
@@ -6292,7 +6292,7 @@
         <v>70</v>
       </c>
       <c r="F205" s="6" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G205" s="3"/>
       <c r="H205" s="3"/>
@@ -6868,7 +6868,7 @@
         <v>70</v>
       </c>
       <c r="F229" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G229" s="3"/>
       <c r="H229" s="3"/>
@@ -6892,7 +6892,7 @@
         <v>70</v>
       </c>
       <c r="F230" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G230" s="3"/>
       <c r="H230" s="3"/>
@@ -6916,7 +6916,7 @@
         <v>70</v>
       </c>
       <c r="F231" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G231" s="3"/>
       <c r="H231" s="3"/>
@@ -7180,7 +7180,7 @@
         <v>70</v>
       </c>
       <c r="F242" s="6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G242" s="8"/>
       <c r="H242" s="3"/>
@@ -7204,7 +7204,7 @@
         <v>70</v>
       </c>
       <c r="F243" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G243" s="8"/>
       <c r="H243" s="3"/>
@@ -7228,7 +7228,7 @@
         <v>70</v>
       </c>
       <c r="F244" s="6" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G244" s="8"/>
       <c r="H244" s="3"/>
@@ -7252,7 +7252,7 @@
         <v>50</v>
       </c>
       <c r="F245" s="11" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="G245" s="8"/>
       <c r="H245" s="3"/>
@@ -7516,7 +7516,7 @@
         <v>70</v>
       </c>
       <c r="F256" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G256" s="3"/>
       <c r="H256" s="3"/>
@@ -7540,7 +7540,7 @@
         <v>70</v>
       </c>
       <c r="F257" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G257" s="3"/>
       <c r="H257" s="3"/>
@@ -7564,7 +7564,7 @@
         <v>70</v>
       </c>
       <c r="F258" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G258" s="3"/>
       <c r="H258" s="3"/>
@@ -7900,7 +7900,7 @@
         <v>70</v>
       </c>
       <c r="F272" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G272" s="3"/>
       <c r="H272" s="3"/>
@@ -7924,7 +7924,7 @@
         <v>70</v>
       </c>
       <c r="F273" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G273" s="3"/>
       <c r="H273" s="3"/>
@@ -7948,7 +7948,7 @@
         <v>70</v>
       </c>
       <c r="F274" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G274" s="3"/>
       <c r="H274" s="3"/>
@@ -8284,7 +8284,7 @@
         <v>48</v>
       </c>
       <c r="F288" s="23" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G288" s="24"/>
       <c r="H288" s="3"/>
@@ -8308,7 +8308,7 @@
         <v>48</v>
       </c>
       <c r="F289" s="23" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G289" s="24"/>
       <c r="H289" s="3"/>
@@ -8323,7 +8323,7 @@
     </row>
     <row r="290" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B290" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C290" s="4" t="s">
         <v>35</v>
@@ -8349,7 +8349,7 @@
         <v>50</v>
       </c>
       <c r="F291" s="28" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G291" s="25"/>
       <c r="H291" s="3"/>
@@ -8373,7 +8373,7 @@
         <v>70</v>
       </c>
       <c r="F292" s="29" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G292" s="3"/>
       <c r="H292" s="3"/>
@@ -8397,7 +8397,7 @@
         <v>70</v>
       </c>
       <c r="F293" s="29" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G293" s="3"/>
       <c r="H293" s="3"/>
@@ -8421,7 +8421,7 @@
         <v>70</v>
       </c>
       <c r="F294" s="29" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G294" s="3"/>
       <c r="H294" s="3"/>
@@ -8445,7 +8445,7 @@
         <v>50</v>
       </c>
       <c r="F295" s="28" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G295" s="25"/>
       <c r="H295" s="3"/>
@@ -8469,7 +8469,7 @@
         <v>70</v>
       </c>
       <c r="F296" s="29" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G296" s="3"/>
       <c r="H296" s="3"/>
@@ -8493,7 +8493,7 @@
         <v>70</v>
       </c>
       <c r="F297" s="29" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G297" s="3"/>
       <c r="H297" s="3"/>
@@ -8517,7 +8517,7 @@
         <v>70</v>
       </c>
       <c r="F298" s="29" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G298" s="3"/>
       <c r="H298" s="3"/>
@@ -8541,7 +8541,7 @@
         <v>50</v>
       </c>
       <c r="F299" s="28" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G299" s="25"/>
       <c r="H299" s="3"/>
@@ -8565,7 +8565,7 @@
         <v>70</v>
       </c>
       <c r="F300" s="29" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G300" s="3"/>
       <c r="H300" s="3"/>
@@ -8589,7 +8589,7 @@
         <v>70</v>
       </c>
       <c r="F301" s="29" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G301" s="3"/>
       <c r="H301" s="3"/>
@@ -8613,7 +8613,7 @@
         <v>70</v>
       </c>
       <c r="F302" s="29" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G302" s="3"/>
       <c r="H302" s="3"/>
@@ -8637,7 +8637,7 @@
         <v>70</v>
       </c>
       <c r="F303" s="13" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G303" s="30"/>
       <c r="H303" s="3"/>
@@ -8661,7 +8661,7 @@
         <v>52</v>
       </c>
       <c r="F304" s="13" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G304" s="30"/>
       <c r="H304" s="3"/>
@@ -8685,7 +8685,7 @@
         <v>52</v>
       </c>
       <c r="F305" s="13" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G305" s="30"/>
       <c r="H305" s="3"/>
@@ -8709,7 +8709,7 @@
         <v>52</v>
       </c>
       <c r="F306" s="13" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G306" s="30"/>
       <c r="H306" s="3"/>
@@ -8733,7 +8733,7 @@
         <v>52</v>
       </c>
       <c r="F307" s="13" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G307" s="30"/>
       <c r="H307" s="3"/>
@@ -8757,7 +8757,7 @@
         <v>52</v>
       </c>
       <c r="F308" s="13" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G308" s="30"/>
       <c r="H308" s="3"/>
@@ -8781,7 +8781,7 @@
         <v>52</v>
       </c>
       <c r="F309" s="13" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G309" s="30"/>
       <c r="H309" s="3"/>
@@ -8805,7 +8805,7 @@
         <v>52</v>
       </c>
       <c r="F310" s="13" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G310" s="30"/>
       <c r="H310" s="3"/>
@@ -8829,7 +8829,7 @@
         <v>52</v>
       </c>
       <c r="F311" s="13" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G311" s="30"/>
       <c r="H311" s="3"/>
@@ -8853,7 +8853,7 @@
         <v>52</v>
       </c>
       <c r="F312" s="13" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G312" s="30"/>
       <c r="H312" s="3"/>
@@ -8877,7 +8877,7 @@
         <v>52</v>
       </c>
       <c r="F313" s="13" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G313" s="30"/>
       <c r="H313" s="3"/>
@@ -8901,7 +8901,7 @@
         <v>52</v>
       </c>
       <c r="F314" s="13" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G314" s="30"/>
       <c r="H314" s="3"/>
@@ -8925,7 +8925,7 @@
         <v>52</v>
       </c>
       <c r="F315" s="13" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G315" s="30"/>
       <c r="H315" s="3"/>
@@ -9227,7 +9227,7 @@
         <v>48</v>
       </c>
       <c r="F328" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G328" s="8"/>
       <c r="H328" s="3"/>
@@ -9392,10 +9392,10 @@
         <v>17</v>
       </c>
       <c r="E335" s="11" t="s">
-        <v>291</v>
+        <v>400</v>
       </c>
       <c r="F335" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G335" s="3"/>
       <c r="H335" s="3"/>
@@ -9995,7 +9995,7 @@
         <v>48</v>
       </c>
       <c r="F360" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G360" s="8"/>
       <c r="H360" s="3"/>
@@ -10019,7 +10019,7 @@
         <v>50</v>
       </c>
       <c r="F361" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G361" s="8"/>
       <c r="H361" s="3"/>
@@ -10040,10 +10040,10 @@
         <v>44</v>
       </c>
       <c r="E362" s="11" t="s">
-        <v>291</v>
+        <v>400</v>
       </c>
       <c r="F362" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G362" s="8"/>
       <c r="H362" s="3"/>

--- a/ArmCoreV1_QSPI/SSCProject/lan9252_app.xlsx
+++ b/ArmCoreV1_QSPI/SSCProject/lan9252_app.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <workbookProtection lockStructure="1"/>
@@ -11,8 +11,8 @@
     <sheet name="Profile" sheetId="11" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Profile!$B$10:$P$75</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Profile!$B$1:$P$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Profile!$B$10:$P$78</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Profile!$B$1:$P$79</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="87">
   <si>
     <t>Device Profile:</t>
   </si>
@@ -308,7 +308,7 @@
     <t>UINT</t>
   </si>
   <si>
-    <t>InU16_CrtFsmState</t>
+    <t>InU16_MlcFsmState</t>
   </si>
   <si>
     <t>InU16_BeamIndexFB</t>
@@ -368,7 +368,7 @@
     <t>InU16_JawInfo</t>
   </si>
   <si>
-    <t>InAU16_Reserve2</t>
+    <t>InU16_JawFsmState</t>
   </si>
   <si>
     <t>//0x7nnx</t>
@@ -383,7 +383,7 @@
     <t>OutputData</t>
   </si>
   <si>
-    <t>OutU16_FsmStateSetting</t>
+    <t>OutU16_MlcFsmSetting</t>
   </si>
   <si>
     <t>OutU16_BeamIndex</t>
@@ -410,7 +410,16 @@
     <t>OutU16_PlanCmd</t>
   </si>
   <si>
-    <t>OutU16_Reserve</t>
+    <t>OutU16_JawXPositionSetting</t>
+  </si>
+  <si>
+    <t>OutU16_JawYPositionSetting</t>
+  </si>
+  <si>
+    <t>OutU16_ErrReset</t>
+  </si>
+  <si>
+    <t>OutU16_JawFsmSetting</t>
   </si>
   <si>
     <t>//0x8nnx</t>
@@ -1100,6 +1109,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -1112,6 +1125,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
@@ -1125,13 +1141,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -1483,7 +1492,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T926"/>
+  <dimension ref="A1:T929"/>
   <sheetFormatPr defaultColWidth="10.7079646017699" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="3.85840707964602" style="2" customWidth="1"/>
@@ -1528,17 +1537,17 @@
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7"/>
+      <c r="T1" s="7"/>
     </row>
     <row r="2" spans="1:20">
       <c r="A2" s="3"/>
       <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="3"/>
@@ -1554,14 +1563,14 @@
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="20"/>
-      <c r="S2" s="20"/>
-      <c r="T2" s="20"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="3"/>
-      <c r="B3" s="8"/>
+      <c r="B3" s="9"/>
       <c r="C3" s="5"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -1576,14 +1585,14 @@
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
-      <c r="Q3" s="20"/>
-      <c r="R3" s="20"/>
-      <c r="S3" s="20"/>
-      <c r="T3" s="20"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="3"/>
-      <c r="B4" s="8"/>
+      <c r="B4" s="9"/>
       <c r="C4" s="5"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -1598,10 +1607,10 @@
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
-      <c r="Q4" s="20"/>
-      <c r="R4" s="20"/>
-      <c r="S4" s="20"/>
-      <c r="T4" s="20"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="3"/>
@@ -1620,10 +1629,10 @@
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
-      <c r="Q5" s="20"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="20"/>
-      <c r="T5" s="20"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="3"/>
@@ -1642,10 +1651,10 @@
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
-      <c r="Q6" s="20"/>
-      <c r="R6" s="20"/>
-      <c r="S6" s="20"/>
-      <c r="T6" s="20"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="3"/>
@@ -1653,25 +1662,25 @@
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="20"/>
-      <c r="R7" s="20"/>
-      <c r="S7" s="20"/>
-      <c r="T7" s="20"/>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+    </row>
+    <row r="8" spans="1:20">
       <c r="A8" s="3"/>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="11" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="4"/>
@@ -1689,7 +1698,7 @@
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:20">
       <c r="A9" s="3"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -1707,539 +1716,539 @@
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:20">
       <c r="A10" s="3"/>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="J10" s="11" t="s">
+      <c r="J10" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="K10" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="L10" s="11" t="s">
+      <c r="L10" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="M10" s="11" t="s">
+      <c r="M10" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="N10" s="19" t="s">
+      <c r="N10" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="O10" s="19" t="s">
+      <c r="O10" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="P10" s="11" t="s">
+      <c r="P10" s="12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" spans="1:16">
-      <c r="A11" s="12"/>
-      <c r="B11" s="13" t="s">
+    <row r="11" s="1" customFormat="1" spans="1:20">
+      <c r="A11" s="14"/>
+      <c r="B11" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="13"/>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="15"/>
+    </row>
+    <row r="12" spans="1:20">
       <c r="A12" s="3"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="16"/>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="18"/>
+    </row>
+    <row r="13" spans="1:20">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
-      <c r="P13" s="12"/>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:16">
-      <c r="A14" s="12"/>
-      <c r="B14" s="18" t="s">
+      <c r="P13" s="14"/>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:20">
+      <c r="A14" s="14"/>
+      <c r="B14" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
-      <c r="L14" s="18"/>
-      <c r="M14" s="18"/>
-      <c r="N14" s="18"/>
-      <c r="O14" s="18"/>
-      <c r="P14" s="18"/>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="20"/>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+    </row>
+    <row r="15" spans="1:20">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
-      <c r="P15" s="12"/>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="P15" s="14"/>
+    </row>
+    <row r="16" spans="1:20">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-      <c r="P16" s="12"/>
+      <c r="P16" s="14"/>
     </row>
     <row r="17" s="1" customFormat="1" hidden="1" outlineLevel="1" spans="1:16">
-      <c r="A17" s="12"/>
-      <c r="B17" s="18" t="s">
+      <c r="A17" s="14"/>
+      <c r="B17" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="18"/>
-      <c r="L17" s="18"/>
-      <c r="M17" s="18"/>
-      <c r="N17" s="18"/>
-      <c r="O17" s="18"/>
-      <c r="P17" s="18"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
     </row>
     <row r="18" hidden="1" outlineLevel="1" spans="1:16">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
-      <c r="P18" s="12"/>
+      <c r="P18" s="14"/>
     </row>
     <row r="19" hidden="1" outlineLevel="1" spans="1:16">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-      <c r="P19" s="12"/>
+      <c r="P19" s="14"/>
     </row>
     <row r="20" s="1" customFormat="1" hidden="1" outlineLevel="1" spans="1:16">
-      <c r="A20" s="12"/>
-      <c r="B20" s="18" t="s">
+      <c r="A20" s="14"/>
+      <c r="B20" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="18"/>
-      <c r="K20" s="18"/>
-      <c r="L20" s="18"/>
-      <c r="M20" s="18"/>
-      <c r="N20" s="18"/>
-      <c r="O20" s="18"/>
-      <c r="P20" s="18"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
     </row>
     <row r="21" hidden="1" outlineLevel="1" spans="1:16">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
-      <c r="P21" s="12"/>
+      <c r="P21" s="14"/>
     </row>
     <row r="22" hidden="1" outlineLevel="1" spans="1:16">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
-      <c r="P22" s="12"/>
+      <c r="P22" s="14"/>
     </row>
     <row r="23" s="1" customFormat="1" hidden="1" outlineLevel="1" spans="1:16">
-      <c r="A23" s="12"/>
-      <c r="B23" s="18" t="s">
+      <c r="A23" s="14"/>
+      <c r="B23" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="18"/>
-      <c r="K23" s="18"/>
-      <c r="L23" s="18"/>
-      <c r="M23" s="18"/>
-      <c r="N23" s="18"/>
-      <c r="O23" s="18"/>
-      <c r="P23" s="18"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
     </row>
     <row r="24" hidden="1" outlineLevel="1" spans="1:16">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
-      <c r="P24" s="12"/>
+      <c r="P24" s="14"/>
     </row>
     <row r="25" hidden="1" outlineLevel="1" spans="1:16">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
-      <c r="P25" s="12"/>
+      <c r="P25" s="14"/>
     </row>
     <row r="26" s="1" customFormat="1" hidden="1" outlineLevel="1" spans="1:16">
-      <c r="A26" s="12"/>
-      <c r="B26" s="18" t="s">
+      <c r="A26" s="14"/>
+      <c r="B26" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="18"/>
-      <c r="K26" s="18"/>
-      <c r="L26" s="18"/>
-      <c r="M26" s="18"/>
-      <c r="N26" s="18"/>
-      <c r="O26" s="18"/>
-      <c r="P26" s="18"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
     </row>
     <row r="27" hidden="1" outlineLevel="1" spans="1:16">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
-      <c r="P27" s="12"/>
+      <c r="P27" s="14"/>
     </row>
     <row r="28" hidden="1" outlineLevel="1" spans="1:16">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
-      <c r="P28" s="12"/>
+      <c r="P28" s="14"/>
     </row>
     <row r="29" s="1" customFormat="1" hidden="1" outlineLevel="1" spans="1:16">
-      <c r="A29" s="12"/>
-      <c r="B29" s="18" t="s">
+      <c r="A29" s="14"/>
+      <c r="B29" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="C29" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="18"/>
-      <c r="J29" s="18"/>
-      <c r="K29" s="18"/>
-      <c r="L29" s="18"/>
-      <c r="M29" s="18"/>
-      <c r="N29" s="18"/>
-      <c r="O29" s="18"/>
-      <c r="P29" s="18"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
     </row>
     <row r="30" hidden="1" outlineLevel="1" spans="1:16">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
-      <c r="P30" s="12"/>
+      <c r="P30" s="14"/>
     </row>
     <row r="31" hidden="1" outlineLevel="1" spans="1:16">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
-      <c r="P31" s="12"/>
+      <c r="P31" s="14"/>
     </row>
     <row r="32" s="1" customFormat="1" hidden="1" outlineLevel="1" spans="1:16">
-      <c r="A32" s="12"/>
-      <c r="B32" s="18" t="s">
+      <c r="A32" s="14"/>
+      <c r="B32" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="18"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="18"/>
-      <c r="M32" s="18"/>
-      <c r="N32" s="18"/>
-      <c r="O32" s="18"/>
-      <c r="P32" s="18"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="20"/>
+      <c r="L32" s="20"/>
+      <c r="M32" s="20"/>
+      <c r="N32" s="20"/>
+      <c r="O32" s="20"/>
+      <c r="P32" s="20"/>
     </row>
     <row r="33" hidden="1" outlineLevel="1" spans="1:16">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
-      <c r="P33" s="12"/>
+      <c r="P33" s="14"/>
     </row>
     <row r="34" hidden="1" outlineLevel="1" spans="1:16">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
-      <c r="P34" s="12"/>
+      <c r="P34" s="14"/>
     </row>
     <row r="35" s="1" customFormat="1" collapsed="1" spans="1:16">
-      <c r="A35" s="12"/>
-      <c r="B35" s="18" t="s">
+      <c r="A35" s="14"/>
+      <c r="B35" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="C35" s="18" t="s">
+      <c r="C35" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="18"/>
-      <c r="K35" s="18"/>
-      <c r="L35" s="18"/>
-      <c r="M35" s="18"/>
-      <c r="N35" s="18"/>
-      <c r="O35" s="18"/>
-      <c r="P35" s="18"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="20"/>
+      <c r="K35" s="20"/>
+      <c r="L35" s="20"/>
+      <c r="M35" s="20"/>
+      <c r="N35" s="20"/>
+      <c r="O35" s="20"/>
+      <c r="P35" s="20"/>
     </row>
     <row r="36" spans="1:16">
       <c r="A36" s="3"/>
@@ -2249,93 +2258,93 @@
       <c r="C36" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D36" s="17"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12" t="s">
+      <c r="D36" s="19"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="12"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
       <c r="J36" s="3"/>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
       <c r="N36" s="3"/>
       <c r="O36" s="3"/>
-      <c r="P36" s="12"/>
+      <c r="P36" s="14"/>
     </row>
     <row r="37" customFormat="1" spans="1:16">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
-      <c r="D37" s="17">
+      <c r="D37" s="19">
         <v>1</v>
       </c>
-      <c r="E37" s="12" t="s">
+      <c r="E37" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F37" s="12" t="s">
+      <c r="F37" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="G37" s="12"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="12"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
       <c r="N37" s="3"/>
       <c r="O37" s="3"/>
-      <c r="P37" s="12"/>
+      <c r="P37" s="14"/>
     </row>
     <row r="38" customFormat="1" spans="1:16">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
-      <c r="D38" s="17">
+      <c r="D38" s="19">
         <v>2</v>
       </c>
-      <c r="E38" s="12" t="s">
+      <c r="E38" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F38" s="12" t="s">
+      <c r="F38" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="G38" s="12"/>
-      <c r="H38" s="12"/>
-      <c r="I38" s="12"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
-      <c r="P38" s="12"/>
+      <c r="P38" s="14"/>
     </row>
     <row r="39" customFormat="1" spans="1:16">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
-      <c r="D39" s="17">
+      <c r="D39" s="19">
         <v>3</v>
       </c>
-      <c r="E39" s="12" t="s">
+      <c r="E39" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F39" s="12" t="s">
+      <c r="F39" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="G39" s="12"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="12"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="14"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-      <c r="P39" s="12"/>
+      <c r="P39" s="14"/>
     </row>
     <row r="40" customFormat="1" spans="1:16">
       <c r="A40" s="3">
@@ -2343,383 +2352,383 @@
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
-      <c r="D40" s="17">
+      <c r="D40" s="19">
         <v>4</v>
       </c>
-      <c r="E40" s="12" t="s">
+      <c r="E40" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F40" s="12" t="s">
+      <c r="F40" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="G40" s="12"/>
-      <c r="H40" s="12"/>
-      <c r="I40" s="12"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="14"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-      <c r="P40" s="12"/>
+      <c r="P40" s="14"/>
     </row>
     <row r="41" customFormat="1" spans="1:16">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
-      <c r="D41" s="17">
+      <c r="D41" s="19">
         <v>5</v>
       </c>
-      <c r="E41" s="12" t="s">
+      <c r="E41" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F41" s="12" t="s">
+      <c r="F41" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="G41" s="12"/>
-      <c r="H41" s="12"/>
-      <c r="I41" s="12"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="14"/>
       <c r="J41" s="3"/>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
       <c r="N41" s="3"/>
       <c r="O41" s="3"/>
-      <c r="P41" s="12"/>
+      <c r="P41" s="14"/>
     </row>
     <row r="42" customFormat="1" spans="1:16">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
-      <c r="D42" s="17">
+      <c r="D42" s="19">
         <v>6</v>
       </c>
-      <c r="E42" s="12" t="s">
+      <c r="E42" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F42" s="12" t="s">
+      <c r="F42" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="G42" s="12"/>
-      <c r="H42" s="12"/>
-      <c r="I42" s="12"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="14"/>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
       <c r="N42" s="3"/>
       <c r="O42" s="3"/>
-      <c r="P42" s="12"/>
+      <c r="P42" s="14"/>
     </row>
     <row r="43" customFormat="1" spans="1:16">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
-      <c r="D43" s="17">
+      <c r="D43" s="19">
         <v>7</v>
       </c>
-      <c r="E43" s="12" t="s">
+      <c r="E43" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F43" s="12" t="s">
+      <c r="F43" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="G43" s="12"/>
-      <c r="H43" s="12"/>
-      <c r="I43" s="12"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="14"/>
       <c r="J43" s="3"/>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
       <c r="N43" s="3"/>
       <c r="O43" s="3"/>
-      <c r="P43" s="12"/>
+      <c r="P43" s="14"/>
     </row>
     <row r="44" customFormat="1" spans="1:16">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
-      <c r="D44" s="17">
+      <c r="D44" s="19">
         <v>8</v>
       </c>
-      <c r="E44" s="12" t="s">
+      <c r="E44" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F44" s="12" t="s">
+      <c r="F44" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="G44" s="12"/>
-      <c r="H44" s="12"/>
-      <c r="I44" s="12"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="14"/>
       <c r="J44" s="3"/>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
       <c r="N44" s="3"/>
       <c r="O44" s="3"/>
-      <c r="P44" s="12"/>
+      <c r="P44" s="14"/>
     </row>
     <row r="45" customFormat="1" spans="1:16">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
-      <c r="D45" s="17">
+      <c r="D45" s="19">
         <v>9</v>
       </c>
-      <c r="E45" s="12" t="s">
+      <c r="E45" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F45" s="12" t="s">
+      <c r="F45" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="G45" s="12"/>
-      <c r="H45" s="12"/>
-      <c r="I45" s="12"/>
+      <c r="G45" s="14"/>
+      <c r="H45" s="14"/>
+      <c r="I45" s="14"/>
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
-      <c r="P45" s="12"/>
+      <c r="P45" s="14"/>
     </row>
     <row r="46" customFormat="1" spans="1:16">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
-      <c r="D46" s="17">
+      <c r="D46" s="19">
         <v>10</v>
       </c>
-      <c r="E46" s="12" t="s">
+      <c r="E46" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F46" s="12" t="s">
+      <c r="F46" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="G46" s="12"/>
-      <c r="H46" s="12"/>
-      <c r="I46" s="12"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="14"/>
       <c r="J46" s="3"/>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
-      <c r="P46" s="12"/>
+      <c r="P46" s="14"/>
     </row>
     <row r="47" customFormat="1" spans="1:16">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
-      <c r="D47" s="17">
+      <c r="D47" s="19">
         <v>11</v>
       </c>
-      <c r="E47" s="12" t="s">
+      <c r="E47" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F47" s="12" t="s">
+      <c r="F47" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="G47" s="12"/>
-      <c r="H47" s="12"/>
-      <c r="I47" s="12"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="14"/>
+      <c r="I47" s="14"/>
       <c r="J47" s="3"/>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
-      <c r="P47" s="12"/>
+      <c r="P47" s="14"/>
     </row>
     <row r="48" customFormat="1" spans="1:16">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
-      <c r="D48" s="17">
+      <c r="D48" s="19">
         <v>12</v>
       </c>
-      <c r="E48" s="12" t="s">
+      <c r="E48" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F48" s="12" t="s">
+      <c r="F48" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="G48" s="12"/>
-      <c r="H48" s="12"/>
-      <c r="I48" s="12"/>
+      <c r="G48" s="14"/>
+      <c r="H48" s="14"/>
+      <c r="I48" s="14"/>
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
-      <c r="P48" s="12"/>
+      <c r="P48" s="14"/>
     </row>
     <row r="49" customFormat="1" spans="1:16">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
-      <c r="D49" s="17">
+      <c r="D49" s="19">
         <v>13</v>
       </c>
-      <c r="E49" s="12" t="s">
+      <c r="E49" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="F49" s="12" t="s">
+      <c r="F49" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="G49" s="12"/>
-      <c r="H49" s="12"/>
-      <c r="I49" s="12"/>
+      <c r="G49" s="14"/>
+      <c r="H49" s="14"/>
+      <c r="I49" s="14"/>
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
       <c r="N49" s="3"/>
       <c r="O49" s="3"/>
-      <c r="P49" s="12"/>
+      <c r="P49" s="14"/>
     </row>
     <row r="50" customFormat="1" spans="1:16">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
-      <c r="D50" s="17">
+      <c r="D50" s="19">
         <v>14</v>
       </c>
-      <c r="E50" s="12" t="s">
+      <c r="E50" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="F50" s="12" t="s">
+      <c r="F50" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="G50" s="12"/>
-      <c r="H50" s="12"/>
-      <c r="I50" s="12"/>
+      <c r="G50" s="14"/>
+      <c r="H50" s="14"/>
+      <c r="I50" s="14"/>
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
       <c r="O50" s="3"/>
-      <c r="P50" s="12"/>
+      <c r="P50" s="14"/>
     </row>
     <row r="51" customFormat="1" spans="1:16">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
-      <c r="D51" s="17">
+      <c r="D51" s="19">
         <v>15</v>
       </c>
-      <c r="E51" s="12" t="s">
+      <c r="E51" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F51" s="12" t="s">
+      <c r="F51" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="G51" s="12"/>
-      <c r="H51" s="12"/>
-      <c r="I51" s="12"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="14"/>
+      <c r="I51" s="14"/>
       <c r="J51" s="3"/>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
       <c r="N51" s="3"/>
       <c r="O51" s="3"/>
-      <c r="P51" s="12"/>
+      <c r="P51" s="14"/>
     </row>
     <row r="52" customFormat="1" spans="1:16">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
-      <c r="D52" s="17">
+      <c r="D52" s="19">
         <v>16</v>
       </c>
-      <c r="E52" s="12" t="s">
+      <c r="E52" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="F52" s="12" t="s">
+      <c r="F52" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="G52" s="12"/>
-      <c r="H52" s="12"/>
-      <c r="I52" s="12"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="14"/>
+      <c r="I52" s="14"/>
       <c r="J52" s="3"/>
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
       <c r="M52" s="3"/>
       <c r="N52" s="3"/>
       <c r="O52" s="3"/>
-      <c r="P52" s="12"/>
+      <c r="P52" s="14"/>
     </row>
     <row r="53" customFormat="1" spans="1:16">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
-      <c r="D53" s="17">
+      <c r="D53" s="19">
         <v>17</v>
       </c>
-      <c r="E53" s="12" t="s">
+      <c r="E53" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F53" s="12" t="s">
+      <c r="F53" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="G53" s="12"/>
-      <c r="H53" s="12"/>
-      <c r="I53" s="12"/>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14"/>
+      <c r="I53" s="14"/>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
       <c r="O53" s="3"/>
-      <c r="P53" s="12"/>
+      <c r="P53" s="14"/>
     </row>
     <row r="54" customFormat="1" spans="1:16">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
-      <c r="D54" s="17">
+      <c r="D54" s="19">
         <v>18</v>
       </c>
-      <c r="E54" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="F54" s="12" t="s">
+      <c r="E54" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F54" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
+      <c r="G54" s="14"/>
+      <c r="H54" s="14"/>
+      <c r="I54" s="14"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
-      <c r="P54" s="12"/>
+      <c r="P54" s="14"/>
     </row>
     <row r="55" s="1" customFormat="1" spans="1:16">
-      <c r="A55" s="12"/>
-      <c r="B55" s="18" t="s">
+      <c r="A55" s="14"/>
+      <c r="B55" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="C55" s="18" t="s">
+      <c r="C55" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="18"/>
-      <c r="E55" s="18"/>
-      <c r="F55" s="18"/>
-      <c r="G55" s="18"/>
-      <c r="H55" s="18"/>
-      <c r="I55" s="18"/>
-      <c r="J55" s="18"/>
-      <c r="K55" s="18"/>
-      <c r="L55" s="18"/>
-      <c r="M55" s="18"/>
-      <c r="N55" s="18"/>
-      <c r="O55" s="18"/>
-      <c r="P55" s="18"/>
+      <c r="D55" s="20"/>
+      <c r="E55" s="20"/>
+      <c r="F55" s="20"/>
+      <c r="G55" s="20"/>
+      <c r="H55" s="20"/>
+      <c r="I55" s="20"/>
+      <c r="J55" s="20"/>
+      <c r="K55" s="20"/>
+      <c r="L55" s="20"/>
+      <c r="M55" s="20"/>
+      <c r="N55" s="20"/>
+      <c r="O55" s="20"/>
+      <c r="P55" s="20"/>
     </row>
     <row r="56" spans="1:16">
       <c r="A56" s="3"/>
@@ -2729,489 +2738,507 @@
       <c r="C56" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D56" s="17"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12" t="s">
+      <c r="D56" s="19"/>
+      <c r="E56" s="14"/>
+      <c r="F56" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="12"/>
+      <c r="G56" s="14"/>
+      <c r="H56" s="14"/>
+      <c r="I56" s="14"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-      <c r="P56" s="12"/>
+      <c r="P56" s="14"/>
     </row>
     <row r="57" customFormat="1" spans="1:16">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
-      <c r="D57" s="17">
+      <c r="D57" s="19">
         <v>1</v>
       </c>
-      <c r="E57" s="12" t="s">
+      <c r="E57" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F57" s="12" t="s">
+      <c r="F57" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
+      <c r="G57" s="14"/>
+      <c r="H57" s="14"/>
+      <c r="I57" s="14"/>
       <c r="J57" s="3"/>
       <c r="K57" s="3"/>
       <c r="L57" s="3"/>
       <c r="M57" s="3"/>
       <c r="N57" s="3"/>
       <c r="O57" s="3"/>
-      <c r="P57" s="12"/>
+      <c r="P57" s="14"/>
     </row>
     <row r="58" customFormat="1" spans="1:16">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
-      <c r="D58" s="17">
+      <c r="D58" s="19">
         <v>2</v>
       </c>
-      <c r="E58" s="12" t="s">
+      <c r="E58" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F58" s="12" t="s">
+      <c r="F58" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
+      <c r="G58" s="14"/>
+      <c r="H58" s="14"/>
+      <c r="I58" s="14"/>
       <c r="J58" s="3"/>
       <c r="K58" s="3"/>
       <c r="L58" s="3"/>
       <c r="M58" s="3"/>
       <c r="N58" s="3"/>
       <c r="O58" s="3"/>
-      <c r="P58" s="12"/>
+      <c r="P58" s="14"/>
     </row>
     <row r="59" customFormat="1" spans="1:16">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
-      <c r="D59" s="17">
+      <c r="D59" s="19">
         <v>3</v>
       </c>
-      <c r="E59" s="12" t="s">
+      <c r="E59" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F59" s="12" t="s">
+      <c r="F59" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="G59" s="12"/>
-      <c r="H59" s="12"/>
-      <c r="I59" s="12"/>
+      <c r="G59" s="14"/>
+      <c r="H59" s="14"/>
+      <c r="I59" s="14"/>
       <c r="J59" s="3"/>
       <c r="K59" s="3"/>
       <c r="L59" s="3"/>
       <c r="M59" s="3"/>
       <c r="N59" s="3"/>
       <c r="O59" s="3"/>
-      <c r="P59" s="12"/>
+      <c r="P59" s="14"/>
     </row>
     <row r="60" customFormat="1" spans="1:16">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
-      <c r="D60" s="17">
+      <c r="D60" s="19">
         <v>4</v>
       </c>
-      <c r="E60" s="12" t="s">
+      <c r="E60" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F60" s="12" t="s">
+      <c r="F60" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="G60" s="12"/>
-      <c r="H60" s="12"/>
-      <c r="I60" s="12"/>
+      <c r="G60" s="14"/>
+      <c r="H60" s="14"/>
+      <c r="I60" s="14"/>
       <c r="J60" s="3"/>
       <c r="K60" s="3"/>
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
       <c r="N60" s="3"/>
       <c r="O60" s="3"/>
-      <c r="P60" s="12"/>
+      <c r="P60" s="14"/>
     </row>
     <row r="61" customFormat="1" spans="1:16">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
-      <c r="D61" s="17">
+      <c r="D61" s="19">
         <v>5</v>
       </c>
-      <c r="E61" s="12" t="s">
+      <c r="E61" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F61" s="12" t="s">
+      <c r="F61" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="G61" s="12"/>
-      <c r="H61" s="12"/>
-      <c r="I61" s="12"/>
+      <c r="G61" s="14"/>
+      <c r="H61" s="14"/>
+      <c r="I61" s="14"/>
       <c r="J61" s="3"/>
       <c r="K61" s="3"/>
       <c r="L61" s="3"/>
       <c r="M61" s="3"/>
       <c r="N61" s="3"/>
       <c r="O61" s="3"/>
-      <c r="P61" s="12"/>
+      <c r="P61" s="14"/>
     </row>
     <row r="62" customFormat="1" spans="1:16">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
-      <c r="D62" s="17">
+      <c r="D62" s="19">
         <v>6</v>
       </c>
-      <c r="E62" s="12" t="s">
+      <c r="E62" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F62" s="12" t="s">
+      <c r="F62" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="G62" s="12"/>
-      <c r="H62" s="12"/>
-      <c r="I62" s="12"/>
+      <c r="G62" s="14"/>
+      <c r="H62" s="14"/>
+      <c r="I62" s="14"/>
       <c r="J62" s="3"/>
       <c r="K62" s="3"/>
       <c r="L62" s="3"/>
       <c r="M62" s="3"/>
       <c r="N62" s="3"/>
       <c r="O62" s="3"/>
-      <c r="P62" s="12"/>
+      <c r="P62" s="14"/>
     </row>
     <row r="63" customFormat="1" spans="1:16">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
-      <c r="D63" s="17">
+      <c r="D63" s="19">
         <v>7</v>
       </c>
-      <c r="E63" s="12" t="s">
+      <c r="E63" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F63" s="12" t="s">
+      <c r="F63" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="G63" s="12"/>
-      <c r="H63" s="12"/>
-      <c r="I63" s="12"/>
+      <c r="G63" s="14"/>
+      <c r="H63" s="14"/>
+      <c r="I63" s="14"/>
       <c r="J63" s="3"/>
       <c r="K63" s="3"/>
       <c r="L63" s="3"/>
       <c r="M63" s="3"/>
       <c r="N63" s="3"/>
       <c r="O63" s="3"/>
-      <c r="P63" s="12"/>
+      <c r="P63" s="14"/>
     </row>
     <row r="64" customFormat="1" spans="1:16">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
-      <c r="D64" s="17">
+      <c r="D64" s="19">
         <v>8</v>
       </c>
-      <c r="E64" s="12" t="s">
+      <c r="E64" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F64" s="12" t="s">
+      <c r="F64" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="G64" s="12"/>
-      <c r="H64" s="12"/>
-      <c r="I64" s="12"/>
+      <c r="G64" s="14"/>
+      <c r="H64" s="14"/>
+      <c r="I64" s="14"/>
       <c r="J64" s="3"/>
       <c r="K64" s="3"/>
       <c r="L64" s="3"/>
       <c r="M64" s="3"/>
       <c r="N64" s="3"/>
       <c r="O64" s="3"/>
-      <c r="P64" s="12"/>
+      <c r="P64" s="14"/>
     </row>
     <row r="65" customFormat="1" spans="1:16">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
-      <c r="D65" s="17">
+      <c r="D65" s="19">
         <v>9</v>
       </c>
-      <c r="E65" s="12" t="s">
+      <c r="E65" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F65" s="12" t="s">
+      <c r="F65" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="G65" s="12"/>
-      <c r="H65" s="12"/>
-      <c r="I65" s="12"/>
+      <c r="G65" s="14"/>
+      <c r="H65" s="14"/>
+      <c r="I65" s="14"/>
       <c r="J65" s="3"/>
       <c r="K65" s="3"/>
       <c r="L65" s="3"/>
       <c r="M65" s="3"/>
       <c r="N65" s="3"/>
       <c r="O65" s="3"/>
-      <c r="P65" s="12"/>
+      <c r="P65" s="14"/>
     </row>
     <row r="66" customFormat="1" spans="1:16">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
-      <c r="D66" s="17">
+      <c r="D66" s="19">
         <v>10</v>
       </c>
-      <c r="E66" s="12" t="s">
+      <c r="E66" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F66" s="12" t="s">
+      <c r="F66" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="G66" s="12"/>
-      <c r="H66" s="12"/>
-      <c r="I66" s="12"/>
+      <c r="G66" s="14"/>
+      <c r="H66" s="14"/>
+      <c r="I66" s="14"/>
       <c r="J66" s="3"/>
       <c r="K66" s="3"/>
       <c r="L66" s="3"/>
       <c r="M66" s="3"/>
       <c r="N66" s="3"/>
       <c r="O66" s="3"/>
-      <c r="P66" s="12"/>
-    </row>
-    <row r="67" s="1" customFormat="1" spans="1:16">
-      <c r="A67" s="12"/>
-      <c r="B67" s="18" t="s">
+      <c r="P66" s="14"/>
+    </row>
+    <row r="67" customFormat="1" spans="1:16">
+      <c r="A67" s="3"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="19">
+        <v>11</v>
+      </c>
+      <c r="E67" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F67" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="C67" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="D67" s="18"/>
-      <c r="E67" s="18"/>
-      <c r="F67" s="21"/>
-      <c r="G67" s="18"/>
-      <c r="H67" s="18"/>
-      <c r="I67" s="18"/>
-      <c r="J67" s="18"/>
-      <c r="K67" s="18"/>
-      <c r="L67" s="18"/>
-      <c r="M67" s="18"/>
-      <c r="N67" s="18"/>
-      <c r="O67" s="18"/>
-      <c r="P67" s="18"/>
-    </row>
-    <row r="68" spans="1:16">
+      <c r="G67" s="14"/>
+      <c r="H67" s="14"/>
+      <c r="I67" s="14"/>
+      <c r="J67" s="3"/>
+      <c r="K67" s="3"/>
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+      <c r="P67" s="14"/>
+    </row>
+    <row r="68" customFormat="1" spans="1:16">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
-      <c r="D68" s="17"/>
-      <c r="E68" s="12"/>
-      <c r="F68" s="12"/>
-      <c r="G68" s="12"/>
-      <c r="H68" s="12"/>
-      <c r="I68" s="12"/>
+      <c r="D68" s="19">
+        <v>12</v>
+      </c>
+      <c r="E68" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F68" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="G68" s="14"/>
+      <c r="H68" s="14"/>
+      <c r="I68" s="14"/>
       <c r="J68" s="3"/>
       <c r="K68" s="3"/>
       <c r="L68" s="3"/>
       <c r="M68" s="3"/>
       <c r="N68" s="3"/>
       <c r="O68" s="3"/>
-      <c r="P68" s="12"/>
-    </row>
-    <row r="69" spans="1:16">
+      <c r="P68" s="14"/>
+    </row>
+    <row r="69" customFormat="1" spans="1:16">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
-      <c r="D69" s="17"/>
-      <c r="E69" s="12"/>
-      <c r="F69" s="12"/>
-      <c r="G69" s="12"/>
-      <c r="H69" s="12"/>
-      <c r="I69" s="12"/>
+      <c r="D69" s="19">
+        <v>13</v>
+      </c>
+      <c r="E69" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F69" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="G69" s="14"/>
+      <c r="H69" s="14"/>
+      <c r="I69" s="14"/>
       <c r="J69" s="3"/>
       <c r="K69" s="3"/>
       <c r="L69" s="3"/>
       <c r="M69" s="3"/>
       <c r="N69" s="3"/>
       <c r="O69" s="3"/>
-      <c r="P69" s="12"/>
+      <c r="P69" s="14"/>
     </row>
     <row r="70" s="1" customFormat="1" spans="1:16">
-      <c r="A70" s="12"/>
-      <c r="B70" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="C70" s="18" t="s">
+      <c r="A70" s="14"/>
+      <c r="B70" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="D70" s="18"/>
-      <c r="E70" s="18"/>
-      <c r="F70" s="12"/>
-      <c r="G70" s="18"/>
-      <c r="H70" s="18"/>
-      <c r="I70" s="18"/>
-      <c r="J70" s="18"/>
-      <c r="K70" s="18"/>
-      <c r="L70" s="18"/>
-      <c r="M70" s="18"/>
-      <c r="N70" s="18"/>
-      <c r="O70" s="18"/>
-      <c r="P70" s="18"/>
+      <c r="C70" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="D70" s="20"/>
+      <c r="E70" s="20"/>
+      <c r="F70" s="21"/>
+      <c r="G70" s="20"/>
+      <c r="H70" s="20"/>
+      <c r="I70" s="20"/>
+      <c r="J70" s="20"/>
+      <c r="K70" s="20"/>
+      <c r="L70" s="20"/>
+      <c r="M70" s="20"/>
+      <c r="N70" s="20"/>
+      <c r="O70" s="20"/>
+      <c r="P70" s="20"/>
     </row>
     <row r="71" spans="1:16">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
-      <c r="D71" s="17"/>
-      <c r="E71" s="12"/>
-      <c r="F71" s="12"/>
-      <c r="G71" s="12"/>
-      <c r="H71" s="12"/>
-      <c r="I71" s="12"/>
+      <c r="D71" s="19"/>
+      <c r="E71" s="14"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="14"/>
+      <c r="H71" s="14"/>
+      <c r="I71" s="14"/>
       <c r="J71" s="3"/>
       <c r="K71" s="3"/>
       <c r="L71" s="3"/>
       <c r="M71" s="3"/>
       <c r="N71" s="3"/>
       <c r="O71" s="3"/>
-      <c r="P71" s="12"/>
+      <c r="P71" s="14"/>
     </row>
     <row r="72" spans="1:16">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
-      <c r="D72" s="17"/>
-      <c r="E72" s="12"/>
-      <c r="F72" s="12"/>
-      <c r="G72" s="12"/>
-      <c r="H72" s="12"/>
-      <c r="I72" s="12"/>
+      <c r="D72" s="19"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="14"/>
+      <c r="H72" s="14"/>
+      <c r="I72" s="14"/>
       <c r="J72" s="3"/>
       <c r="K72" s="3"/>
       <c r="L72" s="3"/>
       <c r="M72" s="3"/>
       <c r="N72" s="3"/>
       <c r="O72" s="3"/>
-      <c r="P72" s="12"/>
+      <c r="P72" s="14"/>
     </row>
     <row r="73" s="1" customFormat="1" spans="1:16">
-      <c r="A73" s="12"/>
-      <c r="B73" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="C73" s="18" t="s">
+      <c r="A73" s="14"/>
+      <c r="B73" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="D73" s="18"/>
-      <c r="E73" s="18"/>
-      <c r="F73" s="18"/>
-      <c r="G73" s="18"/>
-      <c r="H73" s="18"/>
-      <c r="I73" s="18"/>
-      <c r="J73" s="18"/>
-      <c r="K73" s="18"/>
-      <c r="L73" s="18"/>
-      <c r="M73" s="18"/>
-      <c r="N73" s="18"/>
-      <c r="O73" s="18"/>
-      <c r="P73" s="18"/>
+      <c r="C73" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="D73" s="20"/>
+      <c r="E73" s="20"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="20"/>
+      <c r="H73" s="20"/>
+      <c r="I73" s="20"/>
+      <c r="J73" s="20"/>
+      <c r="K73" s="20"/>
+      <c r="L73" s="20"/>
+      <c r="M73" s="20"/>
+      <c r="N73" s="20"/>
+      <c r="O73" s="20"/>
+      <c r="P73" s="20"/>
     </row>
     <row r="74" spans="1:16">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
-      <c r="D74" s="17"/>
-      <c r="E74" s="12"/>
-      <c r="F74" s="12"/>
-      <c r="G74" s="12"/>
-      <c r="H74" s="12"/>
-      <c r="I74" s="12"/>
+      <c r="D74" s="19"/>
+      <c r="E74" s="14"/>
+      <c r="F74" s="14"/>
+      <c r="G74" s="14"/>
+      <c r="H74" s="14"/>
+      <c r="I74" s="14"/>
       <c r="J74" s="3"/>
       <c r="K74" s="3"/>
       <c r="L74" s="3"/>
       <c r="M74" s="3"/>
       <c r="N74" s="3"/>
       <c r="O74" s="3"/>
-      <c r="P74" s="12"/>
+      <c r="P74" s="14"/>
     </row>
     <row r="75" spans="1:16">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
-      <c r="D75" s="17"/>
-      <c r="E75" s="12"/>
-      <c r="F75" s="12"/>
-      <c r="G75" s="12"/>
-      <c r="H75" s="12"/>
-      <c r="I75" s="12"/>
+      <c r="D75" s="19"/>
+      <c r="E75" s="14"/>
+      <c r="F75" s="14"/>
+      <c r="G75" s="14"/>
+      <c r="H75" s="14"/>
+      <c r="I75" s="14"/>
       <c r="J75" s="3"/>
       <c r="K75" s="3"/>
       <c r="L75" s="3"/>
       <c r="M75" s="3"/>
       <c r="N75" s="3"/>
       <c r="O75" s="3"/>
-      <c r="P75" s="12"/>
-    </row>
-    <row r="76" spans="1:16">
-      <c r="A76" s="3"/>
-      <c r="B76" s="3"/>
-      <c r="C76" s="3"/>
-      <c r="D76" s="3"/>
-      <c r="E76" s="3"/>
-      <c r="F76" s="18"/>
-      <c r="G76" s="3"/>
-      <c r="H76" s="3"/>
-      <c r="I76" s="3"/>
-      <c r="J76" s="3"/>
-      <c r="K76" s="3"/>
-      <c r="L76" s="3"/>
-      <c r="M76" s="3"/>
-      <c r="N76" s="3"/>
-      <c r="O76" s="3"/>
-      <c r="P76" s="3"/>
+      <c r="P75" s="14"/>
+    </row>
+    <row r="76" s="1" customFormat="1" spans="1:16">
+      <c r="A76" s="14"/>
+      <c r="B76" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C76" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="D76" s="20"/>
+      <c r="E76" s="20"/>
+      <c r="F76" s="20"/>
+      <c r="G76" s="20"/>
+      <c r="H76" s="20"/>
+      <c r="I76" s="20"/>
+      <c r="J76" s="20"/>
+      <c r="K76" s="20"/>
+      <c r="L76" s="20"/>
+      <c r="M76" s="20"/>
+      <c r="N76" s="20"/>
+      <c r="O76" s="20"/>
+      <c r="P76" s="20"/>
     </row>
     <row r="77" spans="1:16">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
-      <c r="F77" s="12"/>
-      <c r="G77" s="3"/>
-      <c r="H77" s="3"/>
-      <c r="I77" s="3"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="14"/>
+      <c r="F77" s="14"/>
+      <c r="G77" s="14"/>
+      <c r="H77" s="14"/>
+      <c r="I77" s="14"/>
       <c r="J77" s="3"/>
       <c r="K77" s="3"/>
       <c r="L77" s="3"/>
       <c r="M77" s="3"/>
       <c r="N77" s="3"/>
       <c r="O77" s="3"/>
-      <c r="P77" s="3"/>
+      <c r="P77" s="14"/>
     </row>
     <row r="78" spans="1:16">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
-      <c r="F78" s="12"/>
-      <c r="G78" s="3"/>
-      <c r="H78" s="3"/>
-      <c r="I78" s="3"/>
+      <c r="D78" s="19"/>
+      <c r="E78" s="14"/>
+      <c r="F78" s="14"/>
+      <c r="G78" s="14"/>
+      <c r="H78" s="14"/>
+      <c r="I78" s="14"/>
       <c r="J78" s="3"/>
       <c r="K78" s="3"/>
       <c r="L78" s="3"/>
       <c r="M78" s="3"/>
       <c r="N78" s="3"/>
       <c r="O78" s="3"/>
-      <c r="P78" s="3"/>
+      <c r="P78" s="14"/>
     </row>
     <row r="79" spans="1:16">
       <c r="A79" s="3"/>
@@ -3219,7 +3246,7 @@
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
-      <c r="F79" s="18"/>
+      <c r="F79" s="20"/>
       <c r="G79" s="3"/>
       <c r="H79" s="3"/>
       <c r="I79" s="3"/>
@@ -3237,7 +3264,7 @@
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
-      <c r="F80" s="12"/>
+      <c r="F80" s="14"/>
       <c r="G80" s="3"/>
       <c r="H80" s="3"/>
       <c r="I80" s="3"/>
@@ -3255,7 +3282,7 @@
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
-      <c r="F81" s="12"/>
+      <c r="F81" s="14"/>
       <c r="G81" s="3"/>
       <c r="H81" s="3"/>
       <c r="I81" s="3"/>
@@ -3273,7 +3300,7 @@
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
-      <c r="F82" s="3"/>
+      <c r="F82" s="20"/>
       <c r="G82" s="3"/>
       <c r="H82" s="3"/>
       <c r="I82" s="3"/>
@@ -3291,7 +3318,7 @@
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
-      <c r="F83" s="3"/>
+      <c r="F83" s="14"/>
       <c r="G83" s="3"/>
       <c r="H83" s="3"/>
       <c r="I83" s="3"/>
@@ -3309,7 +3336,7 @@
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
-      <c r="F84" s="3"/>
+      <c r="F84" s="14"/>
       <c r="G84" s="3"/>
       <c r="H84" s="3"/>
       <c r="I84" s="3"/>
@@ -3357,40 +3384,85 @@
       <c r="O86" s="3"/>
       <c r="P86" s="3"/>
     </row>
-    <row r="87" spans="3:6">
+    <row r="87" spans="1:16">
+      <c r="A87" s="3"/>
+      <c r="B87" s="3"/>
       <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
       <c r="F87" s="3"/>
-    </row>
-    <row r="88" spans="3:6">
+      <c r="G87" s="3"/>
+      <c r="H87" s="3"/>
+      <c r="I87" s="3"/>
+      <c r="J87" s="3"/>
+      <c r="K87" s="3"/>
+      <c r="L87" s="3"/>
+      <c r="M87" s="3"/>
+      <c r="N87" s="3"/>
+      <c r="O87" s="3"/>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="1:16">
+      <c r="A88" s="3"/>
+      <c r="B88" s="3"/>
       <c r="C88" s="3"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
       <c r="F88" s="3"/>
-    </row>
-    <row r="89" spans="3:6">
+      <c r="G88" s="3"/>
+      <c r="H88" s="3"/>
+      <c r="I88" s="3"/>
+      <c r="J88" s="3"/>
+      <c r="K88" s="3"/>
+      <c r="L88" s="3"/>
+      <c r="M88" s="3"/>
+      <c r="N88" s="3"/>
+      <c r="O88" s="3"/>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="1:16">
+      <c r="A89" s="3"/>
+      <c r="B89" s="3"/>
       <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
       <c r="F89" s="3"/>
-    </row>
-    <row r="90" spans="3:6">
+      <c r="G89" s="3"/>
+      <c r="H89" s="3"/>
+      <c r="I89" s="3"/>
+      <c r="J89" s="3"/>
+      <c r="K89" s="3"/>
+      <c r="L89" s="3"/>
+      <c r="M89" s="3"/>
+      <c r="N89" s="3"/>
+      <c r="O89" s="3"/>
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="1:16">
       <c r="C90" s="3"/>
       <c r="F90" s="3"/>
     </row>
-    <row r="91" spans="3:6">
+    <row r="91" spans="1:16">
       <c r="C91" s="3"/>
       <c r="F91" s="3"/>
     </row>
-    <row r="92" spans="3:6">
+    <row r="92" spans="1:16">
       <c r="C92" s="3"/>
       <c r="F92" s="3"/>
     </row>
-    <row r="93" spans="3:3">
+    <row r="93" spans="1:16">
       <c r="C93" s="3"/>
-    </row>
-    <row r="94" spans="3:3">
+      <c r="F93" s="3"/>
+    </row>
+    <row r="94" spans="1:16">
       <c r="C94" s="3"/>
-    </row>
-    <row r="95" spans="3:3">
+      <c r="F94" s="3"/>
+    </row>
+    <row r="95" spans="1:16">
       <c r="C95" s="3"/>
-    </row>
-    <row r="96" spans="3:3">
+      <c r="F95" s="3"/>
+    </row>
+    <row r="96" spans="1:16">
       <c r="C96" s="3"/>
     </row>
     <row r="97" spans="3:3">
@@ -5883,30 +5955,39 @@
     <row r="926" spans="3:3">
       <c r="C926" s="3"/>
     </row>
+    <row r="927" spans="3:3">
+      <c r="C927" s="3"/>
+    </row>
+    <row r="928" spans="3:3">
+      <c r="C928" s="3"/>
+    </row>
+    <row r="929" spans="3:3">
+      <c r="C929" s="3"/>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatRows="0" insertRows="0" insertHyperlinks="0" deleteRows="0" sort="0" autoFilter="0"/>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B10:P75" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B10:P78" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="F1:P6"/>
   </mergeCells>
   <dataValidations count="6">
-    <dataValidation allowBlank="1" showInputMessage="1" sqref="C11 C14 C17 C20 C23 C26 C29 C32 C35 C55 C67 C70 C73"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Object Code value" error="The Object code value shall be:&#10;VARIABLE&#10;RECORD&#10;ARRAY" sqref="C12:C13 C15:C16 C18:C19 C21:C22 C24:C25 C27:C28 C30:C31 C33:C34 C36:C54 C56:C66 C68:C69 C71:C72 C74:C86">
+    <dataValidation allowBlank="1" showInputMessage="1" sqref="C11 C14 C17 C20 C23 C26 C29 C32 C35 C55 C70 C73 C76"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Object Code value" error="The Object code value shall be:&#10;VARIABLE&#10;RECORD&#10;ARRAY" sqref="C69 C12:C13 C15:C16 C18:C19 C21:C22 C24:C25 C27:C28 C30:C31 C33:C34 C36:C54 C56:C68 C71:C72 C74:C75 C77:C89">
       <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C87:C926">
-      <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Category" error="The value for the entry category shall be &#10;M : (mandatory)&#10;O : (optional) &#10;C : (conditional)" sqref="J12:J13 J15:J16 J18:J19 J21:J22 J24:J25 J27:J28 J30:J31 J33:J34 J36:J54 J56:J66 J68:J69 J71:J72 J74:J86">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Category" error="The value for the entry category shall be &#10;M : (mandatory)&#10;O : (optional) &#10;C : (conditional)" sqref="J69 J12:J13 J15:J16 J18:J19 J21:J22 J24:J25 J27:J28 J30:J31 J33:J34 J36:J54 J56:J68 J71:J72 J74:J75 J77:J89">
       <formula1>"M,O,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Backup/Setting Flag" error="The entry flag shall be&#10;B : (Backup)&#10;S : (Setting)" sqref="K12:K13 K15:K16 K18:K19 K21:K22 K24:K25 K27:K28 K30:K31 K33:K34 K36:K54 K56:K66 K68:K69 K71:K72 K74:K86">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Backup/Setting Flag" error="The entry flag shall be&#10;B : (Backup)&#10;S : (Setting)" sqref="K69 K12:K13 K15:K16 K18:K19 K21:K22 K24:K25 K27:K28 K30:K31 K33:K34 K36:K54 K56:K68 K71:K72 K74:K75 K77:K89">
       <formula1>"B,S"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M12:O13 M18:O19 M24:O25 M30:O31 M68:O69 M74:O75 M15:O16 M21:O22 M27:O28 M33:O34 M71:O72 M36:O54 M56:O66">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M69:O69 M12:O13 M18:O19 M24:O25 M30:O31 M74:O75 M15:O16 M21:O22 M27:O28 M33:O34 M71:O72 M77:O78 M36:O54 M56:O68">
       <formula1>"rx,tx"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C90:C929">
+      <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.236220472440945" right="0.236220472440945" top="0.748031496062992" bottom="0.748031496062992" header="0.31496062992126" footer="0.31496062992126"/>
